--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$382</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$386</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$258</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="426">
   <si>
     <t>Barcode</t>
   </si>
@@ -359,6 +359,12 @@
     <t>Susu Frisian Flag Pak</t>
   </si>
   <si>
+    <t>Extrajoss</t>
+  </si>
+  <si>
+    <t>Extrajoss Box</t>
+  </si>
+  <si>
     <t>Kerupuk Sumber Sari</t>
   </si>
   <si>
@@ -632,6 +638,9 @@
     <t>Sampoerna Kretek</t>
   </si>
   <si>
+    <t>Sampoerna Kretek Bungkus</t>
+  </si>
+  <si>
     <t>Djarum Coklat</t>
   </si>
   <si>
@@ -698,6 +707,9 @@
     <t>Sampoerna A Mild Bungkus</t>
   </si>
   <si>
+    <t>Sampoerna Prima Bungkus</t>
+  </si>
+  <si>
     <t>Esse Change Bungkus</t>
   </si>
   <si>
@@ -1206,6 +1218,9 @@
   </si>
   <si>
     <t>amplop</t>
+  </si>
+  <si>
+    <t>Agar Swallow</t>
   </si>
   <si>
     <t>Djarum Coklat Bungkus SLOP</t>
@@ -1665,7 +1680,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A382" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A386" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -3834,10 +3849,10 @@
         <v>114</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>115</v>
+        <v>11</v>
       </c>
       <c r="D104" s="4">
-        <v>6000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
@@ -3852,20 +3867,20 @@
         <v>104</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>115</v>
+        <v>11</v>
       </c>
       <c r="D105" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E105" s="7"/>
-      <c r="F105" s="7"/>
-      <c r="G105" s="7"/>
-      <c r="H105" s="7"/>
-      <c r="I105" s="7"/>
-      <c r="J105" s="7"/>
+        <v>16000.0</v>
+      </c>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6"/>
+      <c r="J105" s="6"/>
     </row>
     <row r="106">
       <c r="A106" s="4">
@@ -3873,20 +3888,20 @@
         <v>105</v>
       </c>
       <c r="B106" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C106" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C106" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="D106" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="E106" s="7"/>
-      <c r="F106" s="7"/>
-      <c r="G106" s="7"/>
-      <c r="H106" s="7"/>
-      <c r="I106" s="7"/>
-      <c r="J106" s="7"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E106" s="6"/>
+      <c r="F106" s="6"/>
+      <c r="G106" s="6"/>
+      <c r="H106" s="6"/>
+      <c r="I106" s="6"/>
+      <c r="J106" s="6"/>
     </row>
     <row r="107">
       <c r="A107" s="4">
@@ -3897,7 +3912,7 @@
         <v>118</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D107" s="4">
         <v>1000.0</v>
@@ -3918,7 +3933,7 @@
         <v>119</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D108" s="4">
         <v>10000.0</v>
@@ -3939,7 +3954,7 @@
         <v>120</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D109" s="4">
         <v>1000.0</v>
@@ -3960,7 +3975,7 @@
         <v>121</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D110" s="4">
         <v>10000.0</v>
@@ -3981,10 +3996,10 @@
         <v>122</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D111" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E111" s="7"/>
       <c r="F111" s="7"/>
@@ -4002,17 +4017,17 @@
         <v>123</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D112" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E112" s="6"/>
-      <c r="F112" s="6"/>
-      <c r="G112" s="6"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6"/>
-      <c r="J112" s="6"/>
+        <v>10000.0</v>
+      </c>
+      <c r="E112" s="7"/>
+      <c r="F112" s="7"/>
+      <c r="G112" s="7"/>
+      <c r="H112" s="7"/>
+      <c r="I112" s="7"/>
+      <c r="J112" s="7"/>
     </row>
     <row r="113">
       <c r="A113" s="4">
@@ -4023,17 +4038,17 @@
         <v>124</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D113" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-      <c r="G113" s="6"/>
-      <c r="H113" s="6"/>
-      <c r="I113" s="6"/>
-      <c r="J113" s="6"/>
+        <v>500.0</v>
+      </c>
+      <c r="E113" s="7"/>
+      <c r="F113" s="7"/>
+      <c r="G113" s="7"/>
+      <c r="H113" s="7"/>
+      <c r="I113" s="7"/>
+      <c r="J113" s="7"/>
     </row>
     <row r="114">
       <c r="A114" s="4">
@@ -4044,10 +4059,10 @@
         <v>125</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D114" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
@@ -4065,10 +4080,10 @@
         <v>126</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D115" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
@@ -4086,10 +4101,10 @@
         <v>127</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D116" s="4">
-        <v>500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E116" s="6"/>
       <c r="F116" s="6"/>
@@ -4107,10 +4122,10 @@
         <v>128</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D117" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
@@ -4128,10 +4143,10 @@
         <v>129</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D118" s="4">
-        <v>10000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E118" s="6"/>
       <c r="F118" s="6"/>
@@ -4149,10 +4164,10 @@
         <v>130</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D119" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E119" s="6"/>
       <c r="F119" s="6"/>
@@ -4170,10 +4185,10 @@
         <v>131</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D120" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E120" s="6"/>
       <c r="F120" s="6"/>
@@ -4191,10 +4206,10 @@
         <v>132</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D121" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
@@ -4212,17 +4227,13 @@
         <v>133</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D122" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E122" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F122" s="4">
-        <v>1000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E122" s="6"/>
+      <c r="F122" s="6"/>
       <c r="G122" s="6"/>
       <c r="H122" s="6"/>
       <c r="I122" s="6"/>
@@ -4237,10 +4248,10 @@
         <v>134</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D123" s="4">
-        <v>6500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
@@ -4258,13 +4269,17 @@
         <v>135</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D124" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="E124" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F124" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E124" s="6"/>
-      <c r="F124" s="6"/>
       <c r="G124" s="6"/>
       <c r="H124" s="6"/>
       <c r="I124" s="6"/>
@@ -4279,10 +4294,10 @@
         <v>136</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D125" s="4">
-        <v>10000.0</v>
+        <v>6500.0</v>
       </c>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
@@ -4300,17 +4315,13 @@
         <v>137</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D126" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E126" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F126" s="4">
-        <v>13000.0</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E126" s="6"/>
+      <c r="F126" s="6"/>
       <c r="G126" s="6"/>
       <c r="H126" s="6"/>
       <c r="I126" s="6"/>
@@ -4325,10 +4336,10 @@
         <v>138</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D127" s="4">
-        <v>23000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
@@ -4346,17 +4357,21 @@
         <v>139</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D128" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E128" s="7"/>
-      <c r="F128" s="7"/>
-      <c r="G128" s="7"/>
-      <c r="H128" s="7"/>
-      <c r="I128" s="7"/>
-      <c r="J128" s="7"/>
+      <c r="E128" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F128" s="4">
+        <v>13000.0</v>
+      </c>
+      <c r="G128" s="6"/>
+      <c r="H128" s="6"/>
+      <c r="I128" s="6"/>
+      <c r="J128" s="6"/>
     </row>
     <row r="129">
       <c r="A129" s="4">
@@ -4367,10 +4382,10 @@
         <v>140</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D129" s="4">
-        <v>26000.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
@@ -4388,17 +4403,17 @@
         <v>141</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D130" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E130" s="6"/>
-      <c r="F130" s="6"/>
-      <c r="G130" s="6"/>
-      <c r="H130" s="6"/>
-      <c r="I130" s="6"/>
-      <c r="J130" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E130" s="7"/>
+      <c r="F130" s="7"/>
+      <c r="G130" s="7"/>
+      <c r="H130" s="7"/>
+      <c r="I130" s="7"/>
+      <c r="J130" s="7"/>
     </row>
     <row r="131">
       <c r="A131" s="4">
@@ -4409,10 +4424,10 @@
         <v>142</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D131" s="4">
-        <v>21000.0</v>
+        <v>26000.0</v>
       </c>
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
@@ -4430,10 +4445,10 @@
         <v>143</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D132" s="4">
-        <v>2000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E132" s="6"/>
       <c r="F132" s="6"/>
@@ -4451,10 +4466,10 @@
         <v>144</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D133" s="4">
-        <v>36500.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
@@ -4472,10 +4487,10 @@
         <v>145</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D134" s="4">
-        <v>13000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E134" s="6"/>
       <c r="F134" s="6"/>
@@ -4493,10 +4508,10 @@
         <v>146</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D135" s="4">
-        <v>500.0</v>
+        <v>36500.0</v>
       </c>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
@@ -4514,10 +4529,10 @@
         <v>147</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D136" s="4">
-        <v>13500.0</v>
+        <v>13000.0</v>
       </c>
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
@@ -4535,10 +4550,10 @@
         <v>148</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D137" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
@@ -4556,10 +4571,10 @@
         <v>149</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D138" s="4">
-        <v>160000.0</v>
+        <v>13500.0</v>
       </c>
       <c r="E138" s="6"/>
       <c r="F138" s="6"/>
@@ -4577,17 +4592,13 @@
         <v>150</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D139" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E139" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F139" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E139" s="6"/>
+      <c r="F139" s="6"/>
       <c r="G139" s="6"/>
       <c r="H139" s="6"/>
       <c r="I139" s="6"/>
@@ -4602,17 +4613,17 @@
         <v>151</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D140" s="4">
-        <v>65000.0</v>
-      </c>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7"/>
-      <c r="G140" s="7"/>
-      <c r="H140" s="7"/>
-      <c r="I140" s="7"/>
-      <c r="J140" s="7"/>
+        <v>160000.0</v>
+      </c>
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
+      <c r="G140" s="6"/>
+      <c r="H140" s="6"/>
+      <c r="I140" s="6"/>
+      <c r="J140" s="6"/>
     </row>
     <row r="141">
       <c r="A141" s="4">
@@ -4623,17 +4634,21 @@
         <v>152</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D141" s="4">
-        <v>4500.0</v>
-      </c>
-      <c r="E141" s="7"/>
-      <c r="F141" s="7"/>
-      <c r="G141" s="7"/>
-      <c r="H141" s="7"/>
-      <c r="I141" s="7"/>
-      <c r="J141" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E141" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F141" s="4">
+        <v>9000.0</v>
+      </c>
+      <c r="G141" s="6"/>
+      <c r="H141" s="6"/>
+      <c r="I141" s="6"/>
+      <c r="J141" s="6"/>
     </row>
     <row r="142">
       <c r="A142" s="4">
@@ -4644,17 +4659,17 @@
         <v>153</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D142" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E142" s="6"/>
-      <c r="F142" s="6"/>
-      <c r="G142" s="6"/>
-      <c r="H142" s="6"/>
-      <c r="I142" s="6"/>
-      <c r="J142" s="6"/>
+        <v>65000.0</v>
+      </c>
+      <c r="E142" s="7"/>
+      <c r="F142" s="7"/>
+      <c r="G142" s="7"/>
+      <c r="H142" s="7"/>
+      <c r="I142" s="7"/>
+      <c r="J142" s="7"/>
     </row>
     <row r="143">
       <c r="A143" s="4">
@@ -4665,17 +4680,17 @@
         <v>154</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D143" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E143" s="6"/>
-      <c r="F143" s="6"/>
-      <c r="G143" s="6"/>
-      <c r="H143" s="6"/>
-      <c r="I143" s="6"/>
-      <c r="J143" s="6"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E143" s="7"/>
+      <c r="F143" s="7"/>
+      <c r="G143" s="7"/>
+      <c r="H143" s="7"/>
+      <c r="I143" s="7"/>
+      <c r="J143" s="7"/>
     </row>
     <row r="144">
       <c r="A144" s="4">
@@ -4686,7 +4701,7 @@
         <v>155</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D144" s="4">
         <v>2000.0</v>
@@ -4707,7 +4722,7 @@
         <v>156</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D145" s="4">
         <v>17000.0</v>
@@ -4728,7 +4743,7 @@
         <v>157</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D146" s="4">
         <v>2000.0</v>
@@ -4749,7 +4764,7 @@
         <v>158</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D147" s="4">
         <v>17000.0</v>
@@ -4770,7 +4785,7 @@
         <v>159</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D148" s="4">
         <v>2000.0</v>
@@ -4791,7 +4806,7 @@
         <v>160</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D149" s="4">
         <v>17000.0</v>
@@ -4812,7 +4827,7 @@
         <v>161</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D150" s="4">
         <v>2000.0</v>
@@ -4833,7 +4848,7 @@
         <v>162</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D151" s="4">
         <v>17000.0</v>
@@ -4854,10 +4869,10 @@
         <v>163</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D152" s="4">
-        <v>5000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
@@ -4875,10 +4890,10 @@
         <v>164</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D153" s="4">
-        <v>10000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E153" s="6"/>
       <c r="F153" s="6"/>
@@ -4896,10 +4911,10 @@
         <v>165</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D154" s="4">
-        <v>18000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E154" s="6"/>
       <c r="F154" s="6"/>
@@ -4917,10 +4932,10 @@
         <v>166</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D155" s="4">
-        <v>4500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E155" s="6"/>
       <c r="F155" s="6"/>
@@ -4938,10 +4953,10 @@
         <v>167</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D156" s="4">
-        <v>9000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E156" s="6"/>
       <c r="F156" s="6"/>
@@ -4959,17 +4974,17 @@
         <v>168</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D157" s="4">
-        <v>18000.0</v>
-      </c>
-      <c r="E157" s="4"/>
-      <c r="F157" s="4"/>
-      <c r="G157" s="7"/>
-      <c r="H157" s="7"/>
-      <c r="I157" s="7"/>
-      <c r="J157" s="7"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E157" s="6"/>
+      <c r="F157" s="6"/>
+      <c r="G157" s="6"/>
+      <c r="H157" s="6"/>
+      <c r="I157" s="6"/>
+      <c r="J157" s="6"/>
     </row>
     <row r="158">
       <c r="A158" s="4">
@@ -4980,21 +4995,17 @@
         <v>169</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D158" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E158" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F158" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="G158" s="7"/>
-      <c r="H158" s="7"/>
-      <c r="I158" s="7"/>
-      <c r="J158" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E158" s="6"/>
+      <c r="F158" s="6"/>
+      <c r="G158" s="6"/>
+      <c r="H158" s="6"/>
+      <c r="I158" s="6"/>
+      <c r="J158" s="6"/>
     </row>
     <row r="159">
       <c r="A159" s="4">
@@ -5005,17 +5016,13 @@
         <v>170</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D159" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E159" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F159" s="4">
-        <v>12000.0</v>
-      </c>
+        <v>18000.0</v>
+      </c>
+      <c r="E159" s="4"/>
+      <c r="F159" s="4"/>
       <c r="G159" s="7"/>
       <c r="H159" s="7"/>
       <c r="I159" s="7"/>
@@ -5030,16 +5037,16 @@
         <v>171</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D160" s="4">
-        <v>2500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E160" s="4">
         <v>4.0</v>
       </c>
       <c r="F160" s="4">
-        <v>8500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="G160" s="7"/>
       <c r="H160" s="7"/>
@@ -5055,13 +5062,17 @@
         <v>172</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D161" s="4">
-        <v>26000.0</v>
-      </c>
-      <c r="E161" s="7"/>
-      <c r="F161" s="7"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E161" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F161" s="4">
+        <v>12000.0</v>
+      </c>
       <c r="G161" s="7"/>
       <c r="H161" s="7"/>
       <c r="I161" s="7"/>
@@ -5076,16 +5087,16 @@
         <v>173</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D162" s="4">
-        <v>4000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E162" s="4">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F162" s="4">
-        <v>17500.0</v>
+        <v>8500.0</v>
       </c>
       <c r="G162" s="7"/>
       <c r="H162" s="7"/>
@@ -5101,10 +5112,10 @@
         <v>174</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D163" s="4">
-        <v>175000.0</v>
+        <v>26000.0</v>
       </c>
       <c r="E163" s="7"/>
       <c r="F163" s="7"/>
@@ -5122,13 +5133,17 @@
         <v>175</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D164" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E164" s="7"/>
-      <c r="F164" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E164" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F164" s="4">
+        <v>17500.0</v>
+      </c>
       <c r="G164" s="7"/>
       <c r="H164" s="7"/>
       <c r="I164" s="7"/>
@@ -5143,17 +5158,13 @@
         <v>176</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D165" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="E165" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F165" s="4">
-        <v>22000.0</v>
-      </c>
+        <v>175000.0</v>
+      </c>
+      <c r="E165" s="7"/>
+      <c r="F165" s="7"/>
       <c r="G165" s="7"/>
       <c r="H165" s="7"/>
       <c r="I165" s="7"/>
@@ -5168,7 +5179,7 @@
         <v>177</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D166" s="4">
         <v>21000.0</v>
@@ -5189,13 +5200,17 @@
         <v>178</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D167" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E167" s="7"/>
-      <c r="F167" s="7"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E167" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F167" s="4">
+        <v>22000.0</v>
+      </c>
       <c r="G167" s="7"/>
       <c r="H167" s="7"/>
       <c r="I167" s="7"/>
@@ -5210,10 +5225,10 @@
         <v>179</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D168" s="4">
-        <v>245000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E168" s="7"/>
       <c r="F168" s="7"/>
@@ -5231,10 +5246,10 @@
         <v>180</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D169" s="4">
-        <v>42000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E169" s="7"/>
       <c r="F169" s="7"/>
@@ -5252,10 +5267,10 @@
         <v>181</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D170" s="4">
-        <v>44000.0</v>
+        <v>245000.0</v>
       </c>
       <c r="E170" s="7"/>
       <c r="F170" s="7"/>
@@ -5273,10 +5288,10 @@
         <v>182</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D171" s="4">
-        <v>255000.0</v>
+        <v>42000.0</v>
       </c>
       <c r="E171" s="7"/>
       <c r="F171" s="7"/>
@@ -5294,10 +5309,10 @@
         <v>183</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D172" s="4">
-        <v>21000.0</v>
+        <v>44000.0</v>
       </c>
       <c r="E172" s="7"/>
       <c r="F172" s="7"/>
@@ -5315,10 +5330,10 @@
         <v>184</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D173" s="4">
-        <v>42000.0</v>
+        <v>255000.0</v>
       </c>
       <c r="E173" s="7"/>
       <c r="F173" s="7"/>
@@ -5336,17 +5351,17 @@
         <v>185</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D174" s="4">
-        <v>14500.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E174" s="7"/>
       <c r="F174" s="7"/>
-      <c r="G174" s="4"/>
-      <c r="H174" s="4"/>
-      <c r="I174" s="4"/>
-      <c r="J174" s="4"/>
+      <c r="G174" s="7"/>
+      <c r="H174" s="7"/>
+      <c r="I174" s="7"/>
+      <c r="J174" s="7"/>
     </row>
     <row r="175">
       <c r="A175" s="4">
@@ -5357,25 +5372,17 @@
         <v>186</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>187</v>
+        <v>117</v>
       </c>
       <c r="D175" s="4">
-        <v>2000.0</v>
+        <v>42000.0</v>
       </c>
       <c r="E175" s="7"/>
       <c r="F175" s="7"/>
-      <c r="G175" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H175" s="4">
-        <v>5500.0</v>
-      </c>
-      <c r="I175" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J175" s="4">
-        <v>10000.0</v>
-      </c>
+      <c r="G175" s="7"/>
+      <c r="H175" s="7"/>
+      <c r="I175" s="7"/>
+      <c r="J175" s="7"/>
     </row>
     <row r="176">
       <c r="A176" s="4">
@@ -5383,20 +5390,20 @@
         <v>175</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>187</v>
+        <v>117</v>
       </c>
       <c r="D176" s="4">
-        <v>10000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E176" s="7"/>
       <c r="F176" s="7"/>
-      <c r="G176" s="7"/>
-      <c r="H176" s="7"/>
-      <c r="I176" s="7"/>
-      <c r="J176" s="7"/>
+      <c r="G176" s="4"/>
+      <c r="H176" s="4"/>
+      <c r="I176" s="4"/>
+      <c r="J176" s="4"/>
     </row>
     <row r="177">
       <c r="A177" s="4">
@@ -5404,10 +5411,10 @@
         <v>176</v>
       </c>
       <c r="B177" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C177" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="D177" s="4">
         <v>2000.0</v>
@@ -5436,7 +5443,7 @@
         <v>190</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D178" s="4">
         <v>10000.0</v>
@@ -5457,7 +5464,7 @@
         <v>191</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D179" s="4">
         <v>2000.0</v>
@@ -5486,7 +5493,7 @@
         <v>192</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D180" s="4">
         <v>10000.0</v>
@@ -5507,7 +5514,7 @@
         <v>193</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D181" s="4">
         <v>2000.0</v>
@@ -5518,13 +5525,13 @@
         <v>6.0</v>
       </c>
       <c r="H181" s="4">
-        <v>6000.0</v>
+        <v>5500.0</v>
       </c>
       <c r="I181" s="4">
         <v>12.0</v>
       </c>
       <c r="J181" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
     </row>
     <row r="182">
@@ -5536,10 +5543,10 @@
         <v>194</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D182" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E182" s="7"/>
       <c r="F182" s="7"/>
@@ -5557,7 +5564,7 @@
         <v>195</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D183" s="4">
         <v>2000.0</v>
@@ -5586,7 +5593,7 @@
         <v>196</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D184" s="4">
         <v>11000.0</v>
@@ -5607,7 +5614,7 @@
         <v>197</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D185" s="4">
         <v>2000.0</v>
@@ -5618,13 +5625,13 @@
         <v>6.0</v>
       </c>
       <c r="H185" s="4">
-        <v>8000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="I185" s="4">
         <v>12.0</v>
       </c>
       <c r="J185" s="4">
-        <v>15000.0</v>
+        <v>11000.0</v>
       </c>
     </row>
     <row r="186">
@@ -5636,10 +5643,10 @@
         <v>198</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D186" s="4">
-        <v>15000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
@@ -5657,17 +5664,25 @@
         <v>199</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D187" s="4">
-        <v>15000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E187" s="7"/>
       <c r="F187" s="7"/>
-      <c r="G187" s="7"/>
-      <c r="H187" s="7"/>
-      <c r="I187" s="7"/>
-      <c r="J187" s="7"/>
+      <c r="G187" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H187" s="4">
+        <v>8000.0</v>
+      </c>
+      <c r="I187" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J187" s="4">
+        <v>15000.0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4">
@@ -5678,29 +5693,17 @@
         <v>200</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D188" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E188" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F188" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="G188" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H188" s="4">
-        <v>8500.0</v>
-      </c>
-      <c r="I188" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J188" s="4">
-        <v>16000.0</v>
-      </c>
+        <v>15000.0</v>
+      </c>
+      <c r="E188" s="7"/>
+      <c r="F188" s="7"/>
+      <c r="G188" s="7"/>
+      <c r="H188" s="7"/>
+      <c r="I188" s="7"/>
+      <c r="J188" s="7"/>
     </row>
     <row r="189">
       <c r="A189" s="4">
@@ -5711,10 +5714,10 @@
         <v>201</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D189" s="4">
-        <v>16000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E189" s="7"/>
       <c r="F189" s="7"/>
@@ -5732,24 +5735,28 @@
         <v>202</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D190" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E190" s="7"/>
-      <c r="F190" s="7"/>
+      <c r="E190" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F190" s="4">
+        <v>5000.0</v>
+      </c>
       <c r="G190" s="4">
         <v>6.0</v>
       </c>
       <c r="H190" s="4">
-        <v>9000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="I190" s="4">
         <v>12.0</v>
       </c>
       <c r="J190" s="4">
-        <v>17000.0</v>
+        <v>16000.0</v>
       </c>
     </row>
     <row r="191">
@@ -5761,10 +5768,10 @@
         <v>203</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D191" s="4">
-        <v>17000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E191" s="7"/>
       <c r="F191" s="7"/>
@@ -5782,7 +5789,7 @@
         <v>204</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D192" s="4">
         <v>2000.0</v>
@@ -5807,11 +5814,11 @@
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
-      <c r="B193" s="5">
-        <v>8.999909085114E12</v>
+      <c r="B193" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D193" s="4">
         <v>17000.0</v>
@@ -5829,31 +5836,27 @@
         <v>193</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D194" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E194" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F194" s="4">
-        <v>5000.0</v>
-      </c>
+      <c r="E194" s="7"/>
+      <c r="F194" s="7"/>
       <c r="G194" s="4">
         <v>6.0</v>
       </c>
       <c r="H194" s="4">
-        <v>9500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="I194" s="4">
         <v>12.0</v>
       </c>
       <c r="J194" s="4">
-        <v>18000.0</v>
+        <v>17000.0</v>
       </c>
     </row>
     <row r="195">
@@ -5862,13 +5865,13 @@
         <v>194</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D195" s="4">
-        <v>18000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E195" s="7"/>
       <c r="F195" s="7"/>
@@ -5883,27 +5886,31 @@
         <v>195</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D196" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E196" s="7"/>
-      <c r="F196" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E196" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F196" s="4">
+        <v>5000.0</v>
+      </c>
       <c r="G196" s="4">
         <v>6.0</v>
       </c>
       <c r="H196" s="4">
-        <v>14500.0</v>
+        <v>9500.0</v>
       </c>
       <c r="I196" s="4">
         <v>12.0</v>
       </c>
       <c r="J196" s="4">
-        <v>28000.0</v>
+        <v>18000.0</v>
       </c>
     </row>
     <row r="197">
@@ -5912,13 +5919,13 @@
         <v>196</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D197" s="4">
-        <v>28000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E197" s="7"/>
       <c r="F197" s="7"/>
@@ -5933,10 +5940,10 @@
         <v>197</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D198" s="4">
         <v>2500.0</v>
@@ -5947,13 +5954,13 @@
         <v>6.0</v>
       </c>
       <c r="H198" s="4">
-        <v>10500.0</v>
+        <v>14500.0</v>
       </c>
       <c r="I198" s="4">
         <v>12.0</v>
       </c>
       <c r="J198" s="4">
-        <v>20000.0</v>
+        <v>28000.0</v>
       </c>
     </row>
     <row r="199">
@@ -5962,13 +5969,13 @@
         <v>198</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D199" s="4">
-        <v>20000.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E199" s="7"/>
       <c r="F199" s="7"/>
@@ -5983,10 +5990,10 @@
         <v>199</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D200" s="4">
         <v>2500.0</v>
@@ -5997,13 +6004,13 @@
         <v>6.0</v>
       </c>
       <c r="H200" s="4">
-        <v>13000.0</v>
+        <v>10500.0</v>
       </c>
       <c r="I200" s="4">
         <v>12.0</v>
       </c>
       <c r="J200" s="4">
-        <v>25000.0</v>
+        <v>20000.0</v>
       </c>
     </row>
     <row r="201">
@@ -6012,13 +6019,13 @@
         <v>200</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D201" s="4">
-        <v>25000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="E201" s="7"/>
       <c r="F201" s="7"/>
@@ -6033,10 +6040,10 @@
         <v>201</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D202" s="4">
         <v>2500.0</v>
@@ -6047,13 +6054,13 @@
         <v>6.0</v>
       </c>
       <c r="H202" s="4">
-        <v>11000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I202" s="4">
         <v>12.0</v>
       </c>
       <c r="J202" s="4">
-        <v>21000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="203">
@@ -6062,13 +6069,13 @@
         <v>202</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D203" s="4">
-        <v>21000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E203" s="7"/>
       <c r="F203" s="7"/>
@@ -6083,10 +6090,10 @@
         <v>203</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D204" s="4">
         <v>2500.0</v>
@@ -6097,13 +6104,13 @@
         <v>6.0</v>
       </c>
       <c r="H204" s="4">
-        <v>13000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="I204" s="4">
         <v>12.0</v>
       </c>
       <c r="J204" s="4">
-        <v>25000.0</v>
+        <v>21000.0</v>
       </c>
     </row>
     <row r="205">
@@ -6112,13 +6119,13 @@
         <v>204</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D205" s="4">
-        <v>25000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E205" s="7"/>
       <c r="F205" s="7"/>
@@ -6133,10 +6140,10 @@
         <v>205</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D206" s="4">
         <v>2500.0</v>
@@ -6147,13 +6154,13 @@
         <v>6.0</v>
       </c>
       <c r="H206" s="4">
-        <v>14000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I206" s="4">
         <v>12.0</v>
       </c>
       <c r="J206" s="4">
-        <v>28000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="207">
@@ -6162,13 +6169,13 @@
         <v>206</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D207" s="4">
-        <v>28000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E207" s="7"/>
       <c r="F207" s="7"/>
@@ -6183,10 +6190,10 @@
         <v>207</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D208" s="4">
         <v>2500.0</v>
@@ -6197,13 +6204,13 @@
         <v>6.0</v>
       </c>
       <c r="H208" s="4">
-        <v>13000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="I208" s="4">
         <v>12.0</v>
       </c>
       <c r="J208" s="4">
-        <v>25000.0</v>
+        <v>28000.0</v>
       </c>
     </row>
     <row r="209">
@@ -6212,13 +6219,13 @@
         <v>208</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D209" s="4">
-        <v>25000.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E209" s="7"/>
       <c r="F209" s="7"/>
@@ -6233,10 +6240,10 @@
         <v>209</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D210" s="4">
         <v>2500.0</v>
@@ -6247,13 +6254,13 @@
         <v>6.0</v>
       </c>
       <c r="H210" s="4">
-        <v>14000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I210" s="4">
         <v>12.0</v>
       </c>
       <c r="J210" s="4">
-        <v>27000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="211">
@@ -6262,13 +6269,13 @@
         <v>210</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D211" s="4">
-        <v>27000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E211" s="7"/>
       <c r="F211" s="7"/>
@@ -6283,10 +6290,10 @@
         <v>211</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D212" s="4">
         <v>2500.0</v>
@@ -6312,10 +6319,10 @@
         <v>212</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D213" s="4">
         <v>27000.0</v>
@@ -6333,20 +6340,28 @@
         <v>213</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D214" s="4">
-        <v>27000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E214" s="7"/>
       <c r="F214" s="7"/>
-      <c r="G214" s="7"/>
-      <c r="H214" s="7"/>
-      <c r="I214" s="7"/>
-      <c r="J214" s="7"/>
+      <c r="G214" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H214" s="4">
+        <v>14000.0</v>
+      </c>
+      <c r="I214" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J214" s="4">
+        <v>27000.0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="4">
@@ -6354,22 +6369,20 @@
         <v>214</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D215" s="4">
-        <v>37000.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E215" s="7"/>
       <c r="F215" s="7"/>
-      <c r="G215" s="4"/>
-      <c r="H215" s="4"/>
-      <c r="I215" s="4"/>
-      <c r="J215" s="4">
-        <v>37000.0</v>
-      </c>
+      <c r="G215" s="7"/>
+      <c r="H215" s="7"/>
+      <c r="I215" s="7"/>
+      <c r="J215" s="7"/>
     </row>
     <row r="216">
       <c r="A216" s="4">
@@ -6377,13 +6390,13 @@
         <v>215</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D216" s="4">
-        <v>43000.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E216" s="7"/>
       <c r="F216" s="7"/>
@@ -6398,20 +6411,22 @@
         <v>216</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D217" s="4">
-        <v>23000.0</v>
+        <v>37000.0</v>
       </c>
       <c r="E217" s="7"/>
       <c r="F217" s="7"/>
-      <c r="G217" s="7"/>
-      <c r="H217" s="7"/>
-      <c r="I217" s="7"/>
-      <c r="J217" s="7"/>
+      <c r="G217" s="4"/>
+      <c r="H217" s="4"/>
+      <c r="I217" s="4"/>
+      <c r="J217" s="4">
+        <v>37000.0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="4">
@@ -6419,10 +6434,10 @@
         <v>217</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D218" s="4">
         <v>17000.0</v>
@@ -6440,13 +6455,13 @@
         <v>218</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D219" s="4">
-        <v>29000.0</v>
+        <v>43000.0</v>
       </c>
       <c r="E219" s="7"/>
       <c r="F219" s="7"/>
@@ -6461,13 +6476,13 @@
         <v>219</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D220" s="4">
-        <v>13000.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E220" s="7"/>
       <c r="F220" s="7"/>
@@ -6482,13 +6497,13 @@
         <v>220</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>233</v>
+        <v>189</v>
       </c>
       <c r="D221" s="4">
-        <v>500.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E221" s="7"/>
       <c r="F221" s="7"/>
@@ -6506,10 +6521,10 @@
         <v>234</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>233</v>
+        <v>189</v>
       </c>
       <c r="D222" s="4">
-        <v>4000.0</v>
+        <v>29000.0</v>
       </c>
       <c r="E222" s="7"/>
       <c r="F222" s="7"/>
@@ -6527,10 +6542,10 @@
         <v>235</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>233</v>
+        <v>189</v>
       </c>
       <c r="D223" s="4">
-        <v>2500.0</v>
+        <v>13000.0</v>
       </c>
       <c r="E223" s="7"/>
       <c r="F223" s="7"/>
@@ -6551,14 +6566,10 @@
         <v>237</v>
       </c>
       <c r="D224" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E224" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F224" s="4">
-        <v>14000.0</v>
-      </c>
+        <v>500.0</v>
+      </c>
+      <c r="E224" s="7"/>
+      <c r="F224" s="7"/>
       <c r="G224" s="7"/>
       <c r="H224" s="7"/>
       <c r="I224" s="7"/>
@@ -6576,7 +6587,7 @@
         <v>237</v>
       </c>
       <c r="D225" s="4">
-        <v>109000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E225" s="7"/>
       <c r="F225" s="7"/>
@@ -6597,14 +6608,10 @@
         <v>237</v>
       </c>
       <c r="D226" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E226" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F226" s="4">
-        <v>14000.0</v>
-      </c>
+        <v>2500.0</v>
+      </c>
+      <c r="E226" s="7"/>
+      <c r="F226" s="7"/>
       <c r="G226" s="7"/>
       <c r="H226" s="7"/>
       <c r="I226" s="7"/>
@@ -6619,13 +6626,17 @@
         <v>240</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D227" s="4">
-        <v>109000.0</v>
-      </c>
-      <c r="E227" s="7"/>
-      <c r="F227" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E227" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F227" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G227" s="7"/>
       <c r="H227" s="7"/>
       <c r="I227" s="7"/>
@@ -6637,13 +6648,13 @@
         <v>227</v>
       </c>
       <c r="B228" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C228" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="C228" s="5" t="s">
-        <v>237</v>
-      </c>
       <c r="D228" s="4">
-        <v>3000.0</v>
+        <v>109000.0</v>
       </c>
       <c r="E228" s="7"/>
       <c r="F228" s="7"/>
@@ -6658,16 +6669,20 @@
         <v>228</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D229" s="4">
-        <v>114000.0</v>
-      </c>
-      <c r="E229" s="7"/>
-      <c r="F229" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E229" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F229" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G229" s="7"/>
       <c r="H229" s="7"/>
       <c r="I229" s="7"/>
@@ -6679,13 +6694,13 @@
         <v>229</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D230" s="4">
-        <v>3000.0</v>
+        <v>109000.0</v>
       </c>
       <c r="E230" s="7"/>
       <c r="F230" s="7"/>
@@ -6700,13 +6715,13 @@
         <v>230</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D231" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E231" s="7"/>
       <c r="F231" s="7"/>
@@ -6721,13 +6736,13 @@
         <v>231</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D232" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E232" s="7"/>
       <c r="F232" s="7"/>
@@ -6742,13 +6757,13 @@
         <v>232</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D233" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="7"/>
@@ -6763,13 +6778,13 @@
         <v>233</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D234" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E234" s="7"/>
       <c r="F234" s="7"/>
@@ -6784,13 +6799,13 @@
         <v>234</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D235" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E235" s="7"/>
       <c r="F235" s="7"/>
@@ -6805,13 +6820,13 @@
         <v>235</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D236" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E236" s="7"/>
       <c r="F236" s="7"/>
@@ -6826,13 +6841,13 @@
         <v>236</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D237" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="7"/>
@@ -6847,13 +6862,13 @@
         <v>237</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D238" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E238" s="7"/>
       <c r="F238" s="7"/>
@@ -6868,13 +6883,13 @@
         <v>238</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D239" s="4">
-        <v>107000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E239" s="7"/>
       <c r="F239" s="7"/>
@@ -6889,13 +6904,13 @@
         <v>239</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D240" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E240" s="7"/>
       <c r="F240" s="7"/>
@@ -6910,20 +6925,20 @@
         <v>240</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D241" s="4">
-        <v>112000.0</v>
-      </c>
-      <c r="E241" s="6"/>
-      <c r="F241" s="6"/>
-      <c r="G241" s="6"/>
-      <c r="H241" s="6"/>
-      <c r="I241" s="6"/>
-      <c r="J241" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E241" s="7"/>
+      <c r="F241" s="7"/>
+      <c r="G241" s="7"/>
+      <c r="H241" s="7"/>
+      <c r="I241" s="7"/>
+      <c r="J241" s="7"/>
     </row>
     <row r="242">
       <c r="A242" s="4">
@@ -6931,20 +6946,16 @@
         <v>241</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D242" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E242" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F242" s="4">
-        <v>19000.0</v>
-      </c>
+        <v>107000.0</v>
+      </c>
+      <c r="E242" s="7"/>
+      <c r="F242" s="7"/>
       <c r="G242" s="7"/>
       <c r="H242" s="7"/>
       <c r="I242" s="7"/>
@@ -6956,20 +6967,16 @@
         <v>242</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D243" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E243" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F243" s="4">
-        <v>19000.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E243" s="7"/>
+      <c r="F243" s="7"/>
       <c r="G243" s="7"/>
       <c r="H243" s="7"/>
       <c r="I243" s="7"/>
@@ -6981,20 +6988,20 @@
         <v>243</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D244" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E244" s="4"/>
-      <c r="F244" s="4"/>
-      <c r="G244" s="7"/>
-      <c r="H244" s="7"/>
-      <c r="I244" s="7"/>
-      <c r="J244" s="7"/>
+        <v>112000.0</v>
+      </c>
+      <c r="E244" s="6"/>
+      <c r="F244" s="6"/>
+      <c r="G244" s="6"/>
+      <c r="H244" s="6"/>
+      <c r="I244" s="6"/>
+      <c r="J244" s="6"/>
     </row>
     <row r="245">
       <c r="A245" s="4">
@@ -7002,16 +7009,20 @@
         <v>244</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D245" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E245" s="4"/>
-      <c r="F245" s="4"/>
+      <c r="E245" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F245" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G245" s="7"/>
       <c r="H245" s="7"/>
       <c r="I245" s="7"/>
@@ -7023,16 +7034,20 @@
         <v>245</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D246" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E246" s="4"/>
-      <c r="F246" s="4"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E246" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F246" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G246" s="7"/>
       <c r="H246" s="7"/>
       <c r="I246" s="7"/>
@@ -7044,21 +7059,17 @@
         <v>246</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D247" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E247" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F247" s="4">
-        <v>19500.0</v>
-      </c>
-      <c r="G247" s="4"/>
+        <v>86000.0</v>
+      </c>
+      <c r="E247" s="4"/>
+      <c r="F247" s="4"/>
+      <c r="G247" s="7"/>
       <c r="H247" s="7"/>
       <c r="I247" s="7"/>
       <c r="J247" s="7"/>
@@ -7069,20 +7080,16 @@
         <v>247</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D248" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E248" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F248" s="4">
-        <v>6000.0</v>
-      </c>
+        <v>4000.0</v>
+      </c>
+      <c r="E248" s="4"/>
+      <c r="F248" s="4"/>
       <c r="G248" s="7"/>
       <c r="H248" s="7"/>
       <c r="I248" s="7"/>
@@ -7094,16 +7101,16 @@
         <v>248</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D249" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E249" s="7"/>
-      <c r="F249" s="7"/>
+        <v>86000.0</v>
+      </c>
+      <c r="E249" s="4"/>
+      <c r="F249" s="4"/>
       <c r="G249" s="7"/>
       <c r="H249" s="7"/>
       <c r="I249" s="7"/>
@@ -7115,17 +7122,21 @@
         <v>249</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D250" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E250" s="7"/>
-      <c r="F250" s="7"/>
-      <c r="G250" s="7"/>
+      <c r="E250" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F250" s="4">
+        <v>19500.0</v>
+      </c>
+      <c r="G250" s="4"/>
       <c r="H250" s="7"/>
       <c r="I250" s="7"/>
       <c r="J250" s="7"/>
@@ -7136,16 +7147,20 @@
         <v>250</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D251" s="4">
-        <v>89000.0</v>
-      </c>
-      <c r="E251" s="7"/>
-      <c r="F251" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E251" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F251" s="4">
+        <v>6000.0</v>
+      </c>
       <c r="G251" s="7"/>
       <c r="H251" s="7"/>
       <c r="I251" s="7"/>
@@ -7157,13 +7172,13 @@
         <v>251</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D252" s="4">
-        <v>7500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E252" s="7"/>
       <c r="F252" s="7"/>
@@ -7178,13 +7193,13 @@
         <v>252</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D253" s="4">
-        <v>5000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E253" s="7"/>
       <c r="F253" s="7"/>
@@ -7199,13 +7214,13 @@
         <v>253</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D254" s="4">
-        <v>3000.0</v>
+        <v>89000.0</v>
       </c>
       <c r="E254" s="7"/>
       <c r="F254" s="7"/>
@@ -7220,20 +7235,20 @@
         <v>254</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="D255" s="4">
-        <v>80000.0</v>
-      </c>
-      <c r="E255" s="6"/>
-      <c r="F255" s="6"/>
-      <c r="G255" s="6"/>
-      <c r="H255" s="6"/>
-      <c r="I255" s="6"/>
-      <c r="J255" s="6"/>
+        <v>7500.0</v>
+      </c>
+      <c r="E255" s="7"/>
+      <c r="F255" s="7"/>
+      <c r="G255" s="7"/>
+      <c r="H255" s="7"/>
+      <c r="I255" s="7"/>
+      <c r="J255" s="7"/>
     </row>
     <row r="256">
       <c r="A256" s="4">
@@ -7241,13 +7256,13 @@
         <v>255</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="D256" s="4">
-        <v>14000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E256" s="7"/>
       <c r="F256" s="7"/>
@@ -7262,13 +7277,13 @@
         <v>256</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="D257" s="4">
-        <v>14500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E257" s="7"/>
       <c r="F257" s="7"/>
@@ -7283,20 +7298,20 @@
         <v>257</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D258" s="4">
-        <v>15000.0</v>
-      </c>
-      <c r="E258" s="7"/>
-      <c r="F258" s="7"/>
-      <c r="G258" s="7"/>
-      <c r="H258" s="7"/>
-      <c r="I258" s="7"/>
-      <c r="J258" s="7"/>
+        <v>80000.0</v>
+      </c>
+      <c r="E258" s="6"/>
+      <c r="F258" s="6"/>
+      <c r="G258" s="6"/>
+      <c r="H258" s="6"/>
+      <c r="I258" s="6"/>
+      <c r="J258" s="6"/>
     </row>
     <row r="259">
       <c r="A259" s="4">
@@ -7304,13 +7319,13 @@
         <v>258</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D259" s="4">
-        <v>15500.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E259" s="7"/>
       <c r="F259" s="7"/>
@@ -7325,13 +7340,13 @@
         <v>259</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D260" s="4">
-        <v>1500.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E260" s="7"/>
       <c r="F260" s="7"/>
@@ -7346,13 +7361,13 @@
         <v>260</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D261" s="4">
-        <v>12500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E261" s="7"/>
       <c r="F261" s="7"/>
@@ -7370,10 +7385,10 @@
         <v>273</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D262" s="4">
-        <v>500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E262" s="7"/>
       <c r="F262" s="7"/>
@@ -7391,10 +7406,10 @@
         <v>274</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D263" s="4">
-        <v>4500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E263" s="7"/>
       <c r="F263" s="7"/>
@@ -7409,13 +7424,13 @@
         <v>263</v>
       </c>
       <c r="B264" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C264" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C264" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="D264" s="4">
-        <v>3000.0</v>
+        <v>12500.0</v>
       </c>
       <c r="E264" s="7"/>
       <c r="F264" s="7"/>
@@ -7430,13 +7445,13 @@
         <v>264</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D265" s="4">
-        <v>23000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E265" s="7"/>
       <c r="F265" s="7"/>
@@ -7451,20 +7466,16 @@
         <v>265</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D266" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E266" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F266" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>4500.0</v>
+      </c>
+      <c r="E266" s="7"/>
+      <c r="F266" s="7"/>
       <c r="G266" s="7"/>
       <c r="H266" s="7"/>
       <c r="I266" s="7"/>
@@ -7476,16 +7487,16 @@
         <v>266</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D267" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E267" s="4"/>
-      <c r="F267" s="4"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E267" s="7"/>
+      <c r="F267" s="7"/>
       <c r="G267" s="7"/>
       <c r="H267" s="7"/>
       <c r="I267" s="7"/>
@@ -7497,20 +7508,16 @@
         <v>267</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D268" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E268" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F268" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>23000.0</v>
+      </c>
+      <c r="E268" s="7"/>
+      <c r="F268" s="7"/>
       <c r="G268" s="7"/>
       <c r="H268" s="7"/>
       <c r="I268" s="7"/>
@@ -7522,16 +7529,20 @@
         <v>268</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D269" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="E269" s="4"/>
-      <c r="F269" s="4"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E269" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F269" s="4">
+        <v>7500.0</v>
+      </c>
       <c r="G269" s="7"/>
       <c r="H269" s="7"/>
       <c r="I269" s="7"/>
@@ -7543,20 +7554,16 @@
         <v>269</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D270" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E270" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F270" s="4">
         <v>7500.0</v>
       </c>
+      <c r="E270" s="4"/>
+      <c r="F270" s="4"/>
       <c r="G270" s="7"/>
       <c r="H270" s="7"/>
       <c r="I270" s="7"/>
@@ -7568,16 +7575,20 @@
         <v>270</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D271" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E271" s="7"/>
-      <c r="F271" s="7"/>
+        <v>2500.0</v>
+      </c>
+      <c r="E271" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F271" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G271" s="7"/>
       <c r="H271" s="7"/>
       <c r="I271" s="7"/>
@@ -7589,16 +7600,16 @@
         <v>271</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D272" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E272" s="7"/>
-      <c r="F272" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E272" s="4"/>
+      <c r="F272" s="4"/>
       <c r="G272" s="7"/>
       <c r="H272" s="7"/>
       <c r="I272" s="7"/>
@@ -7613,13 +7624,17 @@
         <v>285</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D273" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="E273" s="7"/>
-      <c r="F273" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E273" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F273" s="4">
+        <v>7500.0</v>
+      </c>
       <c r="G273" s="7"/>
       <c r="H273" s="7"/>
       <c r="I273" s="7"/>
@@ -7634,10 +7649,10 @@
         <v>286</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D274" s="4">
-        <v>500.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E274" s="7"/>
       <c r="F274" s="7"/>
@@ -7655,10 +7670,10 @@
         <v>287</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D275" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E275" s="7"/>
       <c r="F275" s="7"/>
@@ -7673,13 +7688,13 @@
         <v>275</v>
       </c>
       <c r="B276" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C276" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="C276" s="5" t="s">
-        <v>284</v>
-      </c>
       <c r="D276" s="4">
-        <v>1000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E276" s="7"/>
       <c r="F276" s="7"/>
@@ -7694,13 +7709,13 @@
         <v>276</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D277" s="4">
-        <v>10000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E277" s="7"/>
       <c r="F277" s="7"/>
@@ -7715,13 +7730,13 @@
         <v>277</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D278" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E278" s="7"/>
       <c r="F278" s="7"/>
@@ -7736,13 +7751,13 @@
         <v>278</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D279" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E279" s="7"/>
       <c r="F279" s="7"/>
@@ -7757,13 +7772,13 @@
         <v>279</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D280" s="4">
-        <v>1000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E280" s="7"/>
       <c r="F280" s="7"/>
@@ -7778,13 +7793,13 @@
         <v>280</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D281" s="4">
-        <v>10000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E281" s="7"/>
       <c r="F281" s="7"/>
@@ -7799,13 +7814,13 @@
         <v>281</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D282" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E282" s="7"/>
       <c r="F282" s="7"/>
@@ -7820,13 +7835,13 @@
         <v>282</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D283" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E283" s="7"/>
       <c r="F283" s="7"/>
@@ -7841,10 +7856,10 @@
         <v>283</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D284" s="4">
         <v>10000.0</v>
@@ -7862,13 +7877,13 @@
         <v>284</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D285" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E285" s="7"/>
       <c r="F285" s="7"/>
@@ -7883,13 +7898,13 @@
         <v>285</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D286" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E286" s="7"/>
       <c r="F286" s="7"/>
@@ -7904,13 +7919,13 @@
         <v>286</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D287" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E287" s="7"/>
       <c r="F287" s="7"/>
@@ -7925,13 +7940,13 @@
         <v>287</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D288" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E288" s="7"/>
       <c r="F288" s="7"/>
@@ -7946,13 +7961,13 @@
         <v>288</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D289" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E289" s="7"/>
       <c r="F289" s="7"/>
@@ -7967,13 +7982,13 @@
         <v>289</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D290" s="4">
-        <v>10000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E290" s="7"/>
       <c r="F290" s="7"/>
@@ -7988,13 +8003,13 @@
         <v>290</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D291" s="4">
-        <v>2000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E291" s="7"/>
       <c r="F291" s="7"/>
@@ -8009,13 +8024,13 @@
         <v>291</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D292" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E292" s="7"/>
       <c r="F292" s="7"/>
@@ -8030,13 +8045,13 @@
         <v>292</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D293" s="4">
-        <v>1000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E293" s="7"/>
       <c r="F293" s="7"/>
@@ -8051,13 +8066,13 @@
         <v>293</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D294" s="4">
-        <v>5000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E294" s="7"/>
       <c r="F294" s="7"/>
@@ -8072,13 +8087,13 @@
         <v>294</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D295" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E295" s="7"/>
       <c r="F295" s="7"/>
@@ -8093,13 +8108,13 @@
         <v>295</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D296" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E296" s="7"/>
       <c r="F296" s="7"/>
@@ -8114,13 +8129,13 @@
         <v>296</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D297" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E297" s="7"/>
       <c r="F297" s="7"/>
@@ -8135,13 +8150,13 @@
         <v>297</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D298" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E298" s="7"/>
       <c r="F298" s="7"/>
@@ -8156,13 +8171,13 @@
         <v>298</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D299" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E299" s="7"/>
       <c r="F299" s="7"/>
@@ -8177,13 +8192,13 @@
         <v>299</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D300" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E300" s="7"/>
       <c r="F300" s="7"/>
@@ -8198,10 +8213,10 @@
         <v>300</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D301" s="4">
         <v>5000.0</v>
@@ -8219,13 +8234,13 @@
         <v>301</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D302" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E302" s="7"/>
       <c r="F302" s="7"/>
@@ -8240,10 +8255,10 @@
         <v>302</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D303" s="4">
         <v>500.0</v>
@@ -8261,10 +8276,10 @@
         <v>303</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D304" s="4">
         <v>5000.0</v>
@@ -8282,13 +8297,13 @@
         <v>304</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D305" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E305" s="7"/>
       <c r="F305" s="7"/>
@@ -8303,13 +8318,13 @@
         <v>305</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D306" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E306" s="7"/>
       <c r="F306" s="7"/>
@@ -8324,13 +8339,13 @@
         <v>306</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D307" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E307" s="7"/>
       <c r="F307" s="7"/>
@@ -8345,13 +8360,13 @@
         <v>307</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D308" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E308" s="7"/>
       <c r="F308" s="7"/>
@@ -8366,20 +8381,16 @@
         <v>308</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D309" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E309" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F309" s="4">
-        <v>4500.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E309" s="7"/>
+      <c r="F309" s="7"/>
       <c r="G309" s="7"/>
       <c r="H309" s="7"/>
       <c r="I309" s="7"/>
@@ -8391,13 +8402,13 @@
         <v>309</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D310" s="4">
-        <v>4500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E310" s="7"/>
       <c r="F310" s="7"/>
@@ -8412,16 +8423,16 @@
         <v>310</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D311" s="4">
-        <v>51000.0</v>
-      </c>
-      <c r="E311" s="4"/>
-      <c r="F311" s="4"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E311" s="7"/>
+      <c r="F311" s="7"/>
       <c r="G311" s="7"/>
       <c r="H311" s="7"/>
       <c r="I311" s="7"/>
@@ -8433,19 +8444,19 @@
         <v>311</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D312" s="4">
-        <v>2000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E312" s="4">
         <v>5.0</v>
       </c>
       <c r="F312" s="4">
-        <v>9000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="G312" s="7"/>
       <c r="H312" s="7"/>
@@ -8458,13 +8469,13 @@
         <v>312</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D313" s="4">
-        <v>52000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E313" s="7"/>
       <c r="F313" s="7"/>
@@ -8479,16 +8490,16 @@
         <v>313</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D314" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E314" s="7"/>
-      <c r="F314" s="7"/>
+        <v>51000.0</v>
+      </c>
+      <c r="E314" s="4"/>
+      <c r="F314" s="4"/>
       <c r="G314" s="7"/>
       <c r="H314" s="7"/>
       <c r="I314" s="7"/>
@@ -8500,16 +8511,20 @@
         <v>314</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D315" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E315" s="7"/>
-      <c r="F315" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E315" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F315" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G315" s="7"/>
       <c r="H315" s="7"/>
       <c r="I315" s="7"/>
@@ -8521,20 +8536,16 @@
         <v>315</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D316" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E316" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F316" s="4">
-        <v>17000.0</v>
-      </c>
+        <v>52000.0</v>
+      </c>
+      <c r="E316" s="7"/>
+      <c r="F316" s="7"/>
       <c r="G316" s="7"/>
       <c r="H316" s="7"/>
       <c r="I316" s="7"/>
@@ -8546,13 +8557,13 @@
         <v>316</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D317" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E317" s="7"/>
       <c r="F317" s="7"/>
@@ -8567,20 +8578,16 @@
         <v>317</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D318" s="4">
-        <v>7000.0</v>
-      </c>
-      <c r="E318" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F318" s="4">
-        <v>32500.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E318" s="7"/>
+      <c r="F318" s="7"/>
       <c r="G318" s="7"/>
       <c r="H318" s="7"/>
       <c r="I318" s="7"/>
@@ -8592,16 +8599,20 @@
         <v>318</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D319" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E319" s="7"/>
-      <c r="F319" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E319" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F319" s="4">
+        <v>17000.0</v>
+      </c>
       <c r="G319" s="7"/>
       <c r="H319" s="7"/>
       <c r="I319" s="7"/>
@@ -8613,13 +8624,13 @@
         <v>319</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D320" s="4">
-        <v>9500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E320" s="7"/>
       <c r="F320" s="7"/>
@@ -8634,16 +8645,20 @@
         <v>320</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D321" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E321" s="7"/>
-      <c r="F321" s="7"/>
+        <v>7000.0</v>
+      </c>
+      <c r="E321" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F321" s="4">
+        <v>32500.0</v>
+      </c>
       <c r="G321" s="7"/>
       <c r="H321" s="7"/>
       <c r="I321" s="7"/>
@@ -8655,13 +8670,13 @@
         <v>321</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D322" s="4">
-        <v>5000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E322" s="7"/>
       <c r="F322" s="7"/>
@@ -8676,20 +8691,16 @@
         <v>322</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D323" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E323" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F323" s="4">
-        <v>22500.0</v>
-      </c>
+        <v>9500.0</v>
+      </c>
+      <c r="E323" s="7"/>
+      <c r="F323" s="7"/>
       <c r="G323" s="7"/>
       <c r="H323" s="7"/>
       <c r="I323" s="7"/>
@@ -8701,20 +8712,16 @@
         <v>323</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D324" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E324" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F324" s="4">
-        <v>12500.0</v>
-      </c>
+      <c r="E324" s="7"/>
+      <c r="F324" s="7"/>
       <c r="G324" s="7"/>
       <c r="H324" s="7"/>
       <c r="I324" s="7"/>
@@ -8726,16 +8733,16 @@
         <v>324</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D325" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E325" s="4"/>
-      <c r="F325" s="4"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E325" s="7"/>
+      <c r="F325" s="7"/>
       <c r="G325" s="7"/>
       <c r="H325" s="7"/>
       <c r="I325" s="7"/>
@@ -8747,17 +8754,21 @@
         <v>325</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D326" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E326" s="4"/>
-      <c r="F326" s="4"/>
-      <c r="G326" s="4"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E326" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F326" s="4">
+        <v>22500.0</v>
+      </c>
+      <c r="G326" s="7"/>
       <c r="H326" s="7"/>
       <c r="I326" s="7"/>
       <c r="J326" s="7"/>
@@ -8768,19 +8779,19 @@
         <v>326</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D327" s="4">
-        <v>3000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E327" s="4">
         <v>5.0</v>
       </c>
       <c r="F327" s="4">
-        <v>11500.0</v>
+        <v>12500.0</v>
       </c>
       <c r="G327" s="7"/>
       <c r="H327" s="7"/>
@@ -8793,16 +8804,16 @@
         <v>327</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D328" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E328" s="7"/>
-      <c r="F328" s="7"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E328" s="4"/>
+      <c r="F328" s="4"/>
       <c r="G328" s="7"/>
       <c r="H328" s="7"/>
       <c r="I328" s="7"/>
@@ -8814,21 +8825,17 @@
         <v>328</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D329" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E329" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F329" s="4">
-        <v>22500.0</v>
-      </c>
-      <c r="G329" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E329" s="4"/>
+      <c r="F329" s="4"/>
+      <c r="G329" s="4"/>
       <c r="H329" s="7"/>
       <c r="I329" s="7"/>
       <c r="J329" s="7"/>
@@ -8839,16 +8846,20 @@
         <v>329</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D330" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E330" s="7"/>
-      <c r="F330" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E330" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F330" s="4">
+        <v>11500.0</v>
+      </c>
       <c r="G330" s="7"/>
       <c r="H330" s="7"/>
       <c r="I330" s="7"/>
@@ -8860,13 +8871,13 @@
         <v>330</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D331" s="4">
-        <v>5000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E331" s="7"/>
       <c r="F331" s="7"/>
@@ -8881,16 +8892,20 @@
         <v>331</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D332" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E332" s="7"/>
-      <c r="F332" s="7"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E332" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F332" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G332" s="7"/>
       <c r="H332" s="7"/>
       <c r="I332" s="7"/>
@@ -8902,10 +8917,10 @@
         <v>332</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>346</v>
+        <v>288</v>
       </c>
       <c r="D333" s="4">
         <v>1000.0</v>
@@ -8926,10 +8941,10 @@
         <v>347</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>346</v>
+        <v>288</v>
       </c>
       <c r="D334" s="4">
-        <v>4000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E334" s="7"/>
       <c r="F334" s="7"/>
@@ -8947,10 +8962,10 @@
         <v>348</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>346</v>
+        <v>288</v>
       </c>
       <c r="D335" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E335" s="7"/>
       <c r="F335" s="7"/>
@@ -8968,10 +8983,10 @@
         <v>349</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D336" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E336" s="7"/>
       <c r="F336" s="7"/>
@@ -8986,13 +9001,13 @@
         <v>336</v>
       </c>
       <c r="B337" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C337" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="C337" s="5" t="s">
-        <v>346</v>
-      </c>
       <c r="D337" s="4">
-        <v>1000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E337" s="7"/>
       <c r="F337" s="7"/>
@@ -9007,13 +9022,13 @@
         <v>337</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D338" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E338" s="7"/>
       <c r="F338" s="7"/>
@@ -9028,13 +9043,13 @@
         <v>338</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D339" s="4">
-        <v>2500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E339" s="7"/>
       <c r="F339" s="7"/>
@@ -9049,13 +9064,13 @@
         <v>339</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D340" s="4">
-        <v>3000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E340" s="7"/>
       <c r="F340" s="7"/>
@@ -9070,13 +9085,13 @@
         <v>340</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D341" s="4">
-        <v>5000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E341" s="7"/>
       <c r="F341" s="7"/>
@@ -9091,13 +9106,13 @@
         <v>341</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D342" s="4">
-        <v>3000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E342" s="7"/>
       <c r="F342" s="7"/>
@@ -9112,20 +9127,16 @@
         <v>342</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D343" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E343" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F343" s="4">
         <v>3000.0</v>
       </c>
+      <c r="E343" s="7"/>
+      <c r="F343" s="7"/>
       <c r="G343" s="7"/>
       <c r="H343" s="7"/>
       <c r="I343" s="7"/>
@@ -9137,13 +9148,13 @@
         <v>343</v>
       </c>
       <c r="B344" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D344" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E344" s="7"/>
       <c r="F344" s="7"/>
@@ -9158,13 +9169,13 @@
         <v>344</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D345" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E345" s="7"/>
       <c r="F345" s="7"/>
@@ -9179,16 +9190,20 @@
         <v>345</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D346" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E346" s="7"/>
-      <c r="F346" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E346" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F346" s="4">
+        <v>3000.0</v>
+      </c>
       <c r="G346" s="7"/>
       <c r="H346" s="7"/>
       <c r="I346" s="7"/>
@@ -9200,13 +9215,13 @@
         <v>346</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D347" s="4">
-        <v>7000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E347" s="7"/>
       <c r="F347" s="7"/>
@@ -9221,13 +9236,13 @@
         <v>347</v>
       </c>
       <c r="B348" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D348" s="4">
-        <v>3000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E348" s="7"/>
       <c r="F348" s="7"/>
@@ -9242,13 +9257,13 @@
         <v>348</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D349" s="4">
-        <v>25000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E349" s="7"/>
       <c r="F349" s="7"/>
@@ -9263,13 +9278,13 @@
         <v>349</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D350" s="4">
-        <v>8000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E350" s="7"/>
       <c r="F350" s="7"/>
@@ -9284,13 +9299,13 @@
         <v>350</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D351" s="4">
-        <v>4000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E351" s="7"/>
       <c r="F351" s="7"/>
@@ -9305,13 +9320,13 @@
         <v>351</v>
       </c>
       <c r="B352" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="D352" s="4">
-        <v>2000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E352" s="7"/>
       <c r="F352" s="7"/>
@@ -9329,10 +9344,10 @@
         <v>367</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="D353" s="4">
-        <v>45000.0</v>
+        <v>8000.0</v>
       </c>
       <c r="E353" s="7"/>
       <c r="F353" s="7"/>
@@ -9350,10 +9365,10 @@
         <v>368</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="D354" s="4">
-        <v>2500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E354" s="7"/>
       <c r="F354" s="7"/>
@@ -9371,10 +9386,10 @@
         <v>369</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D355" s="4">
-        <v>2500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E355" s="7"/>
       <c r="F355" s="7"/>
@@ -9389,13 +9404,13 @@
         <v>355</v>
       </c>
       <c r="B356" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C356" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="C356" s="5" t="s">
-        <v>366</v>
-      </c>
       <c r="D356" s="4">
-        <v>4000.0</v>
+        <v>45000.0</v>
       </c>
       <c r="E356" s="7"/>
       <c r="F356" s="7"/>
@@ -9410,13 +9425,13 @@
         <v>356</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D357" s="4">
-        <v>5000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E357" s="7"/>
       <c r="F357" s="7"/>
@@ -9431,19 +9446,19 @@
         <v>357</v>
       </c>
       <c r="B358" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D358" s="4">
-        <v>500.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E358" s="7"/>
       <c r="F358" s="7"/>
       <c r="G358" s="7"/>
       <c r="H358" s="7"/>
-      <c r="I358" s="4"/>
+      <c r="I358" s="7"/>
       <c r="J358" s="7"/>
     </row>
     <row r="359">
@@ -9452,13 +9467,13 @@
         <v>358</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D359" s="4">
-        <v>1000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E359" s="7"/>
       <c r="F359" s="7"/>
@@ -9473,13 +9488,13 @@
         <v>359</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D360" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E360" s="7"/>
       <c r="F360" s="7"/>
@@ -9494,10 +9509,10 @@
         <v>360</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D361" s="4">
         <v>500.0</v>
@@ -9506,7 +9521,7 @@
       <c r="F361" s="7"/>
       <c r="G361" s="7"/>
       <c r="H361" s="7"/>
-      <c r="I361" s="7"/>
+      <c r="I361" s="4"/>
       <c r="J361" s="7"/>
     </row>
     <row r="362">
@@ -9515,13 +9530,13 @@
         <v>361</v>
       </c>
       <c r="B362" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D362" s="4">
-        <v>1500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E362" s="7"/>
       <c r="F362" s="7"/>
@@ -9536,13 +9551,13 @@
         <v>362</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D363" s="4">
-        <v>12000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E363" s="7"/>
       <c r="F363" s="7"/>
@@ -9557,13 +9572,13 @@
         <v>363</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D364" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E364" s="7"/>
       <c r="F364" s="7"/>
@@ -9578,13 +9593,13 @@
         <v>364</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D365" s="4">
-        <v>1000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E365" s="7"/>
       <c r="F365" s="7"/>
@@ -9599,13 +9614,13 @@
         <v>365</v>
       </c>
       <c r="B366" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D366" s="4">
-        <v>25000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E366" s="7"/>
       <c r="F366" s="7"/>
@@ -9620,13 +9635,13 @@
         <v>366</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D367" s="4">
-        <v>9000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E367" s="7"/>
       <c r="F367" s="7"/>
@@ -9641,15 +9656,15 @@
         <v>367</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D368" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E368" s="4"/>
+      <c r="E368" s="7"/>
       <c r="F368" s="7"/>
       <c r="G368" s="7"/>
       <c r="H368" s="7"/>
@@ -9662,13 +9677,13 @@
         <v>368</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D369" s="4">
-        <v>9000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E369" s="7"/>
       <c r="F369" s="7"/>
@@ -9683,13 +9698,13 @@
         <v>369</v>
       </c>
       <c r="B370" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D370" s="4">
-        <v>4500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E370" s="7"/>
       <c r="F370" s="7"/>
@@ -9704,15 +9719,15 @@
         <v>370</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D371" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E371" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E371" s="4"/>
       <c r="F371" s="7"/>
       <c r="G371" s="7"/>
       <c r="H371" s="7"/>
@@ -9725,13 +9740,13 @@
         <v>371</v>
       </c>
       <c r="B372" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D372" s="4">
-        <v>3000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E372" s="7"/>
       <c r="F372" s="7"/>
@@ -9746,13 +9761,13 @@
         <v>372</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D373" s="4">
-        <v>1000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E373" s="7"/>
       <c r="F373" s="7"/>
@@ -9766,74 +9781,74 @@
         <f t="shared" si="1"/>
         <v>373</v>
       </c>
-      <c r="B374" s="9" t="s">
-        <v>388</v>
+      <c r="B374" s="5" t="s">
+        <v>389</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="D374" s="10">
-        <v>4500.0</v>
-      </c>
-      <c r="E374" s="11"/>
-      <c r="F374" s="11"/>
-      <c r="G374" s="11"/>
-      <c r="H374" s="11"/>
-      <c r="I374" s="11"/>
-      <c r="J374" s="11"/>
+        <v>370</v>
+      </c>
+      <c r="D374" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="E374" s="7"/>
+      <c r="F374" s="7"/>
+      <c r="G374" s="7"/>
+      <c r="H374" s="7"/>
+      <c r="I374" s="7"/>
+      <c r="J374" s="7"/>
     </row>
     <row r="375">
       <c r="A375" s="4">
         <f t="shared" si="1"/>
         <v>374</v>
       </c>
-      <c r="B375" s="9" t="s">
-        <v>389</v>
+      <c r="B375" s="5" t="s">
+        <v>390</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="D375" s="10">
-        <v>50000.0</v>
-      </c>
-      <c r="E375" s="11"/>
-      <c r="F375" s="11"/>
-      <c r="G375" s="11"/>
-      <c r="H375" s="11"/>
-      <c r="I375" s="11"/>
-      <c r="J375" s="11"/>
+        <v>370</v>
+      </c>
+      <c r="D375" s="4">
+        <v>3000.0</v>
+      </c>
+      <c r="E375" s="7"/>
+      <c r="F375" s="7"/>
+      <c r="G375" s="7"/>
+      <c r="H375" s="7"/>
+      <c r="I375" s="7"/>
+      <c r="J375" s="7"/>
     </row>
     <row r="376">
       <c r="A376" s="4">
         <f t="shared" si="1"/>
         <v>375</v>
       </c>
-      <c r="B376" s="9" t="s">
-        <v>390</v>
+      <c r="B376" s="5" t="s">
+        <v>391</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="D376" s="10">
-        <v>12000.0</v>
-      </c>
-      <c r="E376" s="11"/>
-      <c r="F376" s="11"/>
-      <c r="G376" s="11"/>
-      <c r="H376" s="11"/>
-      <c r="I376" s="11"/>
-      <c r="J376" s="11"/>
+        <v>370</v>
+      </c>
+      <c r="D376" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E376" s="7"/>
+      <c r="F376" s="7"/>
+      <c r="G376" s="7"/>
+      <c r="H376" s="7"/>
+      <c r="I376" s="7"/>
+      <c r="J376" s="7"/>
     </row>
     <row r="377">
       <c r="A377" s="4">
         <f t="shared" si="1"/>
         <v>376</v>
       </c>
-      <c r="B377" s="5" t="s">
-        <v>391</v>
+      <c r="B377" s="9" t="s">
+        <v>392</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D377" s="10">
         <v>4500.0</v>
@@ -9851,13 +9866,13 @@
         <v>377</v>
       </c>
       <c r="B378" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="D378" s="10">
-        <v>3000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="E378" s="11"/>
       <c r="F378" s="11"/>
@@ -9872,13 +9887,13 @@
         <v>378</v>
       </c>
       <c r="B379" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="D379" s="10">
-        <v>5000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E379" s="11"/>
       <c r="F379" s="11"/>
@@ -9892,14 +9907,14 @@
         <f t="shared" si="1"/>
         <v>379</v>
       </c>
-      <c r="B380" s="9" t="s">
-        <v>394</v>
+      <c r="B380" s="5" t="s">
+        <v>395</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="D380" s="10">
-        <v>6000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E380" s="11"/>
       <c r="F380" s="11"/>
@@ -9914,13 +9929,13 @@
         <v>380</v>
       </c>
       <c r="B381" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>346</v>
+        <v>397</v>
       </c>
       <c r="D381" s="10">
-        <v>12000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E381" s="11"/>
       <c r="F381" s="11"/>
@@ -9935,30 +9950,35 @@
         <v>381</v>
       </c>
       <c r="B382" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>346</v>
+        <v>397</v>
       </c>
       <c r="D382" s="10">
-        <v>200.0</v>
-      </c>
-      <c r="E382" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="F382" s="10">
-        <v>500.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E382" s="11"/>
+      <c r="F382" s="11"/>
       <c r="G382" s="11"/>
       <c r="H382" s="11"/>
       <c r="I382" s="11"/>
       <c r="J382" s="11"/>
     </row>
     <row r="383">
-      <c r="A383" s="12"/>
-      <c r="B383" s="12"/>
-      <c r="C383" s="12"/>
-      <c r="D383" s="11"/>
+      <c r="A383" s="4">
+        <f t="shared" si="1"/>
+        <v>382</v>
+      </c>
+      <c r="B383" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="C383" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="D383" s="10">
+        <v>6000.0</v>
+      </c>
       <c r="E383" s="11"/>
       <c r="F383" s="11"/>
       <c r="G383" s="11"/>
@@ -9967,10 +9987,19 @@
       <c r="J383" s="11"/>
     </row>
     <row r="384">
-      <c r="A384" s="12"/>
-      <c r="B384" s="12"/>
-      <c r="C384" s="12"/>
-      <c r="D384" s="11"/>
+      <c r="A384" s="4">
+        <f t="shared" si="1"/>
+        <v>383</v>
+      </c>
+      <c r="B384" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="C384" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D384" s="10">
+        <v>12000.0</v>
+      </c>
       <c r="E384" s="11"/>
       <c r="F384" s="11"/>
       <c r="G384" s="11"/>
@@ -9979,24 +10008,50 @@
       <c r="J384" s="11"/>
     </row>
     <row r="385">
-      <c r="A385" s="12"/>
-      <c r="B385" s="12"/>
-      <c r="C385" s="12"/>
-      <c r="D385" s="11"/>
-      <c r="E385" s="11"/>
-      <c r="F385" s="11"/>
+      <c r="A385" s="4">
+        <f t="shared" si="1"/>
+        <v>384</v>
+      </c>
+      <c r="B385" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="C385" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D385" s="10">
+        <v>200.0</v>
+      </c>
+      <c r="E385" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="F385" s="10">
+        <v>500.0</v>
+      </c>
       <c r="G385" s="11"/>
       <c r="H385" s="11"/>
       <c r="I385" s="11"/>
       <c r="J385" s="11"/>
     </row>
     <row r="386">
-      <c r="A386" s="12"/>
-      <c r="B386" s="12"/>
-      <c r="C386" s="12"/>
-      <c r="D386" s="11"/>
-      <c r="E386" s="11"/>
-      <c r="F386" s="11"/>
+      <c r="A386" s="4">
+        <f t="shared" si="1"/>
+        <v>385</v>
+      </c>
+      <c r="B386" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="C386" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D386" s="10">
+        <v>5000.0</v>
+      </c>
+      <c r="E386" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="F386" s="10">
+        <v>4500.0</v>
+      </c>
       <c r="G386" s="11"/>
       <c r="H386" s="11"/>
       <c r="I386" s="11"/>
@@ -11146,37 +11201,37 @@
       <c r="A482" s="12"/>
       <c r="B482" s="12"/>
       <c r="C482" s="12"/>
-      <c r="D482" s="12"/>
-      <c r="E482" s="12"/>
-      <c r="F482" s="12"/>
-      <c r="G482" s="12"/>
-      <c r="H482" s="12"/>
-      <c r="I482" s="12"/>
-      <c r="J482" s="12"/>
+      <c r="D482" s="11"/>
+      <c r="E482" s="11"/>
+      <c r="F482" s="11"/>
+      <c r="G482" s="11"/>
+      <c r="H482" s="11"/>
+      <c r="I482" s="11"/>
+      <c r="J482" s="11"/>
     </row>
     <row r="483">
       <c r="A483" s="12"/>
       <c r="B483" s="12"/>
       <c r="C483" s="12"/>
-      <c r="D483" s="12"/>
-      <c r="E483" s="12"/>
-      <c r="F483" s="12"/>
-      <c r="G483" s="12"/>
-      <c r="H483" s="12"/>
-      <c r="I483" s="12"/>
-      <c r="J483" s="12"/>
+      <c r="D483" s="11"/>
+      <c r="E483" s="11"/>
+      <c r="F483" s="11"/>
+      <c r="G483" s="11"/>
+      <c r="H483" s="11"/>
+      <c r="I483" s="11"/>
+      <c r="J483" s="11"/>
     </row>
     <row r="484">
       <c r="A484" s="12"/>
       <c r="B484" s="12"/>
       <c r="C484" s="12"/>
-      <c r="D484" s="12"/>
-      <c r="E484" s="12"/>
-      <c r="F484" s="12"/>
-      <c r="G484" s="12"/>
-      <c r="H484" s="12"/>
-      <c r="I484" s="12"/>
-      <c r="J484" s="12"/>
+      <c r="D484" s="11"/>
+      <c r="E484" s="11"/>
+      <c r="F484" s="11"/>
+      <c r="G484" s="11"/>
+      <c r="H484" s="11"/>
+      <c r="I484" s="11"/>
+      <c r="J484" s="11"/>
     </row>
     <row r="485">
       <c r="A485" s="12"/>
@@ -19566,15 +19621,51 @@
       <c r="I1183" s="12"/>
       <c r="J1183" s="12"/>
     </row>
+    <row r="1184">
+      <c r="A1184" s="12"/>
+      <c r="B1184" s="12"/>
+      <c r="C1184" s="12"/>
+      <c r="D1184" s="12"/>
+      <c r="E1184" s="12"/>
+      <c r="F1184" s="12"/>
+      <c r="G1184" s="12"/>
+      <c r="H1184" s="12"/>
+      <c r="I1184" s="12"/>
+      <c r="J1184" s="12"/>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="12"/>
+      <c r="B1185" s="12"/>
+      <c r="C1185" s="12"/>
+      <c r="D1185" s="12"/>
+      <c r="E1185" s="12"/>
+      <c r="F1185" s="12"/>
+      <c r="G1185" s="12"/>
+      <c r="H1185" s="12"/>
+      <c r="I1185" s="12"/>
+      <c r="J1185" s="12"/>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="12"/>
+      <c r="B1186" s="12"/>
+      <c r="C1186" s="12"/>
+      <c r="D1186" s="12"/>
+      <c r="E1186" s="12"/>
+      <c r="F1186" s="12"/>
+      <c r="G1186" s="12"/>
+      <c r="H1186" s="12"/>
+      <c r="I1186" s="12"/>
+      <c r="J1186" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$382"/>
-  <conditionalFormatting sqref="A2:J1183">
+  <autoFilter ref="$B$1:$C$386"/>
+  <conditionalFormatting sqref="A2:J1186">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C382">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C386">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19635,7 +19726,7 @@
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4">
@@ -19654,7 +19745,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -19673,7 +19764,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -19692,7 +19783,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -19711,7 +19802,7 @@
         <v>GROSIR5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="4">
@@ -19730,7 +19821,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -19749,7 +19840,7 @@
         <v>GROSIR7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="4">
@@ -19768,7 +19859,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -19787,7 +19878,7 @@
         <v>GROSIR9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="4">
@@ -19806,7 +19897,7 @@
         <v>GROSIR10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="4">
@@ -19825,7 +19916,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -19844,7 +19935,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -19863,7 +19954,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -19882,7 +19973,7 @@
         <v>GROSIR14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="4">
@@ -19901,7 +19992,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -19920,7 +20011,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -19939,7 +20030,7 @@
         <v>GROSIR17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="4">
@@ -19958,7 +20049,7 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
@@ -19977,7 +20068,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -19996,7 +20087,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -20015,7 +20106,7 @@
         <v>GROSIR21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4">
@@ -20034,7 +20125,7 @@
         <v>GROSIR22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="4">
@@ -20053,7 +20144,7 @@
         <v>GROSIR23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="4">
@@ -20072,7 +20163,7 @@
         <v>GROSIR24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="4">
@@ -20091,7 +20182,7 @@
         <v>GROSIR25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="4">
@@ -20110,7 +20201,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -20129,7 +20220,7 @@
         <v>GROSIR27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="4">
@@ -20148,7 +20239,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -20167,7 +20258,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -20186,7 +20277,7 @@
         <v>GROSIR30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="4">
@@ -20205,7 +20296,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -20224,7 +20315,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -20243,7 +20334,7 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
@@ -20262,7 +20353,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -20281,7 +20372,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -20300,7 +20391,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -20319,7 +20410,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -20338,7 +20429,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -20357,7 +20448,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -20376,7 +20467,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,15 +7,15 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$386</definedName>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$258</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$387</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$260</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="429">
   <si>
     <t>Barcode</t>
   </si>
@@ -701,6 +701,9 @@
     <t>Gudang Garam Surya Bungkus</t>
   </si>
   <si>
+    <t>Surya Pro Merah Bungkus</t>
+  </si>
+  <si>
     <t>Gudang Garam Signature</t>
   </si>
   <si>
@@ -1251,6 +1254,12 @@
   </si>
   <si>
     <t>Sampoerna Prima</t>
+  </si>
+  <si>
+    <t>Surya Pro Merah</t>
+  </si>
+  <si>
+    <t>Surya Pro Merah Slop</t>
   </si>
   <si>
     <t>76 Apel Royal</t>
@@ -1680,7 +1689,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A386" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A387" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -6396,7 +6405,7 @@
         <v>189</v>
       </c>
       <c r="D216" s="4">
-        <v>27000.0</v>
+        <v>34000.0</v>
       </c>
       <c r="E216" s="7"/>
       <c r="F216" s="7"/>
@@ -6417,16 +6426,14 @@
         <v>189</v>
       </c>
       <c r="D217" s="4">
-        <v>37000.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E217" s="7"/>
       <c r="F217" s="7"/>
-      <c r="G217" s="4"/>
-      <c r="H217" s="4"/>
-      <c r="I217" s="4"/>
-      <c r="J217" s="4">
-        <v>37000.0</v>
-      </c>
+      <c r="G217" s="7"/>
+      <c r="H217" s="7"/>
+      <c r="I217" s="7"/>
+      <c r="J217" s="7"/>
     </row>
     <row r="218">
       <c r="A218" s="4">
@@ -6440,14 +6447,16 @@
         <v>189</v>
       </c>
       <c r="D218" s="4">
-        <v>17000.0</v>
+        <v>37000.0</v>
       </c>
       <c r="E218" s="7"/>
       <c r="F218" s="7"/>
-      <c r="G218" s="7"/>
-      <c r="H218" s="7"/>
-      <c r="I218" s="7"/>
-      <c r="J218" s="7"/>
+      <c r="G218" s="4"/>
+      <c r="H218" s="4"/>
+      <c r="I218" s="4"/>
+      <c r="J218" s="4">
+        <v>37000.0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="4">
@@ -6461,7 +6470,7 @@
         <v>189</v>
       </c>
       <c r="D219" s="4">
-        <v>43000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E219" s="7"/>
       <c r="F219" s="7"/>
@@ -6482,7 +6491,7 @@
         <v>189</v>
       </c>
       <c r="D220" s="4">
-        <v>23000.0</v>
+        <v>43000.0</v>
       </c>
       <c r="E220" s="7"/>
       <c r="F220" s="7"/>
@@ -6503,7 +6512,7 @@
         <v>189</v>
       </c>
       <c r="D221" s="4">
-        <v>17000.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E221" s="7"/>
       <c r="F221" s="7"/>
@@ -6524,7 +6533,7 @@
         <v>189</v>
       </c>
       <c r="D222" s="4">
-        <v>29000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E222" s="7"/>
       <c r="F222" s="7"/>
@@ -6545,7 +6554,7 @@
         <v>189</v>
       </c>
       <c r="D223" s="4">
-        <v>13000.0</v>
+        <v>29000.0</v>
       </c>
       <c r="E223" s="7"/>
       <c r="F223" s="7"/>
@@ -6563,10 +6572,10 @@
         <v>236</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>237</v>
+        <v>189</v>
       </c>
       <c r="D224" s="4">
-        <v>500.0</v>
+        <v>13000.0</v>
       </c>
       <c r="E224" s="7"/>
       <c r="F224" s="7"/>
@@ -6581,13 +6590,13 @@
         <v>224</v>
       </c>
       <c r="B225" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C225" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="C225" s="5" t="s">
-        <v>237</v>
-      </c>
       <c r="D225" s="4">
-        <v>4000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E225" s="7"/>
       <c r="F225" s="7"/>
@@ -6605,10 +6614,10 @@
         <v>239</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D226" s="4">
-        <v>2500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E226" s="7"/>
       <c r="F226" s="7"/>
@@ -6626,17 +6635,13 @@
         <v>240</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D227" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E227" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F227" s="4">
-        <v>14000.0</v>
-      </c>
+        <v>2500.0</v>
+      </c>
+      <c r="E227" s="7"/>
+      <c r="F227" s="7"/>
       <c r="G227" s="7"/>
       <c r="H227" s="7"/>
       <c r="I227" s="7"/>
@@ -6648,16 +6653,20 @@
         <v>227</v>
       </c>
       <c r="B228" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C228" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C228" s="5" t="s">
-        <v>241</v>
-      </c>
       <c r="D228" s="4">
-        <v>109000.0</v>
-      </c>
-      <c r="E228" s="7"/>
-      <c r="F228" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E228" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F228" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G228" s="7"/>
       <c r="H228" s="7"/>
       <c r="I228" s="7"/>
@@ -6672,17 +6681,13 @@
         <v>243</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D229" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E229" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F229" s="4">
-        <v>14000.0</v>
-      </c>
+        <v>109000.0</v>
+      </c>
+      <c r="E229" s="7"/>
+      <c r="F229" s="7"/>
       <c r="G229" s="7"/>
       <c r="H229" s="7"/>
       <c r="I229" s="7"/>
@@ -6697,13 +6702,17 @@
         <v>244</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D230" s="4">
-        <v>109000.0</v>
-      </c>
-      <c r="E230" s="7"/>
-      <c r="F230" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E230" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F230" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G230" s="7"/>
       <c r="H230" s="7"/>
       <c r="I230" s="7"/>
@@ -6718,10 +6727,10 @@
         <v>245</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D231" s="4">
-        <v>3000.0</v>
+        <v>109000.0</v>
       </c>
       <c r="E231" s="7"/>
       <c r="F231" s="7"/>
@@ -6739,10 +6748,10 @@
         <v>246</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D232" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E232" s="7"/>
       <c r="F232" s="7"/>
@@ -6760,10 +6769,10 @@
         <v>247</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D233" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="7"/>
@@ -6781,10 +6790,10 @@
         <v>248</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D234" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E234" s="7"/>
       <c r="F234" s="7"/>
@@ -6802,10 +6811,10 @@
         <v>249</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D235" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E235" s="7"/>
       <c r="F235" s="7"/>
@@ -6823,10 +6832,10 @@
         <v>250</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D236" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E236" s="7"/>
       <c r="F236" s="7"/>
@@ -6844,10 +6853,10 @@
         <v>251</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D237" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="7"/>
@@ -6865,10 +6874,10 @@
         <v>252</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D238" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E238" s="7"/>
       <c r="F238" s="7"/>
@@ -6886,10 +6895,10 @@
         <v>253</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D239" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E239" s="7"/>
       <c r="F239" s="7"/>
@@ -6907,10 +6916,10 @@
         <v>254</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D240" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E240" s="7"/>
       <c r="F240" s="7"/>
@@ -6928,10 +6937,10 @@
         <v>255</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D241" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E241" s="7"/>
       <c r="F241" s="7"/>
@@ -6949,10 +6958,10 @@
         <v>256</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D242" s="4">
-        <v>107000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E242" s="7"/>
       <c r="F242" s="7"/>
@@ -6970,10 +6979,10 @@
         <v>257</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D243" s="4">
-        <v>3000.0</v>
+        <v>107000.0</v>
       </c>
       <c r="E243" s="7"/>
       <c r="F243" s="7"/>
@@ -6991,17 +7000,17 @@
         <v>258</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D244" s="4">
-        <v>112000.0</v>
-      </c>
-      <c r="E244" s="6"/>
-      <c r="F244" s="6"/>
-      <c r="G244" s="6"/>
-      <c r="H244" s="6"/>
-      <c r="I244" s="6"/>
-      <c r="J244" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E244" s="7"/>
+      <c r="F244" s="7"/>
+      <c r="G244" s="7"/>
+      <c r="H244" s="7"/>
+      <c r="I244" s="7"/>
+      <c r="J244" s="7"/>
     </row>
     <row r="245">
       <c r="A245" s="4">
@@ -7012,21 +7021,17 @@
         <v>259</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D245" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E245" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F245" s="4">
-        <v>19000.0</v>
-      </c>
-      <c r="G245" s="7"/>
-      <c r="H245" s="7"/>
-      <c r="I245" s="7"/>
-      <c r="J245" s="7"/>
+        <v>112000.0</v>
+      </c>
+      <c r="E245" s="6"/>
+      <c r="F245" s="6"/>
+      <c r="G245" s="6"/>
+      <c r="H245" s="6"/>
+      <c r="I245" s="6"/>
+      <c r="J245" s="6"/>
     </row>
     <row r="246">
       <c r="A246" s="4">
@@ -7037,7 +7042,7 @@
         <v>260</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D246" s="4">
         <v>4000.0</v>
@@ -7062,13 +7067,17 @@
         <v>261</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D247" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E247" s="4"/>
-      <c r="F247" s="4"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E247" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F247" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G247" s="7"/>
       <c r="H247" s="7"/>
       <c r="I247" s="7"/>
@@ -7083,10 +7092,10 @@
         <v>262</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D248" s="4">
-        <v>4000.0</v>
+        <v>86000.0</v>
       </c>
       <c r="E248" s="4"/>
       <c r="F248" s="4"/>
@@ -7104,10 +7113,10 @@
         <v>263</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D249" s="4">
-        <v>86000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E249" s="4"/>
       <c r="F249" s="4"/>
@@ -7125,18 +7134,14 @@
         <v>264</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D250" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E250" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F250" s="4">
-        <v>19500.0</v>
-      </c>
-      <c r="G250" s="4"/>
+        <v>86000.0</v>
+      </c>
+      <c r="E250" s="4"/>
+      <c r="F250" s="4"/>
+      <c r="G250" s="7"/>
       <c r="H250" s="7"/>
       <c r="I250" s="7"/>
       <c r="J250" s="7"/>
@@ -7150,18 +7155,18 @@
         <v>265</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D251" s="4">
-        <v>2000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E251" s="4">
         <v>5.0</v>
       </c>
       <c r="F251" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="G251" s="7"/>
+        <v>19500.0</v>
+      </c>
+      <c r="G251" s="4"/>
       <c r="H251" s="7"/>
       <c r="I251" s="7"/>
       <c r="J251" s="7"/>
@@ -7175,13 +7180,17 @@
         <v>266</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D252" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E252" s="7"/>
-      <c r="F252" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E252" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F252" s="4">
+        <v>6000.0</v>
+      </c>
       <c r="G252" s="7"/>
       <c r="H252" s="7"/>
       <c r="I252" s="7"/>
@@ -7196,10 +7205,10 @@
         <v>267</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D253" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E253" s="7"/>
       <c r="F253" s="7"/>
@@ -7217,10 +7226,10 @@
         <v>268</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D254" s="4">
-        <v>89000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E254" s="7"/>
       <c r="F254" s="7"/>
@@ -7238,10 +7247,10 @@
         <v>269</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D255" s="4">
-        <v>7500.0</v>
+        <v>89000.0</v>
       </c>
       <c r="E255" s="7"/>
       <c r="F255" s="7"/>
@@ -7259,10 +7268,10 @@
         <v>270</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D256" s="4">
-        <v>5000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E256" s="7"/>
       <c r="F256" s="7"/>
@@ -7280,10 +7289,10 @@
         <v>271</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D257" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E257" s="7"/>
       <c r="F257" s="7"/>
@@ -7301,17 +7310,17 @@
         <v>272</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="D258" s="4">
-        <v>80000.0</v>
-      </c>
-      <c r="E258" s="6"/>
-      <c r="F258" s="6"/>
-      <c r="G258" s="6"/>
-      <c r="H258" s="6"/>
-      <c r="I258" s="6"/>
-      <c r="J258" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E258" s="7"/>
+      <c r="F258" s="7"/>
+      <c r="G258" s="7"/>
+      <c r="H258" s="7"/>
+      <c r="I258" s="7"/>
+      <c r="J258" s="7"/>
     </row>
     <row r="259">
       <c r="A259" s="4">
@@ -7322,17 +7331,17 @@
         <v>273</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D259" s="4">
-        <v>14000.0</v>
-      </c>
-      <c r="E259" s="7"/>
-      <c r="F259" s="7"/>
-      <c r="G259" s="7"/>
-      <c r="H259" s="7"/>
-      <c r="I259" s="7"/>
-      <c r="J259" s="7"/>
+        <v>80000.0</v>
+      </c>
+      <c r="E259" s="6"/>
+      <c r="F259" s="6"/>
+      <c r="G259" s="6"/>
+      <c r="H259" s="6"/>
+      <c r="I259" s="6"/>
+      <c r="J259" s="6"/>
     </row>
     <row r="260">
       <c r="A260" s="4">
@@ -7340,13 +7349,13 @@
         <v>259</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D260" s="4">
-        <v>14500.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E260" s="7"/>
       <c r="F260" s="7"/>
@@ -7361,13 +7370,13 @@
         <v>260</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D261" s="4">
-        <v>15000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E261" s="7"/>
       <c r="F261" s="7"/>
@@ -7382,13 +7391,13 @@
         <v>261</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D262" s="4">
-        <v>15500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E262" s="7"/>
       <c r="F262" s="7"/>
@@ -7406,10 +7415,10 @@
         <v>274</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D263" s="4">
-        <v>1500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E263" s="7"/>
       <c r="F263" s="7"/>
@@ -7424,13 +7433,13 @@
         <v>263</v>
       </c>
       <c r="B264" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C264" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C264" s="5" t="s">
-        <v>275</v>
-      </c>
       <c r="D264" s="4">
-        <v>12500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E264" s="7"/>
       <c r="F264" s="7"/>
@@ -7448,10 +7457,10 @@
         <v>277</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D265" s="4">
-        <v>500.0</v>
+        <v>12500.0</v>
       </c>
       <c r="E265" s="7"/>
       <c r="F265" s="7"/>
@@ -7469,10 +7478,10 @@
         <v>278</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D266" s="4">
-        <v>4500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E266" s="7"/>
       <c r="F266" s="7"/>
@@ -7490,10 +7499,10 @@
         <v>279</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D267" s="4">
-        <v>3000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E267" s="7"/>
       <c r="F267" s="7"/>
@@ -7511,10 +7520,10 @@
         <v>280</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D268" s="4">
-        <v>23000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E268" s="7"/>
       <c r="F268" s="7"/>
@@ -7532,17 +7541,13 @@
         <v>281</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D269" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E269" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F269" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>23000.0</v>
+      </c>
+      <c r="E269" s="7"/>
+      <c r="F269" s="7"/>
       <c r="G269" s="7"/>
       <c r="H269" s="7"/>
       <c r="I269" s="7"/>
@@ -7557,13 +7562,17 @@
         <v>282</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D270" s="4">
+        <v>2000.0</v>
+      </c>
+      <c r="E270" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F270" s="4">
         <v>7500.0</v>
       </c>
-      <c r="E270" s="4"/>
-      <c r="F270" s="4"/>
       <c r="G270" s="7"/>
       <c r="H270" s="7"/>
       <c r="I270" s="7"/>
@@ -7578,17 +7587,13 @@
         <v>283</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D271" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E271" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F271" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>7500.0</v>
+      </c>
+      <c r="E271" s="4"/>
+      <c r="F271" s="4"/>
       <c r="G271" s="7"/>
       <c r="H271" s="7"/>
       <c r="I271" s="7"/>
@@ -7603,13 +7608,17 @@
         <v>284</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D272" s="4">
+        <v>2500.0</v>
+      </c>
+      <c r="E272" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F272" s="4">
         <v>9000.0</v>
       </c>
-      <c r="E272" s="4"/>
-      <c r="F272" s="4"/>
       <c r="G272" s="7"/>
       <c r="H272" s="7"/>
       <c r="I272" s="7"/>
@@ -7624,17 +7633,13 @@
         <v>285</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D273" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E273" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F273" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>9000.0</v>
+      </c>
+      <c r="E273" s="4"/>
+      <c r="F273" s="4"/>
       <c r="G273" s="7"/>
       <c r="H273" s="7"/>
       <c r="I273" s="7"/>
@@ -7649,13 +7654,17 @@
         <v>286</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D274" s="4">
+        <v>2000.0</v>
+      </c>
+      <c r="E274" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F274" s="4">
         <v>7500.0</v>
       </c>
-      <c r="E274" s="7"/>
-      <c r="F274" s="7"/>
       <c r="G274" s="7"/>
       <c r="H274" s="7"/>
       <c r="I274" s="7"/>
@@ -7670,10 +7679,10 @@
         <v>287</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="D275" s="4">
-        <v>1000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E275" s="7"/>
       <c r="F275" s="7"/>
@@ -7688,13 +7697,13 @@
         <v>275</v>
       </c>
       <c r="B276" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C276" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="C276" s="5" t="s">
-        <v>288</v>
-      </c>
       <c r="D276" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E276" s="7"/>
       <c r="F276" s="7"/>
@@ -7712,10 +7721,10 @@
         <v>290</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D277" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E277" s="7"/>
       <c r="F277" s="7"/>
@@ -7733,10 +7742,10 @@
         <v>291</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D278" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E278" s="7"/>
       <c r="F278" s="7"/>
@@ -7754,10 +7763,10 @@
         <v>292</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D279" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E279" s="7"/>
       <c r="F279" s="7"/>
@@ -7775,10 +7784,10 @@
         <v>293</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D280" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E280" s="7"/>
       <c r="F280" s="7"/>
@@ -7796,10 +7805,10 @@
         <v>294</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D281" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E281" s="7"/>
       <c r="F281" s="7"/>
@@ -7817,10 +7826,10 @@
         <v>295</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D282" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E282" s="7"/>
       <c r="F282" s="7"/>
@@ -7838,10 +7847,10 @@
         <v>296</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D283" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E283" s="7"/>
       <c r="F283" s="7"/>
@@ -7859,10 +7868,10 @@
         <v>297</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D284" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E284" s="7"/>
       <c r="F284" s="7"/>
@@ -7880,10 +7889,10 @@
         <v>298</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D285" s="4">
-        <v>1000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E285" s="7"/>
       <c r="F285" s="7"/>
@@ -7901,10 +7910,10 @@
         <v>299</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D286" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E286" s="7"/>
       <c r="F286" s="7"/>
@@ -7922,7 +7931,7 @@
         <v>300</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D287" s="4">
         <v>10000.0</v>
@@ -7943,10 +7952,10 @@
         <v>301</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D288" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E288" s="7"/>
       <c r="F288" s="7"/>
@@ -7964,10 +7973,10 @@
         <v>302</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D289" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E289" s="7"/>
       <c r="F289" s="7"/>
@@ -7985,10 +7994,10 @@
         <v>303</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D290" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E290" s="7"/>
       <c r="F290" s="7"/>
@@ -8006,10 +8015,10 @@
         <v>304</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D291" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E291" s="7"/>
       <c r="F291" s="7"/>
@@ -8027,10 +8036,10 @@
         <v>305</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D292" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E292" s="7"/>
       <c r="F292" s="7"/>
@@ -8048,10 +8057,10 @@
         <v>306</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D293" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E293" s="7"/>
       <c r="F293" s="7"/>
@@ -8069,10 +8078,10 @@
         <v>307</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D294" s="4">
-        <v>2000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E294" s="7"/>
       <c r="F294" s="7"/>
@@ -8090,10 +8099,10 @@
         <v>308</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D295" s="4">
-        <v>5000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E295" s="7"/>
       <c r="F295" s="7"/>
@@ -8111,10 +8120,10 @@
         <v>309</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D296" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E296" s="7"/>
       <c r="F296" s="7"/>
@@ -8132,10 +8141,10 @@
         <v>310</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D297" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E297" s="7"/>
       <c r="F297" s="7"/>
@@ -8153,10 +8162,10 @@
         <v>311</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D298" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E298" s="7"/>
       <c r="F298" s="7"/>
@@ -8174,10 +8183,10 @@
         <v>312</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D299" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E299" s="7"/>
       <c r="F299" s="7"/>
@@ -8195,10 +8204,10 @@
         <v>313</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D300" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E300" s="7"/>
       <c r="F300" s="7"/>
@@ -8216,10 +8225,10 @@
         <v>314</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D301" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E301" s="7"/>
       <c r="F301" s="7"/>
@@ -8237,10 +8246,10 @@
         <v>315</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D302" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E302" s="7"/>
       <c r="F302" s="7"/>
@@ -8258,7 +8267,7 @@
         <v>316</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D303" s="4">
         <v>500.0</v>
@@ -8279,10 +8288,10 @@
         <v>317</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D304" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E304" s="7"/>
       <c r="F304" s="7"/>
@@ -8300,7 +8309,7 @@
         <v>318</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D305" s="4">
         <v>5000.0</v>
@@ -8321,10 +8330,10 @@
         <v>319</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D306" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E306" s="7"/>
       <c r="F306" s="7"/>
@@ -8342,10 +8351,10 @@
         <v>320</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D307" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E307" s="7"/>
       <c r="F307" s="7"/>
@@ -8363,10 +8372,10 @@
         <v>321</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D308" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E308" s="7"/>
       <c r="F308" s="7"/>
@@ -8384,10 +8393,10 @@
         <v>322</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D309" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E309" s="7"/>
       <c r="F309" s="7"/>
@@ -8405,10 +8414,10 @@
         <v>323</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D310" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E310" s="7"/>
       <c r="F310" s="7"/>
@@ -8426,10 +8435,10 @@
         <v>324</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D311" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E311" s="7"/>
       <c r="F311" s="7"/>
@@ -8447,17 +8456,13 @@
         <v>325</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D312" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E312" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F312" s="4">
-        <v>4500.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E312" s="7"/>
+      <c r="F312" s="7"/>
       <c r="G312" s="7"/>
       <c r="H312" s="7"/>
       <c r="I312" s="7"/>
@@ -8472,13 +8477,17 @@
         <v>326</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D313" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E313" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F313" s="4">
         <v>4500.0</v>
       </c>
-      <c r="E313" s="7"/>
-      <c r="F313" s="7"/>
       <c r="G313" s="7"/>
       <c r="H313" s="7"/>
       <c r="I313" s="7"/>
@@ -8493,13 +8502,13 @@
         <v>327</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D314" s="4">
-        <v>51000.0</v>
-      </c>
-      <c r="E314" s="4"/>
-      <c r="F314" s="4"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E314" s="7"/>
+      <c r="F314" s="7"/>
       <c r="G314" s="7"/>
       <c r="H314" s="7"/>
       <c r="I314" s="7"/>
@@ -8514,17 +8523,13 @@
         <v>328</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D315" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E315" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F315" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>51000.0</v>
+      </c>
+      <c r="E315" s="4"/>
+      <c r="F315" s="4"/>
       <c r="G315" s="7"/>
       <c r="H315" s="7"/>
       <c r="I315" s="7"/>
@@ -8539,13 +8544,17 @@
         <v>329</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D316" s="4">
-        <v>52000.0</v>
-      </c>
-      <c r="E316" s="7"/>
-      <c r="F316" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E316" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F316" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G316" s="7"/>
       <c r="H316" s="7"/>
       <c r="I316" s="7"/>
@@ -8560,10 +8569,10 @@
         <v>330</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D317" s="4">
-        <v>1000.0</v>
+        <v>52000.0</v>
       </c>
       <c r="E317" s="7"/>
       <c r="F317" s="7"/>
@@ -8581,10 +8590,10 @@
         <v>331</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D318" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E318" s="7"/>
       <c r="F318" s="7"/>
@@ -8602,17 +8611,13 @@
         <v>332</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D319" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E319" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F319" s="4">
-        <v>17000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E319" s="7"/>
+      <c r="F319" s="7"/>
       <c r="G319" s="7"/>
       <c r="H319" s="7"/>
       <c r="I319" s="7"/>
@@ -8627,13 +8632,17 @@
         <v>333</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D320" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E320" s="7"/>
-      <c r="F320" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E320" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F320" s="4">
+        <v>17000.0</v>
+      </c>
       <c r="G320" s="7"/>
       <c r="H320" s="7"/>
       <c r="I320" s="7"/>
@@ -8648,17 +8657,13 @@
         <v>334</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D321" s="4">
-        <v>7000.0</v>
-      </c>
-      <c r="E321" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F321" s="4">
-        <v>32500.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E321" s="7"/>
+      <c r="F321" s="7"/>
       <c r="G321" s="7"/>
       <c r="H321" s="7"/>
       <c r="I321" s="7"/>
@@ -8673,13 +8678,17 @@
         <v>335</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D322" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E322" s="7"/>
-      <c r="F322" s="7"/>
+        <v>7000.0</v>
+      </c>
+      <c r="E322" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F322" s="4">
+        <v>32500.0</v>
+      </c>
       <c r="G322" s="7"/>
       <c r="H322" s="7"/>
       <c r="I322" s="7"/>
@@ -8694,10 +8703,10 @@
         <v>336</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D323" s="4">
-        <v>9500.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E323" s="7"/>
       <c r="F323" s="7"/>
@@ -8715,10 +8724,10 @@
         <v>337</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D324" s="4">
-        <v>3500.0</v>
+        <v>9500.0</v>
       </c>
       <c r="E324" s="7"/>
       <c r="F324" s="7"/>
@@ -8736,10 +8745,10 @@
         <v>338</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D325" s="4">
-        <v>5000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E325" s="7"/>
       <c r="F325" s="7"/>
@@ -8757,17 +8766,13 @@
         <v>339</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D326" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E326" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F326" s="4">
-        <v>22500.0</v>
-      </c>
+      <c r="E326" s="7"/>
+      <c r="F326" s="7"/>
       <c r="G326" s="7"/>
       <c r="H326" s="7"/>
       <c r="I326" s="7"/>
@@ -8782,16 +8787,16 @@
         <v>340</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D327" s="4">
-        <v>3500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E327" s="4">
         <v>5.0</v>
       </c>
       <c r="F327" s="4">
-        <v>12500.0</v>
+        <v>22500.0</v>
       </c>
       <c r="G327" s="7"/>
       <c r="H327" s="7"/>
@@ -8807,13 +8812,17 @@
         <v>341</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D328" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E328" s="4"/>
-      <c r="F328" s="4"/>
+      <c r="E328" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F328" s="4">
+        <v>12500.0</v>
+      </c>
       <c r="G328" s="7"/>
       <c r="H328" s="7"/>
       <c r="I328" s="7"/>
@@ -8828,14 +8837,14 @@
         <v>342</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D329" s="4">
-        <v>3000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E329" s="4"/>
       <c r="F329" s="4"/>
-      <c r="G329" s="4"/>
+      <c r="G329" s="7"/>
       <c r="H329" s="7"/>
       <c r="I329" s="7"/>
       <c r="J329" s="7"/>
@@ -8849,18 +8858,14 @@
         <v>343</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D330" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E330" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F330" s="4">
-        <v>11500.0</v>
-      </c>
-      <c r="G330" s="7"/>
+      <c r="E330" s="4"/>
+      <c r="F330" s="4"/>
+      <c r="G330" s="4"/>
       <c r="H330" s="7"/>
       <c r="I330" s="7"/>
       <c r="J330" s="7"/>
@@ -8874,13 +8879,17 @@
         <v>344</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D331" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E331" s="7"/>
-      <c r="F331" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E331" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F331" s="4">
+        <v>11500.0</v>
+      </c>
       <c r="G331" s="7"/>
       <c r="H331" s="7"/>
       <c r="I331" s="7"/>
@@ -8895,17 +8904,13 @@
         <v>345</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D332" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E332" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F332" s="4">
-        <v>22500.0</v>
-      </c>
+        <v>4000.0</v>
+      </c>
+      <c r="E332" s="7"/>
+      <c r="F332" s="7"/>
       <c r="G332" s="7"/>
       <c r="H332" s="7"/>
       <c r="I332" s="7"/>
@@ -8920,13 +8925,17 @@
         <v>346</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D333" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E333" s="7"/>
-      <c r="F333" s="7"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E333" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F333" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G333" s="7"/>
       <c r="H333" s="7"/>
       <c r="I333" s="7"/>
@@ -8941,10 +8950,10 @@
         <v>347</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D334" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E334" s="7"/>
       <c r="F334" s="7"/>
@@ -8962,10 +8971,10 @@
         <v>348</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D335" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E335" s="7"/>
       <c r="F335" s="7"/>
@@ -8983,10 +8992,10 @@
         <v>349</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>350</v>
+        <v>289</v>
       </c>
       <c r="D336" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E336" s="7"/>
       <c r="F336" s="7"/>
@@ -9001,13 +9010,13 @@
         <v>336</v>
       </c>
       <c r="B337" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="C337" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="C337" s="5" t="s">
-        <v>350</v>
-      </c>
       <c r="D337" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E337" s="7"/>
       <c r="F337" s="7"/>
@@ -9025,10 +9034,10 @@
         <v>352</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D338" s="4">
-        <v>1000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E338" s="7"/>
       <c r="F338" s="7"/>
@@ -9046,10 +9055,10 @@
         <v>353</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D339" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E339" s="7"/>
       <c r="F339" s="7"/>
@@ -9067,10 +9076,10 @@
         <v>354</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D340" s="4">
-        <v>1000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E340" s="7"/>
       <c r="F340" s="7"/>
@@ -9088,10 +9097,10 @@
         <v>355</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D341" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E341" s="7"/>
       <c r="F341" s="7"/>
@@ -9109,10 +9118,10 @@
         <v>356</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D342" s="4">
-        <v>2500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E342" s="7"/>
       <c r="F342" s="7"/>
@@ -9130,10 +9139,10 @@
         <v>357</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D343" s="4">
-        <v>3000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E343" s="7"/>
       <c r="F343" s="7"/>
@@ -9151,10 +9160,10 @@
         <v>358</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D344" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E344" s="7"/>
       <c r="F344" s="7"/>
@@ -9172,10 +9181,10 @@
         <v>359</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D345" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E345" s="7"/>
       <c r="F345" s="7"/>
@@ -9193,17 +9202,13 @@
         <v>360</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D346" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E346" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F346" s="4">
         <v>3000.0</v>
       </c>
+      <c r="E346" s="7"/>
+      <c r="F346" s="7"/>
       <c r="G346" s="7"/>
       <c r="H346" s="7"/>
       <c r="I346" s="7"/>
@@ -9218,13 +9223,17 @@
         <v>361</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D347" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E347" s="7"/>
-      <c r="F347" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E347" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F347" s="4">
+        <v>3000.0</v>
+      </c>
       <c r="G347" s="7"/>
       <c r="H347" s="7"/>
       <c r="I347" s="7"/>
@@ -9239,10 +9248,10 @@
         <v>362</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D348" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E348" s="7"/>
       <c r="F348" s="7"/>
@@ -9260,10 +9269,10 @@
         <v>363</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D349" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E349" s="7"/>
       <c r="F349" s="7"/>
@@ -9281,10 +9290,10 @@
         <v>364</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D350" s="4">
-        <v>7000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E350" s="7"/>
       <c r="F350" s="7"/>
@@ -9302,10 +9311,10 @@
         <v>365</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D351" s="4">
-        <v>3000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E351" s="7"/>
       <c r="F351" s="7"/>
@@ -9323,10 +9332,10 @@
         <v>366</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D352" s="4">
-        <v>25000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E352" s="7"/>
       <c r="F352" s="7"/>
@@ -9344,10 +9353,10 @@
         <v>367</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D353" s="4">
-        <v>8000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E353" s="7"/>
       <c r="F353" s="7"/>
@@ -9365,10 +9374,10 @@
         <v>368</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D354" s="4">
-        <v>4000.0</v>
+        <v>8000.0</v>
       </c>
       <c r="E354" s="7"/>
       <c r="F354" s="7"/>
@@ -9386,10 +9395,10 @@
         <v>369</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="D355" s="4">
-        <v>2000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E355" s="7"/>
       <c r="F355" s="7"/>
@@ -9404,13 +9413,13 @@
         <v>355</v>
       </c>
       <c r="B356" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="C356" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="C356" s="5" t="s">
-        <v>370</v>
-      </c>
       <c r="D356" s="4">
-        <v>45000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E356" s="7"/>
       <c r="F356" s="7"/>
@@ -9428,10 +9437,10 @@
         <v>372</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D357" s="4">
-        <v>2500.0</v>
+        <v>45000.0</v>
       </c>
       <c r="E357" s="7"/>
       <c r="F357" s="7"/>
@@ -9449,7 +9458,7 @@
         <v>373</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D358" s="4">
         <v>2500.0</v>
@@ -9470,10 +9479,10 @@
         <v>374</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D359" s="4">
-        <v>4000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E359" s="7"/>
       <c r="F359" s="7"/>
@@ -9491,10 +9500,10 @@
         <v>375</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D360" s="4">
-        <v>5000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E360" s="7"/>
       <c r="F360" s="7"/>
@@ -9512,16 +9521,16 @@
         <v>376</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D361" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E361" s="7"/>
       <c r="F361" s="7"/>
       <c r="G361" s="7"/>
       <c r="H361" s="7"/>
-      <c r="I361" s="4"/>
+      <c r="I361" s="7"/>
       <c r="J361" s="7"/>
     </row>
     <row r="362">
@@ -9533,16 +9542,16 @@
         <v>377</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D362" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E362" s="7"/>
       <c r="F362" s="7"/>
       <c r="G362" s="7"/>
       <c r="H362" s="7"/>
-      <c r="I362" s="7"/>
+      <c r="I362" s="4"/>
       <c r="J362" s="7"/>
     </row>
     <row r="363">
@@ -9554,10 +9563,10 @@
         <v>378</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D363" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E363" s="7"/>
       <c r="F363" s="7"/>
@@ -9575,10 +9584,10 @@
         <v>379</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D364" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E364" s="7"/>
       <c r="F364" s="7"/>
@@ -9596,10 +9605,10 @@
         <v>380</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D365" s="4">
-        <v>1500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E365" s="7"/>
       <c r="F365" s="7"/>
@@ -9617,10 +9626,10 @@
         <v>381</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D366" s="4">
-        <v>12000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E366" s="7"/>
       <c r="F366" s="7"/>
@@ -9638,10 +9647,10 @@
         <v>382</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D367" s="4">
-        <v>3000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E367" s="7"/>
       <c r="F367" s="7"/>
@@ -9659,10 +9668,10 @@
         <v>383</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D368" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E368" s="7"/>
       <c r="F368" s="7"/>
@@ -9680,10 +9689,10 @@
         <v>384</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D369" s="4">
-        <v>25000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E369" s="7"/>
       <c r="F369" s="7"/>
@@ -9701,10 +9710,10 @@
         <v>385</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D370" s="4">
-        <v>9000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E370" s="7"/>
       <c r="F370" s="7"/>
@@ -9722,12 +9731,12 @@
         <v>386</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D371" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E371" s="4"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E371" s="7"/>
       <c r="F371" s="7"/>
       <c r="G371" s="7"/>
       <c r="H371" s="7"/>
@@ -9743,12 +9752,12 @@
         <v>387</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D372" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="E372" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E372" s="4"/>
       <c r="F372" s="7"/>
       <c r="G372" s="7"/>
       <c r="H372" s="7"/>
@@ -9764,10 +9773,10 @@
         <v>388</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D373" s="4">
-        <v>4500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E373" s="7"/>
       <c r="F373" s="7"/>
@@ -9785,10 +9794,10 @@
         <v>389</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D374" s="4">
-        <v>500.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E374" s="7"/>
       <c r="F374" s="7"/>
@@ -9806,10 +9815,10 @@
         <v>390</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D375" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E375" s="7"/>
       <c r="F375" s="7"/>
@@ -9827,10 +9836,10 @@
         <v>391</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D376" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E376" s="7"/>
       <c r="F376" s="7"/>
@@ -9844,21 +9853,21 @@
         <f t="shared" si="1"/>
         <v>376</v>
       </c>
-      <c r="B377" s="9" t="s">
+      <c r="B377" s="5" t="s">
         <v>392</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="D377" s="10">
-        <v>4500.0</v>
-      </c>
-      <c r="E377" s="11"/>
-      <c r="F377" s="11"/>
-      <c r="G377" s="11"/>
-      <c r="H377" s="11"/>
-      <c r="I377" s="11"/>
-      <c r="J377" s="11"/>
+        <v>371</v>
+      </c>
+      <c r="D377" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E377" s="7"/>
+      <c r="F377" s="7"/>
+      <c r="G377" s="7"/>
+      <c r="H377" s="7"/>
+      <c r="I377" s="7"/>
+      <c r="J377" s="7"/>
     </row>
     <row r="378">
       <c r="A378" s="4">
@@ -9869,10 +9878,10 @@
         <v>393</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D378" s="10">
-        <v>50000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E378" s="11"/>
       <c r="F378" s="11"/>
@@ -9890,10 +9899,10 @@
         <v>394</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D379" s="10">
-        <v>12000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="E379" s="11"/>
       <c r="F379" s="11"/>
@@ -9907,14 +9916,14 @@
         <f t="shared" si="1"/>
         <v>379</v>
       </c>
-      <c r="B380" s="5" t="s">
+      <c r="B380" s="9" t="s">
         <v>395</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D380" s="10">
-        <v>4500.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E380" s="11"/>
       <c r="F380" s="11"/>
@@ -9928,14 +9937,14 @@
         <f t="shared" si="1"/>
         <v>380</v>
       </c>
-      <c r="B381" s="9" t="s">
+      <c r="B381" s="5" t="s">
         <v>396</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="D381" s="10">
-        <v>3000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E381" s="11"/>
       <c r="F381" s="11"/>
@@ -9953,10 +9962,10 @@
         <v>397</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D382" s="10">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E382" s="11"/>
       <c r="F382" s="11"/>
@@ -9974,10 +9983,10 @@
         <v>398</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D383" s="10">
-        <v>6000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E383" s="11"/>
       <c r="F383" s="11"/>
@@ -9995,10 +10004,10 @@
         <v>399</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>350</v>
+        <v>398</v>
       </c>
       <c r="D384" s="10">
-        <v>12000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="E384" s="11"/>
       <c r="F384" s="11"/>
@@ -10016,17 +10025,13 @@
         <v>400</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D385" s="10">
-        <v>200.0</v>
-      </c>
-      <c r="E385" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="F385" s="10">
-        <v>500.0</v>
-      </c>
+        <v>12000.0</v>
+      </c>
+      <c r="E385" s="11"/>
+      <c r="F385" s="11"/>
       <c r="G385" s="11"/>
       <c r="H385" s="11"/>
       <c r="I385" s="11"/>
@@ -10041,16 +10046,16 @@
         <v>401</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D386" s="10">
-        <v>5000.0</v>
+        <v>200.0</v>
       </c>
       <c r="E386" s="10">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F386" s="10">
-        <v>4500.0</v>
+        <v>500.0</v>
       </c>
       <c r="G386" s="11"/>
       <c r="H386" s="11"/>
@@ -10058,12 +10063,25 @@
       <c r="J386" s="11"/>
     </row>
     <row r="387">
-      <c r="A387" s="12"/>
-      <c r="B387" s="12"/>
-      <c r="C387" s="12"/>
-      <c r="D387" s="11"/>
-      <c r="E387" s="11"/>
-      <c r="F387" s="11"/>
+      <c r="A387" s="4">
+        <f t="shared" si="1"/>
+        <v>386</v>
+      </c>
+      <c r="B387" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="C387" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D387" s="10">
+        <v>5000.0</v>
+      </c>
+      <c r="E387" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="F387" s="10">
+        <v>4500.0</v>
+      </c>
       <c r="G387" s="11"/>
       <c r="H387" s="11"/>
       <c r="I387" s="11"/>
@@ -11237,13 +11255,13 @@
       <c r="A485" s="12"/>
       <c r="B485" s="12"/>
       <c r="C485" s="12"/>
-      <c r="D485" s="12"/>
-      <c r="E485" s="12"/>
-      <c r="F485" s="12"/>
-      <c r="G485" s="12"/>
-      <c r="H485" s="12"/>
-      <c r="I485" s="12"/>
-      <c r="J485" s="12"/>
+      <c r="D485" s="11"/>
+      <c r="E485" s="11"/>
+      <c r="F485" s="11"/>
+      <c r="G485" s="11"/>
+      <c r="H485" s="11"/>
+      <c r="I485" s="11"/>
+      <c r="J485" s="11"/>
     </row>
     <row r="486">
       <c r="A486" s="12"/>
@@ -19657,15 +19675,27 @@
       <c r="I1186" s="12"/>
       <c r="J1186" s="12"/>
     </row>
+    <row r="1187">
+      <c r="A1187" s="12"/>
+      <c r="B1187" s="12"/>
+      <c r="C1187" s="12"/>
+      <c r="D1187" s="12"/>
+      <c r="E1187" s="12"/>
+      <c r="F1187" s="12"/>
+      <c r="G1187" s="12"/>
+      <c r="H1187" s="12"/>
+      <c r="I1187" s="12"/>
+      <c r="J1187" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$386"/>
-  <conditionalFormatting sqref="A2:J1186">
+  <autoFilter ref="$B$1:$C$387"/>
+  <conditionalFormatting sqref="A2:J1187">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C386">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C387">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19722,7 +19752,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="str">
-        <f t="shared" ref="A2:A41" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
+        <f t="shared" ref="A2:A43" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -19745,7 +19775,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -19764,7 +19794,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -19783,7 +19813,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -19821,7 +19851,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -19859,7 +19889,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -19916,7 +19946,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -19935,7 +19965,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -19954,7 +19984,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -19992,7 +20022,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -20011,7 +20041,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -20049,11 +20079,11 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
-        <v>15000.0</v>
+        <v>33000.0</v>
       </c>
       <c r="E19" s="14"/>
       <c r="F19" s="14"/>
@@ -20068,18 +20098,18 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>234</v>
+        <v>414</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
-        <v>28000.0</v>
-      </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
+        <v>325000.0</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="str">
@@ -20087,11 +20117,11 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>235</v>
+        <v>415</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
-        <v>12000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="14"/>
@@ -20106,18 +20136,18 @@
         <v>GROSIR21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4">
-        <v>15500.0</v>
-      </c>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
+        <v>28000.0</v>
+      </c>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="str">
@@ -20125,11 +20155,11 @@
         <v>GROSIR22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="4">
-        <v>15500.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E23" s="14"/>
       <c r="F23" s="14"/>
@@ -20144,11 +20174,11 @@
         <v>GROSIR23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="4">
-        <v>9000.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
@@ -20163,11 +20193,11 @@
         <v>GROSIR24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>413</v>
+        <v>206</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="4">
-        <v>89000.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E25" s="14"/>
       <c r="F25" s="14"/>
@@ -20182,7 +20212,7 @@
         <v>GROSIR25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="4">
@@ -20201,11 +20231,11 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
-        <v>10000.0</v>
+        <v>89000.0</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="14"/>
@@ -20220,11 +20250,11 @@
         <v>GROSIR27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>415</v>
+        <v>191</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="4">
-        <v>215000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
@@ -20239,18 +20269,18 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>182</v>
+        <v>417</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
-        <v>41000.0</v>
-      </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
+        <v>10000.0</v>
+      </c>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="str">
@@ -20258,18 +20288,18 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
-        <v>44000.0</v>
-      </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
+        <v>215000.0</v>
+      </c>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="str">
@@ -20277,18 +20307,18 @@
         <v>GROSIR30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>417</v>
+        <v>182</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
+        <v>41000.0</v>
+      </c>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="str">
@@ -20296,11 +20326,11 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
-        <v>2000.0</v>
+        <v>44000.0</v>
       </c>
       <c r="E32" s="13"/>
       <c r="F32" s="13"/>
@@ -20315,18 +20345,18 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
-        <v>25000.0</v>
-      </c>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="str">
@@ -20334,11 +20364,11 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
-        <v>9000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E34" s="13"/>
       <c r="F34" s="13"/>
@@ -20353,11 +20383,11 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
-        <v>2500.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E35" s="13"/>
       <c r="F35" s="13"/>
@@ -20372,11 +20402,11 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
-        <v>2500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
@@ -20391,11 +20421,11 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
-        <v>2900.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E37" s="13"/>
       <c r="F37" s="13"/>
@@ -20409,12 +20439,12 @@
         <f t="shared" si="1"/>
         <v>GROSIR37</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>394</v>
+      <c r="B38" s="5" t="s">
+        <v>425</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
-        <v>11000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
@@ -20429,11 +20459,11 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
-        <v>1700.0</v>
+        <v>2900.0</v>
       </c>
       <c r="E39" s="13"/>
       <c r="F39" s="13"/>
@@ -20447,12 +20477,12 @@
         <f t="shared" si="1"/>
         <v>GROSIR39</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="9" t="s">
         <v>395</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
-        <v>4000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
@@ -20467,11 +20497,11 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
-        <v>4500.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
@@ -20481,10 +20511,17 @@
       <c r="J41" s="13"/>
     </row>
     <row r="42">
-      <c r="A42" s="4"/>
-      <c r="B42" s="5"/>
+      <c r="A42" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR41</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>396</v>
+      </c>
       <c r="C42" s="5"/>
-      <c r="D42" s="4"/>
+      <c r="D42" s="4">
+        <v>4000.0</v>
+      </c>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
       <c r="G42" s="13"/>
@@ -20493,10 +20530,17 @@
       <c r="J42" s="13"/>
     </row>
     <row r="43">
-      <c r="A43" s="4"/>
-      <c r="B43" s="5"/>
+      <c r="A43" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR42</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>428</v>
+      </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="4"/>
+      <c r="D43" s="4">
+        <v>4500.0</v>
+      </c>
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
       <c r="G43" s="13"/>
@@ -20521,12 +20565,12 @@
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
       <c r="D45" s="4"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
     </row>
     <row r="46">
       <c r="A46" s="4"/>
@@ -20593,12 +20637,12 @@
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="4"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
     </row>
     <row r="52">
       <c r="A52" s="4"/>
@@ -20617,12 +20661,12 @@
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="4"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="13"/>
     </row>
     <row r="54">
       <c r="A54" s="4"/>
@@ -20713,12 +20757,12 @@
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="4"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="13"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
     </row>
     <row r="62">
       <c r="A62" s="4"/>
@@ -20737,12 +20781,12 @@
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="4"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="14"/>
-      <c r="J63" s="14"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="13"/>
     </row>
     <row r="64">
       <c r="A64" s="4"/>
@@ -20761,12 +20805,12 @@
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
       <c r="D65" s="4"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="13"/>
-      <c r="J65" s="13"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
     </row>
     <row r="66">
       <c r="A66" s="4"/>
@@ -20797,12 +20841,12 @@
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
       <c r="D68" s="4"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="14"/>
-      <c r="J68" s="14"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
     </row>
     <row r="69">
       <c r="A69" s="4"/>
@@ -20845,12 +20889,12 @@
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
       <c r="D72" s="4"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
     </row>
     <row r="73">
       <c r="A73" s="4"/>
@@ -20881,12 +20925,12 @@
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
       <c r="D75" s="4"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="14"/>
-      <c r="J75" s="14"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13"/>
     </row>
     <row r="76">
       <c r="A76" s="4"/>
@@ -20905,12 +20949,12 @@
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="4"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
-      <c r="I77" s="13"/>
-      <c r="J77" s="13"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="14"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14"/>
     </row>
     <row r="78">
       <c r="A78" s="4"/>
@@ -20929,24 +20973,24 @@
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="4"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="14"/>
-      <c r="J79" s="14"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
+      <c r="J79" s="13"/>
     </row>
     <row r="80">
       <c r="A80" s="4"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
       <c r="D80" s="4"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="14"/>
-      <c r="J80" s="14"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="13"/>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="13"/>
+      <c r="J80" s="13"/>
     </row>
     <row r="81">
       <c r="A81" s="4"/>
@@ -20977,24 +21021,24 @@
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
       <c r="D83" s="4"/>
-      <c r="E83" s="13"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13"/>
-      <c r="H83" s="13"/>
-      <c r="I83" s="13"/>
-      <c r="J83" s="13"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14"/>
     </row>
     <row r="84">
       <c r="A84" s="4"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
       <c r="D84" s="4"/>
-      <c r="E84" s="13"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
-      <c r="J84" s="13"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
     </row>
     <row r="85">
       <c r="A85" s="4"/>
@@ -21061,24 +21105,24 @@
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
       <c r="D90" s="4"/>
-      <c r="E90" s="14"/>
-      <c r="F90" s="14"/>
-      <c r="G90" s="14"/>
-      <c r="H90" s="14"/>
-      <c r="I90" s="14"/>
-      <c r="J90" s="14"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="13"/>
+      <c r="G90" s="13"/>
+      <c r="H90" s="13"/>
+      <c r="I90" s="13"/>
+      <c r="J90" s="13"/>
     </row>
     <row r="91">
       <c r="A91" s="4"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
       <c r="D91" s="4"/>
-      <c r="E91" s="14"/>
-      <c r="F91" s="14"/>
-      <c r="G91" s="14"/>
-      <c r="H91" s="14"/>
-      <c r="I91" s="14"/>
-      <c r="J91" s="14"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="13"/>
+      <c r="G91" s="13"/>
+      <c r="H91" s="13"/>
+      <c r="I91" s="13"/>
+      <c r="J91" s="13"/>
     </row>
     <row r="92">
       <c r="A92" s="4"/>
@@ -21109,24 +21153,24 @@
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
       <c r="D94" s="4"/>
-      <c r="E94" s="13"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="13"/>
-      <c r="H94" s="13"/>
-      <c r="I94" s="13"/>
-      <c r="J94" s="13"/>
+      <c r="E94" s="14"/>
+      <c r="F94" s="14"/>
+      <c r="G94" s="14"/>
+      <c r="H94" s="14"/>
+      <c r="I94" s="14"/>
+      <c r="J94" s="14"/>
     </row>
     <row r="95">
       <c r="A95" s="4"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
       <c r="D95" s="4"/>
-      <c r="E95" s="13"/>
-      <c r="F95" s="13"/>
-      <c r="G95" s="13"/>
-      <c r="H95" s="13"/>
-      <c r="I95" s="13"/>
-      <c r="J95" s="13"/>
+      <c r="E95" s="14"/>
+      <c r="F95" s="14"/>
+      <c r="G95" s="14"/>
+      <c r="H95" s="14"/>
+      <c r="I95" s="14"/>
+      <c r="J95" s="14"/>
     </row>
     <row r="96">
       <c r="A96" s="4"/>
@@ -21205,8 +21249,8 @@
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
       <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
-      <c r="F102" s="4"/>
+      <c r="E102" s="13"/>
+      <c r="F102" s="13"/>
       <c r="G102" s="13"/>
       <c r="H102" s="13"/>
       <c r="I102" s="13"/>
@@ -21229,8 +21273,8 @@
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
       <c r="D104" s="4"/>
-      <c r="E104" s="13"/>
-      <c r="F104" s="13"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
       <c r="G104" s="13"/>
       <c r="H104" s="13"/>
       <c r="I104" s="13"/>
@@ -21241,12 +21285,12 @@
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
       <c r="D105" s="4"/>
-      <c r="E105" s="14"/>
-      <c r="F105" s="14"/>
-      <c r="G105" s="14"/>
-      <c r="H105" s="14"/>
-      <c r="I105" s="14"/>
-      <c r="J105" s="14"/>
+      <c r="E105" s="13"/>
+      <c r="F105" s="13"/>
+      <c r="G105" s="13"/>
+      <c r="H105" s="13"/>
+      <c r="I105" s="13"/>
+      <c r="J105" s="13"/>
     </row>
     <row r="106">
       <c r="A106" s="4"/>
@@ -21265,12 +21309,12 @@
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
       <c r="D107" s="4"/>
-      <c r="E107" s="13"/>
-      <c r="F107" s="13"/>
-      <c r="G107" s="13"/>
-      <c r="H107" s="13"/>
-      <c r="I107" s="13"/>
-      <c r="J107" s="13"/>
+      <c r="E107" s="14"/>
+      <c r="F107" s="14"/>
+      <c r="G107" s="14"/>
+      <c r="H107" s="14"/>
+      <c r="I107" s="14"/>
+      <c r="J107" s="14"/>
     </row>
     <row r="108">
       <c r="A108" s="4"/>
@@ -21325,12 +21369,12 @@
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
       <c r="D112" s="4"/>
-      <c r="E112" s="14"/>
-      <c r="F112" s="14"/>
-      <c r="G112" s="14"/>
-      <c r="H112" s="14"/>
-      <c r="I112" s="14"/>
-      <c r="J112" s="14"/>
+      <c r="E112" s="13"/>
+      <c r="F112" s="13"/>
+      <c r="G112" s="13"/>
+      <c r="H112" s="13"/>
+      <c r="I112" s="13"/>
+      <c r="J112" s="13"/>
     </row>
     <row r="113">
       <c r="A113" s="4"/>
@@ -21349,12 +21393,12 @@
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
       <c r="D114" s="4"/>
-      <c r="E114" s="13"/>
-      <c r="F114" s="13"/>
-      <c r="G114" s="13"/>
-      <c r="H114" s="13"/>
-      <c r="I114" s="13"/>
-      <c r="J114" s="13"/>
+      <c r="E114" s="14"/>
+      <c r="F114" s="14"/>
+      <c r="G114" s="14"/>
+      <c r="H114" s="14"/>
+      <c r="I114" s="14"/>
+      <c r="J114" s="14"/>
     </row>
     <row r="115">
       <c r="A115" s="4"/>
@@ -21433,24 +21477,24 @@
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
       <c r="D121" s="4"/>
-      <c r="E121" s="14"/>
-      <c r="F121" s="14"/>
-      <c r="G121" s="14"/>
-      <c r="H121" s="14"/>
-      <c r="I121" s="14"/>
-      <c r="J121" s="14"/>
+      <c r="E121" s="13"/>
+      <c r="F121" s="13"/>
+      <c r="G121" s="13"/>
+      <c r="H121" s="13"/>
+      <c r="I121" s="13"/>
+      <c r="J121" s="13"/>
     </row>
     <row r="122">
       <c r="A122" s="4"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
       <c r="D122" s="4"/>
-      <c r="E122" s="14"/>
-      <c r="F122" s="14"/>
-      <c r="G122" s="14"/>
-      <c r="H122" s="14"/>
-      <c r="I122" s="14"/>
-      <c r="J122" s="14"/>
+      <c r="E122" s="13"/>
+      <c r="F122" s="13"/>
+      <c r="G122" s="13"/>
+      <c r="H122" s="13"/>
+      <c r="I122" s="13"/>
+      <c r="J122" s="13"/>
     </row>
     <row r="123">
       <c r="A123" s="4"/>
@@ -21579,10 +21623,10 @@
       <c r="D133" s="4"/>
       <c r="E133" s="14"/>
       <c r="F133" s="14"/>
-      <c r="G133" s="4"/>
-      <c r="H133" s="4"/>
-      <c r="I133" s="4"/>
-      <c r="J133" s="4"/>
+      <c r="G133" s="14"/>
+      <c r="H133" s="14"/>
+      <c r="I133" s="14"/>
+      <c r="J133" s="14"/>
     </row>
     <row r="134">
       <c r="A134" s="4"/>
@@ -21721,8 +21765,8 @@
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
       <c r="D145" s="4"/>
-      <c r="E145" s="4"/>
-      <c r="F145" s="4"/>
+      <c r="E145" s="14"/>
+      <c r="F145" s="14"/>
       <c r="G145" s="4"/>
       <c r="H145" s="4"/>
       <c r="I145" s="4"/>
@@ -21745,8 +21789,8 @@
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
       <c r="D147" s="4"/>
-      <c r="E147" s="14"/>
-      <c r="F147" s="14"/>
+      <c r="E147" s="4"/>
+      <c r="F147" s="4"/>
       <c r="G147" s="4"/>
       <c r="H147" s="4"/>
       <c r="I147" s="4"/>
@@ -21793,8 +21837,8 @@
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
       <c r="D151" s="4"/>
-      <c r="E151" s="4"/>
-      <c r="F151" s="4"/>
+      <c r="E151" s="14"/>
+      <c r="F151" s="14"/>
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
       <c r="I151" s="4"/>
@@ -21817,8 +21861,8 @@
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
       <c r="D153" s="4"/>
-      <c r="E153" s="14"/>
-      <c r="F153" s="14"/>
+      <c r="E153" s="4"/>
+      <c r="F153" s="4"/>
       <c r="G153" s="4"/>
       <c r="H153" s="4"/>
       <c r="I153" s="4"/>
@@ -22047,8 +22091,8 @@
       <c r="D172" s="4"/>
       <c r="E172" s="14"/>
       <c r="F172" s="14"/>
-      <c r="G172" s="15"/>
-      <c r="H172" s="15"/>
+      <c r="G172" s="14"/>
+      <c r="H172" s="14"/>
       <c r="I172" s="14"/>
       <c r="J172" s="14"/>
     </row>
@@ -22059,10 +22103,10 @@
       <c r="D173" s="4"/>
       <c r="E173" s="14"/>
       <c r="F173" s="14"/>
-      <c r="G173" s="14"/>
-      <c r="H173" s="14"/>
-      <c r="I173" s="14"/>
-      <c r="J173" s="14"/>
+      <c r="G173" s="4"/>
+      <c r="H173" s="4"/>
+      <c r="I173" s="4"/>
+      <c r="J173" s="4"/>
     </row>
     <row r="174">
       <c r="A174" s="4"/>
@@ -22071,8 +22115,8 @@
       <c r="D174" s="4"/>
       <c r="E174" s="14"/>
       <c r="F174" s="14"/>
-      <c r="G174" s="14"/>
-      <c r="H174" s="14"/>
+      <c r="G174" s="15"/>
+      <c r="H174" s="15"/>
       <c r="I174" s="14"/>
       <c r="J174" s="14"/>
     </row>
@@ -22297,12 +22341,12 @@
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
       <c r="D193" s="4"/>
-      <c r="E193" s="13"/>
-      <c r="F193" s="13"/>
-      <c r="G193" s="13"/>
-      <c r="H193" s="13"/>
-      <c r="I193" s="13"/>
-      <c r="J193" s="13"/>
+      <c r="E193" s="14"/>
+      <c r="F193" s="14"/>
+      <c r="G193" s="14"/>
+      <c r="H193" s="14"/>
+      <c r="I193" s="14"/>
+      <c r="J193" s="14"/>
     </row>
     <row r="194">
       <c r="A194" s="4"/>
@@ -22321,12 +22365,12 @@
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
       <c r="D195" s="4"/>
-      <c r="E195" s="14"/>
-      <c r="F195" s="14"/>
-      <c r="G195" s="14"/>
-      <c r="H195" s="14"/>
-      <c r="I195" s="14"/>
-      <c r="J195" s="14"/>
+      <c r="E195" s="13"/>
+      <c r="F195" s="13"/>
+      <c r="G195" s="13"/>
+      <c r="H195" s="13"/>
+      <c r="I195" s="13"/>
+      <c r="J195" s="13"/>
     </row>
     <row r="196">
       <c r="A196" s="4"/>
@@ -22405,12 +22449,12 @@
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
       <c r="D202" s="4"/>
-      <c r="E202" s="13"/>
-      <c r="F202" s="13"/>
-      <c r="G202" s="13"/>
-      <c r="H202" s="13"/>
-      <c r="I202" s="13"/>
-      <c r="J202" s="13"/>
+      <c r="E202" s="14"/>
+      <c r="F202" s="14"/>
+      <c r="G202" s="14"/>
+      <c r="H202" s="14"/>
+      <c r="I202" s="14"/>
+      <c r="J202" s="14"/>
     </row>
     <row r="203">
       <c r="A203" s="4"/>
@@ -22429,12 +22473,12 @@
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
       <c r="D204" s="4"/>
-      <c r="E204" s="14"/>
-      <c r="F204" s="14"/>
-      <c r="G204" s="14"/>
-      <c r="H204" s="14"/>
-      <c r="I204" s="14"/>
-      <c r="J204" s="14"/>
+      <c r="E204" s="13"/>
+      <c r="F204" s="13"/>
+      <c r="G204" s="13"/>
+      <c r="H204" s="13"/>
+      <c r="I204" s="13"/>
+      <c r="J204" s="13"/>
     </row>
     <row r="205">
       <c r="A205" s="4"/>
@@ -22933,8 +22977,8 @@
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
       <c r="D246" s="4"/>
-      <c r="E246" s="4"/>
-      <c r="F246" s="4"/>
+      <c r="E246" s="14"/>
+      <c r="F246" s="14"/>
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="14"/>
@@ -22957,8 +23001,8 @@
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
       <c r="D248" s="4"/>
-      <c r="E248" s="14"/>
-      <c r="F248" s="14"/>
+      <c r="E248" s="4"/>
+      <c r="F248" s="4"/>
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="14"/>
@@ -23021,7 +23065,7 @@
       <c r="F253" s="14"/>
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
-      <c r="I253" s="5"/>
+      <c r="I253" s="14"/>
       <c r="J253" s="14"/>
     </row>
     <row r="254">
@@ -23045,7 +23089,7 @@
       <c r="F255" s="14"/>
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
-      <c r="I255" s="14"/>
+      <c r="I255" s="5"/>
       <c r="J255" s="14"/>
     </row>
     <row r="256">
@@ -23085,10 +23129,10 @@
       <c r="J258" s="14"/>
     </row>
     <row r="259">
-      <c r="A259" s="14"/>
-      <c r="B259" s="14"/>
-      <c r="C259" s="14"/>
-      <c r="D259" s="14"/>
+      <c r="A259" s="4"/>
+      <c r="B259" s="5"/>
+      <c r="C259" s="5"/>
+      <c r="D259" s="4"/>
       <c r="E259" s="14"/>
       <c r="F259" s="14"/>
       <c r="G259" s="14"/>
@@ -23097,10 +23141,10 @@
       <c r="J259" s="14"/>
     </row>
     <row r="260">
-      <c r="A260" s="14"/>
-      <c r="B260" s="14"/>
-      <c r="C260" s="14"/>
-      <c r="D260" s="14"/>
+      <c r="A260" s="4"/>
+      <c r="B260" s="5"/>
+      <c r="C260" s="5"/>
+      <c r="D260" s="4"/>
       <c r="E260" s="14"/>
       <c r="F260" s="14"/>
       <c r="G260" s="14"/>
@@ -23205,28 +23249,28 @@
       <c r="J268" s="14"/>
     </row>
     <row r="269">
-      <c r="A269" s="12"/>
-      <c r="B269" s="12"/>
-      <c r="C269" s="12"/>
-      <c r="D269" s="12"/>
-      <c r="E269" s="12"/>
-      <c r="F269" s="12"/>
-      <c r="G269" s="12"/>
-      <c r="H269" s="12"/>
-      <c r="I269" s="12"/>
-      <c r="J269" s="12"/>
+      <c r="A269" s="14"/>
+      <c r="B269" s="14"/>
+      <c r="C269" s="14"/>
+      <c r="D269" s="14"/>
+      <c r="E269" s="14"/>
+      <c r="F269" s="14"/>
+      <c r="G269" s="14"/>
+      <c r="H269" s="14"/>
+      <c r="I269" s="14"/>
+      <c r="J269" s="14"/>
     </row>
     <row r="270">
-      <c r="A270" s="12"/>
-      <c r="B270" s="12"/>
-      <c r="C270" s="12"/>
-      <c r="D270" s="12"/>
-      <c r="E270" s="12"/>
-      <c r="F270" s="12"/>
-      <c r="G270" s="12"/>
-      <c r="H270" s="12"/>
-      <c r="I270" s="12"/>
-      <c r="J270" s="12"/>
+      <c r="A270" s="14"/>
+      <c r="B270" s="14"/>
+      <c r="C270" s="14"/>
+      <c r="D270" s="14"/>
+      <c r="E270" s="14"/>
+      <c r="F270" s="14"/>
+      <c r="G270" s="14"/>
+      <c r="H270" s="14"/>
+      <c r="I270" s="14"/>
+      <c r="J270" s="14"/>
     </row>
     <row r="271">
       <c r="A271" s="12"/>
@@ -32924,9 +32968,33 @@
       <c r="I1078" s="12"/>
       <c r="J1078" s="12"/>
     </row>
+    <row r="1079">
+      <c r="A1079" s="12"/>
+      <c r="B1079" s="12"/>
+      <c r="C1079" s="12"/>
+      <c r="D1079" s="12"/>
+      <c r="E1079" s="12"/>
+      <c r="F1079" s="12"/>
+      <c r="G1079" s="12"/>
+      <c r="H1079" s="12"/>
+      <c r="I1079" s="12"/>
+      <c r="J1079" s="12"/>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="12"/>
+      <c r="B1080" s="12"/>
+      <c r="C1080" s="12"/>
+      <c r="D1080" s="12"/>
+      <c r="E1080" s="12"/>
+      <c r="F1080" s="12"/>
+      <c r="G1080" s="12"/>
+      <c r="H1080" s="12"/>
+      <c r="I1080" s="12"/>
+      <c r="J1080" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$258"/>
-  <conditionalFormatting sqref="A2:J1078">
+  <autoFilter ref="$B$1:$C$260"/>
+  <conditionalFormatting sqref="A2:J1080">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$387</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$388</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$260</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="430">
   <si>
     <t>Barcode</t>
   </si>
@@ -1083,6 +1083,9 @@
   </si>
   <si>
     <t>Autan</t>
+  </si>
+  <si>
+    <t>Autan Renceng</t>
   </si>
   <si>
     <t>Solatif</t>
@@ -1689,7 +1692,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A387" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A388" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -9121,7 +9124,7 @@
         <v>351</v>
       </c>
       <c r="D342" s="4">
-        <v>4000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E342" s="7"/>
       <c r="F342" s="7"/>
@@ -9142,7 +9145,7 @@
         <v>351</v>
       </c>
       <c r="D343" s="4">
-        <v>2500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E343" s="7"/>
       <c r="F343" s="7"/>
@@ -9163,7 +9166,7 @@
         <v>351</v>
       </c>
       <c r="D344" s="4">
-        <v>3000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E344" s="7"/>
       <c r="F344" s="7"/>
@@ -9184,7 +9187,7 @@
         <v>351</v>
       </c>
       <c r="D345" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E345" s="7"/>
       <c r="F345" s="7"/>
@@ -9205,7 +9208,7 @@
         <v>351</v>
       </c>
       <c r="D346" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E346" s="7"/>
       <c r="F346" s="7"/>
@@ -9226,14 +9229,10 @@
         <v>351</v>
       </c>
       <c r="D347" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E347" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F347" s="4">
         <v>3000.0</v>
       </c>
+      <c r="E347" s="7"/>
+      <c r="F347" s="7"/>
       <c r="G347" s="7"/>
       <c r="H347" s="7"/>
       <c r="I347" s="7"/>
@@ -9251,10 +9250,14 @@
         <v>351</v>
       </c>
       <c r="D348" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E348" s="7"/>
-      <c r="F348" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E348" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F348" s="4">
+        <v>3000.0</v>
+      </c>
       <c r="G348" s="7"/>
       <c r="H348" s="7"/>
       <c r="I348" s="7"/>
@@ -9272,7 +9275,7 @@
         <v>351</v>
       </c>
       <c r="D349" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E349" s="7"/>
       <c r="F349" s="7"/>
@@ -9293,7 +9296,7 @@
         <v>351</v>
       </c>
       <c r="D350" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E350" s="7"/>
       <c r="F350" s="7"/>
@@ -9314,7 +9317,7 @@
         <v>351</v>
       </c>
       <c r="D351" s="4">
-        <v>7000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E351" s="7"/>
       <c r="F351" s="7"/>
@@ -9335,7 +9338,7 @@
         <v>351</v>
       </c>
       <c r="D352" s="4">
-        <v>3000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E352" s="7"/>
       <c r="F352" s="7"/>
@@ -9356,7 +9359,7 @@
         <v>351</v>
       </c>
       <c r="D353" s="4">
-        <v>25000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E353" s="7"/>
       <c r="F353" s="7"/>
@@ -9377,7 +9380,7 @@
         <v>351</v>
       </c>
       <c r="D354" s="4">
-        <v>8000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E354" s="7"/>
       <c r="F354" s="7"/>
@@ -9398,7 +9401,7 @@
         <v>351</v>
       </c>
       <c r="D355" s="4">
-        <v>4000.0</v>
+        <v>8000.0</v>
       </c>
       <c r="E355" s="7"/>
       <c r="F355" s="7"/>
@@ -9416,10 +9419,10 @@
         <v>370</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="D356" s="4">
-        <v>2000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E356" s="7"/>
       <c r="F356" s="7"/>
@@ -9434,13 +9437,13 @@
         <v>356</v>
       </c>
       <c r="B357" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C357" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="C357" s="5" t="s">
-        <v>371</v>
-      </c>
       <c r="D357" s="4">
-        <v>45000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E357" s="7"/>
       <c r="F357" s="7"/>
@@ -9458,10 +9461,10 @@
         <v>373</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D358" s="4">
-        <v>2500.0</v>
+        <v>45000.0</v>
       </c>
       <c r="E358" s="7"/>
       <c r="F358" s="7"/>
@@ -9479,7 +9482,7 @@
         <v>374</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D359" s="4">
         <v>2500.0</v>
@@ -9500,10 +9503,10 @@
         <v>375</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D360" s="4">
-        <v>4000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E360" s="7"/>
       <c r="F360" s="7"/>
@@ -9521,10 +9524,10 @@
         <v>376</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D361" s="4">
-        <v>5000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E361" s="7"/>
       <c r="F361" s="7"/>
@@ -9542,16 +9545,16 @@
         <v>377</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D362" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E362" s="7"/>
       <c r="F362" s="7"/>
       <c r="G362" s="7"/>
       <c r="H362" s="7"/>
-      <c r="I362" s="4"/>
+      <c r="I362" s="7"/>
       <c r="J362" s="7"/>
     </row>
     <row r="363">
@@ -9563,16 +9566,16 @@
         <v>378</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D363" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E363" s="7"/>
       <c r="F363" s="7"/>
       <c r="G363" s="7"/>
       <c r="H363" s="7"/>
-      <c r="I363" s="7"/>
+      <c r="I363" s="4"/>
       <c r="J363" s="7"/>
     </row>
     <row r="364">
@@ -9584,10 +9587,10 @@
         <v>379</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D364" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E364" s="7"/>
       <c r="F364" s="7"/>
@@ -9605,10 +9608,10 @@
         <v>380</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D365" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E365" s="7"/>
       <c r="F365" s="7"/>
@@ -9626,10 +9629,10 @@
         <v>381</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D366" s="4">
-        <v>1500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E366" s="7"/>
       <c r="F366" s="7"/>
@@ -9647,10 +9650,10 @@
         <v>382</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D367" s="4">
-        <v>12000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E367" s="7"/>
       <c r="F367" s="7"/>
@@ -9668,10 +9671,10 @@
         <v>383</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D368" s="4">
-        <v>3000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E368" s="7"/>
       <c r="F368" s="7"/>
@@ -9689,10 +9692,10 @@
         <v>384</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D369" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E369" s="7"/>
       <c r="F369" s="7"/>
@@ -9710,10 +9713,10 @@
         <v>385</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D370" s="4">
-        <v>25000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E370" s="7"/>
       <c r="F370" s="7"/>
@@ -9731,10 +9734,10 @@
         <v>386</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D371" s="4">
-        <v>9000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E371" s="7"/>
       <c r="F371" s="7"/>
@@ -9752,12 +9755,12 @@
         <v>387</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D372" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E372" s="4"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E372" s="7"/>
       <c r="F372" s="7"/>
       <c r="G372" s="7"/>
       <c r="H372" s="7"/>
@@ -9773,12 +9776,12 @@
         <v>388</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D373" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="E373" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E373" s="4"/>
       <c r="F373" s="7"/>
       <c r="G373" s="7"/>
       <c r="H373" s="7"/>
@@ -9794,10 +9797,10 @@
         <v>389</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D374" s="4">
-        <v>4500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E374" s="7"/>
       <c r="F374" s="7"/>
@@ -9815,10 +9818,10 @@
         <v>390</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D375" s="4">
-        <v>500.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E375" s="7"/>
       <c r="F375" s="7"/>
@@ -9836,10 +9839,10 @@
         <v>391</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D376" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E376" s="7"/>
       <c r="F376" s="7"/>
@@ -9857,10 +9860,10 @@
         <v>392</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D377" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E377" s="7"/>
       <c r="F377" s="7"/>
@@ -9874,21 +9877,21 @@
         <f t="shared" si="1"/>
         <v>377</v>
       </c>
-      <c r="B378" s="9" t="s">
+      <c r="B378" s="5" t="s">
         <v>393</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="D378" s="10">
-        <v>4500.0</v>
-      </c>
-      <c r="E378" s="11"/>
-      <c r="F378" s="11"/>
-      <c r="G378" s="11"/>
-      <c r="H378" s="11"/>
-      <c r="I378" s="11"/>
-      <c r="J378" s="11"/>
+        <v>372</v>
+      </c>
+      <c r="D378" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E378" s="7"/>
+      <c r="F378" s="7"/>
+      <c r="G378" s="7"/>
+      <c r="H378" s="7"/>
+      <c r="I378" s="7"/>
+      <c r="J378" s="7"/>
     </row>
     <row r="379">
       <c r="A379" s="4">
@@ -9899,10 +9902,10 @@
         <v>394</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D379" s="10">
-        <v>50000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E379" s="11"/>
       <c r="F379" s="11"/>
@@ -9920,10 +9923,10 @@
         <v>395</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D380" s="10">
-        <v>12000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="E380" s="11"/>
       <c r="F380" s="11"/>
@@ -9937,14 +9940,14 @@
         <f t="shared" si="1"/>
         <v>380</v>
       </c>
-      <c r="B381" s="5" t="s">
+      <c r="B381" s="9" t="s">
         <v>396</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D381" s="10">
-        <v>4500.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E381" s="11"/>
       <c r="F381" s="11"/>
@@ -9958,14 +9961,14 @@
         <f t="shared" si="1"/>
         <v>381</v>
       </c>
-      <c r="B382" s="9" t="s">
+      <c r="B382" s="5" t="s">
         <v>397</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="D382" s="10">
-        <v>3000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E382" s="11"/>
       <c r="F382" s="11"/>
@@ -9983,10 +9986,10 @@
         <v>398</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D383" s="10">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E383" s="11"/>
       <c r="F383" s="11"/>
@@ -10004,10 +10007,10 @@
         <v>399</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D384" s="10">
-        <v>6000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E384" s="11"/>
       <c r="F384" s="11"/>
@@ -10025,10 +10028,10 @@
         <v>400</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>351</v>
+        <v>399</v>
       </c>
       <c r="D385" s="10">
-        <v>12000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="E385" s="11"/>
       <c r="F385" s="11"/>
@@ -10049,14 +10052,10 @@
         <v>351</v>
       </c>
       <c r="D386" s="10">
-        <v>200.0</v>
-      </c>
-      <c r="E386" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="F386" s="10">
-        <v>500.0</v>
-      </c>
+        <v>12000.0</v>
+      </c>
+      <c r="E386" s="11"/>
+      <c r="F386" s="11"/>
       <c r="G386" s="11"/>
       <c r="H386" s="11"/>
       <c r="I386" s="11"/>
@@ -10074,13 +10073,13 @@
         <v>351</v>
       </c>
       <c r="D387" s="10">
-        <v>5000.0</v>
+        <v>200.0</v>
       </c>
       <c r="E387" s="10">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F387" s="10">
-        <v>4500.0</v>
+        <v>500.0</v>
       </c>
       <c r="G387" s="11"/>
       <c r="H387" s="11"/>
@@ -10088,12 +10087,25 @@
       <c r="J387" s="11"/>
     </row>
     <row r="388">
-      <c r="A388" s="12"/>
-      <c r="B388" s="12"/>
-      <c r="C388" s="12"/>
-      <c r="D388" s="11"/>
-      <c r="E388" s="11"/>
-      <c r="F388" s="11"/>
+      <c r="A388" s="4">
+        <f t="shared" si="1"/>
+        <v>387</v>
+      </c>
+      <c r="B388" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="C388" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D388" s="10">
+        <v>5000.0</v>
+      </c>
+      <c r="E388" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="F388" s="10">
+        <v>4500.0</v>
+      </c>
       <c r="G388" s="11"/>
       <c r="H388" s="11"/>
       <c r="I388" s="11"/>
@@ -11267,13 +11279,13 @@
       <c r="A486" s="12"/>
       <c r="B486" s="12"/>
       <c r="C486" s="12"/>
-      <c r="D486" s="12"/>
-      <c r="E486" s="12"/>
-      <c r="F486" s="12"/>
-      <c r="G486" s="12"/>
-      <c r="H486" s="12"/>
-      <c r="I486" s="12"/>
-      <c r="J486" s="12"/>
+      <c r="D486" s="11"/>
+      <c r="E486" s="11"/>
+      <c r="F486" s="11"/>
+      <c r="G486" s="11"/>
+      <c r="H486" s="11"/>
+      <c r="I486" s="11"/>
+      <c r="J486" s="11"/>
     </row>
     <row r="487">
       <c r="A487" s="12"/>
@@ -19687,15 +19699,27 @@
       <c r="I1187" s="12"/>
       <c r="J1187" s="12"/>
     </row>
+    <row r="1188">
+      <c r="A1188" s="12"/>
+      <c r="B1188" s="12"/>
+      <c r="C1188" s="12"/>
+      <c r="D1188" s="12"/>
+      <c r="E1188" s="12"/>
+      <c r="F1188" s="12"/>
+      <c r="G1188" s="12"/>
+      <c r="H1188" s="12"/>
+      <c r="I1188" s="12"/>
+      <c r="J1188" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$387"/>
-  <conditionalFormatting sqref="A2:J1187">
+  <autoFilter ref="$B$1:$C$388"/>
+  <conditionalFormatting sqref="A2:J1188">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C387">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C388">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19775,7 +19799,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -19794,7 +19818,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -19813,7 +19837,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -19851,7 +19875,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -19889,7 +19913,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -19946,7 +19970,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -19965,7 +19989,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -19984,7 +20008,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -20022,7 +20046,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -20041,7 +20065,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -20079,7 +20103,7 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
@@ -20098,7 +20122,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -20117,7 +20141,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -20231,7 +20255,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -20269,7 +20293,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -20288,7 +20312,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -20326,7 +20350,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -20345,7 +20369,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -20364,7 +20388,7 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
@@ -20383,7 +20407,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -20402,7 +20426,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -20421,7 +20445,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -20440,7 +20464,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -20459,7 +20483,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -20478,7 +20502,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -20497,7 +20521,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -20516,7 +20540,7 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
@@ -20535,7 +20559,7 @@
         <v>GROSIR42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -3801,7 +3801,7 @@
         <v>11</v>
       </c>
       <c r="D101" s="4">
-        <v>18500.0</v>
+        <v>19000.0</v>
       </c>
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$388</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$389</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$260</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="431">
   <si>
     <t>Barcode</t>
   </si>
@@ -762,6 +762,9 @@
   </si>
   <si>
     <t>Indomie Goreng</t>
+  </si>
+  <si>
+    <t>Indomie Goreng Jumbo</t>
   </si>
   <si>
     <t>Indomie Goreng Dus</t>
@@ -1692,7 +1695,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A388" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A389" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -6817,10 +6820,14 @@
         <v>242</v>
       </c>
       <c r="D235" s="4">
-        <v>114000.0</v>
-      </c>
-      <c r="E235" s="7"/>
-      <c r="F235" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E235" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F235" s="4">
+        <v>39000.0</v>
+      </c>
       <c r="G235" s="7"/>
       <c r="H235" s="7"/>
       <c r="I235" s="7"/>
@@ -6838,7 +6845,7 @@
         <v>242</v>
       </c>
       <c r="D236" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E236" s="7"/>
       <c r="F236" s="7"/>
@@ -6859,7 +6866,7 @@
         <v>242</v>
       </c>
       <c r="D237" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="7"/>
@@ -6880,7 +6887,7 @@
         <v>242</v>
       </c>
       <c r="D238" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E238" s="7"/>
       <c r="F238" s="7"/>
@@ -6901,7 +6908,7 @@
         <v>242</v>
       </c>
       <c r="D239" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E239" s="7"/>
       <c r="F239" s="7"/>
@@ -6922,7 +6929,7 @@
         <v>242</v>
       </c>
       <c r="D240" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E240" s="7"/>
       <c r="F240" s="7"/>
@@ -6943,7 +6950,7 @@
         <v>242</v>
       </c>
       <c r="D241" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E241" s="7"/>
       <c r="F241" s="7"/>
@@ -6964,7 +6971,7 @@
         <v>242</v>
       </c>
       <c r="D242" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E242" s="7"/>
       <c r="F242" s="7"/>
@@ -6985,7 +6992,7 @@
         <v>242</v>
       </c>
       <c r="D243" s="4">
-        <v>107000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E243" s="7"/>
       <c r="F243" s="7"/>
@@ -7006,7 +7013,7 @@
         <v>242</v>
       </c>
       <c r="D244" s="4">
-        <v>3000.0</v>
+        <v>107000.0</v>
       </c>
       <c r="E244" s="7"/>
       <c r="F244" s="7"/>
@@ -7027,14 +7034,14 @@
         <v>242</v>
       </c>
       <c r="D245" s="4">
-        <v>112000.0</v>
-      </c>
-      <c r="E245" s="6"/>
-      <c r="F245" s="6"/>
-      <c r="G245" s="6"/>
-      <c r="H245" s="6"/>
-      <c r="I245" s="6"/>
-      <c r="J245" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E245" s="7"/>
+      <c r="F245" s="7"/>
+      <c r="G245" s="7"/>
+      <c r="H245" s="7"/>
+      <c r="I245" s="7"/>
+      <c r="J245" s="7"/>
     </row>
     <row r="246">
       <c r="A246" s="4">
@@ -7048,18 +7055,14 @@
         <v>242</v>
       </c>
       <c r="D246" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E246" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F246" s="4">
-        <v>19000.0</v>
-      </c>
-      <c r="G246" s="7"/>
-      <c r="H246" s="7"/>
-      <c r="I246" s="7"/>
-      <c r="J246" s="7"/>
+        <v>112000.0</v>
+      </c>
+      <c r="E246" s="6"/>
+      <c r="F246" s="6"/>
+      <c r="G246" s="6"/>
+      <c r="H246" s="6"/>
+      <c r="I246" s="6"/>
+      <c r="J246" s="6"/>
     </row>
     <row r="247">
       <c r="A247" s="4">
@@ -7098,10 +7101,14 @@
         <v>242</v>
       </c>
       <c r="D248" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E248" s="4"/>
-      <c r="F248" s="4"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E248" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F248" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G248" s="7"/>
       <c r="H248" s="7"/>
       <c r="I248" s="7"/>
@@ -7119,7 +7126,7 @@
         <v>242</v>
       </c>
       <c r="D249" s="4">
-        <v>4000.0</v>
+        <v>86000.0</v>
       </c>
       <c r="E249" s="4"/>
       <c r="F249" s="4"/>
@@ -7140,7 +7147,7 @@
         <v>242</v>
       </c>
       <c r="D250" s="4">
-        <v>86000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E250" s="4"/>
       <c r="F250" s="4"/>
@@ -7161,15 +7168,11 @@
         <v>242</v>
       </c>
       <c r="D251" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E251" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F251" s="4">
-        <v>19500.0</v>
-      </c>
-      <c r="G251" s="4"/>
+        <v>86000.0</v>
+      </c>
+      <c r="E251" s="4"/>
+      <c r="F251" s="4"/>
+      <c r="G251" s="7"/>
       <c r="H251" s="7"/>
       <c r="I251" s="7"/>
       <c r="J251" s="7"/>
@@ -7186,15 +7189,15 @@
         <v>242</v>
       </c>
       <c r="D252" s="4">
-        <v>2000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E252" s="4">
         <v>5.0</v>
       </c>
       <c r="F252" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="G252" s="7"/>
+        <v>19500.0</v>
+      </c>
+      <c r="G252" s="4"/>
       <c r="H252" s="7"/>
       <c r="I252" s="7"/>
       <c r="J252" s="7"/>
@@ -7211,10 +7214,14 @@
         <v>242</v>
       </c>
       <c r="D253" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E253" s="7"/>
-      <c r="F253" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E253" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F253" s="4">
+        <v>6000.0</v>
+      </c>
       <c r="G253" s="7"/>
       <c r="H253" s="7"/>
       <c r="I253" s="7"/>
@@ -7232,7 +7239,7 @@
         <v>242</v>
       </c>
       <c r="D254" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E254" s="7"/>
       <c r="F254" s="7"/>
@@ -7253,7 +7260,7 @@
         <v>242</v>
       </c>
       <c r="D255" s="4">
-        <v>89000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E255" s="7"/>
       <c r="F255" s="7"/>
@@ -7274,7 +7281,7 @@
         <v>242</v>
       </c>
       <c r="D256" s="4">
-        <v>7500.0</v>
+        <v>89000.0</v>
       </c>
       <c r="E256" s="7"/>
       <c r="F256" s="7"/>
@@ -7295,7 +7302,7 @@
         <v>242</v>
       </c>
       <c r="D257" s="4">
-        <v>5000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E257" s="7"/>
       <c r="F257" s="7"/>
@@ -7316,7 +7323,7 @@
         <v>242</v>
       </c>
       <c r="D258" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E258" s="7"/>
       <c r="F258" s="7"/>
@@ -7334,17 +7341,17 @@
         <v>273</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D259" s="4">
-        <v>80000.0</v>
-      </c>
-      <c r="E259" s="6"/>
-      <c r="F259" s="6"/>
-      <c r="G259" s="6"/>
-      <c r="H259" s="6"/>
-      <c r="I259" s="6"/>
-      <c r="J259" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E259" s="7"/>
+      <c r="F259" s="7"/>
+      <c r="G259" s="7"/>
+      <c r="H259" s="7"/>
+      <c r="I259" s="7"/>
+      <c r="J259" s="7"/>
     </row>
     <row r="260">
       <c r="A260" s="4">
@@ -7355,17 +7362,17 @@
         <v>274</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D260" s="4">
-        <v>14000.0</v>
-      </c>
-      <c r="E260" s="7"/>
-      <c r="F260" s="7"/>
-      <c r="G260" s="7"/>
-      <c r="H260" s="7"/>
-      <c r="I260" s="7"/>
-      <c r="J260" s="7"/>
+        <v>80000.0</v>
+      </c>
+      <c r="E260" s="6"/>
+      <c r="F260" s="6"/>
+      <c r="G260" s="6"/>
+      <c r="H260" s="6"/>
+      <c r="I260" s="6"/>
+      <c r="J260" s="6"/>
     </row>
     <row r="261">
       <c r="A261" s="4">
@@ -7373,13 +7380,13 @@
         <v>260</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D261" s="4">
-        <v>14500.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E261" s="7"/>
       <c r="F261" s="7"/>
@@ -7394,13 +7401,13 @@
         <v>261</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D262" s="4">
-        <v>15000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E262" s="7"/>
       <c r="F262" s="7"/>
@@ -7415,13 +7422,13 @@
         <v>262</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D263" s="4">
-        <v>15500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E263" s="7"/>
       <c r="F263" s="7"/>
@@ -7439,10 +7446,10 @@
         <v>275</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D264" s="4">
-        <v>1500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E264" s="7"/>
       <c r="F264" s="7"/>
@@ -7457,13 +7464,13 @@
         <v>264</v>
       </c>
       <c r="B265" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C265" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="C265" s="5" t="s">
-        <v>276</v>
-      </c>
       <c r="D265" s="4">
-        <v>12500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E265" s="7"/>
       <c r="F265" s="7"/>
@@ -7481,10 +7488,10 @@
         <v>278</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D266" s="4">
-        <v>500.0</v>
+        <v>12500.0</v>
       </c>
       <c r="E266" s="7"/>
       <c r="F266" s="7"/>
@@ -7502,10 +7509,10 @@
         <v>279</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D267" s="4">
-        <v>4500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E267" s="7"/>
       <c r="F267" s="7"/>
@@ -7523,10 +7530,10 @@
         <v>280</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D268" s="4">
-        <v>3000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E268" s="7"/>
       <c r="F268" s="7"/>
@@ -7544,10 +7551,10 @@
         <v>281</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D269" s="4">
-        <v>23000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E269" s="7"/>
       <c r="F269" s="7"/>
@@ -7565,17 +7572,13 @@
         <v>282</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D270" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E270" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F270" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>23000.0</v>
+      </c>
+      <c r="E270" s="7"/>
+      <c r="F270" s="7"/>
       <c r="G270" s="7"/>
       <c r="H270" s="7"/>
       <c r="I270" s="7"/>
@@ -7590,13 +7593,17 @@
         <v>283</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D271" s="4">
+        <v>2000.0</v>
+      </c>
+      <c r="E271" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F271" s="4">
         <v>7500.0</v>
       </c>
-      <c r="E271" s="4"/>
-      <c r="F271" s="4"/>
       <c r="G271" s="7"/>
       <c r="H271" s="7"/>
       <c r="I271" s="7"/>
@@ -7611,17 +7618,13 @@
         <v>284</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D272" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E272" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F272" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>7500.0</v>
+      </c>
+      <c r="E272" s="4"/>
+      <c r="F272" s="4"/>
       <c r="G272" s="7"/>
       <c r="H272" s="7"/>
       <c r="I272" s="7"/>
@@ -7636,13 +7639,17 @@
         <v>285</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D273" s="4">
+        <v>2500.0</v>
+      </c>
+      <c r="E273" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F273" s="4">
         <v>9000.0</v>
       </c>
-      <c r="E273" s="4"/>
-      <c r="F273" s="4"/>
       <c r="G273" s="7"/>
       <c r="H273" s="7"/>
       <c r="I273" s="7"/>
@@ -7657,17 +7664,13 @@
         <v>286</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D274" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E274" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F274" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>9000.0</v>
+      </c>
+      <c r="E274" s="4"/>
+      <c r="F274" s="4"/>
       <c r="G274" s="7"/>
       <c r="H274" s="7"/>
       <c r="I274" s="7"/>
@@ -7682,13 +7685,17 @@
         <v>287</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D275" s="4">
+        <v>2000.0</v>
+      </c>
+      <c r="E275" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F275" s="4">
         <v>7500.0</v>
       </c>
-      <c r="E275" s="7"/>
-      <c r="F275" s="7"/>
       <c r="G275" s="7"/>
       <c r="H275" s="7"/>
       <c r="I275" s="7"/>
@@ -7703,10 +7710,10 @@
         <v>288</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="D276" s="4">
-        <v>1000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E276" s="7"/>
       <c r="F276" s="7"/>
@@ -7721,13 +7728,13 @@
         <v>276</v>
       </c>
       <c r="B277" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C277" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="C277" s="5" t="s">
-        <v>289</v>
-      </c>
       <c r="D277" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E277" s="7"/>
       <c r="F277" s="7"/>
@@ -7745,10 +7752,10 @@
         <v>291</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D278" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E278" s="7"/>
       <c r="F278" s="7"/>
@@ -7766,10 +7773,10 @@
         <v>292</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D279" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E279" s="7"/>
       <c r="F279" s="7"/>
@@ -7787,10 +7794,10 @@
         <v>293</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D280" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E280" s="7"/>
       <c r="F280" s="7"/>
@@ -7808,10 +7815,10 @@
         <v>294</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D281" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E281" s="7"/>
       <c r="F281" s="7"/>
@@ -7829,10 +7836,10 @@
         <v>295</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D282" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E282" s="7"/>
       <c r="F282" s="7"/>
@@ -7850,10 +7857,10 @@
         <v>296</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D283" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E283" s="7"/>
       <c r="F283" s="7"/>
@@ -7871,10 +7878,10 @@
         <v>297</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D284" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E284" s="7"/>
       <c r="F284" s="7"/>
@@ -7892,10 +7899,10 @@
         <v>298</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D285" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E285" s="7"/>
       <c r="F285" s="7"/>
@@ -7913,10 +7920,10 @@
         <v>299</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D286" s="4">
-        <v>1000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E286" s="7"/>
       <c r="F286" s="7"/>
@@ -7934,10 +7941,10 @@
         <v>300</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D287" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E287" s="7"/>
       <c r="F287" s="7"/>
@@ -7955,7 +7962,7 @@
         <v>301</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D288" s="4">
         <v>10000.0</v>
@@ -7976,10 +7983,10 @@
         <v>302</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D289" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E289" s="7"/>
       <c r="F289" s="7"/>
@@ -7997,10 +8004,10 @@
         <v>303</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D290" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E290" s="7"/>
       <c r="F290" s="7"/>
@@ -8018,10 +8025,10 @@
         <v>304</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D291" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E291" s="7"/>
       <c r="F291" s="7"/>
@@ -8039,10 +8046,10 @@
         <v>305</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D292" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E292" s="7"/>
       <c r="F292" s="7"/>
@@ -8060,10 +8067,10 @@
         <v>306</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D293" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E293" s="7"/>
       <c r="F293" s="7"/>
@@ -8081,10 +8088,10 @@
         <v>307</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D294" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E294" s="7"/>
       <c r="F294" s="7"/>
@@ -8102,10 +8109,10 @@
         <v>308</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D295" s="4">
-        <v>2000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E295" s="7"/>
       <c r="F295" s="7"/>
@@ -8123,10 +8130,10 @@
         <v>309</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D296" s="4">
-        <v>5000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E296" s="7"/>
       <c r="F296" s="7"/>
@@ -8144,10 +8151,10 @@
         <v>310</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D297" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E297" s="7"/>
       <c r="F297" s="7"/>
@@ -8165,10 +8172,10 @@
         <v>311</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D298" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E298" s="7"/>
       <c r="F298" s="7"/>
@@ -8186,10 +8193,10 @@
         <v>312</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D299" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E299" s="7"/>
       <c r="F299" s="7"/>
@@ -8207,10 +8214,10 @@
         <v>313</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D300" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E300" s="7"/>
       <c r="F300" s="7"/>
@@ -8228,10 +8235,10 @@
         <v>314</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D301" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E301" s="7"/>
       <c r="F301" s="7"/>
@@ -8249,10 +8256,10 @@
         <v>315</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D302" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E302" s="7"/>
       <c r="F302" s="7"/>
@@ -8270,10 +8277,10 @@
         <v>316</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D303" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E303" s="7"/>
       <c r="F303" s="7"/>
@@ -8291,7 +8298,7 @@
         <v>317</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D304" s="4">
         <v>500.0</v>
@@ -8312,10 +8319,10 @@
         <v>318</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D305" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E305" s="7"/>
       <c r="F305" s="7"/>
@@ -8333,7 +8340,7 @@
         <v>319</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D306" s="4">
         <v>5000.0</v>
@@ -8354,10 +8361,10 @@
         <v>320</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D307" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E307" s="7"/>
       <c r="F307" s="7"/>
@@ -8375,10 +8382,10 @@
         <v>321</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D308" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E308" s="7"/>
       <c r="F308" s="7"/>
@@ -8396,10 +8403,10 @@
         <v>322</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D309" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E309" s="7"/>
       <c r="F309" s="7"/>
@@ -8417,10 +8424,10 @@
         <v>323</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D310" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E310" s="7"/>
       <c r="F310" s="7"/>
@@ -8438,10 +8445,10 @@
         <v>324</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D311" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E311" s="7"/>
       <c r="F311" s="7"/>
@@ -8459,10 +8466,10 @@
         <v>325</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D312" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E312" s="7"/>
       <c r="F312" s="7"/>
@@ -8480,17 +8487,13 @@
         <v>326</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D313" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E313" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F313" s="4">
-        <v>4500.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E313" s="7"/>
+      <c r="F313" s="7"/>
       <c r="G313" s="7"/>
       <c r="H313" s="7"/>
       <c r="I313" s="7"/>
@@ -8505,13 +8508,17 @@
         <v>327</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D314" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E314" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F314" s="4">
         <v>4500.0</v>
       </c>
-      <c r="E314" s="7"/>
-      <c r="F314" s="7"/>
       <c r="G314" s="7"/>
       <c r="H314" s="7"/>
       <c r="I314" s="7"/>
@@ -8526,13 +8533,13 @@
         <v>328</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D315" s="4">
-        <v>51000.0</v>
-      </c>
-      <c r="E315" s="4"/>
-      <c r="F315" s="4"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E315" s="7"/>
+      <c r="F315" s="7"/>
       <c r="G315" s="7"/>
       <c r="H315" s="7"/>
       <c r="I315" s="7"/>
@@ -8547,17 +8554,13 @@
         <v>329</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D316" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E316" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F316" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>51000.0</v>
+      </c>
+      <c r="E316" s="4"/>
+      <c r="F316" s="4"/>
       <c r="G316" s="7"/>
       <c r="H316" s="7"/>
       <c r="I316" s="7"/>
@@ -8572,13 +8575,17 @@
         <v>330</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D317" s="4">
-        <v>52000.0</v>
-      </c>
-      <c r="E317" s="7"/>
-      <c r="F317" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E317" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F317" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G317" s="7"/>
       <c r="H317" s="7"/>
       <c r="I317" s="7"/>
@@ -8593,10 +8600,10 @@
         <v>331</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D318" s="4">
-        <v>1000.0</v>
+        <v>52000.0</v>
       </c>
       <c r="E318" s="7"/>
       <c r="F318" s="7"/>
@@ -8614,10 +8621,10 @@
         <v>332</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D319" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E319" s="7"/>
       <c r="F319" s="7"/>
@@ -8635,17 +8642,13 @@
         <v>333</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D320" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E320" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F320" s="4">
-        <v>17000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E320" s="7"/>
+      <c r="F320" s="7"/>
       <c r="G320" s="7"/>
       <c r="H320" s="7"/>
       <c r="I320" s="7"/>
@@ -8660,13 +8663,17 @@
         <v>334</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D321" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E321" s="7"/>
-      <c r="F321" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E321" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F321" s="4">
+        <v>17000.0</v>
+      </c>
       <c r="G321" s="7"/>
       <c r="H321" s="7"/>
       <c r="I321" s="7"/>
@@ -8681,17 +8688,13 @@
         <v>335</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D322" s="4">
-        <v>7000.0</v>
-      </c>
-      <c r="E322" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F322" s="4">
-        <v>32500.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E322" s="7"/>
+      <c r="F322" s="7"/>
       <c r="G322" s="7"/>
       <c r="H322" s="7"/>
       <c r="I322" s="7"/>
@@ -8706,13 +8709,17 @@
         <v>336</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D323" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E323" s="7"/>
-      <c r="F323" s="7"/>
+        <v>7000.0</v>
+      </c>
+      <c r="E323" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F323" s="4">
+        <v>32500.0</v>
+      </c>
       <c r="G323" s="7"/>
       <c r="H323" s="7"/>
       <c r="I323" s="7"/>
@@ -8727,10 +8734,10 @@
         <v>337</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D324" s="4">
-        <v>9500.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E324" s="7"/>
       <c r="F324" s="7"/>
@@ -8748,10 +8755,10 @@
         <v>338</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D325" s="4">
-        <v>3500.0</v>
+        <v>9500.0</v>
       </c>
       <c r="E325" s="7"/>
       <c r="F325" s="7"/>
@@ -8769,10 +8776,10 @@
         <v>339</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D326" s="4">
-        <v>5000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E326" s="7"/>
       <c r="F326" s="7"/>
@@ -8790,17 +8797,13 @@
         <v>340</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D327" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E327" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F327" s="4">
-        <v>22500.0</v>
-      </c>
+      <c r="E327" s="7"/>
+      <c r="F327" s="7"/>
       <c r="G327" s="7"/>
       <c r="H327" s="7"/>
       <c r="I327" s="7"/>
@@ -8815,16 +8818,16 @@
         <v>341</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D328" s="4">
-        <v>3500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E328" s="4">
         <v>5.0</v>
       </c>
       <c r="F328" s="4">
-        <v>12500.0</v>
+        <v>22500.0</v>
       </c>
       <c r="G328" s="7"/>
       <c r="H328" s="7"/>
@@ -8840,13 +8843,17 @@
         <v>342</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D329" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E329" s="4"/>
-      <c r="F329" s="4"/>
+      <c r="E329" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F329" s="4">
+        <v>12500.0</v>
+      </c>
       <c r="G329" s="7"/>
       <c r="H329" s="7"/>
       <c r="I329" s="7"/>
@@ -8861,14 +8868,14 @@
         <v>343</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D330" s="4">
-        <v>3000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E330" s="4"/>
       <c r="F330" s="4"/>
-      <c r="G330" s="4"/>
+      <c r="G330" s="7"/>
       <c r="H330" s="7"/>
       <c r="I330" s="7"/>
       <c r="J330" s="7"/>
@@ -8882,18 +8889,14 @@
         <v>344</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D331" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E331" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F331" s="4">
-        <v>11500.0</v>
-      </c>
-      <c r="G331" s="7"/>
+      <c r="E331" s="4"/>
+      <c r="F331" s="4"/>
+      <c r="G331" s="4"/>
       <c r="H331" s="7"/>
       <c r="I331" s="7"/>
       <c r="J331" s="7"/>
@@ -8907,13 +8910,17 @@
         <v>345</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D332" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E332" s="7"/>
-      <c r="F332" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E332" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F332" s="4">
+        <v>11500.0</v>
+      </c>
       <c r="G332" s="7"/>
       <c r="H332" s="7"/>
       <c r="I332" s="7"/>
@@ -8928,17 +8935,13 @@
         <v>346</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D333" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E333" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F333" s="4">
-        <v>22500.0</v>
-      </c>
+        <v>4000.0</v>
+      </c>
+      <c r="E333" s="7"/>
+      <c r="F333" s="7"/>
       <c r="G333" s="7"/>
       <c r="H333" s="7"/>
       <c r="I333" s="7"/>
@@ -8953,13 +8956,17 @@
         <v>347</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D334" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E334" s="7"/>
-      <c r="F334" s="7"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E334" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F334" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G334" s="7"/>
       <c r="H334" s="7"/>
       <c r="I334" s="7"/>
@@ -8974,10 +8981,10 @@
         <v>348</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D335" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E335" s="7"/>
       <c r="F335" s="7"/>
@@ -8995,10 +9002,10 @@
         <v>349</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D336" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E336" s="7"/>
       <c r="F336" s="7"/>
@@ -9016,10 +9023,10 @@
         <v>350</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>351</v>
+        <v>290</v>
       </c>
       <c r="D337" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E337" s="7"/>
       <c r="F337" s="7"/>
@@ -9034,13 +9041,13 @@
         <v>337</v>
       </c>
       <c r="B338" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C338" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="C338" s="5" t="s">
-        <v>351</v>
-      </c>
       <c r="D338" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E338" s="7"/>
       <c r="F338" s="7"/>
@@ -9058,10 +9065,10 @@
         <v>353</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D339" s="4">
-        <v>1000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E339" s="7"/>
       <c r="F339" s="7"/>
@@ -9079,10 +9086,10 @@
         <v>354</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D340" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E340" s="7"/>
       <c r="F340" s="7"/>
@@ -9100,10 +9107,10 @@
         <v>355</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D341" s="4">
-        <v>1000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E341" s="7"/>
       <c r="F341" s="7"/>
@@ -9121,10 +9128,10 @@
         <v>356</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D342" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E342" s="7"/>
       <c r="F342" s="7"/>
@@ -9142,10 +9149,10 @@
         <v>357</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D343" s="4">
-        <v>4000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E343" s="7"/>
       <c r="F343" s="7"/>
@@ -9163,10 +9170,10 @@
         <v>358</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D344" s="4">
-        <v>2500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E344" s="7"/>
       <c r="F344" s="7"/>
@@ -9184,10 +9191,10 @@
         <v>359</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D345" s="4">
-        <v>3000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E345" s="7"/>
       <c r="F345" s="7"/>
@@ -9205,10 +9212,10 @@
         <v>360</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D346" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E346" s="7"/>
       <c r="F346" s="7"/>
@@ -9226,10 +9233,10 @@
         <v>361</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D347" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E347" s="7"/>
       <c r="F347" s="7"/>
@@ -9247,17 +9254,13 @@
         <v>362</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D348" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E348" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F348" s="4">
         <v>3000.0</v>
       </c>
+      <c r="E348" s="7"/>
+      <c r="F348" s="7"/>
       <c r="G348" s="7"/>
       <c r="H348" s="7"/>
       <c r="I348" s="7"/>
@@ -9272,13 +9275,17 @@
         <v>363</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D349" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E349" s="7"/>
-      <c r="F349" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E349" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F349" s="4">
+        <v>3000.0</v>
+      </c>
       <c r="G349" s="7"/>
       <c r="H349" s="7"/>
       <c r="I349" s="7"/>
@@ -9293,10 +9300,10 @@
         <v>364</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D350" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E350" s="7"/>
       <c r="F350" s="7"/>
@@ -9314,10 +9321,10 @@
         <v>365</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D351" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E351" s="7"/>
       <c r="F351" s="7"/>
@@ -9335,10 +9342,10 @@
         <v>366</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D352" s="4">
-        <v>7000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E352" s="7"/>
       <c r="F352" s="7"/>
@@ -9356,10 +9363,10 @@
         <v>367</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D353" s="4">
-        <v>3000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E353" s="7"/>
       <c r="F353" s="7"/>
@@ -9377,10 +9384,10 @@
         <v>368</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D354" s="4">
-        <v>25000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E354" s="7"/>
       <c r="F354" s="7"/>
@@ -9398,10 +9405,10 @@
         <v>369</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D355" s="4">
-        <v>8000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E355" s="7"/>
       <c r="F355" s="7"/>
@@ -9419,10 +9426,10 @@
         <v>370</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D356" s="4">
-        <v>4000.0</v>
+        <v>8000.0</v>
       </c>
       <c r="E356" s="7"/>
       <c r="F356" s="7"/>
@@ -9440,10 +9447,10 @@
         <v>371</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="D357" s="4">
-        <v>2000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E357" s="7"/>
       <c r="F357" s="7"/>
@@ -9458,13 +9465,13 @@
         <v>357</v>
       </c>
       <c r="B358" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="C358" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="C358" s="5" t="s">
-        <v>372</v>
-      </c>
       <c r="D358" s="4">
-        <v>45000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E358" s="7"/>
       <c r="F358" s="7"/>
@@ -9482,10 +9489,10 @@
         <v>374</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D359" s="4">
-        <v>2500.0</v>
+        <v>45000.0</v>
       </c>
       <c r="E359" s="7"/>
       <c r="F359" s="7"/>
@@ -9503,7 +9510,7 @@
         <v>375</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D360" s="4">
         <v>2500.0</v>
@@ -9524,10 +9531,10 @@
         <v>376</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D361" s="4">
-        <v>4000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E361" s="7"/>
       <c r="F361" s="7"/>
@@ -9545,10 +9552,10 @@
         <v>377</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D362" s="4">
-        <v>5000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E362" s="7"/>
       <c r="F362" s="7"/>
@@ -9566,16 +9573,16 @@
         <v>378</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D363" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E363" s="7"/>
       <c r="F363" s="7"/>
       <c r="G363" s="7"/>
       <c r="H363" s="7"/>
-      <c r="I363" s="4"/>
+      <c r="I363" s="7"/>
       <c r="J363" s="7"/>
     </row>
     <row r="364">
@@ -9587,16 +9594,16 @@
         <v>379</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D364" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E364" s="7"/>
       <c r="F364" s="7"/>
       <c r="G364" s="7"/>
       <c r="H364" s="7"/>
-      <c r="I364" s="7"/>
+      <c r="I364" s="4"/>
       <c r="J364" s="7"/>
     </row>
     <row r="365">
@@ -9608,10 +9615,10 @@
         <v>380</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D365" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E365" s="7"/>
       <c r="F365" s="7"/>
@@ -9629,10 +9636,10 @@
         <v>381</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D366" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E366" s="7"/>
       <c r="F366" s="7"/>
@@ -9650,10 +9657,10 @@
         <v>382</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D367" s="4">
-        <v>1500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E367" s="7"/>
       <c r="F367" s="7"/>
@@ -9671,10 +9678,10 @@
         <v>383</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D368" s="4">
-        <v>12000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E368" s="7"/>
       <c r="F368" s="7"/>
@@ -9692,10 +9699,10 @@
         <v>384</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D369" s="4">
-        <v>3000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E369" s="7"/>
       <c r="F369" s="7"/>
@@ -9713,10 +9720,10 @@
         <v>385</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D370" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E370" s="7"/>
       <c r="F370" s="7"/>
@@ -9734,10 +9741,10 @@
         <v>386</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D371" s="4">
-        <v>25000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E371" s="7"/>
       <c r="F371" s="7"/>
@@ -9755,10 +9762,10 @@
         <v>387</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D372" s="4">
-        <v>9000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E372" s="7"/>
       <c r="F372" s="7"/>
@@ -9776,12 +9783,12 @@
         <v>388</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D373" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E373" s="4"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E373" s="7"/>
       <c r="F373" s="7"/>
       <c r="G373" s="7"/>
       <c r="H373" s="7"/>
@@ -9797,12 +9804,12 @@
         <v>389</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D374" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="E374" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E374" s="4"/>
       <c r="F374" s="7"/>
       <c r="G374" s="7"/>
       <c r="H374" s="7"/>
@@ -9818,10 +9825,10 @@
         <v>390</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D375" s="4">
-        <v>4500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E375" s="7"/>
       <c r="F375" s="7"/>
@@ -9839,10 +9846,10 @@
         <v>391</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D376" s="4">
-        <v>500.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E376" s="7"/>
       <c r="F376" s="7"/>
@@ -9860,10 +9867,10 @@
         <v>392</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D377" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E377" s="7"/>
       <c r="F377" s="7"/>
@@ -9881,10 +9888,10 @@
         <v>393</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D378" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E378" s="7"/>
       <c r="F378" s="7"/>
@@ -9898,21 +9905,21 @@
         <f t="shared" si="1"/>
         <v>378</v>
       </c>
-      <c r="B379" s="9" t="s">
+      <c r="B379" s="5" t="s">
         <v>394</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="D379" s="10">
-        <v>4500.0</v>
-      </c>
-      <c r="E379" s="11"/>
-      <c r="F379" s="11"/>
-      <c r="G379" s="11"/>
-      <c r="H379" s="11"/>
-      <c r="I379" s="11"/>
-      <c r="J379" s="11"/>
+        <v>373</v>
+      </c>
+      <c r="D379" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E379" s="7"/>
+      <c r="F379" s="7"/>
+      <c r="G379" s="7"/>
+      <c r="H379" s="7"/>
+      <c r="I379" s="7"/>
+      <c r="J379" s="7"/>
     </row>
     <row r="380">
       <c r="A380" s="4">
@@ -9923,10 +9930,10 @@
         <v>395</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D380" s="10">
-        <v>50000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E380" s="11"/>
       <c r="F380" s="11"/>
@@ -9944,10 +9951,10 @@
         <v>396</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D381" s="10">
-        <v>12000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="E381" s="11"/>
       <c r="F381" s="11"/>
@@ -9961,14 +9968,14 @@
         <f t="shared" si="1"/>
         <v>381</v>
       </c>
-      <c r="B382" s="5" t="s">
+      <c r="B382" s="9" t="s">
         <v>397</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D382" s="10">
-        <v>4500.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E382" s="11"/>
       <c r="F382" s="11"/>
@@ -9982,14 +9989,14 @@
         <f t="shared" si="1"/>
         <v>382</v>
       </c>
-      <c r="B383" s="9" t="s">
+      <c r="B383" s="5" t="s">
         <v>398</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="D383" s="10">
-        <v>3000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E383" s="11"/>
       <c r="F383" s="11"/>
@@ -10007,10 +10014,10 @@
         <v>399</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D384" s="10">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E384" s="11"/>
       <c r="F384" s="11"/>
@@ -10028,10 +10035,10 @@
         <v>400</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D385" s="10">
-        <v>6000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E385" s="11"/>
       <c r="F385" s="11"/>
@@ -10049,10 +10056,10 @@
         <v>401</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>351</v>
+        <v>400</v>
       </c>
       <c r="D386" s="10">
-        <v>12000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="E386" s="11"/>
       <c r="F386" s="11"/>
@@ -10070,17 +10077,13 @@
         <v>402</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D387" s="10">
-        <v>200.0</v>
-      </c>
-      <c r="E387" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="F387" s="10">
-        <v>500.0</v>
-      </c>
+        <v>12000.0</v>
+      </c>
+      <c r="E387" s="11"/>
+      <c r="F387" s="11"/>
       <c r="G387" s="11"/>
       <c r="H387" s="11"/>
       <c r="I387" s="11"/>
@@ -10095,16 +10098,16 @@
         <v>403</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D388" s="10">
-        <v>5000.0</v>
+        <v>200.0</v>
       </c>
       <c r="E388" s="10">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F388" s="10">
-        <v>4500.0</v>
+        <v>500.0</v>
       </c>
       <c r="G388" s="11"/>
       <c r="H388" s="11"/>
@@ -10112,12 +10115,25 @@
       <c r="J388" s="11"/>
     </row>
     <row r="389">
-      <c r="A389" s="12"/>
-      <c r="B389" s="12"/>
-      <c r="C389" s="12"/>
-      <c r="D389" s="11"/>
-      <c r="E389" s="11"/>
-      <c r="F389" s="11"/>
+      <c r="A389" s="4">
+        <f t="shared" si="1"/>
+        <v>388</v>
+      </c>
+      <c r="B389" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="C389" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="D389" s="10">
+        <v>5000.0</v>
+      </c>
+      <c r="E389" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="F389" s="10">
+        <v>4500.0</v>
+      </c>
       <c r="G389" s="11"/>
       <c r="H389" s="11"/>
       <c r="I389" s="11"/>
@@ -11291,13 +11307,13 @@
       <c r="A487" s="12"/>
       <c r="B487" s="12"/>
       <c r="C487" s="12"/>
-      <c r="D487" s="12"/>
-      <c r="E487" s="12"/>
-      <c r="F487" s="12"/>
-      <c r="G487" s="12"/>
-      <c r="H487" s="12"/>
-      <c r="I487" s="12"/>
-      <c r="J487" s="12"/>
+      <c r="D487" s="11"/>
+      <c r="E487" s="11"/>
+      <c r="F487" s="11"/>
+      <c r="G487" s="11"/>
+      <c r="H487" s="11"/>
+      <c r="I487" s="11"/>
+      <c r="J487" s="11"/>
     </row>
     <row r="488">
       <c r="A488" s="12"/>
@@ -19711,15 +19727,27 @@
       <c r="I1188" s="12"/>
       <c r="J1188" s="12"/>
     </row>
+    <row r="1189">
+      <c r="A1189" s="12"/>
+      <c r="B1189" s="12"/>
+      <c r="C1189" s="12"/>
+      <c r="D1189" s="12"/>
+      <c r="E1189" s="12"/>
+      <c r="F1189" s="12"/>
+      <c r="G1189" s="12"/>
+      <c r="H1189" s="12"/>
+      <c r="I1189" s="12"/>
+      <c r="J1189" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$388"/>
-  <conditionalFormatting sqref="A2:J1188">
+  <autoFilter ref="$B$1:$C$389"/>
+  <conditionalFormatting sqref="A2:J1189">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C388">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C389">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19799,7 +19827,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -19818,7 +19846,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -19837,7 +19865,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -19875,7 +19903,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -19913,7 +19941,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -19970,7 +19998,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -19989,7 +20017,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -20008,7 +20036,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -20046,7 +20074,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -20065,7 +20093,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -20103,7 +20131,7 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
@@ -20122,7 +20150,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -20141,7 +20169,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -20255,7 +20283,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -20293,7 +20321,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -20312,7 +20340,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -20350,7 +20378,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -20369,7 +20397,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -20388,7 +20416,7 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
@@ -20407,7 +20435,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -20426,7 +20454,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -20445,7 +20473,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -20464,7 +20492,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -20483,7 +20511,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -20502,7 +20530,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -20521,7 +20549,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -20540,7 +20568,7 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
@@ -20559,7 +20587,7 @@
         <v>GROSIR42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$389</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$390</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$260</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="432">
   <si>
     <t>Barcode</t>
   </si>
@@ -1068,6 +1068,9 @@
   </si>
   <si>
     <t>Fair and Lovely Facial Foam</t>
+  </si>
+  <si>
+    <t>Posh</t>
   </si>
   <si>
     <t>Obat Nyamuk Bakar</t>
@@ -1695,7 +1698,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A389" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A390" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -9044,10 +9047,10 @@
         <v>351</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>352</v>
+        <v>290</v>
       </c>
       <c r="D338" s="4">
-        <v>1000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E338" s="7"/>
       <c r="F338" s="7"/>
@@ -9062,13 +9065,13 @@
         <v>338</v>
       </c>
       <c r="B339" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="C339" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="C339" s="5" t="s">
-        <v>352</v>
-      </c>
       <c r="D339" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E339" s="7"/>
       <c r="F339" s="7"/>
@@ -9086,10 +9089,10 @@
         <v>354</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D340" s="4">
-        <v>1000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E340" s="7"/>
       <c r="F340" s="7"/>
@@ -9107,10 +9110,10 @@
         <v>355</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D341" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E341" s="7"/>
       <c r="F341" s="7"/>
@@ -9128,10 +9131,10 @@
         <v>356</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D342" s="4">
-        <v>1000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E342" s="7"/>
       <c r="F342" s="7"/>
@@ -9149,10 +9152,10 @@
         <v>357</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D343" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E343" s="7"/>
       <c r="F343" s="7"/>
@@ -9170,10 +9173,10 @@
         <v>358</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D344" s="4">
-        <v>4000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E344" s="7"/>
       <c r="F344" s="7"/>
@@ -9191,10 +9194,10 @@
         <v>359</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D345" s="4">
-        <v>2500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E345" s="7"/>
       <c r="F345" s="7"/>
@@ -9212,10 +9215,10 @@
         <v>360</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D346" s="4">
-        <v>3000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E346" s="7"/>
       <c r="F346" s="7"/>
@@ -9233,10 +9236,10 @@
         <v>361</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D347" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E347" s="7"/>
       <c r="F347" s="7"/>
@@ -9254,10 +9257,10 @@
         <v>362</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D348" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E348" s="7"/>
       <c r="F348" s="7"/>
@@ -9275,17 +9278,13 @@
         <v>363</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D349" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E349" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F349" s="4">
         <v>3000.0</v>
       </c>
+      <c r="E349" s="7"/>
+      <c r="F349" s="7"/>
       <c r="G349" s="7"/>
       <c r="H349" s="7"/>
       <c r="I349" s="7"/>
@@ -9300,13 +9299,17 @@
         <v>364</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D350" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E350" s="7"/>
-      <c r="F350" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E350" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F350" s="4">
+        <v>3000.0</v>
+      </c>
       <c r="G350" s="7"/>
       <c r="H350" s="7"/>
       <c r="I350" s="7"/>
@@ -9321,10 +9324,10 @@
         <v>365</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D351" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E351" s="7"/>
       <c r="F351" s="7"/>
@@ -9342,10 +9345,10 @@
         <v>366</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D352" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E352" s="7"/>
       <c r="F352" s="7"/>
@@ -9363,10 +9366,10 @@
         <v>367</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D353" s="4">
-        <v>7000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E353" s="7"/>
       <c r="F353" s="7"/>
@@ -9384,10 +9387,10 @@
         <v>368</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D354" s="4">
-        <v>3000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E354" s="7"/>
       <c r="F354" s="7"/>
@@ -9405,10 +9408,10 @@
         <v>369</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D355" s="4">
-        <v>25000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E355" s="7"/>
       <c r="F355" s="7"/>
@@ -9426,10 +9429,10 @@
         <v>370</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D356" s="4">
-        <v>8000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E356" s="7"/>
       <c r="F356" s="7"/>
@@ -9447,10 +9450,10 @@
         <v>371</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D357" s="4">
-        <v>4000.0</v>
+        <v>8000.0</v>
       </c>
       <c r="E357" s="7"/>
       <c r="F357" s="7"/>
@@ -9468,10 +9471,10 @@
         <v>372</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="D358" s="4">
-        <v>2000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E358" s="7"/>
       <c r="F358" s="7"/>
@@ -9486,13 +9489,13 @@
         <v>358</v>
       </c>
       <c r="B359" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="C359" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="C359" s="5" t="s">
-        <v>373</v>
-      </c>
       <c r="D359" s="4">
-        <v>45000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E359" s="7"/>
       <c r="F359" s="7"/>
@@ -9510,10 +9513,10 @@
         <v>375</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D360" s="4">
-        <v>2500.0</v>
+        <v>45000.0</v>
       </c>
       <c r="E360" s="7"/>
       <c r="F360" s="7"/>
@@ -9531,7 +9534,7 @@
         <v>376</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D361" s="4">
         <v>2500.0</v>
@@ -9552,10 +9555,10 @@
         <v>377</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D362" s="4">
-        <v>4000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E362" s="7"/>
       <c r="F362" s="7"/>
@@ -9573,10 +9576,10 @@
         <v>378</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D363" s="4">
-        <v>5000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E363" s="7"/>
       <c r="F363" s="7"/>
@@ -9594,16 +9597,16 @@
         <v>379</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D364" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E364" s="7"/>
       <c r="F364" s="7"/>
       <c r="G364" s="7"/>
       <c r="H364" s="7"/>
-      <c r="I364" s="4"/>
+      <c r="I364" s="7"/>
       <c r="J364" s="7"/>
     </row>
     <row r="365">
@@ -9615,16 +9618,16 @@
         <v>380</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D365" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E365" s="7"/>
       <c r="F365" s="7"/>
       <c r="G365" s="7"/>
       <c r="H365" s="7"/>
-      <c r="I365" s="7"/>
+      <c r="I365" s="4"/>
       <c r="J365" s="7"/>
     </row>
     <row r="366">
@@ -9636,10 +9639,10 @@
         <v>381</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D366" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E366" s="7"/>
       <c r="F366" s="7"/>
@@ -9657,10 +9660,10 @@
         <v>382</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D367" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E367" s="7"/>
       <c r="F367" s="7"/>
@@ -9678,10 +9681,10 @@
         <v>383</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D368" s="4">
-        <v>1500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E368" s="7"/>
       <c r="F368" s="7"/>
@@ -9699,10 +9702,10 @@
         <v>384</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D369" s="4">
-        <v>12000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E369" s="7"/>
       <c r="F369" s="7"/>
@@ -9720,10 +9723,10 @@
         <v>385</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D370" s="4">
-        <v>3000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E370" s="7"/>
       <c r="F370" s="7"/>
@@ -9741,10 +9744,10 @@
         <v>386</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D371" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E371" s="7"/>
       <c r="F371" s="7"/>
@@ -9762,10 +9765,10 @@
         <v>387</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D372" s="4">
-        <v>25000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E372" s="7"/>
       <c r="F372" s="7"/>
@@ -9783,10 +9786,10 @@
         <v>388</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D373" s="4">
-        <v>9000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E373" s="7"/>
       <c r="F373" s="7"/>
@@ -9804,12 +9807,12 @@
         <v>389</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D374" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E374" s="4"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E374" s="7"/>
       <c r="F374" s="7"/>
       <c r="G374" s="7"/>
       <c r="H374" s="7"/>
@@ -9825,12 +9828,12 @@
         <v>390</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D375" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="E375" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E375" s="4"/>
       <c r="F375" s="7"/>
       <c r="G375" s="7"/>
       <c r="H375" s="7"/>
@@ -9846,10 +9849,10 @@
         <v>391</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D376" s="4">
-        <v>4500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E376" s="7"/>
       <c r="F376" s="7"/>
@@ -9867,10 +9870,10 @@
         <v>392</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D377" s="4">
-        <v>500.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E377" s="7"/>
       <c r="F377" s="7"/>
@@ -9888,10 +9891,10 @@
         <v>393</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D378" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E378" s="7"/>
       <c r="F378" s="7"/>
@@ -9909,10 +9912,10 @@
         <v>394</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D379" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E379" s="7"/>
       <c r="F379" s="7"/>
@@ -9926,21 +9929,21 @@
         <f t="shared" si="1"/>
         <v>379</v>
       </c>
-      <c r="B380" s="9" t="s">
+      <c r="B380" s="5" t="s">
         <v>395</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="D380" s="10">
-        <v>4500.0</v>
-      </c>
-      <c r="E380" s="11"/>
-      <c r="F380" s="11"/>
-      <c r="G380" s="11"/>
-      <c r="H380" s="11"/>
-      <c r="I380" s="11"/>
-      <c r="J380" s="11"/>
+        <v>374</v>
+      </c>
+      <c r="D380" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E380" s="7"/>
+      <c r="F380" s="7"/>
+      <c r="G380" s="7"/>
+      <c r="H380" s="7"/>
+      <c r="I380" s="7"/>
+      <c r="J380" s="7"/>
     </row>
     <row r="381">
       <c r="A381" s="4">
@@ -9951,10 +9954,10 @@
         <v>396</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D381" s="10">
-        <v>50000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E381" s="11"/>
       <c r="F381" s="11"/>
@@ -9972,10 +9975,10 @@
         <v>397</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D382" s="10">
-        <v>12000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="E382" s="11"/>
       <c r="F382" s="11"/>
@@ -9989,14 +9992,14 @@
         <f t="shared" si="1"/>
         <v>382</v>
       </c>
-      <c r="B383" s="5" t="s">
+      <c r="B383" s="9" t="s">
         <v>398</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D383" s="10">
-        <v>4500.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E383" s="11"/>
       <c r="F383" s="11"/>
@@ -10010,14 +10013,14 @@
         <f t="shared" si="1"/>
         <v>383</v>
       </c>
-      <c r="B384" s="9" t="s">
+      <c r="B384" s="5" t="s">
         <v>399</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="D384" s="10">
-        <v>3000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E384" s="11"/>
       <c r="F384" s="11"/>
@@ -10035,10 +10038,10 @@
         <v>400</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D385" s="10">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E385" s="11"/>
       <c r="F385" s="11"/>
@@ -10056,10 +10059,10 @@
         <v>401</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D386" s="10">
-        <v>6000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E386" s="11"/>
       <c r="F386" s="11"/>
@@ -10077,10 +10080,10 @@
         <v>402</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>352</v>
+        <v>401</v>
       </c>
       <c r="D387" s="10">
-        <v>12000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="E387" s="11"/>
       <c r="F387" s="11"/>
@@ -10098,17 +10101,13 @@
         <v>403</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D388" s="10">
-        <v>200.0</v>
-      </c>
-      <c r="E388" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="F388" s="10">
-        <v>500.0</v>
-      </c>
+        <v>12000.0</v>
+      </c>
+      <c r="E388" s="11"/>
+      <c r="F388" s="11"/>
       <c r="G388" s="11"/>
       <c r="H388" s="11"/>
       <c r="I388" s="11"/>
@@ -10123,16 +10122,16 @@
         <v>404</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D389" s="10">
-        <v>5000.0</v>
+        <v>200.0</v>
       </c>
       <c r="E389" s="10">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F389" s="10">
-        <v>4500.0</v>
+        <v>500.0</v>
       </c>
       <c r="G389" s="11"/>
       <c r="H389" s="11"/>
@@ -10140,12 +10139,25 @@
       <c r="J389" s="11"/>
     </row>
     <row r="390">
-      <c r="A390" s="12"/>
-      <c r="B390" s="12"/>
-      <c r="C390" s="12"/>
-      <c r="D390" s="11"/>
-      <c r="E390" s="11"/>
-      <c r="F390" s="11"/>
+      <c r="A390" s="4">
+        <f t="shared" si="1"/>
+        <v>389</v>
+      </c>
+      <c r="B390" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="C390" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D390" s="10">
+        <v>5000.0</v>
+      </c>
+      <c r="E390" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="F390" s="10">
+        <v>4500.0</v>
+      </c>
       <c r="G390" s="11"/>
       <c r="H390" s="11"/>
       <c r="I390" s="11"/>
@@ -11319,13 +11331,13 @@
       <c r="A488" s="12"/>
       <c r="B488" s="12"/>
       <c r="C488" s="12"/>
-      <c r="D488" s="12"/>
-      <c r="E488" s="12"/>
-      <c r="F488" s="12"/>
-      <c r="G488" s="12"/>
-      <c r="H488" s="12"/>
-      <c r="I488" s="12"/>
-      <c r="J488" s="12"/>
+      <c r="D488" s="11"/>
+      <c r="E488" s="11"/>
+      <c r="F488" s="11"/>
+      <c r="G488" s="11"/>
+      <c r="H488" s="11"/>
+      <c r="I488" s="11"/>
+      <c r="J488" s="11"/>
     </row>
     <row r="489">
       <c r="A489" s="12"/>
@@ -19739,15 +19751,27 @@
       <c r="I1189" s="12"/>
       <c r="J1189" s="12"/>
     </row>
+    <row r="1190">
+      <c r="A1190" s="12"/>
+      <c r="B1190" s="12"/>
+      <c r="C1190" s="12"/>
+      <c r="D1190" s="12"/>
+      <c r="E1190" s="12"/>
+      <c r="F1190" s="12"/>
+      <c r="G1190" s="12"/>
+      <c r="H1190" s="12"/>
+      <c r="I1190" s="12"/>
+      <c r="J1190" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$389"/>
-  <conditionalFormatting sqref="A2:J1189">
+  <autoFilter ref="$B$1:$C$390"/>
+  <conditionalFormatting sqref="A2:J1190">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C389">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C390">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19827,7 +19851,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -19846,7 +19870,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -19865,7 +19889,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -19903,7 +19927,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -19941,7 +19965,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -19998,7 +20022,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -20017,7 +20041,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -20036,7 +20060,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -20074,7 +20098,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -20093,7 +20117,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -20131,7 +20155,7 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
@@ -20150,7 +20174,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -20169,7 +20193,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -20283,7 +20307,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -20321,7 +20345,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -20340,7 +20364,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -20378,7 +20402,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -20397,7 +20421,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -20416,7 +20440,7 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
@@ -20435,7 +20459,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -20454,7 +20478,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -20473,7 +20497,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -20492,7 +20516,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -20511,7 +20535,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -20530,7 +20554,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -20549,7 +20573,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -20568,7 +20592,7 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
@@ -20587,7 +20611,7 @@
         <v>GROSIR42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -2023,7 +2023,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="4">
-        <v>19500.0</v>
+        <v>20500.0</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -3009,7 +3009,7 @@
         <v>11</v>
       </c>
       <c r="D63" s="4">
-        <v>16500.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E63" s="7"/>
       <c r="F63" s="7"/>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$390</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$404</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$260</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="446">
   <si>
     <t>Barcode</t>
   </si>
@@ -113,6 +113,9 @@
     <t>Teh Pucuk Dus</t>
   </si>
   <si>
+    <t>Teh Kotak</t>
+  </si>
+  <si>
     <t>Teh Kotak Dus</t>
   </si>
   <si>
@@ -359,6 +362,12 @@
     <t>Susu Frisian Flag Pak</t>
   </si>
   <si>
+    <t>STMJ</t>
+  </si>
+  <si>
+    <t>STMJ Renceng</t>
+  </si>
+  <si>
     <t>Extrajoss</t>
   </si>
   <si>
@@ -401,6 +410,9 @@
     <t>Tepung Bumbu Serba Guna Sasa</t>
   </si>
   <si>
+    <t>Tepung Bumbu Serba Guna Sasa Renceng</t>
+  </si>
+  <si>
     <t>Masako besar</t>
   </si>
   <si>
@@ -1154,9 +1166,21 @@
     <t>Antangin</t>
   </si>
   <si>
+    <t>Antangin Box</t>
+  </si>
+  <si>
     <t>Tolak Angin</t>
   </si>
   <si>
+    <t>Tolak Angin Box</t>
+  </si>
+  <si>
+    <t>Tolak Linu</t>
+  </si>
+  <si>
+    <t>Tolak Linu Box</t>
+  </si>
+  <si>
     <t>Bodrex Satuan</t>
   </si>
   <si>
@@ -1226,13 +1250,31 @@
     <t>Mie isi 2 Seduh</t>
   </si>
   <si>
-    <t>amplop dus</t>
+    <t>amplop box</t>
   </si>
   <si>
     <t>amplop</t>
   </si>
   <si>
     <t>Agar Swallow</t>
+  </si>
+  <si>
+    <t>Choki choki</t>
+  </si>
+  <si>
+    <t>Fruta Gumnmy</t>
+  </si>
+  <si>
+    <t>Chitato</t>
+  </si>
+  <si>
+    <t>Taro Renceng</t>
+  </si>
+  <si>
+    <t>Garuda Renceng</t>
+  </si>
+  <si>
+    <t>Sosis So Nice Toples</t>
   </si>
   <si>
     <t>Djarum Coklat Bungkus SLOP</t>
@@ -1698,7 +1740,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A390" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A404" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -2136,7 +2178,7 @@
         <v>16</v>
       </c>
       <c r="D22" s="4">
-        <v>79000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
@@ -2157,14 +2199,10 @@
         <v>16</v>
       </c>
       <c r="D23" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E23" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F23" s="4">
-        <v>16500.0</v>
-      </c>
+        <v>80000.0</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
@@ -2182,14 +2220,18 @@
         <v>16</v>
       </c>
       <c r="D24" s="4">
-        <v>39000.0</v>
-      </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E24" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F24" s="4">
+        <v>16500.0</v>
+      </c>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
     </row>
     <row r="25">
       <c r="A25" s="4">
@@ -2203,14 +2245,14 @@
         <v>16</v>
       </c>
       <c r="D25" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
+        <v>39000.0</v>
+      </c>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
     </row>
     <row r="26">
       <c r="A26" s="4">
@@ -2224,7 +2266,7 @@
         <v>16</v>
       </c>
       <c r="D26" s="4">
-        <v>29000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
@@ -2245,7 +2287,7 @@
         <v>16</v>
       </c>
       <c r="D27" s="4">
-        <v>3500.0</v>
+        <v>29000.0</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
@@ -2266,7 +2308,7 @@
         <v>16</v>
       </c>
       <c r="D28" s="4">
-        <v>35000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -2287,12 +2329,12 @@
         <v>16</v>
       </c>
       <c r="D29" s="4">
-        <v>3500.0</v>
+        <v>35000.0</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="4"/>
+      <c r="H29" s="6"/>
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
     </row>
@@ -2308,12 +2350,12 @@
         <v>16</v>
       </c>
       <c r="D30" s="4">
-        <v>19000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
+      <c r="H30" s="4"/>
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
     </row>
@@ -2329,7 +2371,7 @@
         <v>16</v>
       </c>
       <c r="D31" s="4">
-        <v>2500.0</v>
+        <v>19000.0</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -2350,14 +2392,10 @@
         <v>16</v>
       </c>
       <c r="D32" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E32" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F32" s="4">
-        <v>13500.0</v>
-      </c>
+        <v>2500.0</v>
+      </c>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
@@ -2375,10 +2413,14 @@
         <v>16</v>
       </c>
       <c r="D33" s="4">
-        <v>31000.0</v>
-      </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E33" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F33" s="4">
+        <v>13500.0</v>
+      </c>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
@@ -2396,7 +2438,7 @@
         <v>16</v>
       </c>
       <c r="D34" s="4">
-        <v>2500.0</v>
+        <v>31000.0</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
@@ -2417,7 +2459,7 @@
         <v>16</v>
       </c>
       <c r="D35" s="4">
-        <v>46000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
@@ -2438,7 +2480,7 @@
         <v>16</v>
       </c>
       <c r="D36" s="4">
-        <v>6000.0</v>
+        <v>46000.0</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
@@ -2459,7 +2501,7 @@
         <v>16</v>
       </c>
       <c r="D37" s="4">
-        <v>52000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
@@ -2480,7 +2522,7 @@
         <v>16</v>
       </c>
       <c r="D38" s="4">
-        <v>21000.0</v>
+        <v>52000.0</v>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
@@ -2501,7 +2543,7 @@
         <v>16</v>
       </c>
       <c r="D39" s="4">
-        <v>22000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
@@ -2522,7 +2564,7 @@
         <v>16</v>
       </c>
       <c r="D40" s="4">
-        <v>2000.0</v>
+        <v>22000.0</v>
       </c>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
@@ -2543,7 +2585,7 @@
         <v>16</v>
       </c>
       <c r="D41" s="4">
-        <v>32000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
@@ -2564,7 +2606,7 @@
         <v>16</v>
       </c>
       <c r="D42" s="4">
-        <v>47000.0</v>
+        <v>32000.0</v>
       </c>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
@@ -2585,7 +2627,7 @@
         <v>16</v>
       </c>
       <c r="D43" s="4">
-        <v>3500.0</v>
+        <v>47000.0</v>
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
@@ -2606,7 +2648,7 @@
         <v>16</v>
       </c>
       <c r="D44" s="4">
-        <v>36000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
@@ -2627,7 +2669,7 @@
         <v>16</v>
       </c>
       <c r="D45" s="4">
-        <v>7000.0</v>
+        <v>36000.0</v>
       </c>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
@@ -2648,7 +2690,7 @@
         <v>16</v>
       </c>
       <c r="D46" s="4">
-        <v>150000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
@@ -2669,14 +2711,10 @@
         <v>16</v>
       </c>
       <c r="D47" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E47" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F47" s="4">
-        <v>16000.0</v>
-      </c>
+        <v>150000.0</v>
+      </c>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
@@ -2694,10 +2732,14 @@
         <v>16</v>
       </c>
       <c r="D48" s="4">
-        <v>128000.0</v>
-      </c>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E48" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F48" s="4">
+        <v>16000.0</v>
+      </c>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
@@ -2715,14 +2757,14 @@
         <v>16</v>
       </c>
       <c r="D49" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
+        <v>128000.0</v>
+      </c>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
     </row>
     <row r="50">
       <c r="A50" s="4">
@@ -2736,14 +2778,14 @@
         <v>16</v>
       </c>
       <c r="D50" s="4">
-        <v>36000.0</v>
-      </c>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
     </row>
     <row r="51">
       <c r="A51" s="4">
@@ -2754,10 +2796,10 @@
         <v>61</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D51" s="4">
-        <v>20000.0</v>
+        <v>36000.0</v>
       </c>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
@@ -2778,7 +2820,7 @@
         <v>11</v>
       </c>
       <c r="D52" s="4">
-        <v>1000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
@@ -2799,14 +2841,14 @@
         <v>11</v>
       </c>
       <c r="D53" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
     </row>
     <row r="54">
       <c r="A54" s="4">
@@ -2820,14 +2862,14 @@
         <v>11</v>
       </c>
       <c r="D54" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
     </row>
     <row r="55">
       <c r="A55" s="4">
@@ -2841,14 +2883,14 @@
         <v>11</v>
       </c>
       <c r="D55" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
+        <v>2500.0</v>
+      </c>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
     </row>
     <row r="56">
       <c r="A56" s="4">
@@ -2862,14 +2904,14 @@
         <v>11</v>
       </c>
       <c r="D56" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
+        <v>21000.0</v>
+      </c>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
     </row>
     <row r="57">
       <c r="A57" s="4">
@@ -2883,7 +2925,7 @@
         <v>11</v>
       </c>
       <c r="D57" s="4">
-        <v>9500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
@@ -2904,7 +2946,7 @@
         <v>11</v>
       </c>
       <c r="D58" s="4">
-        <v>4500.0</v>
+        <v>9500.0</v>
       </c>
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
@@ -2925,14 +2967,14 @@
         <v>11</v>
       </c>
       <c r="D59" s="4">
-        <v>38000.0</v>
-      </c>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="7"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
     </row>
     <row r="60">
       <c r="A60" s="4">
@@ -2946,14 +2988,14 @@
         <v>11</v>
       </c>
       <c r="D60" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
+        <v>38000.0</v>
+      </c>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
     </row>
     <row r="61">
       <c r="A61" s="4">
@@ -2967,14 +3009,14 @@
         <v>11</v>
       </c>
       <c r="D61" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
     </row>
     <row r="62">
       <c r="A62" s="4">
@@ -2988,14 +3030,14 @@
         <v>11</v>
       </c>
       <c r="D62" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
+        <v>17000.0</v>
+      </c>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
     </row>
     <row r="63">
       <c r="A63" s="4">
@@ -3009,14 +3051,14 @@
         <v>11</v>
       </c>
       <c r="D63" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="7"/>
-      <c r="H63" s="7"/>
-      <c r="I63" s="7"/>
-      <c r="J63" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
     </row>
     <row r="64">
       <c r="A64" s="4">
@@ -3030,14 +3072,14 @@
         <v>11</v>
       </c>
       <c r="D64" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
+        <v>17000.0</v>
+      </c>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
     </row>
     <row r="65">
       <c r="A65" s="4">
@@ -3051,7 +3093,7 @@
         <v>11</v>
       </c>
       <c r="D65" s="4">
-        <v>15000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
@@ -3072,7 +3114,7 @@
         <v>11</v>
       </c>
       <c r="D66" s="4">
-        <v>2000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
@@ -3093,14 +3135,14 @@
         <v>11</v>
       </c>
       <c r="D67" s="4">
-        <v>15000.0</v>
-      </c>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="7"/>
-      <c r="I67" s="7"/>
-      <c r="J67" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
     </row>
     <row r="68">
       <c r="A68" s="4">
@@ -3114,14 +3156,14 @@
         <v>11</v>
       </c>
       <c r="D68" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
+        <v>15000.0</v>
+      </c>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="7"/>
     </row>
     <row r="69">
       <c r="A69" s="4">
@@ -3135,7 +3177,7 @@
         <v>11</v>
       </c>
       <c r="D69" s="4">
-        <v>15000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
@@ -3156,7 +3198,7 @@
         <v>11</v>
       </c>
       <c r="D70" s="4">
-        <v>2000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
@@ -3177,7 +3219,7 @@
         <v>11</v>
       </c>
       <c r="D71" s="4">
-        <v>15000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
@@ -3198,7 +3240,7 @@
         <v>11</v>
       </c>
       <c r="D72" s="4">
-        <v>2000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
@@ -3219,14 +3261,14 @@
         <v>11</v>
       </c>
       <c r="D73" s="4">
-        <v>15000.0</v>
-      </c>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="7"/>
-      <c r="J73" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="6"/>
     </row>
     <row r="74">
       <c r="A74" s="4">
@@ -3240,14 +3282,14 @@
         <v>11</v>
       </c>
       <c r="D74" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
+        <v>15000.0</v>
+      </c>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
     </row>
     <row r="75">
       <c r="A75" s="4">
@@ -3261,7 +3303,7 @@
         <v>11</v>
       </c>
       <c r="D75" s="4">
-        <v>15000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
@@ -3282,7 +3324,7 @@
         <v>11</v>
       </c>
       <c r="D76" s="4">
-        <v>2000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
@@ -3324,14 +3366,14 @@
         <v>11</v>
       </c>
       <c r="D78" s="4">
-        <v>16500.0</v>
-      </c>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
-      <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
-      <c r="I78" s="7"/>
-      <c r="J78" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
     </row>
     <row r="79">
       <c r="A79" s="4">
@@ -3345,14 +3387,14 @@
         <v>11</v>
       </c>
       <c r="D79" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="6"/>
+        <v>16500.0</v>
+      </c>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
+      <c r="I79" s="7"/>
+      <c r="J79" s="7"/>
     </row>
     <row r="80">
       <c r="A80" s="4">
@@ -3366,14 +3408,14 @@
         <v>11</v>
       </c>
       <c r="D80" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-      <c r="I80" s="7"/>
-      <c r="J80" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
     </row>
     <row r="81">
       <c r="A81" s="4">
@@ -3387,14 +3429,14 @@
         <v>11</v>
       </c>
       <c r="D81" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="J81" s="6"/>
+        <v>17000.0</v>
+      </c>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="7"/>
     </row>
     <row r="82">
       <c r="A82" s="4">
@@ -3408,7 +3450,7 @@
         <v>11</v>
       </c>
       <c r="D82" s="4">
-        <v>8500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
@@ -3429,7 +3471,7 @@
         <v>11</v>
       </c>
       <c r="D83" s="4">
-        <v>2000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
@@ -3450,7 +3492,7 @@
         <v>11</v>
       </c>
       <c r="D84" s="4">
-        <v>17000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
@@ -3471,7 +3513,7 @@
         <v>11</v>
       </c>
       <c r="D85" s="4">
-        <v>2000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
@@ -3494,12 +3536,12 @@
       <c r="D86" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
-      <c r="G86" s="7"/>
-      <c r="H86" s="7"/>
-      <c r="I86" s="7"/>
-      <c r="J86" s="7"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="6"/>
+      <c r="J86" s="6"/>
     </row>
     <row r="87">
       <c r="A87" s="4">
@@ -3513,14 +3555,14 @@
         <v>11</v>
       </c>
       <c r="D87" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="7"/>
+      <c r="H87" s="7"/>
+      <c r="I87" s="7"/>
+      <c r="J87" s="7"/>
     </row>
     <row r="88">
       <c r="A88" s="4">
@@ -3555,7 +3597,7 @@
         <v>11</v>
       </c>
       <c r="D89" s="4">
-        <v>90000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
@@ -3576,7 +3618,7 @@
         <v>11</v>
       </c>
       <c r="D90" s="4">
-        <v>2000.0</v>
+        <v>90000.0</v>
       </c>
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
@@ -3597,14 +3639,14 @@
         <v>11</v>
       </c>
       <c r="D91" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-      <c r="G91" s="7"/>
-      <c r="H91" s="7"/>
-      <c r="I91" s="7"/>
-      <c r="J91" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6"/>
+      <c r="J91" s="6"/>
     </row>
     <row r="92">
       <c r="A92" s="4">
@@ -3618,7 +3660,7 @@
         <v>11</v>
       </c>
       <c r="D92" s="4">
-        <v>2500.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E92" s="7"/>
       <c r="F92" s="7"/>
@@ -3639,7 +3681,7 @@
         <v>11</v>
       </c>
       <c r="D93" s="4">
-        <v>23000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="7"/>
@@ -3660,7 +3702,7 @@
         <v>11</v>
       </c>
       <c r="D94" s="4">
-        <v>2000.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E94" s="7"/>
       <c r="F94" s="7"/>
@@ -3681,14 +3723,14 @@
         <v>11</v>
       </c>
       <c r="D95" s="4">
-        <v>15500.0</v>
-      </c>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-      <c r="J95" s="6"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
+      <c r="I95" s="7"/>
+      <c r="J95" s="7"/>
     </row>
     <row r="96">
       <c r="A96" s="4">
@@ -3702,7 +3744,7 @@
         <v>11</v>
       </c>
       <c r="D96" s="4">
-        <v>1500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E96" s="6"/>
       <c r="F96" s="6"/>
@@ -3723,7 +3765,7 @@
         <v>11</v>
       </c>
       <c r="D97" s="4">
-        <v>11500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
@@ -3744,7 +3786,7 @@
         <v>11</v>
       </c>
       <c r="D98" s="4">
-        <v>1000.0</v>
+        <v>11500.0</v>
       </c>
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
@@ -3765,7 +3807,7 @@
         <v>11</v>
       </c>
       <c r="D99" s="4">
-        <v>9000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E99" s="6"/>
       <c r="F99" s="6"/>
@@ -3786,7 +3828,7 @@
         <v>11</v>
       </c>
       <c r="D100" s="4">
-        <v>2500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
@@ -3807,7 +3849,7 @@
         <v>11</v>
       </c>
       <c r="D101" s="4">
-        <v>19000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
@@ -3828,7 +3870,7 @@
         <v>11</v>
       </c>
       <c r="D102" s="4">
-        <v>1500.0</v>
+        <v>19000.0</v>
       </c>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -3849,7 +3891,7 @@
         <v>11</v>
       </c>
       <c r="D103" s="4">
-        <v>8500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
@@ -3870,7 +3912,7 @@
         <v>11</v>
       </c>
       <c r="D104" s="4">
-        <v>2000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
@@ -3891,7 +3933,7 @@
         <v>11</v>
       </c>
       <c r="D105" s="4">
-        <v>16000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
@@ -3909,10 +3951,10 @@
         <v>116</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="D106" s="4">
-        <v>6000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -3927,20 +3969,20 @@
         <v>106</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="D107" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E107" s="7"/>
-      <c r="F107" s="7"/>
-      <c r="G107" s="7"/>
-      <c r="H107" s="7"/>
-      <c r="I107" s="7"/>
-      <c r="J107" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="6"/>
+      <c r="H107" s="6"/>
+      <c r="I107" s="6"/>
+      <c r="J107" s="6"/>
     </row>
     <row r="108">
       <c r="A108" s="4">
@@ -3948,20 +3990,20 @@
         <v>107</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="D108" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="E108" s="7"/>
-      <c r="F108" s="7"/>
-      <c r="G108" s="7"/>
-      <c r="H108" s="7"/>
-      <c r="I108" s="7"/>
-      <c r="J108" s="7"/>
+        <v>16000.0</v>
+      </c>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="6"/>
+      <c r="H108" s="6"/>
+      <c r="I108" s="6"/>
+      <c r="J108" s="6"/>
     </row>
     <row r="109">
       <c r="A109" s="4">
@@ -3969,20 +4011,20 @@
         <v>108</v>
       </c>
       <c r="B109" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C109" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C109" s="5" t="s">
-        <v>117</v>
-      </c>
       <c r="D109" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7"/>
-      <c r="G109" s="7"/>
-      <c r="H109" s="7"/>
-      <c r="I109" s="7"/>
-      <c r="J109" s="7"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="6"/>
+      <c r="H109" s="6"/>
+      <c r="I109" s="6"/>
+      <c r="J109" s="6"/>
     </row>
     <row r="110">
       <c r="A110" s="4">
@@ -3993,10 +4035,10 @@
         <v>121</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D110" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E110" s="7"/>
       <c r="F110" s="7"/>
@@ -4014,10 +4056,10 @@
         <v>122</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D111" s="4">
-        <v>1000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E111" s="7"/>
       <c r="F111" s="7"/>
@@ -4035,10 +4077,10 @@
         <v>123</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D112" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E112" s="7"/>
       <c r="F112" s="7"/>
@@ -4056,10 +4098,10 @@
         <v>124</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D113" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E113" s="7"/>
       <c r="F113" s="7"/>
@@ -4077,17 +4119,17 @@
         <v>125</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D114" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
-      <c r="G114" s="6"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
-      <c r="J114" s="6"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E114" s="7"/>
+      <c r="F114" s="7"/>
+      <c r="G114" s="7"/>
+      <c r="H114" s="7"/>
+      <c r="I114" s="7"/>
+      <c r="J114" s="7"/>
     </row>
     <row r="115">
       <c r="A115" s="4">
@@ -4098,17 +4140,17 @@
         <v>126</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D115" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
-      <c r="G115" s="6"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
-      <c r="J115" s="6"/>
+        <v>10000.0</v>
+      </c>
+      <c r="E115" s="7"/>
+      <c r="F115" s="7"/>
+      <c r="G115" s="7"/>
+      <c r="H115" s="7"/>
+      <c r="I115" s="7"/>
+      <c r="J115" s="7"/>
     </row>
     <row r="116">
       <c r="A116" s="4">
@@ -4119,17 +4161,17 @@
         <v>127</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D116" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E116" s="6"/>
-      <c r="F116" s="6"/>
-      <c r="G116" s="6"/>
-      <c r="H116" s="6"/>
-      <c r="I116" s="6"/>
-      <c r="J116" s="6"/>
+        <v>500.0</v>
+      </c>
+      <c r="E116" s="7"/>
+      <c r="F116" s="7"/>
+      <c r="G116" s="7"/>
+      <c r="H116" s="7"/>
+      <c r="I116" s="7"/>
+      <c r="J116" s="7"/>
     </row>
     <row r="117">
       <c r="A117" s="4">
@@ -4140,10 +4182,10 @@
         <v>128</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D117" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
@@ -4161,10 +4203,10 @@
         <v>129</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D118" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E118" s="6"/>
       <c r="F118" s="6"/>
@@ -4182,10 +4224,10 @@
         <v>130</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D119" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E119" s="6"/>
       <c r="F119" s="6"/>
@@ -4203,10 +4245,10 @@
         <v>131</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D120" s="4">
-        <v>10000.0</v>
+        <v>22000.0</v>
       </c>
       <c r="E120" s="6"/>
       <c r="F120" s="6"/>
@@ -4224,10 +4266,10 @@
         <v>132</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D121" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
@@ -4245,10 +4287,10 @@
         <v>133</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D122" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
@@ -4266,7 +4308,7 @@
         <v>134</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D123" s="4">
         <v>5000.0</v>
@@ -4287,17 +4329,13 @@
         <v>135</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D124" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E124" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F124" s="4">
-        <v>1000.0</v>
-      </c>
+        <v>10000.0</v>
+      </c>
+      <c r="E124" s="6"/>
+      <c r="F124" s="6"/>
       <c r="G124" s="6"/>
       <c r="H124" s="6"/>
       <c r="I124" s="6"/>
@@ -4312,10 +4350,10 @@
         <v>136</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D125" s="4">
-        <v>6500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
@@ -4333,10 +4371,10 @@
         <v>137</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D126" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
@@ -4354,10 +4392,10 @@
         <v>138</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D127" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
@@ -4375,16 +4413,16 @@
         <v>139</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D128" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E128" s="4">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F128" s="4">
-        <v>13000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="G128" s="6"/>
       <c r="H128" s="6"/>
@@ -4400,10 +4438,10 @@
         <v>140</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D129" s="4">
-        <v>23000.0</v>
+        <v>6500.0</v>
       </c>
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
@@ -4421,17 +4459,17 @@
         <v>141</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D130" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="7"/>
-      <c r="H130" s="7"/>
-      <c r="I130" s="7"/>
-      <c r="J130" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E130" s="6"/>
+      <c r="F130" s="6"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="6"/>
     </row>
     <row r="131">
       <c r="A131" s="4">
@@ -4442,10 +4480,10 @@
         <v>142</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D131" s="4">
-        <v>26000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
@@ -4463,13 +4501,17 @@
         <v>143</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D132" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E132" s="6"/>
-      <c r="F132" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E132" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F132" s="4">
+        <v>13000.0</v>
+      </c>
       <c r="G132" s="6"/>
       <c r="H132" s="6"/>
       <c r="I132" s="6"/>
@@ -4484,10 +4526,10 @@
         <v>144</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D133" s="4">
-        <v>21000.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
@@ -4505,17 +4547,17 @@
         <v>145</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D134" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E134" s="6"/>
-      <c r="F134" s="6"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="6"/>
-      <c r="I134" s="6"/>
-      <c r="J134" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E134" s="7"/>
+      <c r="F134" s="7"/>
+      <c r="G134" s="7"/>
+      <c r="H134" s="7"/>
+      <c r="I134" s="7"/>
+      <c r="J134" s="7"/>
     </row>
     <row r="135">
       <c r="A135" s="4">
@@ -4526,10 +4568,10 @@
         <v>146</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D135" s="4">
-        <v>36500.0</v>
+        <v>26000.0</v>
       </c>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
@@ -4547,10 +4589,10 @@
         <v>147</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D136" s="4">
-        <v>13000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
@@ -4568,10 +4610,10 @@
         <v>148</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D137" s="4">
-        <v>500.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
@@ -4589,10 +4631,10 @@
         <v>149</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D138" s="4">
-        <v>13500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E138" s="6"/>
       <c r="F138" s="6"/>
@@ -4610,10 +4652,10 @@
         <v>150</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D139" s="4">
-        <v>5000.0</v>
+        <v>36500.0</v>
       </c>
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
@@ -4631,10 +4673,10 @@
         <v>151</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D140" s="4">
-        <v>160000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="E140" s="6"/>
       <c r="F140" s="6"/>
@@ -4652,17 +4694,13 @@
         <v>152</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D141" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E141" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F141" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>500.0</v>
+      </c>
+      <c r="E141" s="6"/>
+      <c r="F141" s="6"/>
       <c r="G141" s="6"/>
       <c r="H141" s="6"/>
       <c r="I141" s="6"/>
@@ -4677,17 +4715,17 @@
         <v>153</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D142" s="4">
-        <v>65000.0</v>
-      </c>
-      <c r="E142" s="7"/>
-      <c r="F142" s="7"/>
-      <c r="G142" s="7"/>
-      <c r="H142" s="7"/>
-      <c r="I142" s="7"/>
-      <c r="J142" s="7"/>
+        <v>13500.0</v>
+      </c>
+      <c r="E142" s="6"/>
+      <c r="F142" s="6"/>
+      <c r="G142" s="6"/>
+      <c r="H142" s="6"/>
+      <c r="I142" s="6"/>
+      <c r="J142" s="6"/>
     </row>
     <row r="143">
       <c r="A143" s="4">
@@ -4698,17 +4736,17 @@
         <v>154</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D143" s="4">
-        <v>4500.0</v>
-      </c>
-      <c r="E143" s="7"/>
-      <c r="F143" s="7"/>
-      <c r="G143" s="7"/>
-      <c r="H143" s="7"/>
-      <c r="I143" s="7"/>
-      <c r="J143" s="7"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E143" s="6"/>
+      <c r="F143" s="6"/>
+      <c r="G143" s="6"/>
+      <c r="H143" s="6"/>
+      <c r="I143" s="6"/>
+      <c r="J143" s="6"/>
     </row>
     <row r="144">
       <c r="A144" s="4">
@@ -4719,10 +4757,10 @@
         <v>155</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D144" s="4">
-        <v>2000.0</v>
+        <v>160000.0</v>
       </c>
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
@@ -4740,13 +4778,17 @@
         <v>156</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D145" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E145" s="6"/>
-      <c r="F145" s="6"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E145" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F145" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G145" s="6"/>
       <c r="H145" s="6"/>
       <c r="I145" s="6"/>
@@ -4761,17 +4803,17 @@
         <v>157</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D146" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E146" s="6"/>
-      <c r="F146" s="6"/>
-      <c r="G146" s="6"/>
-      <c r="H146" s="6"/>
-      <c r="I146" s="6"/>
-      <c r="J146" s="6"/>
+        <v>65000.0</v>
+      </c>
+      <c r="E146" s="7"/>
+      <c r="F146" s="7"/>
+      <c r="G146" s="7"/>
+      <c r="H146" s="7"/>
+      <c r="I146" s="7"/>
+      <c r="J146" s="7"/>
     </row>
     <row r="147">
       <c r="A147" s="4">
@@ -4782,17 +4824,17 @@
         <v>158</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D147" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E147" s="6"/>
-      <c r="F147" s="6"/>
-      <c r="G147" s="6"/>
-      <c r="H147" s="6"/>
-      <c r="I147" s="6"/>
-      <c r="J147" s="6"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E147" s="7"/>
+      <c r="F147" s="7"/>
+      <c r="G147" s="7"/>
+      <c r="H147" s="7"/>
+      <c r="I147" s="7"/>
+      <c r="J147" s="7"/>
     </row>
     <row r="148">
       <c r="A148" s="4">
@@ -4803,7 +4845,7 @@
         <v>159</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D148" s="4">
         <v>2000.0</v>
@@ -4824,7 +4866,7 @@
         <v>160</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D149" s="4">
         <v>17000.0</v>
@@ -4845,7 +4887,7 @@
         <v>161</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D150" s="4">
         <v>2000.0</v>
@@ -4866,7 +4908,7 @@
         <v>162</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D151" s="4">
         <v>17000.0</v>
@@ -4887,7 +4929,7 @@
         <v>163</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D152" s="4">
         <v>2000.0</v>
@@ -4908,7 +4950,7 @@
         <v>164</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D153" s="4">
         <v>17000.0</v>
@@ -4929,10 +4971,10 @@
         <v>165</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D154" s="4">
-        <v>5000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E154" s="6"/>
       <c r="F154" s="6"/>
@@ -4950,10 +4992,10 @@
         <v>166</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D155" s="4">
-        <v>10000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E155" s="6"/>
       <c r="F155" s="6"/>
@@ -4971,10 +5013,10 @@
         <v>167</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D156" s="4">
-        <v>18000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E156" s="6"/>
       <c r="F156" s="6"/>
@@ -4992,10 +5034,10 @@
         <v>168</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D157" s="4">
-        <v>4500.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E157" s="6"/>
       <c r="F157" s="6"/>
@@ -5013,10 +5055,10 @@
         <v>169</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D158" s="4">
-        <v>9000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E158" s="6"/>
       <c r="F158" s="6"/>
@@ -5034,17 +5076,17 @@
         <v>170</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D159" s="4">
-        <v>18000.0</v>
-      </c>
-      <c r="E159" s="4"/>
-      <c r="F159" s="4"/>
-      <c r="G159" s="7"/>
-      <c r="H159" s="7"/>
-      <c r="I159" s="7"/>
-      <c r="J159" s="7"/>
+        <v>10000.0</v>
+      </c>
+      <c r="E159" s="6"/>
+      <c r="F159" s="6"/>
+      <c r="G159" s="6"/>
+      <c r="H159" s="6"/>
+      <c r="I159" s="6"/>
+      <c r="J159" s="6"/>
     </row>
     <row r="160">
       <c r="A160" s="4">
@@ -5055,21 +5097,17 @@
         <v>171</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D160" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E160" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F160" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="G160" s="7"/>
-      <c r="H160" s="7"/>
-      <c r="I160" s="7"/>
-      <c r="J160" s="7"/>
+        <v>18000.0</v>
+      </c>
+      <c r="E160" s="6"/>
+      <c r="F160" s="6"/>
+      <c r="G160" s="6"/>
+      <c r="H160" s="6"/>
+      <c r="I160" s="6"/>
+      <c r="J160" s="6"/>
     </row>
     <row r="161">
       <c r="A161" s="4">
@@ -5080,21 +5118,17 @@
         <v>172</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D161" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E161" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F161" s="4">
-        <v>12000.0</v>
-      </c>
-      <c r="G161" s="7"/>
-      <c r="H161" s="7"/>
-      <c r="I161" s="7"/>
-      <c r="J161" s="7"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E161" s="6"/>
+      <c r="F161" s="6"/>
+      <c r="G161" s="6"/>
+      <c r="H161" s="6"/>
+      <c r="I161" s="6"/>
+      <c r="J161" s="6"/>
     </row>
     <row r="162">
       <c r="A162" s="4">
@@ -5105,21 +5139,17 @@
         <v>173</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D162" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E162" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F162" s="4">
-        <v>8500.0</v>
-      </c>
-      <c r="G162" s="7"/>
-      <c r="H162" s="7"/>
-      <c r="I162" s="7"/>
-      <c r="J162" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E162" s="6"/>
+      <c r="F162" s="6"/>
+      <c r="G162" s="6"/>
+      <c r="H162" s="6"/>
+      <c r="I162" s="6"/>
+      <c r="J162" s="6"/>
     </row>
     <row r="163">
       <c r="A163" s="4">
@@ -5130,13 +5160,13 @@
         <v>174</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D163" s="4">
-        <v>26000.0</v>
-      </c>
-      <c r="E163" s="7"/>
-      <c r="F163" s="7"/>
+        <v>18000.0</v>
+      </c>
+      <c r="E163" s="4"/>
+      <c r="F163" s="4"/>
       <c r="G163" s="7"/>
       <c r="H163" s="7"/>
       <c r="I163" s="7"/>
@@ -5151,16 +5181,16 @@
         <v>175</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D164" s="4">
-        <v>4000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E164" s="4">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F164" s="4">
-        <v>17500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="G164" s="7"/>
       <c r="H164" s="7"/>
@@ -5176,13 +5206,17 @@
         <v>176</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D165" s="4">
-        <v>175000.0</v>
-      </c>
-      <c r="E165" s="7"/>
-      <c r="F165" s="7"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E165" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F165" s="4">
+        <v>12000.0</v>
+      </c>
       <c r="G165" s="7"/>
       <c r="H165" s="7"/>
       <c r="I165" s="7"/>
@@ -5197,13 +5231,17 @@
         <v>177</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D166" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E166" s="7"/>
-      <c r="F166" s="7"/>
+        <v>2500.0</v>
+      </c>
+      <c r="E166" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F166" s="4">
+        <v>8500.0</v>
+      </c>
       <c r="G166" s="7"/>
       <c r="H166" s="7"/>
       <c r="I166" s="7"/>
@@ -5218,17 +5256,13 @@
         <v>178</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D167" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="E167" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F167" s="4">
-        <v>22000.0</v>
-      </c>
+        <v>26000.0</v>
+      </c>
+      <c r="E167" s="7"/>
+      <c r="F167" s="7"/>
       <c r="G167" s="7"/>
       <c r="H167" s="7"/>
       <c r="I167" s="7"/>
@@ -5243,13 +5277,17 @@
         <v>179</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D168" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E168" s="7"/>
-      <c r="F168" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E168" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F168" s="4">
+        <v>17500.0</v>
+      </c>
       <c r="G168" s="7"/>
       <c r="H168" s="7"/>
       <c r="I168" s="7"/>
@@ -5264,10 +5302,10 @@
         <v>180</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D169" s="4">
-        <v>21000.0</v>
+        <v>175000.0</v>
       </c>
       <c r="E169" s="7"/>
       <c r="F169" s="7"/>
@@ -5285,10 +5323,10 @@
         <v>181</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D170" s="4">
-        <v>245000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E170" s="7"/>
       <c r="F170" s="7"/>
@@ -5306,13 +5344,17 @@
         <v>182</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D171" s="4">
-        <v>42000.0</v>
-      </c>
-      <c r="E171" s="7"/>
-      <c r="F171" s="7"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E171" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F171" s="4">
+        <v>22000.0</v>
+      </c>
       <c r="G171" s="7"/>
       <c r="H171" s="7"/>
       <c r="I171" s="7"/>
@@ -5327,10 +5369,10 @@
         <v>183</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D172" s="4">
-        <v>44000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E172" s="7"/>
       <c r="F172" s="7"/>
@@ -5348,10 +5390,10 @@
         <v>184</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D173" s="4">
-        <v>255000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E173" s="7"/>
       <c r="F173" s="7"/>
@@ -5369,10 +5411,10 @@
         <v>185</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D174" s="4">
-        <v>21000.0</v>
+        <v>245000.0</v>
       </c>
       <c r="E174" s="7"/>
       <c r="F174" s="7"/>
@@ -5390,7 +5432,7 @@
         <v>186</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D175" s="4">
         <v>42000.0</v>
@@ -5411,17 +5453,17 @@
         <v>187</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D176" s="4">
-        <v>14500.0</v>
+        <v>44000.0</v>
       </c>
       <c r="E176" s="7"/>
       <c r="F176" s="7"/>
-      <c r="G176" s="4"/>
-      <c r="H176" s="4"/>
-      <c r="I176" s="4"/>
-      <c r="J176" s="4"/>
+      <c r="G176" s="7"/>
+      <c r="H176" s="7"/>
+      <c r="I176" s="7"/>
+      <c r="J176" s="7"/>
     </row>
     <row r="177">
       <c r="A177" s="4">
@@ -5432,25 +5474,17 @@
         <v>188</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="D177" s="4">
-        <v>2000.0</v>
+        <v>255000.0</v>
       </c>
       <c r="E177" s="7"/>
       <c r="F177" s="7"/>
-      <c r="G177" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H177" s="4">
-        <v>5500.0</v>
-      </c>
-      <c r="I177" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J177" s="4">
-        <v>10000.0</v>
-      </c>
+      <c r="G177" s="7"/>
+      <c r="H177" s="7"/>
+      <c r="I177" s="7"/>
+      <c r="J177" s="7"/>
     </row>
     <row r="178">
       <c r="A178" s="4">
@@ -5458,13 +5492,13 @@
         <v>177</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="D178" s="4">
-        <v>10000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E178" s="7"/>
       <c r="F178" s="7"/>
@@ -5479,28 +5513,20 @@
         <v>178</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="D179" s="4">
-        <v>2000.0</v>
+        <v>42000.0</v>
       </c>
       <c r="E179" s="7"/>
       <c r="F179" s="7"/>
-      <c r="G179" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H179" s="4">
-        <v>5500.0</v>
-      </c>
-      <c r="I179" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J179" s="4">
-        <v>10000.0</v>
-      </c>
+      <c r="G179" s="7"/>
+      <c r="H179" s="7"/>
+      <c r="I179" s="7"/>
+      <c r="J179" s="7"/>
     </row>
     <row r="180">
       <c r="A180" s="4">
@@ -5508,20 +5534,20 @@
         <v>179</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="D180" s="4">
-        <v>10000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E180" s="7"/>
       <c r="F180" s="7"/>
-      <c r="G180" s="7"/>
-      <c r="H180" s="7"/>
-      <c r="I180" s="7"/>
-      <c r="J180" s="7"/>
+      <c r="G180" s="4"/>
+      <c r="H180" s="4"/>
+      <c r="I180" s="4"/>
+      <c r="J180" s="4"/>
     </row>
     <row r="181">
       <c r="A181" s="4">
@@ -5529,10 +5555,10 @@
         <v>180</v>
       </c>
       <c r="B181" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C181" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>189</v>
       </c>
       <c r="D181" s="4">
         <v>2000.0</v>
@@ -5561,7 +5587,7 @@
         <v>194</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D182" s="4">
         <v>10000.0</v>
@@ -5582,7 +5608,7 @@
         <v>195</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D183" s="4">
         <v>2000.0</v>
@@ -5593,13 +5619,13 @@
         <v>6.0</v>
       </c>
       <c r="H183" s="4">
-        <v>6000.0</v>
+        <v>5500.0</v>
       </c>
       <c r="I183" s="4">
         <v>12.0</v>
       </c>
       <c r="J183" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
     </row>
     <row r="184">
@@ -5611,10 +5637,10 @@
         <v>196</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D184" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
@@ -5632,7 +5658,7 @@
         <v>197</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D185" s="4">
         <v>2000.0</v>
@@ -5643,13 +5669,13 @@
         <v>6.0</v>
       </c>
       <c r="H185" s="4">
-        <v>6000.0</v>
+        <v>5500.0</v>
       </c>
       <c r="I185" s="4">
         <v>12.0</v>
       </c>
       <c r="J185" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
     </row>
     <row r="186">
@@ -5661,10 +5687,10 @@
         <v>198</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D186" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
@@ -5682,7 +5708,7 @@
         <v>199</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D187" s="4">
         <v>2000.0</v>
@@ -5693,13 +5719,13 @@
         <v>6.0</v>
       </c>
       <c r="H187" s="4">
-        <v>8000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="I187" s="4">
         <v>12.0</v>
       </c>
       <c r="J187" s="4">
-        <v>15000.0</v>
+        <v>11000.0</v>
       </c>
     </row>
     <row r="188">
@@ -5711,10 +5737,10 @@
         <v>200</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D188" s="4">
-        <v>15000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="E188" s="7"/>
       <c r="F188" s="7"/>
@@ -5732,17 +5758,25 @@
         <v>201</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D189" s="4">
-        <v>15000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E189" s="7"/>
       <c r="F189" s="7"/>
-      <c r="G189" s="7"/>
-      <c r="H189" s="7"/>
-      <c r="I189" s="7"/>
-      <c r="J189" s="7"/>
+      <c r="G189" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H189" s="4">
+        <v>6000.0</v>
+      </c>
+      <c r="I189" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J189" s="4">
+        <v>11000.0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="4">
@@ -5753,29 +5787,17 @@
         <v>202</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D190" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E190" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F190" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="G190" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H190" s="4">
-        <v>8500.0</v>
-      </c>
-      <c r="I190" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J190" s="4">
-        <v>16000.0</v>
-      </c>
+        <v>11000.0</v>
+      </c>
+      <c r="E190" s="7"/>
+      <c r="F190" s="7"/>
+      <c r="G190" s="7"/>
+      <c r="H190" s="7"/>
+      <c r="I190" s="7"/>
+      <c r="J190" s="7"/>
     </row>
     <row r="191">
       <c r="A191" s="4">
@@ -5786,17 +5808,25 @@
         <v>203</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D191" s="4">
-        <v>16000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E191" s="7"/>
       <c r="F191" s="7"/>
-      <c r="G191" s="7"/>
-      <c r="H191" s="7"/>
-      <c r="I191" s="7"/>
-      <c r="J191" s="7"/>
+      <c r="G191" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H191" s="4">
+        <v>8000.0</v>
+      </c>
+      <c r="I191" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J191" s="4">
+        <v>15000.0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4">
@@ -5807,25 +5837,17 @@
         <v>204</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D192" s="4">
-        <v>2000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E192" s="7"/>
       <c r="F192" s="7"/>
-      <c r="G192" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H192" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="I192" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J192" s="4">
-        <v>17000.0</v>
-      </c>
+      <c r="G192" s="7"/>
+      <c r="H192" s="7"/>
+      <c r="I192" s="7"/>
+      <c r="J192" s="7"/>
     </row>
     <row r="193">
       <c r="A193" s="4">
@@ -5836,10 +5858,10 @@
         <v>205</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D193" s="4">
-        <v>17000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E193" s="7"/>
       <c r="F193" s="7"/>
@@ -5857,24 +5879,28 @@
         <v>206</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D194" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E194" s="7"/>
-      <c r="F194" s="7"/>
+      <c r="E194" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F194" s="4">
+        <v>5000.0</v>
+      </c>
       <c r="G194" s="4">
         <v>6.0</v>
       </c>
       <c r="H194" s="4">
-        <v>9000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="I194" s="4">
         <v>12.0</v>
       </c>
       <c r="J194" s="4">
-        <v>17000.0</v>
+        <v>16000.0</v>
       </c>
     </row>
     <row r="195">
@@ -5886,10 +5912,10 @@
         <v>207</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D195" s="4">
-        <v>17000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E195" s="7"/>
       <c r="F195" s="7"/>
@@ -5907,28 +5933,24 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D196" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E196" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F196" s="4">
-        <v>5000.0</v>
-      </c>
+      <c r="E196" s="7"/>
+      <c r="F196" s="7"/>
       <c r="G196" s="4">
         <v>6.0</v>
       </c>
       <c r="H196" s="4">
-        <v>9500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="I196" s="4">
         <v>12.0</v>
       </c>
       <c r="J196" s="4">
-        <v>18000.0</v>
+        <v>17000.0</v>
       </c>
     </row>
     <row r="197">
@@ -5940,10 +5962,10 @@
         <v>209</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D197" s="4">
-        <v>18000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E197" s="7"/>
       <c r="F197" s="7"/>
@@ -5961,10 +5983,10 @@
         <v>210</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D198" s="4">
-        <v>2500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E198" s="7"/>
       <c r="F198" s="7"/>
@@ -5972,13 +5994,13 @@
         <v>6.0</v>
       </c>
       <c r="H198" s="4">
-        <v>14500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="I198" s="4">
         <v>12.0</v>
       </c>
       <c r="J198" s="4">
-        <v>28000.0</v>
+        <v>17000.0</v>
       </c>
     </row>
     <row r="199">
@@ -5990,10 +6012,10 @@
         <v>211</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D199" s="4">
-        <v>28000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E199" s="7"/>
       <c r="F199" s="7"/>
@@ -6011,24 +6033,28 @@
         <v>212</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D200" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E200" s="7"/>
-      <c r="F200" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E200" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F200" s="4">
+        <v>5000.0</v>
+      </c>
       <c r="G200" s="4">
         <v>6.0</v>
       </c>
       <c r="H200" s="4">
-        <v>10500.0</v>
+        <v>9500.0</v>
       </c>
       <c r="I200" s="4">
         <v>12.0</v>
       </c>
       <c r="J200" s="4">
-        <v>20000.0</v>
+        <v>18000.0</v>
       </c>
     </row>
     <row r="201">
@@ -6040,10 +6066,10 @@
         <v>213</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D201" s="4">
-        <v>20000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E201" s="7"/>
       <c r="F201" s="7"/>
@@ -6061,7 +6087,7 @@
         <v>214</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D202" s="4">
         <v>2500.0</v>
@@ -6072,13 +6098,13 @@
         <v>6.0</v>
       </c>
       <c r="H202" s="4">
-        <v>13000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="I202" s="4">
         <v>12.0</v>
       </c>
       <c r="J202" s="4">
-        <v>25000.0</v>
+        <v>28000.0</v>
       </c>
     </row>
     <row r="203">
@@ -6090,10 +6116,10 @@
         <v>215</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D203" s="4">
-        <v>25000.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E203" s="7"/>
       <c r="F203" s="7"/>
@@ -6111,7 +6137,7 @@
         <v>216</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D204" s="4">
         <v>2500.0</v>
@@ -6122,13 +6148,13 @@
         <v>6.0</v>
       </c>
       <c r="H204" s="4">
-        <v>11000.0</v>
+        <v>10500.0</v>
       </c>
       <c r="I204" s="4">
         <v>12.0</v>
       </c>
       <c r="J204" s="4">
-        <v>21000.0</v>
+        <v>20000.0</v>
       </c>
     </row>
     <row r="205">
@@ -6140,10 +6166,10 @@
         <v>217</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D205" s="4">
-        <v>21000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="E205" s="7"/>
       <c r="F205" s="7"/>
@@ -6161,7 +6187,7 @@
         <v>218</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D206" s="4">
         <v>2500.0</v>
@@ -6190,7 +6216,7 @@
         <v>219</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D207" s="4">
         <v>25000.0</v>
@@ -6211,7 +6237,7 @@
         <v>220</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D208" s="4">
         <v>2500.0</v>
@@ -6222,13 +6248,13 @@
         <v>6.0</v>
       </c>
       <c r="H208" s="4">
-        <v>14000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="I208" s="4">
         <v>12.0</v>
       </c>
       <c r="J208" s="4">
-        <v>28000.0</v>
+        <v>21000.0</v>
       </c>
     </row>
     <row r="209">
@@ -6240,10 +6266,10 @@
         <v>221</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D209" s="4">
-        <v>28000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E209" s="7"/>
       <c r="F209" s="7"/>
@@ -6261,7 +6287,7 @@
         <v>222</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D210" s="4">
         <v>2500.0</v>
@@ -6290,7 +6316,7 @@
         <v>223</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D211" s="4">
         <v>25000.0</v>
@@ -6311,7 +6337,7 @@
         <v>224</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D212" s="4">
         <v>2500.0</v>
@@ -6328,7 +6354,7 @@
         <v>12.0</v>
       </c>
       <c r="J212" s="4">
-        <v>27000.0</v>
+        <v>28000.0</v>
       </c>
     </row>
     <row r="213">
@@ -6340,10 +6366,10 @@
         <v>225</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D213" s="4">
-        <v>27000.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E213" s="7"/>
       <c r="F213" s="7"/>
@@ -6361,7 +6387,7 @@
         <v>226</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D214" s="4">
         <v>2500.0</v>
@@ -6372,13 +6398,13 @@
         <v>6.0</v>
       </c>
       <c r="H214" s="4">
-        <v>14000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I214" s="4">
         <v>12.0</v>
       </c>
       <c r="J214" s="4">
-        <v>27000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="215">
@@ -6390,10 +6416,10 @@
         <v>227</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D215" s="4">
-        <v>27000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E215" s="7"/>
       <c r="F215" s="7"/>
@@ -6411,17 +6437,25 @@
         <v>228</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D216" s="4">
-        <v>34000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E216" s="7"/>
       <c r="F216" s="7"/>
-      <c r="G216" s="7"/>
-      <c r="H216" s="7"/>
-      <c r="I216" s="7"/>
-      <c r="J216" s="7"/>
+      <c r="G216" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H216" s="4">
+        <v>14000.0</v>
+      </c>
+      <c r="I216" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J216" s="4">
+        <v>27000.0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="4">
@@ -6432,7 +6466,7 @@
         <v>229</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D217" s="4">
         <v>27000.0</v>
@@ -6453,18 +6487,24 @@
         <v>230</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D218" s="4">
-        <v>37000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E218" s="7"/>
       <c r="F218" s="7"/>
-      <c r="G218" s="4"/>
-      <c r="H218" s="4"/>
-      <c r="I218" s="4"/>
+      <c r="G218" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H218" s="4">
+        <v>14000.0</v>
+      </c>
+      <c r="I218" s="4">
+        <v>12.0</v>
+      </c>
       <c r="J218" s="4">
-        <v>37000.0</v>
+        <v>27000.0</v>
       </c>
     </row>
     <row r="219">
@@ -6476,10 +6516,10 @@
         <v>231</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D219" s="4">
-        <v>16000.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E219" s="7"/>
       <c r="F219" s="7"/>
@@ -6497,10 +6537,10 @@
         <v>232</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D220" s="4">
-        <v>43000.0</v>
+        <v>34000.0</v>
       </c>
       <c r="E220" s="7"/>
       <c r="F220" s="7"/>
@@ -6518,10 +6558,10 @@
         <v>233</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D221" s="4">
-        <v>23000.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E221" s="7"/>
       <c r="F221" s="7"/>
@@ -6539,17 +6579,19 @@
         <v>234</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D222" s="4">
-        <v>17000.0</v>
+        <v>37000.0</v>
       </c>
       <c r="E222" s="7"/>
       <c r="F222" s="7"/>
-      <c r="G222" s="7"/>
-      <c r="H222" s="7"/>
-      <c r="I222" s="7"/>
-      <c r="J222" s="7"/>
+      <c r="G222" s="4"/>
+      <c r="H222" s="4"/>
+      <c r="I222" s="4"/>
+      <c r="J222" s="4">
+        <v>37000.0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="4">
@@ -6560,10 +6602,10 @@
         <v>235</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D223" s="4">
-        <v>29000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E223" s="7"/>
       <c r="F223" s="7"/>
@@ -6581,10 +6623,10 @@
         <v>236</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D224" s="4">
-        <v>13000.0</v>
+        <v>43000.0</v>
       </c>
       <c r="E224" s="7"/>
       <c r="F224" s="7"/>
@@ -6602,10 +6644,10 @@
         <v>237</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>238</v>
+        <v>193</v>
       </c>
       <c r="D225" s="4">
-        <v>500.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E225" s="7"/>
       <c r="F225" s="7"/>
@@ -6620,13 +6662,13 @@
         <v>225</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>238</v>
+        <v>193</v>
       </c>
       <c r="D226" s="4">
-        <v>4000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E226" s="7"/>
       <c r="F226" s="7"/>
@@ -6641,13 +6683,13 @@
         <v>226</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>238</v>
+        <v>193</v>
       </c>
       <c r="D227" s="4">
-        <v>2500.0</v>
+        <v>29000.0</v>
       </c>
       <c r="E227" s="7"/>
       <c r="F227" s="7"/>
@@ -6662,20 +6704,16 @@
         <v>227</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>242</v>
+        <v>193</v>
       </c>
       <c r="D228" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E228" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F228" s="4">
-        <v>14000.0</v>
-      </c>
+        <v>13000.0</v>
+      </c>
+      <c r="E228" s="7"/>
+      <c r="F228" s="7"/>
       <c r="G228" s="7"/>
       <c r="H228" s="7"/>
       <c r="I228" s="7"/>
@@ -6687,13 +6725,13 @@
         <v>228</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C229" s="5" t="s">
         <v>242</v>
       </c>
       <c r="D229" s="4">
-        <v>109000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E229" s="7"/>
       <c r="F229" s="7"/>
@@ -6708,20 +6746,16 @@
         <v>229</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C230" s="5" t="s">
         <v>242</v>
       </c>
       <c r="D230" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E230" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F230" s="4">
-        <v>14000.0</v>
-      </c>
+        <v>4000.0</v>
+      </c>
+      <c r="E230" s="7"/>
+      <c r="F230" s="7"/>
       <c r="G230" s="7"/>
       <c r="H230" s="7"/>
       <c r="I230" s="7"/>
@@ -6733,13 +6767,13 @@
         <v>230</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C231" s="5" t="s">
         <v>242</v>
       </c>
       <c r="D231" s="4">
-        <v>109000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E231" s="7"/>
       <c r="F231" s="7"/>
@@ -6754,16 +6788,20 @@
         <v>231</v>
       </c>
       <c r="B232" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C232" s="5" t="s">
         <v>246</v>
-      </c>
-      <c r="C232" s="5" t="s">
-        <v>242</v>
       </c>
       <c r="D232" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E232" s="7"/>
-      <c r="F232" s="7"/>
+      <c r="E232" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F232" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G232" s="7"/>
       <c r="H232" s="7"/>
       <c r="I232" s="7"/>
@@ -6778,10 +6816,10 @@
         <v>247</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D233" s="4">
-        <v>114000.0</v>
+        <v>109000.0</v>
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="7"/>
@@ -6799,13 +6837,17 @@
         <v>248</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D234" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E234" s="7"/>
-      <c r="F234" s="7"/>
+      <c r="E234" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F234" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G234" s="7"/>
       <c r="H234" s="7"/>
       <c r="I234" s="7"/>
@@ -6820,17 +6862,13 @@
         <v>249</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D235" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E235" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F235" s="4">
-        <v>39000.0</v>
-      </c>
+        <v>109000.0</v>
+      </c>
+      <c r="E235" s="7"/>
+      <c r="F235" s="7"/>
       <c r="G235" s="7"/>
       <c r="H235" s="7"/>
       <c r="I235" s="7"/>
@@ -6845,10 +6883,10 @@
         <v>250</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D236" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E236" s="7"/>
       <c r="F236" s="7"/>
@@ -6866,10 +6904,10 @@
         <v>251</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D237" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="7"/>
@@ -6887,10 +6925,10 @@
         <v>252</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D238" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E238" s="7"/>
       <c r="F238" s="7"/>
@@ -6908,13 +6946,17 @@
         <v>253</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D239" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E239" s="7"/>
-      <c r="F239" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E239" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F239" s="4">
+        <v>39000.0</v>
+      </c>
       <c r="G239" s="7"/>
       <c r="H239" s="7"/>
       <c r="I239" s="7"/>
@@ -6929,7 +6971,7 @@
         <v>254</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D240" s="4">
         <v>114000.0</v>
@@ -6950,7 +6992,7 @@
         <v>255</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D241" s="4">
         <v>3000.0</v>
@@ -6971,7 +7013,7 @@
         <v>256</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D242" s="4">
         <v>114000.0</v>
@@ -6992,7 +7034,7 @@
         <v>257</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D243" s="4">
         <v>3000.0</v>
@@ -7013,10 +7055,10 @@
         <v>258</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D244" s="4">
-        <v>107000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E244" s="7"/>
       <c r="F244" s="7"/>
@@ -7034,7 +7076,7 @@
         <v>259</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D245" s="4">
         <v>3000.0</v>
@@ -7055,17 +7097,17 @@
         <v>260</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D246" s="4">
-        <v>112000.0</v>
-      </c>
-      <c r="E246" s="6"/>
-      <c r="F246" s="6"/>
-      <c r="G246" s="6"/>
-      <c r="H246" s="6"/>
-      <c r="I246" s="6"/>
-      <c r="J246" s="6"/>
+        <v>114000.0</v>
+      </c>
+      <c r="E246" s="7"/>
+      <c r="F246" s="7"/>
+      <c r="G246" s="7"/>
+      <c r="H246" s="7"/>
+      <c r="I246" s="7"/>
+      <c r="J246" s="7"/>
     </row>
     <row r="247">
       <c r="A247" s="4">
@@ -7076,17 +7118,13 @@
         <v>261</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D247" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E247" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F247" s="4">
-        <v>19000.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E247" s="7"/>
+      <c r="F247" s="7"/>
       <c r="G247" s="7"/>
       <c r="H247" s="7"/>
       <c r="I247" s="7"/>
@@ -7101,17 +7139,13 @@
         <v>262</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D248" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E248" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F248" s="4">
-        <v>19000.0</v>
-      </c>
+        <v>107000.0</v>
+      </c>
+      <c r="E248" s="7"/>
+      <c r="F248" s="7"/>
       <c r="G248" s="7"/>
       <c r="H248" s="7"/>
       <c r="I248" s="7"/>
@@ -7126,13 +7160,13 @@
         <v>263</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D249" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E249" s="4"/>
-      <c r="F249" s="4"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E249" s="7"/>
+      <c r="F249" s="7"/>
       <c r="G249" s="7"/>
       <c r="H249" s="7"/>
       <c r="I249" s="7"/>
@@ -7147,17 +7181,17 @@
         <v>264</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D250" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E250" s="4"/>
-      <c r="F250" s="4"/>
-      <c r="G250" s="7"/>
-      <c r="H250" s="7"/>
-      <c r="I250" s="7"/>
-      <c r="J250" s="7"/>
+        <v>112000.0</v>
+      </c>
+      <c r="E250" s="6"/>
+      <c r="F250" s="6"/>
+      <c r="G250" s="6"/>
+      <c r="H250" s="6"/>
+      <c r="I250" s="6"/>
+      <c r="J250" s="6"/>
     </row>
     <row r="251">
       <c r="A251" s="4">
@@ -7168,13 +7202,17 @@
         <v>265</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D251" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E251" s="4"/>
-      <c r="F251" s="4"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E251" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F251" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G251" s="7"/>
       <c r="H251" s="7"/>
       <c r="I251" s="7"/>
@@ -7189,7 +7227,7 @@
         <v>266</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D252" s="4">
         <v>4000.0</v>
@@ -7198,9 +7236,9 @@
         <v>5.0</v>
       </c>
       <c r="F252" s="4">
-        <v>19500.0</v>
-      </c>
-      <c r="G252" s="4"/>
+        <v>19000.0</v>
+      </c>
+      <c r="G252" s="7"/>
       <c r="H252" s="7"/>
       <c r="I252" s="7"/>
       <c r="J252" s="7"/>
@@ -7214,17 +7252,13 @@
         <v>267</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D253" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E253" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F253" s="4">
-        <v>6000.0</v>
-      </c>
+        <v>86000.0</v>
+      </c>
+      <c r="E253" s="4"/>
+      <c r="F253" s="4"/>
       <c r="G253" s="7"/>
       <c r="H253" s="7"/>
       <c r="I253" s="7"/>
@@ -7239,13 +7273,13 @@
         <v>268</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D254" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E254" s="7"/>
-      <c r="F254" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E254" s="4"/>
+      <c r="F254" s="4"/>
       <c r="G254" s="7"/>
       <c r="H254" s="7"/>
       <c r="I254" s="7"/>
@@ -7260,13 +7294,13 @@
         <v>269</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D255" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E255" s="7"/>
-      <c r="F255" s="7"/>
+        <v>86000.0</v>
+      </c>
+      <c r="E255" s="4"/>
+      <c r="F255" s="4"/>
       <c r="G255" s="7"/>
       <c r="H255" s="7"/>
       <c r="I255" s="7"/>
@@ -7281,14 +7315,18 @@
         <v>270</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D256" s="4">
-        <v>89000.0</v>
-      </c>
-      <c r="E256" s="7"/>
-      <c r="F256" s="7"/>
-      <c r="G256" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E256" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F256" s="4">
+        <v>19500.0</v>
+      </c>
+      <c r="G256" s="4"/>
       <c r="H256" s="7"/>
       <c r="I256" s="7"/>
       <c r="J256" s="7"/>
@@ -7302,13 +7340,17 @@
         <v>271</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D257" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E257" s="7"/>
-      <c r="F257" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E257" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F257" s="4">
+        <v>6000.0</v>
+      </c>
       <c r="G257" s="7"/>
       <c r="H257" s="7"/>
       <c r="I257" s="7"/>
@@ -7323,10 +7365,10 @@
         <v>272</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D258" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E258" s="7"/>
       <c r="F258" s="7"/>
@@ -7344,10 +7386,10 @@
         <v>273</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D259" s="4">
-        <v>3000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E259" s="7"/>
       <c r="F259" s="7"/>
@@ -7365,17 +7407,17 @@
         <v>274</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="D260" s="4">
-        <v>80000.0</v>
-      </c>
-      <c r="E260" s="6"/>
-      <c r="F260" s="6"/>
-      <c r="G260" s="6"/>
-      <c r="H260" s="6"/>
-      <c r="I260" s="6"/>
-      <c r="J260" s="6"/>
+        <v>89000.0</v>
+      </c>
+      <c r="E260" s="7"/>
+      <c r="F260" s="7"/>
+      <c r="G260" s="7"/>
+      <c r="H260" s="7"/>
+      <c r="I260" s="7"/>
+      <c r="J260" s="7"/>
     </row>
     <row r="261">
       <c r="A261" s="4">
@@ -7386,10 +7428,10 @@
         <v>275</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="D261" s="4">
-        <v>14000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E261" s="7"/>
       <c r="F261" s="7"/>
@@ -7404,13 +7446,13 @@
         <v>261</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="D262" s="4">
-        <v>14500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E262" s="7"/>
       <c r="F262" s="7"/>
@@ -7425,13 +7467,13 @@
         <v>262</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="D263" s="4">
-        <v>15000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E263" s="7"/>
       <c r="F263" s="7"/>
@@ -7446,20 +7488,20 @@
         <v>263</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D264" s="4">
-        <v>15500.0</v>
-      </c>
-      <c r="E264" s="7"/>
-      <c r="F264" s="7"/>
-      <c r="G264" s="7"/>
-      <c r="H264" s="7"/>
-      <c r="I264" s="7"/>
-      <c r="J264" s="7"/>
+        <v>80000.0</v>
+      </c>
+      <c r="E264" s="6"/>
+      <c r="F264" s="6"/>
+      <c r="G264" s="6"/>
+      <c r="H264" s="6"/>
+      <c r="I264" s="6"/>
+      <c r="J264" s="6"/>
     </row>
     <row r="265">
       <c r="A265" s="4">
@@ -7467,13 +7509,13 @@
         <v>264</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D265" s="4">
-        <v>1500.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E265" s="7"/>
       <c r="F265" s="7"/>
@@ -7488,13 +7530,13 @@
         <v>265</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D266" s="4">
-        <v>12500.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E266" s="7"/>
       <c r="F266" s="7"/>
@@ -7512,10 +7554,10 @@
         <v>279</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D267" s="4">
-        <v>500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E267" s="7"/>
       <c r="F267" s="7"/>
@@ -7530,13 +7572,13 @@
         <v>267</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D268" s="4">
-        <v>4500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E268" s="7"/>
       <c r="F268" s="7"/>
@@ -7551,13 +7593,13 @@
         <v>268</v>
       </c>
       <c r="B269" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C269" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="C269" s="5" t="s">
-        <v>277</v>
-      </c>
       <c r="D269" s="4">
-        <v>3000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E269" s="7"/>
       <c r="F269" s="7"/>
@@ -7575,10 +7617,10 @@
         <v>282</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D270" s="4">
-        <v>23000.0</v>
+        <v>12500.0</v>
       </c>
       <c r="E270" s="7"/>
       <c r="F270" s="7"/>
@@ -7596,17 +7638,13 @@
         <v>283</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D271" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E271" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F271" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>500.0</v>
+      </c>
+      <c r="E271" s="7"/>
+      <c r="F271" s="7"/>
       <c r="G271" s="7"/>
       <c r="H271" s="7"/>
       <c r="I271" s="7"/>
@@ -7621,13 +7659,13 @@
         <v>284</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D272" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E272" s="4"/>
-      <c r="F272" s="4"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E272" s="7"/>
+      <c r="F272" s="7"/>
       <c r="G272" s="7"/>
       <c r="H272" s="7"/>
       <c r="I272" s="7"/>
@@ -7642,17 +7680,13 @@
         <v>285</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D273" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E273" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F273" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E273" s="7"/>
+      <c r="F273" s="7"/>
       <c r="G273" s="7"/>
       <c r="H273" s="7"/>
       <c r="I273" s="7"/>
@@ -7667,13 +7701,13 @@
         <v>286</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D274" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="E274" s="4"/>
-      <c r="F274" s="4"/>
+        <v>23000.0</v>
+      </c>
+      <c r="E274" s="7"/>
+      <c r="F274" s="7"/>
       <c r="G274" s="7"/>
       <c r="H274" s="7"/>
       <c r="I274" s="7"/>
@@ -7688,7 +7722,7 @@
         <v>287</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D275" s="4">
         <v>2000.0</v>
@@ -7713,13 +7747,13 @@
         <v>288</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D276" s="4">
         <v>7500.0</v>
       </c>
-      <c r="E276" s="7"/>
-      <c r="F276" s="7"/>
+      <c r="E276" s="4"/>
+      <c r="F276" s="4"/>
       <c r="G276" s="7"/>
       <c r="H276" s="7"/>
       <c r="I276" s="7"/>
@@ -7734,13 +7768,17 @@
         <v>289</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D277" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E277" s="7"/>
-      <c r="F277" s="7"/>
+        <v>2500.0</v>
+      </c>
+      <c r="E277" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F277" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G277" s="7"/>
       <c r="H277" s="7"/>
       <c r="I277" s="7"/>
@@ -7752,16 +7790,16 @@
         <v>277</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D278" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="E278" s="7"/>
-      <c r="F278" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E278" s="4"/>
+      <c r="F278" s="4"/>
       <c r="G278" s="7"/>
       <c r="H278" s="7"/>
       <c r="I278" s="7"/>
@@ -7773,16 +7811,20 @@
         <v>278</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D279" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E279" s="7"/>
-      <c r="F279" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E279" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F279" s="4">
+        <v>7500.0</v>
+      </c>
       <c r="G279" s="7"/>
       <c r="H279" s="7"/>
       <c r="I279" s="7"/>
@@ -7794,13 +7836,13 @@
         <v>279</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D280" s="4">
-        <v>5000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E280" s="7"/>
       <c r="F280" s="7"/>
@@ -7815,10 +7857,10 @@
         <v>280</v>
       </c>
       <c r="B281" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C281" s="5" t="s">
         <v>294</v>
-      </c>
-      <c r="C281" s="5" t="s">
-        <v>290</v>
       </c>
       <c r="D281" s="4">
         <v>1000.0</v>
@@ -7839,7 +7881,7 @@
         <v>295</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D282" s="4">
         <v>10000.0</v>
@@ -7860,7 +7902,7 @@
         <v>296</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D283" s="4">
         <v>500.0</v>
@@ -7881,7 +7923,7 @@
         <v>297</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D284" s="4">
         <v>5000.0</v>
@@ -7902,7 +7944,7 @@
         <v>298</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D285" s="4">
         <v>1000.0</v>
@@ -7923,7 +7965,7 @@
         <v>299</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D286" s="4">
         <v>10000.0</v>
@@ -7944,10 +7986,10 @@
         <v>300</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D287" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E287" s="7"/>
       <c r="F287" s="7"/>
@@ -7965,10 +8007,10 @@
         <v>301</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D288" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E288" s="7"/>
       <c r="F288" s="7"/>
@@ -7986,10 +8028,10 @@
         <v>302</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D289" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E289" s="7"/>
       <c r="F289" s="7"/>
@@ -8007,10 +8049,10 @@
         <v>303</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D290" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E290" s="7"/>
       <c r="F290" s="7"/>
@@ -8028,10 +8070,10 @@
         <v>304</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D291" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E291" s="7"/>
       <c r="F291" s="7"/>
@@ -8049,10 +8091,10 @@
         <v>305</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D292" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E292" s="7"/>
       <c r="F292" s="7"/>
@@ -8070,10 +8112,10 @@
         <v>306</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D293" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E293" s="7"/>
       <c r="F293" s="7"/>
@@ -8091,10 +8133,10 @@
         <v>307</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D294" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E294" s="7"/>
       <c r="F294" s="7"/>
@@ -8112,10 +8154,10 @@
         <v>308</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D295" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E295" s="7"/>
       <c r="F295" s="7"/>
@@ -8133,10 +8175,10 @@
         <v>309</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D296" s="4">
-        <v>2000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E296" s="7"/>
       <c r="F296" s="7"/>
@@ -8154,7 +8196,7 @@
         <v>310</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D297" s="4">
         <v>5000.0</v>
@@ -8175,7 +8217,7 @@
         <v>311</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D298" s="4">
         <v>1000.0</v>
@@ -8196,10 +8238,10 @@
         <v>312</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D299" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E299" s="7"/>
       <c r="F299" s="7"/>
@@ -8217,10 +8259,10 @@
         <v>313</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D300" s="4">
-        <v>1000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E300" s="7"/>
       <c r="F300" s="7"/>
@@ -8238,7 +8280,7 @@
         <v>314</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D301" s="4">
         <v>5000.0</v>
@@ -8259,7 +8301,7 @@
         <v>315</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D302" s="4">
         <v>1000.0</v>
@@ -8280,7 +8322,7 @@
         <v>316</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D303" s="4">
         <v>5000.0</v>
@@ -8301,10 +8343,10 @@
         <v>317</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D304" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E304" s="7"/>
       <c r="F304" s="7"/>
@@ -8322,10 +8364,10 @@
         <v>318</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D305" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E305" s="7"/>
       <c r="F305" s="7"/>
@@ -8343,10 +8385,10 @@
         <v>319</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D306" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E306" s="7"/>
       <c r="F306" s="7"/>
@@ -8364,7 +8406,7 @@
         <v>320</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D307" s="4">
         <v>5000.0</v>
@@ -8385,7 +8427,7 @@
         <v>321</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D308" s="4">
         <v>500.0</v>
@@ -8406,10 +8448,10 @@
         <v>322</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D309" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E309" s="7"/>
       <c r="F309" s="7"/>
@@ -8427,10 +8469,10 @@
         <v>323</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D310" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E310" s="7"/>
       <c r="F310" s="7"/>
@@ -8448,7 +8490,7 @@
         <v>324</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D311" s="4">
         <v>5000.0</v>
@@ -8469,10 +8511,10 @@
         <v>325</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D312" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E312" s="7"/>
       <c r="F312" s="7"/>
@@ -8490,7 +8532,7 @@
         <v>326</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D313" s="4">
         <v>5000.0</v>
@@ -8511,17 +8553,13 @@
         <v>327</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D314" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E314" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F314" s="4">
-        <v>4500.0</v>
-      </c>
+        <v>500.0</v>
+      </c>
+      <c r="E314" s="7"/>
+      <c r="F314" s="7"/>
       <c r="G314" s="7"/>
       <c r="H314" s="7"/>
       <c r="I314" s="7"/>
@@ -8536,10 +8574,10 @@
         <v>328</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D315" s="4">
-        <v>4500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E315" s="7"/>
       <c r="F315" s="7"/>
@@ -8557,13 +8595,13 @@
         <v>329</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D316" s="4">
-        <v>51000.0</v>
-      </c>
-      <c r="E316" s="4"/>
-      <c r="F316" s="4"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E316" s="7"/>
+      <c r="F316" s="7"/>
       <c r="G316" s="7"/>
       <c r="H316" s="7"/>
       <c r="I316" s="7"/>
@@ -8578,17 +8616,13 @@
         <v>330</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D317" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E317" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F317" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E317" s="7"/>
+      <c r="F317" s="7"/>
       <c r="G317" s="7"/>
       <c r="H317" s="7"/>
       <c r="I317" s="7"/>
@@ -8603,13 +8637,17 @@
         <v>331</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D318" s="4">
-        <v>52000.0</v>
-      </c>
-      <c r="E318" s="7"/>
-      <c r="F318" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E318" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F318" s="4">
+        <v>4500.0</v>
+      </c>
       <c r="G318" s="7"/>
       <c r="H318" s="7"/>
       <c r="I318" s="7"/>
@@ -8624,10 +8662,10 @@
         <v>332</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D319" s="4">
-        <v>1000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E319" s="7"/>
       <c r="F319" s="7"/>
@@ -8645,13 +8683,13 @@
         <v>333</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D320" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E320" s="7"/>
-      <c r="F320" s="7"/>
+        <v>51000.0</v>
+      </c>
+      <c r="E320" s="4"/>
+      <c r="F320" s="4"/>
       <c r="G320" s="7"/>
       <c r="H320" s="7"/>
       <c r="I320" s="7"/>
@@ -8666,16 +8704,16 @@
         <v>334</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D321" s="4">
         <v>2000.0</v>
       </c>
       <c r="E321" s="4">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F321" s="4">
-        <v>17000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="G321" s="7"/>
       <c r="H321" s="7"/>
@@ -8691,10 +8729,10 @@
         <v>335</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D322" s="4">
-        <v>5000.0</v>
+        <v>52000.0</v>
       </c>
       <c r="E322" s="7"/>
       <c r="F322" s="7"/>
@@ -8712,17 +8750,13 @@
         <v>336</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D323" s="4">
-        <v>7000.0</v>
-      </c>
-      <c r="E323" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F323" s="4">
-        <v>32500.0</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E323" s="7"/>
+      <c r="F323" s="7"/>
       <c r="G323" s="7"/>
       <c r="H323" s="7"/>
       <c r="I323" s="7"/>
@@ -8737,10 +8771,10 @@
         <v>337</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D324" s="4">
-        <v>7500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E324" s="7"/>
       <c r="F324" s="7"/>
@@ -8758,13 +8792,17 @@
         <v>338</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D325" s="4">
-        <v>9500.0</v>
-      </c>
-      <c r="E325" s="7"/>
-      <c r="F325" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E325" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F325" s="4">
+        <v>17000.0</v>
+      </c>
       <c r="G325" s="7"/>
       <c r="H325" s="7"/>
       <c r="I325" s="7"/>
@@ -8779,10 +8817,10 @@
         <v>339</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D326" s="4">
-        <v>3500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E326" s="7"/>
       <c r="F326" s="7"/>
@@ -8800,13 +8838,17 @@
         <v>340</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D327" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E327" s="7"/>
-      <c r="F327" s="7"/>
+        <v>7000.0</v>
+      </c>
+      <c r="E327" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F327" s="4">
+        <v>32500.0</v>
+      </c>
       <c r="G327" s="7"/>
       <c r="H327" s="7"/>
       <c r="I327" s="7"/>
@@ -8821,17 +8863,13 @@
         <v>341</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D328" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E328" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F328" s="4">
-        <v>22500.0</v>
-      </c>
+        <v>7500.0</v>
+      </c>
+      <c r="E328" s="7"/>
+      <c r="F328" s="7"/>
       <c r="G328" s="7"/>
       <c r="H328" s="7"/>
       <c r="I328" s="7"/>
@@ -8846,17 +8884,13 @@
         <v>342</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D329" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E329" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F329" s="4">
-        <v>12500.0</v>
-      </c>
+        <v>9500.0</v>
+      </c>
+      <c r="E329" s="7"/>
+      <c r="F329" s="7"/>
       <c r="G329" s="7"/>
       <c r="H329" s="7"/>
       <c r="I329" s="7"/>
@@ -8871,13 +8905,13 @@
         <v>343</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D330" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E330" s="4"/>
-      <c r="F330" s="4"/>
+      <c r="E330" s="7"/>
+      <c r="F330" s="7"/>
       <c r="G330" s="7"/>
       <c r="H330" s="7"/>
       <c r="I330" s="7"/>
@@ -8892,14 +8926,14 @@
         <v>344</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D331" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E331" s="4"/>
-      <c r="F331" s="4"/>
-      <c r="G331" s="4"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E331" s="7"/>
+      <c r="F331" s="7"/>
+      <c r="G331" s="7"/>
       <c r="H331" s="7"/>
       <c r="I331" s="7"/>
       <c r="J331" s="7"/>
@@ -8913,16 +8947,16 @@
         <v>345</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D332" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E332" s="4">
         <v>5.0</v>
       </c>
       <c r="F332" s="4">
-        <v>11500.0</v>
+        <v>22500.0</v>
       </c>
       <c r="G332" s="7"/>
       <c r="H332" s="7"/>
@@ -8938,13 +8972,17 @@
         <v>346</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D333" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E333" s="7"/>
-      <c r="F333" s="7"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E333" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F333" s="4">
+        <v>12500.0</v>
+      </c>
       <c r="G333" s="7"/>
       <c r="H333" s="7"/>
       <c r="I333" s="7"/>
@@ -8959,17 +8997,13 @@
         <v>347</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D334" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E334" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F334" s="4">
-        <v>22500.0</v>
-      </c>
+        <v>3500.0</v>
+      </c>
+      <c r="E334" s="4"/>
+      <c r="F334" s="4"/>
       <c r="G334" s="7"/>
       <c r="H334" s="7"/>
       <c r="I334" s="7"/>
@@ -8984,14 +9018,14 @@
         <v>348</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D335" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E335" s="7"/>
-      <c r="F335" s="7"/>
-      <c r="G335" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E335" s="4"/>
+      <c r="F335" s="4"/>
+      <c r="G335" s="4"/>
       <c r="H335" s="7"/>
       <c r="I335" s="7"/>
       <c r="J335" s="7"/>
@@ -9005,13 +9039,17 @@
         <v>349</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D336" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E336" s="7"/>
-      <c r="F336" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E336" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F336" s="4">
+        <v>11500.0</v>
+      </c>
       <c r="G336" s="7"/>
       <c r="H336" s="7"/>
       <c r="I336" s="7"/>
@@ -9026,10 +9064,10 @@
         <v>350</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D337" s="4">
-        <v>3000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E337" s="7"/>
       <c r="F337" s="7"/>
@@ -9047,13 +9085,17 @@
         <v>351</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D338" s="4">
-        <v>14000.0</v>
-      </c>
-      <c r="E338" s="7"/>
-      <c r="F338" s="7"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E338" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F338" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G338" s="7"/>
       <c r="H338" s="7"/>
       <c r="I338" s="7"/>
@@ -9068,7 +9110,7 @@
         <v>352</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>353</v>
+        <v>294</v>
       </c>
       <c r="D339" s="4">
         <v>1000.0</v>
@@ -9086,13 +9128,13 @@
         <v>339</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>353</v>
+        <v>294</v>
       </c>
       <c r="D340" s="4">
-        <v>4000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E340" s="7"/>
       <c r="F340" s="7"/>
@@ -9107,13 +9149,13 @@
         <v>340</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>353</v>
+        <v>294</v>
       </c>
       <c r="D341" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E341" s="7"/>
       <c r="F341" s="7"/>
@@ -9128,13 +9170,13 @@
         <v>341</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>353</v>
+        <v>294</v>
       </c>
       <c r="D342" s="4">
-        <v>10000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E342" s="7"/>
       <c r="F342" s="7"/>
@@ -9149,10 +9191,10 @@
         <v>342</v>
       </c>
       <c r="B343" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C343" s="5" t="s">
         <v>357</v>
-      </c>
-      <c r="C343" s="5" t="s">
-        <v>353</v>
       </c>
       <c r="D343" s="4">
         <v>1000.0</v>
@@ -9173,10 +9215,10 @@
         <v>358</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D344" s="4">
-        <v>10000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E344" s="7"/>
       <c r="F344" s="7"/>
@@ -9194,10 +9236,10 @@
         <v>359</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D345" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E345" s="7"/>
       <c r="F345" s="7"/>
@@ -9215,10 +9257,10 @@
         <v>360</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D346" s="4">
-        <v>2500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E346" s="7"/>
       <c r="F346" s="7"/>
@@ -9236,10 +9278,10 @@
         <v>361</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D347" s="4">
-        <v>3000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E347" s="7"/>
       <c r="F347" s="7"/>
@@ -9257,10 +9299,10 @@
         <v>362</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D348" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E348" s="7"/>
       <c r="F348" s="7"/>
@@ -9278,10 +9320,10 @@
         <v>363</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D349" s="4">
-        <v>3000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E349" s="7"/>
       <c r="F349" s="7"/>
@@ -9299,17 +9341,13 @@
         <v>364</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D350" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E350" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F350" s="4">
-        <v>3000.0</v>
-      </c>
+        <v>2500.0</v>
+      </c>
+      <c r="E350" s="7"/>
+      <c r="F350" s="7"/>
       <c r="G350" s="7"/>
       <c r="H350" s="7"/>
       <c r="I350" s="7"/>
@@ -9324,10 +9362,10 @@
         <v>365</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D351" s="4">
-        <v>500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E351" s="7"/>
       <c r="F351" s="7"/>
@@ -9345,10 +9383,10 @@
         <v>366</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D352" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E352" s="7"/>
       <c r="F352" s="7"/>
@@ -9366,10 +9404,10 @@
         <v>367</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D353" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E353" s="7"/>
       <c r="F353" s="7"/>
@@ -9387,13 +9425,17 @@
         <v>368</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D354" s="4">
-        <v>7000.0</v>
-      </c>
-      <c r="E354" s="7"/>
-      <c r="F354" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E354" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F354" s="4">
+        <v>3000.0</v>
+      </c>
       <c r="G354" s="7"/>
       <c r="H354" s="7"/>
       <c r="I354" s="7"/>
@@ -9408,10 +9450,10 @@
         <v>369</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D355" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E355" s="7"/>
       <c r="F355" s="7"/>
@@ -9429,10 +9471,10 @@
         <v>370</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D356" s="4">
-        <v>25000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E356" s="7"/>
       <c r="F356" s="7"/>
@@ -9450,10 +9492,10 @@
         <v>371</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D357" s="4">
-        <v>8000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E357" s="7"/>
       <c r="F357" s="7"/>
@@ -9471,10 +9513,10 @@
         <v>372</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D358" s="4">
-        <v>4000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E358" s="7"/>
       <c r="F358" s="7"/>
@@ -9492,10 +9534,10 @@
         <v>373</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="D359" s="4">
-        <v>2000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E359" s="7"/>
       <c r="F359" s="7"/>
@@ -9510,13 +9552,13 @@
         <v>359</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="D360" s="4">
-        <v>45000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E360" s="7"/>
       <c r="F360" s="7"/>
@@ -9531,13 +9573,13 @@
         <v>360</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="D361" s="4">
-        <v>2500.0</v>
+        <v>8000.0</v>
       </c>
       <c r="E361" s="7"/>
       <c r="F361" s="7"/>
@@ -9552,13 +9594,13 @@
         <v>361</v>
       </c>
       <c r="B362" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="D362" s="4">
-        <v>2500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E362" s="7"/>
       <c r="F362" s="7"/>
@@ -9573,13 +9615,13 @@
         <v>362</v>
       </c>
       <c r="B363" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C363" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="C363" s="5" t="s">
-        <v>374</v>
-      </c>
       <c r="D363" s="4">
-        <v>4000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E363" s="7"/>
       <c r="F363" s="7"/>
@@ -9597,10 +9639,10 @@
         <v>379</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D364" s="4">
-        <v>5000.0</v>
+        <v>45000.0</v>
       </c>
       <c r="E364" s="7"/>
       <c r="F364" s="7"/>
@@ -9618,16 +9660,16 @@
         <v>380</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D365" s="4">
-        <v>500.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E365" s="7"/>
       <c r="F365" s="7"/>
       <c r="G365" s="7"/>
       <c r="H365" s="7"/>
-      <c r="I365" s="4"/>
+      <c r="I365" s="7"/>
       <c r="J365" s="7"/>
     </row>
     <row r="366">
@@ -9639,10 +9681,10 @@
         <v>381</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D366" s="4">
-        <v>1000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E366" s="7"/>
       <c r="F366" s="7"/>
@@ -9660,10 +9702,10 @@
         <v>382</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D367" s="4">
-        <v>10000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E367" s="7"/>
       <c r="F367" s="7"/>
@@ -9681,10 +9723,10 @@
         <v>383</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D368" s="4">
-        <v>500.0</v>
+        <v>40000.0</v>
       </c>
       <c r="E368" s="7"/>
       <c r="F368" s="7"/>
@@ -9702,10 +9744,10 @@
         <v>384</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D369" s="4">
-        <v>1500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E369" s="7"/>
       <c r="F369" s="7"/>
@@ -9723,16 +9765,16 @@
         <v>385</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D370" s="4">
-        <v>12000.0</v>
+        <v>46000.0</v>
       </c>
       <c r="E370" s="7"/>
       <c r="F370" s="7"/>
       <c r="G370" s="7"/>
       <c r="H370" s="7"/>
-      <c r="I370" s="7"/>
+      <c r="I370" s="4"/>
       <c r="J370" s="7"/>
     </row>
     <row r="371">
@@ -9744,16 +9786,16 @@
         <v>386</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D371" s="4">
-        <v>3000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E371" s="7"/>
       <c r="F371" s="7"/>
       <c r="G371" s="7"/>
       <c r="H371" s="7"/>
-      <c r="I371" s="7"/>
+      <c r="I371" s="4"/>
       <c r="J371" s="7"/>
     </row>
     <row r="372">
@@ -9765,16 +9807,16 @@
         <v>387</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D372" s="4">
-        <v>1000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E372" s="7"/>
       <c r="F372" s="7"/>
       <c r="G372" s="7"/>
       <c r="H372" s="7"/>
-      <c r="I372" s="7"/>
+      <c r="I372" s="4"/>
       <c r="J372" s="7"/>
     </row>
     <row r="373">
@@ -9786,16 +9828,16 @@
         <v>388</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D373" s="4">
-        <v>25000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E373" s="7"/>
       <c r="F373" s="7"/>
       <c r="G373" s="7"/>
       <c r="H373" s="7"/>
-      <c r="I373" s="7"/>
+      <c r="I373" s="4"/>
       <c r="J373" s="7"/>
     </row>
     <row r="374">
@@ -9807,10 +9849,10 @@
         <v>389</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D374" s="4">
-        <v>9000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E374" s="7"/>
       <c r="F374" s="7"/>
@@ -9828,12 +9870,12 @@
         <v>390</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D375" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E375" s="4"/>
+        <v>10000.0</v>
+      </c>
+      <c r="E375" s="7"/>
       <c r="F375" s="7"/>
       <c r="G375" s="7"/>
       <c r="H375" s="7"/>
@@ -9849,10 +9891,10 @@
         <v>391</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D376" s="4">
-        <v>9000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E376" s="7"/>
       <c r="F376" s="7"/>
@@ -9870,10 +9912,10 @@
         <v>392</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D377" s="4">
-        <v>4500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E377" s="7"/>
       <c r="F377" s="7"/>
@@ -9891,10 +9933,10 @@
         <v>393</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D378" s="4">
-        <v>500.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E378" s="7"/>
       <c r="F378" s="7"/>
@@ -9912,7 +9954,7 @@
         <v>394</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D379" s="4">
         <v>3000.0</v>
@@ -9933,7 +9975,7 @@
         <v>395</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D380" s="4">
         <v>1000.0</v>
@@ -9950,63 +9992,63 @@
         <f t="shared" si="1"/>
         <v>380</v>
       </c>
-      <c r="B381" s="9" t="s">
+      <c r="B381" s="5" t="s">
         <v>396</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="D381" s="10">
-        <v>4500.0</v>
-      </c>
-      <c r="E381" s="11"/>
-      <c r="F381" s="11"/>
-      <c r="G381" s="11"/>
-      <c r="H381" s="11"/>
-      <c r="I381" s="11"/>
-      <c r="J381" s="11"/>
+        <v>378</v>
+      </c>
+      <c r="D381" s="4">
+        <v>25000.0</v>
+      </c>
+      <c r="E381" s="7"/>
+      <c r="F381" s="7"/>
+      <c r="G381" s="7"/>
+      <c r="H381" s="7"/>
+      <c r="I381" s="7"/>
+      <c r="J381" s="7"/>
     </row>
     <row r="382">
       <c r="A382" s="4">
         <f t="shared" si="1"/>
         <v>381</v>
       </c>
-      <c r="B382" s="9" t="s">
+      <c r="B382" s="5" t="s">
         <v>397</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="D382" s="10">
-        <v>50000.0</v>
-      </c>
-      <c r="E382" s="11"/>
-      <c r="F382" s="11"/>
-      <c r="G382" s="11"/>
-      <c r="H382" s="11"/>
-      <c r="I382" s="11"/>
-      <c r="J382" s="11"/>
+        <v>378</v>
+      </c>
+      <c r="D382" s="4">
+        <v>9000.0</v>
+      </c>
+      <c r="E382" s="7"/>
+      <c r="F382" s="7"/>
+      <c r="G382" s="7"/>
+      <c r="H382" s="7"/>
+      <c r="I382" s="7"/>
+      <c r="J382" s="7"/>
     </row>
     <row r="383">
       <c r="A383" s="4">
         <f t="shared" si="1"/>
         <v>382</v>
       </c>
-      <c r="B383" s="9" t="s">
+      <c r="B383" s="5" t="s">
         <v>398</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="D383" s="10">
-        <v>12000.0</v>
-      </c>
-      <c r="E383" s="11"/>
-      <c r="F383" s="11"/>
-      <c r="G383" s="11"/>
-      <c r="H383" s="11"/>
-      <c r="I383" s="11"/>
-      <c r="J383" s="11"/>
+        <v>378</v>
+      </c>
+      <c r="D383" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E383" s="4"/>
+      <c r="F383" s="7"/>
+      <c r="G383" s="7"/>
+      <c r="H383" s="7"/>
+      <c r="I383" s="7"/>
+      <c r="J383" s="7"/>
     </row>
     <row r="384">
       <c r="A384" s="4">
@@ -10017,101 +10059,101 @@
         <v>399</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="D384" s="10">
-        <v>4500.0</v>
-      </c>
-      <c r="E384" s="11"/>
-      <c r="F384" s="11"/>
-      <c r="G384" s="11"/>
-      <c r="H384" s="11"/>
-      <c r="I384" s="11"/>
-      <c r="J384" s="11"/>
+        <v>378</v>
+      </c>
+      <c r="D384" s="4">
+        <v>9000.0</v>
+      </c>
+      <c r="E384" s="7"/>
+      <c r="F384" s="7"/>
+      <c r="G384" s="7"/>
+      <c r="H384" s="7"/>
+      <c r="I384" s="7"/>
+      <c r="J384" s="7"/>
     </row>
     <row r="385">
       <c r="A385" s="4">
         <f t="shared" si="1"/>
         <v>384</v>
       </c>
-      <c r="B385" s="9" t="s">
+      <c r="B385" s="5" t="s">
         <v>400</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="D385" s="10">
-        <v>3000.0</v>
-      </c>
-      <c r="E385" s="11"/>
-      <c r="F385" s="11"/>
-      <c r="G385" s="11"/>
-      <c r="H385" s="11"/>
-      <c r="I385" s="11"/>
-      <c r="J385" s="11"/>
+        <v>378</v>
+      </c>
+      <c r="D385" s="4">
+        <v>4500.0</v>
+      </c>
+      <c r="E385" s="7"/>
+      <c r="F385" s="7"/>
+      <c r="G385" s="7"/>
+      <c r="H385" s="7"/>
+      <c r="I385" s="7"/>
+      <c r="J385" s="7"/>
     </row>
     <row r="386">
       <c r="A386" s="4">
         <f t="shared" si="1"/>
         <v>385</v>
       </c>
-      <c r="B386" s="9" t="s">
+      <c r="B386" s="5" t="s">
         <v>401</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="D386" s="10">
-        <v>5000.0</v>
-      </c>
-      <c r="E386" s="11"/>
-      <c r="F386" s="11"/>
-      <c r="G386" s="11"/>
-      <c r="H386" s="11"/>
-      <c r="I386" s="11"/>
-      <c r="J386" s="11"/>
+        <v>378</v>
+      </c>
+      <c r="D386" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="E386" s="7"/>
+      <c r="F386" s="7"/>
+      <c r="G386" s="7"/>
+      <c r="H386" s="7"/>
+      <c r="I386" s="7"/>
+      <c r="J386" s="7"/>
     </row>
     <row r="387">
       <c r="A387" s="4">
         <f t="shared" si="1"/>
         <v>386</v>
       </c>
-      <c r="B387" s="9" t="s">
+      <c r="B387" s="5" t="s">
         <v>402</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="D387" s="10">
-        <v>6000.0</v>
-      </c>
-      <c r="E387" s="11"/>
-      <c r="F387" s="11"/>
-      <c r="G387" s="11"/>
-      <c r="H387" s="11"/>
-      <c r="I387" s="11"/>
-      <c r="J387" s="11"/>
+        <v>378</v>
+      </c>
+      <c r="D387" s="4">
+        <v>3000.0</v>
+      </c>
+      <c r="E387" s="7"/>
+      <c r="F387" s="7"/>
+      <c r="G387" s="7"/>
+      <c r="H387" s="7"/>
+      <c r="I387" s="7"/>
+      <c r="J387" s="7"/>
     </row>
     <row r="388">
       <c r="A388" s="4">
         <f t="shared" si="1"/>
         <v>387</v>
       </c>
-      <c r="B388" s="9" t="s">
+      <c r="B388" s="5" t="s">
         <v>403</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="D388" s="10">
-        <v>12000.0</v>
-      </c>
-      <c r="E388" s="11"/>
-      <c r="F388" s="11"/>
-      <c r="G388" s="11"/>
-      <c r="H388" s="11"/>
-      <c r="I388" s="11"/>
-      <c r="J388" s="11"/>
+        <v>378</v>
+      </c>
+      <c r="D388" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E388" s="7"/>
+      <c r="F388" s="7"/>
+      <c r="G388" s="7"/>
+      <c r="H388" s="7"/>
+      <c r="I388" s="7"/>
+      <c r="J388" s="7"/>
     </row>
     <row r="389">
       <c r="A389" s="4">
@@ -10122,17 +10164,13 @@
         <v>404</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="D389" s="10">
-        <v>200.0</v>
-      </c>
-      <c r="E389" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="F389" s="10">
-        <v>500.0</v>
-      </c>
+        <v>4500.0</v>
+      </c>
+      <c r="E389" s="11"/>
+      <c r="F389" s="11"/>
       <c r="G389" s="11"/>
       <c r="H389" s="11"/>
       <c r="I389" s="11"/>
@@ -10147,27 +10185,32 @@
         <v>405</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="D390" s="10">
-        <v>5000.0</v>
-      </c>
-      <c r="E390" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="F390" s="10">
-        <v>4500.0</v>
-      </c>
+        <v>50000.0</v>
+      </c>
+      <c r="E390" s="11"/>
+      <c r="F390" s="11"/>
       <c r="G390" s="11"/>
       <c r="H390" s="11"/>
       <c r="I390" s="11"/>
       <c r="J390" s="11"/>
     </row>
     <row r="391">
-      <c r="A391" s="12"/>
-      <c r="B391" s="12"/>
-      <c r="C391" s="12"/>
-      <c r="D391" s="11"/>
+      <c r="A391" s="4">
+        <f t="shared" si="1"/>
+        <v>390</v>
+      </c>
+      <c r="B391" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="C391" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="D391" s="10">
+        <v>12000.0</v>
+      </c>
       <c r="E391" s="11"/>
       <c r="F391" s="11"/>
       <c r="G391" s="11"/>
@@ -10176,10 +10219,19 @@
       <c r="J391" s="11"/>
     </row>
     <row r="392">
-      <c r="A392" s="12"/>
-      <c r="B392" s="12"/>
-      <c r="C392" s="12"/>
-      <c r="D392" s="11"/>
+      <c r="A392" s="4">
+        <f t="shared" si="1"/>
+        <v>391</v>
+      </c>
+      <c r="B392" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C392" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="D392" s="10">
+        <v>4500.0</v>
+      </c>
       <c r="E392" s="11"/>
       <c r="F392" s="11"/>
       <c r="G392" s="11"/>
@@ -10188,10 +10240,19 @@
       <c r="J392" s="11"/>
     </row>
     <row r="393">
-      <c r="A393" s="12"/>
-      <c r="B393" s="12"/>
-      <c r="C393" s="12"/>
-      <c r="D393" s="11"/>
+      <c r="A393" s="4">
+        <f t="shared" si="1"/>
+        <v>392</v>
+      </c>
+      <c r="B393" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="C393" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="D393" s="10">
+        <v>3000.0</v>
+      </c>
       <c r="E393" s="11"/>
       <c r="F393" s="11"/>
       <c r="G393" s="11"/>
@@ -10200,10 +10261,19 @@
       <c r="J393" s="11"/>
     </row>
     <row r="394">
-      <c r="A394" s="12"/>
-      <c r="B394" s="12"/>
-      <c r="C394" s="12"/>
-      <c r="D394" s="11"/>
+      <c r="A394" s="4">
+        <f t="shared" si="1"/>
+        <v>393</v>
+      </c>
+      <c r="B394" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C394" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="D394" s="10">
+        <v>5000.0</v>
+      </c>
       <c r="E394" s="11"/>
       <c r="F394" s="11"/>
       <c r="G394" s="11"/>
@@ -10212,10 +10282,19 @@
       <c r="J394" s="11"/>
     </row>
     <row r="395">
-      <c r="A395" s="12"/>
-      <c r="B395" s="12"/>
-      <c r="C395" s="12"/>
-      <c r="D395" s="11"/>
+      <c r="A395" s="4">
+        <f t="shared" si="1"/>
+        <v>394</v>
+      </c>
+      <c r="B395" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="C395" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="D395" s="10">
+        <v>6000.0</v>
+      </c>
       <c r="E395" s="11"/>
       <c r="F395" s="11"/>
       <c r="G395" s="11"/>
@@ -10224,10 +10303,19 @@
       <c r="J395" s="11"/>
     </row>
     <row r="396">
-      <c r="A396" s="12"/>
-      <c r="B396" s="12"/>
-      <c r="C396" s="12"/>
-      <c r="D396" s="11"/>
+      <c r="A396" s="4">
+        <f t="shared" si="1"/>
+        <v>395</v>
+      </c>
+      <c r="B396" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="C396" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D396" s="10">
+        <v>12000.0</v>
+      </c>
       <c r="E396" s="11"/>
       <c r="F396" s="11"/>
       <c r="G396" s="11"/>
@@ -10236,34 +10324,69 @@
       <c r="J396" s="11"/>
     </row>
     <row r="397">
-      <c r="A397" s="12"/>
-      <c r="B397" s="12"/>
-      <c r="C397" s="12"/>
-      <c r="D397" s="11"/>
-      <c r="E397" s="11"/>
-      <c r="F397" s="11"/>
+      <c r="A397" s="4">
+        <f t="shared" si="1"/>
+        <v>396</v>
+      </c>
+      <c r="B397" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="C397" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D397" s="10">
+        <v>200.0</v>
+      </c>
+      <c r="E397" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="F397" s="10">
+        <v>500.0</v>
+      </c>
       <c r="G397" s="11"/>
       <c r="H397" s="11"/>
       <c r="I397" s="11"/>
       <c r="J397" s="11"/>
     </row>
     <row r="398">
-      <c r="A398" s="12"/>
-      <c r="B398" s="12"/>
-      <c r="C398" s="12"/>
-      <c r="D398" s="11"/>
-      <c r="E398" s="11"/>
-      <c r="F398" s="11"/>
+      <c r="A398" s="4">
+        <f t="shared" si="1"/>
+        <v>397</v>
+      </c>
+      <c r="B398" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="C398" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D398" s="10">
+        <v>5000.0</v>
+      </c>
+      <c r="E398" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="F398" s="10">
+        <v>4500.0</v>
+      </c>
       <c r="G398" s="11"/>
       <c r="H398" s="11"/>
       <c r="I398" s="11"/>
       <c r="J398" s="11"/>
     </row>
     <row r="399">
-      <c r="A399" s="12"/>
-      <c r="B399" s="12"/>
-      <c r="C399" s="12"/>
-      <c r="D399" s="11"/>
+      <c r="A399" s="4">
+        <f t="shared" si="1"/>
+        <v>398</v>
+      </c>
+      <c r="B399" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="C399" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D399" s="10">
+        <v>18000.0</v>
+      </c>
       <c r="E399" s="11"/>
       <c r="F399" s="11"/>
       <c r="G399" s="11"/>
@@ -10272,10 +10395,19 @@
       <c r="J399" s="11"/>
     </row>
     <row r="400">
-      <c r="A400" s="12"/>
-      <c r="B400" s="12"/>
-      <c r="C400" s="12"/>
-      <c r="D400" s="11"/>
+      <c r="A400" s="4">
+        <f t="shared" si="1"/>
+        <v>399</v>
+      </c>
+      <c r="B400" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="C400" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D400" s="10">
+        <v>17000.0</v>
+      </c>
       <c r="E400" s="11"/>
       <c r="F400" s="11"/>
       <c r="G400" s="11"/>
@@ -10284,10 +10416,19 @@
       <c r="J400" s="11"/>
     </row>
     <row r="401">
-      <c r="A401" s="12"/>
-      <c r="B401" s="12"/>
-      <c r="C401" s="12"/>
-      <c r="D401" s="11"/>
+      <c r="A401" s="4">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="B401" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="C401" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D401" s="10">
+        <v>17500.0</v>
+      </c>
       <c r="E401" s="11"/>
       <c r="F401" s="11"/>
       <c r="G401" s="11"/>
@@ -10296,10 +10437,19 @@
       <c r="J401" s="11"/>
     </row>
     <row r="402">
-      <c r="A402" s="12"/>
-      <c r="B402" s="12"/>
-      <c r="C402" s="12"/>
-      <c r="D402" s="11"/>
+      <c r="A402" s="4">
+        <f t="shared" si="1"/>
+        <v>401</v>
+      </c>
+      <c r="B402" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="C402" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D402" s="10">
+        <v>9000.0</v>
+      </c>
       <c r="E402" s="11"/>
       <c r="F402" s="11"/>
       <c r="G402" s="11"/>
@@ -10308,10 +10458,19 @@
       <c r="J402" s="11"/>
     </row>
     <row r="403">
-      <c r="A403" s="12"/>
-      <c r="B403" s="12"/>
-      <c r="C403" s="12"/>
-      <c r="D403" s="11"/>
+      <c r="A403" s="4">
+        <f t="shared" si="1"/>
+        <v>402</v>
+      </c>
+      <c r="B403" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="C403" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D403" s="10">
+        <v>9000.0</v>
+      </c>
       <c r="E403" s="11"/>
       <c r="F403" s="11"/>
       <c r="G403" s="11"/>
@@ -10320,10 +10479,19 @@
       <c r="J403" s="11"/>
     </row>
     <row r="404">
-      <c r="A404" s="12"/>
-      <c r="B404" s="12"/>
-      <c r="C404" s="12"/>
-      <c r="D404" s="11"/>
+      <c r="A404" s="4">
+        <f t="shared" si="1"/>
+        <v>403</v>
+      </c>
+      <c r="B404" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="C404" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D404" s="10">
+        <v>19500.0</v>
+      </c>
       <c r="E404" s="11"/>
       <c r="F404" s="11"/>
       <c r="G404" s="11"/>
@@ -11343,97 +11511,97 @@
       <c r="A489" s="12"/>
       <c r="B489" s="12"/>
       <c r="C489" s="12"/>
-      <c r="D489" s="12"/>
-      <c r="E489" s="12"/>
-      <c r="F489" s="12"/>
-      <c r="G489" s="12"/>
-      <c r="H489" s="12"/>
-      <c r="I489" s="12"/>
-      <c r="J489" s="12"/>
+      <c r="D489" s="11"/>
+      <c r="E489" s="11"/>
+      <c r="F489" s="11"/>
+      <c r="G489" s="11"/>
+      <c r="H489" s="11"/>
+      <c r="I489" s="11"/>
+      <c r="J489" s="11"/>
     </row>
     <row r="490">
       <c r="A490" s="12"/>
       <c r="B490" s="12"/>
       <c r="C490" s="12"/>
-      <c r="D490" s="12"/>
-      <c r="E490" s="12"/>
-      <c r="F490" s="12"/>
-      <c r="G490" s="12"/>
-      <c r="H490" s="12"/>
-      <c r="I490" s="12"/>
-      <c r="J490" s="12"/>
+      <c r="D490" s="11"/>
+      <c r="E490" s="11"/>
+      <c r="F490" s="11"/>
+      <c r="G490" s="11"/>
+      <c r="H490" s="11"/>
+      <c r="I490" s="11"/>
+      <c r="J490" s="11"/>
     </row>
     <row r="491">
       <c r="A491" s="12"/>
       <c r="B491" s="12"/>
       <c r="C491" s="12"/>
-      <c r="D491" s="12"/>
-      <c r="E491" s="12"/>
-      <c r="F491" s="12"/>
-      <c r="G491" s="12"/>
-      <c r="H491" s="12"/>
-      <c r="I491" s="12"/>
-      <c r="J491" s="12"/>
+      <c r="D491" s="11"/>
+      <c r="E491" s="11"/>
+      <c r="F491" s="11"/>
+      <c r="G491" s="11"/>
+      <c r="H491" s="11"/>
+      <c r="I491" s="11"/>
+      <c r="J491" s="11"/>
     </row>
     <row r="492">
       <c r="A492" s="12"/>
       <c r="B492" s="12"/>
       <c r="C492" s="12"/>
-      <c r="D492" s="12"/>
-      <c r="E492" s="12"/>
-      <c r="F492" s="12"/>
-      <c r="G492" s="12"/>
-      <c r="H492" s="12"/>
-      <c r="I492" s="12"/>
-      <c r="J492" s="12"/>
+      <c r="D492" s="11"/>
+      <c r="E492" s="11"/>
+      <c r="F492" s="11"/>
+      <c r="G492" s="11"/>
+      <c r="H492" s="11"/>
+      <c r="I492" s="11"/>
+      <c r="J492" s="11"/>
     </row>
     <row r="493">
       <c r="A493" s="12"/>
       <c r="B493" s="12"/>
       <c r="C493" s="12"/>
-      <c r="D493" s="12"/>
-      <c r="E493" s="12"/>
-      <c r="F493" s="12"/>
-      <c r="G493" s="12"/>
-      <c r="H493" s="12"/>
-      <c r="I493" s="12"/>
-      <c r="J493" s="12"/>
+      <c r="D493" s="11"/>
+      <c r="E493" s="11"/>
+      <c r="F493" s="11"/>
+      <c r="G493" s="11"/>
+      <c r="H493" s="11"/>
+      <c r="I493" s="11"/>
+      <c r="J493" s="11"/>
     </row>
     <row r="494">
       <c r="A494" s="12"/>
       <c r="B494" s="12"/>
       <c r="C494" s="12"/>
-      <c r="D494" s="12"/>
-      <c r="E494" s="12"/>
-      <c r="F494" s="12"/>
-      <c r="G494" s="12"/>
-      <c r="H494" s="12"/>
-      <c r="I494" s="12"/>
-      <c r="J494" s="12"/>
+      <c r="D494" s="11"/>
+      <c r="E494" s="11"/>
+      <c r="F494" s="11"/>
+      <c r="G494" s="11"/>
+      <c r="H494" s="11"/>
+      <c r="I494" s="11"/>
+      <c r="J494" s="11"/>
     </row>
     <row r="495">
       <c r="A495" s="12"/>
       <c r="B495" s="12"/>
       <c r="C495" s="12"/>
-      <c r="D495" s="12"/>
-      <c r="E495" s="12"/>
-      <c r="F495" s="12"/>
-      <c r="G495" s="12"/>
-      <c r="H495" s="12"/>
-      <c r="I495" s="12"/>
-      <c r="J495" s="12"/>
+      <c r="D495" s="11"/>
+      <c r="E495" s="11"/>
+      <c r="F495" s="11"/>
+      <c r="G495" s="11"/>
+      <c r="H495" s="11"/>
+      <c r="I495" s="11"/>
+      <c r="J495" s="11"/>
     </row>
     <row r="496">
       <c r="A496" s="12"/>
       <c r="B496" s="12"/>
       <c r="C496" s="12"/>
-      <c r="D496" s="12"/>
-      <c r="E496" s="12"/>
-      <c r="F496" s="12"/>
-      <c r="G496" s="12"/>
-      <c r="H496" s="12"/>
-      <c r="I496" s="12"/>
-      <c r="J496" s="12"/>
+      <c r="D496" s="11"/>
+      <c r="E496" s="11"/>
+      <c r="F496" s="11"/>
+      <c r="G496" s="11"/>
+      <c r="H496" s="11"/>
+      <c r="I496" s="11"/>
+      <c r="J496" s="11"/>
     </row>
     <row r="497">
       <c r="A497" s="12"/>
@@ -19763,15 +19931,111 @@
       <c r="I1190" s="12"/>
       <c r="J1190" s="12"/>
     </row>
+    <row r="1191">
+      <c r="A1191" s="12"/>
+      <c r="B1191" s="12"/>
+      <c r="C1191" s="12"/>
+      <c r="D1191" s="12"/>
+      <c r="E1191" s="12"/>
+      <c r="F1191" s="12"/>
+      <c r="G1191" s="12"/>
+      <c r="H1191" s="12"/>
+      <c r="I1191" s="12"/>
+      <c r="J1191" s="12"/>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="12"/>
+      <c r="B1192" s="12"/>
+      <c r="C1192" s="12"/>
+      <c r="D1192" s="12"/>
+      <c r="E1192" s="12"/>
+      <c r="F1192" s="12"/>
+      <c r="G1192" s="12"/>
+      <c r="H1192" s="12"/>
+      <c r="I1192" s="12"/>
+      <c r="J1192" s="12"/>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="12"/>
+      <c r="B1193" s="12"/>
+      <c r="C1193" s="12"/>
+      <c r="D1193" s="12"/>
+      <c r="E1193" s="12"/>
+      <c r="F1193" s="12"/>
+      <c r="G1193" s="12"/>
+      <c r="H1193" s="12"/>
+      <c r="I1193" s="12"/>
+      <c r="J1193" s="12"/>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="12"/>
+      <c r="B1194" s="12"/>
+      <c r="C1194" s="12"/>
+      <c r="D1194" s="12"/>
+      <c r="E1194" s="12"/>
+      <c r="F1194" s="12"/>
+      <c r="G1194" s="12"/>
+      <c r="H1194" s="12"/>
+      <c r="I1194" s="12"/>
+      <c r="J1194" s="12"/>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="12"/>
+      <c r="B1195" s="12"/>
+      <c r="C1195" s="12"/>
+      <c r="D1195" s="12"/>
+      <c r="E1195" s="12"/>
+      <c r="F1195" s="12"/>
+      <c r="G1195" s="12"/>
+      <c r="H1195" s="12"/>
+      <c r="I1195" s="12"/>
+      <c r="J1195" s="12"/>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="12"/>
+      <c r="B1196" s="12"/>
+      <c r="C1196" s="12"/>
+      <c r="D1196" s="12"/>
+      <c r="E1196" s="12"/>
+      <c r="F1196" s="12"/>
+      <c r="G1196" s="12"/>
+      <c r="H1196" s="12"/>
+      <c r="I1196" s="12"/>
+      <c r="J1196" s="12"/>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="12"/>
+      <c r="B1197" s="12"/>
+      <c r="C1197" s="12"/>
+      <c r="D1197" s="12"/>
+      <c r="E1197" s="12"/>
+      <c r="F1197" s="12"/>
+      <c r="G1197" s="12"/>
+      <c r="H1197" s="12"/>
+      <c r="I1197" s="12"/>
+      <c r="J1197" s="12"/>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="12"/>
+      <c r="B1198" s="12"/>
+      <c r="C1198" s="12"/>
+      <c r="D1198" s="12"/>
+      <c r="E1198" s="12"/>
+      <c r="F1198" s="12"/>
+      <c r="G1198" s="12"/>
+      <c r="H1198" s="12"/>
+      <c r="I1198" s="12"/>
+      <c r="J1198" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$390"/>
-  <conditionalFormatting sqref="A2:J1190">
+  <autoFilter ref="$B$1:$C$404"/>
+  <conditionalFormatting sqref="A2:J1198">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C390">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C404">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19832,7 +20096,7 @@
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4">
@@ -19851,7 +20115,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -19870,7 +20134,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -19889,7 +20153,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -19908,7 +20172,7 @@
         <v>GROSIR5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="4">
@@ -19927,7 +20191,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -19946,7 +20210,7 @@
         <v>GROSIR7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="4">
@@ -19965,7 +20229,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -19984,7 +20248,7 @@
         <v>GROSIR9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="4">
@@ -20003,7 +20267,7 @@
         <v>GROSIR10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="4">
@@ -20022,7 +20286,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -20041,7 +20305,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -20060,7 +20324,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -20079,7 +20343,7 @@
         <v>GROSIR14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="4">
@@ -20098,7 +20362,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -20117,7 +20381,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -20136,7 +20400,7 @@
         <v>GROSIR17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="4">
@@ -20155,7 +20419,7 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
@@ -20174,7 +20438,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -20193,7 +20457,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -20212,7 +20476,7 @@
         <v>GROSIR21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4">
@@ -20231,7 +20495,7 @@
         <v>GROSIR22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="4">
@@ -20250,7 +20514,7 @@
         <v>GROSIR23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="4">
@@ -20269,7 +20533,7 @@
         <v>GROSIR24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="4">
@@ -20288,7 +20552,7 @@
         <v>GROSIR25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="4">
@@ -20307,7 +20571,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -20326,7 +20590,7 @@
         <v>GROSIR27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="4">
@@ -20345,7 +20609,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -20364,7 +20628,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -20383,7 +20647,7 @@
         <v>GROSIR30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="4">
@@ -20402,7 +20666,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -20421,7 +20685,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -20440,7 +20704,7 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
@@ -20459,7 +20723,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -20478,7 +20742,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -20497,7 +20761,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -20516,7 +20780,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -20535,7 +20799,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -20554,7 +20818,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -20573,7 +20837,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -20592,7 +20856,7 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
@@ -20611,7 +20875,7 @@
         <v>GROSIR42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="446">
   <si>
     <t>Barcode</t>
   </si>
@@ -2180,8 +2180,13 @@
       <c r="D22" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
+      <c r="E22" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F22" s="6">
+        <f>3500*5</f>
+        <v>17500</v>
+      </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
@@ -10337,12 +10342,8 @@
       <c r="D397" s="10">
         <v>200.0</v>
       </c>
-      <c r="E397" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="F397" s="10">
-        <v>500.0</v>
-      </c>
+      <c r="E397" s="10"/>
+      <c r="F397" s="10"/>
       <c r="G397" s="11"/>
       <c r="H397" s="11"/>
       <c r="I397" s="11"/>
@@ -20092,7 +20093,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="str">
-        <f t="shared" ref="A2:A43" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
+        <f t="shared" ref="A2:A44" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -20889,10 +20890,17 @@
       <c r="J43" s="13"/>
     </row>
     <row r="44">
-      <c r="A44" s="4"/>
-      <c r="B44" s="5"/>
+      <c r="A44" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR43</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="4"/>
+      <c r="D44" s="4">
+        <v>3500.0</v>
+      </c>
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
       <c r="G44" s="13"/>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$404</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$405</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$260</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="447">
   <si>
     <t>Barcode</t>
   </si>
@@ -494,34 +494,34 @@
     <t>Gula Merah 250g</t>
   </si>
   <si>
-    <t>Indofood Racik Sayur Lodeh</t>
-  </si>
-  <si>
-    <t>Indofood Racik Sayur Lodeh Renceng</t>
-  </si>
-  <si>
-    <t>Indofood Racik Sayur Asem</t>
-  </si>
-  <si>
-    <t>Indofood Racik Sayur Asem Renceng</t>
-  </si>
-  <si>
-    <t>Indofood Racik Sayur Sop</t>
-  </si>
-  <si>
-    <t>Indofood Racik Sayur Sop Renceng</t>
-  </si>
-  <si>
-    <t>Indofood Racik Ayam Goreng</t>
-  </si>
-  <si>
-    <t>Indofood Racik Ayam Goreng Renceng</t>
-  </si>
-  <si>
-    <t>Indofood Racik Nasi Goreng</t>
-  </si>
-  <si>
-    <t>Indofood Racik Nasi Goreng Renceng</t>
+    <t>Racik Lodeh</t>
+  </si>
+  <si>
+    <t>Racik Lodeh Renceng</t>
+  </si>
+  <si>
+    <t>Racik Asem</t>
+  </si>
+  <si>
+    <t>Racik Asem Renceng</t>
+  </si>
+  <si>
+    <t>Racik Sop</t>
+  </si>
+  <si>
+    <t>Racik Sop Renceng</t>
+  </si>
+  <si>
+    <t>Racik Ayam Goreng</t>
+  </si>
+  <si>
+    <t>Racik Ayam Goreng Renceng</t>
+  </si>
+  <si>
+    <t>Racik Nasi Goreng</t>
+  </si>
+  <si>
+    <t>Racik Nasi Goreng Renceng</t>
   </si>
   <si>
     <t>Bawang Putih</t>
@@ -671,10 +671,10 @@
     <t>Camel Bungkus</t>
   </si>
   <si>
-    <t>Marlboro Filter Black</t>
-  </si>
-  <si>
-    <t>Marlboro Filter Black Bungkus</t>
+    <t>Marlboro Black</t>
+  </si>
+  <si>
+    <t>Marlboro Black Bungkus</t>
   </si>
   <si>
     <t>Dji Sam Soe</t>
@@ -1275,6 +1275,9 @@
   </si>
   <si>
     <t>Sosis So Nice Toples</t>
+  </si>
+  <si>
+    <t>Siip 500 dus</t>
   </si>
   <si>
     <t>Djarum Coklat Bungkus SLOP</t>
@@ -1740,7 +1743,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A404" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A405" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -10501,10 +10504,19 @@
       <c r="J404" s="11"/>
     </row>
     <row r="405">
-      <c r="A405" s="12"/>
-      <c r="B405" s="12"/>
-      <c r="C405" s="12"/>
-      <c r="D405" s="11"/>
+      <c r="A405" s="4">
+        <f t="shared" si="1"/>
+        <v>404</v>
+      </c>
+      <c r="B405" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="C405" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D405" s="10">
+        <v>8500.0</v>
+      </c>
       <c r="E405" s="11"/>
       <c r="F405" s="11"/>
       <c r="G405" s="11"/>
@@ -20029,14 +20041,14 @@
       <c r="J1198" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$404"/>
+  <autoFilter ref="$B$1:$C$405"/>
   <conditionalFormatting sqref="A2:J1198">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C404">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C405">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20116,7 +20128,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -20135,7 +20147,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -20154,7 +20166,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -20192,7 +20204,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -20230,7 +20242,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -20287,7 +20299,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -20306,7 +20318,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -20325,7 +20337,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -20363,7 +20375,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -20382,7 +20394,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -20420,7 +20432,7 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
@@ -20439,7 +20451,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -20458,7 +20470,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -20572,7 +20584,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -20610,7 +20622,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -20629,7 +20641,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -20667,7 +20679,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -20686,7 +20698,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -20705,7 +20717,7 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
@@ -20724,7 +20736,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -20743,7 +20755,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -20762,7 +20774,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -20781,7 +20793,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -20800,7 +20812,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -20838,7 +20850,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -20876,7 +20888,7 @@
         <v>GROSIR42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$405</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$409</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$260</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="451">
   <si>
     <t>Barcode</t>
   </si>
@@ -62,6 +62,18 @@
     <t>Nutrisari Florida Orange Renceng</t>
   </si>
   <si>
+    <t>Marimas</t>
+  </si>
+  <si>
+    <t>Marimas Renceng</t>
+  </si>
+  <si>
+    <t>Adem Sari Bubuk</t>
+  </si>
+  <si>
+    <t>Adem Sari Bubuk PAK</t>
+  </si>
+  <si>
     <t>Aqua 1500ml</t>
   </si>
   <si>
@@ -83,10 +95,10 @@
     <t>Ale Ale Dus</t>
   </si>
   <si>
-    <t>Adem Sari</t>
-  </si>
-  <si>
-    <t>Adem Sari Dus</t>
+    <t>Adem Sari Minuman</t>
+  </si>
+  <si>
+    <t>Adem Sari Minuman Dus</t>
   </si>
   <si>
     <t>Teh Gelas</t>
@@ -1743,7 +1755,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A405" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A409" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1834,10 +1846,10 @@
         <v>15</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D6" s="4">
-        <v>6000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -1852,16 +1864,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D7" s="4">
-        <v>52000.0</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>10000.0</v>
+      </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -1873,13 +1889,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D8" s="4">
-        <v>1000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -1894,13 +1910,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D9" s="4">
-        <v>20000.0</v>
+        <v>52000.0</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
@@ -1915,13 +1931,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="D10" s="4">
-        <v>1000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -1939,17 +1955,17 @@
         <v>21</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D11" s="4">
-        <v>20000.0</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
+        <v>52000.0</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
     </row>
     <row r="12">
       <c r="A12" s="4">
@@ -1960,10 +1976,10 @@
         <v>22</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D12" s="4">
-        <v>7000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
@@ -1981,10 +1997,10 @@
         <v>23</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D13" s="4">
-        <v>150000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -2002,7 +2018,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4">
         <v>1000.0</v>
@@ -2023,10 +2039,10 @@
         <v>25</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D15" s="4">
-        <v>19500.0</v>
+        <v>20000.0</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -2044,10 +2060,10 @@
         <v>26</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D16" s="4">
-        <v>1000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
@@ -2065,17 +2081,17 @@
         <v>27</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D17" s="4">
-        <v>20500.0</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
+        <v>150000.0</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
     </row>
     <row r="18">
       <c r="A18" s="4">
@@ -2086,7 +2102,7 @@
         <v>28</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D18" s="4">
         <v>1000.0</v>
@@ -2107,10 +2123,10 @@
         <v>29</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D19" s="4">
-        <v>20000.0</v>
+        <v>19500.0</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
@@ -2128,23 +2144,15 @@
         <v>30</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D20" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E20" s="8">
-        <v>5.0</v>
-      </c>
-      <c r="F20" s="8">
-        <v>14500.0</v>
-      </c>
-      <c r="G20" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="H20" s="4">
-        <v>29000.0</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
     </row>
@@ -2157,10 +2165,10 @@
         <v>31</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D21" s="4">
-        <v>63000.0</v>
+        <v>20500.0</v>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
@@ -2178,18 +2186,13 @@
         <v>32</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D22" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E22" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F22" s="6">
-        <f>3500*5</f>
-        <v>17500</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
@@ -2204,17 +2207,17 @@
         <v>33</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D23" s="4">
-        <v>80000.0</v>
-      </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+        <v>20000.0</v>
+      </c>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
     </row>
     <row r="24">
       <c r="A24" s="4">
@@ -2225,19 +2228,23 @@
         <v>34</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D24" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="8">
         <v>5.0</v>
       </c>
-      <c r="F24" s="4">
-        <v>16500.0</v>
-      </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
+      <c r="F24" s="8">
+        <v>14500.0</v>
+      </c>
+      <c r="G24" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="H24" s="4">
+        <v>29000.0</v>
+      </c>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
     </row>
@@ -2250,10 +2257,10 @@
         <v>35</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D25" s="4">
-        <v>39000.0</v>
+        <v>63000.0</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
@@ -2271,13 +2278,18 @@
         <v>36</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D26" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E26" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F26" s="6">
+        <f>3500*5</f>
+        <v>17500</v>
+      </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -2292,10 +2304,10 @@
         <v>37</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D27" s="4">
-        <v>29000.0</v>
+        <v>80000.0</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
@@ -2313,13 +2325,17 @@
         <v>38</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D28" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
+      <c r="E28" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F28" s="4">
+        <v>16500.0</v>
+      </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -2334,17 +2350,17 @@
         <v>39</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D29" s="4">
-        <v>35000.0</v>
-      </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
+        <v>39000.0</v>
+      </c>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
     </row>
     <row r="30">
       <c r="A30" s="4">
@@ -2355,15 +2371,15 @@
         <v>40</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D30" s="4">
-        <v>3500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="4"/>
+      <c r="H30" s="6"/>
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
     </row>
@@ -2376,10 +2392,10 @@
         <v>41</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D31" s="4">
-        <v>19000.0</v>
+        <v>29000.0</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -2397,10 +2413,10 @@
         <v>42</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D32" s="4">
-        <v>2500.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
@@ -2418,17 +2434,13 @@
         <v>43</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D33" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E33" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F33" s="4">
-        <v>13500.0</v>
-      </c>
+        <v>35000.0</v>
+      </c>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
@@ -2443,15 +2455,15 @@
         <v>44</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D34" s="4">
-        <v>31000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
+      <c r="H34" s="4"/>
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
@@ -2464,10 +2476,10 @@
         <v>45</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D35" s="4">
-        <v>2500.0</v>
+        <v>19000.0</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
@@ -2485,10 +2497,10 @@
         <v>46</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D36" s="4">
-        <v>46000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
@@ -2506,13 +2518,17 @@
         <v>47</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D37" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E37" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F37" s="4">
+        <v>13500.0</v>
+      </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
@@ -2527,10 +2543,10 @@
         <v>48</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D38" s="4">
-        <v>52000.0</v>
+        <v>31000.0</v>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
@@ -2548,10 +2564,10 @@
         <v>49</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D39" s="4">
-        <v>21000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
@@ -2569,10 +2585,10 @@
         <v>50</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D40" s="4">
-        <v>22000.0</v>
+        <v>46000.0</v>
       </c>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
@@ -2590,10 +2606,10 @@
         <v>51</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D41" s="4">
-        <v>2000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
@@ -2611,10 +2627,10 @@
         <v>52</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D42" s="4">
-        <v>32000.0</v>
+        <v>52000.0</v>
       </c>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
@@ -2632,10 +2648,10 @@
         <v>53</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D43" s="4">
-        <v>47000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
@@ -2653,10 +2669,10 @@
         <v>54</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D44" s="4">
-        <v>3500.0</v>
+        <v>22000.0</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
@@ -2674,10 +2690,10 @@
         <v>55</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D45" s="4">
-        <v>36000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
@@ -2695,10 +2711,10 @@
         <v>56</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D46" s="4">
-        <v>7000.0</v>
+        <v>32000.0</v>
       </c>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
@@ -2716,10 +2732,10 @@
         <v>57</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D47" s="4">
-        <v>150000.0</v>
+        <v>47000.0</v>
       </c>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
@@ -2737,17 +2753,13 @@
         <v>58</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D48" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E48" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F48" s="4">
-        <v>16000.0</v>
-      </c>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
@@ -2762,10 +2774,10 @@
         <v>59</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D49" s="4">
-        <v>128000.0</v>
+        <v>36000.0</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
@@ -2783,17 +2795,17 @@
         <v>60</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D50" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
+        <v>7000.0</v>
+      </c>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
     </row>
     <row r="51">
       <c r="A51" s="4">
@@ -2804,10 +2816,10 @@
         <v>61</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D51" s="4">
-        <v>36000.0</v>
+        <v>150000.0</v>
       </c>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
@@ -2825,13 +2837,17 @@
         <v>62</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D52" s="4">
-        <v>20000.0</v>
-      </c>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E52" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F52" s="4">
+        <v>16000.0</v>
+      </c>
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
       <c r="I52" s="6"/>
@@ -2846,10 +2862,10 @@
         <v>63</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D53" s="4">
-        <v>1000.0</v>
+        <v>128000.0</v>
       </c>
       <c r="E53" s="6"/>
       <c r="F53" s="6"/>
@@ -2867,10 +2883,10 @@
         <v>64</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D54" s="4">
-        <v>5000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
@@ -2888,10 +2904,10 @@
         <v>65</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D55" s="4">
-        <v>2500.0</v>
+        <v>36000.0</v>
       </c>
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
@@ -2912,14 +2928,14 @@
         <v>11</v>
       </c>
       <c r="D56" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
+        <v>20000.0</v>
+      </c>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
     </row>
     <row r="57">
       <c r="A57" s="4">
@@ -2933,7 +2949,7 @@
         <v>11</v>
       </c>
       <c r="D57" s="4">
-        <v>2000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
@@ -2954,14 +2970,14 @@
         <v>11</v>
       </c>
       <c r="D58" s="4">
-        <v>9500.0</v>
-      </c>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
     </row>
     <row r="59">
       <c r="A59" s="4">
@@ -2975,7 +2991,7 @@
         <v>11</v>
       </c>
       <c r="D59" s="4">
-        <v>4500.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
@@ -2996,7 +3012,7 @@
         <v>11</v>
       </c>
       <c r="D60" s="4">
-        <v>38000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
@@ -3038,14 +3054,14 @@
         <v>11</v>
       </c>
       <c r="D62" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
+        <v>9500.0</v>
+      </c>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
     </row>
     <row r="63">
       <c r="A63" s="4">
@@ -3059,7 +3075,7 @@
         <v>11</v>
       </c>
       <c r="D63" s="4">
-        <v>2000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
@@ -3080,7 +3096,7 @@
         <v>11</v>
       </c>
       <c r="D64" s="4">
-        <v>17000.0</v>
+        <v>38000.0</v>
       </c>
       <c r="E64" s="7"/>
       <c r="F64" s="7"/>
@@ -3122,14 +3138,14 @@
         <v>11</v>
       </c>
       <c r="D66" s="4">
-        <v>15000.0</v>
-      </c>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
+        <v>17000.0</v>
+      </c>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7"/>
+      <c r="J66" s="7"/>
     </row>
     <row r="67">
       <c r="A67" s="4">
@@ -3164,7 +3180,7 @@
         <v>11</v>
       </c>
       <c r="D68" s="4">
-        <v>15000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="7"/>
@@ -3250,12 +3266,12 @@
       <c r="D72" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="7"/>
+      <c r="J72" s="7"/>
     </row>
     <row r="73">
       <c r="A73" s="4">
@@ -3292,12 +3308,12 @@
       <c r="D74" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
     </row>
     <row r="75">
       <c r="A75" s="4">
@@ -3374,14 +3390,14 @@
         <v>11</v>
       </c>
       <c r="D78" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
+        <v>15000.0</v>
+      </c>
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
+      <c r="G78" s="7"/>
+      <c r="H78" s="7"/>
+      <c r="I78" s="7"/>
+      <c r="J78" s="7"/>
     </row>
     <row r="79">
       <c r="A79" s="4">
@@ -3395,14 +3411,14 @@
         <v>11</v>
       </c>
       <c r="D79" s="4">
-        <v>16500.0</v>
-      </c>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
-      <c r="I79" s="7"/>
-      <c r="J79" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6"/>
+      <c r="J79" s="6"/>
     </row>
     <row r="80">
       <c r="A80" s="4">
@@ -3416,7 +3432,7 @@
         <v>11</v>
       </c>
       <c r="D80" s="4">
-        <v>2000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
@@ -3437,14 +3453,14 @@
         <v>11</v>
       </c>
       <c r="D81" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
-      <c r="I81" s="7"/>
-      <c r="J81" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="6"/>
     </row>
     <row r="82">
       <c r="A82" s="4">
@@ -3479,14 +3495,14 @@
         <v>11</v>
       </c>
       <c r="D83" s="4">
-        <v>8500.0</v>
-      </c>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="6"/>
-      <c r="J83" s="6"/>
+        <v>16500.0</v>
+      </c>
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7"/>
+      <c r="J83" s="7"/>
     </row>
     <row r="84">
       <c r="A84" s="4">
@@ -3523,12 +3539,12 @@
       <c r="D85" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
-      <c r="J85" s="6"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="7"/>
+      <c r="H85" s="7"/>
+      <c r="I85" s="7"/>
+      <c r="J85" s="7"/>
     </row>
     <row r="86">
       <c r="A86" s="4">
@@ -3563,14 +3579,14 @@
         <v>11</v>
       </c>
       <c r="D87" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E87" s="7"/>
-      <c r="F87" s="7"/>
-      <c r="G87" s="7"/>
-      <c r="H87" s="7"/>
-      <c r="I87" s="7"/>
-      <c r="J87" s="7"/>
+        <v>8500.0</v>
+      </c>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="6"/>
+      <c r="J87" s="6"/>
     </row>
     <row r="88">
       <c r="A88" s="4">
@@ -3584,7 +3600,7 @@
         <v>11</v>
       </c>
       <c r="D88" s="4">
-        <v>10000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
@@ -3605,7 +3621,7 @@
         <v>11</v>
       </c>
       <c r="D89" s="4">
-        <v>10000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
@@ -3626,7 +3642,7 @@
         <v>11</v>
       </c>
       <c r="D90" s="4">
-        <v>90000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
@@ -3649,12 +3665,12 @@
       <c r="D91" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E91" s="6"/>
-      <c r="F91" s="6"/>
-      <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6"/>
-      <c r="J91" s="6"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
+      <c r="G91" s="7"/>
+      <c r="H91" s="7"/>
+      <c r="I91" s="7"/>
+      <c r="J91" s="7"/>
     </row>
     <row r="92">
       <c r="A92" s="4">
@@ -3668,14 +3684,14 @@
         <v>11</v>
       </c>
       <c r="D92" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-      <c r="G92" s="7"/>
-      <c r="H92" s="7"/>
-      <c r="I92" s="7"/>
-      <c r="J92" s="7"/>
+        <v>10000.0</v>
+      </c>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="6"/>
+      <c r="J92" s="6"/>
     </row>
     <row r="93">
       <c r="A93" s="4">
@@ -3689,14 +3705,14 @@
         <v>11</v>
       </c>
       <c r="D93" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7"/>
-      <c r="I93" s="7"/>
-      <c r="J93" s="7"/>
+        <v>10000.0</v>
+      </c>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="6"/>
+      <c r="J93" s="6"/>
     </row>
     <row r="94">
       <c r="A94" s="4">
@@ -3710,14 +3726,14 @@
         <v>11</v>
       </c>
       <c r="D94" s="4">
-        <v>23000.0</v>
-      </c>
-      <c r="E94" s="7"/>
-      <c r="F94" s="7"/>
-      <c r="G94" s="7"/>
-      <c r="H94" s="7"/>
-      <c r="I94" s="7"/>
-      <c r="J94" s="7"/>
+        <v>90000.0</v>
+      </c>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6"/>
+      <c r="J94" s="6"/>
     </row>
     <row r="95">
       <c r="A95" s="4">
@@ -3733,12 +3749,12 @@
       <c r="D95" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="7"/>
-      <c r="H95" s="7"/>
-      <c r="I95" s="7"/>
-      <c r="J95" s="7"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="6"/>
+      <c r="J95" s="6"/>
     </row>
     <row r="96">
       <c r="A96" s="4">
@@ -3752,14 +3768,14 @@
         <v>11</v>
       </c>
       <c r="D96" s="4">
-        <v>15500.0</v>
-      </c>
-      <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-      <c r="J96" s="6"/>
+        <v>17000.0</v>
+      </c>
+      <c r="E96" s="7"/>
+      <c r="F96" s="7"/>
+      <c r="G96" s="7"/>
+      <c r="H96" s="7"/>
+      <c r="I96" s="7"/>
+      <c r="J96" s="7"/>
     </row>
     <row r="97">
       <c r="A97" s="4">
@@ -3773,14 +3789,14 @@
         <v>11</v>
       </c>
       <c r="D97" s="4">
-        <v>1500.0</v>
-      </c>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
-      <c r="J97" s="6"/>
+        <v>2500.0</v>
+      </c>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="7"/>
+      <c r="I97" s="7"/>
+      <c r="J97" s="7"/>
     </row>
     <row r="98">
       <c r="A98" s="4">
@@ -3794,14 +3810,14 @@
         <v>11</v>
       </c>
       <c r="D98" s="4">
-        <v>11500.0</v>
-      </c>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6"/>
-      <c r="J98" s="6"/>
+        <v>23000.0</v>
+      </c>
+      <c r="E98" s="7"/>
+      <c r="F98" s="7"/>
+      <c r="G98" s="7"/>
+      <c r="H98" s="7"/>
+      <c r="I98" s="7"/>
+      <c r="J98" s="7"/>
     </row>
     <row r="99">
       <c r="A99" s="4">
@@ -3815,14 +3831,14 @@
         <v>11</v>
       </c>
       <c r="D99" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-      <c r="J99" s="6"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E99" s="7"/>
+      <c r="F99" s="7"/>
+      <c r="G99" s="7"/>
+      <c r="H99" s="7"/>
+      <c r="I99" s="7"/>
+      <c r="J99" s="7"/>
     </row>
     <row r="100">
       <c r="A100" s="4">
@@ -3836,7 +3852,7 @@
         <v>11</v>
       </c>
       <c r="D100" s="4">
-        <v>9000.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
@@ -3857,7 +3873,7 @@
         <v>11</v>
       </c>
       <c r="D101" s="4">
-        <v>2500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
@@ -3878,7 +3894,7 @@
         <v>11</v>
       </c>
       <c r="D102" s="4">
-        <v>19000.0</v>
+        <v>11500.0</v>
       </c>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -3899,7 +3915,7 @@
         <v>11</v>
       </c>
       <c r="D103" s="4">
-        <v>1500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
@@ -3920,7 +3936,7 @@
         <v>11</v>
       </c>
       <c r="D104" s="4">
-        <v>8500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
@@ -3941,7 +3957,7 @@
         <v>11</v>
       </c>
       <c r="D105" s="4">
-        <v>3500.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
@@ -3962,7 +3978,7 @@
         <v>11</v>
       </c>
       <c r="D106" s="4">
-        <v>15000.0</v>
+        <v>19000.0</v>
       </c>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -3983,7 +3999,7 @@
         <v>11</v>
       </c>
       <c r="D107" s="4">
-        <v>2000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
@@ -4004,7 +4020,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="4">
-        <v>16000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
@@ -4022,10 +4038,10 @@
         <v>119</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="D109" s="4">
-        <v>6000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
@@ -4040,20 +4056,20 @@
         <v>109</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="D110" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E110" s="7"/>
-      <c r="F110" s="7"/>
-      <c r="G110" s="7"/>
-      <c r="H110" s="7"/>
-      <c r="I110" s="7"/>
-      <c r="J110" s="7"/>
+        <v>15000.0</v>
+      </c>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="6"/>
+      <c r="H110" s="6"/>
+      <c r="I110" s="6"/>
+      <c r="J110" s="6"/>
     </row>
     <row r="111">
       <c r="A111" s="4">
@@ -4061,20 +4077,20 @@
         <v>110</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="D111" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="E111" s="7"/>
-      <c r="F111" s="7"/>
-      <c r="G111" s="7"/>
-      <c r="H111" s="7"/>
-      <c r="I111" s="7"/>
-      <c r="J111" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E111" s="6"/>
+      <c r="F111" s="6"/>
+      <c r="G111" s="6"/>
+      <c r="H111" s="6"/>
+      <c r="I111" s="6"/>
+      <c r="J111" s="6"/>
     </row>
     <row r="112">
       <c r="A112" s="4">
@@ -4082,20 +4098,20 @@
         <v>111</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="D112" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E112" s="7"/>
-      <c r="F112" s="7"/>
-      <c r="G112" s="7"/>
-      <c r="H112" s="7"/>
-      <c r="I112" s="7"/>
-      <c r="J112" s="7"/>
+        <v>16000.0</v>
+      </c>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="6"/>
+      <c r="H112" s="6"/>
+      <c r="I112" s="6"/>
+      <c r="J112" s="6"/>
     </row>
     <row r="113">
       <c r="A113" s="4">
@@ -4103,20 +4119,20 @@
         <v>112</v>
       </c>
       <c r="B113" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C113" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C113" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="D113" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
-      <c r="G113" s="7"/>
-      <c r="H113" s="7"/>
-      <c r="I113" s="7"/>
-      <c r="J113" s="7"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6"/>
+      <c r="G113" s="6"/>
+      <c r="H113" s="6"/>
+      <c r="I113" s="6"/>
+      <c r="J113" s="6"/>
     </row>
     <row r="114">
       <c r="A114" s="4">
@@ -4127,7 +4143,7 @@
         <v>125</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D114" s="4">
         <v>1000.0</v>
@@ -4148,7 +4164,7 @@
         <v>126</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D115" s="4">
         <v>10000.0</v>
@@ -4169,10 +4185,10 @@
         <v>127</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D116" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E116" s="7"/>
       <c r="F116" s="7"/>
@@ -4190,17 +4206,17 @@
         <v>128</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D117" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
-      <c r="G117" s="6"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="6"/>
-      <c r="J117" s="6"/>
+        <v>10000.0</v>
+      </c>
+      <c r="E117" s="7"/>
+      <c r="F117" s="7"/>
+      <c r="G117" s="7"/>
+      <c r="H117" s="7"/>
+      <c r="I117" s="7"/>
+      <c r="J117" s="7"/>
     </row>
     <row r="118">
       <c r="A118" s="4">
@@ -4211,17 +4227,17 @@
         <v>129</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D118" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E118" s="6"/>
-      <c r="F118" s="6"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-      <c r="J118" s="6"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E118" s="7"/>
+      <c r="F118" s="7"/>
+      <c r="G118" s="7"/>
+      <c r="H118" s="7"/>
+      <c r="I118" s="7"/>
+      <c r="J118" s="7"/>
     </row>
     <row r="119">
       <c r="A119" s="4">
@@ -4232,17 +4248,17 @@
         <v>130</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D119" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-      <c r="J119" s="6"/>
+        <v>10000.0</v>
+      </c>
+      <c r="E119" s="7"/>
+      <c r="F119" s="7"/>
+      <c r="G119" s="7"/>
+      <c r="H119" s="7"/>
+      <c r="I119" s="7"/>
+      <c r="J119" s="7"/>
     </row>
     <row r="120">
       <c r="A120" s="4">
@@ -4253,17 +4269,17 @@
         <v>131</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D120" s="4">
-        <v>22000.0</v>
-      </c>
-      <c r="E120" s="6"/>
-      <c r="F120" s="6"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="6"/>
+        <v>500.0</v>
+      </c>
+      <c r="E120" s="7"/>
+      <c r="F120" s="7"/>
+      <c r="G120" s="7"/>
+      <c r="H120" s="7"/>
+      <c r="I120" s="7"/>
+      <c r="J120" s="7"/>
     </row>
     <row r="121">
       <c r="A121" s="4">
@@ -4274,10 +4290,10 @@
         <v>132</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D121" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
@@ -4295,10 +4311,10 @@
         <v>133</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D122" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
@@ -4316,10 +4332,10 @@
         <v>134</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D123" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
@@ -4337,10 +4353,10 @@
         <v>135</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D124" s="4">
-        <v>10000.0</v>
+        <v>22000.0</v>
       </c>
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
@@ -4358,10 +4374,10 @@
         <v>136</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D125" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
@@ -4379,10 +4395,10 @@
         <v>137</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D126" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
@@ -4400,7 +4416,7 @@
         <v>138</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D127" s="4">
         <v>5000.0</v>
@@ -4421,17 +4437,13 @@
         <v>139</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D128" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E128" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F128" s="4">
-        <v>1000.0</v>
-      </c>
+        <v>10000.0</v>
+      </c>
+      <c r="E128" s="6"/>
+      <c r="F128" s="6"/>
       <c r="G128" s="6"/>
       <c r="H128" s="6"/>
       <c r="I128" s="6"/>
@@ -4446,10 +4458,10 @@
         <v>140</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D129" s="4">
-        <v>6500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
@@ -4467,10 +4479,10 @@
         <v>141</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D130" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
@@ -4488,10 +4500,10 @@
         <v>142</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D131" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
@@ -4509,16 +4521,16 @@
         <v>143</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D132" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E132" s="4">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F132" s="4">
-        <v>13000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="G132" s="6"/>
       <c r="H132" s="6"/>
@@ -4534,10 +4546,10 @@
         <v>144</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D133" s="4">
-        <v>23000.0</v>
+        <v>6500.0</v>
       </c>
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
@@ -4555,17 +4567,17 @@
         <v>145</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D134" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E134" s="7"/>
-      <c r="F134" s="7"/>
-      <c r="G134" s="7"/>
-      <c r="H134" s="7"/>
-      <c r="I134" s="7"/>
-      <c r="J134" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
+      <c r="G134" s="6"/>
+      <c r="H134" s="6"/>
+      <c r="I134" s="6"/>
+      <c r="J134" s="6"/>
     </row>
     <row r="135">
       <c r="A135" s="4">
@@ -4576,10 +4588,10 @@
         <v>146</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D135" s="4">
-        <v>26000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
@@ -4597,13 +4609,17 @@
         <v>147</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D136" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E136" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F136" s="4">
+        <v>13000.0</v>
+      </c>
       <c r="G136" s="6"/>
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
@@ -4618,10 +4634,10 @@
         <v>148</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D137" s="4">
-        <v>21000.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
@@ -4639,17 +4655,17 @@
         <v>149</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D138" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E138" s="6"/>
-      <c r="F138" s="6"/>
-      <c r="G138" s="6"/>
-      <c r="H138" s="6"/>
-      <c r="I138" s="6"/>
-      <c r="J138" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E138" s="7"/>
+      <c r="F138" s="7"/>
+      <c r="G138" s="7"/>
+      <c r="H138" s="7"/>
+      <c r="I138" s="7"/>
+      <c r="J138" s="7"/>
     </row>
     <row r="139">
       <c r="A139" s="4">
@@ -4660,10 +4676,10 @@
         <v>150</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D139" s="4">
-        <v>36500.0</v>
+        <v>26000.0</v>
       </c>
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
@@ -4681,10 +4697,10 @@
         <v>151</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D140" s="4">
-        <v>13000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E140" s="6"/>
       <c r="F140" s="6"/>
@@ -4702,10 +4718,10 @@
         <v>152</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D141" s="4">
-        <v>500.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
@@ -4723,10 +4739,10 @@
         <v>153</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D142" s="4">
-        <v>13500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E142" s="6"/>
       <c r="F142" s="6"/>
@@ -4744,10 +4760,10 @@
         <v>154</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D143" s="4">
-        <v>5000.0</v>
+        <v>36500.0</v>
       </c>
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
@@ -4765,10 +4781,10 @@
         <v>155</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D144" s="4">
-        <v>160000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
@@ -4786,17 +4802,13 @@
         <v>156</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D145" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E145" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F145" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>500.0</v>
+      </c>
+      <c r="E145" s="6"/>
+      <c r="F145" s="6"/>
       <c r="G145" s="6"/>
       <c r="H145" s="6"/>
       <c r="I145" s="6"/>
@@ -4811,17 +4823,17 @@
         <v>157</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D146" s="4">
-        <v>65000.0</v>
-      </c>
-      <c r="E146" s="7"/>
-      <c r="F146" s="7"/>
-      <c r="G146" s="7"/>
-      <c r="H146" s="7"/>
-      <c r="I146" s="7"/>
-      <c r="J146" s="7"/>
+        <v>13500.0</v>
+      </c>
+      <c r="E146" s="6"/>
+      <c r="F146" s="6"/>
+      <c r="G146" s="6"/>
+      <c r="H146" s="6"/>
+      <c r="I146" s="6"/>
+      <c r="J146" s="6"/>
     </row>
     <row r="147">
       <c r="A147" s="4">
@@ -4832,17 +4844,17 @@
         <v>158</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D147" s="4">
-        <v>4500.0</v>
-      </c>
-      <c r="E147" s="7"/>
-      <c r="F147" s="7"/>
-      <c r="G147" s="7"/>
-      <c r="H147" s="7"/>
-      <c r="I147" s="7"/>
-      <c r="J147" s="7"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E147" s="6"/>
+      <c r="F147" s="6"/>
+      <c r="G147" s="6"/>
+      <c r="H147" s="6"/>
+      <c r="I147" s="6"/>
+      <c r="J147" s="6"/>
     </row>
     <row r="148">
       <c r="A148" s="4">
@@ -4853,10 +4865,10 @@
         <v>159</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D148" s="4">
-        <v>2000.0</v>
+        <v>160000.0</v>
       </c>
       <c r="E148" s="6"/>
       <c r="F148" s="6"/>
@@ -4874,13 +4886,17 @@
         <v>160</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D149" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E149" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F149" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G149" s="6"/>
       <c r="H149" s="6"/>
       <c r="I149" s="6"/>
@@ -4895,17 +4911,17 @@
         <v>161</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D150" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
-      <c r="G150" s="6"/>
-      <c r="H150" s="6"/>
-      <c r="I150" s="6"/>
-      <c r="J150" s="6"/>
+        <v>65000.0</v>
+      </c>
+      <c r="E150" s="7"/>
+      <c r="F150" s="7"/>
+      <c r="G150" s="7"/>
+      <c r="H150" s="7"/>
+      <c r="I150" s="7"/>
+      <c r="J150" s="7"/>
     </row>
     <row r="151">
       <c r="A151" s="4">
@@ -4916,17 +4932,17 @@
         <v>162</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D151" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E151" s="6"/>
-      <c r="F151" s="6"/>
-      <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
-      <c r="I151" s="6"/>
-      <c r="J151" s="6"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E151" s="7"/>
+      <c r="F151" s="7"/>
+      <c r="G151" s="7"/>
+      <c r="H151" s="7"/>
+      <c r="I151" s="7"/>
+      <c r="J151" s="7"/>
     </row>
     <row r="152">
       <c r="A152" s="4">
@@ -4937,7 +4953,7 @@
         <v>163</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D152" s="4">
         <v>2000.0</v>
@@ -4958,7 +4974,7 @@
         <v>164</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D153" s="4">
         <v>17000.0</v>
@@ -4979,7 +4995,7 @@
         <v>165</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D154" s="4">
         <v>2000.0</v>
@@ -5000,7 +5016,7 @@
         <v>166</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D155" s="4">
         <v>17000.0</v>
@@ -5021,7 +5037,7 @@
         <v>167</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D156" s="4">
         <v>2000.0</v>
@@ -5042,7 +5058,7 @@
         <v>168</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D157" s="4">
         <v>17000.0</v>
@@ -5063,10 +5079,10 @@
         <v>169</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D158" s="4">
-        <v>5000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E158" s="6"/>
       <c r="F158" s="6"/>
@@ -5084,10 +5100,10 @@
         <v>170</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D159" s="4">
-        <v>10000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E159" s="6"/>
       <c r="F159" s="6"/>
@@ -5105,10 +5121,10 @@
         <v>171</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D160" s="4">
-        <v>18000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E160" s="6"/>
       <c r="F160" s="6"/>
@@ -5126,10 +5142,10 @@
         <v>172</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D161" s="4">
-        <v>4500.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E161" s="6"/>
       <c r="F161" s="6"/>
@@ -5147,10 +5163,10 @@
         <v>173</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D162" s="4">
-        <v>9000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E162" s="6"/>
       <c r="F162" s="6"/>
@@ -5168,17 +5184,17 @@
         <v>174</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D163" s="4">
-        <v>18000.0</v>
-      </c>
-      <c r="E163" s="4"/>
-      <c r="F163" s="4"/>
-      <c r="G163" s="7"/>
-      <c r="H163" s="7"/>
-      <c r="I163" s="7"/>
-      <c r="J163" s="7"/>
+        <v>10000.0</v>
+      </c>
+      <c r="E163" s="6"/>
+      <c r="F163" s="6"/>
+      <c r="G163" s="6"/>
+      <c r="H163" s="6"/>
+      <c r="I163" s="6"/>
+      <c r="J163" s="6"/>
     </row>
     <row r="164">
       <c r="A164" s="4">
@@ -5189,21 +5205,17 @@
         <v>175</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D164" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E164" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F164" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="G164" s="7"/>
-      <c r="H164" s="7"/>
-      <c r="I164" s="7"/>
-      <c r="J164" s="7"/>
+        <v>18000.0</v>
+      </c>
+      <c r="E164" s="6"/>
+      <c r="F164" s="6"/>
+      <c r="G164" s="6"/>
+      <c r="H164" s="6"/>
+      <c r="I164" s="6"/>
+      <c r="J164" s="6"/>
     </row>
     <row r="165">
       <c r="A165" s="4">
@@ -5214,21 +5226,17 @@
         <v>176</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D165" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E165" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F165" s="4">
-        <v>12000.0</v>
-      </c>
-      <c r="G165" s="7"/>
-      <c r="H165" s="7"/>
-      <c r="I165" s="7"/>
-      <c r="J165" s="7"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E165" s="6"/>
+      <c r="F165" s="6"/>
+      <c r="G165" s="6"/>
+      <c r="H165" s="6"/>
+      <c r="I165" s="6"/>
+      <c r="J165" s="6"/>
     </row>
     <row r="166">
       <c r="A166" s="4">
@@ -5239,21 +5247,17 @@
         <v>177</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D166" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E166" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F166" s="4">
-        <v>8500.0</v>
-      </c>
-      <c r="G166" s="7"/>
-      <c r="H166" s="7"/>
-      <c r="I166" s="7"/>
-      <c r="J166" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E166" s="6"/>
+      <c r="F166" s="6"/>
+      <c r="G166" s="6"/>
+      <c r="H166" s="6"/>
+      <c r="I166" s="6"/>
+      <c r="J166" s="6"/>
     </row>
     <row r="167">
       <c r="A167" s="4">
@@ -5264,13 +5268,13 @@
         <v>178</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D167" s="4">
-        <v>26000.0</v>
-      </c>
-      <c r="E167" s="7"/>
-      <c r="F167" s="7"/>
+        <v>18000.0</v>
+      </c>
+      <c r="E167" s="4"/>
+      <c r="F167" s="4"/>
       <c r="G167" s="7"/>
       <c r="H167" s="7"/>
       <c r="I167" s="7"/>
@@ -5285,16 +5289,16 @@
         <v>179</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D168" s="4">
-        <v>4000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E168" s="4">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F168" s="4">
-        <v>17500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="G168" s="7"/>
       <c r="H168" s="7"/>
@@ -5310,13 +5314,17 @@
         <v>180</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D169" s="4">
-        <v>175000.0</v>
-      </c>
-      <c r="E169" s="7"/>
-      <c r="F169" s="7"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E169" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F169" s="4">
+        <v>12000.0</v>
+      </c>
       <c r="G169" s="7"/>
       <c r="H169" s="7"/>
       <c r="I169" s="7"/>
@@ -5331,13 +5339,17 @@
         <v>181</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D170" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E170" s="7"/>
-      <c r="F170" s="7"/>
+        <v>2500.0</v>
+      </c>
+      <c r="E170" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F170" s="4">
+        <v>8500.0</v>
+      </c>
       <c r="G170" s="7"/>
       <c r="H170" s="7"/>
       <c r="I170" s="7"/>
@@ -5352,17 +5364,13 @@
         <v>182</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D171" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="E171" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F171" s="4">
-        <v>22000.0</v>
-      </c>
+        <v>26000.0</v>
+      </c>
+      <c r="E171" s="7"/>
+      <c r="F171" s="7"/>
       <c r="G171" s="7"/>
       <c r="H171" s="7"/>
       <c r="I171" s="7"/>
@@ -5377,13 +5385,17 @@
         <v>183</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D172" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E172" s="7"/>
-      <c r="F172" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E172" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F172" s="4">
+        <v>17500.0</v>
+      </c>
       <c r="G172" s="7"/>
       <c r="H172" s="7"/>
       <c r="I172" s="7"/>
@@ -5398,10 +5410,10 @@
         <v>184</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D173" s="4">
-        <v>21000.0</v>
+        <v>175000.0</v>
       </c>
       <c r="E173" s="7"/>
       <c r="F173" s="7"/>
@@ -5419,10 +5431,10 @@
         <v>185</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D174" s="4">
-        <v>245000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E174" s="7"/>
       <c r="F174" s="7"/>
@@ -5440,13 +5452,17 @@
         <v>186</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D175" s="4">
-        <v>42000.0</v>
-      </c>
-      <c r="E175" s="7"/>
-      <c r="F175" s="7"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E175" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F175" s="4">
+        <v>22000.0</v>
+      </c>
       <c r="G175" s="7"/>
       <c r="H175" s="7"/>
       <c r="I175" s="7"/>
@@ -5461,10 +5477,10 @@
         <v>187</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D176" s="4">
-        <v>44000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E176" s="7"/>
       <c r="F176" s="7"/>
@@ -5482,10 +5498,10 @@
         <v>188</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D177" s="4">
-        <v>255000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E177" s="7"/>
       <c r="F177" s="7"/>
@@ -5503,10 +5519,10 @@
         <v>189</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D178" s="4">
-        <v>21000.0</v>
+        <v>245000.0</v>
       </c>
       <c r="E178" s="7"/>
       <c r="F178" s="7"/>
@@ -5524,7 +5540,7 @@
         <v>190</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D179" s="4">
         <v>42000.0</v>
@@ -5545,17 +5561,17 @@
         <v>191</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D180" s="4">
-        <v>14500.0</v>
+        <v>44000.0</v>
       </c>
       <c r="E180" s="7"/>
       <c r="F180" s="7"/>
-      <c r="G180" s="4"/>
-      <c r="H180" s="4"/>
-      <c r="I180" s="4"/>
-      <c r="J180" s="4"/>
+      <c r="G180" s="7"/>
+      <c r="H180" s="7"/>
+      <c r="I180" s="7"/>
+      <c r="J180" s="7"/>
     </row>
     <row r="181">
       <c r="A181" s="4">
@@ -5566,25 +5582,17 @@
         <v>192</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>193</v>
+        <v>124</v>
       </c>
       <c r="D181" s="4">
-        <v>2000.0</v>
+        <v>255000.0</v>
       </c>
       <c r="E181" s="7"/>
       <c r="F181" s="7"/>
-      <c r="G181" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H181" s="4">
-        <v>5500.0</v>
-      </c>
-      <c r="I181" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J181" s="4">
-        <v>10000.0</v>
-      </c>
+      <c r="G181" s="7"/>
+      <c r="H181" s="7"/>
+      <c r="I181" s="7"/>
+      <c r="J181" s="7"/>
     </row>
     <row r="182">
       <c r="A182" s="4">
@@ -5592,13 +5600,13 @@
         <v>181</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>193</v>
+        <v>124</v>
       </c>
       <c r="D182" s="4">
-        <v>10000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E182" s="7"/>
       <c r="F182" s="7"/>
@@ -5613,28 +5621,20 @@
         <v>182</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>193</v>
+        <v>124</v>
       </c>
       <c r="D183" s="4">
-        <v>2000.0</v>
+        <v>42000.0</v>
       </c>
       <c r="E183" s="7"/>
       <c r="F183" s="7"/>
-      <c r="G183" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H183" s="4">
-        <v>5500.0</v>
-      </c>
-      <c r="I183" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J183" s="4">
-        <v>10000.0</v>
-      </c>
+      <c r="G183" s="7"/>
+      <c r="H183" s="7"/>
+      <c r="I183" s="7"/>
+      <c r="J183" s="7"/>
     </row>
     <row r="184">
       <c r="A184" s="4">
@@ -5642,20 +5642,20 @@
         <v>183</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>193</v>
+        <v>124</v>
       </c>
       <c r="D184" s="4">
-        <v>10000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
-      <c r="G184" s="7"/>
-      <c r="H184" s="7"/>
-      <c r="I184" s="7"/>
-      <c r="J184" s="7"/>
+      <c r="G184" s="4"/>
+      <c r="H184" s="4"/>
+      <c r="I184" s="4"/>
+      <c r="J184" s="4"/>
     </row>
     <row r="185">
       <c r="A185" s="4">
@@ -5663,10 +5663,10 @@
         <v>184</v>
       </c>
       <c r="B185" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C185" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>193</v>
       </c>
       <c r="D185" s="4">
         <v>2000.0</v>
@@ -5695,7 +5695,7 @@
         <v>198</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D186" s="4">
         <v>10000.0</v>
@@ -5716,7 +5716,7 @@
         <v>199</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D187" s="4">
         <v>2000.0</v>
@@ -5727,13 +5727,13 @@
         <v>6.0</v>
       </c>
       <c r="H187" s="4">
-        <v>6000.0</v>
+        <v>5500.0</v>
       </c>
       <c r="I187" s="4">
         <v>12.0</v>
       </c>
       <c r="J187" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
     </row>
     <row r="188">
@@ -5745,10 +5745,10 @@
         <v>200</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D188" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E188" s="7"/>
       <c r="F188" s="7"/>
@@ -5766,7 +5766,7 @@
         <v>201</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D189" s="4">
         <v>2000.0</v>
@@ -5777,13 +5777,13 @@
         <v>6.0</v>
       </c>
       <c r="H189" s="4">
-        <v>6000.0</v>
+        <v>5500.0</v>
       </c>
       <c r="I189" s="4">
         <v>12.0</v>
       </c>
       <c r="J189" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
     </row>
     <row r="190">
@@ -5795,10 +5795,10 @@
         <v>202</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D190" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E190" s="7"/>
       <c r="F190" s="7"/>
@@ -5816,7 +5816,7 @@
         <v>203</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D191" s="4">
         <v>2000.0</v>
@@ -5827,13 +5827,13 @@
         <v>6.0</v>
       </c>
       <c r="H191" s="4">
-        <v>8000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="I191" s="4">
         <v>12.0</v>
       </c>
       <c r="J191" s="4">
-        <v>15000.0</v>
+        <v>11000.0</v>
       </c>
     </row>
     <row r="192">
@@ -5845,10 +5845,10 @@
         <v>204</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D192" s="4">
-        <v>15000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="E192" s="7"/>
       <c r="F192" s="7"/>
@@ -5866,17 +5866,25 @@
         <v>205</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D193" s="4">
-        <v>15000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E193" s="7"/>
       <c r="F193" s="7"/>
-      <c r="G193" s="7"/>
-      <c r="H193" s="7"/>
-      <c r="I193" s="7"/>
-      <c r="J193" s="7"/>
+      <c r="G193" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H193" s="4">
+        <v>6000.0</v>
+      </c>
+      <c r="I193" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J193" s="4">
+        <v>11000.0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4">
@@ -5887,29 +5895,17 @@
         <v>206</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D194" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E194" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F194" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="G194" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H194" s="4">
-        <v>8500.0</v>
-      </c>
-      <c r="I194" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J194" s="4">
-        <v>16000.0</v>
-      </c>
+        <v>11000.0</v>
+      </c>
+      <c r="E194" s="7"/>
+      <c r="F194" s="7"/>
+      <c r="G194" s="7"/>
+      <c r="H194" s="7"/>
+      <c r="I194" s="7"/>
+      <c r="J194" s="7"/>
     </row>
     <row r="195">
       <c r="A195" s="4">
@@ -5920,17 +5916,25 @@
         <v>207</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D195" s="4">
-        <v>16000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E195" s="7"/>
       <c r="F195" s="7"/>
-      <c r="G195" s="7"/>
-      <c r="H195" s="7"/>
-      <c r="I195" s="7"/>
-      <c r="J195" s="7"/>
+      <c r="G195" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H195" s="4">
+        <v>8000.0</v>
+      </c>
+      <c r="I195" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J195" s="4">
+        <v>15000.0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="4">
@@ -5941,25 +5945,17 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D196" s="4">
-        <v>2000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E196" s="7"/>
       <c r="F196" s="7"/>
-      <c r="G196" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H196" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="I196" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J196" s="4">
-        <v>17000.0</v>
-      </c>
+      <c r="G196" s="7"/>
+      <c r="H196" s="7"/>
+      <c r="I196" s="7"/>
+      <c r="J196" s="7"/>
     </row>
     <row r="197">
       <c r="A197" s="4">
@@ -5970,10 +5966,10 @@
         <v>209</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D197" s="4">
-        <v>17000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E197" s="7"/>
       <c r="F197" s="7"/>
@@ -5991,24 +5987,28 @@
         <v>210</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D198" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E198" s="7"/>
-      <c r="F198" s="7"/>
+      <c r="E198" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F198" s="4">
+        <v>5000.0</v>
+      </c>
       <c r="G198" s="4">
         <v>6.0</v>
       </c>
       <c r="H198" s="4">
-        <v>9000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="I198" s="4">
         <v>12.0</v>
       </c>
       <c r="J198" s="4">
-        <v>17000.0</v>
+        <v>16000.0</v>
       </c>
     </row>
     <row r="199">
@@ -6020,10 +6020,10 @@
         <v>211</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D199" s="4">
-        <v>17000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E199" s="7"/>
       <c r="F199" s="7"/>
@@ -6041,28 +6041,24 @@
         <v>212</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D200" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E200" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F200" s="4">
-        <v>5000.0</v>
-      </c>
+      <c r="E200" s="7"/>
+      <c r="F200" s="7"/>
       <c r="G200" s="4">
         <v>6.0</v>
       </c>
       <c r="H200" s="4">
-        <v>9500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="I200" s="4">
         <v>12.0</v>
       </c>
       <c r="J200" s="4">
-        <v>18000.0</v>
+        <v>17000.0</v>
       </c>
     </row>
     <row r="201">
@@ -6074,10 +6070,10 @@
         <v>213</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D201" s="4">
-        <v>18000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E201" s="7"/>
       <c r="F201" s="7"/>
@@ -6095,10 +6091,10 @@
         <v>214</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D202" s="4">
-        <v>2500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E202" s="7"/>
       <c r="F202" s="7"/>
@@ -6106,13 +6102,13 @@
         <v>6.0</v>
       </c>
       <c r="H202" s="4">
-        <v>14500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="I202" s="4">
         <v>12.0</v>
       </c>
       <c r="J202" s="4">
-        <v>28000.0</v>
+        <v>17000.0</v>
       </c>
     </row>
     <row r="203">
@@ -6124,10 +6120,10 @@
         <v>215</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D203" s="4">
-        <v>28000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E203" s="7"/>
       <c r="F203" s="7"/>
@@ -6145,24 +6141,28 @@
         <v>216</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D204" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E204" s="7"/>
-      <c r="F204" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E204" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F204" s="4">
+        <v>5000.0</v>
+      </c>
       <c r="G204" s="4">
         <v>6.0</v>
       </c>
       <c r="H204" s="4">
-        <v>10500.0</v>
+        <v>9500.0</v>
       </c>
       <c r="I204" s="4">
         <v>12.0</v>
       </c>
       <c r="J204" s="4">
-        <v>20000.0</v>
+        <v>18000.0</v>
       </c>
     </row>
     <row r="205">
@@ -6174,10 +6174,10 @@
         <v>217</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D205" s="4">
-        <v>20000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E205" s="7"/>
       <c r="F205" s="7"/>
@@ -6195,7 +6195,7 @@
         <v>218</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D206" s="4">
         <v>2500.0</v>
@@ -6206,13 +6206,13 @@
         <v>6.0</v>
       </c>
       <c r="H206" s="4">
-        <v>13000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="I206" s="4">
         <v>12.0</v>
       </c>
       <c r="J206" s="4">
-        <v>25000.0</v>
+        <v>28000.0</v>
       </c>
     </row>
     <row r="207">
@@ -6224,10 +6224,10 @@
         <v>219</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D207" s="4">
-        <v>25000.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E207" s="7"/>
       <c r="F207" s="7"/>
@@ -6245,7 +6245,7 @@
         <v>220</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D208" s="4">
         <v>2500.0</v>
@@ -6256,13 +6256,13 @@
         <v>6.0</v>
       </c>
       <c r="H208" s="4">
-        <v>11000.0</v>
+        <v>10500.0</v>
       </c>
       <c r="I208" s="4">
         <v>12.0</v>
       </c>
       <c r="J208" s="4">
-        <v>21000.0</v>
+        <v>20000.0</v>
       </c>
     </row>
     <row r="209">
@@ -6274,10 +6274,10 @@
         <v>221</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D209" s="4">
-        <v>21000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="E209" s="7"/>
       <c r="F209" s="7"/>
@@ -6295,7 +6295,7 @@
         <v>222</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D210" s="4">
         <v>2500.0</v>
@@ -6324,7 +6324,7 @@
         <v>223</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D211" s="4">
         <v>25000.0</v>
@@ -6345,7 +6345,7 @@
         <v>224</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D212" s="4">
         <v>2500.0</v>
@@ -6356,13 +6356,13 @@
         <v>6.0</v>
       </c>
       <c r="H212" s="4">
-        <v>14000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="I212" s="4">
         <v>12.0</v>
       </c>
       <c r="J212" s="4">
-        <v>28000.0</v>
+        <v>21000.0</v>
       </c>
     </row>
     <row r="213">
@@ -6374,10 +6374,10 @@
         <v>225</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D213" s="4">
-        <v>28000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E213" s="7"/>
       <c r="F213" s="7"/>
@@ -6395,7 +6395,7 @@
         <v>226</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D214" s="4">
         <v>2500.0</v>
@@ -6424,7 +6424,7 @@
         <v>227</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D215" s="4">
         <v>25000.0</v>
@@ -6445,7 +6445,7 @@
         <v>228</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D216" s="4">
         <v>2500.0</v>
@@ -6462,7 +6462,7 @@
         <v>12.0</v>
       </c>
       <c r="J216" s="4">
-        <v>27000.0</v>
+        <v>28000.0</v>
       </c>
     </row>
     <row r="217">
@@ -6474,10 +6474,10 @@
         <v>229</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D217" s="4">
-        <v>27000.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E217" s="7"/>
       <c r="F217" s="7"/>
@@ -6495,7 +6495,7 @@
         <v>230</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D218" s="4">
         <v>2500.0</v>
@@ -6506,13 +6506,13 @@
         <v>6.0</v>
       </c>
       <c r="H218" s="4">
-        <v>14000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I218" s="4">
         <v>12.0</v>
       </c>
       <c r="J218" s="4">
-        <v>27000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="219">
@@ -6524,10 +6524,10 @@
         <v>231</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D219" s="4">
-        <v>27000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E219" s="7"/>
       <c r="F219" s="7"/>
@@ -6545,17 +6545,25 @@
         <v>232</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D220" s="4">
-        <v>34000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E220" s="7"/>
       <c r="F220" s="7"/>
-      <c r="G220" s="7"/>
-      <c r="H220" s="7"/>
-      <c r="I220" s="7"/>
-      <c r="J220" s="7"/>
+      <c r="G220" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H220" s="4">
+        <v>14000.0</v>
+      </c>
+      <c r="I220" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J220" s="4">
+        <v>27000.0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="4">
@@ -6566,7 +6574,7 @@
         <v>233</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D221" s="4">
         <v>27000.0</v>
@@ -6587,18 +6595,24 @@
         <v>234</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D222" s="4">
-        <v>37000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E222" s="7"/>
       <c r="F222" s="7"/>
-      <c r="G222" s="4"/>
-      <c r="H222" s="4"/>
-      <c r="I222" s="4"/>
+      <c r="G222" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H222" s="4">
+        <v>14000.0</v>
+      </c>
+      <c r="I222" s="4">
+        <v>12.0</v>
+      </c>
       <c r="J222" s="4">
-        <v>37000.0</v>
+        <v>27000.0</v>
       </c>
     </row>
     <row r="223">
@@ -6610,10 +6624,10 @@
         <v>235</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D223" s="4">
-        <v>16000.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E223" s="7"/>
       <c r="F223" s="7"/>
@@ -6631,10 +6645,10 @@
         <v>236</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D224" s="4">
-        <v>43000.0</v>
+        <v>34000.0</v>
       </c>
       <c r="E224" s="7"/>
       <c r="F224" s="7"/>
@@ -6652,10 +6666,10 @@
         <v>237</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D225" s="4">
-        <v>23000.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E225" s="7"/>
       <c r="F225" s="7"/>
@@ -6673,17 +6687,19 @@
         <v>238</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D226" s="4">
-        <v>17000.0</v>
+        <v>37000.0</v>
       </c>
       <c r="E226" s="7"/>
       <c r="F226" s="7"/>
-      <c r="G226" s="7"/>
-      <c r="H226" s="7"/>
-      <c r="I226" s="7"/>
-      <c r="J226" s="7"/>
+      <c r="G226" s="4"/>
+      <c r="H226" s="4"/>
+      <c r="I226" s="4"/>
+      <c r="J226" s="4">
+        <v>37000.0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="4">
@@ -6694,10 +6710,10 @@
         <v>239</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D227" s="4">
-        <v>29000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E227" s="7"/>
       <c r="F227" s="7"/>
@@ -6715,10 +6731,10 @@
         <v>240</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D228" s="4">
-        <v>13000.0</v>
+        <v>43000.0</v>
       </c>
       <c r="E228" s="7"/>
       <c r="F228" s="7"/>
@@ -6736,10 +6752,10 @@
         <v>241</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>242</v>
+        <v>197</v>
       </c>
       <c r="D229" s="4">
-        <v>500.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E229" s="7"/>
       <c r="F229" s="7"/>
@@ -6754,13 +6770,13 @@
         <v>229</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>242</v>
+        <v>197</v>
       </c>
       <c r="D230" s="4">
-        <v>4000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E230" s="7"/>
       <c r="F230" s="7"/>
@@ -6775,13 +6791,13 @@
         <v>230</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>242</v>
+        <v>197</v>
       </c>
       <c r="D231" s="4">
-        <v>2500.0</v>
+        <v>29000.0</v>
       </c>
       <c r="E231" s="7"/>
       <c r="F231" s="7"/>
@@ -6796,20 +6812,16 @@
         <v>231</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>246</v>
+        <v>197</v>
       </c>
       <c r="D232" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E232" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F232" s="4">
-        <v>14000.0</v>
-      </c>
+        <v>13000.0</v>
+      </c>
+      <c r="E232" s="7"/>
+      <c r="F232" s="7"/>
       <c r="G232" s="7"/>
       <c r="H232" s="7"/>
       <c r="I232" s="7"/>
@@ -6821,13 +6833,13 @@
         <v>232</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C233" s="5" t="s">
         <v>246</v>
       </c>
       <c r="D233" s="4">
-        <v>109000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="7"/>
@@ -6842,20 +6854,16 @@
         <v>233</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C234" s="5" t="s">
         <v>246</v>
       </c>
       <c r="D234" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E234" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F234" s="4">
-        <v>14000.0</v>
-      </c>
+        <v>4000.0</v>
+      </c>
+      <c r="E234" s="7"/>
+      <c r="F234" s="7"/>
       <c r="G234" s="7"/>
       <c r="H234" s="7"/>
       <c r="I234" s="7"/>
@@ -6867,13 +6875,13 @@
         <v>234</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C235" s="5" t="s">
         <v>246</v>
       </c>
       <c r="D235" s="4">
-        <v>109000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E235" s="7"/>
       <c r="F235" s="7"/>
@@ -6888,16 +6896,20 @@
         <v>235</v>
       </c>
       <c r="B236" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C236" s="5" t="s">
         <v>250</v>
-      </c>
-      <c r="C236" s="5" t="s">
-        <v>246</v>
       </c>
       <c r="D236" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E236" s="7"/>
-      <c r="F236" s="7"/>
+      <c r="E236" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F236" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G236" s="7"/>
       <c r="H236" s="7"/>
       <c r="I236" s="7"/>
@@ -6912,10 +6924,10 @@
         <v>251</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D237" s="4">
-        <v>114000.0</v>
+        <v>109000.0</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="7"/>
@@ -6933,13 +6945,17 @@
         <v>252</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D238" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E238" s="7"/>
-      <c r="F238" s="7"/>
+      <c r="E238" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F238" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G238" s="7"/>
       <c r="H238" s="7"/>
       <c r="I238" s="7"/>
@@ -6954,17 +6970,13 @@
         <v>253</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D239" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E239" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F239" s="4">
-        <v>39000.0</v>
-      </c>
+        <v>109000.0</v>
+      </c>
+      <c r="E239" s="7"/>
+      <c r="F239" s="7"/>
       <c r="G239" s="7"/>
       <c r="H239" s="7"/>
       <c r="I239" s="7"/>
@@ -6979,10 +6991,10 @@
         <v>254</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D240" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E240" s="7"/>
       <c r="F240" s="7"/>
@@ -7000,10 +7012,10 @@
         <v>255</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D241" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E241" s="7"/>
       <c r="F241" s="7"/>
@@ -7021,10 +7033,10 @@
         <v>256</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D242" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E242" s="7"/>
       <c r="F242" s="7"/>
@@ -7042,13 +7054,17 @@
         <v>257</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D243" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E243" s="7"/>
-      <c r="F243" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E243" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F243" s="4">
+        <v>39000.0</v>
+      </c>
       <c r="G243" s="7"/>
       <c r="H243" s="7"/>
       <c r="I243" s="7"/>
@@ -7063,7 +7079,7 @@
         <v>258</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D244" s="4">
         <v>114000.0</v>
@@ -7084,7 +7100,7 @@
         <v>259</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D245" s="4">
         <v>3000.0</v>
@@ -7105,7 +7121,7 @@
         <v>260</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D246" s="4">
         <v>114000.0</v>
@@ -7126,7 +7142,7 @@
         <v>261</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D247" s="4">
         <v>3000.0</v>
@@ -7147,10 +7163,10 @@
         <v>262</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D248" s="4">
-        <v>107000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E248" s="7"/>
       <c r="F248" s="7"/>
@@ -7168,7 +7184,7 @@
         <v>263</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D249" s="4">
         <v>3000.0</v>
@@ -7189,17 +7205,17 @@
         <v>264</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D250" s="4">
-        <v>112000.0</v>
-      </c>
-      <c r="E250" s="6"/>
-      <c r="F250" s="6"/>
-      <c r="G250" s="6"/>
-      <c r="H250" s="6"/>
-      <c r="I250" s="6"/>
-      <c r="J250" s="6"/>
+        <v>114000.0</v>
+      </c>
+      <c r="E250" s="7"/>
+      <c r="F250" s="7"/>
+      <c r="G250" s="7"/>
+      <c r="H250" s="7"/>
+      <c r="I250" s="7"/>
+      <c r="J250" s="7"/>
     </row>
     <row r="251">
       <c r="A251" s="4">
@@ -7210,17 +7226,13 @@
         <v>265</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D251" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E251" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F251" s="4">
-        <v>19000.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E251" s="7"/>
+      <c r="F251" s="7"/>
       <c r="G251" s="7"/>
       <c r="H251" s="7"/>
       <c r="I251" s="7"/>
@@ -7235,17 +7247,13 @@
         <v>266</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D252" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E252" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F252" s="4">
-        <v>19000.0</v>
-      </c>
+        <v>107000.0</v>
+      </c>
+      <c r="E252" s="7"/>
+      <c r="F252" s="7"/>
       <c r="G252" s="7"/>
       <c r="H252" s="7"/>
       <c r="I252" s="7"/>
@@ -7260,13 +7268,13 @@
         <v>267</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D253" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E253" s="4"/>
-      <c r="F253" s="4"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E253" s="7"/>
+      <c r="F253" s="7"/>
       <c r="G253" s="7"/>
       <c r="H253" s="7"/>
       <c r="I253" s="7"/>
@@ -7281,17 +7289,17 @@
         <v>268</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D254" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E254" s="4"/>
-      <c r="F254" s="4"/>
-      <c r="G254" s="7"/>
-      <c r="H254" s="7"/>
-      <c r="I254" s="7"/>
-      <c r="J254" s="7"/>
+        <v>112000.0</v>
+      </c>
+      <c r="E254" s="6"/>
+      <c r="F254" s="6"/>
+      <c r="G254" s="6"/>
+      <c r="H254" s="6"/>
+      <c r="I254" s="6"/>
+      <c r="J254" s="6"/>
     </row>
     <row r="255">
       <c r="A255" s="4">
@@ -7302,13 +7310,17 @@
         <v>269</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D255" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E255" s="4"/>
-      <c r="F255" s="4"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E255" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F255" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G255" s="7"/>
       <c r="H255" s="7"/>
       <c r="I255" s="7"/>
@@ -7323,7 +7335,7 @@
         <v>270</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D256" s="4">
         <v>4000.0</v>
@@ -7332,9 +7344,9 @@
         <v>5.0</v>
       </c>
       <c r="F256" s="4">
-        <v>19500.0</v>
-      </c>
-      <c r="G256" s="4"/>
+        <v>19000.0</v>
+      </c>
+      <c r="G256" s="7"/>
       <c r="H256" s="7"/>
       <c r="I256" s="7"/>
       <c r="J256" s="7"/>
@@ -7348,17 +7360,13 @@
         <v>271</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D257" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E257" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F257" s="4">
-        <v>6000.0</v>
-      </c>
+        <v>86000.0</v>
+      </c>
+      <c r="E257" s="4"/>
+      <c r="F257" s="4"/>
       <c r="G257" s="7"/>
       <c r="H257" s="7"/>
       <c r="I257" s="7"/>
@@ -7373,13 +7381,13 @@
         <v>272</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D258" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E258" s="7"/>
-      <c r="F258" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E258" s="4"/>
+      <c r="F258" s="4"/>
       <c r="G258" s="7"/>
       <c r="H258" s="7"/>
       <c r="I258" s="7"/>
@@ -7394,13 +7402,13 @@
         <v>273</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D259" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E259" s="7"/>
-      <c r="F259" s="7"/>
+        <v>86000.0</v>
+      </c>
+      <c r="E259" s="4"/>
+      <c r="F259" s="4"/>
       <c r="G259" s="7"/>
       <c r="H259" s="7"/>
       <c r="I259" s="7"/>
@@ -7415,14 +7423,18 @@
         <v>274</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D260" s="4">
-        <v>89000.0</v>
-      </c>
-      <c r="E260" s="7"/>
-      <c r="F260" s="7"/>
-      <c r="G260" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E260" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F260" s="4">
+        <v>19500.0</v>
+      </c>
+      <c r="G260" s="4"/>
       <c r="H260" s="7"/>
       <c r="I260" s="7"/>
       <c r="J260" s="7"/>
@@ -7436,13 +7448,17 @@
         <v>275</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D261" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E261" s="7"/>
-      <c r="F261" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E261" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F261" s="4">
+        <v>6000.0</v>
+      </c>
       <c r="G261" s="7"/>
       <c r="H261" s="7"/>
       <c r="I261" s="7"/>
@@ -7457,10 +7473,10 @@
         <v>276</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D262" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E262" s="7"/>
       <c r="F262" s="7"/>
@@ -7478,10 +7494,10 @@
         <v>277</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D263" s="4">
-        <v>3000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E263" s="7"/>
       <c r="F263" s="7"/>
@@ -7499,17 +7515,17 @@
         <v>278</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="D264" s="4">
-        <v>80000.0</v>
-      </c>
-      <c r="E264" s="6"/>
-      <c r="F264" s="6"/>
-      <c r="G264" s="6"/>
-      <c r="H264" s="6"/>
-      <c r="I264" s="6"/>
-      <c r="J264" s="6"/>
+        <v>89000.0</v>
+      </c>
+      <c r="E264" s="7"/>
+      <c r="F264" s="7"/>
+      <c r="G264" s="7"/>
+      <c r="H264" s="7"/>
+      <c r="I264" s="7"/>
+      <c r="J264" s="7"/>
     </row>
     <row r="265">
       <c r="A265" s="4">
@@ -7520,10 +7536,10 @@
         <v>279</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="D265" s="4">
-        <v>14000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E265" s="7"/>
       <c r="F265" s="7"/>
@@ -7538,13 +7554,13 @@
         <v>265</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="D266" s="4">
-        <v>14500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E266" s="7"/>
       <c r="F266" s="7"/>
@@ -7559,13 +7575,13 @@
         <v>266</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="D267" s="4">
-        <v>15000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E267" s="7"/>
       <c r="F267" s="7"/>
@@ -7580,20 +7596,20 @@
         <v>267</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D268" s="4">
-        <v>15500.0</v>
-      </c>
-      <c r="E268" s="7"/>
-      <c r="F268" s="7"/>
-      <c r="G268" s="7"/>
-      <c r="H268" s="7"/>
-      <c r="I268" s="7"/>
-      <c r="J268" s="7"/>
+        <v>80000.0</v>
+      </c>
+      <c r="E268" s="6"/>
+      <c r="F268" s="6"/>
+      <c r="G268" s="6"/>
+      <c r="H268" s="6"/>
+      <c r="I268" s="6"/>
+      <c r="J268" s="6"/>
     </row>
     <row r="269">
       <c r="A269" s="4">
@@ -7601,13 +7617,13 @@
         <v>268</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D269" s="4">
-        <v>1500.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E269" s="7"/>
       <c r="F269" s="7"/>
@@ -7622,13 +7638,13 @@
         <v>269</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D270" s="4">
-        <v>12500.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E270" s="7"/>
       <c r="F270" s="7"/>
@@ -7646,10 +7662,10 @@
         <v>283</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D271" s="4">
-        <v>500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E271" s="7"/>
       <c r="F271" s="7"/>
@@ -7664,13 +7680,13 @@
         <v>271</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D272" s="4">
-        <v>4500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E272" s="7"/>
       <c r="F272" s="7"/>
@@ -7685,13 +7701,13 @@
         <v>272</v>
       </c>
       <c r="B273" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C273" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="C273" s="5" t="s">
-        <v>281</v>
-      </c>
       <c r="D273" s="4">
-        <v>3000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E273" s="7"/>
       <c r="F273" s="7"/>
@@ -7709,10 +7725,10 @@
         <v>286</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D274" s="4">
-        <v>23000.0</v>
+        <v>12500.0</v>
       </c>
       <c r="E274" s="7"/>
       <c r="F274" s="7"/>
@@ -7730,17 +7746,13 @@
         <v>287</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D275" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E275" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F275" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>500.0</v>
+      </c>
+      <c r="E275" s="7"/>
+      <c r="F275" s="7"/>
       <c r="G275" s="7"/>
       <c r="H275" s="7"/>
       <c r="I275" s="7"/>
@@ -7755,13 +7767,13 @@
         <v>288</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D276" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E276" s="4"/>
-      <c r="F276" s="4"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E276" s="7"/>
+      <c r="F276" s="7"/>
       <c r="G276" s="7"/>
       <c r="H276" s="7"/>
       <c r="I276" s="7"/>
@@ -7776,17 +7788,13 @@
         <v>289</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D277" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E277" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F277" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E277" s="7"/>
+      <c r="F277" s="7"/>
       <c r="G277" s="7"/>
       <c r="H277" s="7"/>
       <c r="I277" s="7"/>
@@ -7801,13 +7809,13 @@
         <v>290</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D278" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="E278" s="4"/>
-      <c r="F278" s="4"/>
+        <v>23000.0</v>
+      </c>
+      <c r="E278" s="7"/>
+      <c r="F278" s="7"/>
       <c r="G278" s="7"/>
       <c r="H278" s="7"/>
       <c r="I278" s="7"/>
@@ -7822,7 +7830,7 @@
         <v>291</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D279" s="4">
         <v>2000.0</v>
@@ -7847,13 +7855,13 @@
         <v>292</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D280" s="4">
         <v>7500.0</v>
       </c>
-      <c r="E280" s="7"/>
-      <c r="F280" s="7"/>
+      <c r="E280" s="4"/>
+      <c r="F280" s="4"/>
       <c r="G280" s="7"/>
       <c r="H280" s="7"/>
       <c r="I280" s="7"/>
@@ -7868,13 +7876,17 @@
         <v>293</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D281" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E281" s="7"/>
-      <c r="F281" s="7"/>
+        <v>2500.0</v>
+      </c>
+      <c r="E281" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F281" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G281" s="7"/>
       <c r="H281" s="7"/>
       <c r="I281" s="7"/>
@@ -7886,16 +7898,16 @@
         <v>281</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D282" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="E282" s="7"/>
-      <c r="F282" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E282" s="4"/>
+      <c r="F282" s="4"/>
       <c r="G282" s="7"/>
       <c r="H282" s="7"/>
       <c r="I282" s="7"/>
@@ -7907,16 +7919,20 @@
         <v>282</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D283" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E283" s="7"/>
-      <c r="F283" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E283" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F283" s="4">
+        <v>7500.0</v>
+      </c>
       <c r="G283" s="7"/>
       <c r="H283" s="7"/>
       <c r="I283" s="7"/>
@@ -7928,13 +7944,13 @@
         <v>283</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D284" s="4">
-        <v>5000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E284" s="7"/>
       <c r="F284" s="7"/>
@@ -7949,10 +7965,10 @@
         <v>284</v>
       </c>
       <c r="B285" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C285" s="5" t="s">
         <v>298</v>
-      </c>
-      <c r="C285" s="5" t="s">
-        <v>294</v>
       </c>
       <c r="D285" s="4">
         <v>1000.0</v>
@@ -7973,7 +7989,7 @@
         <v>299</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D286" s="4">
         <v>10000.0</v>
@@ -7994,7 +8010,7 @@
         <v>300</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D287" s="4">
         <v>500.0</v>
@@ -8015,7 +8031,7 @@
         <v>301</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D288" s="4">
         <v>5000.0</v>
@@ -8036,7 +8052,7 @@
         <v>302</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D289" s="4">
         <v>1000.0</v>
@@ -8057,7 +8073,7 @@
         <v>303</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D290" s="4">
         <v>10000.0</v>
@@ -8078,10 +8094,10 @@
         <v>304</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D291" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E291" s="7"/>
       <c r="F291" s="7"/>
@@ -8099,10 +8115,10 @@
         <v>305</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D292" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E292" s="7"/>
       <c r="F292" s="7"/>
@@ -8120,10 +8136,10 @@
         <v>306</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D293" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E293" s="7"/>
       <c r="F293" s="7"/>
@@ -8141,10 +8157,10 @@
         <v>307</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D294" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E294" s="7"/>
       <c r="F294" s="7"/>
@@ -8162,10 +8178,10 @@
         <v>308</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D295" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E295" s="7"/>
       <c r="F295" s="7"/>
@@ -8183,10 +8199,10 @@
         <v>309</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D296" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E296" s="7"/>
       <c r="F296" s="7"/>
@@ -8204,10 +8220,10 @@
         <v>310</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D297" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E297" s="7"/>
       <c r="F297" s="7"/>
@@ -8225,10 +8241,10 @@
         <v>311</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D298" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E298" s="7"/>
       <c r="F298" s="7"/>
@@ -8246,10 +8262,10 @@
         <v>312</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D299" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E299" s="7"/>
       <c r="F299" s="7"/>
@@ -8267,10 +8283,10 @@
         <v>313</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D300" s="4">
-        <v>2000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E300" s="7"/>
       <c r="F300" s="7"/>
@@ -8288,7 +8304,7 @@
         <v>314</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D301" s="4">
         <v>5000.0</v>
@@ -8309,7 +8325,7 @@
         <v>315</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D302" s="4">
         <v>1000.0</v>
@@ -8330,10 +8346,10 @@
         <v>316</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D303" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E303" s="7"/>
       <c r="F303" s="7"/>
@@ -8351,10 +8367,10 @@
         <v>317</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D304" s="4">
-        <v>1000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E304" s="7"/>
       <c r="F304" s="7"/>
@@ -8372,7 +8388,7 @@
         <v>318</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D305" s="4">
         <v>5000.0</v>
@@ -8393,7 +8409,7 @@
         <v>319</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D306" s="4">
         <v>1000.0</v>
@@ -8414,7 +8430,7 @@
         <v>320</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D307" s="4">
         <v>5000.0</v>
@@ -8435,10 +8451,10 @@
         <v>321</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D308" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E308" s="7"/>
       <c r="F308" s="7"/>
@@ -8456,10 +8472,10 @@
         <v>322</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D309" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E309" s="7"/>
       <c r="F309" s="7"/>
@@ -8477,10 +8493,10 @@
         <v>323</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D310" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E310" s="7"/>
       <c r="F310" s="7"/>
@@ -8498,7 +8514,7 @@
         <v>324</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D311" s="4">
         <v>5000.0</v>
@@ -8519,7 +8535,7 @@
         <v>325</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D312" s="4">
         <v>500.0</v>
@@ -8540,10 +8556,10 @@
         <v>326</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D313" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E313" s="7"/>
       <c r="F313" s="7"/>
@@ -8561,10 +8577,10 @@
         <v>327</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D314" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E314" s="7"/>
       <c r="F314" s="7"/>
@@ -8582,7 +8598,7 @@
         <v>328</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D315" s="4">
         <v>5000.0</v>
@@ -8603,10 +8619,10 @@
         <v>329</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D316" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E316" s="7"/>
       <c r="F316" s="7"/>
@@ -8624,7 +8640,7 @@
         <v>330</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D317" s="4">
         <v>5000.0</v>
@@ -8645,17 +8661,13 @@
         <v>331</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D318" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E318" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F318" s="4">
-        <v>4500.0</v>
-      </c>
+        <v>500.0</v>
+      </c>
+      <c r="E318" s="7"/>
+      <c r="F318" s="7"/>
       <c r="G318" s="7"/>
       <c r="H318" s="7"/>
       <c r="I318" s="7"/>
@@ -8670,10 +8682,10 @@
         <v>332</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D319" s="4">
-        <v>4500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E319" s="7"/>
       <c r="F319" s="7"/>
@@ -8691,13 +8703,13 @@
         <v>333</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D320" s="4">
-        <v>51000.0</v>
-      </c>
-      <c r="E320" s="4"/>
-      <c r="F320" s="4"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E320" s="7"/>
+      <c r="F320" s="7"/>
       <c r="G320" s="7"/>
       <c r="H320" s="7"/>
       <c r="I320" s="7"/>
@@ -8712,17 +8724,13 @@
         <v>334</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D321" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E321" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F321" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E321" s="7"/>
+      <c r="F321" s="7"/>
       <c r="G321" s="7"/>
       <c r="H321" s="7"/>
       <c r="I321" s="7"/>
@@ -8737,13 +8745,17 @@
         <v>335</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D322" s="4">
-        <v>52000.0</v>
-      </c>
-      <c r="E322" s="7"/>
-      <c r="F322" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E322" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F322" s="4">
+        <v>4500.0</v>
+      </c>
       <c r="G322" s="7"/>
       <c r="H322" s="7"/>
       <c r="I322" s="7"/>
@@ -8758,10 +8770,10 @@
         <v>336</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D323" s="4">
-        <v>1000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E323" s="7"/>
       <c r="F323" s="7"/>
@@ -8779,13 +8791,13 @@
         <v>337</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D324" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E324" s="7"/>
-      <c r="F324" s="7"/>
+        <v>51000.0</v>
+      </c>
+      <c r="E324" s="4"/>
+      <c r="F324" s="4"/>
       <c r="G324" s="7"/>
       <c r="H324" s="7"/>
       <c r="I324" s="7"/>
@@ -8800,16 +8812,16 @@
         <v>338</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D325" s="4">
         <v>2000.0</v>
       </c>
       <c r="E325" s="4">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F325" s="4">
-        <v>17000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="G325" s="7"/>
       <c r="H325" s="7"/>
@@ -8825,10 +8837,10 @@
         <v>339</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D326" s="4">
-        <v>5000.0</v>
+        <v>52000.0</v>
       </c>
       <c r="E326" s="7"/>
       <c r="F326" s="7"/>
@@ -8846,17 +8858,13 @@
         <v>340</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D327" s="4">
-        <v>7000.0</v>
-      </c>
-      <c r="E327" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F327" s="4">
-        <v>32500.0</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E327" s="7"/>
+      <c r="F327" s="7"/>
       <c r="G327" s="7"/>
       <c r="H327" s="7"/>
       <c r="I327" s="7"/>
@@ -8871,10 +8879,10 @@
         <v>341</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D328" s="4">
-        <v>7500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E328" s="7"/>
       <c r="F328" s="7"/>
@@ -8892,13 +8900,17 @@
         <v>342</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D329" s="4">
-        <v>9500.0</v>
-      </c>
-      <c r="E329" s="7"/>
-      <c r="F329" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E329" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F329" s="4">
+        <v>17000.0</v>
+      </c>
       <c r="G329" s="7"/>
       <c r="H329" s="7"/>
       <c r="I329" s="7"/>
@@ -8913,10 +8925,10 @@
         <v>343</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D330" s="4">
-        <v>3500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E330" s="7"/>
       <c r="F330" s="7"/>
@@ -8934,13 +8946,17 @@
         <v>344</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D331" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E331" s="7"/>
-      <c r="F331" s="7"/>
+        <v>7000.0</v>
+      </c>
+      <c r="E331" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F331" s="4">
+        <v>32500.0</v>
+      </c>
       <c r="G331" s="7"/>
       <c r="H331" s="7"/>
       <c r="I331" s="7"/>
@@ -8955,17 +8971,13 @@
         <v>345</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D332" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E332" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F332" s="4">
-        <v>22500.0</v>
-      </c>
+        <v>7500.0</v>
+      </c>
+      <c r="E332" s="7"/>
+      <c r="F332" s="7"/>
       <c r="G332" s="7"/>
       <c r="H332" s="7"/>
       <c r="I332" s="7"/>
@@ -8980,17 +8992,13 @@
         <v>346</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D333" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E333" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F333" s="4">
-        <v>12500.0</v>
-      </c>
+        <v>9500.0</v>
+      </c>
+      <c r="E333" s="7"/>
+      <c r="F333" s="7"/>
       <c r="G333" s="7"/>
       <c r="H333" s="7"/>
       <c r="I333" s="7"/>
@@ -9005,13 +9013,13 @@
         <v>347</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D334" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E334" s="4"/>
-      <c r="F334" s="4"/>
+      <c r="E334" s="7"/>
+      <c r="F334" s="7"/>
       <c r="G334" s="7"/>
       <c r="H334" s="7"/>
       <c r="I334" s="7"/>
@@ -9026,14 +9034,14 @@
         <v>348</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D335" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E335" s="4"/>
-      <c r="F335" s="4"/>
-      <c r="G335" s="4"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E335" s="7"/>
+      <c r="F335" s="7"/>
+      <c r="G335" s="7"/>
       <c r="H335" s="7"/>
       <c r="I335" s="7"/>
       <c r="J335" s="7"/>
@@ -9047,16 +9055,16 @@
         <v>349</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D336" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E336" s="4">
         <v>5.0</v>
       </c>
       <c r="F336" s="4">
-        <v>11500.0</v>
+        <v>22500.0</v>
       </c>
       <c r="G336" s="7"/>
       <c r="H336" s="7"/>
@@ -9072,13 +9080,17 @@
         <v>350</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D337" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E337" s="7"/>
-      <c r="F337" s="7"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E337" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F337" s="4">
+        <v>12500.0</v>
+      </c>
       <c r="G337" s="7"/>
       <c r="H337" s="7"/>
       <c r="I337" s="7"/>
@@ -9093,17 +9105,13 @@
         <v>351</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D338" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E338" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F338" s="4">
-        <v>22500.0</v>
-      </c>
+        <v>3500.0</v>
+      </c>
+      <c r="E338" s="4"/>
+      <c r="F338" s="4"/>
       <c r="G338" s="7"/>
       <c r="H338" s="7"/>
       <c r="I338" s="7"/>
@@ -9118,14 +9126,14 @@
         <v>352</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D339" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E339" s="7"/>
-      <c r="F339" s="7"/>
-      <c r="G339" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E339" s="4"/>
+      <c r="F339" s="4"/>
+      <c r="G339" s="4"/>
       <c r="H339" s="7"/>
       <c r="I339" s="7"/>
       <c r="J339" s="7"/>
@@ -9139,13 +9147,17 @@
         <v>353</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D340" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E340" s="7"/>
-      <c r="F340" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E340" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F340" s="4">
+        <v>11500.0</v>
+      </c>
       <c r="G340" s="7"/>
       <c r="H340" s="7"/>
       <c r="I340" s="7"/>
@@ -9160,10 +9172,10 @@
         <v>354</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D341" s="4">
-        <v>3000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E341" s="7"/>
       <c r="F341" s="7"/>
@@ -9181,13 +9193,17 @@
         <v>355</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D342" s="4">
-        <v>14000.0</v>
-      </c>
-      <c r="E342" s="7"/>
-      <c r="F342" s="7"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E342" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F342" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G342" s="7"/>
       <c r="H342" s="7"/>
       <c r="I342" s="7"/>
@@ -9202,7 +9218,7 @@
         <v>356</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>357</v>
+        <v>298</v>
       </c>
       <c r="D343" s="4">
         <v>1000.0</v>
@@ -9220,13 +9236,13 @@
         <v>343</v>
       </c>
       <c r="B344" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>357</v>
+        <v>298</v>
       </c>
       <c r="D344" s="4">
-        <v>4000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E344" s="7"/>
       <c r="F344" s="7"/>
@@ -9241,13 +9257,13 @@
         <v>344</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>357</v>
+        <v>298</v>
       </c>
       <c r="D345" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E345" s="7"/>
       <c r="F345" s="7"/>
@@ -9262,13 +9278,13 @@
         <v>345</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>357</v>
+        <v>298</v>
       </c>
       <c r="D346" s="4">
-        <v>10000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E346" s="7"/>
       <c r="F346" s="7"/>
@@ -9283,10 +9299,10 @@
         <v>346</v>
       </c>
       <c r="B347" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C347" s="5" t="s">
         <v>361</v>
-      </c>
-      <c r="C347" s="5" t="s">
-        <v>357</v>
       </c>
       <c r="D347" s="4">
         <v>1000.0</v>
@@ -9307,10 +9323,10 @@
         <v>362</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D348" s="4">
-        <v>10000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E348" s="7"/>
       <c r="F348" s="7"/>
@@ -9328,10 +9344,10 @@
         <v>363</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D349" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E349" s="7"/>
       <c r="F349" s="7"/>
@@ -9349,10 +9365,10 @@
         <v>364</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D350" s="4">
-        <v>2500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E350" s="7"/>
       <c r="F350" s="7"/>
@@ -9370,10 +9386,10 @@
         <v>365</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D351" s="4">
-        <v>3000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E351" s="7"/>
       <c r="F351" s="7"/>
@@ -9391,10 +9407,10 @@
         <v>366</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D352" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E352" s="7"/>
       <c r="F352" s="7"/>
@@ -9412,10 +9428,10 @@
         <v>367</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D353" s="4">
-        <v>3000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E353" s="7"/>
       <c r="F353" s="7"/>
@@ -9433,17 +9449,13 @@
         <v>368</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D354" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E354" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F354" s="4">
-        <v>3000.0</v>
-      </c>
+        <v>2500.0</v>
+      </c>
+      <c r="E354" s="7"/>
+      <c r="F354" s="7"/>
       <c r="G354" s="7"/>
       <c r="H354" s="7"/>
       <c r="I354" s="7"/>
@@ -9458,10 +9470,10 @@
         <v>369</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D355" s="4">
-        <v>500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E355" s="7"/>
       <c r="F355" s="7"/>
@@ -9479,10 +9491,10 @@
         <v>370</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D356" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E356" s="7"/>
       <c r="F356" s="7"/>
@@ -9500,10 +9512,10 @@
         <v>371</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D357" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E357" s="7"/>
       <c r="F357" s="7"/>
@@ -9521,13 +9533,17 @@
         <v>372</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D358" s="4">
-        <v>7000.0</v>
-      </c>
-      <c r="E358" s="7"/>
-      <c r="F358" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E358" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F358" s="4">
+        <v>3000.0</v>
+      </c>
       <c r="G358" s="7"/>
       <c r="H358" s="7"/>
       <c r="I358" s="7"/>
@@ -9542,10 +9558,10 @@
         <v>373</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D359" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E359" s="7"/>
       <c r="F359" s="7"/>
@@ -9563,10 +9579,10 @@
         <v>374</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D360" s="4">
-        <v>25000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E360" s="7"/>
       <c r="F360" s="7"/>
@@ -9584,10 +9600,10 @@
         <v>375</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D361" s="4">
-        <v>8000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E361" s="7"/>
       <c r="F361" s="7"/>
@@ -9605,10 +9621,10 @@
         <v>376</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D362" s="4">
-        <v>4000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E362" s="7"/>
       <c r="F362" s="7"/>
@@ -9626,10 +9642,10 @@
         <v>377</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="D363" s="4">
-        <v>2000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E363" s="7"/>
       <c r="F363" s="7"/>
@@ -9644,13 +9660,13 @@
         <v>363</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="D364" s="4">
-        <v>45000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E364" s="7"/>
       <c r="F364" s="7"/>
@@ -9665,13 +9681,13 @@
         <v>364</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="D365" s="4">
-        <v>2500.0</v>
+        <v>8000.0</v>
       </c>
       <c r="E365" s="7"/>
       <c r="F365" s="7"/>
@@ -9686,13 +9702,13 @@
         <v>365</v>
       </c>
       <c r="B366" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="D366" s="4">
-        <v>2500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E366" s="7"/>
       <c r="F366" s="7"/>
@@ -9707,13 +9723,13 @@
         <v>366</v>
       </c>
       <c r="B367" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C367" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="C367" s="5" t="s">
-        <v>378</v>
-      </c>
       <c r="D367" s="4">
-        <v>4000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E367" s="7"/>
       <c r="F367" s="7"/>
@@ -9731,10 +9747,10 @@
         <v>383</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D368" s="4">
-        <v>40000.0</v>
+        <v>45000.0</v>
       </c>
       <c r="E368" s="7"/>
       <c r="F368" s="7"/>
@@ -9752,10 +9768,10 @@
         <v>384</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D369" s="4">
-        <v>5000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E369" s="7"/>
       <c r="F369" s="7"/>
@@ -9773,16 +9789,16 @@
         <v>385</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D370" s="4">
-        <v>46000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E370" s="7"/>
       <c r="F370" s="7"/>
       <c r="G370" s="7"/>
       <c r="H370" s="7"/>
-      <c r="I370" s="4"/>
+      <c r="I370" s="7"/>
       <c r="J370" s="7"/>
     </row>
     <row r="371">
@@ -9794,16 +9810,16 @@
         <v>386</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D371" s="4">
-        <v>2000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E371" s="7"/>
       <c r="F371" s="7"/>
       <c r="G371" s="7"/>
       <c r="H371" s="7"/>
-      <c r="I371" s="4"/>
+      <c r="I371" s="7"/>
       <c r="J371" s="7"/>
     </row>
     <row r="372">
@@ -9815,16 +9831,16 @@
         <v>387</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D372" s="4">
-        <v>17000.0</v>
+        <v>40000.0</v>
       </c>
       <c r="E372" s="7"/>
       <c r="F372" s="7"/>
       <c r="G372" s="7"/>
       <c r="H372" s="7"/>
-      <c r="I372" s="4"/>
+      <c r="I372" s="7"/>
       <c r="J372" s="7"/>
     </row>
     <row r="373">
@@ -9836,16 +9852,16 @@
         <v>388</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D373" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E373" s="7"/>
       <c r="F373" s="7"/>
       <c r="G373" s="7"/>
       <c r="H373" s="7"/>
-      <c r="I373" s="4"/>
+      <c r="I373" s="7"/>
       <c r="J373" s="7"/>
     </row>
     <row r="374">
@@ -9857,16 +9873,16 @@
         <v>389</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D374" s="4">
-        <v>1000.0</v>
+        <v>46000.0</v>
       </c>
       <c r="E374" s="7"/>
       <c r="F374" s="7"/>
       <c r="G374" s="7"/>
       <c r="H374" s="7"/>
-      <c r="I374" s="7"/>
+      <c r="I374" s="4"/>
       <c r="J374" s="7"/>
     </row>
     <row r="375">
@@ -9878,16 +9894,16 @@
         <v>390</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D375" s="4">
-        <v>10000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E375" s="7"/>
       <c r="F375" s="7"/>
       <c r="G375" s="7"/>
       <c r="H375" s="7"/>
-      <c r="I375" s="7"/>
+      <c r="I375" s="4"/>
       <c r="J375" s="7"/>
     </row>
     <row r="376">
@@ -9899,16 +9915,16 @@
         <v>391</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D376" s="4">
-        <v>500.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E376" s="7"/>
       <c r="F376" s="7"/>
       <c r="G376" s="7"/>
       <c r="H376" s="7"/>
-      <c r="I376" s="7"/>
+      <c r="I376" s="4"/>
       <c r="J376" s="7"/>
     </row>
     <row r="377">
@@ -9920,16 +9936,16 @@
         <v>392</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D377" s="4">
-        <v>1500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E377" s="7"/>
       <c r="F377" s="7"/>
       <c r="G377" s="7"/>
       <c r="H377" s="7"/>
-      <c r="I377" s="7"/>
+      <c r="I377" s="4"/>
       <c r="J377" s="7"/>
     </row>
     <row r="378">
@@ -9941,10 +9957,10 @@
         <v>393</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D378" s="4">
-        <v>12000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E378" s="7"/>
       <c r="F378" s="7"/>
@@ -9962,10 +9978,10 @@
         <v>394</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D379" s="4">
-        <v>3000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E379" s="7"/>
       <c r="F379" s="7"/>
@@ -9983,10 +9999,10 @@
         <v>395</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D380" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E380" s="7"/>
       <c r="F380" s="7"/>
@@ -10004,10 +10020,10 @@
         <v>396</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D381" s="4">
-        <v>25000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E381" s="7"/>
       <c r="F381" s="7"/>
@@ -10025,10 +10041,10 @@
         <v>397</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D382" s="4">
-        <v>9000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E382" s="7"/>
       <c r="F382" s="7"/>
@@ -10046,12 +10062,12 @@
         <v>398</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D383" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E383" s="4"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E383" s="7"/>
       <c r="F383" s="7"/>
       <c r="G383" s="7"/>
       <c r="H383" s="7"/>
@@ -10067,10 +10083,10 @@
         <v>399</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D384" s="4">
-        <v>9000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E384" s="7"/>
       <c r="F384" s="7"/>
@@ -10088,10 +10104,10 @@
         <v>400</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D385" s="4">
-        <v>4500.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E385" s="7"/>
       <c r="F385" s="7"/>
@@ -10109,10 +10125,10 @@
         <v>401</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D386" s="4">
-        <v>500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E386" s="7"/>
       <c r="F386" s="7"/>
@@ -10130,12 +10146,12 @@
         <v>402</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D387" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E387" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E387" s="4"/>
       <c r="F387" s="7"/>
       <c r="G387" s="7"/>
       <c r="H387" s="7"/>
@@ -10151,10 +10167,10 @@
         <v>403</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D388" s="4">
-        <v>1000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E388" s="7"/>
       <c r="F388" s="7"/>
@@ -10168,63 +10184,63 @@
         <f t="shared" si="1"/>
         <v>388</v>
       </c>
-      <c r="B389" s="9" t="s">
+      <c r="B389" s="5" t="s">
         <v>404</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="D389" s="10">
+        <v>382</v>
+      </c>
+      <c r="D389" s="4">
         <v>4500.0</v>
       </c>
-      <c r="E389" s="11"/>
-      <c r="F389" s="11"/>
-      <c r="G389" s="11"/>
-      <c r="H389" s="11"/>
-      <c r="I389" s="11"/>
-      <c r="J389" s="11"/>
+      <c r="E389" s="7"/>
+      <c r="F389" s="7"/>
+      <c r="G389" s="7"/>
+      <c r="H389" s="7"/>
+      <c r="I389" s="7"/>
+      <c r="J389" s="7"/>
     </row>
     <row r="390">
       <c r="A390" s="4">
         <f t="shared" si="1"/>
         <v>389</v>
       </c>
-      <c r="B390" s="9" t="s">
+      <c r="B390" s="5" t="s">
         <v>405</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="D390" s="10">
-        <v>50000.0</v>
-      </c>
-      <c r="E390" s="11"/>
-      <c r="F390" s="11"/>
-      <c r="G390" s="11"/>
-      <c r="H390" s="11"/>
-      <c r="I390" s="11"/>
-      <c r="J390" s="11"/>
+        <v>382</v>
+      </c>
+      <c r="D390" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="E390" s="7"/>
+      <c r="F390" s="7"/>
+      <c r="G390" s="7"/>
+      <c r="H390" s="7"/>
+      <c r="I390" s="7"/>
+      <c r="J390" s="7"/>
     </row>
     <row r="391">
       <c r="A391" s="4">
         <f t="shared" si="1"/>
         <v>390</v>
       </c>
-      <c r="B391" s="9" t="s">
+      <c r="B391" s="5" t="s">
         <v>406</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="D391" s="10">
-        <v>12000.0</v>
-      </c>
-      <c r="E391" s="11"/>
-      <c r="F391" s="11"/>
-      <c r="G391" s="11"/>
-      <c r="H391" s="11"/>
-      <c r="I391" s="11"/>
-      <c r="J391" s="11"/>
+        <v>382</v>
+      </c>
+      <c r="D391" s="4">
+        <v>3000.0</v>
+      </c>
+      <c r="E391" s="7"/>
+      <c r="F391" s="7"/>
+      <c r="G391" s="7"/>
+      <c r="H391" s="7"/>
+      <c r="I391" s="7"/>
+      <c r="J391" s="7"/>
     </row>
     <row r="392">
       <c r="A392" s="4">
@@ -10235,17 +10251,17 @@
         <v>407</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="D392" s="10">
-        <v>4500.0</v>
-      </c>
-      <c r="E392" s="11"/>
-      <c r="F392" s="11"/>
-      <c r="G392" s="11"/>
-      <c r="H392" s="11"/>
-      <c r="I392" s="11"/>
-      <c r="J392" s="11"/>
+        <v>382</v>
+      </c>
+      <c r="D392" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E392" s="7"/>
+      <c r="F392" s="7"/>
+      <c r="G392" s="7"/>
+      <c r="H392" s="7"/>
+      <c r="I392" s="7"/>
+      <c r="J392" s="7"/>
     </row>
     <row r="393">
       <c r="A393" s="4">
@@ -10256,10 +10272,10 @@
         <v>408</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="D393" s="10">
-        <v>3000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E393" s="11"/>
       <c r="F393" s="11"/>
@@ -10277,10 +10293,10 @@
         <v>409</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="D394" s="10">
-        <v>5000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="E394" s="11"/>
       <c r="F394" s="11"/>
@@ -10298,10 +10314,10 @@
         <v>410</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="D395" s="10">
-        <v>6000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E395" s="11"/>
       <c r="F395" s="11"/>
@@ -10315,14 +10331,14 @@
         <f t="shared" si="1"/>
         <v>395</v>
       </c>
-      <c r="B396" s="9" t="s">
+      <c r="B396" s="5" t="s">
         <v>411</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="D396" s="10">
-        <v>12000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E396" s="11"/>
       <c r="F396" s="11"/>
@@ -10340,13 +10356,13 @@
         <v>412</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>357</v>
+        <v>413</v>
       </c>
       <c r="D397" s="10">
-        <v>200.0</v>
-      </c>
-      <c r="E397" s="10"/>
-      <c r="F397" s="10"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E397" s="11"/>
+      <c r="F397" s="11"/>
       <c r="G397" s="11"/>
       <c r="H397" s="11"/>
       <c r="I397" s="11"/>
@@ -10361,17 +10377,13 @@
         <v>413</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>357</v>
+        <v>413</v>
       </c>
       <c r="D398" s="10">
         <v>5000.0</v>
       </c>
-      <c r="E398" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="F398" s="10">
-        <v>4500.0</v>
-      </c>
+      <c r="E398" s="11"/>
+      <c r="F398" s="11"/>
       <c r="G398" s="11"/>
       <c r="H398" s="11"/>
       <c r="I398" s="11"/>
@@ -10386,10 +10398,10 @@
         <v>414</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>357</v>
+        <v>413</v>
       </c>
       <c r="D399" s="10">
-        <v>18000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="E399" s="11"/>
       <c r="F399" s="11"/>
@@ -10407,10 +10419,10 @@
         <v>415</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D400" s="10">
-        <v>17000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E400" s="11"/>
       <c r="F400" s="11"/>
@@ -10428,13 +10440,13 @@
         <v>416</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D401" s="10">
-        <v>17500.0</v>
-      </c>
-      <c r="E401" s="11"/>
-      <c r="F401" s="11"/>
+        <v>200.0</v>
+      </c>
+      <c r="E401" s="10"/>
+      <c r="F401" s="10"/>
       <c r="G401" s="11"/>
       <c r="H401" s="11"/>
       <c r="I401" s="11"/>
@@ -10449,13 +10461,17 @@
         <v>417</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D402" s="10">
-        <v>9000.0</v>
-      </c>
-      <c r="E402" s="11"/>
-      <c r="F402" s="11"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E402" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="F402" s="10">
+        <v>4500.0</v>
+      </c>
       <c r="G402" s="11"/>
       <c r="H402" s="11"/>
       <c r="I402" s="11"/>
@@ -10470,10 +10486,10 @@
         <v>418</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D403" s="10">
-        <v>9000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E403" s="11"/>
       <c r="F403" s="11"/>
@@ -10491,10 +10507,10 @@
         <v>419</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D404" s="10">
-        <v>19500.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E404" s="11"/>
       <c r="F404" s="11"/>
@@ -10512,10 +10528,10 @@
         <v>420</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D405" s="10">
-        <v>8500.0</v>
+        <v>17500.0</v>
       </c>
       <c r="E405" s="11"/>
       <c r="F405" s="11"/>
@@ -10525,10 +10541,19 @@
       <c r="J405" s="11"/>
     </row>
     <row r="406">
-      <c r="A406" s="12"/>
-      <c r="B406" s="12"/>
-      <c r="C406" s="12"/>
-      <c r="D406" s="11"/>
+      <c r="A406" s="4">
+        <f t="shared" si="1"/>
+        <v>405</v>
+      </c>
+      <c r="B406" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="C406" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D406" s="10">
+        <v>9000.0</v>
+      </c>
       <c r="E406" s="11"/>
       <c r="F406" s="11"/>
       <c r="G406" s="11"/>
@@ -10537,10 +10562,19 @@
       <c r="J406" s="11"/>
     </row>
     <row r="407">
-      <c r="A407" s="12"/>
-      <c r="B407" s="12"/>
-      <c r="C407" s="12"/>
-      <c r="D407" s="11"/>
+      <c r="A407" s="4">
+        <f t="shared" si="1"/>
+        <v>406</v>
+      </c>
+      <c r="B407" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="C407" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D407" s="10">
+        <v>9000.0</v>
+      </c>
       <c r="E407" s="11"/>
       <c r="F407" s="11"/>
       <c r="G407" s="11"/>
@@ -10549,10 +10583,19 @@
       <c r="J407" s="11"/>
     </row>
     <row r="408">
-      <c r="A408" s="12"/>
-      <c r="B408" s="12"/>
-      <c r="C408" s="12"/>
-      <c r="D408" s="11"/>
+      <c r="A408" s="4">
+        <f t="shared" si="1"/>
+        <v>407</v>
+      </c>
+      <c r="B408" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="C408" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D408" s="10">
+        <v>19500.0</v>
+      </c>
       <c r="E408" s="11"/>
       <c r="F408" s="11"/>
       <c r="G408" s="11"/>
@@ -10561,10 +10604,19 @@
       <c r="J408" s="11"/>
     </row>
     <row r="409">
-      <c r="A409" s="12"/>
-      <c r="B409" s="12"/>
-      <c r="C409" s="12"/>
-      <c r="D409" s="11"/>
+      <c r="A409" s="4">
+        <f t="shared" si="1"/>
+        <v>408</v>
+      </c>
+      <c r="B409" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="C409" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D409" s="10">
+        <v>8500.0</v>
+      </c>
       <c r="E409" s="11"/>
       <c r="F409" s="11"/>
       <c r="G409" s="11"/>
@@ -11620,49 +11672,49 @@
       <c r="A497" s="12"/>
       <c r="B497" s="12"/>
       <c r="C497" s="12"/>
-      <c r="D497" s="12"/>
-      <c r="E497" s="12"/>
-      <c r="F497" s="12"/>
-      <c r="G497" s="12"/>
-      <c r="H497" s="12"/>
-      <c r="I497" s="12"/>
-      <c r="J497" s="12"/>
+      <c r="D497" s="11"/>
+      <c r="E497" s="11"/>
+      <c r="F497" s="11"/>
+      <c r="G497" s="11"/>
+      <c r="H497" s="11"/>
+      <c r="I497" s="11"/>
+      <c r="J497" s="11"/>
     </row>
     <row r="498">
       <c r="A498" s="12"/>
       <c r="B498" s="12"/>
       <c r="C498" s="12"/>
-      <c r="D498" s="12"/>
-      <c r="E498" s="12"/>
-      <c r="F498" s="12"/>
-      <c r="G498" s="12"/>
-      <c r="H498" s="12"/>
-      <c r="I498" s="12"/>
-      <c r="J498" s="12"/>
+      <c r="D498" s="11"/>
+      <c r="E498" s="11"/>
+      <c r="F498" s="11"/>
+      <c r="G498" s="11"/>
+      <c r="H498" s="11"/>
+      <c r="I498" s="11"/>
+      <c r="J498" s="11"/>
     </row>
     <row r="499">
       <c r="A499" s="12"/>
       <c r="B499" s="12"/>
       <c r="C499" s="12"/>
-      <c r="D499" s="12"/>
-      <c r="E499" s="12"/>
-      <c r="F499" s="12"/>
-      <c r="G499" s="12"/>
-      <c r="H499" s="12"/>
-      <c r="I499" s="12"/>
-      <c r="J499" s="12"/>
+      <c r="D499" s="11"/>
+      <c r="E499" s="11"/>
+      <c r="F499" s="11"/>
+      <c r="G499" s="11"/>
+      <c r="H499" s="11"/>
+      <c r="I499" s="11"/>
+      <c r="J499" s="11"/>
     </row>
     <row r="500">
       <c r="A500" s="12"/>
       <c r="B500" s="12"/>
       <c r="C500" s="12"/>
-      <c r="D500" s="12"/>
-      <c r="E500" s="12"/>
-      <c r="F500" s="12"/>
-      <c r="G500" s="12"/>
-      <c r="H500" s="12"/>
-      <c r="I500" s="12"/>
-      <c r="J500" s="12"/>
+      <c r="D500" s="11"/>
+      <c r="E500" s="11"/>
+      <c r="F500" s="11"/>
+      <c r="G500" s="11"/>
+      <c r="H500" s="11"/>
+      <c r="I500" s="11"/>
+      <c r="J500" s="11"/>
     </row>
     <row r="501">
       <c r="A501" s="12"/>
@@ -20040,15 +20092,63 @@
       <c r="I1198" s="12"/>
       <c r="J1198" s="12"/>
     </row>
+    <row r="1199">
+      <c r="A1199" s="12"/>
+      <c r="B1199" s="12"/>
+      <c r="C1199" s="12"/>
+      <c r="D1199" s="12"/>
+      <c r="E1199" s="12"/>
+      <c r="F1199" s="12"/>
+      <c r="G1199" s="12"/>
+      <c r="H1199" s="12"/>
+      <c r="I1199" s="12"/>
+      <c r="J1199" s="12"/>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="12"/>
+      <c r="B1200" s="12"/>
+      <c r="C1200" s="12"/>
+      <c r="D1200" s="12"/>
+      <c r="E1200" s="12"/>
+      <c r="F1200" s="12"/>
+      <c r="G1200" s="12"/>
+      <c r="H1200" s="12"/>
+      <c r="I1200" s="12"/>
+      <c r="J1200" s="12"/>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="12"/>
+      <c r="B1201" s="12"/>
+      <c r="C1201" s="12"/>
+      <c r="D1201" s="12"/>
+      <c r="E1201" s="12"/>
+      <c r="F1201" s="12"/>
+      <c r="G1201" s="12"/>
+      <c r="H1201" s="12"/>
+      <c r="I1201" s="12"/>
+      <c r="J1201" s="12"/>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="12"/>
+      <c r="B1202" s="12"/>
+      <c r="C1202" s="12"/>
+      <c r="D1202" s="12"/>
+      <c r="E1202" s="12"/>
+      <c r="F1202" s="12"/>
+      <c r="G1202" s="12"/>
+      <c r="H1202" s="12"/>
+      <c r="I1202" s="12"/>
+      <c r="J1202" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$405"/>
-  <conditionalFormatting sqref="A2:J1198">
+  <autoFilter ref="$B$1:$C$409"/>
+  <conditionalFormatting sqref="A2:J1202">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C405">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C409">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20109,7 +20209,7 @@
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4">
@@ -20128,7 +20228,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -20147,7 +20247,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -20166,7 +20266,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -20185,7 +20285,7 @@
         <v>GROSIR5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="4">
@@ -20204,7 +20304,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -20223,7 +20323,7 @@
         <v>GROSIR7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="4">
@@ -20242,7 +20342,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -20261,7 +20361,7 @@
         <v>GROSIR9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="4">
@@ -20280,7 +20380,7 @@
         <v>GROSIR10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="4">
@@ -20299,7 +20399,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -20318,7 +20418,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -20337,7 +20437,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -20356,7 +20456,7 @@
         <v>GROSIR14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="4">
@@ -20375,7 +20475,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -20394,7 +20494,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -20413,7 +20513,7 @@
         <v>GROSIR17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="4">
@@ -20432,7 +20532,7 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
@@ -20451,7 +20551,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -20470,7 +20570,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -20489,7 +20589,7 @@
         <v>GROSIR21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4">
@@ -20508,7 +20608,7 @@
         <v>GROSIR22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="4">
@@ -20527,7 +20627,7 @@
         <v>GROSIR23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="4">
@@ -20546,7 +20646,7 @@
         <v>GROSIR24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="4">
@@ -20565,7 +20665,7 @@
         <v>GROSIR25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="4">
@@ -20584,7 +20684,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -20603,7 +20703,7 @@
         <v>GROSIR27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="4">
@@ -20622,7 +20722,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -20641,7 +20741,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -20660,7 +20760,7 @@
         <v>GROSIR30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="4">
@@ -20679,7 +20779,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -20698,7 +20798,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -20717,7 +20817,7 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
@@ -20736,7 +20836,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -20755,7 +20855,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -20774,7 +20874,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -20793,7 +20893,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -20812,7 +20912,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -20831,7 +20931,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -20850,7 +20950,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -20869,7 +20969,7 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
@@ -20888,7 +20988,7 @@
         <v>GROSIR42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="4">
@@ -20907,7 +21007,7 @@
         <v>GROSIR43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$409</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$412</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$260</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="454">
   <si>
     <t>Barcode</t>
   </si>
@@ -386,6 +386,12 @@
     <t>Extrajoss Box</t>
   </si>
   <si>
+    <t>Fresco</t>
+  </si>
+  <si>
+    <t>Fresco R</t>
+  </si>
+  <si>
     <t>Kerupuk Sumber Sari</t>
   </si>
   <si>
@@ -1290,6 +1296,9 @@
   </si>
   <si>
     <t>Siip 500 dus</t>
+  </si>
+  <si>
+    <t>Pilus 1000 Renceng</t>
   </si>
   <si>
     <t>Djarum Coklat Bungkus SLOP</t>
@@ -1755,7 +1764,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A409" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A412" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -2328,14 +2337,10 @@
         <v>20</v>
       </c>
       <c r="D28" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E28" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F28" s="4">
-        <v>16500.0</v>
-      </c>
+        <v>4000.0</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -2353,7 +2358,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="4">
-        <v>39000.0</v>
+        <v>40000.0</v>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
@@ -4122,10 +4127,10 @@
         <v>123</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="D113" s="4">
-        <v>6000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
@@ -4140,20 +4145,20 @@
         <v>113</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="D114" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E114" s="7"/>
-      <c r="F114" s="7"/>
-      <c r="G114" s="7"/>
-      <c r="H114" s="7"/>
-      <c r="I114" s="7"/>
-      <c r="J114" s="7"/>
+        <v>16000.0</v>
+      </c>
+      <c r="E114" s="6"/>
+      <c r="F114" s="6"/>
+      <c r="G114" s="6"/>
+      <c r="H114" s="6"/>
+      <c r="I114" s="6"/>
+      <c r="J114" s="6"/>
     </row>
     <row r="115">
       <c r="A115" s="4">
@@ -4161,20 +4166,20 @@
         <v>114</v>
       </c>
       <c r="B115" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C115" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C115" s="5" t="s">
-        <v>124</v>
-      </c>
       <c r="D115" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7"/>
-      <c r="G115" s="7"/>
-      <c r="H115" s="7"/>
-      <c r="I115" s="7"/>
-      <c r="J115" s="7"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="6"/>
+      <c r="H115" s="6"/>
+      <c r="I115" s="6"/>
+      <c r="J115" s="6"/>
     </row>
     <row r="116">
       <c r="A116" s="4">
@@ -4185,7 +4190,7 @@
         <v>127</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D116" s="4">
         <v>1000.0</v>
@@ -4206,7 +4211,7 @@
         <v>128</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D117" s="4">
         <v>10000.0</v>
@@ -4227,7 +4232,7 @@
         <v>129</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D118" s="4">
         <v>1000.0</v>
@@ -4248,7 +4253,7 @@
         <v>130</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D119" s="4">
         <v>10000.0</v>
@@ -4269,10 +4274,10 @@
         <v>131</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D120" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E120" s="7"/>
       <c r="F120" s="7"/>
@@ -4290,17 +4295,17 @@
         <v>132</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D121" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E121" s="6"/>
-      <c r="F121" s="6"/>
-      <c r="G121" s="6"/>
-      <c r="H121" s="6"/>
-      <c r="I121" s="6"/>
-      <c r="J121" s="6"/>
+        <v>10000.0</v>
+      </c>
+      <c r="E121" s="7"/>
+      <c r="F121" s="7"/>
+      <c r="G121" s="7"/>
+      <c r="H121" s="7"/>
+      <c r="I121" s="7"/>
+      <c r="J121" s="7"/>
     </row>
     <row r="122">
       <c r="A122" s="4">
@@ -4311,17 +4316,17 @@
         <v>133</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D122" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E122" s="6"/>
-      <c r="F122" s="6"/>
-      <c r="G122" s="6"/>
-      <c r="H122" s="6"/>
-      <c r="I122" s="6"/>
-      <c r="J122" s="6"/>
+        <v>500.0</v>
+      </c>
+      <c r="E122" s="7"/>
+      <c r="F122" s="7"/>
+      <c r="G122" s="7"/>
+      <c r="H122" s="7"/>
+      <c r="I122" s="7"/>
+      <c r="J122" s="7"/>
     </row>
     <row r="123">
       <c r="A123" s="4">
@@ -4332,10 +4337,10 @@
         <v>134</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D123" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
@@ -4353,10 +4358,10 @@
         <v>135</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D124" s="4">
-        <v>22000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
@@ -4374,10 +4379,10 @@
         <v>136</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D125" s="4">
-        <v>10000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
@@ -4395,10 +4400,10 @@
         <v>137</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D126" s="4">
-        <v>500.0</v>
+        <v>22000.0</v>
       </c>
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
@@ -4416,10 +4421,10 @@
         <v>138</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D127" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
@@ -4437,10 +4442,10 @@
         <v>139</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D128" s="4">
-        <v>10000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
@@ -4458,10 +4463,10 @@
         <v>140</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D129" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
@@ -4479,10 +4484,10 @@
         <v>141</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D130" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
@@ -4500,10 +4505,10 @@
         <v>142</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D131" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
@@ -4521,17 +4526,13 @@
         <v>143</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D132" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E132" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F132" s="4">
-        <v>1000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E132" s="6"/>
+      <c r="F132" s="6"/>
       <c r="G132" s="6"/>
       <c r="H132" s="6"/>
       <c r="I132" s="6"/>
@@ -4546,10 +4547,10 @@
         <v>144</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D133" s="4">
-        <v>6500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
@@ -4567,13 +4568,17 @@
         <v>145</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D134" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="E134" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F134" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E134" s="6"/>
-      <c r="F134" s="6"/>
       <c r="G134" s="6"/>
       <c r="H134" s="6"/>
       <c r="I134" s="6"/>
@@ -4588,10 +4593,10 @@
         <v>146</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D135" s="4">
-        <v>10000.0</v>
+        <v>6500.0</v>
       </c>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
@@ -4609,17 +4614,13 @@
         <v>147</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D136" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E136" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F136" s="4">
-        <v>13000.0</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E136" s="6"/>
+      <c r="F136" s="6"/>
       <c r="G136" s="6"/>
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
@@ -4634,10 +4635,10 @@
         <v>148</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D137" s="4">
-        <v>23000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
@@ -4655,17 +4656,21 @@
         <v>149</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D138" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E138" s="7"/>
-      <c r="F138" s="7"/>
-      <c r="G138" s="7"/>
-      <c r="H138" s="7"/>
-      <c r="I138" s="7"/>
-      <c r="J138" s="7"/>
+      <c r="E138" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F138" s="4">
+        <v>13000.0</v>
+      </c>
+      <c r="G138" s="6"/>
+      <c r="H138" s="6"/>
+      <c r="I138" s="6"/>
+      <c r="J138" s="6"/>
     </row>
     <row r="139">
       <c r="A139" s="4">
@@ -4676,10 +4681,10 @@
         <v>150</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D139" s="4">
-        <v>26000.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
@@ -4697,17 +4702,17 @@
         <v>151</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D140" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E140" s="6"/>
-      <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6"/>
-      <c r="J140" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E140" s="7"/>
+      <c r="F140" s="7"/>
+      <c r="G140" s="7"/>
+      <c r="H140" s="7"/>
+      <c r="I140" s="7"/>
+      <c r="J140" s="7"/>
     </row>
     <row r="141">
       <c r="A141" s="4">
@@ -4718,10 +4723,10 @@
         <v>152</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D141" s="4">
-        <v>21000.0</v>
+        <v>26000.0</v>
       </c>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
@@ -4739,10 +4744,10 @@
         <v>153</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D142" s="4">
-        <v>2000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E142" s="6"/>
       <c r="F142" s="6"/>
@@ -4760,10 +4765,10 @@
         <v>154</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D143" s="4">
-        <v>36500.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
@@ -4781,10 +4786,10 @@
         <v>155</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D144" s="4">
-        <v>13000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
@@ -4802,10 +4807,10 @@
         <v>156</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D145" s="4">
-        <v>500.0</v>
+        <v>36500.0</v>
       </c>
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
@@ -4823,10 +4828,10 @@
         <v>157</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D146" s="4">
-        <v>13500.0</v>
+        <v>13000.0</v>
       </c>
       <c r="E146" s="6"/>
       <c r="F146" s="6"/>
@@ -4844,10 +4849,10 @@
         <v>158</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D147" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E147" s="6"/>
       <c r="F147" s="6"/>
@@ -4865,10 +4870,10 @@
         <v>159</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D148" s="4">
-        <v>160000.0</v>
+        <v>13500.0</v>
       </c>
       <c r="E148" s="6"/>
       <c r="F148" s="6"/>
@@ -4886,17 +4891,13 @@
         <v>160</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D149" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E149" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F149" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E149" s="6"/>
+      <c r="F149" s="6"/>
       <c r="G149" s="6"/>
       <c r="H149" s="6"/>
       <c r="I149" s="6"/>
@@ -4911,17 +4912,17 @@
         <v>161</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D150" s="4">
-        <v>65000.0</v>
-      </c>
-      <c r="E150" s="7"/>
-      <c r="F150" s="7"/>
-      <c r="G150" s="7"/>
-      <c r="H150" s="7"/>
-      <c r="I150" s="7"/>
-      <c r="J150" s="7"/>
+        <v>160000.0</v>
+      </c>
+      <c r="E150" s="6"/>
+      <c r="F150" s="6"/>
+      <c r="G150" s="6"/>
+      <c r="H150" s="6"/>
+      <c r="I150" s="6"/>
+      <c r="J150" s="6"/>
     </row>
     <row r="151">
       <c r="A151" s="4">
@@ -4932,17 +4933,21 @@
         <v>162</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D151" s="4">
-        <v>4500.0</v>
-      </c>
-      <c r="E151" s="7"/>
-      <c r="F151" s="7"/>
-      <c r="G151" s="7"/>
-      <c r="H151" s="7"/>
-      <c r="I151" s="7"/>
-      <c r="J151" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E151" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F151" s="4">
+        <v>9000.0</v>
+      </c>
+      <c r="G151" s="6"/>
+      <c r="H151" s="6"/>
+      <c r="I151" s="6"/>
+      <c r="J151" s="6"/>
     </row>
     <row r="152">
       <c r="A152" s="4">
@@ -4953,17 +4958,17 @@
         <v>163</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D152" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E152" s="6"/>
-      <c r="F152" s="6"/>
-      <c r="G152" s="6"/>
-      <c r="H152" s="6"/>
-      <c r="I152" s="6"/>
-      <c r="J152" s="6"/>
+        <v>65000.0</v>
+      </c>
+      <c r="E152" s="7"/>
+      <c r="F152" s="7"/>
+      <c r="G152" s="7"/>
+      <c r="H152" s="7"/>
+      <c r="I152" s="7"/>
+      <c r="J152" s="7"/>
     </row>
     <row r="153">
       <c r="A153" s="4">
@@ -4974,17 +4979,17 @@
         <v>164</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D153" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E153" s="6"/>
-      <c r="F153" s="6"/>
-      <c r="G153" s="6"/>
-      <c r="H153" s="6"/>
-      <c r="I153" s="6"/>
-      <c r="J153" s="6"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
+      <c r="G153" s="7"/>
+      <c r="H153" s="7"/>
+      <c r="I153" s="7"/>
+      <c r="J153" s="7"/>
     </row>
     <row r="154">
       <c r="A154" s="4">
@@ -4995,7 +5000,7 @@
         <v>165</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D154" s="4">
         <v>2000.0</v>
@@ -5016,7 +5021,7 @@
         <v>166</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D155" s="4">
         <v>17000.0</v>
@@ -5037,7 +5042,7 @@
         <v>167</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D156" s="4">
         <v>2000.0</v>
@@ -5058,7 +5063,7 @@
         <v>168</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D157" s="4">
         <v>17000.0</v>
@@ -5079,7 +5084,7 @@
         <v>169</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D158" s="4">
         <v>2000.0</v>
@@ -5100,7 +5105,7 @@
         <v>170</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D159" s="4">
         <v>17000.0</v>
@@ -5121,7 +5126,7 @@
         <v>171</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D160" s="4">
         <v>2000.0</v>
@@ -5142,7 +5147,7 @@
         <v>172</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D161" s="4">
         <v>17000.0</v>
@@ -5163,10 +5168,10 @@
         <v>173</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D162" s="4">
-        <v>5000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E162" s="6"/>
       <c r="F162" s="6"/>
@@ -5184,10 +5189,10 @@
         <v>174</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D163" s="4">
-        <v>10000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E163" s="6"/>
       <c r="F163" s="6"/>
@@ -5205,10 +5210,10 @@
         <v>175</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D164" s="4">
-        <v>18000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E164" s="6"/>
       <c r="F164" s="6"/>
@@ -5226,10 +5231,10 @@
         <v>176</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D165" s="4">
-        <v>4500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E165" s="6"/>
       <c r="F165" s="6"/>
@@ -5247,10 +5252,10 @@
         <v>177</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D166" s="4">
-        <v>9000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E166" s="6"/>
       <c r="F166" s="6"/>
@@ -5268,17 +5273,17 @@
         <v>178</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D167" s="4">
-        <v>18000.0</v>
-      </c>
-      <c r="E167" s="4"/>
-      <c r="F167" s="4"/>
-      <c r="G167" s="7"/>
-      <c r="H167" s="7"/>
-      <c r="I167" s="7"/>
-      <c r="J167" s="7"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E167" s="6"/>
+      <c r="F167" s="6"/>
+      <c r="G167" s="6"/>
+      <c r="H167" s="6"/>
+      <c r="I167" s="6"/>
+      <c r="J167" s="6"/>
     </row>
     <row r="168">
       <c r="A168" s="4">
@@ -5289,21 +5294,17 @@
         <v>179</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D168" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E168" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F168" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="G168" s="7"/>
-      <c r="H168" s="7"/>
-      <c r="I168" s="7"/>
-      <c r="J168" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E168" s="6"/>
+      <c r="F168" s="6"/>
+      <c r="G168" s="6"/>
+      <c r="H168" s="6"/>
+      <c r="I168" s="6"/>
+      <c r="J168" s="6"/>
     </row>
     <row r="169">
       <c r="A169" s="4">
@@ -5314,17 +5315,13 @@
         <v>180</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D169" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E169" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F169" s="4">
-        <v>12000.0</v>
-      </c>
+        <v>18000.0</v>
+      </c>
+      <c r="E169" s="4"/>
+      <c r="F169" s="4"/>
       <c r="G169" s="7"/>
       <c r="H169" s="7"/>
       <c r="I169" s="7"/>
@@ -5339,16 +5336,16 @@
         <v>181</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D170" s="4">
-        <v>2500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E170" s="4">
         <v>4.0</v>
       </c>
       <c r="F170" s="4">
-        <v>8500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="G170" s="7"/>
       <c r="H170" s="7"/>
@@ -5364,13 +5361,13 @@
         <v>182</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D171" s="4">
-        <v>26000.0</v>
-      </c>
-      <c r="E171" s="7"/>
-      <c r="F171" s="7"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E171" s="4"/>
+      <c r="F171" s="4"/>
       <c r="G171" s="7"/>
       <c r="H171" s="7"/>
       <c r="I171" s="7"/>
@@ -5385,16 +5382,16 @@
         <v>183</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D172" s="4">
-        <v>4000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E172" s="4">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F172" s="4">
-        <v>17500.0</v>
+        <v>8500.0</v>
       </c>
       <c r="G172" s="7"/>
       <c r="H172" s="7"/>
@@ -5410,10 +5407,10 @@
         <v>184</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D173" s="4">
-        <v>175000.0</v>
+        <v>26000.0</v>
       </c>
       <c r="E173" s="7"/>
       <c r="F173" s="7"/>
@@ -5431,13 +5428,17 @@
         <v>185</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D174" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E174" s="7"/>
-      <c r="F174" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E174" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F174" s="4">
+        <v>17500.0</v>
+      </c>
       <c r="G174" s="7"/>
       <c r="H174" s="7"/>
       <c r="I174" s="7"/>
@@ -5452,17 +5453,13 @@
         <v>186</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D175" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="E175" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F175" s="4">
-        <v>22000.0</v>
-      </c>
+        <v>175000.0</v>
+      </c>
+      <c r="E175" s="7"/>
+      <c r="F175" s="7"/>
       <c r="G175" s="7"/>
       <c r="H175" s="7"/>
       <c r="I175" s="7"/>
@@ -5477,7 +5474,7 @@
         <v>187</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D176" s="4">
         <v>21000.0</v>
@@ -5498,13 +5495,17 @@
         <v>188</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D177" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E177" s="7"/>
-      <c r="F177" s="7"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E177" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F177" s="4">
+        <v>22000.0</v>
+      </c>
       <c r="G177" s="7"/>
       <c r="H177" s="7"/>
       <c r="I177" s="7"/>
@@ -5519,10 +5520,10 @@
         <v>189</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D178" s="4">
-        <v>245000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E178" s="7"/>
       <c r="F178" s="7"/>
@@ -5540,10 +5541,10 @@
         <v>190</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D179" s="4">
-        <v>42000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E179" s="7"/>
       <c r="F179" s="7"/>
@@ -5561,10 +5562,10 @@
         <v>191</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D180" s="4">
-        <v>44000.0</v>
+        <v>245000.0</v>
       </c>
       <c r="E180" s="7"/>
       <c r="F180" s="7"/>
@@ -5582,10 +5583,10 @@
         <v>192</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D181" s="4">
-        <v>255000.0</v>
+        <v>42000.0</v>
       </c>
       <c r="E181" s="7"/>
       <c r="F181" s="7"/>
@@ -5603,10 +5604,10 @@
         <v>193</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D182" s="4">
-        <v>21000.0</v>
+        <v>44000.0</v>
       </c>
       <c r="E182" s="7"/>
       <c r="F182" s="7"/>
@@ -5624,10 +5625,10 @@
         <v>194</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D183" s="4">
-        <v>42000.0</v>
+        <v>255000.0</v>
       </c>
       <c r="E183" s="7"/>
       <c r="F183" s="7"/>
@@ -5645,17 +5646,17 @@
         <v>195</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D184" s="4">
-        <v>14500.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
-      <c r="G184" s="4"/>
-      <c r="H184" s="4"/>
-      <c r="I184" s="4"/>
-      <c r="J184" s="4"/>
+      <c r="G184" s="7"/>
+      <c r="H184" s="7"/>
+      <c r="I184" s="7"/>
+      <c r="J184" s="7"/>
     </row>
     <row r="185">
       <c r="A185" s="4">
@@ -5666,25 +5667,17 @@
         <v>196</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="D185" s="4">
-        <v>2000.0</v>
+        <v>42000.0</v>
       </c>
       <c r="E185" s="7"/>
       <c r="F185" s="7"/>
-      <c r="G185" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H185" s="4">
-        <v>5500.0</v>
-      </c>
-      <c r="I185" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J185" s="4">
-        <v>10000.0</v>
-      </c>
+      <c r="G185" s="7"/>
+      <c r="H185" s="7"/>
+      <c r="I185" s="7"/>
+      <c r="J185" s="7"/>
     </row>
     <row r="186">
       <c r="A186" s="4">
@@ -5692,20 +5685,20 @@
         <v>185</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="D186" s="4">
-        <v>10000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
-      <c r="G186" s="7"/>
-      <c r="H186" s="7"/>
-      <c r="I186" s="7"/>
-      <c r="J186" s="7"/>
+      <c r="G186" s="4"/>
+      <c r="H186" s="4"/>
+      <c r="I186" s="4"/>
+      <c r="J186" s="4"/>
     </row>
     <row r="187">
       <c r="A187" s="4">
@@ -5713,10 +5706,10 @@
         <v>186</v>
       </c>
       <c r="B187" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C187" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>197</v>
       </c>
       <c r="D187" s="4">
         <v>2000.0</v>
@@ -5745,7 +5738,7 @@
         <v>200</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D188" s="4">
         <v>10000.0</v>
@@ -5766,7 +5759,7 @@
         <v>201</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D189" s="4">
         <v>2000.0</v>
@@ -5795,7 +5788,7 @@
         <v>202</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D190" s="4">
         <v>10000.0</v>
@@ -5816,7 +5809,7 @@
         <v>203</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D191" s="4">
         <v>2000.0</v>
@@ -5827,13 +5820,13 @@
         <v>6.0</v>
       </c>
       <c r="H191" s="4">
-        <v>6000.0</v>
+        <v>5500.0</v>
       </c>
       <c r="I191" s="4">
         <v>12.0</v>
       </c>
       <c r="J191" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
     </row>
     <row r="192">
@@ -5845,10 +5838,10 @@
         <v>204</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D192" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E192" s="7"/>
       <c r="F192" s="7"/>
@@ -5866,7 +5859,7 @@
         <v>205</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D193" s="4">
         <v>2000.0</v>
@@ -5895,7 +5888,7 @@
         <v>206</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D194" s="4">
         <v>11000.0</v>
@@ -5916,7 +5909,7 @@
         <v>207</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D195" s="4">
         <v>2000.0</v>
@@ -5927,13 +5920,13 @@
         <v>6.0</v>
       </c>
       <c r="H195" s="4">
-        <v>8000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="I195" s="4">
         <v>12.0</v>
       </c>
       <c r="J195" s="4">
-        <v>15000.0</v>
+        <v>11000.0</v>
       </c>
     </row>
     <row r="196">
@@ -5945,10 +5938,10 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D196" s="4">
-        <v>15000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="E196" s="7"/>
       <c r="F196" s="7"/>
@@ -5966,17 +5959,25 @@
         <v>209</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D197" s="4">
-        <v>15000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E197" s="7"/>
       <c r="F197" s="7"/>
-      <c r="G197" s="7"/>
-      <c r="H197" s="7"/>
-      <c r="I197" s="7"/>
-      <c r="J197" s="7"/>
+      <c r="G197" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H197" s="4">
+        <v>8000.0</v>
+      </c>
+      <c r="I197" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J197" s="4">
+        <v>15000.0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="4">
@@ -5987,29 +5988,17 @@
         <v>210</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D198" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E198" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F198" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="G198" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H198" s="4">
-        <v>8500.0</v>
-      </c>
-      <c r="I198" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J198" s="4">
-        <v>16000.0</v>
-      </c>
+        <v>15000.0</v>
+      </c>
+      <c r="E198" s="7"/>
+      <c r="F198" s="7"/>
+      <c r="G198" s="7"/>
+      <c r="H198" s="7"/>
+      <c r="I198" s="7"/>
+      <c r="J198" s="7"/>
     </row>
     <row r="199">
       <c r="A199" s="4">
@@ -6020,10 +6009,10 @@
         <v>211</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D199" s="4">
-        <v>16000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E199" s="7"/>
       <c r="F199" s="7"/>
@@ -6041,24 +6030,28 @@
         <v>212</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D200" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E200" s="7"/>
-      <c r="F200" s="7"/>
+      <c r="E200" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F200" s="4">
+        <v>5000.0</v>
+      </c>
       <c r="G200" s="4">
         <v>6.0</v>
       </c>
       <c r="H200" s="4">
-        <v>9000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="I200" s="4">
         <v>12.0</v>
       </c>
       <c r="J200" s="4">
-        <v>17000.0</v>
+        <v>16000.0</v>
       </c>
     </row>
     <row r="201">
@@ -6070,10 +6063,10 @@
         <v>213</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D201" s="4">
-        <v>17000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E201" s="7"/>
       <c r="F201" s="7"/>
@@ -6091,7 +6084,7 @@
         <v>214</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D202" s="4">
         <v>2000.0</v>
@@ -6120,7 +6113,7 @@
         <v>215</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D203" s="4">
         <v>17000.0</v>
@@ -6141,28 +6134,24 @@
         <v>216</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D204" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E204" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F204" s="4">
-        <v>5000.0</v>
-      </c>
+      <c r="E204" s="7"/>
+      <c r="F204" s="7"/>
       <c r="G204" s="4">
         <v>6.0</v>
       </c>
       <c r="H204" s="4">
-        <v>9500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="I204" s="4">
         <v>12.0</v>
       </c>
       <c r="J204" s="4">
-        <v>18000.0</v>
+        <v>17000.0</v>
       </c>
     </row>
     <row r="205">
@@ -6174,10 +6163,10 @@
         <v>217</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D205" s="4">
-        <v>18000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E205" s="7"/>
       <c r="F205" s="7"/>
@@ -6195,24 +6184,28 @@
         <v>218</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D206" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E206" s="7"/>
-      <c r="F206" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E206" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F206" s="4">
+        <v>5000.0</v>
+      </c>
       <c r="G206" s="4">
         <v>6.0</v>
       </c>
       <c r="H206" s="4">
-        <v>14500.0</v>
+        <v>9500.0</v>
       </c>
       <c r="I206" s="4">
         <v>12.0</v>
       </c>
       <c r="J206" s="4">
-        <v>28000.0</v>
+        <v>18000.0</v>
       </c>
     </row>
     <row r="207">
@@ -6224,10 +6217,10 @@
         <v>219</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D207" s="4">
-        <v>28000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E207" s="7"/>
       <c r="F207" s="7"/>
@@ -6245,7 +6238,7 @@
         <v>220</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D208" s="4">
         <v>2500.0</v>
@@ -6256,13 +6249,13 @@
         <v>6.0</v>
       </c>
       <c r="H208" s="4">
-        <v>10500.0</v>
+        <v>14500.0</v>
       </c>
       <c r="I208" s="4">
         <v>12.0</v>
       </c>
       <c r="J208" s="4">
-        <v>20000.0</v>
+        <v>28000.0</v>
       </c>
     </row>
     <row r="209">
@@ -6274,10 +6267,10 @@
         <v>221</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D209" s="4">
-        <v>20000.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E209" s="7"/>
       <c r="F209" s="7"/>
@@ -6295,7 +6288,7 @@
         <v>222</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D210" s="4">
         <v>2500.0</v>
@@ -6306,13 +6299,13 @@
         <v>6.0</v>
       </c>
       <c r="H210" s="4">
-        <v>13000.0</v>
+        <v>10500.0</v>
       </c>
       <c r="I210" s="4">
         <v>12.0</v>
       </c>
       <c r="J210" s="4">
-        <v>25000.0</v>
+        <v>20000.0</v>
       </c>
     </row>
     <row r="211">
@@ -6324,10 +6317,10 @@
         <v>223</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D211" s="4">
-        <v>25000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="E211" s="7"/>
       <c r="F211" s="7"/>
@@ -6345,7 +6338,7 @@
         <v>224</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D212" s="4">
         <v>2500.0</v>
@@ -6356,13 +6349,13 @@
         <v>6.0</v>
       </c>
       <c r="H212" s="4">
-        <v>11000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I212" s="4">
         <v>12.0</v>
       </c>
       <c r="J212" s="4">
-        <v>21000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="213">
@@ -6374,10 +6367,10 @@
         <v>225</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D213" s="4">
-        <v>21000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E213" s="7"/>
       <c r="F213" s="7"/>
@@ -6395,7 +6388,7 @@
         <v>226</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D214" s="4">
         <v>2500.0</v>
@@ -6406,13 +6399,13 @@
         <v>6.0</v>
       </c>
       <c r="H214" s="4">
-        <v>13000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="I214" s="4">
         <v>12.0</v>
       </c>
       <c r="J214" s="4">
-        <v>25000.0</v>
+        <v>21000.0</v>
       </c>
     </row>
     <row r="215">
@@ -6424,10 +6417,10 @@
         <v>227</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D215" s="4">
-        <v>25000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E215" s="7"/>
       <c r="F215" s="7"/>
@@ -6445,7 +6438,7 @@
         <v>228</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D216" s="4">
         <v>2500.0</v>
@@ -6456,13 +6449,13 @@
         <v>6.0</v>
       </c>
       <c r="H216" s="4">
-        <v>14000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I216" s="4">
         <v>12.0</v>
       </c>
       <c r="J216" s="4">
-        <v>28000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="217">
@@ -6474,10 +6467,10 @@
         <v>229</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D217" s="4">
-        <v>28000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E217" s="7"/>
       <c r="F217" s="7"/>
@@ -6495,7 +6488,7 @@
         <v>230</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D218" s="4">
         <v>2500.0</v>
@@ -6506,13 +6499,13 @@
         <v>6.0</v>
       </c>
       <c r="H218" s="4">
-        <v>13000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="I218" s="4">
         <v>12.0</v>
       </c>
       <c r="J218" s="4">
-        <v>25000.0</v>
+        <v>28000.0</v>
       </c>
     </row>
     <row r="219">
@@ -6524,10 +6517,10 @@
         <v>231</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D219" s="4">
-        <v>25000.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E219" s="7"/>
       <c r="F219" s="7"/>
@@ -6545,7 +6538,7 @@
         <v>232</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D220" s="4">
         <v>2500.0</v>
@@ -6556,13 +6549,13 @@
         <v>6.0</v>
       </c>
       <c r="H220" s="4">
-        <v>14000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I220" s="4">
         <v>12.0</v>
       </c>
       <c r="J220" s="4">
-        <v>27000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="221">
@@ -6574,10 +6567,10 @@
         <v>233</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D221" s="4">
-        <v>27000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E221" s="7"/>
       <c r="F221" s="7"/>
@@ -6595,7 +6588,7 @@
         <v>234</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D222" s="4">
         <v>2500.0</v>
@@ -6624,7 +6617,7 @@
         <v>235</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D223" s="4">
         <v>27000.0</v>
@@ -6645,17 +6638,25 @@
         <v>236</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D224" s="4">
-        <v>34000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E224" s="7"/>
       <c r="F224" s="7"/>
-      <c r="G224" s="7"/>
-      <c r="H224" s="7"/>
-      <c r="I224" s="7"/>
-      <c r="J224" s="7"/>
+      <c r="G224" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H224" s="4">
+        <v>14000.0</v>
+      </c>
+      <c r="I224" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J224" s="4">
+        <v>27000.0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="4">
@@ -6666,7 +6667,7 @@
         <v>237</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D225" s="4">
         <v>27000.0</v>
@@ -6687,19 +6688,17 @@
         <v>238</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D226" s="4">
-        <v>37000.0</v>
+        <v>34000.0</v>
       </c>
       <c r="E226" s="7"/>
       <c r="F226" s="7"/>
-      <c r="G226" s="4"/>
-      <c r="H226" s="4"/>
-      <c r="I226" s="4"/>
-      <c r="J226" s="4">
-        <v>37000.0</v>
-      </c>
+      <c r="G226" s="7"/>
+      <c r="H226" s="7"/>
+      <c r="I226" s="7"/>
+      <c r="J226" s="7"/>
     </row>
     <row r="227">
       <c r="A227" s="4">
@@ -6710,10 +6709,10 @@
         <v>239</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D227" s="4">
-        <v>16000.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E227" s="7"/>
       <c r="F227" s="7"/>
@@ -6731,17 +6730,19 @@
         <v>240</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D228" s="4">
-        <v>43000.0</v>
+        <v>37000.0</v>
       </c>
       <c r="E228" s="7"/>
       <c r="F228" s="7"/>
-      <c r="G228" s="7"/>
-      <c r="H228" s="7"/>
-      <c r="I228" s="7"/>
-      <c r="J228" s="7"/>
+      <c r="G228" s="4"/>
+      <c r="H228" s="4"/>
+      <c r="I228" s="4"/>
+      <c r="J228" s="4">
+        <v>37000.0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="4">
@@ -6752,10 +6753,10 @@
         <v>241</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D229" s="4">
-        <v>23000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E229" s="7"/>
       <c r="F229" s="7"/>
@@ -6773,10 +6774,10 @@
         <v>242</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D230" s="4">
-        <v>17000.0</v>
+        <v>43000.0</v>
       </c>
       <c r="E230" s="7"/>
       <c r="F230" s="7"/>
@@ -6794,10 +6795,10 @@
         <v>243</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D231" s="4">
-        <v>29000.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E231" s="7"/>
       <c r="F231" s="7"/>
@@ -6815,10 +6816,10 @@
         <v>244</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D232" s="4">
-        <v>13000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E232" s="7"/>
       <c r="F232" s="7"/>
@@ -6836,10 +6837,10 @@
         <v>245</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
       <c r="D233" s="4">
-        <v>500.0</v>
+        <v>29000.0</v>
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="7"/>
@@ -6854,13 +6855,13 @@
         <v>233</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
       <c r="D234" s="4">
-        <v>4000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="E234" s="7"/>
       <c r="F234" s="7"/>
@@ -6875,13 +6876,13 @@
         <v>234</v>
       </c>
       <c r="B235" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C235" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="C235" s="5" t="s">
-        <v>246</v>
-      </c>
       <c r="D235" s="4">
-        <v>2500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E235" s="7"/>
       <c r="F235" s="7"/>
@@ -6899,17 +6900,13 @@
         <v>249</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D236" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E236" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F236" s="4">
-        <v>14000.0</v>
-      </c>
+        <v>4000.0</v>
+      </c>
+      <c r="E236" s="7"/>
+      <c r="F236" s="7"/>
       <c r="G236" s="7"/>
       <c r="H236" s="7"/>
       <c r="I236" s="7"/>
@@ -6921,13 +6918,13 @@
         <v>236</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D237" s="4">
-        <v>109000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="7"/>
@@ -6942,10 +6939,10 @@
         <v>237</v>
       </c>
       <c r="B238" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C238" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="C238" s="5" t="s">
-        <v>250</v>
       </c>
       <c r="D238" s="4">
         <v>3000.0</v>
@@ -6970,7 +6967,7 @@
         <v>253</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D239" s="4">
         <v>109000.0</v>
@@ -6991,13 +6988,17 @@
         <v>254</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D240" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E240" s="7"/>
-      <c r="F240" s="7"/>
+      <c r="E240" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F240" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G240" s="7"/>
       <c r="H240" s="7"/>
       <c r="I240" s="7"/>
@@ -7012,10 +7013,10 @@
         <v>255</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D241" s="4">
-        <v>114000.0</v>
+        <v>109000.0</v>
       </c>
       <c r="E241" s="7"/>
       <c r="F241" s="7"/>
@@ -7033,7 +7034,7 @@
         <v>256</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D242" s="4">
         <v>3000.0</v>
@@ -7054,17 +7055,13 @@
         <v>257</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D243" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E243" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F243" s="4">
-        <v>39000.0</v>
-      </c>
+        <v>114000.0</v>
+      </c>
+      <c r="E243" s="7"/>
+      <c r="F243" s="7"/>
       <c r="G243" s="7"/>
       <c r="H243" s="7"/>
       <c r="I243" s="7"/>
@@ -7079,10 +7076,10 @@
         <v>258</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D244" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E244" s="7"/>
       <c r="F244" s="7"/>
@@ -7100,13 +7097,17 @@
         <v>259</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D245" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E245" s="7"/>
-      <c r="F245" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E245" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F245" s="4">
+        <v>39000.0</v>
+      </c>
       <c r="G245" s="7"/>
       <c r="H245" s="7"/>
       <c r="I245" s="7"/>
@@ -7121,7 +7122,7 @@
         <v>260</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D246" s="4">
         <v>114000.0</v>
@@ -7142,7 +7143,7 @@
         <v>261</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D247" s="4">
         <v>3000.0</v>
@@ -7163,7 +7164,7 @@
         <v>262</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D248" s="4">
         <v>114000.0</v>
@@ -7184,7 +7185,7 @@
         <v>263</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D249" s="4">
         <v>3000.0</v>
@@ -7205,7 +7206,7 @@
         <v>264</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D250" s="4">
         <v>114000.0</v>
@@ -7226,7 +7227,7 @@
         <v>265</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D251" s="4">
         <v>3000.0</v>
@@ -7247,10 +7248,10 @@
         <v>266</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D252" s="4">
-        <v>107000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E252" s="7"/>
       <c r="F252" s="7"/>
@@ -7268,7 +7269,7 @@
         <v>267</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D253" s="4">
         <v>3000.0</v>
@@ -7289,17 +7290,17 @@
         <v>268</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D254" s="4">
-        <v>112000.0</v>
-      </c>
-      <c r="E254" s="6"/>
-      <c r="F254" s="6"/>
-      <c r="G254" s="6"/>
-      <c r="H254" s="6"/>
-      <c r="I254" s="6"/>
-      <c r="J254" s="6"/>
+        <v>107000.0</v>
+      </c>
+      <c r="E254" s="7"/>
+      <c r="F254" s="7"/>
+      <c r="G254" s="7"/>
+      <c r="H254" s="7"/>
+      <c r="I254" s="7"/>
+      <c r="J254" s="7"/>
     </row>
     <row r="255">
       <c r="A255" s="4">
@@ -7310,17 +7311,13 @@
         <v>269</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D255" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E255" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F255" s="4">
-        <v>19000.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E255" s="7"/>
+      <c r="F255" s="7"/>
       <c r="G255" s="7"/>
       <c r="H255" s="7"/>
       <c r="I255" s="7"/>
@@ -7335,21 +7332,17 @@
         <v>270</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D256" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E256" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F256" s="4">
-        <v>19000.0</v>
-      </c>
-      <c r="G256" s="7"/>
-      <c r="H256" s="7"/>
-      <c r="I256" s="7"/>
-      <c r="J256" s="7"/>
+        <v>112000.0</v>
+      </c>
+      <c r="E256" s="6"/>
+      <c r="F256" s="6"/>
+      <c r="G256" s="6"/>
+      <c r="H256" s="6"/>
+      <c r="I256" s="6"/>
+      <c r="J256" s="6"/>
     </row>
     <row r="257">
       <c r="A257" s="4">
@@ -7360,13 +7353,17 @@
         <v>271</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D257" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E257" s="4"/>
-      <c r="F257" s="4"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E257" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F257" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G257" s="7"/>
       <c r="H257" s="7"/>
       <c r="I257" s="7"/>
@@ -7381,13 +7378,17 @@
         <v>272</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D258" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E258" s="4"/>
-      <c r="F258" s="4"/>
+      <c r="E258" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F258" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G258" s="7"/>
       <c r="H258" s="7"/>
       <c r="I258" s="7"/>
@@ -7402,7 +7403,7 @@
         <v>273</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D259" s="4">
         <v>86000.0</v>
@@ -7423,18 +7424,14 @@
         <v>274</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D260" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E260" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F260" s="4">
-        <v>19500.0</v>
-      </c>
-      <c r="G260" s="4"/>
+      <c r="E260" s="4"/>
+      <c r="F260" s="4"/>
+      <c r="G260" s="7"/>
       <c r="H260" s="7"/>
       <c r="I260" s="7"/>
       <c r="J260" s="7"/>
@@ -7448,17 +7445,13 @@
         <v>275</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D261" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E261" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F261" s="4">
-        <v>6000.0</v>
-      </c>
+        <v>86000.0</v>
+      </c>
+      <c r="E261" s="4"/>
+      <c r="F261" s="4"/>
       <c r="G261" s="7"/>
       <c r="H261" s="7"/>
       <c r="I261" s="7"/>
@@ -7473,14 +7466,18 @@
         <v>276</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D262" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E262" s="7"/>
-      <c r="F262" s="7"/>
-      <c r="G262" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E262" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F262" s="4">
+        <v>19500.0</v>
+      </c>
+      <c r="G262" s="4"/>
       <c r="H262" s="7"/>
       <c r="I262" s="7"/>
       <c r="J262" s="7"/>
@@ -7494,13 +7491,17 @@
         <v>277</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D263" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E263" s="7"/>
-      <c r="F263" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E263" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F263" s="4">
+        <v>6000.0</v>
+      </c>
       <c r="G263" s="7"/>
       <c r="H263" s="7"/>
       <c r="I263" s="7"/>
@@ -7515,10 +7516,10 @@
         <v>278</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D264" s="4">
-        <v>89000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E264" s="7"/>
       <c r="F264" s="7"/>
@@ -7536,10 +7537,10 @@
         <v>279</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D265" s="4">
-        <v>7500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E265" s="7"/>
       <c r="F265" s="7"/>
@@ -7557,10 +7558,10 @@
         <v>280</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D266" s="4">
-        <v>5000.0</v>
+        <v>89000.0</v>
       </c>
       <c r="E266" s="7"/>
       <c r="F266" s="7"/>
@@ -7578,10 +7579,10 @@
         <v>281</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D267" s="4">
-        <v>3000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E267" s="7"/>
       <c r="F267" s="7"/>
@@ -7599,17 +7600,17 @@
         <v>282</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>283</v>
+        <v>252</v>
       </c>
       <c r="D268" s="4">
-        <v>80000.0</v>
-      </c>
-      <c r="E268" s="6"/>
-      <c r="F268" s="6"/>
-      <c r="G268" s="6"/>
-      <c r="H268" s="6"/>
-      <c r="I268" s="6"/>
-      <c r="J268" s="6"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E268" s="7"/>
+      <c r="F268" s="7"/>
+      <c r="G268" s="7"/>
+      <c r="H268" s="7"/>
+      <c r="I268" s="7"/>
+      <c r="J268" s="7"/>
     </row>
     <row r="269">
       <c r="A269" s="4">
@@ -7620,10 +7621,10 @@
         <v>283</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>283</v>
+        <v>252</v>
       </c>
       <c r="D269" s="4">
-        <v>14000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E269" s="7"/>
       <c r="F269" s="7"/>
@@ -7638,20 +7639,20 @@
         <v>269</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D270" s="4">
-        <v>14500.0</v>
-      </c>
-      <c r="E270" s="7"/>
-      <c r="F270" s="7"/>
-      <c r="G270" s="7"/>
-      <c r="H270" s="7"/>
-      <c r="I270" s="7"/>
-      <c r="J270" s="7"/>
+        <v>80000.0</v>
+      </c>
+      <c r="E270" s="6"/>
+      <c r="F270" s="6"/>
+      <c r="G270" s="6"/>
+      <c r="H270" s="6"/>
+      <c r="I270" s="6"/>
+      <c r="J270" s="6"/>
     </row>
     <row r="271">
       <c r="A271" s="4">
@@ -7659,13 +7660,13 @@
         <v>270</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D271" s="4">
-        <v>15000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E271" s="7"/>
       <c r="F271" s="7"/>
@@ -7680,13 +7681,13 @@
         <v>271</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D272" s="4">
-        <v>15500.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E272" s="7"/>
       <c r="F272" s="7"/>
@@ -7701,13 +7702,13 @@
         <v>272</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C273" s="5" t="s">
         <v>285</v>
       </c>
       <c r="D273" s="4">
-        <v>1500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E273" s="7"/>
       <c r="F273" s="7"/>
@@ -7722,13 +7723,13 @@
         <v>273</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C274" s="5" t="s">
         <v>285</v>
       </c>
       <c r="D274" s="4">
-        <v>12500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E274" s="7"/>
       <c r="F274" s="7"/>
@@ -7743,13 +7744,13 @@
         <v>274</v>
       </c>
       <c r="B275" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C275" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="C275" s="5" t="s">
-        <v>285</v>
-      </c>
       <c r="D275" s="4">
-        <v>500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E275" s="7"/>
       <c r="F275" s="7"/>
@@ -7767,10 +7768,10 @@
         <v>288</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D276" s="4">
-        <v>4500.0</v>
+        <v>12500.0</v>
       </c>
       <c r="E276" s="7"/>
       <c r="F276" s="7"/>
@@ -7788,10 +7789,10 @@
         <v>289</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D277" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E277" s="7"/>
       <c r="F277" s="7"/>
@@ -7809,10 +7810,10 @@
         <v>290</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D278" s="4">
-        <v>23000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E278" s="7"/>
       <c r="F278" s="7"/>
@@ -7830,17 +7831,13 @@
         <v>291</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D279" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E279" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F279" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E279" s="7"/>
+      <c r="F279" s="7"/>
       <c r="G279" s="7"/>
       <c r="H279" s="7"/>
       <c r="I279" s="7"/>
@@ -7855,13 +7852,13 @@
         <v>292</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D280" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E280" s="4"/>
-      <c r="F280" s="4"/>
+        <v>23000.0</v>
+      </c>
+      <c r="E280" s="7"/>
+      <c r="F280" s="7"/>
       <c r="G280" s="7"/>
       <c r="H280" s="7"/>
       <c r="I280" s="7"/>
@@ -7876,16 +7873,16 @@
         <v>293</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D281" s="4">
-        <v>2500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E281" s="4">
         <v>5.0</v>
       </c>
       <c r="F281" s="4">
-        <v>9000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="G281" s="7"/>
       <c r="H281" s="7"/>
@@ -7901,10 +7898,10 @@
         <v>294</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D282" s="4">
-        <v>9000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E282" s="4"/>
       <c r="F282" s="4"/>
@@ -7922,16 +7919,16 @@
         <v>295</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D283" s="4">
-        <v>2000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E283" s="4">
         <v>5.0</v>
       </c>
       <c r="F283" s="4">
-        <v>7500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="G283" s="7"/>
       <c r="H283" s="7"/>
@@ -7947,13 +7944,13 @@
         <v>296</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D284" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E284" s="7"/>
-      <c r="F284" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E284" s="4"/>
+      <c r="F284" s="4"/>
       <c r="G284" s="7"/>
       <c r="H284" s="7"/>
       <c r="I284" s="7"/>
@@ -7968,13 +7965,17 @@
         <v>297</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="D285" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E285" s="7"/>
-      <c r="F285" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E285" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F285" s="4">
+        <v>7500.0</v>
+      </c>
       <c r="G285" s="7"/>
       <c r="H285" s="7"/>
       <c r="I285" s="7"/>
@@ -7986,13 +7987,13 @@
         <v>285</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="D286" s="4">
-        <v>10000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E286" s="7"/>
       <c r="F286" s="7"/>
@@ -8007,13 +8008,13 @@
         <v>286</v>
       </c>
       <c r="B287" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C287" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="C287" s="5" t="s">
-        <v>298</v>
-      </c>
       <c r="D287" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E287" s="7"/>
       <c r="F287" s="7"/>
@@ -8031,10 +8032,10 @@
         <v>301</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D288" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E288" s="7"/>
       <c r="F288" s="7"/>
@@ -8052,10 +8053,10 @@
         <v>302</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D289" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E289" s="7"/>
       <c r="F289" s="7"/>
@@ -8073,10 +8074,10 @@
         <v>303</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D290" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E290" s="7"/>
       <c r="F290" s="7"/>
@@ -8094,10 +8095,10 @@
         <v>304</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D291" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E291" s="7"/>
       <c r="F291" s="7"/>
@@ -8115,10 +8116,10 @@
         <v>305</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D292" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E292" s="7"/>
       <c r="F292" s="7"/>
@@ -8136,10 +8137,10 @@
         <v>306</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D293" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E293" s="7"/>
       <c r="F293" s="7"/>
@@ -8157,10 +8158,10 @@
         <v>307</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D294" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E294" s="7"/>
       <c r="F294" s="7"/>
@@ -8178,7 +8179,7 @@
         <v>308</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D295" s="4">
         <v>1000.0</v>
@@ -8199,7 +8200,7 @@
         <v>309</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D296" s="4">
         <v>10000.0</v>
@@ -8220,10 +8221,10 @@
         <v>310</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D297" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E297" s="7"/>
       <c r="F297" s="7"/>
@@ -8241,10 +8242,10 @@
         <v>311</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D298" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E298" s="7"/>
       <c r="F298" s="7"/>
@@ -8262,10 +8263,10 @@
         <v>312</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D299" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E299" s="7"/>
       <c r="F299" s="7"/>
@@ -8283,7 +8284,7 @@
         <v>313</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D300" s="4">
         <v>500.0</v>
@@ -8304,7 +8305,7 @@
         <v>314</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D301" s="4">
         <v>5000.0</v>
@@ -8325,10 +8326,10 @@
         <v>315</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D302" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E302" s="7"/>
       <c r="F302" s="7"/>
@@ -8346,10 +8347,10 @@
         <v>316</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D303" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E303" s="7"/>
       <c r="F303" s="7"/>
@@ -8367,10 +8368,10 @@
         <v>317</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D304" s="4">
-        <v>2000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E304" s="7"/>
       <c r="F304" s="7"/>
@@ -8388,10 +8389,10 @@
         <v>318</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D305" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E305" s="7"/>
       <c r="F305" s="7"/>
@@ -8409,10 +8410,10 @@
         <v>319</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D306" s="4">
-        <v>1000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E306" s="7"/>
       <c r="F306" s="7"/>
@@ -8430,7 +8431,7 @@
         <v>320</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D307" s="4">
         <v>5000.0</v>
@@ -8451,7 +8452,7 @@
         <v>321</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D308" s="4">
         <v>1000.0</v>
@@ -8472,7 +8473,7 @@
         <v>322</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D309" s="4">
         <v>5000.0</v>
@@ -8493,7 +8494,7 @@
         <v>323</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D310" s="4">
         <v>1000.0</v>
@@ -8514,7 +8515,7 @@
         <v>324</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D311" s="4">
         <v>5000.0</v>
@@ -8535,10 +8536,10 @@
         <v>325</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D312" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E312" s="7"/>
       <c r="F312" s="7"/>
@@ -8556,10 +8557,10 @@
         <v>326</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D313" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E313" s="7"/>
       <c r="F313" s="7"/>
@@ -8577,10 +8578,10 @@
         <v>327</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D314" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E314" s="7"/>
       <c r="F314" s="7"/>
@@ -8598,10 +8599,10 @@
         <v>328</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D315" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E315" s="7"/>
       <c r="F315" s="7"/>
@@ -8619,10 +8620,10 @@
         <v>329</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D316" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E316" s="7"/>
       <c r="F316" s="7"/>
@@ -8640,7 +8641,7 @@
         <v>330</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D317" s="4">
         <v>5000.0</v>
@@ -8661,7 +8662,7 @@
         <v>331</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D318" s="4">
         <v>500.0</v>
@@ -8682,7 +8683,7 @@
         <v>332</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D319" s="4">
         <v>5000.0</v>
@@ -8703,10 +8704,10 @@
         <v>333</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D320" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E320" s="7"/>
       <c r="F320" s="7"/>
@@ -8724,7 +8725,7 @@
         <v>334</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D321" s="4">
         <v>5000.0</v>
@@ -8745,17 +8746,13 @@
         <v>335</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D322" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E322" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F322" s="4">
-        <v>4500.0</v>
-      </c>
+      <c r="E322" s="7"/>
+      <c r="F322" s="7"/>
       <c r="G322" s="7"/>
       <c r="H322" s="7"/>
       <c r="I322" s="7"/>
@@ -8770,10 +8767,10 @@
         <v>336</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D323" s="4">
-        <v>4500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E323" s="7"/>
       <c r="F323" s="7"/>
@@ -8791,13 +8788,17 @@
         <v>337</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D324" s="4">
-        <v>51000.0</v>
-      </c>
-      <c r="E324" s="4"/>
-      <c r="F324" s="4"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E324" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F324" s="4">
+        <v>4500.0</v>
+      </c>
       <c r="G324" s="7"/>
       <c r="H324" s="7"/>
       <c r="I324" s="7"/>
@@ -8812,17 +8813,13 @@
         <v>338</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D325" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E325" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F325" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>4500.0</v>
+      </c>
+      <c r="E325" s="7"/>
+      <c r="F325" s="7"/>
       <c r="G325" s="7"/>
       <c r="H325" s="7"/>
       <c r="I325" s="7"/>
@@ -8837,13 +8834,13 @@
         <v>339</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D326" s="4">
-        <v>52000.0</v>
-      </c>
-      <c r="E326" s="7"/>
-      <c r="F326" s="7"/>
+        <v>51000.0</v>
+      </c>
+      <c r="E326" s="4"/>
+      <c r="F326" s="4"/>
       <c r="G326" s="7"/>
       <c r="H326" s="7"/>
       <c r="I326" s="7"/>
@@ -8858,13 +8855,17 @@
         <v>340</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D327" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E327" s="7"/>
-      <c r="F327" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E327" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F327" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G327" s="7"/>
       <c r="H327" s="7"/>
       <c r="I327" s="7"/>
@@ -8879,10 +8880,10 @@
         <v>341</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D328" s="4">
-        <v>5000.0</v>
+        <v>52000.0</v>
       </c>
       <c r="E328" s="7"/>
       <c r="F328" s="7"/>
@@ -8900,17 +8901,13 @@
         <v>342</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D329" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E329" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F329" s="4">
-        <v>17000.0</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E329" s="7"/>
+      <c r="F329" s="7"/>
       <c r="G329" s="7"/>
       <c r="H329" s="7"/>
       <c r="I329" s="7"/>
@@ -8925,7 +8922,7 @@
         <v>343</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D330" s="4">
         <v>5000.0</v>
@@ -8946,16 +8943,16 @@
         <v>344</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D331" s="4">
-        <v>7000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E331" s="4">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F331" s="4">
-        <v>32500.0</v>
+        <v>17000.0</v>
       </c>
       <c r="G331" s="7"/>
       <c r="H331" s="7"/>
@@ -8971,10 +8968,10 @@
         <v>345</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D332" s="4">
-        <v>7500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E332" s="7"/>
       <c r="F332" s="7"/>
@@ -8992,13 +8989,17 @@
         <v>346</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D333" s="4">
-        <v>9500.0</v>
-      </c>
-      <c r="E333" s="7"/>
-      <c r="F333" s="7"/>
+        <v>7000.0</v>
+      </c>
+      <c r="E333" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F333" s="4">
+        <v>32500.0</v>
+      </c>
       <c r="G333" s="7"/>
       <c r="H333" s="7"/>
       <c r="I333" s="7"/>
@@ -9013,10 +9014,10 @@
         <v>347</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D334" s="4">
-        <v>3500.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E334" s="7"/>
       <c r="F334" s="7"/>
@@ -9034,10 +9035,10 @@
         <v>348</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D335" s="4">
-        <v>5000.0</v>
+        <v>9500.0</v>
       </c>
       <c r="E335" s="7"/>
       <c r="F335" s="7"/>
@@ -9055,17 +9056,13 @@
         <v>349</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D336" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E336" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F336" s="4">
-        <v>22500.0</v>
-      </c>
+        <v>3500.0</v>
+      </c>
+      <c r="E336" s="7"/>
+      <c r="F336" s="7"/>
       <c r="G336" s="7"/>
       <c r="H336" s="7"/>
       <c r="I336" s="7"/>
@@ -9080,17 +9077,13 @@
         <v>350</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D337" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E337" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F337" s="4">
-        <v>12500.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E337" s="7"/>
+      <c r="F337" s="7"/>
       <c r="G337" s="7"/>
       <c r="H337" s="7"/>
       <c r="I337" s="7"/>
@@ -9105,13 +9098,17 @@
         <v>351</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D338" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E338" s="4"/>
-      <c r="F338" s="4"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E338" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F338" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G338" s="7"/>
       <c r="H338" s="7"/>
       <c r="I338" s="7"/>
@@ -9126,14 +9123,18 @@
         <v>352</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D339" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E339" s="4"/>
-      <c r="F339" s="4"/>
-      <c r="G339" s="4"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E339" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F339" s="4">
+        <v>12500.0</v>
+      </c>
+      <c r="G339" s="7"/>
       <c r="H339" s="7"/>
       <c r="I339" s="7"/>
       <c r="J339" s="7"/>
@@ -9147,17 +9148,13 @@
         <v>353</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D340" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E340" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F340" s="4">
-        <v>11500.0</v>
-      </c>
+        <v>3500.0</v>
+      </c>
+      <c r="E340" s="4"/>
+      <c r="F340" s="4"/>
       <c r="G340" s="7"/>
       <c r="H340" s="7"/>
       <c r="I340" s="7"/>
@@ -9172,14 +9169,14 @@
         <v>354</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D341" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E341" s="7"/>
-      <c r="F341" s="7"/>
-      <c r="G341" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E341" s="4"/>
+      <c r="F341" s="4"/>
+      <c r="G341" s="4"/>
       <c r="H341" s="7"/>
       <c r="I341" s="7"/>
       <c r="J341" s="7"/>
@@ -9193,16 +9190,16 @@
         <v>355</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D342" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E342" s="4">
         <v>5.0</v>
       </c>
       <c r="F342" s="4">
-        <v>22500.0</v>
+        <v>11500.0</v>
       </c>
       <c r="G342" s="7"/>
       <c r="H342" s="7"/>
@@ -9218,10 +9215,10 @@
         <v>356</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D343" s="4">
-        <v>1000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E343" s="7"/>
       <c r="F343" s="7"/>
@@ -9239,13 +9236,17 @@
         <v>357</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D344" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E344" s="7"/>
-      <c r="F344" s="7"/>
+      <c r="E344" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F344" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G344" s="7"/>
       <c r="H344" s="7"/>
       <c r="I344" s="7"/>
@@ -9260,10 +9261,10 @@
         <v>358</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D345" s="4">
-        <v>3000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E345" s="7"/>
       <c r="F345" s="7"/>
@@ -9281,10 +9282,10 @@
         <v>359</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D346" s="4">
-        <v>14000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E346" s="7"/>
       <c r="F346" s="7"/>
@@ -9302,10 +9303,10 @@
         <v>360</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>361</v>
+        <v>300</v>
       </c>
       <c r="D347" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E347" s="7"/>
       <c r="F347" s="7"/>
@@ -9320,13 +9321,13 @@
         <v>347</v>
       </c>
       <c r="B348" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>361</v>
+        <v>300</v>
       </c>
       <c r="D348" s="4">
-        <v>4000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E348" s="7"/>
       <c r="F348" s="7"/>
@@ -9341,10 +9342,10 @@
         <v>348</v>
       </c>
       <c r="B349" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="C349" s="5" t="s">
         <v>363</v>
-      </c>
-      <c r="C349" s="5" t="s">
-        <v>361</v>
       </c>
       <c r="D349" s="4">
         <v>1000.0</v>
@@ -9365,10 +9366,10 @@
         <v>364</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D350" s="4">
-        <v>10000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E350" s="7"/>
       <c r="F350" s="7"/>
@@ -9386,7 +9387,7 @@
         <v>365</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D351" s="4">
         <v>1000.0</v>
@@ -9407,7 +9408,7 @@
         <v>366</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D352" s="4">
         <v>10000.0</v>
@@ -9428,10 +9429,10 @@
         <v>367</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D353" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E353" s="7"/>
       <c r="F353" s="7"/>
@@ -9449,10 +9450,10 @@
         <v>368</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D354" s="4">
-        <v>2500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E354" s="7"/>
       <c r="F354" s="7"/>
@@ -9470,10 +9471,10 @@
         <v>369</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D355" s="4">
-        <v>3000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E355" s="7"/>
       <c r="F355" s="7"/>
@@ -9491,10 +9492,10 @@
         <v>370</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D356" s="4">
-        <v>5000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E356" s="7"/>
       <c r="F356" s="7"/>
@@ -9512,7 +9513,7 @@
         <v>371</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D357" s="4">
         <v>3000.0</v>
@@ -9533,17 +9534,13 @@
         <v>372</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D358" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E358" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F358" s="4">
-        <v>3000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E358" s="7"/>
+      <c r="F358" s="7"/>
       <c r="G358" s="7"/>
       <c r="H358" s="7"/>
       <c r="I358" s="7"/>
@@ -9558,10 +9555,10 @@
         <v>373</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D359" s="4">
-        <v>500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E359" s="7"/>
       <c r="F359" s="7"/>
@@ -9579,13 +9576,17 @@
         <v>374</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D360" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E360" s="7"/>
-      <c r="F360" s="7"/>
+      <c r="E360" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F360" s="4">
+        <v>3000.0</v>
+      </c>
       <c r="G360" s="7"/>
       <c r="H360" s="7"/>
       <c r="I360" s="7"/>
@@ -9600,10 +9601,10 @@
         <v>375</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D361" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E361" s="7"/>
       <c r="F361" s="7"/>
@@ -9621,10 +9622,10 @@
         <v>376</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D362" s="4">
-        <v>7000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E362" s="7"/>
       <c r="F362" s="7"/>
@@ -9642,10 +9643,10 @@
         <v>377</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D363" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E363" s="7"/>
       <c r="F363" s="7"/>
@@ -9663,10 +9664,10 @@
         <v>378</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D364" s="4">
-        <v>25000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E364" s="7"/>
       <c r="F364" s="7"/>
@@ -9684,10 +9685,10 @@
         <v>379</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D365" s="4">
-        <v>8000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E365" s="7"/>
       <c r="F365" s="7"/>
@@ -9705,10 +9706,10 @@
         <v>380</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D366" s="4">
-        <v>4000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E366" s="7"/>
       <c r="F366" s="7"/>
@@ -9726,10 +9727,10 @@
         <v>381</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="D367" s="4">
-        <v>2000.0</v>
+        <v>8000.0</v>
       </c>
       <c r="E367" s="7"/>
       <c r="F367" s="7"/>
@@ -9744,13 +9745,13 @@
         <v>367</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="D368" s="4">
-        <v>45000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E368" s="7"/>
       <c r="F368" s="7"/>
@@ -9765,13 +9766,13 @@
         <v>368</v>
       </c>
       <c r="B369" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C369" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="C369" s="5" t="s">
-        <v>382</v>
-      </c>
       <c r="D369" s="4">
-        <v>2500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E369" s="7"/>
       <c r="F369" s="7"/>
@@ -9789,10 +9790,10 @@
         <v>385</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D370" s="4">
-        <v>2500.0</v>
+        <v>45000.0</v>
       </c>
       <c r="E370" s="7"/>
       <c r="F370" s="7"/>
@@ -9810,10 +9811,10 @@
         <v>386</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D371" s="4">
-        <v>4000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E371" s="7"/>
       <c r="F371" s="7"/>
@@ -9831,10 +9832,10 @@
         <v>387</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D372" s="4">
-        <v>40000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E372" s="7"/>
       <c r="F372" s="7"/>
@@ -9852,10 +9853,10 @@
         <v>388</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D373" s="4">
-        <v>5000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E373" s="7"/>
       <c r="F373" s="7"/>
@@ -9873,16 +9874,16 @@
         <v>389</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D374" s="4">
-        <v>46000.0</v>
+        <v>40000.0</v>
       </c>
       <c r="E374" s="7"/>
       <c r="F374" s="7"/>
       <c r="G374" s="7"/>
       <c r="H374" s="7"/>
-      <c r="I374" s="4"/>
+      <c r="I374" s="7"/>
       <c r="J374" s="7"/>
     </row>
     <row r="375">
@@ -9894,16 +9895,16 @@
         <v>390</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D375" s="4">
-        <v>2000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E375" s="7"/>
       <c r="F375" s="7"/>
       <c r="G375" s="7"/>
       <c r="H375" s="7"/>
-      <c r="I375" s="4"/>
+      <c r="I375" s="7"/>
       <c r="J375" s="7"/>
     </row>
     <row r="376">
@@ -9915,10 +9916,10 @@
         <v>391</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D376" s="4">
-        <v>17000.0</v>
+        <v>46000.0</v>
       </c>
       <c r="E376" s="7"/>
       <c r="F376" s="7"/>
@@ -9936,10 +9937,10 @@
         <v>392</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D377" s="4">
-        <v>500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E377" s="7"/>
       <c r="F377" s="7"/>
@@ -9957,16 +9958,16 @@
         <v>393</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D378" s="4">
-        <v>1000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E378" s="7"/>
       <c r="F378" s="7"/>
       <c r="G378" s="7"/>
       <c r="H378" s="7"/>
-      <c r="I378" s="7"/>
+      <c r="I378" s="4"/>
       <c r="J378" s="7"/>
     </row>
     <row r="379">
@@ -9978,16 +9979,16 @@
         <v>394</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D379" s="4">
-        <v>10000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E379" s="7"/>
       <c r="F379" s="7"/>
       <c r="G379" s="7"/>
       <c r="H379" s="7"/>
-      <c r="I379" s="7"/>
+      <c r="I379" s="4"/>
       <c r="J379" s="7"/>
     </row>
     <row r="380">
@@ -9999,10 +10000,10 @@
         <v>395</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D380" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E380" s="7"/>
       <c r="F380" s="7"/>
@@ -10020,10 +10021,10 @@
         <v>396</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D381" s="4">
-        <v>1500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E381" s="7"/>
       <c r="F381" s="7"/>
@@ -10041,10 +10042,10 @@
         <v>397</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D382" s="4">
-        <v>12000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E382" s="7"/>
       <c r="F382" s="7"/>
@@ -10062,10 +10063,10 @@
         <v>398</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D383" s="4">
-        <v>3000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E383" s="7"/>
       <c r="F383" s="7"/>
@@ -10083,10 +10084,10 @@
         <v>399</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D384" s="4">
-        <v>1000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E384" s="7"/>
       <c r="F384" s="7"/>
@@ -10104,10 +10105,10 @@
         <v>400</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D385" s="4">
-        <v>25000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E385" s="7"/>
       <c r="F385" s="7"/>
@@ -10125,10 +10126,10 @@
         <v>401</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D386" s="4">
-        <v>9000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E386" s="7"/>
       <c r="F386" s="7"/>
@@ -10146,12 +10147,12 @@
         <v>402</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D387" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E387" s="4"/>
+        <v>25000.0</v>
+      </c>
+      <c r="E387" s="7"/>
       <c r="F387" s="7"/>
       <c r="G387" s="7"/>
       <c r="H387" s="7"/>
@@ -10167,7 +10168,7 @@
         <v>403</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D388" s="4">
         <v>9000.0</v>
@@ -10188,12 +10189,12 @@
         <v>404</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D389" s="4">
-        <v>4500.0</v>
-      </c>
-      <c r="E389" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E389" s="4"/>
       <c r="F389" s="7"/>
       <c r="G389" s="7"/>
       <c r="H389" s="7"/>
@@ -10209,10 +10210,10 @@
         <v>405</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D390" s="4">
-        <v>500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E390" s="7"/>
       <c r="F390" s="7"/>
@@ -10230,10 +10231,10 @@
         <v>406</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D391" s="4">
-        <v>3000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E391" s="7"/>
       <c r="F391" s="7"/>
@@ -10251,10 +10252,10 @@
         <v>407</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D392" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E392" s="7"/>
       <c r="F392" s="7"/>
@@ -10268,42 +10269,42 @@
         <f t="shared" si="1"/>
         <v>392</v>
       </c>
-      <c r="B393" s="9" t="s">
+      <c r="B393" s="5" t="s">
         <v>408</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="D393" s="10">
-        <v>4500.0</v>
-      </c>
-      <c r="E393" s="11"/>
-      <c r="F393" s="11"/>
-      <c r="G393" s="11"/>
-      <c r="H393" s="11"/>
-      <c r="I393" s="11"/>
-      <c r="J393" s="11"/>
+        <v>384</v>
+      </c>
+      <c r="D393" s="4">
+        <v>3000.0</v>
+      </c>
+      <c r="E393" s="7"/>
+      <c r="F393" s="7"/>
+      <c r="G393" s="7"/>
+      <c r="H393" s="7"/>
+      <c r="I393" s="7"/>
+      <c r="J393" s="7"/>
     </row>
     <row r="394">
       <c r="A394" s="4">
         <f t="shared" si="1"/>
         <v>393</v>
       </c>
-      <c r="B394" s="9" t="s">
+      <c r="B394" s="5" t="s">
         <v>409</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="D394" s="10">
-        <v>50000.0</v>
-      </c>
-      <c r="E394" s="11"/>
-      <c r="F394" s="11"/>
-      <c r="G394" s="11"/>
-      <c r="H394" s="11"/>
-      <c r="I394" s="11"/>
-      <c r="J394" s="11"/>
+        <v>384</v>
+      </c>
+      <c r="D394" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E394" s="7"/>
+      <c r="F394" s="7"/>
+      <c r="G394" s="7"/>
+      <c r="H394" s="7"/>
+      <c r="I394" s="7"/>
+      <c r="J394" s="7"/>
     </row>
     <row r="395">
       <c r="A395" s="4">
@@ -10314,10 +10315,10 @@
         <v>410</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D395" s="10">
-        <v>12000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E395" s="11"/>
       <c r="F395" s="11"/>
@@ -10331,14 +10332,14 @@
         <f t="shared" si="1"/>
         <v>395</v>
       </c>
-      <c r="B396" s="5" t="s">
+      <c r="B396" s="9" t="s">
         <v>411</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D396" s="10">
-        <v>4500.0</v>
+        <v>50000.0</v>
       </c>
       <c r="E396" s="11"/>
       <c r="F396" s="11"/>
@@ -10356,10 +10357,10 @@
         <v>412</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="D397" s="10">
-        <v>3000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E397" s="11"/>
       <c r="F397" s="11"/>
@@ -10373,14 +10374,14 @@
         <f t="shared" si="1"/>
         <v>397</v>
       </c>
-      <c r="B398" s="9" t="s">
+      <c r="B398" s="5" t="s">
         <v>413</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="D398" s="10">
-        <v>5000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E398" s="11"/>
       <c r="F398" s="11"/>
@@ -10398,10 +10399,10 @@
         <v>414</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D399" s="10">
-        <v>6000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E399" s="11"/>
       <c r="F399" s="11"/>
@@ -10419,10 +10420,10 @@
         <v>415</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>361</v>
+        <v>415</v>
       </c>
       <c r="D400" s="10">
-        <v>12000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E400" s="11"/>
       <c r="F400" s="11"/>
@@ -10440,13 +10441,13 @@
         <v>416</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>361</v>
+        <v>415</v>
       </c>
       <c r="D401" s="10">
-        <v>200.0</v>
-      </c>
-      <c r="E401" s="10"/>
-      <c r="F401" s="10"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E401" s="11"/>
+      <c r="F401" s="11"/>
       <c r="G401" s="11"/>
       <c r="H401" s="11"/>
       <c r="I401" s="11"/>
@@ -10461,17 +10462,13 @@
         <v>417</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D402" s="10">
-        <v>5000.0</v>
-      </c>
-      <c r="E402" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="F402" s="10">
-        <v>4500.0</v>
-      </c>
+        <v>12000.0</v>
+      </c>
+      <c r="E402" s="11"/>
+      <c r="F402" s="11"/>
       <c r="G402" s="11"/>
       <c r="H402" s="11"/>
       <c r="I402" s="11"/>
@@ -10486,13 +10483,13 @@
         <v>418</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D403" s="10">
-        <v>18000.0</v>
-      </c>
-      <c r="E403" s="11"/>
-      <c r="F403" s="11"/>
+        <v>200.0</v>
+      </c>
+      <c r="E403" s="10"/>
+      <c r="F403" s="10"/>
       <c r="G403" s="11"/>
       <c r="H403" s="11"/>
       <c r="I403" s="11"/>
@@ -10507,13 +10504,17 @@
         <v>419</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D404" s="10">
-        <v>17000.0</v>
-      </c>
-      <c r="E404" s="11"/>
-      <c r="F404" s="11"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E404" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="F404" s="10">
+        <v>4500.0</v>
+      </c>
       <c r="G404" s="11"/>
       <c r="H404" s="11"/>
       <c r="I404" s="11"/>
@@ -10528,10 +10529,10 @@
         <v>420</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D405" s="10">
-        <v>17500.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E405" s="11"/>
       <c r="F405" s="11"/>
@@ -10549,10 +10550,10 @@
         <v>421</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D406" s="10">
-        <v>9000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E406" s="11"/>
       <c r="F406" s="11"/>
@@ -10570,10 +10571,10 @@
         <v>422</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D407" s="10">
-        <v>9000.0</v>
+        <v>17500.0</v>
       </c>
       <c r="E407" s="11"/>
       <c r="F407" s="11"/>
@@ -10591,10 +10592,10 @@
         <v>423</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D408" s="10">
-        <v>19500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E408" s="11"/>
       <c r="F408" s="11"/>
@@ -10612,10 +10613,10 @@
         <v>424</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D409" s="10">
-        <v>8500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E409" s="11"/>
       <c r="F409" s="11"/>
@@ -10625,10 +10626,19 @@
       <c r="J409" s="11"/>
     </row>
     <row r="410">
-      <c r="A410" s="12"/>
-      <c r="B410" s="12"/>
-      <c r="C410" s="12"/>
-      <c r="D410" s="11"/>
+      <c r="A410" s="4">
+        <f t="shared" si="1"/>
+        <v>409</v>
+      </c>
+      <c r="B410" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="C410" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="D410" s="10">
+        <v>19500.0</v>
+      </c>
       <c r="E410" s="11"/>
       <c r="F410" s="11"/>
       <c r="G410" s="11"/>
@@ -10637,10 +10647,19 @@
       <c r="J410" s="11"/>
     </row>
     <row r="411">
-      <c r="A411" s="12"/>
-      <c r="B411" s="12"/>
-      <c r="C411" s="12"/>
-      <c r="D411" s="11"/>
+      <c r="A411" s="4">
+        <f t="shared" si="1"/>
+        <v>410</v>
+      </c>
+      <c r="B411" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="C411" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="D411" s="10">
+        <v>8500.0</v>
+      </c>
       <c r="E411" s="11"/>
       <c r="F411" s="11"/>
       <c r="G411" s="11"/>
@@ -10649,10 +10668,19 @@
       <c r="J411" s="11"/>
     </row>
     <row r="412">
-      <c r="A412" s="12"/>
-      <c r="B412" s="12"/>
-      <c r="C412" s="12"/>
-      <c r="D412" s="11"/>
+      <c r="A412" s="4">
+        <f t="shared" si="1"/>
+        <v>411</v>
+      </c>
+      <c r="B412" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="C412" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="D412" s="10">
+        <v>9000.0</v>
+      </c>
       <c r="E412" s="11"/>
       <c r="F412" s="11"/>
       <c r="G412" s="11"/>
@@ -11720,25 +11748,25 @@
       <c r="A501" s="12"/>
       <c r="B501" s="12"/>
       <c r="C501" s="12"/>
-      <c r="D501" s="12"/>
-      <c r="E501" s="12"/>
-      <c r="F501" s="12"/>
-      <c r="G501" s="12"/>
-      <c r="H501" s="12"/>
-      <c r="I501" s="12"/>
-      <c r="J501" s="12"/>
+      <c r="D501" s="11"/>
+      <c r="E501" s="11"/>
+      <c r="F501" s="11"/>
+      <c r="G501" s="11"/>
+      <c r="H501" s="11"/>
+      <c r="I501" s="11"/>
+      <c r="J501" s="11"/>
     </row>
     <row r="502">
       <c r="A502" s="12"/>
       <c r="B502" s="12"/>
       <c r="C502" s="12"/>
-      <c r="D502" s="12"/>
-      <c r="E502" s="12"/>
-      <c r="F502" s="12"/>
-      <c r="G502" s="12"/>
-      <c r="H502" s="12"/>
-      <c r="I502" s="12"/>
-      <c r="J502" s="12"/>
+      <c r="D502" s="11"/>
+      <c r="E502" s="11"/>
+      <c r="F502" s="11"/>
+      <c r="G502" s="11"/>
+      <c r="H502" s="11"/>
+      <c r="I502" s="11"/>
+      <c r="J502" s="11"/>
     </row>
     <row r="503">
       <c r="A503" s="12"/>
@@ -20140,15 +20168,39 @@
       <c r="I1202" s="12"/>
       <c r="J1202" s="12"/>
     </row>
+    <row r="1203">
+      <c r="A1203" s="12"/>
+      <c r="B1203" s="12"/>
+      <c r="C1203" s="12"/>
+      <c r="D1203" s="12"/>
+      <c r="E1203" s="12"/>
+      <c r="F1203" s="12"/>
+      <c r="G1203" s="12"/>
+      <c r="H1203" s="12"/>
+      <c r="I1203" s="12"/>
+      <c r="J1203" s="12"/>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="12"/>
+      <c r="B1204" s="12"/>
+      <c r="C1204" s="12"/>
+      <c r="D1204" s="12"/>
+      <c r="E1204" s="12"/>
+      <c r="F1204" s="12"/>
+      <c r="G1204" s="12"/>
+      <c r="H1204" s="12"/>
+      <c r="I1204" s="12"/>
+      <c r="J1204" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$409"/>
-  <conditionalFormatting sqref="A2:J1202">
+  <autoFilter ref="$B$1:$C$412"/>
+  <conditionalFormatting sqref="A2:J1204">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C409">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C412">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20209,7 +20261,7 @@
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4">
@@ -20228,7 +20280,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -20247,7 +20299,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -20266,7 +20318,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -20285,7 +20337,7 @@
         <v>GROSIR5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="4">
@@ -20304,7 +20356,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -20323,7 +20375,7 @@
         <v>GROSIR7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="4">
@@ -20342,7 +20394,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -20361,7 +20413,7 @@
         <v>GROSIR9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="4">
@@ -20380,7 +20432,7 @@
         <v>GROSIR10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="4">
@@ -20399,7 +20451,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -20418,7 +20470,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -20437,7 +20489,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -20456,7 +20508,7 @@
         <v>GROSIR14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="4">
@@ -20475,7 +20527,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -20494,7 +20546,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -20513,7 +20565,7 @@
         <v>GROSIR17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="4">
@@ -20532,7 +20584,7 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
@@ -20551,7 +20603,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -20570,7 +20622,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -20589,7 +20641,7 @@
         <v>GROSIR21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4">
@@ -20608,7 +20660,7 @@
         <v>GROSIR22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="4">
@@ -20627,7 +20679,7 @@
         <v>GROSIR23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="4">
@@ -20646,7 +20698,7 @@
         <v>GROSIR24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="4">
@@ -20665,7 +20717,7 @@
         <v>GROSIR25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="4">
@@ -20684,7 +20736,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -20703,7 +20755,7 @@
         <v>GROSIR27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="4">
@@ -20722,7 +20774,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -20741,7 +20793,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -20760,7 +20812,7 @@
         <v>GROSIR30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="4">
@@ -20779,7 +20831,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -20798,7 +20850,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -20817,7 +20869,7 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
@@ -20836,7 +20888,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -20855,7 +20907,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -20874,7 +20926,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -20893,7 +20945,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -20912,7 +20964,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -20931,7 +20983,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -20950,7 +21002,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -20969,7 +21021,7 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
@@ -20988,7 +21040,7 @@
         <v>GROSIR42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$412</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$414</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$260</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="456">
   <si>
     <t>Barcode</t>
   </si>
@@ -258,6 +258,12 @@
   </si>
   <si>
     <t>Good Day Moccacino Renceng</t>
+  </si>
+  <si>
+    <t>Good Day Cappuccino</t>
+  </si>
+  <si>
+    <t>Good Day Cappuccino Renceng</t>
   </si>
   <si>
     <t>Good Day Chococinno</t>
@@ -1764,7 +1770,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A412" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A414" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -3248,7 +3254,7 @@
         <v>11</v>
       </c>
       <c r="D71" s="4">
-        <v>2000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
@@ -3269,14 +3275,14 @@
         <v>11</v>
       </c>
       <c r="D72" s="4">
-        <v>15000.0</v>
-      </c>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="7"/>
-      <c r="J72" s="7"/>
+        <v>21000.0</v>
+      </c>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
     </row>
     <row r="73">
       <c r="A73" s="4">
@@ -3313,12 +3319,12 @@
       <c r="D74" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
     </row>
     <row r="75">
       <c r="A75" s="4">
@@ -3397,12 +3403,12 @@
       <c r="D78" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
-      <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
-      <c r="I78" s="7"/>
-      <c r="J78" s="7"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
     </row>
     <row r="79">
       <c r="A79" s="4">
@@ -3439,12 +3445,12 @@
       <c r="D80" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7"/>
+      <c r="J80" s="7"/>
     </row>
     <row r="81">
       <c r="A81" s="4">
@@ -3479,7 +3485,7 @@
         <v>11</v>
       </c>
       <c r="D82" s="4">
-        <v>2000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
@@ -3500,14 +3506,14 @@
         <v>11</v>
       </c>
       <c r="D83" s="4">
-        <v>16500.0</v>
-      </c>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
-      <c r="G83" s="7"/>
-      <c r="H83" s="7"/>
-      <c r="I83" s="7"/>
-      <c r="J83" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="6"/>
+      <c r="J83" s="6"/>
     </row>
     <row r="84">
       <c r="A84" s="4">
@@ -3542,7 +3548,7 @@
         <v>11</v>
       </c>
       <c r="D85" s="4">
-        <v>17000.0</v>
+        <v>16500.0</v>
       </c>
       <c r="E85" s="7"/>
       <c r="F85" s="7"/>
@@ -3584,14 +3590,14 @@
         <v>11</v>
       </c>
       <c r="D87" s="4">
-        <v>8500.0</v>
-      </c>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
+        <v>17000.0</v>
+      </c>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="7"/>
+      <c r="H87" s="7"/>
+      <c r="I87" s="7"/>
+      <c r="J87" s="7"/>
     </row>
     <row r="88">
       <c r="A88" s="4">
@@ -3626,7 +3632,7 @@
         <v>11</v>
       </c>
       <c r="D89" s="4">
-        <v>17000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
@@ -3668,14 +3674,14 @@
         <v>11</v>
       </c>
       <c r="D91" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-      <c r="G91" s="7"/>
-      <c r="H91" s="7"/>
-      <c r="I91" s="7"/>
-      <c r="J91" s="7"/>
+        <v>17000.0</v>
+      </c>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6"/>
+      <c r="J91" s="6"/>
     </row>
     <row r="92">
       <c r="A92" s="4">
@@ -3689,7 +3695,7 @@
         <v>11</v>
       </c>
       <c r="D92" s="4">
-        <v>10000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
@@ -3710,14 +3716,14 @@
         <v>11</v>
       </c>
       <c r="D93" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
-      <c r="J93" s="6"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
+      <c r="I93" s="7"/>
+      <c r="J93" s="7"/>
     </row>
     <row r="94">
       <c r="A94" s="4">
@@ -3731,7 +3737,7 @@
         <v>11</v>
       </c>
       <c r="D94" s="4">
-        <v>90000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
@@ -3752,7 +3758,7 @@
         <v>11</v>
       </c>
       <c r="D95" s="4">
-        <v>2000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
@@ -3773,14 +3779,14 @@
         <v>11</v>
       </c>
       <c r="D96" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
-      <c r="G96" s="7"/>
-      <c r="H96" s="7"/>
-      <c r="I96" s="7"/>
-      <c r="J96" s="7"/>
+        <v>90000.0</v>
+      </c>
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6"/>
+      <c r="J96" s="6"/>
     </row>
     <row r="97">
       <c r="A97" s="4">
@@ -3794,14 +3800,14 @@
         <v>11</v>
       </c>
       <c r="D97" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="G97" s="7"/>
-      <c r="H97" s="7"/>
-      <c r="I97" s="7"/>
-      <c r="J97" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6"/>
+      <c r="J97" s="6"/>
     </row>
     <row r="98">
       <c r="A98" s="4">
@@ -3815,7 +3821,7 @@
         <v>11</v>
       </c>
       <c r="D98" s="4">
-        <v>23000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E98" s="7"/>
       <c r="F98" s="7"/>
@@ -3836,7 +3842,7 @@
         <v>11</v>
       </c>
       <c r="D99" s="4">
-        <v>2000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E99" s="7"/>
       <c r="F99" s="7"/>
@@ -3857,14 +3863,14 @@
         <v>11</v>
       </c>
       <c r="D100" s="4">
-        <v>15500.0</v>
-      </c>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-      <c r="J100" s="6"/>
+        <v>23000.0</v>
+      </c>
+      <c r="E100" s="7"/>
+      <c r="F100" s="7"/>
+      <c r="G100" s="7"/>
+      <c r="H100" s="7"/>
+      <c r="I100" s="7"/>
+      <c r="J100" s="7"/>
     </row>
     <row r="101">
       <c r="A101" s="4">
@@ -3878,14 +3884,14 @@
         <v>11</v>
       </c>
       <c r="D101" s="4">
-        <v>1500.0</v>
-      </c>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-      <c r="J101" s="6"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7"/>
+      <c r="J101" s="7"/>
     </row>
     <row r="102">
       <c r="A102" s="4">
@@ -3899,7 +3905,7 @@
         <v>11</v>
       </c>
       <c r="D102" s="4">
-        <v>11500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -3920,7 +3926,7 @@
         <v>11</v>
       </c>
       <c r="D103" s="4">
-        <v>1000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
@@ -3941,7 +3947,7 @@
         <v>11</v>
       </c>
       <c r="D104" s="4">
-        <v>9000.0</v>
+        <v>11500.0</v>
       </c>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
@@ -3962,7 +3968,7 @@
         <v>11</v>
       </c>
       <c r="D105" s="4">
-        <v>2500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
@@ -3983,7 +3989,7 @@
         <v>11</v>
       </c>
       <c r="D106" s="4">
-        <v>19000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -4004,7 +4010,7 @@
         <v>11</v>
       </c>
       <c r="D107" s="4">
-        <v>1500.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
@@ -4025,7 +4031,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="4">
-        <v>8500.0</v>
+        <v>19000.0</v>
       </c>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
@@ -4046,7 +4052,7 @@
         <v>11</v>
       </c>
       <c r="D109" s="4">
-        <v>3500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
@@ -4067,7 +4073,7 @@
         <v>11</v>
       </c>
       <c r="D110" s="4">
-        <v>15000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
@@ -4088,7 +4094,7 @@
         <v>11</v>
       </c>
       <c r="D111" s="4">
-        <v>2000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
@@ -4109,7 +4115,7 @@
         <v>11</v>
       </c>
       <c r="D112" s="4">
-        <v>16000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
@@ -4130,7 +4136,7 @@
         <v>11</v>
       </c>
       <c r="D113" s="4">
-        <v>1500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
@@ -4169,10 +4175,10 @@
         <v>125</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>126</v>
+        <v>11</v>
       </c>
       <c r="D115" s="4">
-        <v>6000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
@@ -4187,20 +4193,20 @@
         <v>115</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>126</v>
+        <v>11</v>
       </c>
       <c r="D116" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
-      <c r="G116" s="7"/>
-      <c r="H116" s="7"/>
-      <c r="I116" s="7"/>
-      <c r="J116" s="7"/>
+        <v>16000.0</v>
+      </c>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="6"/>
+      <c r="H116" s="6"/>
+      <c r="I116" s="6"/>
+      <c r="J116" s="6"/>
     </row>
     <row r="117">
       <c r="A117" s="4">
@@ -4208,20 +4214,20 @@
         <v>116</v>
       </c>
       <c r="B117" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C117" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C117" s="5" t="s">
-        <v>126</v>
-      </c>
       <c r="D117" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
-      <c r="G117" s="7"/>
-      <c r="H117" s="7"/>
-      <c r="I117" s="7"/>
-      <c r="J117" s="7"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E117" s="6"/>
+      <c r="F117" s="6"/>
+      <c r="G117" s="6"/>
+      <c r="H117" s="6"/>
+      <c r="I117" s="6"/>
+      <c r="J117" s="6"/>
     </row>
     <row r="118">
       <c r="A118" s="4">
@@ -4232,7 +4238,7 @@
         <v>129</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D118" s="4">
         <v>1000.0</v>
@@ -4253,7 +4259,7 @@
         <v>130</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D119" s="4">
         <v>10000.0</v>
@@ -4274,7 +4280,7 @@
         <v>131</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D120" s="4">
         <v>1000.0</v>
@@ -4295,7 +4301,7 @@
         <v>132</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D121" s="4">
         <v>10000.0</v>
@@ -4316,10 +4322,10 @@
         <v>133</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D122" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E122" s="7"/>
       <c r="F122" s="7"/>
@@ -4337,17 +4343,17 @@
         <v>134</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D123" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E123" s="6"/>
-      <c r="F123" s="6"/>
-      <c r="G123" s="6"/>
-      <c r="H123" s="6"/>
-      <c r="I123" s="6"/>
-      <c r="J123" s="6"/>
+        <v>10000.0</v>
+      </c>
+      <c r="E123" s="7"/>
+      <c r="F123" s="7"/>
+      <c r="G123" s="7"/>
+      <c r="H123" s="7"/>
+      <c r="I123" s="7"/>
+      <c r="J123" s="7"/>
     </row>
     <row r="124">
       <c r="A124" s="4">
@@ -4358,17 +4364,17 @@
         <v>135</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D124" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E124" s="6"/>
-      <c r="F124" s="6"/>
-      <c r="G124" s="6"/>
-      <c r="H124" s="6"/>
-      <c r="I124" s="6"/>
-      <c r="J124" s="6"/>
+        <v>500.0</v>
+      </c>
+      <c r="E124" s="7"/>
+      <c r="F124" s="7"/>
+      <c r="G124" s="7"/>
+      <c r="H124" s="7"/>
+      <c r="I124" s="7"/>
+      <c r="J124" s="7"/>
     </row>
     <row r="125">
       <c r="A125" s="4">
@@ -4379,10 +4385,10 @@
         <v>136</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D125" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
@@ -4400,10 +4406,10 @@
         <v>137</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D126" s="4">
-        <v>22000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
@@ -4421,10 +4427,10 @@
         <v>138</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D127" s="4">
-        <v>10000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
@@ -4442,10 +4448,10 @@
         <v>139</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D128" s="4">
-        <v>500.0</v>
+        <v>22000.0</v>
       </c>
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
@@ -4463,10 +4469,10 @@
         <v>140</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D129" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
@@ -4484,10 +4490,10 @@
         <v>141</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D130" s="4">
-        <v>10000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
@@ -4505,10 +4511,10 @@
         <v>142</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D131" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
@@ -4526,10 +4532,10 @@
         <v>143</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D132" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E132" s="6"/>
       <c r="F132" s="6"/>
@@ -4547,10 +4553,10 @@
         <v>144</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D133" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
@@ -4568,17 +4574,13 @@
         <v>145</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D134" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E134" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F134" s="4">
-        <v>1000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
       <c r="G134" s="6"/>
       <c r="H134" s="6"/>
       <c r="I134" s="6"/>
@@ -4593,10 +4595,10 @@
         <v>146</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D135" s="4">
-        <v>6500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
@@ -4614,13 +4616,17 @@
         <v>147</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D136" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="E136" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F136" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
       <c r="G136" s="6"/>
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
@@ -4635,10 +4641,10 @@
         <v>148</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D137" s="4">
-        <v>10000.0</v>
+        <v>6500.0</v>
       </c>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
@@ -4656,17 +4662,13 @@
         <v>149</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D138" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E138" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F138" s="4">
-        <v>13000.0</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E138" s="6"/>
+      <c r="F138" s="6"/>
       <c r="G138" s="6"/>
       <c r="H138" s="6"/>
       <c r="I138" s="6"/>
@@ -4681,10 +4683,10 @@
         <v>150</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D139" s="4">
-        <v>23000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
@@ -4702,17 +4704,21 @@
         <v>151</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D140" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7"/>
-      <c r="G140" s="7"/>
-      <c r="H140" s="7"/>
-      <c r="I140" s="7"/>
-      <c r="J140" s="7"/>
+      <c r="E140" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F140" s="4">
+        <v>13000.0</v>
+      </c>
+      <c r="G140" s="6"/>
+      <c r="H140" s="6"/>
+      <c r="I140" s="6"/>
+      <c r="J140" s="6"/>
     </row>
     <row r="141">
       <c r="A141" s="4">
@@ -4723,10 +4729,10 @@
         <v>152</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D141" s="4">
-        <v>26000.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
@@ -4744,17 +4750,17 @@
         <v>153</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D142" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E142" s="6"/>
-      <c r="F142" s="6"/>
-      <c r="G142" s="6"/>
-      <c r="H142" s="6"/>
-      <c r="I142" s="6"/>
-      <c r="J142" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E142" s="7"/>
+      <c r="F142" s="7"/>
+      <c r="G142" s="7"/>
+      <c r="H142" s="7"/>
+      <c r="I142" s="7"/>
+      <c r="J142" s="7"/>
     </row>
     <row r="143">
       <c r="A143" s="4">
@@ -4765,10 +4771,10 @@
         <v>154</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D143" s="4">
-        <v>21000.0</v>
+        <v>26000.0</v>
       </c>
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
@@ -4786,10 +4792,10 @@
         <v>155</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D144" s="4">
-        <v>2000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
@@ -4807,10 +4813,10 @@
         <v>156</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D145" s="4">
-        <v>36500.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
@@ -4828,10 +4834,10 @@
         <v>157</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D146" s="4">
-        <v>13000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E146" s="6"/>
       <c r="F146" s="6"/>
@@ -4849,10 +4855,10 @@
         <v>158</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D147" s="4">
-        <v>500.0</v>
+        <v>36500.0</v>
       </c>
       <c r="E147" s="6"/>
       <c r="F147" s="6"/>
@@ -4870,10 +4876,10 @@
         <v>159</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D148" s="4">
-        <v>13500.0</v>
+        <v>13000.0</v>
       </c>
       <c r="E148" s="6"/>
       <c r="F148" s="6"/>
@@ -4891,10 +4897,10 @@
         <v>160</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D149" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
@@ -4912,10 +4918,10 @@
         <v>161</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D150" s="4">
-        <v>160000.0</v>
+        <v>13500.0</v>
       </c>
       <c r="E150" s="6"/>
       <c r="F150" s="6"/>
@@ -4933,17 +4939,13 @@
         <v>162</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D151" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E151" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F151" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E151" s="6"/>
+      <c r="F151" s="6"/>
       <c r="G151" s="6"/>
       <c r="H151" s="6"/>
       <c r="I151" s="6"/>
@@ -4958,17 +4960,17 @@
         <v>163</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D152" s="4">
-        <v>65000.0</v>
-      </c>
-      <c r="E152" s="7"/>
-      <c r="F152" s="7"/>
-      <c r="G152" s="7"/>
-      <c r="H152" s="7"/>
-      <c r="I152" s="7"/>
-      <c r="J152" s="7"/>
+        <v>160000.0</v>
+      </c>
+      <c r="E152" s="6"/>
+      <c r="F152" s="6"/>
+      <c r="G152" s="6"/>
+      <c r="H152" s="6"/>
+      <c r="I152" s="6"/>
+      <c r="J152" s="6"/>
     </row>
     <row r="153">
       <c r="A153" s="4">
@@ -4979,17 +4981,21 @@
         <v>164</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D153" s="4">
-        <v>4500.0</v>
-      </c>
-      <c r="E153" s="7"/>
-      <c r="F153" s="7"/>
-      <c r="G153" s="7"/>
-      <c r="H153" s="7"/>
-      <c r="I153" s="7"/>
-      <c r="J153" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E153" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F153" s="4">
+        <v>9000.0</v>
+      </c>
+      <c r="G153" s="6"/>
+      <c r="H153" s="6"/>
+      <c r="I153" s="6"/>
+      <c r="J153" s="6"/>
     </row>
     <row r="154">
       <c r="A154" s="4">
@@ -5000,17 +5006,17 @@
         <v>165</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D154" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E154" s="6"/>
-      <c r="F154" s="6"/>
-      <c r="G154" s="6"/>
-      <c r="H154" s="6"/>
-      <c r="I154" s="6"/>
-      <c r="J154" s="6"/>
+        <v>65000.0</v>
+      </c>
+      <c r="E154" s="7"/>
+      <c r="F154" s="7"/>
+      <c r="G154" s="7"/>
+      <c r="H154" s="7"/>
+      <c r="I154" s="7"/>
+      <c r="J154" s="7"/>
     </row>
     <row r="155">
       <c r="A155" s="4">
@@ -5021,17 +5027,17 @@
         <v>166</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D155" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E155" s="6"/>
-      <c r="F155" s="6"/>
-      <c r="G155" s="6"/>
-      <c r="H155" s="6"/>
-      <c r="I155" s="6"/>
-      <c r="J155" s="6"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E155" s="7"/>
+      <c r="F155" s="7"/>
+      <c r="G155" s="7"/>
+      <c r="H155" s="7"/>
+      <c r="I155" s="7"/>
+      <c r="J155" s="7"/>
     </row>
     <row r="156">
       <c r="A156" s="4">
@@ -5042,7 +5048,7 @@
         <v>167</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D156" s="4">
         <v>2000.0</v>
@@ -5063,7 +5069,7 @@
         <v>168</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D157" s="4">
         <v>17000.0</v>
@@ -5084,7 +5090,7 @@
         <v>169</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D158" s="4">
         <v>2000.0</v>
@@ -5105,7 +5111,7 @@
         <v>170</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D159" s="4">
         <v>17000.0</v>
@@ -5126,7 +5132,7 @@
         <v>171</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D160" s="4">
         <v>2000.0</v>
@@ -5147,7 +5153,7 @@
         <v>172</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D161" s="4">
         <v>17000.0</v>
@@ -5168,7 +5174,7 @@
         <v>173</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D162" s="4">
         <v>2000.0</v>
@@ -5189,7 +5195,7 @@
         <v>174</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D163" s="4">
         <v>17000.0</v>
@@ -5210,10 +5216,10 @@
         <v>175</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D164" s="4">
-        <v>5000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E164" s="6"/>
       <c r="F164" s="6"/>
@@ -5231,10 +5237,10 @@
         <v>176</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D165" s="4">
-        <v>10000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E165" s="6"/>
       <c r="F165" s="6"/>
@@ -5252,10 +5258,10 @@
         <v>177</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D166" s="4">
-        <v>18000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E166" s="6"/>
       <c r="F166" s="6"/>
@@ -5273,10 +5279,10 @@
         <v>178</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D167" s="4">
-        <v>4500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E167" s="6"/>
       <c r="F167" s="6"/>
@@ -5294,10 +5300,10 @@
         <v>179</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D168" s="4">
-        <v>9000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E168" s="6"/>
       <c r="F168" s="6"/>
@@ -5315,17 +5321,17 @@
         <v>180</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D169" s="4">
-        <v>18000.0</v>
-      </c>
-      <c r="E169" s="4"/>
-      <c r="F169" s="4"/>
-      <c r="G169" s="7"/>
-      <c r="H169" s="7"/>
-      <c r="I169" s="7"/>
-      <c r="J169" s="7"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E169" s="6"/>
+      <c r="F169" s="6"/>
+      <c r="G169" s="6"/>
+      <c r="H169" s="6"/>
+      <c r="I169" s="6"/>
+      <c r="J169" s="6"/>
     </row>
     <row r="170">
       <c r="A170" s="4">
@@ -5336,21 +5342,17 @@
         <v>181</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D170" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E170" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F170" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="G170" s="7"/>
-      <c r="H170" s="7"/>
-      <c r="I170" s="7"/>
-      <c r="J170" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E170" s="6"/>
+      <c r="F170" s="6"/>
+      <c r="G170" s="6"/>
+      <c r="H170" s="6"/>
+      <c r="I170" s="6"/>
+      <c r="J170" s="6"/>
     </row>
     <row r="171">
       <c r="A171" s="4">
@@ -5361,10 +5363,10 @@
         <v>182</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D171" s="4">
-        <v>3500.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E171" s="4"/>
       <c r="F171" s="4"/>
@@ -5382,16 +5384,16 @@
         <v>183</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D172" s="4">
-        <v>2500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E172" s="4">
         <v>4.0</v>
       </c>
       <c r="F172" s="4">
-        <v>8500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="G172" s="7"/>
       <c r="H172" s="7"/>
@@ -5407,13 +5409,13 @@
         <v>184</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D173" s="4">
-        <v>26000.0</v>
-      </c>
-      <c r="E173" s="7"/>
-      <c r="F173" s="7"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E173" s="4"/>
+      <c r="F173" s="4"/>
       <c r="G173" s="7"/>
       <c r="H173" s="7"/>
       <c r="I173" s="7"/>
@@ -5428,16 +5430,16 @@
         <v>185</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D174" s="4">
-        <v>4000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E174" s="4">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F174" s="4">
-        <v>17500.0</v>
+        <v>8500.0</v>
       </c>
       <c r="G174" s="7"/>
       <c r="H174" s="7"/>
@@ -5453,10 +5455,10 @@
         <v>186</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D175" s="4">
-        <v>175000.0</v>
+        <v>26000.0</v>
       </c>
       <c r="E175" s="7"/>
       <c r="F175" s="7"/>
@@ -5474,13 +5476,17 @@
         <v>187</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D176" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E176" s="7"/>
-      <c r="F176" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E176" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F176" s="4">
+        <v>17500.0</v>
+      </c>
       <c r="G176" s="7"/>
       <c r="H176" s="7"/>
       <c r="I176" s="7"/>
@@ -5495,17 +5501,13 @@
         <v>188</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D177" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="E177" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F177" s="4">
-        <v>22000.0</v>
-      </c>
+        <v>175000.0</v>
+      </c>
+      <c r="E177" s="7"/>
+      <c r="F177" s="7"/>
       <c r="G177" s="7"/>
       <c r="H177" s="7"/>
       <c r="I177" s="7"/>
@@ -5520,7 +5522,7 @@
         <v>189</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D178" s="4">
         <v>21000.0</v>
@@ -5541,13 +5543,17 @@
         <v>190</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D179" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E179" s="7"/>
-      <c r="F179" s="7"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E179" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F179" s="4">
+        <v>22000.0</v>
+      </c>
       <c r="G179" s="7"/>
       <c r="H179" s="7"/>
       <c r="I179" s="7"/>
@@ -5562,10 +5568,10 @@
         <v>191</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D180" s="4">
-        <v>245000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E180" s="7"/>
       <c r="F180" s="7"/>
@@ -5583,10 +5589,10 @@
         <v>192</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D181" s="4">
-        <v>42000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E181" s="7"/>
       <c r="F181" s="7"/>
@@ -5604,10 +5610,10 @@
         <v>193</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D182" s="4">
-        <v>44000.0</v>
+        <v>245000.0</v>
       </c>
       <c r="E182" s="7"/>
       <c r="F182" s="7"/>
@@ -5625,10 +5631,10 @@
         <v>194</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D183" s="4">
-        <v>255000.0</v>
+        <v>42000.0</v>
       </c>
       <c r="E183" s="7"/>
       <c r="F183" s="7"/>
@@ -5646,10 +5652,10 @@
         <v>195</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D184" s="4">
-        <v>21000.0</v>
+        <v>44000.0</v>
       </c>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
@@ -5667,10 +5673,10 @@
         <v>196</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D185" s="4">
-        <v>42000.0</v>
+        <v>255000.0</v>
       </c>
       <c r="E185" s="7"/>
       <c r="F185" s="7"/>
@@ -5688,17 +5694,17 @@
         <v>197</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D186" s="4">
-        <v>14500.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
-      <c r="G186" s="4"/>
-      <c r="H186" s="4"/>
-      <c r="I186" s="4"/>
-      <c r="J186" s="4"/>
+      <c r="G186" s="7"/>
+      <c r="H186" s="7"/>
+      <c r="I186" s="7"/>
+      <c r="J186" s="7"/>
     </row>
     <row r="187">
       <c r="A187" s="4">
@@ -5709,25 +5715,17 @@
         <v>198</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="D187" s="4">
-        <v>2000.0</v>
+        <v>42000.0</v>
       </c>
       <c r="E187" s="7"/>
       <c r="F187" s="7"/>
-      <c r="G187" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H187" s="4">
-        <v>5500.0</v>
-      </c>
-      <c r="I187" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J187" s="4">
-        <v>10000.0</v>
-      </c>
+      <c r="G187" s="7"/>
+      <c r="H187" s="7"/>
+      <c r="I187" s="7"/>
+      <c r="J187" s="7"/>
     </row>
     <row r="188">
       <c r="A188" s="4">
@@ -5735,20 +5733,20 @@
         <v>187</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="D188" s="4">
-        <v>10000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E188" s="7"/>
       <c r="F188" s="7"/>
-      <c r="G188" s="7"/>
-      <c r="H188" s="7"/>
-      <c r="I188" s="7"/>
-      <c r="J188" s="7"/>
+      <c r="G188" s="4"/>
+      <c r="H188" s="4"/>
+      <c r="I188" s="4"/>
+      <c r="J188" s="4"/>
     </row>
     <row r="189">
       <c r="A189" s="4">
@@ -5756,10 +5754,10 @@
         <v>188</v>
       </c>
       <c r="B189" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C189" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>199</v>
       </c>
       <c r="D189" s="4">
         <v>2000.0</v>
@@ -5788,7 +5786,7 @@
         <v>202</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D190" s="4">
         <v>10000.0</v>
@@ -5809,7 +5807,7 @@
         <v>203</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D191" s="4">
         <v>2000.0</v>
@@ -5838,7 +5836,7 @@
         <v>204</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D192" s="4">
         <v>10000.0</v>
@@ -5859,7 +5857,7 @@
         <v>205</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D193" s="4">
         <v>2000.0</v>
@@ -5870,13 +5868,13 @@
         <v>6.0</v>
       </c>
       <c r="H193" s="4">
-        <v>6000.0</v>
+        <v>5500.0</v>
       </c>
       <c r="I193" s="4">
         <v>12.0</v>
       </c>
       <c r="J193" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
     </row>
     <row r="194">
@@ -5888,10 +5886,10 @@
         <v>206</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D194" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E194" s="7"/>
       <c r="F194" s="7"/>
@@ -5909,7 +5907,7 @@
         <v>207</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D195" s="4">
         <v>2000.0</v>
@@ -5938,7 +5936,7 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D196" s="4">
         <v>11000.0</v>
@@ -5959,7 +5957,7 @@
         <v>209</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D197" s="4">
         <v>2000.0</v>
@@ -5970,13 +5968,13 @@
         <v>6.0</v>
       </c>
       <c r="H197" s="4">
-        <v>8000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="I197" s="4">
         <v>12.0</v>
       </c>
       <c r="J197" s="4">
-        <v>15000.0</v>
+        <v>11000.0</v>
       </c>
     </row>
     <row r="198">
@@ -5988,10 +5986,10 @@
         <v>210</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D198" s="4">
-        <v>15000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="E198" s="7"/>
       <c r="F198" s="7"/>
@@ -6009,17 +6007,25 @@
         <v>211</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D199" s="4">
-        <v>15000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E199" s="7"/>
       <c r="F199" s="7"/>
-      <c r="G199" s="7"/>
-      <c r="H199" s="7"/>
-      <c r="I199" s="7"/>
-      <c r="J199" s="7"/>
+      <c r="G199" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H199" s="4">
+        <v>8000.0</v>
+      </c>
+      <c r="I199" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J199" s="4">
+        <v>15000.0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="4">
@@ -6030,29 +6036,17 @@
         <v>212</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D200" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E200" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F200" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="G200" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H200" s="4">
-        <v>8500.0</v>
-      </c>
-      <c r="I200" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J200" s="4">
-        <v>16000.0</v>
-      </c>
+        <v>15000.0</v>
+      </c>
+      <c r="E200" s="7"/>
+      <c r="F200" s="7"/>
+      <c r="G200" s="7"/>
+      <c r="H200" s="7"/>
+      <c r="I200" s="7"/>
+      <c r="J200" s="7"/>
     </row>
     <row r="201">
       <c r="A201" s="4">
@@ -6063,10 +6057,10 @@
         <v>213</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D201" s="4">
-        <v>16000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E201" s="7"/>
       <c r="F201" s="7"/>
@@ -6084,24 +6078,28 @@
         <v>214</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D202" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E202" s="7"/>
-      <c r="F202" s="7"/>
+      <c r="E202" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F202" s="4">
+        <v>5000.0</v>
+      </c>
       <c r="G202" s="4">
         <v>6.0</v>
       </c>
       <c r="H202" s="4">
-        <v>9000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="I202" s="4">
         <v>12.0</v>
       </c>
       <c r="J202" s="4">
-        <v>17000.0</v>
+        <v>16000.0</v>
       </c>
     </row>
     <row r="203">
@@ -6113,10 +6111,10 @@
         <v>215</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D203" s="4">
-        <v>17000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E203" s="7"/>
       <c r="F203" s="7"/>
@@ -6134,7 +6132,7 @@
         <v>216</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D204" s="4">
         <v>2000.0</v>
@@ -6163,7 +6161,7 @@
         <v>217</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D205" s="4">
         <v>17000.0</v>
@@ -6184,28 +6182,24 @@
         <v>218</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D206" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E206" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F206" s="4">
-        <v>5000.0</v>
-      </c>
+      <c r="E206" s="7"/>
+      <c r="F206" s="7"/>
       <c r="G206" s="4">
         <v>6.0</v>
       </c>
       <c r="H206" s="4">
-        <v>9500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="I206" s="4">
         <v>12.0</v>
       </c>
       <c r="J206" s="4">
-        <v>18000.0</v>
+        <v>17000.0</v>
       </c>
     </row>
     <row r="207">
@@ -6217,10 +6211,10 @@
         <v>219</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D207" s="4">
-        <v>18000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E207" s="7"/>
       <c r="F207" s="7"/>
@@ -6238,24 +6232,28 @@
         <v>220</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D208" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E208" s="7"/>
-      <c r="F208" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E208" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F208" s="4">
+        <v>5000.0</v>
+      </c>
       <c r="G208" s="4">
         <v>6.0</v>
       </c>
       <c r="H208" s="4">
-        <v>14500.0</v>
+        <v>9500.0</v>
       </c>
       <c r="I208" s="4">
         <v>12.0</v>
       </c>
       <c r="J208" s="4">
-        <v>28000.0</v>
+        <v>18000.0</v>
       </c>
     </row>
     <row r="209">
@@ -6267,10 +6265,10 @@
         <v>221</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D209" s="4">
-        <v>28000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E209" s="7"/>
       <c r="F209" s="7"/>
@@ -6288,7 +6286,7 @@
         <v>222</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D210" s="4">
         <v>2500.0</v>
@@ -6299,13 +6297,13 @@
         <v>6.0</v>
       </c>
       <c r="H210" s="4">
-        <v>10500.0</v>
+        <v>14500.0</v>
       </c>
       <c r="I210" s="4">
         <v>12.0</v>
       </c>
       <c r="J210" s="4">
-        <v>20000.0</v>
+        <v>28000.0</v>
       </c>
     </row>
     <row r="211">
@@ -6317,10 +6315,10 @@
         <v>223</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D211" s="4">
-        <v>20000.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E211" s="7"/>
       <c r="F211" s="7"/>
@@ -6338,7 +6336,7 @@
         <v>224</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D212" s="4">
         <v>2500.0</v>
@@ -6349,13 +6347,13 @@
         <v>6.0</v>
       </c>
       <c r="H212" s="4">
-        <v>13000.0</v>
+        <v>10500.0</v>
       </c>
       <c r="I212" s="4">
         <v>12.0</v>
       </c>
       <c r="J212" s="4">
-        <v>25000.0</v>
+        <v>20000.0</v>
       </c>
     </row>
     <row r="213">
@@ -6367,10 +6365,10 @@
         <v>225</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D213" s="4">
-        <v>25000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="E213" s="7"/>
       <c r="F213" s="7"/>
@@ -6388,7 +6386,7 @@
         <v>226</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D214" s="4">
         <v>2500.0</v>
@@ -6399,13 +6397,13 @@
         <v>6.0</v>
       </c>
       <c r="H214" s="4">
-        <v>11000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I214" s="4">
         <v>12.0</v>
       </c>
       <c r="J214" s="4">
-        <v>21000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="215">
@@ -6417,10 +6415,10 @@
         <v>227</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D215" s="4">
-        <v>21000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E215" s="7"/>
       <c r="F215" s="7"/>
@@ -6438,7 +6436,7 @@
         <v>228</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D216" s="4">
         <v>2500.0</v>
@@ -6449,13 +6447,13 @@
         <v>6.0</v>
       </c>
       <c r="H216" s="4">
-        <v>13000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="I216" s="4">
         <v>12.0</v>
       </c>
       <c r="J216" s="4">
-        <v>25000.0</v>
+        <v>21000.0</v>
       </c>
     </row>
     <row r="217">
@@ -6467,10 +6465,10 @@
         <v>229</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D217" s="4">
-        <v>25000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E217" s="7"/>
       <c r="F217" s="7"/>
@@ -6488,7 +6486,7 @@
         <v>230</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D218" s="4">
         <v>2500.0</v>
@@ -6499,13 +6497,13 @@
         <v>6.0</v>
       </c>
       <c r="H218" s="4">
-        <v>14000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I218" s="4">
         <v>12.0</v>
       </c>
       <c r="J218" s="4">
-        <v>28000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="219">
@@ -6517,10 +6515,10 @@
         <v>231</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D219" s="4">
-        <v>28000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E219" s="7"/>
       <c r="F219" s="7"/>
@@ -6538,7 +6536,7 @@
         <v>232</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D220" s="4">
         <v>2500.0</v>
@@ -6549,13 +6547,13 @@
         <v>6.0</v>
       </c>
       <c r="H220" s="4">
-        <v>13000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="I220" s="4">
         <v>12.0</v>
       </c>
       <c r="J220" s="4">
-        <v>25000.0</v>
+        <v>28000.0</v>
       </c>
     </row>
     <row r="221">
@@ -6567,10 +6565,10 @@
         <v>233</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D221" s="4">
-        <v>25000.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E221" s="7"/>
       <c r="F221" s="7"/>
@@ -6588,7 +6586,7 @@
         <v>234</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D222" s="4">
         <v>2500.0</v>
@@ -6599,13 +6597,13 @@
         <v>6.0</v>
       </c>
       <c r="H222" s="4">
-        <v>14000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I222" s="4">
         <v>12.0</v>
       </c>
       <c r="J222" s="4">
-        <v>27000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="223">
@@ -6617,10 +6615,10 @@
         <v>235</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D223" s="4">
-        <v>27000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E223" s="7"/>
       <c r="F223" s="7"/>
@@ -6638,7 +6636,7 @@
         <v>236</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D224" s="4">
         <v>2500.0</v>
@@ -6667,7 +6665,7 @@
         <v>237</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D225" s="4">
         <v>27000.0</v>
@@ -6688,17 +6686,25 @@
         <v>238</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D226" s="4">
-        <v>34000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E226" s="7"/>
       <c r="F226" s="7"/>
-      <c r="G226" s="7"/>
-      <c r="H226" s="7"/>
-      <c r="I226" s="7"/>
-      <c r="J226" s="7"/>
+      <c r="G226" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H226" s="4">
+        <v>14000.0</v>
+      </c>
+      <c r="I226" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J226" s="4">
+        <v>27000.0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="4">
@@ -6709,7 +6715,7 @@
         <v>239</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D227" s="4">
         <v>27000.0</v>
@@ -6730,19 +6736,17 @@
         <v>240</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D228" s="4">
-        <v>37000.0</v>
+        <v>34000.0</v>
       </c>
       <c r="E228" s="7"/>
       <c r="F228" s="7"/>
-      <c r="G228" s="4"/>
-      <c r="H228" s="4"/>
-      <c r="I228" s="4"/>
-      <c r="J228" s="4">
-        <v>37000.0</v>
-      </c>
+      <c r="G228" s="7"/>
+      <c r="H228" s="7"/>
+      <c r="I228" s="7"/>
+      <c r="J228" s="7"/>
     </row>
     <row r="229">
       <c r="A229" s="4">
@@ -6753,10 +6757,10 @@
         <v>241</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D229" s="4">
-        <v>16000.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E229" s="7"/>
       <c r="F229" s="7"/>
@@ -6774,17 +6778,19 @@
         <v>242</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D230" s="4">
-        <v>43000.0</v>
+        <v>37000.0</v>
       </c>
       <c r="E230" s="7"/>
       <c r="F230" s="7"/>
-      <c r="G230" s="7"/>
-      <c r="H230" s="7"/>
-      <c r="I230" s="7"/>
-      <c r="J230" s="7"/>
+      <c r="G230" s="4"/>
+      <c r="H230" s="4"/>
+      <c r="I230" s="4"/>
+      <c r="J230" s="4">
+        <v>37000.0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="4">
@@ -6795,10 +6801,10 @@
         <v>243</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D231" s="4">
-        <v>23000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E231" s="7"/>
       <c r="F231" s="7"/>
@@ -6816,10 +6822,10 @@
         <v>244</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D232" s="4">
-        <v>17000.0</v>
+        <v>43000.0</v>
       </c>
       <c r="E232" s="7"/>
       <c r="F232" s="7"/>
@@ -6837,10 +6843,10 @@
         <v>245</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D233" s="4">
-        <v>29000.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="7"/>
@@ -6858,10 +6864,10 @@
         <v>246</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D234" s="4">
-        <v>13000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E234" s="7"/>
       <c r="F234" s="7"/>
@@ -6879,10 +6885,10 @@
         <v>247</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>248</v>
+        <v>201</v>
       </c>
       <c r="D235" s="4">
-        <v>500.0</v>
+        <v>29000.0</v>
       </c>
       <c r="E235" s="7"/>
       <c r="F235" s="7"/>
@@ -6897,13 +6903,13 @@
         <v>235</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>248</v>
+        <v>201</v>
       </c>
       <c r="D236" s="4">
-        <v>4000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="E236" s="7"/>
       <c r="F236" s="7"/>
@@ -6918,13 +6924,13 @@
         <v>236</v>
       </c>
       <c r="B237" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C237" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="C237" s="5" t="s">
-        <v>248</v>
-      </c>
       <c r="D237" s="4">
-        <v>2500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="7"/>
@@ -6942,17 +6948,13 @@
         <v>251</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D238" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E238" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F238" s="4">
-        <v>14000.0</v>
-      </c>
+        <v>4000.0</v>
+      </c>
+      <c r="E238" s="7"/>
+      <c r="F238" s="7"/>
       <c r="G238" s="7"/>
       <c r="H238" s="7"/>
       <c r="I238" s="7"/>
@@ -6964,13 +6966,13 @@
         <v>238</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D239" s="4">
-        <v>109000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E239" s="7"/>
       <c r="F239" s="7"/>
@@ -6985,10 +6987,10 @@
         <v>239</v>
       </c>
       <c r="B240" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C240" s="5" t="s">
         <v>254</v>
-      </c>
-      <c r="C240" s="5" t="s">
-        <v>252</v>
       </c>
       <c r="D240" s="4">
         <v>3000.0</v>
@@ -7013,7 +7015,7 @@
         <v>255</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D241" s="4">
         <v>109000.0</v>
@@ -7034,13 +7036,17 @@
         <v>256</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D242" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E242" s="7"/>
-      <c r="F242" s="7"/>
+      <c r="E242" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F242" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G242" s="7"/>
       <c r="H242" s="7"/>
       <c r="I242" s="7"/>
@@ -7055,10 +7061,10 @@
         <v>257</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D243" s="4">
-        <v>114000.0</v>
+        <v>109000.0</v>
       </c>
       <c r="E243" s="7"/>
       <c r="F243" s="7"/>
@@ -7076,7 +7082,7 @@
         <v>258</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D244" s="4">
         <v>3000.0</v>
@@ -7097,17 +7103,13 @@
         <v>259</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D245" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E245" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F245" s="4">
-        <v>39000.0</v>
-      </c>
+        <v>114000.0</v>
+      </c>
+      <c r="E245" s="7"/>
+      <c r="F245" s="7"/>
       <c r="G245" s="7"/>
       <c r="H245" s="7"/>
       <c r="I245" s="7"/>
@@ -7122,10 +7124,10 @@
         <v>260</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D246" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E246" s="7"/>
       <c r="F246" s="7"/>
@@ -7143,13 +7145,17 @@
         <v>261</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D247" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E247" s="7"/>
-      <c r="F247" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E247" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F247" s="4">
+        <v>39000.0</v>
+      </c>
       <c r="G247" s="7"/>
       <c r="H247" s="7"/>
       <c r="I247" s="7"/>
@@ -7164,7 +7170,7 @@
         <v>262</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D248" s="4">
         <v>114000.0</v>
@@ -7185,7 +7191,7 @@
         <v>263</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D249" s="4">
         <v>3000.0</v>
@@ -7206,7 +7212,7 @@
         <v>264</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D250" s="4">
         <v>114000.0</v>
@@ -7227,7 +7233,7 @@
         <v>265</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D251" s="4">
         <v>3000.0</v>
@@ -7248,7 +7254,7 @@
         <v>266</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D252" s="4">
         <v>114000.0</v>
@@ -7269,7 +7275,7 @@
         <v>267</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D253" s="4">
         <v>3000.0</v>
@@ -7290,10 +7296,10 @@
         <v>268</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D254" s="4">
-        <v>107000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E254" s="7"/>
       <c r="F254" s="7"/>
@@ -7311,7 +7317,7 @@
         <v>269</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D255" s="4">
         <v>3000.0</v>
@@ -7332,17 +7338,17 @@
         <v>270</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D256" s="4">
-        <v>112000.0</v>
-      </c>
-      <c r="E256" s="6"/>
-      <c r="F256" s="6"/>
-      <c r="G256" s="6"/>
-      <c r="H256" s="6"/>
-      <c r="I256" s="6"/>
-      <c r="J256" s="6"/>
+        <v>107000.0</v>
+      </c>
+      <c r="E256" s="7"/>
+      <c r="F256" s="7"/>
+      <c r="G256" s="7"/>
+      <c r="H256" s="7"/>
+      <c r="I256" s="7"/>
+      <c r="J256" s="7"/>
     </row>
     <row r="257">
       <c r="A257" s="4">
@@ -7353,17 +7359,13 @@
         <v>271</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D257" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E257" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F257" s="4">
-        <v>19000.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E257" s="7"/>
+      <c r="F257" s="7"/>
       <c r="G257" s="7"/>
       <c r="H257" s="7"/>
       <c r="I257" s="7"/>
@@ -7378,21 +7380,17 @@
         <v>272</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D258" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E258" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F258" s="4">
-        <v>19000.0</v>
-      </c>
-      <c r="G258" s="7"/>
-      <c r="H258" s="7"/>
-      <c r="I258" s="7"/>
-      <c r="J258" s="7"/>
+        <v>112000.0</v>
+      </c>
+      <c r="E258" s="6"/>
+      <c r="F258" s="6"/>
+      <c r="G258" s="6"/>
+      <c r="H258" s="6"/>
+      <c r="I258" s="6"/>
+      <c r="J258" s="6"/>
     </row>
     <row r="259">
       <c r="A259" s="4">
@@ -7403,13 +7401,17 @@
         <v>273</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D259" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E259" s="4"/>
-      <c r="F259" s="4"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E259" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F259" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G259" s="7"/>
       <c r="H259" s="7"/>
       <c r="I259" s="7"/>
@@ -7424,13 +7426,17 @@
         <v>274</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D260" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E260" s="4"/>
-      <c r="F260" s="4"/>
+      <c r="E260" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F260" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G260" s="7"/>
       <c r="H260" s="7"/>
       <c r="I260" s="7"/>
@@ -7445,7 +7451,7 @@
         <v>275</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D261" s="4">
         <v>86000.0</v>
@@ -7466,18 +7472,14 @@
         <v>276</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D262" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E262" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F262" s="4">
-        <v>19500.0</v>
-      </c>
-      <c r="G262" s="4"/>
+      <c r="E262" s="4"/>
+      <c r="F262" s="4"/>
+      <c r="G262" s="7"/>
       <c r="H262" s="7"/>
       <c r="I262" s="7"/>
       <c r="J262" s="7"/>
@@ -7491,17 +7493,13 @@
         <v>277</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D263" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E263" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F263" s="4">
-        <v>6000.0</v>
-      </c>
+        <v>86000.0</v>
+      </c>
+      <c r="E263" s="4"/>
+      <c r="F263" s="4"/>
       <c r="G263" s="7"/>
       <c r="H263" s="7"/>
       <c r="I263" s="7"/>
@@ -7516,14 +7514,18 @@
         <v>278</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D264" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E264" s="7"/>
-      <c r="F264" s="7"/>
-      <c r="G264" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E264" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F264" s="4">
+        <v>19500.0</v>
+      </c>
+      <c r="G264" s="4"/>
       <c r="H264" s="7"/>
       <c r="I264" s="7"/>
       <c r="J264" s="7"/>
@@ -7537,13 +7539,17 @@
         <v>279</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D265" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E265" s="7"/>
-      <c r="F265" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E265" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F265" s="4">
+        <v>6000.0</v>
+      </c>
       <c r="G265" s="7"/>
       <c r="H265" s="7"/>
       <c r="I265" s="7"/>
@@ -7558,10 +7564,10 @@
         <v>280</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D266" s="4">
-        <v>89000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E266" s="7"/>
       <c r="F266" s="7"/>
@@ -7579,10 +7585,10 @@
         <v>281</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D267" s="4">
-        <v>7500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E267" s="7"/>
       <c r="F267" s="7"/>
@@ -7600,10 +7606,10 @@
         <v>282</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D268" s="4">
-        <v>5000.0</v>
+        <v>89000.0</v>
       </c>
       <c r="E268" s="7"/>
       <c r="F268" s="7"/>
@@ -7621,10 +7627,10 @@
         <v>283</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D269" s="4">
-        <v>3000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E269" s="7"/>
       <c r="F269" s="7"/>
@@ -7642,17 +7648,17 @@
         <v>284</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>285</v>
+        <v>254</v>
       </c>
       <c r="D270" s="4">
-        <v>80000.0</v>
-      </c>
-      <c r="E270" s="6"/>
-      <c r="F270" s="6"/>
-      <c r="G270" s="6"/>
-      <c r="H270" s="6"/>
-      <c r="I270" s="6"/>
-      <c r="J270" s="6"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E270" s="7"/>
+      <c r="F270" s="7"/>
+      <c r="G270" s="7"/>
+      <c r="H270" s="7"/>
+      <c r="I270" s="7"/>
+      <c r="J270" s="7"/>
     </row>
     <row r="271">
       <c r="A271" s="4">
@@ -7663,10 +7669,10 @@
         <v>285</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>285</v>
+        <v>254</v>
       </c>
       <c r="D271" s="4">
-        <v>14000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E271" s="7"/>
       <c r="F271" s="7"/>
@@ -7681,20 +7687,20 @@
         <v>271</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D272" s="4">
-        <v>14500.0</v>
-      </c>
-      <c r="E272" s="7"/>
-      <c r="F272" s="7"/>
-      <c r="G272" s="7"/>
-      <c r="H272" s="7"/>
-      <c r="I272" s="7"/>
-      <c r="J272" s="7"/>
+        <v>80000.0</v>
+      </c>
+      <c r="E272" s="6"/>
+      <c r="F272" s="6"/>
+      <c r="G272" s="6"/>
+      <c r="H272" s="6"/>
+      <c r="I272" s="6"/>
+      <c r="J272" s="6"/>
     </row>
     <row r="273">
       <c r="A273" s="4">
@@ -7702,13 +7708,13 @@
         <v>272</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D273" s="4">
-        <v>15000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E273" s="7"/>
       <c r="F273" s="7"/>
@@ -7723,13 +7729,13 @@
         <v>273</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D274" s="4">
-        <v>15500.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E274" s="7"/>
       <c r="F274" s="7"/>
@@ -7744,13 +7750,13 @@
         <v>274</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C275" s="5" t="s">
         <v>287</v>
       </c>
       <c r="D275" s="4">
-        <v>1500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E275" s="7"/>
       <c r="F275" s="7"/>
@@ -7765,13 +7771,13 @@
         <v>275</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C276" s="5" t="s">
         <v>287</v>
       </c>
       <c r="D276" s="4">
-        <v>12500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E276" s="7"/>
       <c r="F276" s="7"/>
@@ -7786,13 +7792,13 @@
         <v>276</v>
       </c>
       <c r="B277" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C277" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="C277" s="5" t="s">
-        <v>287</v>
-      </c>
       <c r="D277" s="4">
-        <v>500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E277" s="7"/>
       <c r="F277" s="7"/>
@@ -7810,10 +7816,10 @@
         <v>290</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D278" s="4">
-        <v>4500.0</v>
+        <v>12500.0</v>
       </c>
       <c r="E278" s="7"/>
       <c r="F278" s="7"/>
@@ -7831,10 +7837,10 @@
         <v>291</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D279" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E279" s="7"/>
       <c r="F279" s="7"/>
@@ -7852,10 +7858,10 @@
         <v>292</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D280" s="4">
-        <v>23000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E280" s="7"/>
       <c r="F280" s="7"/>
@@ -7873,17 +7879,13 @@
         <v>293</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D281" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E281" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F281" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E281" s="7"/>
+      <c r="F281" s="7"/>
       <c r="G281" s="7"/>
       <c r="H281" s="7"/>
       <c r="I281" s="7"/>
@@ -7898,13 +7900,13 @@
         <v>294</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D282" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E282" s="4"/>
-      <c r="F282" s="4"/>
+        <v>23000.0</v>
+      </c>
+      <c r="E282" s="7"/>
+      <c r="F282" s="7"/>
       <c r="G282" s="7"/>
       <c r="H282" s="7"/>
       <c r="I282" s="7"/>
@@ -7919,16 +7921,16 @@
         <v>295</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D283" s="4">
-        <v>2500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E283" s="4">
         <v>5.0</v>
       </c>
       <c r="F283" s="4">
-        <v>9000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="G283" s="7"/>
       <c r="H283" s="7"/>
@@ -7944,10 +7946,10 @@
         <v>296</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D284" s="4">
-        <v>9000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E284" s="4"/>
       <c r="F284" s="4"/>
@@ -7965,16 +7967,16 @@
         <v>297</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D285" s="4">
-        <v>2000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E285" s="4">
         <v>5.0</v>
       </c>
       <c r="F285" s="4">
-        <v>7500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="G285" s="7"/>
       <c r="H285" s="7"/>
@@ -7990,13 +7992,13 @@
         <v>298</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D286" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E286" s="7"/>
-      <c r="F286" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E286" s="4"/>
+      <c r="F286" s="4"/>
       <c r="G286" s="7"/>
       <c r="H286" s="7"/>
       <c r="I286" s="7"/>
@@ -8011,13 +8013,17 @@
         <v>299</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="D287" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E287" s="7"/>
-      <c r="F287" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E287" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F287" s="4">
+        <v>7500.0</v>
+      </c>
       <c r="G287" s="7"/>
       <c r="H287" s="7"/>
       <c r="I287" s="7"/>
@@ -8029,13 +8035,13 @@
         <v>287</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="D288" s="4">
-        <v>10000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E288" s="7"/>
       <c r="F288" s="7"/>
@@ -8050,13 +8056,13 @@
         <v>288</v>
       </c>
       <c r="B289" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C289" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="C289" s="5" t="s">
-        <v>300</v>
-      </c>
       <c r="D289" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E289" s="7"/>
       <c r="F289" s="7"/>
@@ -8074,10 +8080,10 @@
         <v>303</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D290" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E290" s="7"/>
       <c r="F290" s="7"/>
@@ -8095,10 +8101,10 @@
         <v>304</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D291" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E291" s="7"/>
       <c r="F291" s="7"/>
@@ -8116,10 +8122,10 @@
         <v>305</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D292" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E292" s="7"/>
       <c r="F292" s="7"/>
@@ -8137,10 +8143,10 @@
         <v>306</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D293" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E293" s="7"/>
       <c r="F293" s="7"/>
@@ -8158,10 +8164,10 @@
         <v>307</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D294" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E294" s="7"/>
       <c r="F294" s="7"/>
@@ -8179,10 +8185,10 @@
         <v>308</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D295" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E295" s="7"/>
       <c r="F295" s="7"/>
@@ -8200,10 +8206,10 @@
         <v>309</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D296" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E296" s="7"/>
       <c r="F296" s="7"/>
@@ -8221,7 +8227,7 @@
         <v>310</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D297" s="4">
         <v>1000.0</v>
@@ -8242,7 +8248,7 @@
         <v>311</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D298" s="4">
         <v>10000.0</v>
@@ -8263,10 +8269,10 @@
         <v>312</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D299" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E299" s="7"/>
       <c r="F299" s="7"/>
@@ -8284,10 +8290,10 @@
         <v>313</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D300" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E300" s="7"/>
       <c r="F300" s="7"/>
@@ -8305,10 +8311,10 @@
         <v>314</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D301" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E301" s="7"/>
       <c r="F301" s="7"/>
@@ -8326,7 +8332,7 @@
         <v>315</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D302" s="4">
         <v>500.0</v>
@@ -8347,7 +8353,7 @@
         <v>316</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D303" s="4">
         <v>5000.0</v>
@@ -8368,10 +8374,10 @@
         <v>317</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D304" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E304" s="7"/>
       <c r="F304" s="7"/>
@@ -8389,10 +8395,10 @@
         <v>318</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D305" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E305" s="7"/>
       <c r="F305" s="7"/>
@@ -8410,10 +8416,10 @@
         <v>319</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D306" s="4">
-        <v>2000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E306" s="7"/>
       <c r="F306" s="7"/>
@@ -8431,10 +8437,10 @@
         <v>320</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D307" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E307" s="7"/>
       <c r="F307" s="7"/>
@@ -8452,10 +8458,10 @@
         <v>321</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D308" s="4">
-        <v>1000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E308" s="7"/>
       <c r="F308" s="7"/>
@@ -8473,7 +8479,7 @@
         <v>322</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D309" s="4">
         <v>5000.0</v>
@@ -8494,7 +8500,7 @@
         <v>323</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D310" s="4">
         <v>1000.0</v>
@@ -8515,7 +8521,7 @@
         <v>324</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D311" s="4">
         <v>5000.0</v>
@@ -8536,7 +8542,7 @@
         <v>325</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D312" s="4">
         <v>1000.0</v>
@@ -8557,7 +8563,7 @@
         <v>326</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D313" s="4">
         <v>5000.0</v>
@@ -8578,10 +8584,10 @@
         <v>327</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D314" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E314" s="7"/>
       <c r="F314" s="7"/>
@@ -8599,10 +8605,10 @@
         <v>328</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D315" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E315" s="7"/>
       <c r="F315" s="7"/>
@@ -8620,10 +8626,10 @@
         <v>329</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D316" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E316" s="7"/>
       <c r="F316" s="7"/>
@@ -8641,10 +8647,10 @@
         <v>330</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D317" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E317" s="7"/>
       <c r="F317" s="7"/>
@@ -8662,10 +8668,10 @@
         <v>331</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D318" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E318" s="7"/>
       <c r="F318" s="7"/>
@@ -8683,7 +8689,7 @@
         <v>332</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D319" s="4">
         <v>5000.0</v>
@@ -8704,7 +8710,7 @@
         <v>333</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D320" s="4">
         <v>500.0</v>
@@ -8725,7 +8731,7 @@
         <v>334</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D321" s="4">
         <v>5000.0</v>
@@ -8746,10 +8752,10 @@
         <v>335</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D322" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E322" s="7"/>
       <c r="F322" s="7"/>
@@ -8767,7 +8773,7 @@
         <v>336</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D323" s="4">
         <v>5000.0</v>
@@ -8788,17 +8794,13 @@
         <v>337</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D324" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E324" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F324" s="4">
-        <v>4500.0</v>
-      </c>
+      <c r="E324" s="7"/>
+      <c r="F324" s="7"/>
       <c r="G324" s="7"/>
       <c r="H324" s="7"/>
       <c r="I324" s="7"/>
@@ -8813,10 +8815,10 @@
         <v>338</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D325" s="4">
-        <v>4500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E325" s="7"/>
       <c r="F325" s="7"/>
@@ -8834,13 +8836,17 @@
         <v>339</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D326" s="4">
-        <v>51000.0</v>
-      </c>
-      <c r="E326" s="4"/>
-      <c r="F326" s="4"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E326" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F326" s="4">
+        <v>4500.0</v>
+      </c>
       <c r="G326" s="7"/>
       <c r="H326" s="7"/>
       <c r="I326" s="7"/>
@@ -8855,17 +8861,13 @@
         <v>340</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D327" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E327" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F327" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>4500.0</v>
+      </c>
+      <c r="E327" s="7"/>
+      <c r="F327" s="7"/>
       <c r="G327" s="7"/>
       <c r="H327" s="7"/>
       <c r="I327" s="7"/>
@@ -8880,13 +8882,13 @@
         <v>341</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D328" s="4">
-        <v>52000.0</v>
-      </c>
-      <c r="E328" s="7"/>
-      <c r="F328" s="7"/>
+        <v>51000.0</v>
+      </c>
+      <c r="E328" s="4"/>
+      <c r="F328" s="4"/>
       <c r="G328" s="7"/>
       <c r="H328" s="7"/>
       <c r="I328" s="7"/>
@@ -8901,13 +8903,17 @@
         <v>342</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D329" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E329" s="7"/>
-      <c r="F329" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E329" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F329" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G329" s="7"/>
       <c r="H329" s="7"/>
       <c r="I329" s="7"/>
@@ -8922,10 +8928,10 @@
         <v>343</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D330" s="4">
-        <v>5000.0</v>
+        <v>52000.0</v>
       </c>
       <c r="E330" s="7"/>
       <c r="F330" s="7"/>
@@ -8943,17 +8949,13 @@
         <v>344</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D331" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E331" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F331" s="4">
-        <v>17000.0</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E331" s="7"/>
+      <c r="F331" s="7"/>
       <c r="G331" s="7"/>
       <c r="H331" s="7"/>
       <c r="I331" s="7"/>
@@ -8968,7 +8970,7 @@
         <v>345</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D332" s="4">
         <v>5000.0</v>
@@ -8989,16 +8991,16 @@
         <v>346</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D333" s="4">
-        <v>7000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E333" s="4">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F333" s="4">
-        <v>32500.0</v>
+        <v>17000.0</v>
       </c>
       <c r="G333" s="7"/>
       <c r="H333" s="7"/>
@@ -9014,10 +9016,10 @@
         <v>347</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D334" s="4">
-        <v>7500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E334" s="7"/>
       <c r="F334" s="7"/>
@@ -9035,13 +9037,17 @@
         <v>348</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D335" s="4">
-        <v>9500.0</v>
-      </c>
-      <c r="E335" s="7"/>
-      <c r="F335" s="7"/>
+        <v>7000.0</v>
+      </c>
+      <c r="E335" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F335" s="4">
+        <v>32500.0</v>
+      </c>
       <c r="G335" s="7"/>
       <c r="H335" s="7"/>
       <c r="I335" s="7"/>
@@ -9056,10 +9062,10 @@
         <v>349</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D336" s="4">
-        <v>3500.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E336" s="7"/>
       <c r="F336" s="7"/>
@@ -9077,10 +9083,10 @@
         <v>350</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D337" s="4">
-        <v>5000.0</v>
+        <v>9500.0</v>
       </c>
       <c r="E337" s="7"/>
       <c r="F337" s="7"/>
@@ -9098,17 +9104,13 @@
         <v>351</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D338" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E338" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F338" s="4">
-        <v>22500.0</v>
-      </c>
+        <v>3500.0</v>
+      </c>
+      <c r="E338" s="7"/>
+      <c r="F338" s="7"/>
       <c r="G338" s="7"/>
       <c r="H338" s="7"/>
       <c r="I338" s="7"/>
@@ -9123,17 +9125,13 @@
         <v>352</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D339" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E339" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F339" s="4">
-        <v>12500.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E339" s="7"/>
+      <c r="F339" s="7"/>
       <c r="G339" s="7"/>
       <c r="H339" s="7"/>
       <c r="I339" s="7"/>
@@ -9148,13 +9146,17 @@
         <v>353</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D340" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E340" s="4"/>
-      <c r="F340" s="4"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E340" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F340" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G340" s="7"/>
       <c r="H340" s="7"/>
       <c r="I340" s="7"/>
@@ -9169,14 +9171,18 @@
         <v>354</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D341" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E341" s="4"/>
-      <c r="F341" s="4"/>
-      <c r="G341" s="4"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E341" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F341" s="4">
+        <v>12500.0</v>
+      </c>
+      <c r="G341" s="7"/>
       <c r="H341" s="7"/>
       <c r="I341" s="7"/>
       <c r="J341" s="7"/>
@@ -9190,17 +9196,13 @@
         <v>355</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D342" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E342" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F342" s="4">
-        <v>11500.0</v>
-      </c>
+        <v>3500.0</v>
+      </c>
+      <c r="E342" s="4"/>
+      <c r="F342" s="4"/>
       <c r="G342" s="7"/>
       <c r="H342" s="7"/>
       <c r="I342" s="7"/>
@@ -9215,14 +9217,14 @@
         <v>356</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D343" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E343" s="7"/>
-      <c r="F343" s="7"/>
-      <c r="G343" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E343" s="4"/>
+      <c r="F343" s="4"/>
+      <c r="G343" s="4"/>
       <c r="H343" s="7"/>
       <c r="I343" s="7"/>
       <c r="J343" s="7"/>
@@ -9236,16 +9238,16 @@
         <v>357</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D344" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E344" s="4">
         <v>5.0</v>
       </c>
       <c r="F344" s="4">
-        <v>22500.0</v>
+        <v>11500.0</v>
       </c>
       <c r="G344" s="7"/>
       <c r="H344" s="7"/>
@@ -9261,10 +9263,10 @@
         <v>358</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D345" s="4">
-        <v>1000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E345" s="7"/>
       <c r="F345" s="7"/>
@@ -9282,13 +9284,17 @@
         <v>359</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D346" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E346" s="7"/>
-      <c r="F346" s="7"/>
+      <c r="E346" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F346" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G346" s="7"/>
       <c r="H346" s="7"/>
       <c r="I346" s="7"/>
@@ -9303,10 +9309,10 @@
         <v>360</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D347" s="4">
-        <v>3000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E347" s="7"/>
       <c r="F347" s="7"/>
@@ -9324,10 +9330,10 @@
         <v>361</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D348" s="4">
-        <v>14000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E348" s="7"/>
       <c r="F348" s="7"/>
@@ -9345,10 +9351,10 @@
         <v>362</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>363</v>
+        <v>302</v>
       </c>
       <c r="D349" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E349" s="7"/>
       <c r="F349" s="7"/>
@@ -9363,13 +9369,13 @@
         <v>349</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>363</v>
+        <v>302</v>
       </c>
       <c r="D350" s="4">
-        <v>4000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E350" s="7"/>
       <c r="F350" s="7"/>
@@ -9384,10 +9390,10 @@
         <v>350</v>
       </c>
       <c r="B351" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C351" s="5" t="s">
         <v>365</v>
-      </c>
-      <c r="C351" s="5" t="s">
-        <v>363</v>
       </c>
       <c r="D351" s="4">
         <v>1000.0</v>
@@ -9408,10 +9414,10 @@
         <v>366</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D352" s="4">
-        <v>10000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E352" s="7"/>
       <c r="F352" s="7"/>
@@ -9429,7 +9435,7 @@
         <v>367</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D353" s="4">
         <v>1000.0</v>
@@ -9450,7 +9456,7 @@
         <v>368</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D354" s="4">
         <v>10000.0</v>
@@ -9471,10 +9477,10 @@
         <v>369</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D355" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E355" s="7"/>
       <c r="F355" s="7"/>
@@ -9492,10 +9498,10 @@
         <v>370</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D356" s="4">
-        <v>2500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E356" s="7"/>
       <c r="F356" s="7"/>
@@ -9513,10 +9519,10 @@
         <v>371</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D357" s="4">
-        <v>3000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E357" s="7"/>
       <c r="F357" s="7"/>
@@ -9534,10 +9540,10 @@
         <v>372</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D358" s="4">
-        <v>5000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E358" s="7"/>
       <c r="F358" s="7"/>
@@ -9555,7 +9561,7 @@
         <v>373</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D359" s="4">
         <v>3000.0</v>
@@ -9576,17 +9582,13 @@
         <v>374</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D360" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E360" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F360" s="4">
-        <v>3000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E360" s="7"/>
+      <c r="F360" s="7"/>
       <c r="G360" s="7"/>
       <c r="H360" s="7"/>
       <c r="I360" s="7"/>
@@ -9601,10 +9603,10 @@
         <v>375</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D361" s="4">
-        <v>500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E361" s="7"/>
       <c r="F361" s="7"/>
@@ -9622,13 +9624,17 @@
         <v>376</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D362" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E362" s="7"/>
-      <c r="F362" s="7"/>
+      <c r="E362" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F362" s="4">
+        <v>3000.0</v>
+      </c>
       <c r="G362" s="7"/>
       <c r="H362" s="7"/>
       <c r="I362" s="7"/>
@@ -9643,10 +9649,10 @@
         <v>377</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D363" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E363" s="7"/>
       <c r="F363" s="7"/>
@@ -9664,10 +9670,10 @@
         <v>378</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D364" s="4">
-        <v>7000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E364" s="7"/>
       <c r="F364" s="7"/>
@@ -9685,10 +9691,10 @@
         <v>379</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D365" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E365" s="7"/>
       <c r="F365" s="7"/>
@@ -9706,10 +9712,10 @@
         <v>380</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D366" s="4">
-        <v>25000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E366" s="7"/>
       <c r="F366" s="7"/>
@@ -9727,10 +9733,10 @@
         <v>381</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D367" s="4">
-        <v>8000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E367" s="7"/>
       <c r="F367" s="7"/>
@@ -9748,10 +9754,10 @@
         <v>382</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D368" s="4">
-        <v>4000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E368" s="7"/>
       <c r="F368" s="7"/>
@@ -9769,10 +9775,10 @@
         <v>383</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="D369" s="4">
-        <v>2000.0</v>
+        <v>8000.0</v>
       </c>
       <c r="E369" s="7"/>
       <c r="F369" s="7"/>
@@ -9787,13 +9793,13 @@
         <v>369</v>
       </c>
       <c r="B370" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="D370" s="4">
-        <v>45000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E370" s="7"/>
       <c r="F370" s="7"/>
@@ -9808,13 +9814,13 @@
         <v>370</v>
       </c>
       <c r="B371" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C371" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="C371" s="5" t="s">
-        <v>384</v>
-      </c>
       <c r="D371" s="4">
-        <v>2500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E371" s="7"/>
       <c r="F371" s="7"/>
@@ -9832,10 +9838,10 @@
         <v>387</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D372" s="4">
-        <v>2500.0</v>
+        <v>45000.0</v>
       </c>
       <c r="E372" s="7"/>
       <c r="F372" s="7"/>
@@ -9853,10 +9859,10 @@
         <v>388</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D373" s="4">
-        <v>4000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E373" s="7"/>
       <c r="F373" s="7"/>
@@ -9874,10 +9880,10 @@
         <v>389</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D374" s="4">
-        <v>40000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E374" s="7"/>
       <c r="F374" s="7"/>
@@ -9895,10 +9901,10 @@
         <v>390</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D375" s="4">
-        <v>5000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E375" s="7"/>
       <c r="F375" s="7"/>
@@ -9916,16 +9922,16 @@
         <v>391</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D376" s="4">
-        <v>46000.0</v>
+        <v>40000.0</v>
       </c>
       <c r="E376" s="7"/>
       <c r="F376" s="7"/>
       <c r="G376" s="7"/>
       <c r="H376" s="7"/>
-      <c r="I376" s="4"/>
+      <c r="I376" s="7"/>
       <c r="J376" s="7"/>
     </row>
     <row r="377">
@@ -9937,16 +9943,16 @@
         <v>392</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D377" s="4">
-        <v>2000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E377" s="7"/>
       <c r="F377" s="7"/>
       <c r="G377" s="7"/>
       <c r="H377" s="7"/>
-      <c r="I377" s="4"/>
+      <c r="I377" s="7"/>
       <c r="J377" s="7"/>
     </row>
     <row r="378">
@@ -9958,10 +9964,10 @@
         <v>393</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D378" s="4">
-        <v>17000.0</v>
+        <v>46000.0</v>
       </c>
       <c r="E378" s="7"/>
       <c r="F378" s="7"/>
@@ -9979,10 +9985,10 @@
         <v>394</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D379" s="4">
-        <v>500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E379" s="7"/>
       <c r="F379" s="7"/>
@@ -10000,16 +10006,16 @@
         <v>395</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D380" s="4">
-        <v>1000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E380" s="7"/>
       <c r="F380" s="7"/>
       <c r="G380" s="7"/>
       <c r="H380" s="7"/>
-      <c r="I380" s="7"/>
+      <c r="I380" s="4"/>
       <c r="J380" s="7"/>
     </row>
     <row r="381">
@@ -10021,16 +10027,16 @@
         <v>396</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D381" s="4">
-        <v>10000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E381" s="7"/>
       <c r="F381" s="7"/>
       <c r="G381" s="7"/>
       <c r="H381" s="7"/>
-      <c r="I381" s="7"/>
+      <c r="I381" s="4"/>
       <c r="J381" s="7"/>
     </row>
     <row r="382">
@@ -10042,10 +10048,10 @@
         <v>397</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D382" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E382" s="7"/>
       <c r="F382" s="7"/>
@@ -10063,10 +10069,10 @@
         <v>398</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D383" s="4">
-        <v>1500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E383" s="7"/>
       <c r="F383" s="7"/>
@@ -10084,10 +10090,10 @@
         <v>399</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D384" s="4">
-        <v>12000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E384" s="7"/>
       <c r="F384" s="7"/>
@@ -10105,10 +10111,10 @@
         <v>400</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D385" s="4">
-        <v>3000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E385" s="7"/>
       <c r="F385" s="7"/>
@@ -10126,10 +10132,10 @@
         <v>401</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D386" s="4">
-        <v>1000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E386" s="7"/>
       <c r="F386" s="7"/>
@@ -10147,10 +10153,10 @@
         <v>402</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D387" s="4">
-        <v>25000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E387" s="7"/>
       <c r="F387" s="7"/>
@@ -10168,10 +10174,10 @@
         <v>403</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D388" s="4">
-        <v>9000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E388" s="7"/>
       <c r="F388" s="7"/>
@@ -10189,12 +10195,12 @@
         <v>404</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D389" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E389" s="4"/>
+        <v>25000.0</v>
+      </c>
+      <c r="E389" s="7"/>
       <c r="F389" s="7"/>
       <c r="G389" s="7"/>
       <c r="H389" s="7"/>
@@ -10210,7 +10216,7 @@
         <v>405</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D390" s="4">
         <v>9000.0</v>
@@ -10231,12 +10237,12 @@
         <v>406</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D391" s="4">
-        <v>4500.0</v>
-      </c>
-      <c r="E391" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E391" s="4"/>
       <c r="F391" s="7"/>
       <c r="G391" s="7"/>
       <c r="H391" s="7"/>
@@ -10252,10 +10258,10 @@
         <v>407</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D392" s="4">
-        <v>500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E392" s="7"/>
       <c r="F392" s="7"/>
@@ -10273,10 +10279,10 @@
         <v>408</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D393" s="4">
-        <v>3000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E393" s="7"/>
       <c r="F393" s="7"/>
@@ -10294,10 +10300,10 @@
         <v>409</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D394" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E394" s="7"/>
       <c r="F394" s="7"/>
@@ -10311,42 +10317,42 @@
         <f t="shared" si="1"/>
         <v>394</v>
       </c>
-      <c r="B395" s="9" t="s">
+      <c r="B395" s="5" t="s">
         <v>410</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="D395" s="10">
-        <v>4500.0</v>
-      </c>
-      <c r="E395" s="11"/>
-      <c r="F395" s="11"/>
-      <c r="G395" s="11"/>
-      <c r="H395" s="11"/>
-      <c r="I395" s="11"/>
-      <c r="J395" s="11"/>
+        <v>386</v>
+      </c>
+      <c r="D395" s="4">
+        <v>3000.0</v>
+      </c>
+      <c r="E395" s="7"/>
+      <c r="F395" s="7"/>
+      <c r="G395" s="7"/>
+      <c r="H395" s="7"/>
+      <c r="I395" s="7"/>
+      <c r="J395" s="7"/>
     </row>
     <row r="396">
       <c r="A396" s="4">
         <f t="shared" si="1"/>
         <v>395</v>
       </c>
-      <c r="B396" s="9" t="s">
+      <c r="B396" s="5" t="s">
         <v>411</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="D396" s="10">
-        <v>50000.0</v>
-      </c>
-      <c r="E396" s="11"/>
-      <c r="F396" s="11"/>
-      <c r="G396" s="11"/>
-      <c r="H396" s="11"/>
-      <c r="I396" s="11"/>
-      <c r="J396" s="11"/>
+        <v>386</v>
+      </c>
+      <c r="D396" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E396" s="7"/>
+      <c r="F396" s="7"/>
+      <c r="G396" s="7"/>
+      <c r="H396" s="7"/>
+      <c r="I396" s="7"/>
+      <c r="J396" s="7"/>
     </row>
     <row r="397">
       <c r="A397" s="4">
@@ -10357,10 +10363,10 @@
         <v>412</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D397" s="10">
-        <v>12000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E397" s="11"/>
       <c r="F397" s="11"/>
@@ -10374,14 +10380,14 @@
         <f t="shared" si="1"/>
         <v>397</v>
       </c>
-      <c r="B398" s="5" t="s">
+      <c r="B398" s="9" t="s">
         <v>413</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D398" s="10">
-        <v>4500.0</v>
+        <v>50000.0</v>
       </c>
       <c r="E398" s="11"/>
       <c r="F398" s="11"/>
@@ -10399,10 +10405,10 @@
         <v>414</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>415</v>
+        <v>386</v>
       </c>
       <c r="D399" s="10">
-        <v>3000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E399" s="11"/>
       <c r="F399" s="11"/>
@@ -10416,14 +10422,14 @@
         <f t="shared" si="1"/>
         <v>399</v>
       </c>
-      <c r="B400" s="9" t="s">
+      <c r="B400" s="5" t="s">
         <v>415</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>415</v>
+        <v>386</v>
       </c>
       <c r="D400" s="10">
-        <v>5000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E400" s="11"/>
       <c r="F400" s="11"/>
@@ -10441,10 +10447,10 @@
         <v>416</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D401" s="10">
-        <v>6000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E401" s="11"/>
       <c r="F401" s="11"/>
@@ -10462,10 +10468,10 @@
         <v>417</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>363</v>
+        <v>417</v>
       </c>
       <c r="D402" s="10">
-        <v>12000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E402" s="11"/>
       <c r="F402" s="11"/>
@@ -10483,13 +10489,13 @@
         <v>418</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>363</v>
+        <v>417</v>
       </c>
       <c r="D403" s="10">
-        <v>200.0</v>
-      </c>
-      <c r="E403" s="10"/>
-      <c r="F403" s="10"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E403" s="11"/>
+      <c r="F403" s="11"/>
       <c r="G403" s="11"/>
       <c r="H403" s="11"/>
       <c r="I403" s="11"/>
@@ -10504,17 +10510,13 @@
         <v>419</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D404" s="10">
-        <v>5000.0</v>
-      </c>
-      <c r="E404" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="F404" s="10">
-        <v>4500.0</v>
-      </c>
+        <v>12000.0</v>
+      </c>
+      <c r="E404" s="11"/>
+      <c r="F404" s="11"/>
       <c r="G404" s="11"/>
       <c r="H404" s="11"/>
       <c r="I404" s="11"/>
@@ -10529,13 +10531,13 @@
         <v>420</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D405" s="10">
-        <v>18000.0</v>
-      </c>
-      <c r="E405" s="11"/>
-      <c r="F405" s="11"/>
+        <v>200.0</v>
+      </c>
+      <c r="E405" s="10"/>
+      <c r="F405" s="10"/>
       <c r="G405" s="11"/>
       <c r="H405" s="11"/>
       <c r="I405" s="11"/>
@@ -10550,13 +10552,17 @@
         <v>421</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D406" s="10">
-        <v>17000.0</v>
-      </c>
-      <c r="E406" s="11"/>
-      <c r="F406" s="11"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E406" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="F406" s="10">
+        <v>4500.0</v>
+      </c>
       <c r="G406" s="11"/>
       <c r="H406" s="11"/>
       <c r="I406" s="11"/>
@@ -10571,10 +10577,10 @@
         <v>422</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D407" s="10">
-        <v>17500.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E407" s="11"/>
       <c r="F407" s="11"/>
@@ -10592,10 +10598,10 @@
         <v>423</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D408" s="10">
-        <v>9000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E408" s="11"/>
       <c r="F408" s="11"/>
@@ -10613,10 +10619,10 @@
         <v>424</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D409" s="10">
-        <v>9000.0</v>
+        <v>17500.0</v>
       </c>
       <c r="E409" s="11"/>
       <c r="F409" s="11"/>
@@ -10634,10 +10640,10 @@
         <v>425</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D410" s="10">
-        <v>19500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E410" s="11"/>
       <c r="F410" s="11"/>
@@ -10655,10 +10661,10 @@
         <v>426</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D411" s="10">
-        <v>8500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E411" s="11"/>
       <c r="F411" s="11"/>
@@ -10676,10 +10682,10 @@
         <v>427</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D412" s="10">
-        <v>9000.0</v>
+        <v>19500.0</v>
       </c>
       <c r="E412" s="11"/>
       <c r="F412" s="11"/>
@@ -10689,10 +10695,19 @@
       <c r="J412" s="11"/>
     </row>
     <row r="413">
-      <c r="A413" s="12"/>
-      <c r="B413" s="12"/>
-      <c r="C413" s="12"/>
-      <c r="D413" s="11"/>
+      <c r="A413" s="4">
+        <f t="shared" si="1"/>
+        <v>412</v>
+      </c>
+      <c r="B413" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="C413" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="D413" s="10">
+        <v>8500.0</v>
+      </c>
       <c r="E413" s="11"/>
       <c r="F413" s="11"/>
       <c r="G413" s="11"/>
@@ -10701,10 +10716,19 @@
       <c r="J413" s="11"/>
     </row>
     <row r="414">
-      <c r="A414" s="12"/>
-      <c r="B414" s="12"/>
-      <c r="C414" s="12"/>
-      <c r="D414" s="11"/>
+      <c r="A414" s="4">
+        <f t="shared" si="1"/>
+        <v>413</v>
+      </c>
+      <c r="B414" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="C414" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="D414" s="10">
+        <v>9000.0</v>
+      </c>
       <c r="E414" s="11"/>
       <c r="F414" s="11"/>
       <c r="G414" s="11"/>
@@ -11772,25 +11796,25 @@
       <c r="A503" s="12"/>
       <c r="B503" s="12"/>
       <c r="C503" s="12"/>
-      <c r="D503" s="12"/>
-      <c r="E503" s="12"/>
-      <c r="F503" s="12"/>
-      <c r="G503" s="12"/>
-      <c r="H503" s="12"/>
-      <c r="I503" s="12"/>
-      <c r="J503" s="12"/>
+      <c r="D503" s="11"/>
+      <c r="E503" s="11"/>
+      <c r="F503" s="11"/>
+      <c r="G503" s="11"/>
+      <c r="H503" s="11"/>
+      <c r="I503" s="11"/>
+      <c r="J503" s="11"/>
     </row>
     <row r="504">
       <c r="A504" s="12"/>
       <c r="B504" s="12"/>
       <c r="C504" s="12"/>
-      <c r="D504" s="12"/>
-      <c r="E504" s="12"/>
-      <c r="F504" s="12"/>
-      <c r="G504" s="12"/>
-      <c r="H504" s="12"/>
-      <c r="I504" s="12"/>
-      <c r="J504" s="12"/>
+      <c r="D504" s="11"/>
+      <c r="E504" s="11"/>
+      <c r="F504" s="11"/>
+      <c r="G504" s="11"/>
+      <c r="H504" s="11"/>
+      <c r="I504" s="11"/>
+      <c r="J504" s="11"/>
     </row>
     <row r="505">
       <c r="A505" s="12"/>
@@ -20192,15 +20216,39 @@
       <c r="I1204" s="12"/>
       <c r="J1204" s="12"/>
     </row>
+    <row r="1205">
+      <c r="A1205" s="12"/>
+      <c r="B1205" s="12"/>
+      <c r="C1205" s="12"/>
+      <c r="D1205" s="12"/>
+      <c r="E1205" s="12"/>
+      <c r="F1205" s="12"/>
+      <c r="G1205" s="12"/>
+      <c r="H1205" s="12"/>
+      <c r="I1205" s="12"/>
+      <c r="J1205" s="12"/>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="12"/>
+      <c r="B1206" s="12"/>
+      <c r="C1206" s="12"/>
+      <c r="D1206" s="12"/>
+      <c r="E1206" s="12"/>
+      <c r="F1206" s="12"/>
+      <c r="G1206" s="12"/>
+      <c r="H1206" s="12"/>
+      <c r="I1206" s="12"/>
+      <c r="J1206" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$412"/>
-  <conditionalFormatting sqref="A2:J1204">
+  <autoFilter ref="$B$1:$C$414"/>
+  <conditionalFormatting sqref="A2:J1206">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C412">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C414">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20261,7 +20309,7 @@
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4">
@@ -20280,7 +20328,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -20299,7 +20347,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -20318,7 +20366,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -20337,7 +20385,7 @@
         <v>GROSIR5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="4">
@@ -20356,7 +20404,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -20375,7 +20423,7 @@
         <v>GROSIR7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="4">
@@ -20394,7 +20442,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -20413,7 +20461,7 @@
         <v>GROSIR9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="4">
@@ -20432,7 +20480,7 @@
         <v>GROSIR10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="4">
@@ -20451,7 +20499,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -20470,7 +20518,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -20489,7 +20537,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -20508,7 +20556,7 @@
         <v>GROSIR14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="4">
@@ -20527,7 +20575,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -20546,7 +20594,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -20565,7 +20613,7 @@
         <v>GROSIR17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="4">
@@ -20584,7 +20632,7 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
@@ -20603,7 +20651,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -20622,7 +20670,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -20641,7 +20689,7 @@
         <v>GROSIR21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4">
@@ -20660,7 +20708,7 @@
         <v>GROSIR22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="4">
@@ -20679,7 +20727,7 @@
         <v>GROSIR23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="4">
@@ -20698,7 +20746,7 @@
         <v>GROSIR24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="4">
@@ -20717,7 +20765,7 @@
         <v>GROSIR25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="4">
@@ -20736,7 +20784,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -20755,7 +20803,7 @@
         <v>GROSIR27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="4">
@@ -20774,7 +20822,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -20793,7 +20841,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -20812,7 +20860,7 @@
         <v>GROSIR30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="4">
@@ -20831,7 +20879,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -20850,7 +20898,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -20869,7 +20917,7 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
@@ -20888,7 +20936,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -20907,7 +20955,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -20926,7 +20974,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -20945,7 +20993,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -20964,7 +21012,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -20983,7 +21031,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -21002,7 +21050,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -21021,7 +21069,7 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
@@ -21040,7 +21088,7 @@
         <v>GROSIR42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="457">
   <si>
     <t>Barcode</t>
   </si>
@@ -1383,6 +1383,9 @@
   </si>
   <si>
     <t>Pepsodent Kecil</t>
+  </si>
+  <si>
+    <t>Korek Tokai</t>
   </si>
 </sst>
 </file>
@@ -6974,8 +6977,12 @@
       <c r="D239" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E239" s="7"/>
-      <c r="F239" s="7"/>
+      <c r="E239" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F239" s="4">
+        <v>10000.0</v>
+      </c>
       <c r="G239" s="7"/>
       <c r="H239" s="7"/>
       <c r="I239" s="7"/>
@@ -11808,13 +11815,13 @@
       <c r="A504" s="12"/>
       <c r="B504" s="12"/>
       <c r="C504" s="12"/>
-      <c r="D504" s="11"/>
-      <c r="E504" s="11"/>
-      <c r="F504" s="11"/>
-      <c r="G504" s="11"/>
-      <c r="H504" s="11"/>
-      <c r="I504" s="11"/>
-      <c r="J504" s="11"/>
+      <c r="D504" s="12"/>
+      <c r="E504" s="12"/>
+      <c r="F504" s="12"/>
+      <c r="G504" s="12"/>
+      <c r="H504" s="12"/>
+      <c r="I504" s="12"/>
+      <c r="J504" s="12"/>
     </row>
     <row r="505">
       <c r="A505" s="12"/>
@@ -20228,21 +20235,9 @@
       <c r="I1205" s="12"/>
       <c r="J1205" s="12"/>
     </row>
-    <row r="1206">
-      <c r="A1206" s="12"/>
-      <c r="B1206" s="12"/>
-      <c r="C1206" s="12"/>
-      <c r="D1206" s="12"/>
-      <c r="E1206" s="12"/>
-      <c r="F1206" s="12"/>
-      <c r="G1206" s="12"/>
-      <c r="H1206" s="12"/>
-      <c r="I1206" s="12"/>
-      <c r="J1206" s="12"/>
-    </row>
   </sheetData>
   <autoFilter ref="$B$1:$C$414"/>
-  <conditionalFormatting sqref="A2:J1206">
+  <conditionalFormatting sqref="A2:J1205">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
@@ -20305,7 +20300,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="str">
-        <f t="shared" ref="A2:A44" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
+        <f t="shared" ref="A2:A45" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -21121,10 +21116,17 @@
       <c r="J44" s="13"/>
     </row>
     <row r="45">
-      <c r="A45" s="4"/>
-      <c r="B45" s="5"/>
+      <c r="A45" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR44</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>456</v>
+      </c>
       <c r="C45" s="5"/>
-      <c r="D45" s="4"/>
+      <c r="D45" s="4">
+        <v>2000.0</v>
+      </c>
       <c r="E45" s="13"/>
       <c r="F45" s="13"/>
       <c r="G45" s="13"/>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$414</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$416</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$260</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="458">
   <si>
     <t>Barcode</t>
   </si>
@@ -762,6 +762,9 @@
   </si>
   <si>
     <t>Harmoni</t>
+  </si>
+  <si>
+    <t>Marlboro Black SLOP</t>
   </si>
   <si>
     <t>Korek Api Durian</t>
@@ -1773,7 +1776,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A414" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A416" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -6927,13 +6930,13 @@
         <v>236</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="D237" s="4">
-        <v>500.0</v>
+        <v>39000.0</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="7"/>
@@ -6948,13 +6951,13 @@
         <v>237</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="D238" s="4">
-        <v>4000.0</v>
+        <v>382000.0</v>
       </c>
       <c r="E238" s="7"/>
       <c r="F238" s="7"/>
@@ -6969,20 +6972,16 @@
         <v>238</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D239" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E239" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F239" s="4">
-        <v>10000.0</v>
-      </c>
+        <v>500.0</v>
+      </c>
+      <c r="E239" s="7"/>
+      <c r="F239" s="7"/>
       <c r="G239" s="7"/>
       <c r="H239" s="7"/>
       <c r="I239" s="7"/>
@@ -6994,20 +6993,16 @@
         <v>239</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D240" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E240" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F240" s="4">
-        <v>14000.0</v>
-      </c>
+        <v>4000.0</v>
+      </c>
+      <c r="E240" s="7"/>
+      <c r="F240" s="7"/>
       <c r="G240" s="7"/>
       <c r="H240" s="7"/>
       <c r="I240" s="7"/>
@@ -7019,16 +7014,20 @@
         <v>240</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D241" s="4">
-        <v>109000.0</v>
-      </c>
-      <c r="E241" s="7"/>
-      <c r="F241" s="7"/>
+        <v>2500.0</v>
+      </c>
+      <c r="E241" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F241" s="4">
+        <v>10000.0</v>
+      </c>
       <c r="G241" s="7"/>
       <c r="H241" s="7"/>
       <c r="I241" s="7"/>
@@ -7040,10 +7039,10 @@
         <v>241</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D242" s="4">
         <v>3000.0</v>
@@ -7065,10 +7064,10 @@
         <v>242</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D243" s="4">
         <v>109000.0</v>
@@ -7086,16 +7085,20 @@
         <v>243</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D244" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E244" s="7"/>
-      <c r="F244" s="7"/>
+      <c r="E244" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F244" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G244" s="7"/>
       <c r="H244" s="7"/>
       <c r="I244" s="7"/>
@@ -7107,13 +7110,13 @@
         <v>244</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D245" s="4">
-        <v>114000.0</v>
+        <v>109000.0</v>
       </c>
       <c r="E245" s="7"/>
       <c r="F245" s="7"/>
@@ -7128,10 +7131,10 @@
         <v>245</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D246" s="4">
         <v>3000.0</v>
@@ -7149,20 +7152,16 @@
         <v>246</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D247" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E247" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F247" s="4">
-        <v>39000.0</v>
-      </c>
+        <v>114000.0</v>
+      </c>
+      <c r="E247" s="7"/>
+      <c r="F247" s="7"/>
       <c r="G247" s="7"/>
       <c r="H247" s="7"/>
       <c r="I247" s="7"/>
@@ -7174,13 +7173,13 @@
         <v>247</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D248" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E248" s="7"/>
       <c r="F248" s="7"/>
@@ -7195,16 +7194,20 @@
         <v>248</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D249" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E249" s="7"/>
-      <c r="F249" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E249" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F249" s="4">
+        <v>39000.0</v>
+      </c>
       <c r="G249" s="7"/>
       <c r="H249" s="7"/>
       <c r="I249" s="7"/>
@@ -7216,10 +7219,10 @@
         <v>249</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D250" s="4">
         <v>114000.0</v>
@@ -7237,10 +7240,10 @@
         <v>250</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D251" s="4">
         <v>3000.0</v>
@@ -7258,10 +7261,10 @@
         <v>251</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D252" s="4">
         <v>114000.0</v>
@@ -7279,10 +7282,10 @@
         <v>252</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D253" s="4">
         <v>3000.0</v>
@@ -7300,10 +7303,10 @@
         <v>253</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D254" s="4">
         <v>114000.0</v>
@@ -7321,10 +7324,10 @@
         <v>254</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D255" s="4">
         <v>3000.0</v>
@@ -7342,13 +7345,13 @@
         <v>255</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D256" s="4">
-        <v>107000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E256" s="7"/>
       <c r="F256" s="7"/>
@@ -7363,10 +7366,10 @@
         <v>256</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D257" s="4">
         <v>3000.0</v>
@@ -7384,20 +7387,20 @@
         <v>257</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D258" s="4">
-        <v>112000.0</v>
-      </c>
-      <c r="E258" s="6"/>
-      <c r="F258" s="6"/>
-      <c r="G258" s="6"/>
-      <c r="H258" s="6"/>
-      <c r="I258" s="6"/>
-      <c r="J258" s="6"/>
+        <v>107000.0</v>
+      </c>
+      <c r="E258" s="7"/>
+      <c r="F258" s="7"/>
+      <c r="G258" s="7"/>
+      <c r="H258" s="7"/>
+      <c r="I258" s="7"/>
+      <c r="J258" s="7"/>
     </row>
     <row r="259">
       <c r="A259" s="4">
@@ -7405,20 +7408,16 @@
         <v>258</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D259" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E259" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F259" s="4">
-        <v>19000.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E259" s="7"/>
+      <c r="F259" s="7"/>
       <c r="G259" s="7"/>
       <c r="H259" s="7"/>
       <c r="I259" s="7"/>
@@ -7430,24 +7429,20 @@
         <v>259</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D260" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E260" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F260" s="4">
-        <v>19000.0</v>
-      </c>
-      <c r="G260" s="7"/>
-      <c r="H260" s="7"/>
-      <c r="I260" s="7"/>
-      <c r="J260" s="7"/>
+        <v>112000.0</v>
+      </c>
+      <c r="E260" s="6"/>
+      <c r="F260" s="6"/>
+      <c r="G260" s="6"/>
+      <c r="H260" s="6"/>
+      <c r="I260" s="6"/>
+      <c r="J260" s="6"/>
     </row>
     <row r="261">
       <c r="A261" s="4">
@@ -7455,16 +7450,20 @@
         <v>260</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D261" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E261" s="4"/>
-      <c r="F261" s="4"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E261" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F261" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G261" s="7"/>
       <c r="H261" s="7"/>
       <c r="I261" s="7"/>
@@ -7476,16 +7475,20 @@
         <v>261</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D262" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E262" s="4"/>
-      <c r="F262" s="4"/>
+      <c r="E262" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F262" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G262" s="7"/>
       <c r="H262" s="7"/>
       <c r="I262" s="7"/>
@@ -7497,10 +7500,10 @@
         <v>262</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D263" s="4">
         <v>86000.0</v>
@@ -7518,21 +7521,17 @@
         <v>263</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D264" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E264" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F264" s="4">
-        <v>19500.0</v>
-      </c>
-      <c r="G264" s="4"/>
+      <c r="E264" s="4"/>
+      <c r="F264" s="4"/>
+      <c r="G264" s="7"/>
       <c r="H264" s="7"/>
       <c r="I264" s="7"/>
       <c r="J264" s="7"/>
@@ -7543,20 +7542,16 @@
         <v>264</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D265" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E265" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F265" s="4">
-        <v>6000.0</v>
-      </c>
+        <v>86000.0</v>
+      </c>
+      <c r="E265" s="4"/>
+      <c r="F265" s="4"/>
       <c r="G265" s="7"/>
       <c r="H265" s="7"/>
       <c r="I265" s="7"/>
@@ -7568,17 +7563,21 @@
         <v>265</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D266" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E266" s="7"/>
-      <c r="F266" s="7"/>
-      <c r="G266" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E266" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F266" s="4">
+        <v>19500.0</v>
+      </c>
+      <c r="G266" s="4"/>
       <c r="H266" s="7"/>
       <c r="I266" s="7"/>
       <c r="J266" s="7"/>
@@ -7589,16 +7588,20 @@
         <v>266</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D267" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E267" s="7"/>
-      <c r="F267" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E267" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F267" s="4">
+        <v>6000.0</v>
+      </c>
       <c r="G267" s="7"/>
       <c r="H267" s="7"/>
       <c r="I267" s="7"/>
@@ -7610,13 +7613,13 @@
         <v>267</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D268" s="4">
-        <v>89000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E268" s="7"/>
       <c r="F268" s="7"/>
@@ -7631,13 +7634,13 @@
         <v>268</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D269" s="4">
-        <v>7500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E269" s="7"/>
       <c r="F269" s="7"/>
@@ -7652,13 +7655,13 @@
         <v>269</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D270" s="4">
-        <v>5000.0</v>
+        <v>89000.0</v>
       </c>
       <c r="E270" s="7"/>
       <c r="F270" s="7"/>
@@ -7673,13 +7676,13 @@
         <v>270</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D271" s="4">
-        <v>3000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E271" s="7"/>
       <c r="F271" s="7"/>
@@ -7694,20 +7697,20 @@
         <v>271</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="D272" s="4">
-        <v>80000.0</v>
-      </c>
-      <c r="E272" s="6"/>
-      <c r="F272" s="6"/>
-      <c r="G272" s="6"/>
-      <c r="H272" s="6"/>
-      <c r="I272" s="6"/>
-      <c r="J272" s="6"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E272" s="7"/>
+      <c r="F272" s="7"/>
+      <c r="G272" s="7"/>
+      <c r="H272" s="7"/>
+      <c r="I272" s="7"/>
+      <c r="J272" s="7"/>
     </row>
     <row r="273">
       <c r="A273" s="4">
@@ -7715,13 +7718,13 @@
         <v>272</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="D273" s="4">
-        <v>14000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E273" s="7"/>
       <c r="F273" s="7"/>
@@ -7739,17 +7742,17 @@
         <v>287</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D274" s="4">
-        <v>14500.0</v>
-      </c>
-      <c r="E274" s="7"/>
-      <c r="F274" s="7"/>
-      <c r="G274" s="7"/>
-      <c r="H274" s="7"/>
-      <c r="I274" s="7"/>
-      <c r="J274" s="7"/>
+        <v>80000.0</v>
+      </c>
+      <c r="E274" s="6"/>
+      <c r="F274" s="6"/>
+      <c r="G274" s="6"/>
+      <c r="H274" s="6"/>
+      <c r="I274" s="6"/>
+      <c r="J274" s="6"/>
     </row>
     <row r="275">
       <c r="A275" s="4">
@@ -7757,13 +7760,13 @@
         <v>274</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D275" s="4">
-        <v>15000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E275" s="7"/>
       <c r="F275" s="7"/>
@@ -7778,13 +7781,13 @@
         <v>275</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D276" s="4">
-        <v>15500.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E276" s="7"/>
       <c r="F276" s="7"/>
@@ -7802,10 +7805,10 @@
         <v>288</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D277" s="4">
-        <v>1500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E277" s="7"/>
       <c r="F277" s="7"/>
@@ -7820,13 +7823,13 @@
         <v>277</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D278" s="4">
-        <v>12500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E278" s="7"/>
       <c r="F278" s="7"/>
@@ -7841,13 +7844,13 @@
         <v>278</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D279" s="4">
-        <v>500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E279" s="7"/>
       <c r="F279" s="7"/>
@@ -7862,13 +7865,13 @@
         <v>279</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D280" s="4">
-        <v>4500.0</v>
+        <v>12500.0</v>
       </c>
       <c r="E280" s="7"/>
       <c r="F280" s="7"/>
@@ -7883,13 +7886,13 @@
         <v>280</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D281" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E281" s="7"/>
       <c r="F281" s="7"/>
@@ -7904,13 +7907,13 @@
         <v>281</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D282" s="4">
-        <v>23000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E282" s="7"/>
       <c r="F282" s="7"/>
@@ -7925,20 +7928,16 @@
         <v>282</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D283" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E283" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F283" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E283" s="7"/>
+      <c r="F283" s="7"/>
       <c r="G283" s="7"/>
       <c r="H283" s="7"/>
       <c r="I283" s="7"/>
@@ -7950,16 +7949,16 @@
         <v>283</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D284" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E284" s="4"/>
-      <c r="F284" s="4"/>
+        <v>23000.0</v>
+      </c>
+      <c r="E284" s="7"/>
+      <c r="F284" s="7"/>
       <c r="G284" s="7"/>
       <c r="H284" s="7"/>
       <c r="I284" s="7"/>
@@ -7971,19 +7970,19 @@
         <v>284</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D285" s="4">
-        <v>2500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E285" s="4">
         <v>5.0</v>
       </c>
       <c r="F285" s="4">
-        <v>9000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="G285" s="7"/>
       <c r="H285" s="7"/>
@@ -7996,13 +7995,13 @@
         <v>285</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D286" s="4">
-        <v>9000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E286" s="4"/>
       <c r="F286" s="4"/>
@@ -8017,19 +8016,19 @@
         <v>286</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D287" s="4">
-        <v>2000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E287" s="4">
         <v>5.0</v>
       </c>
       <c r="F287" s="4">
-        <v>7500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="G287" s="7"/>
       <c r="H287" s="7"/>
@@ -8042,16 +8041,16 @@
         <v>287</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D288" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E288" s="7"/>
-      <c r="F288" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E288" s="4"/>
+      <c r="F288" s="4"/>
       <c r="G288" s="7"/>
       <c r="H288" s="7"/>
       <c r="I288" s="7"/>
@@ -8063,16 +8062,20 @@
         <v>288</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="D289" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E289" s="7"/>
-      <c r="F289" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E289" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F289" s="4">
+        <v>7500.0</v>
+      </c>
       <c r="G289" s="7"/>
       <c r="H289" s="7"/>
       <c r="I289" s="7"/>
@@ -8084,13 +8087,13 @@
         <v>289</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="D290" s="4">
-        <v>10000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E290" s="7"/>
       <c r="F290" s="7"/>
@@ -8105,13 +8108,13 @@
         <v>290</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D291" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E291" s="7"/>
       <c r="F291" s="7"/>
@@ -8126,13 +8129,13 @@
         <v>291</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D292" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E292" s="7"/>
       <c r="F292" s="7"/>
@@ -8147,13 +8150,13 @@
         <v>292</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D293" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E293" s="7"/>
       <c r="F293" s="7"/>
@@ -8168,13 +8171,13 @@
         <v>293</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D294" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E294" s="7"/>
       <c r="F294" s="7"/>
@@ -8189,13 +8192,13 @@
         <v>294</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D295" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E295" s="7"/>
       <c r="F295" s="7"/>
@@ -8210,13 +8213,13 @@
         <v>295</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D296" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E296" s="7"/>
       <c r="F296" s="7"/>
@@ -8231,13 +8234,13 @@
         <v>296</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D297" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E297" s="7"/>
       <c r="F297" s="7"/>
@@ -8252,13 +8255,13 @@
         <v>297</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D298" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E298" s="7"/>
       <c r="F298" s="7"/>
@@ -8273,10 +8276,10 @@
         <v>298</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D299" s="4">
         <v>1000.0</v>
@@ -8294,10 +8297,10 @@
         <v>299</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D300" s="4">
         <v>10000.0</v>
@@ -8315,13 +8318,13 @@
         <v>300</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D301" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E301" s="7"/>
       <c r="F301" s="7"/>
@@ -8336,13 +8339,13 @@
         <v>301</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D302" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E302" s="7"/>
       <c r="F302" s="7"/>
@@ -8357,13 +8360,13 @@
         <v>302</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D303" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E303" s="7"/>
       <c r="F303" s="7"/>
@@ -8378,10 +8381,10 @@
         <v>303</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D304" s="4">
         <v>500.0</v>
@@ -8399,10 +8402,10 @@
         <v>304</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D305" s="4">
         <v>5000.0</v>
@@ -8420,13 +8423,13 @@
         <v>305</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D306" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E306" s="7"/>
       <c r="F306" s="7"/>
@@ -8441,13 +8444,13 @@
         <v>306</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D307" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E307" s="7"/>
       <c r="F307" s="7"/>
@@ -8462,13 +8465,13 @@
         <v>307</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D308" s="4">
-        <v>2000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E308" s="7"/>
       <c r="F308" s="7"/>
@@ -8483,13 +8486,13 @@
         <v>308</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D309" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E309" s="7"/>
       <c r="F309" s="7"/>
@@ -8504,13 +8507,13 @@
         <v>309</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D310" s="4">
-        <v>1000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E310" s="7"/>
       <c r="F310" s="7"/>
@@ -8525,10 +8528,10 @@
         <v>310</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D311" s="4">
         <v>5000.0</v>
@@ -8546,10 +8549,10 @@
         <v>311</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D312" s="4">
         <v>1000.0</v>
@@ -8567,10 +8570,10 @@
         <v>312</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D313" s="4">
         <v>5000.0</v>
@@ -8588,10 +8591,10 @@
         <v>313</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D314" s="4">
         <v>1000.0</v>
@@ -8609,10 +8612,10 @@
         <v>314</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D315" s="4">
         <v>5000.0</v>
@@ -8630,13 +8633,13 @@
         <v>315</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D316" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E316" s="7"/>
       <c r="F316" s="7"/>
@@ -8651,13 +8654,13 @@
         <v>316</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D317" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E317" s="7"/>
       <c r="F317" s="7"/>
@@ -8672,13 +8675,13 @@
         <v>317</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D318" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E318" s="7"/>
       <c r="F318" s="7"/>
@@ -8693,13 +8696,13 @@
         <v>318</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D319" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E319" s="7"/>
       <c r="F319" s="7"/>
@@ -8714,13 +8717,13 @@
         <v>319</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D320" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E320" s="7"/>
       <c r="F320" s="7"/>
@@ -8735,10 +8738,10 @@
         <v>320</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D321" s="4">
         <v>5000.0</v>
@@ -8756,10 +8759,10 @@
         <v>321</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D322" s="4">
         <v>500.0</v>
@@ -8777,10 +8780,10 @@
         <v>322</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D323" s="4">
         <v>5000.0</v>
@@ -8798,13 +8801,13 @@
         <v>323</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D324" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E324" s="7"/>
       <c r="F324" s="7"/>
@@ -8819,10 +8822,10 @@
         <v>324</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D325" s="4">
         <v>5000.0</v>
@@ -8840,20 +8843,16 @@
         <v>325</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D326" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E326" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F326" s="4">
-        <v>4500.0</v>
-      </c>
+      <c r="E326" s="7"/>
+      <c r="F326" s="7"/>
       <c r="G326" s="7"/>
       <c r="H326" s="7"/>
       <c r="I326" s="7"/>
@@ -8865,13 +8864,13 @@
         <v>326</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D327" s="4">
-        <v>4500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E327" s="7"/>
       <c r="F327" s="7"/>
@@ -8886,16 +8885,20 @@
         <v>327</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D328" s="4">
-        <v>51000.0</v>
-      </c>
-      <c r="E328" s="4"/>
-      <c r="F328" s="4"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E328" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F328" s="4">
+        <v>4500.0</v>
+      </c>
       <c r="G328" s="7"/>
       <c r="H328" s="7"/>
       <c r="I328" s="7"/>
@@ -8907,20 +8910,16 @@
         <v>328</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D329" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E329" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F329" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>4500.0</v>
+      </c>
+      <c r="E329" s="7"/>
+      <c r="F329" s="7"/>
       <c r="G329" s="7"/>
       <c r="H329" s="7"/>
       <c r="I329" s="7"/>
@@ -8932,16 +8931,16 @@
         <v>329</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D330" s="4">
-        <v>52000.0</v>
-      </c>
-      <c r="E330" s="7"/>
-      <c r="F330" s="7"/>
+        <v>51000.0</v>
+      </c>
+      <c r="E330" s="4"/>
+      <c r="F330" s="4"/>
       <c r="G330" s="7"/>
       <c r="H330" s="7"/>
       <c r="I330" s="7"/>
@@ -8953,16 +8952,20 @@
         <v>330</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D331" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E331" s="7"/>
-      <c r="F331" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E331" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F331" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G331" s="7"/>
       <c r="H331" s="7"/>
       <c r="I331" s="7"/>
@@ -8974,13 +8977,13 @@
         <v>331</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D332" s="4">
-        <v>5000.0</v>
+        <v>52000.0</v>
       </c>
       <c r="E332" s="7"/>
       <c r="F332" s="7"/>
@@ -8995,20 +8998,16 @@
         <v>332</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D333" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E333" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F333" s="4">
-        <v>17000.0</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E333" s="7"/>
+      <c r="F333" s="7"/>
       <c r="G333" s="7"/>
       <c r="H333" s="7"/>
       <c r="I333" s="7"/>
@@ -9020,10 +9019,10 @@
         <v>333</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D334" s="4">
         <v>5000.0</v>
@@ -9041,19 +9040,19 @@
         <v>334</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D335" s="4">
-        <v>7000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E335" s="4">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F335" s="4">
-        <v>32500.0</v>
+        <v>17000.0</v>
       </c>
       <c r="G335" s="7"/>
       <c r="H335" s="7"/>
@@ -9066,13 +9065,13 @@
         <v>335</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D336" s="4">
-        <v>7500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E336" s="7"/>
       <c r="F336" s="7"/>
@@ -9087,16 +9086,20 @@
         <v>336</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D337" s="4">
-        <v>9500.0</v>
-      </c>
-      <c r="E337" s="7"/>
-      <c r="F337" s="7"/>
+        <v>7000.0</v>
+      </c>
+      <c r="E337" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F337" s="4">
+        <v>32500.0</v>
+      </c>
       <c r="G337" s="7"/>
       <c r="H337" s="7"/>
       <c r="I337" s="7"/>
@@ -9108,13 +9111,13 @@
         <v>337</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D338" s="4">
-        <v>3500.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E338" s="7"/>
       <c r="F338" s="7"/>
@@ -9129,13 +9132,13 @@
         <v>338</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D339" s="4">
-        <v>5000.0</v>
+        <v>9500.0</v>
       </c>
       <c r="E339" s="7"/>
       <c r="F339" s="7"/>
@@ -9150,20 +9153,16 @@
         <v>339</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D340" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E340" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F340" s="4">
-        <v>22500.0</v>
-      </c>
+        <v>3500.0</v>
+      </c>
+      <c r="E340" s="7"/>
+      <c r="F340" s="7"/>
       <c r="G340" s="7"/>
       <c r="H340" s="7"/>
       <c r="I340" s="7"/>
@@ -9175,20 +9174,16 @@
         <v>340</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D341" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E341" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F341" s="4">
-        <v>12500.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E341" s="7"/>
+      <c r="F341" s="7"/>
       <c r="G341" s="7"/>
       <c r="H341" s="7"/>
       <c r="I341" s="7"/>
@@ -9200,16 +9195,20 @@
         <v>341</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D342" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E342" s="4"/>
-      <c r="F342" s="4"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E342" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F342" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G342" s="7"/>
       <c r="H342" s="7"/>
       <c r="I342" s="7"/>
@@ -9221,17 +9220,21 @@
         <v>342</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D343" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E343" s="4"/>
-      <c r="F343" s="4"/>
-      <c r="G343" s="4"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E343" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F343" s="4">
+        <v>12500.0</v>
+      </c>
+      <c r="G343" s="7"/>
       <c r="H343" s="7"/>
       <c r="I343" s="7"/>
       <c r="J343" s="7"/>
@@ -9242,20 +9245,16 @@
         <v>343</v>
       </c>
       <c r="B344" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D344" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E344" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F344" s="4">
-        <v>11500.0</v>
-      </c>
+        <v>3500.0</v>
+      </c>
+      <c r="E344" s="4"/>
+      <c r="F344" s="4"/>
       <c r="G344" s="7"/>
       <c r="H344" s="7"/>
       <c r="I344" s="7"/>
@@ -9267,17 +9266,17 @@
         <v>344</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D345" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E345" s="7"/>
-      <c r="F345" s="7"/>
-      <c r="G345" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E345" s="4"/>
+      <c r="F345" s="4"/>
+      <c r="G345" s="4"/>
       <c r="H345" s="7"/>
       <c r="I345" s="7"/>
       <c r="J345" s="7"/>
@@ -9288,19 +9287,19 @@
         <v>345</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D346" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E346" s="4">
         <v>5.0</v>
       </c>
       <c r="F346" s="4">
-        <v>22500.0</v>
+        <v>11500.0</v>
       </c>
       <c r="G346" s="7"/>
       <c r="H346" s="7"/>
@@ -9313,13 +9312,13 @@
         <v>346</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D347" s="4">
-        <v>1000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E347" s="7"/>
       <c r="F347" s="7"/>
@@ -9334,16 +9333,20 @@
         <v>347</v>
       </c>
       <c r="B348" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D348" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E348" s="7"/>
-      <c r="F348" s="7"/>
+      <c r="E348" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F348" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G348" s="7"/>
       <c r="H348" s="7"/>
       <c r="I348" s="7"/>
@@ -9355,13 +9358,13 @@
         <v>348</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D349" s="4">
-        <v>3000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E349" s="7"/>
       <c r="F349" s="7"/>
@@ -9376,13 +9379,13 @@
         <v>349</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D350" s="4">
-        <v>14000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E350" s="7"/>
       <c r="F350" s="7"/>
@@ -9397,13 +9400,13 @@
         <v>350</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>365</v>
+        <v>303</v>
       </c>
       <c r="D351" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E351" s="7"/>
       <c r="F351" s="7"/>
@@ -9418,13 +9421,13 @@
         <v>351</v>
       </c>
       <c r="B352" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>365</v>
+        <v>303</v>
       </c>
       <c r="D352" s="4">
-        <v>4000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E352" s="7"/>
       <c r="F352" s="7"/>
@@ -9439,10 +9442,10 @@
         <v>352</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D353" s="4">
         <v>1000.0</v>
@@ -9460,13 +9463,13 @@
         <v>353</v>
       </c>
       <c r="B354" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D354" s="4">
-        <v>10000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E354" s="7"/>
       <c r="F354" s="7"/>
@@ -9481,10 +9484,10 @@
         <v>354</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D355" s="4">
         <v>1000.0</v>
@@ -9502,10 +9505,10 @@
         <v>355</v>
       </c>
       <c r="B356" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D356" s="4">
         <v>10000.0</v>
@@ -9523,13 +9526,13 @@
         <v>356</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D357" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E357" s="7"/>
       <c r="F357" s="7"/>
@@ -9544,13 +9547,13 @@
         <v>357</v>
       </c>
       <c r="B358" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D358" s="4">
-        <v>2500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E358" s="7"/>
       <c r="F358" s="7"/>
@@ -9565,13 +9568,13 @@
         <v>358</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D359" s="4">
-        <v>3000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E359" s="7"/>
       <c r="F359" s="7"/>
@@ -9586,13 +9589,13 @@
         <v>359</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D360" s="4">
-        <v>5000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E360" s="7"/>
       <c r="F360" s="7"/>
@@ -9607,10 +9610,10 @@
         <v>360</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D361" s="4">
         <v>3000.0</v>
@@ -9628,20 +9631,16 @@
         <v>361</v>
       </c>
       <c r="B362" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D362" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E362" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F362" s="4">
-        <v>3000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E362" s="7"/>
+      <c r="F362" s="7"/>
       <c r="G362" s="7"/>
       <c r="H362" s="7"/>
       <c r="I362" s="7"/>
@@ -9653,13 +9652,13 @@
         <v>362</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D363" s="4">
-        <v>500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E363" s="7"/>
       <c r="F363" s="7"/>
@@ -9674,16 +9673,20 @@
         <v>363</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D364" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E364" s="7"/>
-      <c r="F364" s="7"/>
+      <c r="E364" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F364" s="4">
+        <v>3000.0</v>
+      </c>
       <c r="G364" s="7"/>
       <c r="H364" s="7"/>
       <c r="I364" s="7"/>
@@ -9695,13 +9698,13 @@
         <v>364</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D365" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E365" s="7"/>
       <c r="F365" s="7"/>
@@ -9716,13 +9719,13 @@
         <v>365</v>
       </c>
       <c r="B366" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D366" s="4">
-        <v>7000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E366" s="7"/>
       <c r="F366" s="7"/>
@@ -9737,13 +9740,13 @@
         <v>366</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D367" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E367" s="7"/>
       <c r="F367" s="7"/>
@@ -9758,13 +9761,13 @@
         <v>367</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D368" s="4">
-        <v>25000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E368" s="7"/>
       <c r="F368" s="7"/>
@@ -9779,13 +9782,13 @@
         <v>368</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D369" s="4">
-        <v>8000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E369" s="7"/>
       <c r="F369" s="7"/>
@@ -9800,13 +9803,13 @@
         <v>369</v>
       </c>
       <c r="B370" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D370" s="4">
-        <v>4000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E370" s="7"/>
       <c r="F370" s="7"/>
@@ -9821,13 +9824,13 @@
         <v>370</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="D371" s="4">
-        <v>2000.0</v>
+        <v>8000.0</v>
       </c>
       <c r="E371" s="7"/>
       <c r="F371" s="7"/>
@@ -9842,13 +9845,13 @@
         <v>371</v>
       </c>
       <c r="B372" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="D372" s="4">
-        <v>45000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E372" s="7"/>
       <c r="F372" s="7"/>
@@ -9863,13 +9866,13 @@
         <v>372</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D373" s="4">
-        <v>2500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E373" s="7"/>
       <c r="F373" s="7"/>
@@ -9884,13 +9887,13 @@
         <v>373</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D374" s="4">
-        <v>2500.0</v>
+        <v>45000.0</v>
       </c>
       <c r="E374" s="7"/>
       <c r="F374" s="7"/>
@@ -9905,13 +9908,13 @@
         <v>374</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D375" s="4">
-        <v>4000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E375" s="7"/>
       <c r="F375" s="7"/>
@@ -9926,13 +9929,13 @@
         <v>375</v>
       </c>
       <c r="B376" s="5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D376" s="4">
-        <v>40000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E376" s="7"/>
       <c r="F376" s="7"/>
@@ -9947,13 +9950,13 @@
         <v>376</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D377" s="4">
-        <v>5000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E377" s="7"/>
       <c r="F377" s="7"/>
@@ -9968,19 +9971,19 @@
         <v>377</v>
       </c>
       <c r="B378" s="5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D378" s="4">
-        <v>46000.0</v>
+        <v>40000.0</v>
       </c>
       <c r="E378" s="7"/>
       <c r="F378" s="7"/>
       <c r="G378" s="7"/>
       <c r="H378" s="7"/>
-      <c r="I378" s="4"/>
+      <c r="I378" s="7"/>
       <c r="J378" s="7"/>
     </row>
     <row r="379">
@@ -9989,19 +9992,19 @@
         <v>378</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D379" s="4">
-        <v>2000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E379" s="7"/>
       <c r="F379" s="7"/>
       <c r="G379" s="7"/>
       <c r="H379" s="7"/>
-      <c r="I379" s="4"/>
+      <c r="I379" s="7"/>
       <c r="J379" s="7"/>
     </row>
     <row r="380">
@@ -10010,13 +10013,13 @@
         <v>379</v>
       </c>
       <c r="B380" s="5" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D380" s="4">
-        <v>17000.0</v>
+        <v>46000.0</v>
       </c>
       <c r="E380" s="7"/>
       <c r="F380" s="7"/>
@@ -10031,13 +10034,13 @@
         <v>380</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D381" s="4">
-        <v>500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E381" s="7"/>
       <c r="F381" s="7"/>
@@ -10052,19 +10055,19 @@
         <v>381</v>
       </c>
       <c r="B382" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D382" s="4">
-        <v>1000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E382" s="7"/>
       <c r="F382" s="7"/>
       <c r="G382" s="7"/>
       <c r="H382" s="7"/>
-      <c r="I382" s="7"/>
+      <c r="I382" s="4"/>
       <c r="J382" s="7"/>
     </row>
     <row r="383">
@@ -10073,19 +10076,19 @@
         <v>382</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D383" s="4">
-        <v>10000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E383" s="7"/>
       <c r="F383" s="7"/>
       <c r="G383" s="7"/>
       <c r="H383" s="7"/>
-      <c r="I383" s="7"/>
+      <c r="I383" s="4"/>
       <c r="J383" s="7"/>
     </row>
     <row r="384">
@@ -10094,13 +10097,13 @@
         <v>383</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D384" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E384" s="7"/>
       <c r="F384" s="7"/>
@@ -10115,13 +10118,13 @@
         <v>384</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D385" s="4">
-        <v>1500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E385" s="7"/>
       <c r="F385" s="7"/>
@@ -10136,13 +10139,13 @@
         <v>385</v>
       </c>
       <c r="B386" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D386" s="4">
-        <v>12000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E386" s="7"/>
       <c r="F386" s="7"/>
@@ -10157,13 +10160,13 @@
         <v>386</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D387" s="4">
-        <v>3000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E387" s="7"/>
       <c r="F387" s="7"/>
@@ -10178,13 +10181,13 @@
         <v>387</v>
       </c>
       <c r="B388" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D388" s="4">
-        <v>1000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E388" s="7"/>
       <c r="F388" s="7"/>
@@ -10199,13 +10202,13 @@
         <v>388</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D389" s="4">
-        <v>25000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E389" s="7"/>
       <c r="F389" s="7"/>
@@ -10220,13 +10223,13 @@
         <v>389</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D390" s="4">
-        <v>9000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E390" s="7"/>
       <c r="F390" s="7"/>
@@ -10241,15 +10244,15 @@
         <v>390</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D391" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E391" s="4"/>
+        <v>25000.0</v>
+      </c>
+      <c r="E391" s="7"/>
       <c r="F391" s="7"/>
       <c r="G391" s="7"/>
       <c r="H391" s="7"/>
@@ -10262,10 +10265,10 @@
         <v>391</v>
       </c>
       <c r="B392" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D392" s="4">
         <v>9000.0</v>
@@ -10283,15 +10286,15 @@
         <v>392</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D393" s="4">
-        <v>4500.0</v>
-      </c>
-      <c r="E393" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E393" s="4"/>
       <c r="F393" s="7"/>
       <c r="G393" s="7"/>
       <c r="H393" s="7"/>
@@ -10304,13 +10307,13 @@
         <v>393</v>
       </c>
       <c r="B394" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D394" s="4">
-        <v>500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E394" s="7"/>
       <c r="F394" s="7"/>
@@ -10325,13 +10328,13 @@
         <v>394</v>
       </c>
       <c r="B395" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D395" s="4">
-        <v>3000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E395" s="7"/>
       <c r="F395" s="7"/>
@@ -10346,13 +10349,13 @@
         <v>395</v>
       </c>
       <c r="B396" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D396" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E396" s="7"/>
       <c r="F396" s="7"/>
@@ -10366,42 +10369,42 @@
         <f t="shared" si="1"/>
         <v>396</v>
       </c>
-      <c r="B397" s="9" t="s">
-        <v>412</v>
+      <c r="B397" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="D397" s="10">
-        <v>4500.0</v>
-      </c>
-      <c r="E397" s="11"/>
-      <c r="F397" s="11"/>
-      <c r="G397" s="11"/>
-      <c r="H397" s="11"/>
-      <c r="I397" s="11"/>
-      <c r="J397" s="11"/>
+        <v>387</v>
+      </c>
+      <c r="D397" s="4">
+        <v>3000.0</v>
+      </c>
+      <c r="E397" s="7"/>
+      <c r="F397" s="7"/>
+      <c r="G397" s="7"/>
+      <c r="H397" s="7"/>
+      <c r="I397" s="7"/>
+      <c r="J397" s="7"/>
     </row>
     <row r="398">
       <c r="A398" s="4">
         <f t="shared" si="1"/>
         <v>397</v>
       </c>
-      <c r="B398" s="9" t="s">
-        <v>413</v>
+      <c r="B398" s="5" t="s">
+        <v>412</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="D398" s="10">
-        <v>50000.0</v>
-      </c>
-      <c r="E398" s="11"/>
-      <c r="F398" s="11"/>
-      <c r="G398" s="11"/>
-      <c r="H398" s="11"/>
-      <c r="I398" s="11"/>
-      <c r="J398" s="11"/>
+        <v>387</v>
+      </c>
+      <c r="D398" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E398" s="7"/>
+      <c r="F398" s="7"/>
+      <c r="G398" s="7"/>
+      <c r="H398" s="7"/>
+      <c r="I398" s="7"/>
+      <c r="J398" s="7"/>
     </row>
     <row r="399">
       <c r="A399" s="4">
@@ -10409,13 +10412,13 @@
         <v>398</v>
       </c>
       <c r="B399" s="9" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D399" s="10">
-        <v>12000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E399" s="11"/>
       <c r="F399" s="11"/>
@@ -10429,14 +10432,14 @@
         <f t="shared" si="1"/>
         <v>399</v>
       </c>
-      <c r="B400" s="5" t="s">
-        <v>415</v>
+      <c r="B400" s="9" t="s">
+        <v>414</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D400" s="10">
-        <v>4500.0</v>
+        <v>50000.0</v>
       </c>
       <c r="E400" s="11"/>
       <c r="F400" s="11"/>
@@ -10451,13 +10454,13 @@
         <v>400</v>
       </c>
       <c r="B401" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>417</v>
+        <v>387</v>
       </c>
       <c r="D401" s="10">
-        <v>3000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E401" s="11"/>
       <c r="F401" s="11"/>
@@ -10471,14 +10474,14 @@
         <f t="shared" si="1"/>
         <v>401</v>
       </c>
-      <c r="B402" s="9" t="s">
-        <v>417</v>
+      <c r="B402" s="5" t="s">
+        <v>416</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>417</v>
+        <v>387</v>
       </c>
       <c r="D402" s="10">
-        <v>5000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E402" s="11"/>
       <c r="F402" s="11"/>
@@ -10493,13 +10496,13 @@
         <v>402</v>
       </c>
       <c r="B403" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="C403" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="C403" s="5" t="s">
-        <v>417</v>
-      </c>
       <c r="D403" s="10">
-        <v>6000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E403" s="11"/>
       <c r="F403" s="11"/>
@@ -10514,13 +10517,13 @@
         <v>403</v>
       </c>
       <c r="B404" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>365</v>
+        <v>418</v>
       </c>
       <c r="D404" s="10">
-        <v>12000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E404" s="11"/>
       <c r="F404" s="11"/>
@@ -10535,16 +10538,16 @@
         <v>404</v>
       </c>
       <c r="B405" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>365</v>
+        <v>418</v>
       </c>
       <c r="D405" s="10">
-        <v>200.0</v>
-      </c>
-      <c r="E405" s="10"/>
-      <c r="F405" s="10"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E405" s="11"/>
+      <c r="F405" s="11"/>
       <c r="G405" s="11"/>
       <c r="H405" s="11"/>
       <c r="I405" s="11"/>
@@ -10556,20 +10559,16 @@
         <v>405</v>
       </c>
       <c r="B406" s="9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D406" s="10">
-        <v>5000.0</v>
-      </c>
-      <c r="E406" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="F406" s="10">
-        <v>4500.0</v>
-      </c>
+        <v>12000.0</v>
+      </c>
+      <c r="E406" s="11"/>
+      <c r="F406" s="11"/>
       <c r="G406" s="11"/>
       <c r="H406" s="11"/>
       <c r="I406" s="11"/>
@@ -10581,16 +10580,16 @@
         <v>406</v>
       </c>
       <c r="B407" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D407" s="10">
-        <v>18000.0</v>
-      </c>
-      <c r="E407" s="11"/>
-      <c r="F407" s="11"/>
+        <v>200.0</v>
+      </c>
+      <c r="E407" s="10"/>
+      <c r="F407" s="10"/>
       <c r="G407" s="11"/>
       <c r="H407" s="11"/>
       <c r="I407" s="11"/>
@@ -10602,16 +10601,20 @@
         <v>407</v>
       </c>
       <c r="B408" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D408" s="10">
-        <v>17000.0</v>
-      </c>
-      <c r="E408" s="11"/>
-      <c r="F408" s="11"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E408" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="F408" s="10">
+        <v>4500.0</v>
+      </c>
       <c r="G408" s="11"/>
       <c r="H408" s="11"/>
       <c r="I408" s="11"/>
@@ -10623,13 +10626,13 @@
         <v>408</v>
       </c>
       <c r="B409" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D409" s="10">
-        <v>17500.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E409" s="11"/>
       <c r="F409" s="11"/>
@@ -10644,13 +10647,13 @@
         <v>409</v>
       </c>
       <c r="B410" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D410" s="10">
-        <v>9000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E410" s="11"/>
       <c r="F410" s="11"/>
@@ -10665,13 +10668,13 @@
         <v>410</v>
       </c>
       <c r="B411" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D411" s="10">
-        <v>9000.0</v>
+        <v>17500.0</v>
       </c>
       <c r="E411" s="11"/>
       <c r="F411" s="11"/>
@@ -10686,13 +10689,13 @@
         <v>411</v>
       </c>
       <c r="B412" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D412" s="10">
-        <v>19500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E412" s="11"/>
       <c r="F412" s="11"/>
@@ -10707,13 +10710,13 @@
         <v>412</v>
       </c>
       <c r="B413" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D413" s="10">
-        <v>8500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E413" s="11"/>
       <c r="F413" s="11"/>
@@ -10728,13 +10731,13 @@
         <v>413</v>
       </c>
       <c r="B414" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D414" s="10">
-        <v>9000.0</v>
+        <v>19500.0</v>
       </c>
       <c r="E414" s="11"/>
       <c r="F414" s="11"/>
@@ -10744,10 +10747,19 @@
       <c r="J414" s="11"/>
     </row>
     <row r="415">
-      <c r="A415" s="12"/>
-      <c r="B415" s="12"/>
-      <c r="C415" s="12"/>
-      <c r="D415" s="11"/>
+      <c r="A415" s="4">
+        <f t="shared" si="1"/>
+        <v>414</v>
+      </c>
+      <c r="B415" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="C415" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="D415" s="10">
+        <v>8500.0</v>
+      </c>
       <c r="E415" s="11"/>
       <c r="F415" s="11"/>
       <c r="G415" s="11"/>
@@ -10756,10 +10768,19 @@
       <c r="J415" s="11"/>
     </row>
     <row r="416">
-      <c r="A416" s="12"/>
-      <c r="B416" s="12"/>
-      <c r="C416" s="12"/>
-      <c r="D416" s="11"/>
+      <c r="A416" s="4">
+        <f t="shared" si="1"/>
+        <v>415</v>
+      </c>
+      <c r="B416" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="C416" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="D416" s="10">
+        <v>9000.0</v>
+      </c>
       <c r="E416" s="11"/>
       <c r="F416" s="11"/>
       <c r="G416" s="11"/>
@@ -11815,25 +11836,25 @@
       <c r="A504" s="12"/>
       <c r="B504" s="12"/>
       <c r="C504" s="12"/>
-      <c r="D504" s="12"/>
-      <c r="E504" s="12"/>
-      <c r="F504" s="12"/>
-      <c r="G504" s="12"/>
-      <c r="H504" s="12"/>
-      <c r="I504" s="12"/>
-      <c r="J504" s="12"/>
+      <c r="D504" s="11"/>
+      <c r="E504" s="11"/>
+      <c r="F504" s="11"/>
+      <c r="G504" s="11"/>
+      <c r="H504" s="11"/>
+      <c r="I504" s="11"/>
+      <c r="J504" s="11"/>
     </row>
     <row r="505">
       <c r="A505" s="12"/>
       <c r="B505" s="12"/>
       <c r="C505" s="12"/>
-      <c r="D505" s="12"/>
-      <c r="E505" s="12"/>
-      <c r="F505" s="12"/>
-      <c r="G505" s="12"/>
-      <c r="H505" s="12"/>
-      <c r="I505" s="12"/>
-      <c r="J505" s="12"/>
+      <c r="D505" s="11"/>
+      <c r="E505" s="11"/>
+      <c r="F505" s="11"/>
+      <c r="G505" s="11"/>
+      <c r="H505" s="11"/>
+      <c r="I505" s="11"/>
+      <c r="J505" s="11"/>
     </row>
     <row r="506">
       <c r="A506" s="12"/>
@@ -20235,15 +20256,39 @@
       <c r="I1205" s="12"/>
       <c r="J1205" s="12"/>
     </row>
+    <row r="1206">
+      <c r="A1206" s="12"/>
+      <c r="B1206" s="12"/>
+      <c r="C1206" s="12"/>
+      <c r="D1206" s="12"/>
+      <c r="E1206" s="12"/>
+      <c r="F1206" s="12"/>
+      <c r="G1206" s="12"/>
+      <c r="H1206" s="12"/>
+      <c r="I1206" s="12"/>
+      <c r="J1206" s="12"/>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="12"/>
+      <c r="B1207" s="12"/>
+      <c r="C1207" s="12"/>
+      <c r="D1207" s="12"/>
+      <c r="E1207" s="12"/>
+      <c r="F1207" s="12"/>
+      <c r="G1207" s="12"/>
+      <c r="H1207" s="12"/>
+      <c r="I1207" s="12"/>
+      <c r="J1207" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$414"/>
-  <conditionalFormatting sqref="A2:J1205">
+  <autoFilter ref="$B$1:$C$416"/>
+  <conditionalFormatting sqref="A2:J1207">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C414">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C416">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20323,7 +20368,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -20342,7 +20387,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -20361,7 +20406,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -20399,7 +20444,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -20437,7 +20482,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -20494,7 +20539,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -20513,7 +20558,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -20532,7 +20577,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -20570,7 +20615,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -20589,7 +20634,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -20627,7 +20672,7 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
@@ -20646,7 +20691,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -20665,7 +20710,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -20779,7 +20824,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -20817,7 +20862,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -20836,7 +20881,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -20874,7 +20919,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -20893,7 +20938,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -20912,7 +20957,7 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
@@ -20931,7 +20976,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -20950,7 +20995,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -20969,7 +21014,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -20988,7 +21033,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -21007,7 +21052,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -21026,7 +21071,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -21045,7 +21090,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -21064,7 +21109,7 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
@@ -21083,7 +21128,7 @@
         <v>GROSIR42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="4">
@@ -21121,7 +21166,7 @@
         <v>GROSIR44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="459">
   <si>
     <t>Barcode</t>
   </si>
@@ -764,7 +764,10 @@
     <t>Harmoni</t>
   </si>
   <si>
-    <t>Marlboro Black SLOP</t>
+    <t>Marlboro Black 20</t>
+  </si>
+  <si>
+    <t>Marlboro Black 20 SLOP</t>
   </si>
   <si>
     <t>Korek Api Durian</t>
@@ -6930,7 +6933,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C237" s="5" t="s">
         <v>201</v>
@@ -6951,7 +6954,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C238" s="5" t="s">
         <v>201</v>
@@ -6972,10 +6975,10 @@
         <v>238</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D239" s="4">
         <v>500.0</v>
@@ -6993,10 +6996,10 @@
         <v>239</v>
       </c>
       <c r="B240" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C240" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="C240" s="5" t="s">
-        <v>251</v>
       </c>
       <c r="D240" s="4">
         <v>4000.0</v>
@@ -7014,10 +7017,10 @@
         <v>240</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D241" s="4">
         <v>2500.0</v>
@@ -7039,10 +7042,10 @@
         <v>241</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D242" s="4">
         <v>3000.0</v>
@@ -7064,10 +7067,10 @@
         <v>242</v>
       </c>
       <c r="B243" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C243" s="5" t="s">
         <v>256</v>
-      </c>
-      <c r="C243" s="5" t="s">
-        <v>255</v>
       </c>
       <c r="D243" s="4">
         <v>109000.0</v>
@@ -7085,10 +7088,10 @@
         <v>243</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D244" s="4">
         <v>3000.0</v>
@@ -7110,10 +7113,10 @@
         <v>244</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D245" s="4">
         <v>109000.0</v>
@@ -7131,10 +7134,10 @@
         <v>245</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D246" s="4">
         <v>3000.0</v>
@@ -7152,10 +7155,10 @@
         <v>246</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D247" s="4">
         <v>114000.0</v>
@@ -7173,10 +7176,10 @@
         <v>247</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D248" s="4">
         <v>3000.0</v>
@@ -7194,10 +7197,10 @@
         <v>248</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D249" s="4">
         <v>4000.0</v>
@@ -7219,10 +7222,10 @@
         <v>249</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D250" s="4">
         <v>114000.0</v>
@@ -7240,10 +7243,10 @@
         <v>250</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D251" s="4">
         <v>3000.0</v>
@@ -7261,10 +7264,10 @@
         <v>251</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D252" s="4">
         <v>114000.0</v>
@@ -7282,10 +7285,10 @@
         <v>252</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D253" s="4">
         <v>3000.0</v>
@@ -7303,10 +7306,10 @@
         <v>253</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D254" s="4">
         <v>114000.0</v>
@@ -7324,10 +7327,10 @@
         <v>254</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D255" s="4">
         <v>3000.0</v>
@@ -7345,10 +7348,10 @@
         <v>255</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D256" s="4">
         <v>114000.0</v>
@@ -7366,10 +7369,10 @@
         <v>256</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D257" s="4">
         <v>3000.0</v>
@@ -7387,10 +7390,10 @@
         <v>257</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D258" s="4">
         <v>107000.0</v>
@@ -7408,10 +7411,10 @@
         <v>258</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D259" s="4">
         <v>3000.0</v>
@@ -7429,10 +7432,10 @@
         <v>259</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D260" s="4">
         <v>112000.0</v>
@@ -7450,10 +7453,10 @@
         <v>260</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D261" s="4">
         <v>4000.0</v>
@@ -7475,10 +7478,10 @@
         <v>261</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D262" s="4">
         <v>4000.0</v>
@@ -7500,10 +7503,10 @@
         <v>262</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D263" s="4">
         <v>86000.0</v>
@@ -7521,10 +7524,10 @@
         <v>263</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D264" s="4">
         <v>4000.0</v>
@@ -7542,10 +7545,10 @@
         <v>264</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D265" s="4">
         <v>86000.0</v>
@@ -7563,10 +7566,10 @@
         <v>265</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D266" s="4">
         <v>4000.0</v>
@@ -7588,10 +7591,10 @@
         <v>266</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D267" s="4">
         <v>2000.0</v>
@@ -7613,10 +7616,10 @@
         <v>267</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D268" s="4">
         <v>1000.0</v>
@@ -7634,10 +7637,10 @@
         <v>268</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D269" s="4">
         <v>4000.0</v>
@@ -7655,10 +7658,10 @@
         <v>269</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D270" s="4">
         <v>89000.0</v>
@@ -7676,10 +7679,10 @@
         <v>270</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D271" s="4">
         <v>7500.0</v>
@@ -7697,10 +7700,10 @@
         <v>271</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D272" s="4">
         <v>5000.0</v>
@@ -7718,10 +7721,10 @@
         <v>272</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D273" s="4">
         <v>3000.0</v>
@@ -7739,10 +7742,10 @@
         <v>273</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D274" s="4">
         <v>80000.0</v>
@@ -7760,10 +7763,10 @@
         <v>274</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D275" s="4">
         <v>14000.0</v>
@@ -7781,10 +7784,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D276" s="4">
         <v>14500.0</v>
@@ -7802,10 +7805,10 @@
         <v>276</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D277" s="4">
         <v>15000.0</v>
@@ -7823,10 +7826,10 @@
         <v>277</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D278" s="4">
         <v>15500.0</v>
@@ -7844,10 +7847,10 @@
         <v>278</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D279" s="4">
         <v>1500.0</v>
@@ -7865,10 +7868,10 @@
         <v>279</v>
       </c>
       <c r="B280" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C280" s="5" t="s">
         <v>291</v>
-      </c>
-      <c r="C280" s="5" t="s">
-        <v>290</v>
       </c>
       <c r="D280" s="4">
         <v>12500.0</v>
@@ -7886,10 +7889,10 @@
         <v>280</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D281" s="4">
         <v>500.0</v>
@@ -7907,10 +7910,10 @@
         <v>281</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D282" s="4">
         <v>4500.0</v>
@@ -7928,10 +7931,10 @@
         <v>282</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D283" s="4">
         <v>3000.0</v>
@@ -7949,10 +7952,10 @@
         <v>283</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D284" s="4">
         <v>23000.0</v>
@@ -7970,10 +7973,10 @@
         <v>284</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D285" s="4">
         <v>2000.0</v>
@@ -7995,10 +7998,10 @@
         <v>285</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D286" s="4">
         <v>7500.0</v>
@@ -8016,10 +8019,10 @@
         <v>286</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D287" s="4">
         <v>2500.0</v>
@@ -8041,10 +8044,10 @@
         <v>287</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D288" s="4">
         <v>9000.0</v>
@@ -8062,10 +8065,10 @@
         <v>288</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D289" s="4">
         <v>2000.0</v>
@@ -8087,10 +8090,10 @@
         <v>289</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D290" s="4">
         <v>7500.0</v>
@@ -8108,10 +8111,10 @@
         <v>290</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D291" s="4">
         <v>1000.0</v>
@@ -8129,10 +8132,10 @@
         <v>291</v>
       </c>
       <c r="B292" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="C292" s="5" t="s">
         <v>304</v>
-      </c>
-      <c r="C292" s="5" t="s">
-        <v>303</v>
       </c>
       <c r="D292" s="4">
         <v>10000.0</v>
@@ -8150,10 +8153,10 @@
         <v>292</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D293" s="4">
         <v>500.0</v>
@@ -8171,10 +8174,10 @@
         <v>293</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D294" s="4">
         <v>5000.0</v>
@@ -8192,10 +8195,10 @@
         <v>294</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D295" s="4">
         <v>1000.0</v>
@@ -8213,10 +8216,10 @@
         <v>295</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D296" s="4">
         <v>10000.0</v>
@@ -8234,10 +8237,10 @@
         <v>296</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D297" s="4">
         <v>500.0</v>
@@ -8255,10 +8258,10 @@
         <v>297</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D298" s="4">
         <v>5000.0</v>
@@ -8276,10 +8279,10 @@
         <v>298</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D299" s="4">
         <v>1000.0</v>
@@ -8297,10 +8300,10 @@
         <v>299</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D300" s="4">
         <v>10000.0</v>
@@ -8318,10 +8321,10 @@
         <v>300</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D301" s="4">
         <v>1000.0</v>
@@ -8339,10 +8342,10 @@
         <v>301</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D302" s="4">
         <v>10000.0</v>
@@ -8360,10 +8363,10 @@
         <v>302</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D303" s="4">
         <v>10000.0</v>
@@ -8381,10 +8384,10 @@
         <v>303</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D304" s="4">
         <v>500.0</v>
@@ -8402,10 +8405,10 @@
         <v>304</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D305" s="4">
         <v>5000.0</v>
@@ -8423,10 +8426,10 @@
         <v>305</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D306" s="4">
         <v>500.0</v>
@@ -8444,10 +8447,10 @@
         <v>306</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D307" s="4">
         <v>5000.0</v>
@@ -8465,10 +8468,10 @@
         <v>307</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D308" s="4">
         <v>1000.0</v>
@@ -8486,10 +8489,10 @@
         <v>308</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D309" s="4">
         <v>10000.0</v>
@@ -8507,10 +8510,10 @@
         <v>309</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D310" s="4">
         <v>2000.0</v>
@@ -8528,10 +8531,10 @@
         <v>310</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D311" s="4">
         <v>5000.0</v>
@@ -8549,10 +8552,10 @@
         <v>311</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D312" s="4">
         <v>1000.0</v>
@@ -8570,10 +8573,10 @@
         <v>312</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D313" s="4">
         <v>5000.0</v>
@@ -8591,10 +8594,10 @@
         <v>313</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D314" s="4">
         <v>1000.0</v>
@@ -8612,10 +8615,10 @@
         <v>314</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D315" s="4">
         <v>5000.0</v>
@@ -8633,10 +8636,10 @@
         <v>315</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D316" s="4">
         <v>1000.0</v>
@@ -8654,10 +8657,10 @@
         <v>316</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D317" s="4">
         <v>5000.0</v>
@@ -8675,10 +8678,10 @@
         <v>317</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D318" s="4">
         <v>500.0</v>
@@ -8696,10 +8699,10 @@
         <v>318</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D319" s="4">
         <v>500.0</v>
@@ -8717,10 +8720,10 @@
         <v>319</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D320" s="4">
         <v>5000.0</v>
@@ -8738,10 +8741,10 @@
         <v>320</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D321" s="4">
         <v>5000.0</v>
@@ -8759,10 +8762,10 @@
         <v>321</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D322" s="4">
         <v>500.0</v>
@@ -8780,10 +8783,10 @@
         <v>322</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D323" s="4">
         <v>5000.0</v>
@@ -8801,10 +8804,10 @@
         <v>323</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D324" s="4">
         <v>500.0</v>
@@ -8822,10 +8825,10 @@
         <v>324</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D325" s="4">
         <v>5000.0</v>
@@ -8843,10 +8846,10 @@
         <v>325</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D326" s="4">
         <v>1000.0</v>
@@ -8864,10 +8867,10 @@
         <v>326</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D327" s="4">
         <v>5000.0</v>
@@ -8885,10 +8888,10 @@
         <v>327</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D328" s="4">
         <v>1000.0</v>
@@ -8910,10 +8913,10 @@
         <v>328</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D329" s="4">
         <v>4500.0</v>
@@ -8931,10 +8934,10 @@
         <v>329</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D330" s="4">
         <v>51000.0</v>
@@ -8952,10 +8955,10 @@
         <v>330</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D331" s="4">
         <v>2000.0</v>
@@ -8977,10 +8980,10 @@
         <v>331</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D332" s="4">
         <v>52000.0</v>
@@ -8998,10 +9001,10 @@
         <v>332</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D333" s="4">
         <v>1000.0</v>
@@ -9019,10 +9022,10 @@
         <v>333</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D334" s="4">
         <v>5000.0</v>
@@ -9040,10 +9043,10 @@
         <v>334</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D335" s="4">
         <v>2000.0</v>
@@ -9065,10 +9068,10 @@
         <v>335</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D336" s="4">
         <v>5000.0</v>
@@ -9086,10 +9089,10 @@
         <v>336</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D337" s="4">
         <v>7000.0</v>
@@ -9111,10 +9114,10 @@
         <v>337</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D338" s="4">
         <v>7500.0</v>
@@ -9132,10 +9135,10 @@
         <v>338</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D339" s="4">
         <v>9500.0</v>
@@ -9153,10 +9156,10 @@
         <v>339</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D340" s="4">
         <v>3500.0</v>
@@ -9174,10 +9177,10 @@
         <v>340</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D341" s="4">
         <v>5000.0</v>
@@ -9195,10 +9198,10 @@
         <v>341</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D342" s="4">
         <v>5000.0</v>
@@ -9220,10 +9223,10 @@
         <v>342</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D343" s="4">
         <v>3500.0</v>
@@ -9245,10 +9248,10 @@
         <v>343</v>
       </c>
       <c r="B344" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D344" s="4">
         <v>3500.0</v>
@@ -9266,10 +9269,10 @@
         <v>344</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D345" s="4">
         <v>3000.0</v>
@@ -9287,10 +9290,10 @@
         <v>345</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D346" s="4">
         <v>3000.0</v>
@@ -9312,10 +9315,10 @@
         <v>346</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D347" s="4">
         <v>4000.0</v>
@@ -9333,10 +9336,10 @@
         <v>347</v>
       </c>
       <c r="B348" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D348" s="4">
         <v>5000.0</v>
@@ -9358,10 +9361,10 @@
         <v>348</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D349" s="4">
         <v>1000.0</v>
@@ -9379,10 +9382,10 @@
         <v>349</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D350" s="4">
         <v>5000.0</v>
@@ -9400,10 +9403,10 @@
         <v>350</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D351" s="4">
         <v>3000.0</v>
@@ -9421,10 +9424,10 @@
         <v>351</v>
       </c>
       <c r="B352" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D352" s="4">
         <v>14000.0</v>
@@ -9442,10 +9445,10 @@
         <v>352</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D353" s="4">
         <v>1000.0</v>
@@ -9463,10 +9466,10 @@
         <v>353</v>
       </c>
       <c r="B354" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C354" s="5" t="s">
         <v>367</v>
-      </c>
-      <c r="C354" s="5" t="s">
-        <v>366</v>
       </c>
       <c r="D354" s="4">
         <v>4000.0</v>
@@ -9484,10 +9487,10 @@
         <v>354</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D355" s="4">
         <v>1000.0</v>
@@ -9505,10 +9508,10 @@
         <v>355</v>
       </c>
       <c r="B356" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D356" s="4">
         <v>10000.0</v>
@@ -9526,10 +9529,10 @@
         <v>356</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D357" s="4">
         <v>1000.0</v>
@@ -9547,10 +9550,10 @@
         <v>357</v>
       </c>
       <c r="B358" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D358" s="4">
         <v>10000.0</v>
@@ -9568,10 +9571,10 @@
         <v>358</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D359" s="4">
         <v>4000.0</v>
@@ -9589,10 +9592,10 @@
         <v>359</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D360" s="4">
         <v>2500.0</v>
@@ -9610,10 +9613,10 @@
         <v>360</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D361" s="4">
         <v>3000.0</v>
@@ -9631,10 +9634,10 @@
         <v>361</v>
       </c>
       <c r="B362" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D362" s="4">
         <v>5000.0</v>
@@ -9652,10 +9655,10 @@
         <v>362</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D363" s="4">
         <v>3000.0</v>
@@ -9673,10 +9676,10 @@
         <v>363</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D364" s="4">
         <v>1000.0</v>
@@ -9698,10 +9701,10 @@
         <v>364</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D365" s="4">
         <v>500.0</v>
@@ -9719,10 +9722,10 @@
         <v>365</v>
       </c>
       <c r="B366" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D366" s="4">
         <v>1000.0</v>
@@ -9740,10 +9743,10 @@
         <v>366</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D367" s="4">
         <v>5000.0</v>
@@ -9761,10 +9764,10 @@
         <v>367</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D368" s="4">
         <v>7000.0</v>
@@ -9782,10 +9785,10 @@
         <v>368</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D369" s="4">
         <v>3000.0</v>
@@ -9803,10 +9806,10 @@
         <v>369</v>
       </c>
       <c r="B370" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D370" s="4">
         <v>25000.0</v>
@@ -9824,10 +9827,10 @@
         <v>370</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D371" s="4">
         <v>8000.0</v>
@@ -9845,10 +9848,10 @@
         <v>371</v>
       </c>
       <c r="B372" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D372" s="4">
         <v>4000.0</v>
@@ -9866,10 +9869,10 @@
         <v>372</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D373" s="4">
         <v>2000.0</v>
@@ -9887,10 +9890,10 @@
         <v>373</v>
       </c>
       <c r="B374" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C374" s="5" t="s">
         <v>388</v>
-      </c>
-      <c r="C374" s="5" t="s">
-        <v>387</v>
       </c>
       <c r="D374" s="4">
         <v>45000.0</v>
@@ -9908,10 +9911,10 @@
         <v>374</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D375" s="4">
         <v>2500.0</v>
@@ -9929,10 +9932,10 @@
         <v>375</v>
       </c>
       <c r="B376" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D376" s="4">
         <v>2500.0</v>
@@ -9950,10 +9953,10 @@
         <v>376</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D377" s="4">
         <v>4000.0</v>
@@ -9971,10 +9974,10 @@
         <v>377</v>
       </c>
       <c r="B378" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D378" s="4">
         <v>40000.0</v>
@@ -9992,10 +9995,10 @@
         <v>378</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D379" s="4">
         <v>5000.0</v>
@@ -10013,10 +10016,10 @@
         <v>379</v>
       </c>
       <c r="B380" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D380" s="4">
         <v>46000.0</v>
@@ -10034,10 +10037,10 @@
         <v>380</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D381" s="4">
         <v>2000.0</v>
@@ -10055,10 +10058,10 @@
         <v>381</v>
       </c>
       <c r="B382" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D382" s="4">
         <v>17000.0</v>
@@ -10076,10 +10079,10 @@
         <v>382</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D383" s="4">
         <v>500.0</v>
@@ -10097,10 +10100,10 @@
         <v>383</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D384" s="4">
         <v>1000.0</v>
@@ -10118,10 +10121,10 @@
         <v>384</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D385" s="4">
         <v>10000.0</v>
@@ -10139,10 +10142,10 @@
         <v>385</v>
       </c>
       <c r="B386" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D386" s="4">
         <v>500.0</v>
@@ -10160,10 +10163,10 @@
         <v>386</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D387" s="4">
         <v>1500.0</v>
@@ -10181,10 +10184,10 @@
         <v>387</v>
       </c>
       <c r="B388" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D388" s="4">
         <v>12000.0</v>
@@ -10202,10 +10205,10 @@
         <v>388</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D389" s="4">
         <v>3000.0</v>
@@ -10223,10 +10226,10 @@
         <v>389</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D390" s="4">
         <v>1000.0</v>
@@ -10244,10 +10247,10 @@
         <v>390</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D391" s="4">
         <v>25000.0</v>
@@ -10265,10 +10268,10 @@
         <v>391</v>
       </c>
       <c r="B392" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D392" s="4">
         <v>9000.0</v>
@@ -10286,10 +10289,10 @@
         <v>392</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D393" s="4">
         <v>1000.0</v>
@@ -10307,10 +10310,10 @@
         <v>393</v>
       </c>
       <c r="B394" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D394" s="4">
         <v>9000.0</v>
@@ -10328,10 +10331,10 @@
         <v>394</v>
       </c>
       <c r="B395" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D395" s="4">
         <v>4500.0</v>
@@ -10349,10 +10352,10 @@
         <v>395</v>
       </c>
       <c r="B396" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D396" s="4">
         <v>500.0</v>
@@ -10370,10 +10373,10 @@
         <v>396</v>
       </c>
       <c r="B397" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D397" s="4">
         <v>3000.0</v>
@@ -10391,10 +10394,10 @@
         <v>397</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D398" s="4">
         <v>1000.0</v>
@@ -10412,10 +10415,10 @@
         <v>398</v>
       </c>
       <c r="B399" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D399" s="10">
         <v>4500.0</v>
@@ -10433,10 +10436,10 @@
         <v>399</v>
       </c>
       <c r="B400" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D400" s="10">
         <v>50000.0</v>
@@ -10454,10 +10457,10 @@
         <v>400</v>
       </c>
       <c r="B401" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D401" s="10">
         <v>12000.0</v>
@@ -10475,10 +10478,10 @@
         <v>401</v>
       </c>
       <c r="B402" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D402" s="10">
         <v>4500.0</v>
@@ -10496,10 +10499,10 @@
         <v>402</v>
       </c>
       <c r="B403" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D403" s="10">
         <v>3000.0</v>
@@ -10517,10 +10520,10 @@
         <v>403</v>
       </c>
       <c r="B404" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D404" s="10">
         <v>5000.0</v>
@@ -10538,10 +10541,10 @@
         <v>404</v>
       </c>
       <c r="B405" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="C405" s="5" t="s">
         <v>419</v>
-      </c>
-      <c r="C405" s="5" t="s">
-        <v>418</v>
       </c>
       <c r="D405" s="10">
         <v>6000.0</v>
@@ -10559,10 +10562,10 @@
         <v>405</v>
       </c>
       <c r="B406" s="9" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D406" s="10">
         <v>12000.0</v>
@@ -10580,10 +10583,10 @@
         <v>406</v>
       </c>
       <c r="B407" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D407" s="10">
         <v>200.0</v>
@@ -10601,10 +10604,10 @@
         <v>407</v>
       </c>
       <c r="B408" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D408" s="10">
         <v>5000.0</v>
@@ -10626,10 +10629,10 @@
         <v>408</v>
       </c>
       <c r="B409" s="9" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D409" s="10">
         <v>18000.0</v>
@@ -10647,10 +10650,10 @@
         <v>409</v>
       </c>
       <c r="B410" s="9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D410" s="10">
         <v>17000.0</v>
@@ -10668,10 +10671,10 @@
         <v>410</v>
       </c>
       <c r="B411" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D411" s="10">
         <v>17500.0</v>
@@ -10689,10 +10692,10 @@
         <v>411</v>
       </c>
       <c r="B412" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D412" s="10">
         <v>9000.0</v>
@@ -10710,10 +10713,10 @@
         <v>412</v>
       </c>
       <c r="B413" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D413" s="10">
         <v>9000.0</v>
@@ -10731,10 +10734,10 @@
         <v>413</v>
       </c>
       <c r="B414" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D414" s="10">
         <v>19500.0</v>
@@ -10752,10 +10755,10 @@
         <v>414</v>
       </c>
       <c r="B415" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D415" s="10">
         <v>8500.0</v>
@@ -10773,10 +10776,10 @@
         <v>415</v>
       </c>
       <c r="B416" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D416" s="10">
         <v>9000.0</v>
@@ -20368,7 +20371,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -20387,7 +20390,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -20406,7 +20409,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -20444,7 +20447,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -20482,7 +20485,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -20539,7 +20542,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -20558,7 +20561,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -20577,7 +20580,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -20615,7 +20618,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -20634,7 +20637,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -20672,7 +20675,7 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
@@ -20691,7 +20694,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -20710,7 +20713,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -20824,7 +20827,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -20862,7 +20865,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -20881,7 +20884,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -20919,7 +20922,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -20938,7 +20941,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -20957,7 +20960,7 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
@@ -20976,7 +20979,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -20995,7 +20998,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -21014,7 +21017,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -21033,7 +21036,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -21052,7 +21055,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -21071,7 +21074,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -21090,7 +21093,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -21109,7 +21112,7 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
@@ -21128,7 +21131,7 @@
         <v>GROSIR42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="4">
@@ -21166,7 +21169,7 @@
         <v>GROSIR44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,15 +7,15 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$416</definedName>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$260</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$425</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$261</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="478">
   <si>
     <t>Barcode</t>
   </si>
@@ -191,6 +191,12 @@
     <t>Aqua 600ml Dus</t>
   </si>
   <si>
+    <t>Minral 1.5L Dus</t>
+  </si>
+  <si>
+    <t>Fanta 250ml</t>
+  </si>
+  <si>
     <t>Golda</t>
   </si>
   <si>
@@ -1280,10 +1286,10 @@
     <t>Mie isi 2 Seduh</t>
   </si>
   <si>
-    <t>amplop box</t>
-  </si>
-  <si>
-    <t>amplop</t>
+    <t>Amplop box</t>
+  </si>
+  <si>
+    <t>Amplop</t>
   </si>
   <si>
     <t>Agar Swallow</t>
@@ -1298,7 +1304,10 @@
     <t>Chitato</t>
   </si>
   <si>
-    <t>Taro Renceng</t>
+    <t>Roma Malkist 1000 Renceng</t>
+  </si>
+  <si>
+    <t>Taro 1000 Renceng</t>
   </si>
   <si>
     <t>Garuda Renceng</t>
@@ -1310,9 +1319,24 @@
     <t>Siip 500 dus</t>
   </si>
   <si>
+    <t>Pilus 500 Renceng</t>
+  </si>
+  <si>
     <t>Pilus 1000 Renceng</t>
   </si>
   <si>
+    <t>Chocolatos 500</t>
+  </si>
+  <si>
+    <t>Wow Spagheti</t>
+  </si>
+  <si>
+    <t>Wow Spagheti Renceng</t>
+  </si>
+  <si>
+    <t>Cat Choize</t>
+  </si>
+  <si>
     <t>Djarum Coklat Bungkus SLOP</t>
   </si>
   <si>
@@ -1392,6 +1416,39 @@
   </si>
   <si>
     <t>Korek Tokai</t>
+  </si>
+  <si>
+    <t>Good Day Mocha dus</t>
+  </si>
+  <si>
+    <t>Good Day Choco dus</t>
+  </si>
+  <si>
+    <t>Good Day Coolin dus</t>
+  </si>
+  <si>
+    <t>Kapal Api Mix dus</t>
+  </si>
+  <si>
+    <t>Luwak White Coffe dus</t>
+  </si>
+  <si>
+    <t>Indocafe bag</t>
+  </si>
+  <si>
+    <t>Daia 1000 dus</t>
+  </si>
+  <si>
+    <t>Rinso 1000 bag</t>
+  </si>
+  <si>
+    <t>Adem Sari</t>
+  </si>
+  <si>
+    <t>Bendera putih sak dus</t>
+  </si>
+  <si>
+    <t>Top Kopi Gula Aren dus</t>
   </si>
 </sst>
 </file>
@@ -1779,7 +1836,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A416" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A424" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -2776,7 +2833,7 @@
         <v>20</v>
       </c>
       <c r="D48" s="4">
-        <v>3500.0</v>
+        <v>35000.0</v>
       </c>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
@@ -2797,7 +2854,7 @@
         <v>20</v>
       </c>
       <c r="D49" s="4">
-        <v>36000.0</v>
+        <v>33000.0</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
@@ -2818,7 +2875,7 @@
         <v>20</v>
       </c>
       <c r="D50" s="4">
-        <v>7000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
@@ -2839,7 +2896,7 @@
         <v>20</v>
       </c>
       <c r="D51" s="4">
-        <v>150000.0</v>
+        <v>36000.0</v>
       </c>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
@@ -2860,14 +2917,10 @@
         <v>20</v>
       </c>
       <c r="D52" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E52" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F52" s="4">
-        <v>16000.0</v>
-      </c>
+        <v>7000.0</v>
+      </c>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
       <c r="I52" s="6"/>
@@ -2885,7 +2938,7 @@
         <v>20</v>
       </c>
       <c r="D53" s="4">
-        <v>128000.0</v>
+        <v>150000.0</v>
       </c>
       <c r="E53" s="6"/>
       <c r="F53" s="6"/>
@@ -2906,14 +2959,18 @@
         <v>20</v>
       </c>
       <c r="D54" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E54" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F54" s="4">
+        <v>16000.0</v>
+      </c>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
     </row>
     <row r="55">
       <c r="A55" s="4">
@@ -2927,7 +2984,7 @@
         <v>20</v>
       </c>
       <c r="D55" s="4">
-        <v>36000.0</v>
+        <v>128000.0</v>
       </c>
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
@@ -2945,17 +3002,17 @@
         <v>66</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D56" s="4">
-        <v>20000.0</v>
-      </c>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
     </row>
     <row r="57">
       <c r="A57" s="4">
@@ -2966,10 +3023,10 @@
         <v>67</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D57" s="4">
-        <v>1000.0</v>
+        <v>36000.0</v>
       </c>
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
@@ -2990,14 +3047,14 @@
         <v>11</v>
       </c>
       <c r="D58" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
+        <v>20000.0</v>
+      </c>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
     </row>
     <row r="59">
       <c r="A59" s="4">
@@ -3011,7 +3068,7 @@
         <v>11</v>
       </c>
       <c r="D59" s="4">
-        <v>2500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
@@ -3032,7 +3089,7 @@
         <v>11</v>
       </c>
       <c r="D60" s="4">
-        <v>21000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
@@ -3053,7 +3110,7 @@
         <v>11</v>
       </c>
       <c r="D61" s="4">
-        <v>2000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
@@ -3074,14 +3131,14 @@
         <v>11</v>
       </c>
       <c r="D62" s="4">
-        <v>9500.0</v>
-      </c>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
+        <v>21000.0</v>
+      </c>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
     </row>
     <row r="63">
       <c r="A63" s="4">
@@ -3095,7 +3152,7 @@
         <v>11</v>
       </c>
       <c r="D63" s="4">
-        <v>4500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
@@ -3116,14 +3173,14 @@
         <v>11</v>
       </c>
       <c r="D64" s="4">
-        <v>38000.0</v>
-      </c>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="7"/>
-      <c r="J64" s="7"/>
+        <v>9500.0</v>
+      </c>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
     </row>
     <row r="65">
       <c r="A65" s="4">
@@ -3137,7 +3194,7 @@
         <v>11</v>
       </c>
       <c r="D65" s="4">
-        <v>2000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
@@ -3158,7 +3215,7 @@
         <v>11</v>
       </c>
       <c r="D66" s="4">
-        <v>17000.0</v>
+        <v>38000.0</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="7"/>
@@ -3242,14 +3299,14 @@
         <v>11</v>
       </c>
       <c r="D70" s="4">
-        <v>15000.0</v>
-      </c>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
+        <v>17000.0</v>
+      </c>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
+      <c r="J70" s="7"/>
     </row>
     <row r="71">
       <c r="A71" s="4">
@@ -3263,7 +3320,7 @@
         <v>11</v>
       </c>
       <c r="D71" s="4">
-        <v>2500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
@@ -3284,7 +3341,7 @@
         <v>11</v>
       </c>
       <c r="D72" s="4">
-        <v>21000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
@@ -3305,7 +3362,7 @@
         <v>11</v>
       </c>
       <c r="D73" s="4">
-        <v>2000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
@@ -3326,14 +3383,14 @@
         <v>11</v>
       </c>
       <c r="D74" s="4">
-        <v>15000.0</v>
-      </c>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
+        <v>21000.0</v>
+      </c>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
     </row>
     <row r="75">
       <c r="A75" s="4">
@@ -3370,12 +3427,12 @@
       <c r="D76" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="7"/>
+      <c r="J76" s="7"/>
     </row>
     <row r="77">
       <c r="A77" s="4">
@@ -3454,12 +3511,12 @@
       <c r="D80" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-      <c r="I80" s="7"/>
-      <c r="J80" s="7"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
     </row>
     <row r="81">
       <c r="A81" s="4">
@@ -3496,12 +3553,12 @@
       <c r="D82" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
-      <c r="J82" s="6"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="7"/>
+      <c r="J82" s="7"/>
     </row>
     <row r="83">
       <c r="A83" s="4">
@@ -3536,7 +3593,7 @@
         <v>11</v>
       </c>
       <c r="D84" s="4">
-        <v>2000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
@@ -3557,14 +3614,14 @@
         <v>11</v>
       </c>
       <c r="D85" s="4">
-        <v>16500.0</v>
-      </c>
-      <c r="E85" s="7"/>
-      <c r="F85" s="7"/>
-      <c r="G85" s="7"/>
-      <c r="H85" s="7"/>
-      <c r="I85" s="7"/>
-      <c r="J85" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="6"/>
     </row>
     <row r="86">
       <c r="A86" s="4">
@@ -3599,7 +3656,7 @@
         <v>11</v>
       </c>
       <c r="D87" s="4">
-        <v>17000.0</v>
+        <v>16500.0</v>
       </c>
       <c r="E87" s="7"/>
       <c r="F87" s="7"/>
@@ -3641,14 +3698,14 @@
         <v>11</v>
       </c>
       <c r="D89" s="4">
-        <v>8500.0</v>
-      </c>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6"/>
-      <c r="J89" s="6"/>
+        <v>17000.0</v>
+      </c>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
+      <c r="G89" s="7"/>
+      <c r="H89" s="7"/>
+      <c r="I89" s="7"/>
+      <c r="J89" s="7"/>
     </row>
     <row r="90">
       <c r="A90" s="4">
@@ -3683,7 +3740,7 @@
         <v>11</v>
       </c>
       <c r="D91" s="4">
-        <v>17000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="E91" s="6"/>
       <c r="F91" s="6"/>
@@ -3725,14 +3782,14 @@
         <v>11</v>
       </c>
       <c r="D93" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="7"/>
-      <c r="H93" s="7"/>
-      <c r="I93" s="7"/>
-      <c r="J93" s="7"/>
+        <v>17000.0</v>
+      </c>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="6"/>
+      <c r="J93" s="6"/>
     </row>
     <row r="94">
       <c r="A94" s="4">
@@ -3746,7 +3803,7 @@
         <v>11</v>
       </c>
       <c r="D94" s="4">
-        <v>10000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
@@ -3767,14 +3824,14 @@
         <v>11</v>
       </c>
       <c r="D95" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-      <c r="J95" s="6"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
+      <c r="I95" s="7"/>
+      <c r="J95" s="7"/>
     </row>
     <row r="96">
       <c r="A96" s="4">
@@ -3788,7 +3845,7 @@
         <v>11</v>
       </c>
       <c r="D96" s="4">
-        <v>90000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E96" s="6"/>
       <c r="F96" s="6"/>
@@ -3809,7 +3866,7 @@
         <v>11</v>
       </c>
       <c r="D97" s="4">
-        <v>2000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
@@ -3830,14 +3887,14 @@
         <v>11</v>
       </c>
       <c r="D98" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
-      <c r="G98" s="7"/>
-      <c r="H98" s="7"/>
-      <c r="I98" s="7"/>
-      <c r="J98" s="7"/>
+        <v>90000.0</v>
+      </c>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="6"/>
     </row>
     <row r="99">
       <c r="A99" s="4">
@@ -3851,14 +3908,14 @@
         <v>11</v>
       </c>
       <c r="D99" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="7"/>
-      <c r="H99" s="7"/>
-      <c r="I99" s="7"/>
-      <c r="J99" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6"/>
+      <c r="J99" s="6"/>
     </row>
     <row r="100">
       <c r="A100" s="4">
@@ -3872,7 +3929,7 @@
         <v>11</v>
       </c>
       <c r="D100" s="4">
-        <v>23000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E100" s="7"/>
       <c r="F100" s="7"/>
@@ -3893,7 +3950,7 @@
         <v>11</v>
       </c>
       <c r="D101" s="4">
-        <v>2000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E101" s="7"/>
       <c r="F101" s="7"/>
@@ -3914,14 +3971,14 @@
         <v>11</v>
       </c>
       <c r="D102" s="4">
-        <v>15500.0</v>
-      </c>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
-      <c r="J102" s="6"/>
+        <v>23000.0</v>
+      </c>
+      <c r="E102" s="7"/>
+      <c r="F102" s="7"/>
+      <c r="G102" s="7"/>
+      <c r="H102" s="7"/>
+      <c r="I102" s="7"/>
+      <c r="J102" s="7"/>
     </row>
     <row r="103">
       <c r="A103" s="4">
@@ -3935,14 +3992,14 @@
         <v>11</v>
       </c>
       <c r="D103" s="4">
-        <v>1500.0</v>
-      </c>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6"/>
-      <c r="J103" s="6"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E103" s="7"/>
+      <c r="F103" s="7"/>
+      <c r="G103" s="7"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="7"/>
+      <c r="J103" s="7"/>
     </row>
     <row r="104">
       <c r="A104" s="4">
@@ -3956,7 +4013,7 @@
         <v>11</v>
       </c>
       <c r="D104" s="4">
-        <v>11500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
@@ -3977,7 +4034,7 @@
         <v>11</v>
       </c>
       <c r="D105" s="4">
-        <v>1000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
@@ -3998,7 +4055,7 @@
         <v>11</v>
       </c>
       <c r="D106" s="4">
-        <v>9000.0</v>
+        <v>11500.0</v>
       </c>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -4019,7 +4076,7 @@
         <v>11</v>
       </c>
       <c r="D107" s="4">
-        <v>2500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
@@ -4040,7 +4097,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="4">
-        <v>19000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
@@ -4061,7 +4118,7 @@
         <v>11</v>
       </c>
       <c r="D109" s="4">
-        <v>1500.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
@@ -4082,7 +4139,7 @@
         <v>11</v>
       </c>
       <c r="D110" s="4">
-        <v>8500.0</v>
+        <v>19000.0</v>
       </c>
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
@@ -4103,7 +4160,7 @@
         <v>11</v>
       </c>
       <c r="D111" s="4">
-        <v>3500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
@@ -4124,7 +4181,7 @@
         <v>11</v>
       </c>
       <c r="D112" s="4">
-        <v>15000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
@@ -4145,7 +4202,7 @@
         <v>11</v>
       </c>
       <c r="D113" s="4">
-        <v>2000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
@@ -4166,7 +4223,7 @@
         <v>11</v>
       </c>
       <c r="D114" s="4">
-        <v>16000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
@@ -4187,7 +4244,7 @@
         <v>11</v>
       </c>
       <c r="D115" s="4">
-        <v>1500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
@@ -4226,10 +4283,10 @@
         <v>127</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>128</v>
+        <v>11</v>
       </c>
       <c r="D117" s="4">
-        <v>6000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
@@ -4244,20 +4301,20 @@
         <v>117</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>128</v>
+        <v>11</v>
       </c>
       <c r="D118" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E118" s="7"/>
-      <c r="F118" s="7"/>
-      <c r="G118" s="7"/>
-      <c r="H118" s="7"/>
-      <c r="I118" s="7"/>
-      <c r="J118" s="7"/>
+        <v>16000.0</v>
+      </c>
+      <c r="E118" s="6"/>
+      <c r="F118" s="6"/>
+      <c r="G118" s="6"/>
+      <c r="H118" s="6"/>
+      <c r="I118" s="6"/>
+      <c r="J118" s="6"/>
     </row>
     <row r="119">
       <c r="A119" s="4">
@@ -4265,20 +4322,20 @@
         <v>118</v>
       </c>
       <c r="B119" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C119" s="5" t="s">
-        <v>128</v>
-      </c>
       <c r="D119" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="E119" s="7"/>
-      <c r="F119" s="7"/>
-      <c r="G119" s="7"/>
-      <c r="H119" s="7"/>
-      <c r="I119" s="7"/>
-      <c r="J119" s="7"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="6"/>
+      <c r="H119" s="6"/>
+      <c r="I119" s="6"/>
+      <c r="J119" s="6"/>
     </row>
     <row r="120">
       <c r="A120" s="4">
@@ -4289,7 +4346,7 @@
         <v>131</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D120" s="4">
         <v>1000.0</v>
@@ -4310,7 +4367,7 @@
         <v>132</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D121" s="4">
         <v>10000.0</v>
@@ -4331,7 +4388,7 @@
         <v>133</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D122" s="4">
         <v>1000.0</v>
@@ -4352,7 +4409,7 @@
         <v>134</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D123" s="4">
         <v>10000.0</v>
@@ -4373,10 +4430,10 @@
         <v>135</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D124" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E124" s="7"/>
       <c r="F124" s="7"/>
@@ -4394,17 +4451,17 @@
         <v>136</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D125" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E125" s="6"/>
-      <c r="F125" s="6"/>
-      <c r="G125" s="6"/>
-      <c r="H125" s="6"/>
-      <c r="I125" s="6"/>
-      <c r="J125" s="6"/>
+        <v>10000.0</v>
+      </c>
+      <c r="E125" s="7"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="7"/>
+      <c r="H125" s="7"/>
+      <c r="I125" s="7"/>
+      <c r="J125" s="7"/>
     </row>
     <row r="126">
       <c r="A126" s="4">
@@ -4415,17 +4472,17 @@
         <v>137</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D126" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E126" s="6"/>
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
-      <c r="J126" s="6"/>
+        <v>500.0</v>
+      </c>
+      <c r="E126" s="7"/>
+      <c r="F126" s="7"/>
+      <c r="G126" s="7"/>
+      <c r="H126" s="7"/>
+      <c r="I126" s="7"/>
+      <c r="J126" s="7"/>
     </row>
     <row r="127">
       <c r="A127" s="4">
@@ -4436,10 +4493,10 @@
         <v>138</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D127" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
@@ -4457,10 +4514,10 @@
         <v>139</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D128" s="4">
-        <v>22000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
@@ -4478,10 +4535,10 @@
         <v>140</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D129" s="4">
-        <v>10000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
@@ -4499,10 +4556,10 @@
         <v>141</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D130" s="4">
-        <v>500.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
@@ -4520,10 +4577,10 @@
         <v>142</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D131" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
@@ -4541,10 +4598,10 @@
         <v>143</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D132" s="4">
-        <v>10000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E132" s="6"/>
       <c r="F132" s="6"/>
@@ -4562,10 +4619,10 @@
         <v>144</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D133" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
@@ -4583,10 +4640,10 @@
         <v>145</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D134" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E134" s="6"/>
       <c r="F134" s="6"/>
@@ -4604,10 +4661,10 @@
         <v>146</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D135" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
@@ -4625,17 +4682,13 @@
         <v>147</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D136" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E136" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F136" s="4">
-        <v>1000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E136" s="6"/>
+      <c r="F136" s="6"/>
       <c r="G136" s="6"/>
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
@@ -4650,10 +4703,10 @@
         <v>148</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D137" s="4">
-        <v>6500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
@@ -4671,13 +4724,17 @@
         <v>149</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D138" s="4">
+        <v>500.0</v>
+      </c>
+      <c r="E138" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F138" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E138" s="6"/>
-      <c r="F138" s="6"/>
       <c r="G138" s="6"/>
       <c r="H138" s="6"/>
       <c r="I138" s="6"/>
@@ -4692,10 +4749,10 @@
         <v>150</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D139" s="4">
-        <v>10000.0</v>
+        <v>6500.0</v>
       </c>
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
@@ -4713,17 +4770,13 @@
         <v>151</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D140" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E140" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F140" s="4">
-        <v>13000.0</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
       <c r="G140" s="6"/>
       <c r="H140" s="6"/>
       <c r="I140" s="6"/>
@@ -4738,10 +4791,10 @@
         <v>152</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D141" s="4">
-        <v>23000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
@@ -4759,17 +4812,21 @@
         <v>153</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D142" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E142" s="7"/>
-      <c r="F142" s="7"/>
-      <c r="G142" s="7"/>
-      <c r="H142" s="7"/>
-      <c r="I142" s="7"/>
-      <c r="J142" s="7"/>
+      <c r="E142" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F142" s="4">
+        <v>13000.0</v>
+      </c>
+      <c r="G142" s="6"/>
+      <c r="H142" s="6"/>
+      <c r="I142" s="6"/>
+      <c r="J142" s="6"/>
     </row>
     <row r="143">
       <c r="A143" s="4">
@@ -4780,10 +4837,10 @@
         <v>154</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D143" s="4">
-        <v>26000.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
@@ -4801,17 +4858,17 @@
         <v>155</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D144" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E144" s="6"/>
-      <c r="F144" s="6"/>
-      <c r="G144" s="6"/>
-      <c r="H144" s="6"/>
-      <c r="I144" s="6"/>
-      <c r="J144" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E144" s="7"/>
+      <c r="F144" s="7"/>
+      <c r="G144" s="7"/>
+      <c r="H144" s="7"/>
+      <c r="I144" s="7"/>
+      <c r="J144" s="7"/>
     </row>
     <row r="145">
       <c r="A145" s="4">
@@ -4822,10 +4879,10 @@
         <v>156</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D145" s="4">
-        <v>21000.0</v>
+        <v>26000.0</v>
       </c>
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
@@ -4843,10 +4900,10 @@
         <v>157</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D146" s="4">
-        <v>2000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E146" s="6"/>
       <c r="F146" s="6"/>
@@ -4864,10 +4921,10 @@
         <v>158</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D147" s="4">
-        <v>36500.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E147" s="6"/>
       <c r="F147" s="6"/>
@@ -4885,10 +4942,10 @@
         <v>159</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D148" s="4">
-        <v>13000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E148" s="6"/>
       <c r="F148" s="6"/>
@@ -4906,10 +4963,10 @@
         <v>160</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D149" s="4">
-        <v>500.0</v>
+        <v>36500.0</v>
       </c>
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
@@ -4927,10 +4984,10 @@
         <v>161</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D150" s="4">
-        <v>13500.0</v>
+        <v>13000.0</v>
       </c>
       <c r="E150" s="6"/>
       <c r="F150" s="6"/>
@@ -4948,10 +5005,10 @@
         <v>162</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D151" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E151" s="6"/>
       <c r="F151" s="6"/>
@@ -4969,10 +5026,10 @@
         <v>163</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D152" s="4">
-        <v>160000.0</v>
+        <v>13500.0</v>
       </c>
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
@@ -4990,17 +5047,13 @@
         <v>164</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D153" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E153" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F153" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E153" s="6"/>
+      <c r="F153" s="6"/>
       <c r="G153" s="6"/>
       <c r="H153" s="6"/>
       <c r="I153" s="6"/>
@@ -5015,17 +5068,17 @@
         <v>165</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D154" s="4">
-        <v>65000.0</v>
-      </c>
-      <c r="E154" s="7"/>
-      <c r="F154" s="7"/>
-      <c r="G154" s="7"/>
-      <c r="H154" s="7"/>
-      <c r="I154" s="7"/>
-      <c r="J154" s="7"/>
+        <v>160000.0</v>
+      </c>
+      <c r="E154" s="6"/>
+      <c r="F154" s="6"/>
+      <c r="G154" s="6"/>
+      <c r="H154" s="6"/>
+      <c r="I154" s="6"/>
+      <c r="J154" s="6"/>
     </row>
     <row r="155">
       <c r="A155" s="4">
@@ -5036,17 +5089,21 @@
         <v>166</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D155" s="4">
-        <v>4500.0</v>
-      </c>
-      <c r="E155" s="7"/>
-      <c r="F155" s="7"/>
-      <c r="G155" s="7"/>
-      <c r="H155" s="7"/>
-      <c r="I155" s="7"/>
-      <c r="J155" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E155" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F155" s="4">
+        <v>9000.0</v>
+      </c>
+      <c r="G155" s="6"/>
+      <c r="H155" s="6"/>
+      <c r="I155" s="6"/>
+      <c r="J155" s="6"/>
     </row>
     <row r="156">
       <c r="A156" s="4">
@@ -5057,17 +5114,17 @@
         <v>167</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D156" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E156" s="6"/>
-      <c r="F156" s="6"/>
-      <c r="G156" s="6"/>
-      <c r="H156" s="6"/>
-      <c r="I156" s="6"/>
-      <c r="J156" s="6"/>
+        <v>65000.0</v>
+      </c>
+      <c r="E156" s="7"/>
+      <c r="F156" s="7"/>
+      <c r="G156" s="7"/>
+      <c r="H156" s="7"/>
+      <c r="I156" s="7"/>
+      <c r="J156" s="7"/>
     </row>
     <row r="157">
       <c r="A157" s="4">
@@ -5078,17 +5135,17 @@
         <v>168</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D157" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="E157" s="6"/>
-      <c r="F157" s="6"/>
-      <c r="G157" s="6"/>
-      <c r="H157" s="6"/>
-      <c r="I157" s="6"/>
-      <c r="J157" s="6"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="7"/>
+      <c r="H157" s="7"/>
+      <c r="I157" s="7"/>
+      <c r="J157" s="7"/>
     </row>
     <row r="158">
       <c r="A158" s="4">
@@ -5099,7 +5156,7 @@
         <v>169</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D158" s="4">
         <v>2000.0</v>
@@ -5120,7 +5177,7 @@
         <v>170</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D159" s="4">
         <v>17000.0</v>
@@ -5141,7 +5198,7 @@
         <v>171</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D160" s="4">
         <v>2000.0</v>
@@ -5162,7 +5219,7 @@
         <v>172</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D161" s="4">
         <v>17000.0</v>
@@ -5183,7 +5240,7 @@
         <v>173</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D162" s="4">
         <v>2000.0</v>
@@ -5204,7 +5261,7 @@
         <v>174</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D163" s="4">
         <v>17000.0</v>
@@ -5225,7 +5282,7 @@
         <v>175</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D164" s="4">
         <v>2000.0</v>
@@ -5246,7 +5303,7 @@
         <v>176</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D165" s="4">
         <v>17000.0</v>
@@ -5267,10 +5324,10 @@
         <v>177</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D166" s="4">
-        <v>5000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E166" s="6"/>
       <c r="F166" s="6"/>
@@ -5288,10 +5345,10 @@
         <v>178</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D167" s="4">
-        <v>10000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E167" s="6"/>
       <c r="F167" s="6"/>
@@ -5309,10 +5366,10 @@
         <v>179</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D168" s="4">
-        <v>18000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E168" s="6"/>
       <c r="F168" s="6"/>
@@ -5330,10 +5387,10 @@
         <v>180</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D169" s="4">
-        <v>4500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E169" s="6"/>
       <c r="F169" s="6"/>
@@ -5351,10 +5408,10 @@
         <v>181</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D170" s="4">
-        <v>9000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E170" s="6"/>
       <c r="F170" s="6"/>
@@ -5372,17 +5429,17 @@
         <v>182</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D171" s="4">
-        <v>18000.0</v>
-      </c>
-      <c r="E171" s="4"/>
-      <c r="F171" s="4"/>
-      <c r="G171" s="7"/>
-      <c r="H171" s="7"/>
-      <c r="I171" s="7"/>
-      <c r="J171" s="7"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E171" s="6"/>
+      <c r="F171" s="6"/>
+      <c r="G171" s="6"/>
+      <c r="H171" s="6"/>
+      <c r="I171" s="6"/>
+      <c r="J171" s="6"/>
     </row>
     <row r="172">
       <c r="A172" s="4">
@@ -5393,21 +5450,17 @@
         <v>183</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D172" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E172" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F172" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="G172" s="7"/>
-      <c r="H172" s="7"/>
-      <c r="I172" s="7"/>
-      <c r="J172" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E172" s="6"/>
+      <c r="F172" s="6"/>
+      <c r="G172" s="6"/>
+      <c r="H172" s="6"/>
+      <c r="I172" s="6"/>
+      <c r="J172" s="6"/>
     </row>
     <row r="173">
       <c r="A173" s="4">
@@ -5418,10 +5471,10 @@
         <v>184</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D173" s="4">
-        <v>3500.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
@@ -5439,16 +5492,16 @@
         <v>185</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D174" s="4">
-        <v>2500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E174" s="4">
         <v>4.0</v>
       </c>
       <c r="F174" s="4">
-        <v>8500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="G174" s="7"/>
       <c r="H174" s="7"/>
@@ -5464,13 +5517,13 @@
         <v>186</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D175" s="4">
-        <v>26000.0</v>
-      </c>
-      <c r="E175" s="7"/>
-      <c r="F175" s="7"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E175" s="4"/>
+      <c r="F175" s="4"/>
       <c r="G175" s="7"/>
       <c r="H175" s="7"/>
       <c r="I175" s="7"/>
@@ -5485,16 +5538,16 @@
         <v>187</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D176" s="4">
-        <v>4000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E176" s="4">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F176" s="4">
-        <v>17500.0</v>
+        <v>8500.0</v>
       </c>
       <c r="G176" s="7"/>
       <c r="H176" s="7"/>
@@ -5510,10 +5563,10 @@
         <v>188</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D177" s="4">
-        <v>175000.0</v>
+        <v>26000.0</v>
       </c>
       <c r="E177" s="7"/>
       <c r="F177" s="7"/>
@@ -5531,13 +5584,17 @@
         <v>189</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D178" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E178" s="7"/>
-      <c r="F178" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E178" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F178" s="4">
+        <v>17500.0</v>
+      </c>
       <c r="G178" s="7"/>
       <c r="H178" s="7"/>
       <c r="I178" s="7"/>
@@ -5552,17 +5609,13 @@
         <v>190</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D179" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="E179" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F179" s="4">
-        <v>22000.0</v>
-      </c>
+        <v>175000.0</v>
+      </c>
+      <c r="E179" s="7"/>
+      <c r="F179" s="7"/>
       <c r="G179" s="7"/>
       <c r="H179" s="7"/>
       <c r="I179" s="7"/>
@@ -5577,7 +5630,7 @@
         <v>191</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D180" s="4">
         <v>21000.0</v>
@@ -5598,13 +5651,17 @@
         <v>192</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D181" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E181" s="7"/>
-      <c r="F181" s="7"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E181" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F181" s="4">
+        <v>22000.0</v>
+      </c>
       <c r="G181" s="7"/>
       <c r="H181" s="7"/>
       <c r="I181" s="7"/>
@@ -5619,10 +5676,10 @@
         <v>193</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D182" s="4">
-        <v>245000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E182" s="7"/>
       <c r="F182" s="7"/>
@@ -5640,10 +5697,10 @@
         <v>194</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D183" s="4">
-        <v>42000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E183" s="7"/>
       <c r="F183" s="7"/>
@@ -5661,10 +5718,10 @@
         <v>195</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D184" s="4">
-        <v>44000.0</v>
+        <v>245000.0</v>
       </c>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
@@ -5682,10 +5739,10 @@
         <v>196</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D185" s="4">
-        <v>255000.0</v>
+        <v>42000.0</v>
       </c>
       <c r="E185" s="7"/>
       <c r="F185" s="7"/>
@@ -5703,10 +5760,10 @@
         <v>197</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D186" s="4">
-        <v>21000.0</v>
+        <v>44000.0</v>
       </c>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
@@ -5724,10 +5781,10 @@
         <v>198</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D187" s="4">
-        <v>42000.0</v>
+        <v>255000.0</v>
       </c>
       <c r="E187" s="7"/>
       <c r="F187" s="7"/>
@@ -5745,17 +5802,17 @@
         <v>199</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D188" s="4">
-        <v>14500.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E188" s="7"/>
       <c r="F188" s="7"/>
-      <c r="G188" s="4"/>
-      <c r="H188" s="4"/>
-      <c r="I188" s="4"/>
-      <c r="J188" s="4"/>
+      <c r="G188" s="7"/>
+      <c r="H188" s="7"/>
+      <c r="I188" s="7"/>
+      <c r="J188" s="7"/>
     </row>
     <row r="189">
       <c r="A189" s="4">
@@ -5766,25 +5823,17 @@
         <v>200</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>201</v>
+        <v>130</v>
       </c>
       <c r="D189" s="4">
-        <v>2000.0</v>
+        <v>42000.0</v>
       </c>
       <c r="E189" s="7"/>
       <c r="F189" s="7"/>
-      <c r="G189" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H189" s="4">
-        <v>5500.0</v>
-      </c>
-      <c r="I189" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J189" s="4">
-        <v>10000.0</v>
-      </c>
+      <c r="G189" s="7"/>
+      <c r="H189" s="7"/>
+      <c r="I189" s="7"/>
+      <c r="J189" s="7"/>
     </row>
     <row r="190">
       <c r="A190" s="4">
@@ -5792,20 +5841,20 @@
         <v>189</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>201</v>
+        <v>130</v>
       </c>
       <c r="D190" s="4">
-        <v>10000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E190" s="7"/>
       <c r="F190" s="7"/>
-      <c r="G190" s="7"/>
-      <c r="H190" s="7"/>
-      <c r="I190" s="7"/>
-      <c r="J190" s="7"/>
+      <c r="G190" s="4"/>
+      <c r="H190" s="4"/>
+      <c r="I190" s="4"/>
+      <c r="J190" s="4"/>
     </row>
     <row r="191">
       <c r="A191" s="4">
@@ -5813,10 +5862,10 @@
         <v>190</v>
       </c>
       <c r="B191" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C191" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="D191" s="4">
         <v>2000.0</v>
@@ -5845,7 +5894,7 @@
         <v>204</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D192" s="4">
         <v>10000.0</v>
@@ -5866,7 +5915,7 @@
         <v>205</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D193" s="4">
         <v>2000.0</v>
@@ -5895,7 +5944,7 @@
         <v>206</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D194" s="4">
         <v>10000.0</v>
@@ -5916,7 +5965,7 @@
         <v>207</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D195" s="4">
         <v>2000.0</v>
@@ -5927,13 +5976,13 @@
         <v>6.0</v>
       </c>
       <c r="H195" s="4">
-        <v>6000.0</v>
+        <v>5500.0</v>
       </c>
       <c r="I195" s="4">
         <v>12.0</v>
       </c>
       <c r="J195" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
     </row>
     <row r="196">
@@ -5945,10 +5994,10 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D196" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E196" s="7"/>
       <c r="F196" s="7"/>
@@ -5966,7 +6015,7 @@
         <v>209</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D197" s="4">
         <v>2000.0</v>
@@ -5995,7 +6044,7 @@
         <v>210</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D198" s="4">
         <v>11000.0</v>
@@ -6016,7 +6065,7 @@
         <v>211</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D199" s="4">
         <v>2000.0</v>
@@ -6027,13 +6076,13 @@
         <v>6.0</v>
       </c>
       <c r="H199" s="4">
-        <v>8000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="I199" s="4">
         <v>12.0</v>
       </c>
       <c r="J199" s="4">
-        <v>15000.0</v>
+        <v>11000.0</v>
       </c>
     </row>
     <row r="200">
@@ -6045,10 +6094,10 @@
         <v>212</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D200" s="4">
-        <v>15000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="E200" s="7"/>
       <c r="F200" s="7"/>
@@ -6066,17 +6115,25 @@
         <v>213</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D201" s="4">
-        <v>15000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E201" s="7"/>
       <c r="F201" s="7"/>
-      <c r="G201" s="7"/>
-      <c r="H201" s="7"/>
-      <c r="I201" s="7"/>
-      <c r="J201" s="7"/>
+      <c r="G201" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H201" s="4">
+        <v>8000.0</v>
+      </c>
+      <c r="I201" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J201" s="4">
+        <v>15000.0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4">
@@ -6087,29 +6144,17 @@
         <v>214</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D202" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E202" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F202" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="G202" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H202" s="4">
-        <v>8500.0</v>
-      </c>
-      <c r="I202" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J202" s="4">
-        <v>16000.0</v>
-      </c>
+        <v>15000.0</v>
+      </c>
+      <c r="E202" s="7"/>
+      <c r="F202" s="7"/>
+      <c r="G202" s="7"/>
+      <c r="H202" s="7"/>
+      <c r="I202" s="7"/>
+      <c r="J202" s="7"/>
     </row>
     <row r="203">
       <c r="A203" s="4">
@@ -6120,10 +6165,10 @@
         <v>215</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D203" s="4">
-        <v>16000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E203" s="7"/>
       <c r="F203" s="7"/>
@@ -6141,24 +6186,28 @@
         <v>216</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D204" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E204" s="7"/>
-      <c r="F204" s="7"/>
+      <c r="E204" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F204" s="4">
+        <v>5000.0</v>
+      </c>
       <c r="G204" s="4">
         <v>6.0</v>
       </c>
       <c r="H204" s="4">
-        <v>9000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="I204" s="4">
         <v>12.0</v>
       </c>
       <c r="J204" s="4">
-        <v>17000.0</v>
+        <v>16000.0</v>
       </c>
     </row>
     <row r="205">
@@ -6170,10 +6219,10 @@
         <v>217</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D205" s="4">
-        <v>17000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E205" s="7"/>
       <c r="F205" s="7"/>
@@ -6191,7 +6240,7 @@
         <v>218</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D206" s="4">
         <v>2000.0</v>
@@ -6220,7 +6269,7 @@
         <v>219</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D207" s="4">
         <v>17000.0</v>
@@ -6241,28 +6290,24 @@
         <v>220</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D208" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E208" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F208" s="4">
-        <v>5000.0</v>
-      </c>
+      <c r="E208" s="7"/>
+      <c r="F208" s="7"/>
       <c r="G208" s="4">
         <v>6.0</v>
       </c>
       <c r="H208" s="4">
-        <v>9500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="I208" s="4">
         <v>12.0</v>
       </c>
       <c r="J208" s="4">
-        <v>18000.0</v>
+        <v>17000.0</v>
       </c>
     </row>
     <row r="209">
@@ -6274,10 +6319,10 @@
         <v>221</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D209" s="4">
-        <v>18000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E209" s="7"/>
       <c r="F209" s="7"/>
@@ -6295,24 +6340,28 @@
         <v>222</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D210" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E210" s="7"/>
-      <c r="F210" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E210" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F210" s="4">
+        <v>5000.0</v>
+      </c>
       <c r="G210" s="4">
         <v>6.0</v>
       </c>
       <c r="H210" s="4">
-        <v>14500.0</v>
+        <v>9500.0</v>
       </c>
       <c r="I210" s="4">
         <v>12.0</v>
       </c>
       <c r="J210" s="4">
-        <v>28000.0</v>
+        <v>18000.0</v>
       </c>
     </row>
     <row r="211">
@@ -6324,10 +6373,10 @@
         <v>223</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D211" s="4">
-        <v>28000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E211" s="7"/>
       <c r="F211" s="7"/>
@@ -6345,7 +6394,7 @@
         <v>224</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D212" s="4">
         <v>2500.0</v>
@@ -6356,13 +6405,13 @@
         <v>6.0</v>
       </c>
       <c r="H212" s="4">
-        <v>10500.0</v>
+        <v>14500.0</v>
       </c>
       <c r="I212" s="4">
         <v>12.0</v>
       </c>
       <c r="J212" s="4">
-        <v>20000.0</v>
+        <v>28000.0</v>
       </c>
     </row>
     <row r="213">
@@ -6374,10 +6423,10 @@
         <v>225</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D213" s="4">
-        <v>20000.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E213" s="7"/>
       <c r="F213" s="7"/>
@@ -6395,7 +6444,7 @@
         <v>226</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D214" s="4">
         <v>2500.0</v>
@@ -6406,13 +6455,13 @@
         <v>6.0</v>
       </c>
       <c r="H214" s="4">
-        <v>13000.0</v>
+        <v>10500.0</v>
       </c>
       <c r="I214" s="4">
         <v>12.0</v>
       </c>
       <c r="J214" s="4">
-        <v>25000.0</v>
+        <v>20000.0</v>
       </c>
     </row>
     <row r="215">
@@ -6424,10 +6473,10 @@
         <v>227</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D215" s="4">
-        <v>25000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="E215" s="7"/>
       <c r="F215" s="7"/>
@@ -6445,7 +6494,7 @@
         <v>228</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D216" s="4">
         <v>2500.0</v>
@@ -6456,13 +6505,13 @@
         <v>6.0</v>
       </c>
       <c r="H216" s="4">
-        <v>11000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I216" s="4">
         <v>12.0</v>
       </c>
       <c r="J216" s="4">
-        <v>21000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="217">
@@ -6474,10 +6523,10 @@
         <v>229</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D217" s="4">
-        <v>21000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E217" s="7"/>
       <c r="F217" s="7"/>
@@ -6495,7 +6544,7 @@
         <v>230</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D218" s="4">
         <v>2500.0</v>
@@ -6506,13 +6555,13 @@
         <v>6.0</v>
       </c>
       <c r="H218" s="4">
-        <v>13000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="I218" s="4">
         <v>12.0</v>
       </c>
       <c r="J218" s="4">
-        <v>25000.0</v>
+        <v>21000.0</v>
       </c>
     </row>
     <row r="219">
@@ -6524,10 +6573,10 @@
         <v>231</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D219" s="4">
-        <v>25000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E219" s="7"/>
       <c r="F219" s="7"/>
@@ -6545,7 +6594,7 @@
         <v>232</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D220" s="4">
         <v>2500.0</v>
@@ -6556,13 +6605,13 @@
         <v>6.0</v>
       </c>
       <c r="H220" s="4">
-        <v>14000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I220" s="4">
         <v>12.0</v>
       </c>
       <c r="J220" s="4">
-        <v>28000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="221">
@@ -6574,10 +6623,10 @@
         <v>233</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D221" s="4">
-        <v>28000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E221" s="7"/>
       <c r="F221" s="7"/>
@@ -6595,7 +6644,7 @@
         <v>234</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D222" s="4">
         <v>2500.0</v>
@@ -6606,13 +6655,13 @@
         <v>6.0</v>
       </c>
       <c r="H222" s="4">
-        <v>13000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="I222" s="4">
         <v>12.0</v>
       </c>
       <c r="J222" s="4">
-        <v>25000.0</v>
+        <v>28000.0</v>
       </c>
     </row>
     <row r="223">
@@ -6624,10 +6673,10 @@
         <v>235</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D223" s="4">
-        <v>25000.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E223" s="7"/>
       <c r="F223" s="7"/>
@@ -6645,7 +6694,7 @@
         <v>236</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D224" s="4">
         <v>2500.0</v>
@@ -6656,13 +6705,13 @@
         <v>6.0</v>
       </c>
       <c r="H224" s="4">
-        <v>14000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I224" s="4">
         <v>12.0</v>
       </c>
       <c r="J224" s="4">
-        <v>27000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="225">
@@ -6674,10 +6723,10 @@
         <v>237</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D225" s="4">
-        <v>27000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E225" s="7"/>
       <c r="F225" s="7"/>
@@ -6695,7 +6744,7 @@
         <v>238</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D226" s="4">
         <v>2500.0</v>
@@ -6724,7 +6773,7 @@
         <v>239</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D227" s="4">
         <v>27000.0</v>
@@ -6745,17 +6794,25 @@
         <v>240</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D228" s="4">
-        <v>34000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E228" s="7"/>
       <c r="F228" s="7"/>
-      <c r="G228" s="7"/>
-      <c r="H228" s="7"/>
-      <c r="I228" s="7"/>
-      <c r="J228" s="7"/>
+      <c r="G228" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H228" s="4">
+        <v>14000.0</v>
+      </c>
+      <c r="I228" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J228" s="4">
+        <v>27000.0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="4">
@@ -6766,7 +6823,7 @@
         <v>241</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D229" s="4">
         <v>27000.0</v>
@@ -6787,19 +6844,17 @@
         <v>242</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D230" s="4">
-        <v>37000.0</v>
+        <v>34000.0</v>
       </c>
       <c r="E230" s="7"/>
       <c r="F230" s="7"/>
-      <c r="G230" s="4"/>
-      <c r="H230" s="4"/>
-      <c r="I230" s="4"/>
-      <c r="J230" s="4">
-        <v>37000.0</v>
-      </c>
+      <c r="G230" s="7"/>
+      <c r="H230" s="7"/>
+      <c r="I230" s="7"/>
+      <c r="J230" s="7"/>
     </row>
     <row r="231">
       <c r="A231" s="4">
@@ -6810,10 +6865,10 @@
         <v>243</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D231" s="4">
-        <v>16000.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E231" s="7"/>
       <c r="F231" s="7"/>
@@ -6831,17 +6886,19 @@
         <v>244</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D232" s="4">
-        <v>43000.0</v>
+        <v>37000.0</v>
       </c>
       <c r="E232" s="7"/>
       <c r="F232" s="7"/>
-      <c r="G232" s="7"/>
-      <c r="H232" s="7"/>
-      <c r="I232" s="7"/>
-      <c r="J232" s="7"/>
+      <c r="G232" s="4"/>
+      <c r="H232" s="4"/>
+      <c r="I232" s="4"/>
+      <c r="J232" s="4">
+        <v>37000.0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="4">
@@ -6852,10 +6909,10 @@
         <v>245</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D233" s="4">
-        <v>23000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="7"/>
@@ -6873,10 +6930,10 @@
         <v>246</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D234" s="4">
-        <v>17000.0</v>
+        <v>43000.0</v>
       </c>
       <c r="E234" s="7"/>
       <c r="F234" s="7"/>
@@ -6894,10 +6951,10 @@
         <v>247</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D235" s="4">
-        <v>29000.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E235" s="7"/>
       <c r="F235" s="7"/>
@@ -6915,10 +6972,10 @@
         <v>248</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D236" s="4">
-        <v>13000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E236" s="7"/>
       <c r="F236" s="7"/>
@@ -6936,10 +6993,10 @@
         <v>249</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D237" s="4">
-        <v>39000.0</v>
+        <v>29000.0</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="7"/>
@@ -6957,10 +7014,10 @@
         <v>250</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D238" s="4">
-        <v>382000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="E238" s="7"/>
       <c r="F238" s="7"/>
@@ -6978,10 +7035,10 @@
         <v>251</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>252</v>
+        <v>203</v>
       </c>
       <c r="D239" s="4">
-        <v>500.0</v>
+        <v>39000.0</v>
       </c>
       <c r="E239" s="7"/>
       <c r="F239" s="7"/>
@@ -6996,13 +7053,13 @@
         <v>239</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>252</v>
+        <v>203</v>
       </c>
       <c r="D240" s="4">
-        <v>4000.0</v>
+        <v>382000.0</v>
       </c>
       <c r="E240" s="7"/>
       <c r="F240" s="7"/>
@@ -7017,20 +7074,16 @@
         <v>240</v>
       </c>
       <c r="B241" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C241" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="C241" s="5" t="s">
-        <v>252</v>
-      </c>
       <c r="D241" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E241" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F241" s="4">
-        <v>10000.0</v>
-      </c>
+        <v>500.0</v>
+      </c>
+      <c r="E241" s="7"/>
+      <c r="F241" s="7"/>
       <c r="G241" s="7"/>
       <c r="H241" s="7"/>
       <c r="I241" s="7"/>
@@ -7045,17 +7098,13 @@
         <v>255</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D242" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E242" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F242" s="4">
-        <v>14000.0</v>
-      </c>
+        <v>4000.0</v>
+      </c>
+      <c r="E242" s="7"/>
+      <c r="F242" s="7"/>
       <c r="G242" s="7"/>
       <c r="H242" s="7"/>
       <c r="I242" s="7"/>
@@ -7067,16 +7116,20 @@
         <v>242</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D243" s="4">
-        <v>109000.0</v>
-      </c>
-      <c r="E243" s="7"/>
-      <c r="F243" s="7"/>
+        <v>2500.0</v>
+      </c>
+      <c r="E243" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F243" s="4">
+        <v>10000.0</v>
+      </c>
       <c r="G243" s="7"/>
       <c r="H243" s="7"/>
       <c r="I243" s="7"/>
@@ -7088,10 +7141,10 @@
         <v>243</v>
       </c>
       <c r="B244" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C244" s="5" t="s">
         <v>258</v>
-      </c>
-      <c r="C244" s="5" t="s">
-        <v>256</v>
       </c>
       <c r="D244" s="4">
         <v>3000.0</v>
@@ -7116,7 +7169,7 @@
         <v>259</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D245" s="4">
         <v>109000.0</v>
@@ -7137,13 +7190,17 @@
         <v>260</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D246" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E246" s="7"/>
-      <c r="F246" s="7"/>
+      <c r="E246" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F246" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G246" s="7"/>
       <c r="H246" s="7"/>
       <c r="I246" s="7"/>
@@ -7158,10 +7215,10 @@
         <v>261</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D247" s="4">
-        <v>114000.0</v>
+        <v>109000.0</v>
       </c>
       <c r="E247" s="7"/>
       <c r="F247" s="7"/>
@@ -7179,7 +7236,7 @@
         <v>262</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D248" s="4">
         <v>3000.0</v>
@@ -7200,17 +7257,13 @@
         <v>263</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D249" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E249" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F249" s="4">
-        <v>39000.0</v>
-      </c>
+        <v>114000.0</v>
+      </c>
+      <c r="E249" s="7"/>
+      <c r="F249" s="7"/>
       <c r="G249" s="7"/>
       <c r="H249" s="7"/>
       <c r="I249" s="7"/>
@@ -7225,10 +7278,10 @@
         <v>264</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D250" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E250" s="7"/>
       <c r="F250" s="7"/>
@@ -7246,13 +7299,17 @@
         <v>265</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D251" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E251" s="7"/>
-      <c r="F251" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E251" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F251" s="4">
+        <v>39000.0</v>
+      </c>
       <c r="G251" s="7"/>
       <c r="H251" s="7"/>
       <c r="I251" s="7"/>
@@ -7267,7 +7324,7 @@
         <v>266</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D252" s="4">
         <v>114000.0</v>
@@ -7288,7 +7345,7 @@
         <v>267</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D253" s="4">
         <v>3000.0</v>
@@ -7309,7 +7366,7 @@
         <v>268</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D254" s="4">
         <v>114000.0</v>
@@ -7330,7 +7387,7 @@
         <v>269</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D255" s="4">
         <v>3000.0</v>
@@ -7351,7 +7408,7 @@
         <v>270</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D256" s="4">
         <v>114000.0</v>
@@ -7372,7 +7429,7 @@
         <v>271</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D257" s="4">
         <v>3000.0</v>
@@ -7393,10 +7450,10 @@
         <v>272</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D258" s="4">
-        <v>107000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E258" s="7"/>
       <c r="F258" s="7"/>
@@ -7414,7 +7471,7 @@
         <v>273</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D259" s="4">
         <v>3000.0</v>
@@ -7435,17 +7492,17 @@
         <v>274</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D260" s="4">
-        <v>112000.0</v>
-      </c>
-      <c r="E260" s="6"/>
-      <c r="F260" s="6"/>
-      <c r="G260" s="6"/>
-      <c r="H260" s="6"/>
-      <c r="I260" s="6"/>
-      <c r="J260" s="6"/>
+        <v>107000.0</v>
+      </c>
+      <c r="E260" s="7"/>
+      <c r="F260" s="7"/>
+      <c r="G260" s="7"/>
+      <c r="H260" s="7"/>
+      <c r="I260" s="7"/>
+      <c r="J260" s="7"/>
     </row>
     <row r="261">
       <c r="A261" s="4">
@@ -7456,17 +7513,13 @@
         <v>275</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D261" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E261" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F261" s="4">
-        <v>19000.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E261" s="7"/>
+      <c r="F261" s="7"/>
       <c r="G261" s="7"/>
       <c r="H261" s="7"/>
       <c r="I261" s="7"/>
@@ -7481,21 +7534,17 @@
         <v>276</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D262" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E262" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F262" s="4">
-        <v>19000.0</v>
-      </c>
-      <c r="G262" s="7"/>
-      <c r="H262" s="7"/>
-      <c r="I262" s="7"/>
-      <c r="J262" s="7"/>
+        <v>112000.0</v>
+      </c>
+      <c r="E262" s="6"/>
+      <c r="F262" s="6"/>
+      <c r="G262" s="6"/>
+      <c r="H262" s="6"/>
+      <c r="I262" s="6"/>
+      <c r="J262" s="6"/>
     </row>
     <row r="263">
       <c r="A263" s="4">
@@ -7506,13 +7555,17 @@
         <v>277</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D263" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E263" s="4"/>
-      <c r="F263" s="4"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E263" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F263" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G263" s="7"/>
       <c r="H263" s="7"/>
       <c r="I263" s="7"/>
@@ -7527,13 +7580,17 @@
         <v>278</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D264" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E264" s="4"/>
-      <c r="F264" s="4"/>
+      <c r="E264" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F264" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G264" s="7"/>
       <c r="H264" s="7"/>
       <c r="I264" s="7"/>
@@ -7548,7 +7605,7 @@
         <v>279</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D265" s="4">
         <v>86000.0</v>
@@ -7569,18 +7626,14 @@
         <v>280</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D266" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E266" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F266" s="4">
-        <v>19500.0</v>
-      </c>
-      <c r="G266" s="4"/>
+      <c r="E266" s="4"/>
+      <c r="F266" s="4"/>
+      <c r="G266" s="7"/>
       <c r="H266" s="7"/>
       <c r="I266" s="7"/>
       <c r="J266" s="7"/>
@@ -7594,17 +7647,13 @@
         <v>281</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D267" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E267" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F267" s="4">
-        <v>6000.0</v>
-      </c>
+        <v>86000.0</v>
+      </c>
+      <c r="E267" s="4"/>
+      <c r="F267" s="4"/>
       <c r="G267" s="7"/>
       <c r="H267" s="7"/>
       <c r="I267" s="7"/>
@@ -7619,14 +7668,18 @@
         <v>282</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D268" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E268" s="7"/>
-      <c r="F268" s="7"/>
-      <c r="G268" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E268" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F268" s="4">
+        <v>19500.0</v>
+      </c>
+      <c r="G268" s="4"/>
       <c r="H268" s="7"/>
       <c r="I268" s="7"/>
       <c r="J268" s="7"/>
@@ -7640,13 +7693,17 @@
         <v>283</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D269" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E269" s="7"/>
-      <c r="F269" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E269" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F269" s="4">
+        <v>6000.0</v>
+      </c>
       <c r="G269" s="7"/>
       <c r="H269" s="7"/>
       <c r="I269" s="7"/>
@@ -7661,10 +7718,10 @@
         <v>284</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D270" s="4">
-        <v>89000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E270" s="7"/>
       <c r="F270" s="7"/>
@@ -7682,10 +7739,10 @@
         <v>285</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D271" s="4">
-        <v>7500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E271" s="7"/>
       <c r="F271" s="7"/>
@@ -7703,10 +7760,10 @@
         <v>286</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D272" s="4">
-        <v>5000.0</v>
+        <v>89000.0</v>
       </c>
       <c r="E272" s="7"/>
       <c r="F272" s="7"/>
@@ -7724,10 +7781,10 @@
         <v>287</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D273" s="4">
-        <v>3000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E273" s="7"/>
       <c r="F273" s="7"/>
@@ -7745,17 +7802,17 @@
         <v>288</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="D274" s="4">
-        <v>80000.0</v>
-      </c>
-      <c r="E274" s="6"/>
-      <c r="F274" s="6"/>
-      <c r="G274" s="6"/>
-      <c r="H274" s="6"/>
-      <c r="I274" s="6"/>
-      <c r="J274" s="6"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E274" s="7"/>
+      <c r="F274" s="7"/>
+      <c r="G274" s="7"/>
+      <c r="H274" s="7"/>
+      <c r="I274" s="7"/>
+      <c r="J274" s="7"/>
     </row>
     <row r="275">
       <c r="A275" s="4">
@@ -7766,10 +7823,10 @@
         <v>289</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="D275" s="4">
-        <v>14000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E275" s="7"/>
       <c r="F275" s="7"/>
@@ -7784,20 +7841,20 @@
         <v>275</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D276" s="4">
-        <v>14500.0</v>
-      </c>
-      <c r="E276" s="7"/>
-      <c r="F276" s="7"/>
-      <c r="G276" s="7"/>
-      <c r="H276" s="7"/>
-      <c r="I276" s="7"/>
-      <c r="J276" s="7"/>
+        <v>80000.0</v>
+      </c>
+      <c r="E276" s="6"/>
+      <c r="F276" s="6"/>
+      <c r="G276" s="6"/>
+      <c r="H276" s="6"/>
+      <c r="I276" s="6"/>
+      <c r="J276" s="6"/>
     </row>
     <row r="277">
       <c r="A277" s="4">
@@ -7805,13 +7862,13 @@
         <v>276</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D277" s="4">
-        <v>15000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E277" s="7"/>
       <c r="F277" s="7"/>
@@ -7826,13 +7883,13 @@
         <v>277</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D278" s="4">
-        <v>15500.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E278" s="7"/>
       <c r="F278" s="7"/>
@@ -7847,13 +7904,13 @@
         <v>278</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C279" s="5" t="s">
         <v>291</v>
       </c>
       <c r="D279" s="4">
-        <v>1500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E279" s="7"/>
       <c r="F279" s="7"/>
@@ -7868,13 +7925,13 @@
         <v>279</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C280" s="5" t="s">
         <v>291</v>
       </c>
       <c r="D280" s="4">
-        <v>12500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E280" s="7"/>
       <c r="F280" s="7"/>
@@ -7889,13 +7946,13 @@
         <v>280</v>
       </c>
       <c r="B281" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C281" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="C281" s="5" t="s">
-        <v>291</v>
-      </c>
       <c r="D281" s="4">
-        <v>500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E281" s="7"/>
       <c r="F281" s="7"/>
@@ -7913,10 +7970,10 @@
         <v>294</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D282" s="4">
-        <v>4500.0</v>
+        <v>12500.0</v>
       </c>
       <c r="E282" s="7"/>
       <c r="F282" s="7"/>
@@ -7934,10 +7991,10 @@
         <v>295</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D283" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E283" s="7"/>
       <c r="F283" s="7"/>
@@ -7955,10 +8012,10 @@
         <v>296</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D284" s="4">
-        <v>23000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E284" s="7"/>
       <c r="F284" s="7"/>
@@ -7976,17 +8033,13 @@
         <v>297</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D285" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E285" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F285" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E285" s="7"/>
+      <c r="F285" s="7"/>
       <c r="G285" s="7"/>
       <c r="H285" s="7"/>
       <c r="I285" s="7"/>
@@ -8001,13 +8054,13 @@
         <v>298</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D286" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E286" s="4"/>
-      <c r="F286" s="4"/>
+        <v>23000.0</v>
+      </c>
+      <c r="E286" s="7"/>
+      <c r="F286" s="7"/>
       <c r="G286" s="7"/>
       <c r="H286" s="7"/>
       <c r="I286" s="7"/>
@@ -8022,16 +8075,16 @@
         <v>299</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D287" s="4">
-        <v>2500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E287" s="4">
         <v>5.0</v>
       </c>
       <c r="F287" s="4">
-        <v>9000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="G287" s="7"/>
       <c r="H287" s="7"/>
@@ -8047,10 +8100,10 @@
         <v>300</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D288" s="4">
-        <v>9000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E288" s="4"/>
       <c r="F288" s="4"/>
@@ -8068,16 +8121,16 @@
         <v>301</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D289" s="4">
-        <v>2000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E289" s="4">
         <v>5.0</v>
       </c>
       <c r="F289" s="4">
-        <v>7500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="G289" s="7"/>
       <c r="H289" s="7"/>
@@ -8093,13 +8146,13 @@
         <v>302</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D290" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E290" s="7"/>
-      <c r="F290" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E290" s="4"/>
+      <c r="F290" s="4"/>
       <c r="G290" s="7"/>
       <c r="H290" s="7"/>
       <c r="I290" s="7"/>
@@ -8114,13 +8167,17 @@
         <v>303</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="D291" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E291" s="7"/>
-      <c r="F291" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E291" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F291" s="4">
+        <v>7500.0</v>
+      </c>
       <c r="G291" s="7"/>
       <c r="H291" s="7"/>
       <c r="I291" s="7"/>
@@ -8132,13 +8189,13 @@
         <v>291</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="D292" s="4">
-        <v>10000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E292" s="7"/>
       <c r="F292" s="7"/>
@@ -8153,13 +8210,13 @@
         <v>292</v>
       </c>
       <c r="B293" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="C293" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="C293" s="5" t="s">
-        <v>304</v>
-      </c>
       <c r="D293" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E293" s="7"/>
       <c r="F293" s="7"/>
@@ -8177,10 +8234,10 @@
         <v>307</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D294" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E294" s="7"/>
       <c r="F294" s="7"/>
@@ -8198,10 +8255,10 @@
         <v>308</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D295" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E295" s="7"/>
       <c r="F295" s="7"/>
@@ -8219,10 +8276,10 @@
         <v>309</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D296" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E296" s="7"/>
       <c r="F296" s="7"/>
@@ -8240,10 +8297,10 @@
         <v>310</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D297" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E297" s="7"/>
       <c r="F297" s="7"/>
@@ -8261,10 +8318,10 @@
         <v>311</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D298" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E298" s="7"/>
       <c r="F298" s="7"/>
@@ -8282,10 +8339,10 @@
         <v>312</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D299" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E299" s="7"/>
       <c r="F299" s="7"/>
@@ -8303,10 +8360,10 @@
         <v>313</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D300" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E300" s="7"/>
       <c r="F300" s="7"/>
@@ -8324,7 +8381,7 @@
         <v>314</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D301" s="4">
         <v>1000.0</v>
@@ -8345,7 +8402,7 @@
         <v>315</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D302" s="4">
         <v>10000.0</v>
@@ -8366,10 +8423,10 @@
         <v>316</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D303" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E303" s="7"/>
       <c r="F303" s="7"/>
@@ -8387,10 +8444,10 @@
         <v>317</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D304" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E304" s="7"/>
       <c r="F304" s="7"/>
@@ -8408,10 +8465,10 @@
         <v>318</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D305" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E305" s="7"/>
       <c r="F305" s="7"/>
@@ -8429,7 +8486,7 @@
         <v>319</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D306" s="4">
         <v>500.0</v>
@@ -8450,7 +8507,7 @@
         <v>320</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D307" s="4">
         <v>5000.0</v>
@@ -8471,10 +8528,10 @@
         <v>321</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D308" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E308" s="7"/>
       <c r="F308" s="7"/>
@@ -8492,10 +8549,10 @@
         <v>322</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D309" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E309" s="7"/>
       <c r="F309" s="7"/>
@@ -8513,10 +8570,10 @@
         <v>323</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D310" s="4">
-        <v>2000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E310" s="7"/>
       <c r="F310" s="7"/>
@@ -8534,10 +8591,10 @@
         <v>324</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D311" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E311" s="7"/>
       <c r="F311" s="7"/>
@@ -8555,10 +8612,10 @@
         <v>325</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D312" s="4">
-        <v>1000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E312" s="7"/>
       <c r="F312" s="7"/>
@@ -8576,7 +8633,7 @@
         <v>326</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D313" s="4">
         <v>5000.0</v>
@@ -8597,7 +8654,7 @@
         <v>327</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D314" s="4">
         <v>1000.0</v>
@@ -8618,7 +8675,7 @@
         <v>328</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D315" s="4">
         <v>5000.0</v>
@@ -8639,7 +8696,7 @@
         <v>329</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D316" s="4">
         <v>1000.0</v>
@@ -8660,7 +8717,7 @@
         <v>330</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D317" s="4">
         <v>5000.0</v>
@@ -8681,10 +8738,10 @@
         <v>331</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D318" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E318" s="7"/>
       <c r="F318" s="7"/>
@@ -8702,10 +8759,10 @@
         <v>332</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D319" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E319" s="7"/>
       <c r="F319" s="7"/>
@@ -8723,10 +8780,10 @@
         <v>333</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D320" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E320" s="7"/>
       <c r="F320" s="7"/>
@@ -8744,10 +8801,10 @@
         <v>334</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D321" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E321" s="7"/>
       <c r="F321" s="7"/>
@@ -8765,10 +8822,10 @@
         <v>335</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D322" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E322" s="7"/>
       <c r="F322" s="7"/>
@@ -8786,7 +8843,7 @@
         <v>336</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D323" s="4">
         <v>5000.0</v>
@@ -8807,7 +8864,7 @@
         <v>337</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D324" s="4">
         <v>500.0</v>
@@ -8828,7 +8885,7 @@
         <v>338</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D325" s="4">
         <v>5000.0</v>
@@ -8849,10 +8906,10 @@
         <v>339</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D326" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E326" s="7"/>
       <c r="F326" s="7"/>
@@ -8870,7 +8927,7 @@
         <v>340</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D327" s="4">
         <v>5000.0</v>
@@ -8891,17 +8948,13 @@
         <v>341</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D328" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E328" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F328" s="4">
-        <v>4500.0</v>
-      </c>
+      <c r="E328" s="7"/>
+      <c r="F328" s="7"/>
       <c r="G328" s="7"/>
       <c r="H328" s="7"/>
       <c r="I328" s="7"/>
@@ -8916,10 +8969,10 @@
         <v>342</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D329" s="4">
-        <v>4500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E329" s="7"/>
       <c r="F329" s="7"/>
@@ -8937,13 +8990,17 @@
         <v>343</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D330" s="4">
-        <v>51000.0</v>
-      </c>
-      <c r="E330" s="4"/>
-      <c r="F330" s="4"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E330" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F330" s="4">
+        <v>4500.0</v>
+      </c>
       <c r="G330" s="7"/>
       <c r="H330" s="7"/>
       <c r="I330" s="7"/>
@@ -8958,17 +9015,13 @@
         <v>344</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D331" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E331" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F331" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>4500.0</v>
+      </c>
+      <c r="E331" s="7"/>
+      <c r="F331" s="7"/>
       <c r="G331" s="7"/>
       <c r="H331" s="7"/>
       <c r="I331" s="7"/>
@@ -8983,13 +9036,13 @@
         <v>345</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D332" s="4">
-        <v>52000.0</v>
-      </c>
-      <c r="E332" s="7"/>
-      <c r="F332" s="7"/>
+        <v>51000.0</v>
+      </c>
+      <c r="E332" s="4"/>
+      <c r="F332" s="4"/>
       <c r="G332" s="7"/>
       <c r="H332" s="7"/>
       <c r="I332" s="7"/>
@@ -9004,13 +9057,17 @@
         <v>346</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D333" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E333" s="7"/>
-      <c r="F333" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E333" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F333" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G333" s="7"/>
       <c r="H333" s="7"/>
       <c r="I333" s="7"/>
@@ -9025,10 +9082,10 @@
         <v>347</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D334" s="4">
-        <v>5000.0</v>
+        <v>52000.0</v>
       </c>
       <c r="E334" s="7"/>
       <c r="F334" s="7"/>
@@ -9046,17 +9103,13 @@
         <v>348</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D335" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E335" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F335" s="4">
-        <v>17000.0</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E335" s="7"/>
+      <c r="F335" s="7"/>
       <c r="G335" s="7"/>
       <c r="H335" s="7"/>
       <c r="I335" s="7"/>
@@ -9071,7 +9124,7 @@
         <v>349</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D336" s="4">
         <v>5000.0</v>
@@ -9092,16 +9145,16 @@
         <v>350</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D337" s="4">
-        <v>7000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E337" s="4">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F337" s="4">
-        <v>32500.0</v>
+        <v>17000.0</v>
       </c>
       <c r="G337" s="7"/>
       <c r="H337" s="7"/>
@@ -9117,10 +9170,10 @@
         <v>351</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D338" s="4">
-        <v>7500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E338" s="7"/>
       <c r="F338" s="7"/>
@@ -9138,13 +9191,17 @@
         <v>352</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D339" s="4">
-        <v>9500.0</v>
-      </c>
-      <c r="E339" s="7"/>
-      <c r="F339" s="7"/>
+        <v>7000.0</v>
+      </c>
+      <c r="E339" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F339" s="4">
+        <v>32500.0</v>
+      </c>
       <c r="G339" s="7"/>
       <c r="H339" s="7"/>
       <c r="I339" s="7"/>
@@ -9159,10 +9216,10 @@
         <v>353</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D340" s="4">
-        <v>3500.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E340" s="7"/>
       <c r="F340" s="7"/>
@@ -9180,10 +9237,10 @@
         <v>354</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D341" s="4">
-        <v>5000.0</v>
+        <v>9500.0</v>
       </c>
       <c r="E341" s="7"/>
       <c r="F341" s="7"/>
@@ -9201,17 +9258,13 @@
         <v>355</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D342" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E342" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F342" s="4">
-        <v>22500.0</v>
-      </c>
+        <v>3500.0</v>
+      </c>
+      <c r="E342" s="7"/>
+      <c r="F342" s="7"/>
       <c r="G342" s="7"/>
       <c r="H342" s="7"/>
       <c r="I342" s="7"/>
@@ -9226,17 +9279,13 @@
         <v>356</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D343" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E343" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F343" s="4">
-        <v>12500.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E343" s="7"/>
+      <c r="F343" s="7"/>
       <c r="G343" s="7"/>
       <c r="H343" s="7"/>
       <c r="I343" s="7"/>
@@ -9251,13 +9300,17 @@
         <v>357</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D344" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E344" s="4"/>
-      <c r="F344" s="4"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E344" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F344" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G344" s="7"/>
       <c r="H344" s="7"/>
       <c r="I344" s="7"/>
@@ -9272,14 +9325,18 @@
         <v>358</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D345" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E345" s="4"/>
-      <c r="F345" s="4"/>
-      <c r="G345" s="4"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E345" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F345" s="4">
+        <v>12500.0</v>
+      </c>
+      <c r="G345" s="7"/>
       <c r="H345" s="7"/>
       <c r="I345" s="7"/>
       <c r="J345" s="7"/>
@@ -9293,17 +9350,13 @@
         <v>359</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D346" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E346" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F346" s="4">
-        <v>11500.0</v>
-      </c>
+        <v>3500.0</v>
+      </c>
+      <c r="E346" s="4"/>
+      <c r="F346" s="4"/>
       <c r="G346" s="7"/>
       <c r="H346" s="7"/>
       <c r="I346" s="7"/>
@@ -9318,14 +9371,14 @@
         <v>360</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D347" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E347" s="7"/>
-      <c r="F347" s="7"/>
-      <c r="G347" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E347" s="4"/>
+      <c r="F347" s="4"/>
+      <c r="G347" s="4"/>
       <c r="H347" s="7"/>
       <c r="I347" s="7"/>
       <c r="J347" s="7"/>
@@ -9339,16 +9392,16 @@
         <v>361</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D348" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E348" s="4">
         <v>5.0</v>
       </c>
       <c r="F348" s="4">
-        <v>22500.0</v>
+        <v>11500.0</v>
       </c>
       <c r="G348" s="7"/>
       <c r="H348" s="7"/>
@@ -9364,10 +9417,10 @@
         <v>362</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D349" s="4">
-        <v>1000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E349" s="7"/>
       <c r="F349" s="7"/>
@@ -9385,13 +9438,17 @@
         <v>363</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D350" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E350" s="7"/>
-      <c r="F350" s="7"/>
+      <c r="E350" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F350" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G350" s="7"/>
       <c r="H350" s="7"/>
       <c r="I350" s="7"/>
@@ -9406,10 +9463,10 @@
         <v>364</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D351" s="4">
-        <v>3000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E351" s="7"/>
       <c r="F351" s="7"/>
@@ -9427,10 +9484,10 @@
         <v>365</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D352" s="4">
-        <v>14000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E352" s="7"/>
       <c r="F352" s="7"/>
@@ -9448,10 +9505,10 @@
         <v>366</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>367</v>
+        <v>306</v>
       </c>
       <c r="D353" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E353" s="7"/>
       <c r="F353" s="7"/>
@@ -9466,13 +9523,13 @@
         <v>353</v>
       </c>
       <c r="B354" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>367</v>
+        <v>306</v>
       </c>
       <c r="D354" s="4">
-        <v>4000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E354" s="7"/>
       <c r="F354" s="7"/>
@@ -9487,10 +9544,10 @@
         <v>354</v>
       </c>
       <c r="B355" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C355" s="5" t="s">
         <v>369</v>
-      </c>
-      <c r="C355" s="5" t="s">
-        <v>367</v>
       </c>
       <c r="D355" s="4">
         <v>1000.0</v>
@@ -9511,10 +9568,10 @@
         <v>370</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D356" s="4">
-        <v>10000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E356" s="7"/>
       <c r="F356" s="7"/>
@@ -9532,7 +9589,7 @@
         <v>371</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D357" s="4">
         <v>1000.0</v>
@@ -9553,7 +9610,7 @@
         <v>372</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D358" s="4">
         <v>10000.0</v>
@@ -9574,10 +9631,10 @@
         <v>373</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D359" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E359" s="7"/>
       <c r="F359" s="7"/>
@@ -9595,10 +9652,10 @@
         <v>374</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D360" s="4">
-        <v>2500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E360" s="7"/>
       <c r="F360" s="7"/>
@@ -9616,10 +9673,10 @@
         <v>375</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D361" s="4">
-        <v>3000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E361" s="7"/>
       <c r="F361" s="7"/>
@@ -9637,10 +9694,10 @@
         <v>376</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D362" s="4">
-        <v>5000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E362" s="7"/>
       <c r="F362" s="7"/>
@@ -9658,7 +9715,7 @@
         <v>377</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D363" s="4">
         <v>3000.0</v>
@@ -9679,17 +9736,13 @@
         <v>378</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D364" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E364" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F364" s="4">
-        <v>3000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E364" s="7"/>
+      <c r="F364" s="7"/>
       <c r="G364" s="7"/>
       <c r="H364" s="7"/>
       <c r="I364" s="7"/>
@@ -9704,10 +9757,10 @@
         <v>379</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D365" s="4">
-        <v>500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E365" s="7"/>
       <c r="F365" s="7"/>
@@ -9725,13 +9778,17 @@
         <v>380</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D366" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E366" s="7"/>
-      <c r="F366" s="7"/>
+      <c r="E366" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F366" s="4">
+        <v>3000.0</v>
+      </c>
       <c r="G366" s="7"/>
       <c r="H366" s="7"/>
       <c r="I366" s="7"/>
@@ -9746,10 +9803,10 @@
         <v>381</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D367" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E367" s="7"/>
       <c r="F367" s="7"/>
@@ -9767,10 +9824,10 @@
         <v>382</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D368" s="4">
-        <v>7000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E368" s="7"/>
       <c r="F368" s="7"/>
@@ -9788,10 +9845,10 @@
         <v>383</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D369" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E369" s="7"/>
       <c r="F369" s="7"/>
@@ -9809,10 +9866,10 @@
         <v>384</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D370" s="4">
-        <v>25000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E370" s="7"/>
       <c r="F370" s="7"/>
@@ -9830,10 +9887,10 @@
         <v>385</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D371" s="4">
-        <v>8000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E371" s="7"/>
       <c r="F371" s="7"/>
@@ -9851,10 +9908,10 @@
         <v>386</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D372" s="4">
-        <v>4000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E372" s="7"/>
       <c r="F372" s="7"/>
@@ -9872,10 +9929,10 @@
         <v>387</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="D373" s="4">
-        <v>2000.0</v>
+        <v>8000.0</v>
       </c>
       <c r="E373" s="7"/>
       <c r="F373" s="7"/>
@@ -9890,13 +9947,13 @@
         <v>373</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="D374" s="4">
-        <v>45000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E374" s="7"/>
       <c r="F374" s="7"/>
@@ -9911,13 +9968,13 @@
         <v>374</v>
       </c>
       <c r="B375" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C375" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="C375" s="5" t="s">
-        <v>388</v>
-      </c>
       <c r="D375" s="4">
-        <v>2500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E375" s="7"/>
       <c r="F375" s="7"/>
@@ -9935,10 +9992,10 @@
         <v>391</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D376" s="4">
-        <v>2500.0</v>
+        <v>45000.0</v>
       </c>
       <c r="E376" s="7"/>
       <c r="F376" s="7"/>
@@ -9956,10 +10013,10 @@
         <v>392</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D377" s="4">
-        <v>4000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E377" s="7"/>
       <c r="F377" s="7"/>
@@ -9977,10 +10034,10 @@
         <v>393</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D378" s="4">
-        <v>40000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E378" s="7"/>
       <c r="F378" s="7"/>
@@ -9998,10 +10055,10 @@
         <v>394</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D379" s="4">
-        <v>5000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E379" s="7"/>
       <c r="F379" s="7"/>
@@ -10019,16 +10076,16 @@
         <v>395</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D380" s="4">
-        <v>46000.0</v>
+        <v>40000.0</v>
       </c>
       <c r="E380" s="7"/>
       <c r="F380" s="7"/>
       <c r="G380" s="7"/>
       <c r="H380" s="7"/>
-      <c r="I380" s="4"/>
+      <c r="I380" s="7"/>
       <c r="J380" s="7"/>
     </row>
     <row r="381">
@@ -10040,16 +10097,16 @@
         <v>396</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D381" s="4">
-        <v>2000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E381" s="7"/>
       <c r="F381" s="7"/>
       <c r="G381" s="7"/>
       <c r="H381" s="7"/>
-      <c r="I381" s="4"/>
+      <c r="I381" s="7"/>
       <c r="J381" s="7"/>
     </row>
     <row r="382">
@@ -10061,10 +10118,10 @@
         <v>397</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D382" s="4">
-        <v>17000.0</v>
+        <v>46000.0</v>
       </c>
       <c r="E382" s="7"/>
       <c r="F382" s="7"/>
@@ -10082,10 +10139,10 @@
         <v>398</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D383" s="4">
-        <v>500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E383" s="7"/>
       <c r="F383" s="7"/>
@@ -10103,16 +10160,16 @@
         <v>399</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D384" s="4">
-        <v>1000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E384" s="7"/>
       <c r="F384" s="7"/>
       <c r="G384" s="7"/>
       <c r="H384" s="7"/>
-      <c r="I384" s="7"/>
+      <c r="I384" s="4"/>
       <c r="J384" s="7"/>
     </row>
     <row r="385">
@@ -10124,16 +10181,16 @@
         <v>400</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D385" s="4">
-        <v>10000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E385" s="7"/>
       <c r="F385" s="7"/>
       <c r="G385" s="7"/>
       <c r="H385" s="7"/>
-      <c r="I385" s="7"/>
+      <c r="I385" s="4"/>
       <c r="J385" s="7"/>
     </row>
     <row r="386">
@@ -10145,10 +10202,10 @@
         <v>401</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D386" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E386" s="7"/>
       <c r="F386" s="7"/>
@@ -10166,10 +10223,10 @@
         <v>402</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D387" s="4">
-        <v>1500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E387" s="7"/>
       <c r="F387" s="7"/>
@@ -10187,10 +10244,10 @@
         <v>403</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D388" s="4">
-        <v>12000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E388" s="7"/>
       <c r="F388" s="7"/>
@@ -10208,10 +10265,10 @@
         <v>404</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D389" s="4">
-        <v>3000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E389" s="7"/>
       <c r="F389" s="7"/>
@@ -10229,10 +10286,10 @@
         <v>405</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D390" s="4">
-        <v>1000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E390" s="7"/>
       <c r="F390" s="7"/>
@@ -10250,10 +10307,10 @@
         <v>406</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D391" s="4">
-        <v>25000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E391" s="7"/>
       <c r="F391" s="7"/>
@@ -10271,10 +10328,10 @@
         <v>407</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D392" s="4">
-        <v>9000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E392" s="7"/>
       <c r="F392" s="7"/>
@@ -10292,12 +10349,12 @@
         <v>408</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D393" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E393" s="4"/>
+        <v>25000.0</v>
+      </c>
+      <c r="E393" s="7"/>
       <c r="F393" s="7"/>
       <c r="G393" s="7"/>
       <c r="H393" s="7"/>
@@ -10313,7 +10370,7 @@
         <v>409</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D394" s="4">
         <v>9000.0</v>
@@ -10334,12 +10391,12 @@
         <v>410</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D395" s="4">
-        <v>4500.0</v>
-      </c>
-      <c r="E395" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E395" s="4"/>
       <c r="F395" s="7"/>
       <c r="G395" s="7"/>
       <c r="H395" s="7"/>
@@ -10355,10 +10412,10 @@
         <v>411</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D396" s="4">
-        <v>500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E396" s="7"/>
       <c r="F396" s="7"/>
@@ -10376,10 +10433,10 @@
         <v>412</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D397" s="4">
-        <v>3000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E397" s="7"/>
       <c r="F397" s="7"/>
@@ -10397,10 +10454,10 @@
         <v>413</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D398" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E398" s="7"/>
       <c r="F398" s="7"/>
@@ -10414,42 +10471,42 @@
         <f t="shared" si="1"/>
         <v>398</v>
       </c>
-      <c r="B399" s="9" t="s">
+      <c r="B399" s="5" t="s">
         <v>414</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="D399" s="10">
-        <v>4500.0</v>
-      </c>
-      <c r="E399" s="11"/>
-      <c r="F399" s="11"/>
-      <c r="G399" s="11"/>
-      <c r="H399" s="11"/>
-      <c r="I399" s="11"/>
-      <c r="J399" s="11"/>
+        <v>390</v>
+      </c>
+      <c r="D399" s="4">
+        <v>3000.0</v>
+      </c>
+      <c r="E399" s="7"/>
+      <c r="F399" s="7"/>
+      <c r="G399" s="7"/>
+      <c r="H399" s="7"/>
+      <c r="I399" s="7"/>
+      <c r="J399" s="7"/>
     </row>
     <row r="400">
       <c r="A400" s="4">
         <f t="shared" si="1"/>
         <v>399</v>
       </c>
-      <c r="B400" s="9" t="s">
+      <c r="B400" s="5" t="s">
         <v>415</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="D400" s="10">
-        <v>50000.0</v>
-      </c>
-      <c r="E400" s="11"/>
-      <c r="F400" s="11"/>
-      <c r="G400" s="11"/>
-      <c r="H400" s="11"/>
-      <c r="I400" s="11"/>
-      <c r="J400" s="11"/>
+        <v>390</v>
+      </c>
+      <c r="D400" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E400" s="7"/>
+      <c r="F400" s="7"/>
+      <c r="G400" s="7"/>
+      <c r="H400" s="7"/>
+      <c r="I400" s="7"/>
+      <c r="J400" s="7"/>
     </row>
     <row r="401">
       <c r="A401" s="4">
@@ -10460,10 +10517,10 @@
         <v>416</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D401" s="10">
-        <v>12000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E401" s="11"/>
       <c r="F401" s="11"/>
@@ -10477,14 +10534,14 @@
         <f t="shared" si="1"/>
         <v>401</v>
       </c>
-      <c r="B402" s="5" t="s">
+      <c r="B402" s="9" t="s">
         <v>417</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D402" s="10">
-        <v>4500.0</v>
+        <v>50000.0</v>
       </c>
       <c r="E402" s="11"/>
       <c r="F402" s="11"/>
@@ -10502,10 +10559,10 @@
         <v>418</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>419</v>
+        <v>390</v>
       </c>
       <c r="D403" s="10">
-        <v>3000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E403" s="11"/>
       <c r="F403" s="11"/>
@@ -10519,14 +10576,14 @@
         <f t="shared" si="1"/>
         <v>403</v>
       </c>
-      <c r="B404" s="9" t="s">
+      <c r="B404" s="5" t="s">
         <v>419</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>419</v>
+        <v>390</v>
       </c>
       <c r="D404" s="10">
-        <v>5000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E404" s="11"/>
       <c r="F404" s="11"/>
@@ -10544,10 +10601,10 @@
         <v>420</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D405" s="10">
-        <v>6000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E405" s="11"/>
       <c r="F405" s="11"/>
@@ -10565,10 +10622,10 @@
         <v>421</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>367</v>
+        <v>421</v>
       </c>
       <c r="D406" s="10">
-        <v>12000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E406" s="11"/>
       <c r="F406" s="11"/>
@@ -10586,13 +10643,13 @@
         <v>422</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>367</v>
+        <v>421</v>
       </c>
       <c r="D407" s="10">
-        <v>200.0</v>
-      </c>
-      <c r="E407" s="10"/>
-      <c r="F407" s="10"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E407" s="11"/>
+      <c r="F407" s="11"/>
       <c r="G407" s="11"/>
       <c r="H407" s="11"/>
       <c r="I407" s="11"/>
@@ -10607,17 +10664,13 @@
         <v>423</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D408" s="10">
-        <v>5000.0</v>
-      </c>
-      <c r="E408" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="F408" s="10">
-        <v>4500.0</v>
-      </c>
+        <v>12000.0</v>
+      </c>
+      <c r="E408" s="11"/>
+      <c r="F408" s="11"/>
       <c r="G408" s="11"/>
       <c r="H408" s="11"/>
       <c r="I408" s="11"/>
@@ -10632,13 +10685,13 @@
         <v>424</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D409" s="10">
-        <v>18000.0</v>
-      </c>
-      <c r="E409" s="11"/>
-      <c r="F409" s="11"/>
+        <v>200.0</v>
+      </c>
+      <c r="E409" s="10"/>
+      <c r="F409" s="10"/>
       <c r="G409" s="11"/>
       <c r="H409" s="11"/>
       <c r="I409" s="11"/>
@@ -10653,13 +10706,17 @@
         <v>425</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D410" s="10">
-        <v>17000.0</v>
-      </c>
-      <c r="E410" s="11"/>
-      <c r="F410" s="11"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E410" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="F410" s="10">
+        <v>4500.0</v>
+      </c>
       <c r="G410" s="11"/>
       <c r="H410" s="11"/>
       <c r="I410" s="11"/>
@@ -10674,10 +10731,10 @@
         <v>426</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D411" s="10">
-        <v>17500.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E411" s="11"/>
       <c r="F411" s="11"/>
@@ -10695,10 +10752,10 @@
         <v>427</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D412" s="10">
-        <v>9000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E412" s="11"/>
       <c r="F412" s="11"/>
@@ -10716,10 +10773,10 @@
         <v>428</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D413" s="10">
-        <v>9000.0</v>
+        <v>17500.0</v>
       </c>
       <c r="E413" s="11"/>
       <c r="F413" s="11"/>
@@ -10737,10 +10794,10 @@
         <v>429</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D414" s="10">
-        <v>19500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E414" s="11"/>
       <c r="F414" s="11"/>
@@ -10758,10 +10815,10 @@
         <v>430</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D415" s="10">
-        <v>8500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E415" s="11"/>
       <c r="F415" s="11"/>
@@ -10779,7 +10836,7 @@
         <v>431</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D416" s="10">
         <v>9000.0</v>
@@ -10792,10 +10849,19 @@
       <c r="J416" s="11"/>
     </row>
     <row r="417">
-      <c r="A417" s="12"/>
-      <c r="B417" s="12"/>
-      <c r="C417" s="12"/>
-      <c r="D417" s="11"/>
+      <c r="A417" s="4">
+        <f t="shared" si="1"/>
+        <v>416</v>
+      </c>
+      <c r="B417" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="C417" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D417" s="10">
+        <v>19500.0</v>
+      </c>
       <c r="E417" s="11"/>
       <c r="F417" s="11"/>
       <c r="G417" s="11"/>
@@ -10804,10 +10870,19 @@
       <c r="J417" s="11"/>
     </row>
     <row r="418">
-      <c r="A418" s="12"/>
-      <c r="B418" s="12"/>
-      <c r="C418" s="12"/>
-      <c r="D418" s="11"/>
+      <c r="A418" s="4">
+        <f t="shared" si="1"/>
+        <v>417</v>
+      </c>
+      <c r="B418" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="C418" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D418" s="10">
+        <v>8500.0</v>
+      </c>
       <c r="E418" s="11"/>
       <c r="F418" s="11"/>
       <c r="G418" s="11"/>
@@ -10816,10 +10891,19 @@
       <c r="J418" s="11"/>
     </row>
     <row r="419">
-      <c r="A419" s="12"/>
-      <c r="B419" s="12"/>
-      <c r="C419" s="12"/>
-      <c r="D419" s="11"/>
+      <c r="A419" s="4">
+        <f t="shared" si="1"/>
+        <v>418</v>
+      </c>
+      <c r="B419" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="C419" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D419" s="10">
+        <v>4500.0</v>
+      </c>
       <c r="E419" s="11"/>
       <c r="F419" s="11"/>
       <c r="G419" s="11"/>
@@ -10828,10 +10912,19 @@
       <c r="J419" s="11"/>
     </row>
     <row r="420">
-      <c r="A420" s="12"/>
-      <c r="B420" s="12"/>
-      <c r="C420" s="12"/>
-      <c r="D420" s="11"/>
+      <c r="A420" s="4">
+        <f t="shared" si="1"/>
+        <v>419</v>
+      </c>
+      <c r="B420" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C420" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D420" s="10">
+        <v>9000.0</v>
+      </c>
       <c r="E420" s="11"/>
       <c r="F420" s="11"/>
       <c r="G420" s="11"/>
@@ -10840,10 +10933,19 @@
       <c r="J420" s="11"/>
     </row>
     <row r="421">
-      <c r="A421" s="12"/>
-      <c r="B421" s="12"/>
-      <c r="C421" s="12"/>
-      <c r="D421" s="11"/>
+      <c r="A421" s="4">
+        <f t="shared" si="1"/>
+        <v>420</v>
+      </c>
+      <c r="B421" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="C421" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D421" s="10">
+        <v>14000.0</v>
+      </c>
       <c r="E421" s="11"/>
       <c r="F421" s="11"/>
       <c r="G421" s="11"/>
@@ -10852,10 +10954,19 @@
       <c r="J421" s="11"/>
     </row>
     <row r="422">
-      <c r="A422" s="12"/>
-      <c r="B422" s="12"/>
-      <c r="C422" s="12"/>
-      <c r="D422" s="11"/>
+      <c r="A422" s="4">
+        <f t="shared" si="1"/>
+        <v>421</v>
+      </c>
+      <c r="B422" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="C422" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D422" s="10">
+        <v>3000.0</v>
+      </c>
       <c r="E422" s="11"/>
       <c r="F422" s="11"/>
       <c r="G422" s="11"/>
@@ -10864,10 +10975,19 @@
       <c r="J422" s="11"/>
     </row>
     <row r="423">
-      <c r="A423" s="12"/>
-      <c r="B423" s="12"/>
-      <c r="C423" s="12"/>
-      <c r="D423" s="11"/>
+      <c r="A423" s="4">
+        <f t="shared" si="1"/>
+        <v>422</v>
+      </c>
+      <c r="B423" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="C423" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D423" s="10">
+        <v>12000.0</v>
+      </c>
       <c r="E423" s="11"/>
       <c r="F423" s="11"/>
       <c r="G423" s="11"/>
@@ -10876,10 +10996,19 @@
       <c r="J423" s="11"/>
     </row>
     <row r="424">
-      <c r="A424" s="12"/>
-      <c r="B424" s="12"/>
-      <c r="C424" s="12"/>
-      <c r="D424" s="11"/>
+      <c r="A424" s="4">
+        <f t="shared" si="1"/>
+        <v>423</v>
+      </c>
+      <c r="B424" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C424" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D424" s="10">
+        <v>20000.0</v>
+      </c>
       <c r="E424" s="11"/>
       <c r="F424" s="11"/>
       <c r="G424" s="11"/>
@@ -11863,49 +11992,49 @@
       <c r="A506" s="12"/>
       <c r="B506" s="12"/>
       <c r="C506" s="12"/>
-      <c r="D506" s="12"/>
-      <c r="E506" s="12"/>
-      <c r="F506" s="12"/>
-      <c r="G506" s="12"/>
-      <c r="H506" s="12"/>
-      <c r="I506" s="12"/>
-      <c r="J506" s="12"/>
+      <c r="D506" s="11"/>
+      <c r="E506" s="11"/>
+      <c r="F506" s="11"/>
+      <c r="G506" s="11"/>
+      <c r="H506" s="11"/>
+      <c r="I506" s="11"/>
+      <c r="J506" s="11"/>
     </row>
     <row r="507">
       <c r="A507" s="12"/>
       <c r="B507" s="12"/>
       <c r="C507" s="12"/>
-      <c r="D507" s="12"/>
-      <c r="E507" s="12"/>
-      <c r="F507" s="12"/>
-      <c r="G507" s="12"/>
-      <c r="H507" s="12"/>
-      <c r="I507" s="12"/>
-      <c r="J507" s="12"/>
+      <c r="D507" s="11"/>
+      <c r="E507" s="11"/>
+      <c r="F507" s="11"/>
+      <c r="G507" s="11"/>
+      <c r="H507" s="11"/>
+      <c r="I507" s="11"/>
+      <c r="J507" s="11"/>
     </row>
     <row r="508">
       <c r="A508" s="12"/>
       <c r="B508" s="12"/>
       <c r="C508" s="12"/>
-      <c r="D508" s="12"/>
-      <c r="E508" s="12"/>
-      <c r="F508" s="12"/>
-      <c r="G508" s="12"/>
-      <c r="H508" s="12"/>
-      <c r="I508" s="12"/>
-      <c r="J508" s="12"/>
+      <c r="D508" s="11"/>
+      <c r="E508" s="11"/>
+      <c r="F508" s="11"/>
+      <c r="G508" s="11"/>
+      <c r="H508" s="11"/>
+      <c r="I508" s="11"/>
+      <c r="J508" s="11"/>
     </row>
     <row r="509">
       <c r="A509" s="12"/>
       <c r="B509" s="12"/>
       <c r="C509" s="12"/>
-      <c r="D509" s="12"/>
-      <c r="E509" s="12"/>
-      <c r="F509" s="12"/>
-      <c r="G509" s="12"/>
-      <c r="H509" s="12"/>
-      <c r="I509" s="12"/>
-      <c r="J509" s="12"/>
+      <c r="D509" s="11"/>
+      <c r="E509" s="11"/>
+      <c r="F509" s="11"/>
+      <c r="G509" s="11"/>
+      <c r="H509" s="11"/>
+      <c r="I509" s="11"/>
+      <c r="J509" s="11"/>
     </row>
     <row r="510">
       <c r="A510" s="12"/>
@@ -20283,15 +20412,63 @@
       <c r="I1207" s="12"/>
       <c r="J1207" s="12"/>
     </row>
+    <row r="1208">
+      <c r="A1208" s="12"/>
+      <c r="B1208" s="12"/>
+      <c r="C1208" s="12"/>
+      <c r="D1208" s="12"/>
+      <c r="E1208" s="12"/>
+      <c r="F1208" s="12"/>
+      <c r="G1208" s="12"/>
+      <c r="H1208" s="12"/>
+      <c r="I1208" s="12"/>
+      <c r="J1208" s="12"/>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="12"/>
+      <c r="B1209" s="12"/>
+      <c r="C1209" s="12"/>
+      <c r="D1209" s="12"/>
+      <c r="E1209" s="12"/>
+      <c r="F1209" s="12"/>
+      <c r="G1209" s="12"/>
+      <c r="H1209" s="12"/>
+      <c r="I1209" s="12"/>
+      <c r="J1209" s="12"/>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="12"/>
+      <c r="B1210" s="12"/>
+      <c r="C1210" s="12"/>
+      <c r="D1210" s="12"/>
+      <c r="E1210" s="12"/>
+      <c r="F1210" s="12"/>
+      <c r="G1210" s="12"/>
+      <c r="H1210" s="12"/>
+      <c r="I1210" s="12"/>
+      <c r="J1210" s="12"/>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="12"/>
+      <c r="B1211" s="12"/>
+      <c r="C1211" s="12"/>
+      <c r="D1211" s="12"/>
+      <c r="E1211" s="12"/>
+      <c r="F1211" s="12"/>
+      <c r="G1211" s="12"/>
+      <c r="H1211" s="12"/>
+      <c r="I1211" s="12"/>
+      <c r="J1211" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$416"/>
-  <conditionalFormatting sqref="A2:J1207">
+  <autoFilter ref="$B$1:$C$425"/>
+  <conditionalFormatting sqref="A2:J1211">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C416">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C424">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20348,11 +20525,11 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="str">
-        <f t="shared" ref="A2:A45" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
+        <f t="shared" ref="A2:A58" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4">
@@ -20371,7 +20548,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -20390,7 +20567,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -20409,7 +20586,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -20428,7 +20605,7 @@
         <v>GROSIR5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="4">
@@ -20447,7 +20624,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -20466,7 +20643,7 @@
         <v>GROSIR7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="4">
@@ -20485,7 +20662,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -20504,7 +20681,7 @@
         <v>GROSIR9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="4">
@@ -20523,7 +20700,7 @@
         <v>GROSIR10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="4">
@@ -20542,7 +20719,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -20561,7 +20738,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -20580,7 +20757,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -20599,7 +20776,7 @@
         <v>GROSIR14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="4">
@@ -20618,7 +20795,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -20637,7 +20814,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -20656,7 +20833,7 @@
         <v>GROSIR17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="4">
@@ -20675,18 +20852,18 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>442</v>
+        <v>243</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
-        <v>33000.0</v>
-      </c>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
+        <v>26500.0</v>
+      </c>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="str">
@@ -20694,11 +20871,11 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
-        <v>325000.0</v>
+        <v>33000.0</v>
       </c>
       <c r="E20" s="14"/>
       <c r="F20" s="14"/>
@@ -20713,11 +20890,11 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
-        <v>15000.0</v>
+        <v>325000.0</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="14"/>
@@ -20732,18 +20909,18 @@
         <v>GROSIR21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>247</v>
+        <v>452</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4">
-        <v>28000.0</v>
-      </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
+        <v>15000.0</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="str">
@@ -20751,18 +20928,18 @@
         <v>GROSIR22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="4">
-        <v>12000.0</v>
-      </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
+        <v>28000.0</v>
+      </c>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="str">
@@ -20770,11 +20947,11 @@
         <v>GROSIR23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="4">
-        <v>15500.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
@@ -20808,11 +20985,11 @@
         <v>GROSIR25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="4">
-        <v>9000.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
@@ -20827,11 +21004,11 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>445</v>
+        <v>207</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
-        <v>89000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="14"/>
@@ -20846,11 +21023,11 @@
         <v>GROSIR27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>203</v>
+        <v>453</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="4">
-        <v>9000.0</v>
+        <v>89000.0</v>
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
@@ -20865,11 +21042,11 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>446</v>
+        <v>205</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
-        <v>10000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E29" s="14"/>
       <c r="F29" s="14"/>
@@ -20884,11 +21061,11 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
-        <v>215000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
@@ -20903,18 +21080,18 @@
         <v>GROSIR30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>194</v>
+        <v>455</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="4">
-        <v>41000.0</v>
-      </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
+        <v>215000.0</v>
+      </c>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="str">
@@ -20922,11 +21099,11 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>448</v>
+        <v>196</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
-        <v>44000.0</v>
+        <v>41000.0</v>
       </c>
       <c r="E32" s="13"/>
       <c r="F32" s="13"/>
@@ -20941,18 +21118,18 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
+        <v>43000.0</v>
+      </c>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="str">
@@ -20960,18 +21137,18 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="str">
@@ -20979,11 +21156,11 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
-        <v>25000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E35" s="13"/>
       <c r="F35" s="13"/>
@@ -20998,11 +21175,11 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
-        <v>9000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
@@ -21017,11 +21194,11 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
-        <v>2500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E37" s="13"/>
       <c r="F37" s="13"/>
@@ -21036,7 +21213,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -21055,11 +21232,11 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
-        <v>2900.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E39" s="13"/>
       <c r="F39" s="13"/>
@@ -21073,12 +21250,12 @@
         <f t="shared" si="1"/>
         <v>GROSIR39</v>
       </c>
-      <c r="B40" s="9" t="s">
-        <v>416</v>
+      <c r="B40" s="5" t="s">
+        <v>463</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
-        <v>11000.0</v>
+        <v>2900.0</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
@@ -21092,12 +21269,12 @@
         <f t="shared" si="1"/>
         <v>GROSIR40</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>456</v>
+      <c r="B41" s="9" t="s">
+        <v>418</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
-        <v>1700.0</v>
+        <v>11000.0</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
@@ -21112,11 +21289,11 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>417</v>
+        <v>464</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
-        <v>4000.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
@@ -21131,11 +21308,11 @@
         <v>GROSIR42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>457</v>
+        <v>419</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="4">
-        <v>4500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
@@ -21150,11 +21327,11 @@
         <v>GROSIR43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>36</v>
+        <v>465</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="4">
-        <v>3500.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
@@ -21169,11 +21346,11 @@
         <v>GROSIR44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>458</v>
+        <v>36</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="4">
-        <v>2000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E45" s="13"/>
       <c r="F45" s="13"/>
@@ -21183,10 +21360,17 @@
       <c r="J45" s="13"/>
     </row>
     <row r="46">
-      <c r="A46" s="4"/>
-      <c r="B46" s="5"/>
+      <c r="A46" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR45</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>466</v>
+      </c>
       <c r="C46" s="5"/>
-      <c r="D46" s="4"/>
+      <c r="D46" s="4">
+        <v>2000.0</v>
+      </c>
       <c r="E46" s="13"/>
       <c r="F46" s="13"/>
       <c r="G46" s="13"/>
@@ -21195,82 +21379,131 @@
       <c r="J46" s="13"/>
     </row>
     <row r="47">
-      <c r="A47" s="4"/>
-      <c r="B47" s="5"/>
+      <c r="A47" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR46</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="C47" s="5"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14"/>
+      <c r="D47" s="4">
+        <v>3500.0</v>
+      </c>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
     </row>
     <row r="48">
-      <c r="A48" s="4"/>
-      <c r="B48" s="5"/>
+      <c r="A48" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR47</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>467</v>
+      </c>
       <c r="C48" s="5"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
+      <c r="D48" s="4">
+        <v>169000.0</v>
+      </c>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
     </row>
     <row r="49">
-      <c r="A49" s="4"/>
-      <c r="B49" s="5"/>
+      <c r="A49" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR48</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>468</v>
+      </c>
       <c r="C49" s="5"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14"/>
+      <c r="D49" s="4">
+        <v>171000.0</v>
+      </c>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
     </row>
     <row r="50">
-      <c r="A50" s="4"/>
-      <c r="B50" s="5"/>
+      <c r="A50" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR49</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>469</v>
+      </c>
       <c r="C50" s="5"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
+      <c r="D50" s="4">
+        <v>169000.0</v>
+      </c>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
     </row>
     <row r="51">
-      <c r="A51" s="4"/>
-      <c r="B51" s="5"/>
+      <c r="A51" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR50</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>470</v>
+      </c>
       <c r="C51" s="5"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14"/>
+      <c r="D51" s="4">
+        <v>196000.0</v>
+      </c>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
     </row>
     <row r="52">
-      <c r="A52" s="4"/>
-      <c r="B52" s="5"/>
+      <c r="A52" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR51</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>471</v>
+      </c>
       <c r="C52" s="5"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
+      <c r="D52" s="4">
+        <v>175000.0</v>
+      </c>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
     </row>
     <row r="53">
-      <c r="A53" s="4"/>
-      <c r="B53" s="5"/>
+      <c r="A53" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR52</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>472</v>
+      </c>
       <c r="C53" s="5"/>
-      <c r="D53" s="4"/>
+      <c r="D53" s="4">
+        <v>163000.0</v>
+      </c>
       <c r="E53" s="13"/>
       <c r="F53" s="13"/>
       <c r="G53" s="13"/>
@@ -21279,10 +21512,17 @@
       <c r="J53" s="13"/>
     </row>
     <row r="54">
-      <c r="A54" s="4"/>
-      <c r="B54" s="5"/>
+      <c r="A54" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR53</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>473</v>
+      </c>
       <c r="C54" s="5"/>
-      <c r="D54" s="4"/>
+      <c r="D54" s="4">
+        <v>57000.0</v>
+      </c>
       <c r="E54" s="13"/>
       <c r="F54" s="13"/>
       <c r="G54" s="13"/>
@@ -21291,100 +21531,128 @@
       <c r="J54" s="13"/>
     </row>
     <row r="55">
-      <c r="A55" s="4"/>
-      <c r="B55" s="5"/>
+      <c r="A55" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR54</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>474</v>
+      </c>
       <c r="C55" s="5"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="14"/>
+      <c r="D55" s="4">
+        <v>56000.0</v>
+      </c>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
     </row>
     <row r="56">
-      <c r="A56" s="4"/>
-      <c r="B56" s="5"/>
+      <c r="A56" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR55</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="C56" s="5"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
+      <c r="D56" s="4">
+        <v>150000.0</v>
+      </c>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
     </row>
     <row r="57">
-      <c r="A57" s="4"/>
-      <c r="B57" s="5"/>
+      <c r="A57" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR56</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>476</v>
+      </c>
       <c r="C57" s="5"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="14"/>
+      <c r="D57" s="4">
+        <v>155000.0</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
     </row>
     <row r="58">
-      <c r="A58" s="4"/>
-      <c r="B58" s="5"/>
+      <c r="A58" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR57</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>477</v>
+      </c>
       <c r="C58" s="5"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
+      <c r="D58" s="4">
+        <v>198000.0</v>
+      </c>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
     </row>
     <row r="59">
       <c r="A59" s="4"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="4"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="14"/>
-      <c r="J59" s="14"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
     </row>
     <row r="60">
       <c r="A60" s="4"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="4"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
     </row>
     <row r="61">
       <c r="A61" s="4"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="4"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
     </row>
     <row r="62">
       <c r="A62" s="4"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="4"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="13"/>
-      <c r="J62" s="13"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
     </row>
     <row r="63">
       <c r="A63" s="4"/>
@@ -21415,24 +21683,24 @@
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
       <c r="D65" s="4"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="14"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
     </row>
     <row r="66">
       <c r="A66" s="4"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
       <c r="D66" s="4"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="13"/>
-      <c r="J66" s="13"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
     </row>
     <row r="67">
       <c r="A67" s="4"/>
@@ -21475,48 +21743,48 @@
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
       <c r="D70" s="4"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
     </row>
     <row r="71">
       <c r="A71" s="4"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
       <c r="D71" s="4"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="13"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
     </row>
     <row r="72">
       <c r="A72" s="4"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
       <c r="D72" s="4"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="14"/>
-      <c r="J72" s="14"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="13"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="13"/>
+      <c r="J72" s="13"/>
     </row>
     <row r="73">
       <c r="A73" s="4"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
       <c r="D73" s="4"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
     </row>
     <row r="74">
       <c r="A74" s="4"/>
@@ -21559,24 +21827,24 @@
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="4"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="14"/>
-      <c r="J77" s="14"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="13"/>
     </row>
     <row r="78">
       <c r="A78" s="4"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="4"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
-      <c r="J78" s="13"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="14"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
     </row>
     <row r="79">
       <c r="A79" s="4"/>
@@ -21607,12 +21875,12 @@
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
       <c r="D81" s="4"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="14"/>
-      <c r="J81" s="14"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
+      <c r="H81" s="13"/>
+      <c r="I81" s="13"/>
+      <c r="J81" s="13"/>
     </row>
     <row r="82">
       <c r="A82" s="4"/>
@@ -21655,12 +21923,12 @@
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
       <c r="D85" s="4"/>
-      <c r="E85" s="13"/>
-      <c r="F85" s="13"/>
-      <c r="G85" s="13"/>
-      <c r="H85" s="13"/>
-      <c r="I85" s="13"/>
-      <c r="J85" s="13"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
     </row>
     <row r="86">
       <c r="A86" s="4"/>
@@ -21739,12 +22007,12 @@
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
       <c r="D92" s="4"/>
-      <c r="E92" s="14"/>
-      <c r="F92" s="14"/>
-      <c r="G92" s="14"/>
-      <c r="H92" s="14"/>
-      <c r="I92" s="14"/>
-      <c r="J92" s="14"/>
+      <c r="E92" s="13"/>
+      <c r="F92" s="13"/>
+      <c r="G92" s="13"/>
+      <c r="H92" s="13"/>
+      <c r="I92" s="13"/>
+      <c r="J92" s="13"/>
     </row>
     <row r="93">
       <c r="A93" s="4"/>
@@ -21787,12 +22055,12 @@
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
       <c r="D96" s="4"/>
-      <c r="E96" s="13"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
-      <c r="H96" s="13"/>
-      <c r="I96" s="13"/>
-      <c r="J96" s="13"/>
+      <c r="E96" s="14"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
+      <c r="J96" s="14"/>
     </row>
     <row r="97">
       <c r="A97" s="4"/>
@@ -21883,8 +22151,8 @@
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
       <c r="D104" s="4"/>
-      <c r="E104" s="4"/>
-      <c r="F104" s="4"/>
+      <c r="E104" s="13"/>
+      <c r="F104" s="13"/>
       <c r="G104" s="13"/>
       <c r="H104" s="13"/>
       <c r="I104" s="13"/>
@@ -21895,8 +22163,8 @@
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
       <c r="D105" s="4"/>
-      <c r="E105" s="13"/>
-      <c r="F105" s="13"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
       <c r="G105" s="13"/>
       <c r="H105" s="13"/>
       <c r="I105" s="13"/>
@@ -21919,24 +22187,24 @@
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
       <c r="D107" s="4"/>
-      <c r="E107" s="14"/>
-      <c r="F107" s="14"/>
-      <c r="G107" s="14"/>
-      <c r="H107" s="14"/>
-      <c r="I107" s="14"/>
-      <c r="J107" s="14"/>
+      <c r="E107" s="13"/>
+      <c r="F107" s="13"/>
+      <c r="G107" s="13"/>
+      <c r="H107" s="13"/>
+      <c r="I107" s="13"/>
+      <c r="J107" s="13"/>
     </row>
     <row r="108">
       <c r="A108" s="4"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
       <c r="D108" s="4"/>
-      <c r="E108" s="13"/>
-      <c r="F108" s="13"/>
-      <c r="G108" s="13"/>
-      <c r="H108" s="13"/>
-      <c r="I108" s="13"/>
-      <c r="J108" s="13"/>
+      <c r="E108" s="14"/>
+      <c r="F108" s="14"/>
+      <c r="G108" s="14"/>
+      <c r="H108" s="14"/>
+      <c r="I108" s="14"/>
+      <c r="J108" s="14"/>
     </row>
     <row r="109">
       <c r="A109" s="4"/>
@@ -22003,24 +22271,24 @@
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
       <c r="D114" s="4"/>
-      <c r="E114" s="14"/>
-      <c r="F114" s="14"/>
-      <c r="G114" s="14"/>
-      <c r="H114" s="14"/>
-      <c r="I114" s="14"/>
-      <c r="J114" s="14"/>
+      <c r="E114" s="13"/>
+      <c r="F114" s="13"/>
+      <c r="G114" s="13"/>
+      <c r="H114" s="13"/>
+      <c r="I114" s="13"/>
+      <c r="J114" s="13"/>
     </row>
     <row r="115">
       <c r="A115" s="4"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
       <c r="D115" s="4"/>
-      <c r="E115" s="13"/>
-      <c r="F115" s="13"/>
-      <c r="G115" s="13"/>
-      <c r="H115" s="13"/>
-      <c r="I115" s="13"/>
-      <c r="J115" s="13"/>
+      <c r="E115" s="14"/>
+      <c r="F115" s="14"/>
+      <c r="G115" s="14"/>
+      <c r="H115" s="14"/>
+      <c r="I115" s="14"/>
+      <c r="J115" s="14"/>
     </row>
     <row r="116">
       <c r="A116" s="4"/>
@@ -22111,12 +22379,12 @@
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
       <c r="D123" s="4"/>
-      <c r="E123" s="14"/>
-      <c r="F123" s="14"/>
-      <c r="G123" s="14"/>
-      <c r="H123" s="14"/>
-      <c r="I123" s="14"/>
-      <c r="J123" s="14"/>
+      <c r="E123" s="13"/>
+      <c r="F123" s="13"/>
+      <c r="G123" s="13"/>
+      <c r="H123" s="13"/>
+      <c r="I123" s="13"/>
+      <c r="J123" s="13"/>
     </row>
     <row r="124">
       <c r="A124" s="4"/>
@@ -22257,10 +22525,10 @@
       <c r="D135" s="4"/>
       <c r="E135" s="14"/>
       <c r="F135" s="14"/>
-      <c r="G135" s="4"/>
-      <c r="H135" s="4"/>
-      <c r="I135" s="4"/>
-      <c r="J135" s="4"/>
+      <c r="G135" s="14"/>
+      <c r="H135" s="14"/>
+      <c r="I135" s="14"/>
+      <c r="J135" s="14"/>
     </row>
     <row r="136">
       <c r="A136" s="4"/>
@@ -22269,10 +22537,10 @@
       <c r="D136" s="4"/>
       <c r="E136" s="14"/>
       <c r="F136" s="14"/>
-      <c r="G136" s="14"/>
-      <c r="H136" s="14"/>
-      <c r="I136" s="14"/>
-      <c r="J136" s="14"/>
+      <c r="G136" s="4"/>
+      <c r="H136" s="4"/>
+      <c r="I136" s="4"/>
+      <c r="J136" s="4"/>
     </row>
     <row r="137">
       <c r="A137" s="4"/>
@@ -22281,10 +22549,10 @@
       <c r="D137" s="4"/>
       <c r="E137" s="14"/>
       <c r="F137" s="14"/>
-      <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
-      <c r="I137" s="4"/>
-      <c r="J137" s="4"/>
+      <c r="G137" s="14"/>
+      <c r="H137" s="14"/>
+      <c r="I137" s="14"/>
+      <c r="J137" s="14"/>
     </row>
     <row r="138">
       <c r="A138" s="4"/>
@@ -22293,10 +22561,10 @@
       <c r="D138" s="4"/>
       <c r="E138" s="14"/>
       <c r="F138" s="14"/>
-      <c r="G138" s="14"/>
-      <c r="H138" s="14"/>
-      <c r="I138" s="14"/>
-      <c r="J138" s="14"/>
+      <c r="G138" s="4"/>
+      <c r="H138" s="4"/>
+      <c r="I138" s="4"/>
+      <c r="J138" s="4"/>
     </row>
     <row r="139">
       <c r="A139" s="4"/>
@@ -22305,10 +22573,10 @@
       <c r="D139" s="4"/>
       <c r="E139" s="14"/>
       <c r="F139" s="14"/>
-      <c r="G139" s="4"/>
-      <c r="H139" s="4"/>
-      <c r="I139" s="4"/>
-      <c r="J139" s="4"/>
+      <c r="G139" s="14"/>
+      <c r="H139" s="14"/>
+      <c r="I139" s="14"/>
+      <c r="J139" s="14"/>
     </row>
     <row r="140">
       <c r="A140" s="4"/>
@@ -22317,10 +22585,10 @@
       <c r="D140" s="4"/>
       <c r="E140" s="14"/>
       <c r="F140" s="14"/>
-      <c r="G140" s="14"/>
-      <c r="H140" s="14"/>
-      <c r="I140" s="14"/>
-      <c r="J140" s="14"/>
+      <c r="G140" s="4"/>
+      <c r="H140" s="4"/>
+      <c r="I140" s="4"/>
+      <c r="J140" s="4"/>
     </row>
     <row r="141">
       <c r="A141" s="4"/>
@@ -22329,10 +22597,10 @@
       <c r="D141" s="4"/>
       <c r="E141" s="14"/>
       <c r="F141" s="14"/>
-      <c r="G141" s="4"/>
-      <c r="H141" s="4"/>
-      <c r="I141" s="4"/>
-      <c r="J141" s="4"/>
+      <c r="G141" s="14"/>
+      <c r="H141" s="14"/>
+      <c r="I141" s="14"/>
+      <c r="J141" s="14"/>
     </row>
     <row r="142">
       <c r="A142" s="4"/>
@@ -22341,10 +22609,10 @@
       <c r="D142" s="4"/>
       <c r="E142" s="14"/>
       <c r="F142" s="14"/>
-      <c r="G142" s="14"/>
-      <c r="H142" s="14"/>
-      <c r="I142" s="14"/>
-      <c r="J142" s="14"/>
+      <c r="G142" s="4"/>
+      <c r="H142" s="4"/>
+      <c r="I142" s="4"/>
+      <c r="J142" s="4"/>
     </row>
     <row r="143">
       <c r="A143" s="4"/>
@@ -22353,10 +22621,10 @@
       <c r="D143" s="4"/>
       <c r="E143" s="14"/>
       <c r="F143" s="14"/>
-      <c r="G143" s="4"/>
-      <c r="H143" s="4"/>
-      <c r="I143" s="4"/>
-      <c r="J143" s="4"/>
+      <c r="G143" s="14"/>
+      <c r="H143" s="14"/>
+      <c r="I143" s="14"/>
+      <c r="J143" s="14"/>
     </row>
     <row r="144">
       <c r="A144" s="4"/>
@@ -22365,10 +22633,10 @@
       <c r="D144" s="4"/>
       <c r="E144" s="14"/>
       <c r="F144" s="14"/>
-      <c r="G144" s="14"/>
-      <c r="H144" s="14"/>
-      <c r="I144" s="14"/>
-      <c r="J144" s="14"/>
+      <c r="G144" s="4"/>
+      <c r="H144" s="4"/>
+      <c r="I144" s="4"/>
+      <c r="J144" s="4"/>
     </row>
     <row r="145">
       <c r="A145" s="4"/>
@@ -22377,10 +22645,10 @@
       <c r="D145" s="4"/>
       <c r="E145" s="14"/>
       <c r="F145" s="14"/>
-      <c r="G145" s="4"/>
-      <c r="H145" s="4"/>
-      <c r="I145" s="4"/>
-      <c r="J145" s="4"/>
+      <c r="G145" s="14"/>
+      <c r="H145" s="14"/>
+      <c r="I145" s="14"/>
+      <c r="J145" s="14"/>
     </row>
     <row r="146">
       <c r="A146" s="4"/>
@@ -22389,34 +22657,34 @@
       <c r="D146" s="4"/>
       <c r="E146" s="14"/>
       <c r="F146" s="14"/>
-      <c r="G146" s="14"/>
-      <c r="H146" s="14"/>
-      <c r="I146" s="14"/>
-      <c r="J146" s="14"/>
+      <c r="G146" s="4"/>
+      <c r="H146" s="4"/>
+      <c r="I146" s="4"/>
+      <c r="J146" s="4"/>
     </row>
     <row r="147">
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
       <c r="D147" s="4"/>
-      <c r="E147" s="4"/>
-      <c r="F147" s="4"/>
-      <c r="G147" s="4"/>
-      <c r="H147" s="4"/>
-      <c r="I147" s="4"/>
-      <c r="J147" s="4"/>
+      <c r="E147" s="14"/>
+      <c r="F147" s="14"/>
+      <c r="G147" s="14"/>
+      <c r="H147" s="14"/>
+      <c r="I147" s="14"/>
+      <c r="J147" s="14"/>
     </row>
     <row r="148">
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
       <c r="D148" s="4"/>
-      <c r="E148" s="14"/>
-      <c r="F148" s="14"/>
-      <c r="G148" s="14"/>
-      <c r="H148" s="14"/>
-      <c r="I148" s="14"/>
-      <c r="J148" s="14"/>
+      <c r="E148" s="4"/>
+      <c r="F148" s="4"/>
+      <c r="G148" s="4"/>
+      <c r="H148" s="4"/>
+      <c r="I148" s="4"/>
+      <c r="J148" s="4"/>
     </row>
     <row r="149">
       <c r="A149" s="4"/>
@@ -22425,10 +22693,10 @@
       <c r="D149" s="4"/>
       <c r="E149" s="14"/>
       <c r="F149" s="14"/>
-      <c r="G149" s="4"/>
-      <c r="H149" s="4"/>
-      <c r="I149" s="4"/>
-      <c r="J149" s="4"/>
+      <c r="G149" s="14"/>
+      <c r="H149" s="14"/>
+      <c r="I149" s="14"/>
+      <c r="J149" s="14"/>
     </row>
     <row r="150">
       <c r="A150" s="4"/>
@@ -22437,10 +22705,10 @@
       <c r="D150" s="4"/>
       <c r="E150" s="14"/>
       <c r="F150" s="14"/>
-      <c r="G150" s="14"/>
-      <c r="H150" s="14"/>
-      <c r="I150" s="14"/>
-      <c r="J150" s="14"/>
+      <c r="G150" s="4"/>
+      <c r="H150" s="4"/>
+      <c r="I150" s="4"/>
+      <c r="J150" s="4"/>
     </row>
     <row r="151">
       <c r="A151" s="4"/>
@@ -22449,10 +22717,10 @@
       <c r="D151" s="4"/>
       <c r="E151" s="14"/>
       <c r="F151" s="14"/>
-      <c r="G151" s="4"/>
-      <c r="H151" s="4"/>
-      <c r="I151" s="4"/>
-      <c r="J151" s="4"/>
+      <c r="G151" s="14"/>
+      <c r="H151" s="14"/>
+      <c r="I151" s="14"/>
+      <c r="J151" s="14"/>
     </row>
     <row r="152">
       <c r="A152" s="4"/>
@@ -22461,34 +22729,34 @@
       <c r="D152" s="4"/>
       <c r="E152" s="14"/>
       <c r="F152" s="14"/>
-      <c r="G152" s="14"/>
-      <c r="H152" s="14"/>
-      <c r="I152" s="14"/>
-      <c r="J152" s="14"/>
+      <c r="G152" s="4"/>
+      <c r="H152" s="4"/>
+      <c r="I152" s="4"/>
+      <c r="J152" s="4"/>
     </row>
     <row r="153">
       <c r="A153" s="4"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
       <c r="D153" s="4"/>
-      <c r="E153" s="4"/>
-      <c r="F153" s="4"/>
-      <c r="G153" s="4"/>
-      <c r="H153" s="4"/>
-      <c r="I153" s="4"/>
-      <c r="J153" s="4"/>
+      <c r="E153" s="14"/>
+      <c r="F153" s="14"/>
+      <c r="G153" s="14"/>
+      <c r="H153" s="14"/>
+      <c r="I153" s="14"/>
+      <c r="J153" s="14"/>
     </row>
     <row r="154">
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
       <c r="D154" s="4"/>
-      <c r="E154" s="14"/>
-      <c r="F154" s="14"/>
-      <c r="G154" s="14"/>
-      <c r="H154" s="14"/>
-      <c r="I154" s="14"/>
-      <c r="J154" s="14"/>
+      <c r="E154" s="4"/>
+      <c r="F154" s="4"/>
+      <c r="G154" s="4"/>
+      <c r="H154" s="4"/>
+      <c r="I154" s="4"/>
+      <c r="J154" s="4"/>
     </row>
     <row r="155">
       <c r="A155" s="4"/>
@@ -22497,10 +22765,10 @@
       <c r="D155" s="4"/>
       <c r="E155" s="14"/>
       <c r="F155" s="14"/>
-      <c r="G155" s="4"/>
-      <c r="H155" s="4"/>
-      <c r="I155" s="4"/>
-      <c r="J155" s="4"/>
+      <c r="G155" s="14"/>
+      <c r="H155" s="14"/>
+      <c r="I155" s="14"/>
+      <c r="J155" s="14"/>
     </row>
     <row r="156">
       <c r="A156" s="4"/>
@@ -22509,10 +22777,10 @@
       <c r="D156" s="4"/>
       <c r="E156" s="14"/>
       <c r="F156" s="14"/>
-      <c r="G156" s="14"/>
-      <c r="H156" s="14"/>
-      <c r="I156" s="14"/>
-      <c r="J156" s="14"/>
+      <c r="G156" s="4"/>
+      <c r="H156" s="4"/>
+      <c r="I156" s="4"/>
+      <c r="J156" s="4"/>
     </row>
     <row r="157">
       <c r="A157" s="4"/>
@@ -22521,10 +22789,10 @@
       <c r="D157" s="4"/>
       <c r="E157" s="14"/>
       <c r="F157" s="14"/>
-      <c r="G157" s="4"/>
-      <c r="H157" s="4"/>
-      <c r="I157" s="4"/>
-      <c r="J157" s="4"/>
+      <c r="G157" s="14"/>
+      <c r="H157" s="14"/>
+      <c r="I157" s="14"/>
+      <c r="J157" s="14"/>
     </row>
     <row r="158">
       <c r="A158" s="4"/>
@@ -22533,10 +22801,10 @@
       <c r="D158" s="4"/>
       <c r="E158" s="14"/>
       <c r="F158" s="14"/>
-      <c r="G158" s="14"/>
-      <c r="H158" s="14"/>
-      <c r="I158" s="14"/>
-      <c r="J158" s="14"/>
+      <c r="G158" s="4"/>
+      <c r="H158" s="4"/>
+      <c r="I158" s="4"/>
+      <c r="J158" s="4"/>
     </row>
     <row r="159">
       <c r="A159" s="4"/>
@@ -22545,10 +22813,10 @@
       <c r="D159" s="4"/>
       <c r="E159" s="14"/>
       <c r="F159" s="14"/>
-      <c r="G159" s="4"/>
-      <c r="H159" s="4"/>
-      <c r="I159" s="4"/>
-      <c r="J159" s="4"/>
+      <c r="G159" s="14"/>
+      <c r="H159" s="14"/>
+      <c r="I159" s="14"/>
+      <c r="J159" s="14"/>
     </row>
     <row r="160">
       <c r="A160" s="4"/>
@@ -22557,10 +22825,10 @@
       <c r="D160" s="4"/>
       <c r="E160" s="14"/>
       <c r="F160" s="14"/>
-      <c r="G160" s="14"/>
-      <c r="H160" s="14"/>
-      <c r="I160" s="14"/>
-      <c r="J160" s="14"/>
+      <c r="G160" s="4"/>
+      <c r="H160" s="4"/>
+      <c r="I160" s="4"/>
+      <c r="J160" s="4"/>
     </row>
     <row r="161">
       <c r="A161" s="4"/>
@@ -22569,10 +22837,10 @@
       <c r="D161" s="4"/>
       <c r="E161" s="14"/>
       <c r="F161" s="14"/>
-      <c r="G161" s="4"/>
-      <c r="H161" s="4"/>
-      <c r="I161" s="4"/>
-      <c r="J161" s="4"/>
+      <c r="G161" s="14"/>
+      <c r="H161" s="14"/>
+      <c r="I161" s="14"/>
+      <c r="J161" s="14"/>
     </row>
     <row r="162">
       <c r="A162" s="4"/>
@@ -22581,10 +22849,10 @@
       <c r="D162" s="4"/>
       <c r="E162" s="14"/>
       <c r="F162" s="14"/>
-      <c r="G162" s="14"/>
-      <c r="H162" s="14"/>
-      <c r="I162" s="14"/>
-      <c r="J162" s="14"/>
+      <c r="G162" s="4"/>
+      <c r="H162" s="4"/>
+      <c r="I162" s="4"/>
+      <c r="J162" s="4"/>
     </row>
     <row r="163">
       <c r="A163" s="4"/>
@@ -22593,10 +22861,10 @@
       <c r="D163" s="4"/>
       <c r="E163" s="14"/>
       <c r="F163" s="14"/>
-      <c r="G163" s="4"/>
-      <c r="H163" s="4"/>
-      <c r="I163" s="4"/>
-      <c r="J163" s="4"/>
+      <c r="G163" s="14"/>
+      <c r="H163" s="14"/>
+      <c r="I163" s="14"/>
+      <c r="J163" s="14"/>
     </row>
     <row r="164">
       <c r="A164" s="4"/>
@@ -22605,10 +22873,10 @@
       <c r="D164" s="4"/>
       <c r="E164" s="14"/>
       <c r="F164" s="14"/>
-      <c r="G164" s="14"/>
-      <c r="H164" s="14"/>
-      <c r="I164" s="14"/>
-      <c r="J164" s="14"/>
+      <c r="G164" s="4"/>
+      <c r="H164" s="4"/>
+      <c r="I164" s="4"/>
+      <c r="J164" s="4"/>
     </row>
     <row r="165">
       <c r="A165" s="4"/>
@@ -22617,10 +22885,10 @@
       <c r="D165" s="4"/>
       <c r="E165" s="14"/>
       <c r="F165" s="14"/>
-      <c r="G165" s="4"/>
-      <c r="H165" s="4"/>
-      <c r="I165" s="4"/>
-      <c r="J165" s="4"/>
+      <c r="G165" s="14"/>
+      <c r="H165" s="14"/>
+      <c r="I165" s="14"/>
+      <c r="J165" s="14"/>
     </row>
     <row r="166">
       <c r="A166" s="4"/>
@@ -22629,10 +22897,10 @@
       <c r="D166" s="4"/>
       <c r="E166" s="14"/>
       <c r="F166" s="14"/>
-      <c r="G166" s="14"/>
-      <c r="H166" s="14"/>
-      <c r="I166" s="14"/>
-      <c r="J166" s="14"/>
+      <c r="G166" s="4"/>
+      <c r="H166" s="4"/>
+      <c r="I166" s="4"/>
+      <c r="J166" s="4"/>
     </row>
     <row r="167">
       <c r="A167" s="4"/>
@@ -22641,10 +22909,10 @@
       <c r="D167" s="4"/>
       <c r="E167" s="14"/>
       <c r="F167" s="14"/>
-      <c r="G167" s="4"/>
-      <c r="H167" s="4"/>
-      <c r="I167" s="4"/>
-      <c r="J167" s="4"/>
+      <c r="G167" s="14"/>
+      <c r="H167" s="14"/>
+      <c r="I167" s="14"/>
+      <c r="J167" s="14"/>
     </row>
     <row r="168">
       <c r="A168" s="4"/>
@@ -22653,10 +22921,10 @@
       <c r="D168" s="4"/>
       <c r="E168" s="14"/>
       <c r="F168" s="14"/>
-      <c r="G168" s="14"/>
-      <c r="H168" s="14"/>
-      <c r="I168" s="14"/>
-      <c r="J168" s="14"/>
+      <c r="G168" s="4"/>
+      <c r="H168" s="4"/>
+      <c r="I168" s="4"/>
+      <c r="J168" s="4"/>
     </row>
     <row r="169">
       <c r="A169" s="4"/>
@@ -22665,10 +22933,10 @@
       <c r="D169" s="4"/>
       <c r="E169" s="14"/>
       <c r="F169" s="14"/>
-      <c r="G169" s="4"/>
-      <c r="H169" s="4"/>
-      <c r="I169" s="4"/>
-      <c r="J169" s="4"/>
+      <c r="G169" s="14"/>
+      <c r="H169" s="14"/>
+      <c r="I169" s="14"/>
+      <c r="J169" s="14"/>
     </row>
     <row r="170">
       <c r="A170" s="4"/>
@@ -22677,10 +22945,10 @@
       <c r="D170" s="4"/>
       <c r="E170" s="14"/>
       <c r="F170" s="14"/>
-      <c r="G170" s="14"/>
-      <c r="H170" s="14"/>
-      <c r="I170" s="14"/>
-      <c r="J170" s="14"/>
+      <c r="G170" s="4"/>
+      <c r="H170" s="4"/>
+      <c r="I170" s="4"/>
+      <c r="J170" s="4"/>
     </row>
     <row r="171">
       <c r="A171" s="4"/>
@@ -22689,10 +22957,10 @@
       <c r="D171" s="4"/>
       <c r="E171" s="14"/>
       <c r="F171" s="14"/>
-      <c r="G171" s="4"/>
-      <c r="H171" s="4"/>
-      <c r="I171" s="4"/>
-      <c r="J171" s="4"/>
+      <c r="G171" s="14"/>
+      <c r="H171" s="14"/>
+      <c r="I171" s="14"/>
+      <c r="J171" s="14"/>
     </row>
     <row r="172">
       <c r="A172" s="4"/>
@@ -22701,10 +22969,10 @@
       <c r="D172" s="4"/>
       <c r="E172" s="14"/>
       <c r="F172" s="14"/>
-      <c r="G172" s="14"/>
-      <c r="H172" s="14"/>
-      <c r="I172" s="14"/>
-      <c r="J172" s="14"/>
+      <c r="G172" s="4"/>
+      <c r="H172" s="4"/>
+      <c r="I172" s="4"/>
+      <c r="J172" s="4"/>
     </row>
     <row r="173">
       <c r="A173" s="4"/>
@@ -22713,10 +22981,10 @@
       <c r="D173" s="4"/>
       <c r="E173" s="14"/>
       <c r="F173" s="14"/>
-      <c r="G173" s="4"/>
-      <c r="H173" s="4"/>
-      <c r="I173" s="4"/>
-      <c r="J173" s="4"/>
+      <c r="G173" s="14"/>
+      <c r="H173" s="14"/>
+      <c r="I173" s="14"/>
+      <c r="J173" s="14"/>
     </row>
     <row r="174">
       <c r="A174" s="4"/>
@@ -22725,10 +22993,10 @@
       <c r="D174" s="4"/>
       <c r="E174" s="14"/>
       <c r="F174" s="14"/>
-      <c r="G174" s="15"/>
-      <c r="H174" s="15"/>
-      <c r="I174" s="14"/>
-      <c r="J174" s="14"/>
+      <c r="G174" s="4"/>
+      <c r="H174" s="4"/>
+      <c r="I174" s="4"/>
+      <c r="J174" s="4"/>
     </row>
     <row r="175">
       <c r="A175" s="4"/>
@@ -22737,8 +23005,8 @@
       <c r="D175" s="4"/>
       <c r="E175" s="14"/>
       <c r="F175" s="14"/>
-      <c r="G175" s="14"/>
-      <c r="H175" s="14"/>
+      <c r="G175" s="15"/>
+      <c r="H175" s="15"/>
       <c r="I175" s="14"/>
       <c r="J175" s="14"/>
     </row>
@@ -22975,24 +23243,24 @@
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
       <c r="D195" s="4"/>
-      <c r="E195" s="13"/>
-      <c r="F195" s="13"/>
-      <c r="G195" s="13"/>
-      <c r="H195" s="13"/>
-      <c r="I195" s="13"/>
-      <c r="J195" s="13"/>
+      <c r="E195" s="14"/>
+      <c r="F195" s="14"/>
+      <c r="G195" s="14"/>
+      <c r="H195" s="14"/>
+      <c r="I195" s="14"/>
+      <c r="J195" s="14"/>
     </row>
     <row r="196">
       <c r="A196" s="4"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
       <c r="D196" s="4"/>
-      <c r="E196" s="14"/>
-      <c r="F196" s="14"/>
-      <c r="G196" s="14"/>
-      <c r="H196" s="14"/>
-      <c r="I196" s="14"/>
-      <c r="J196" s="14"/>
+      <c r="E196" s="13"/>
+      <c r="F196" s="13"/>
+      <c r="G196" s="13"/>
+      <c r="H196" s="13"/>
+      <c r="I196" s="13"/>
+      <c r="J196" s="13"/>
     </row>
     <row r="197">
       <c r="A197" s="4"/>
@@ -23083,24 +23351,24 @@
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
       <c r="D204" s="4"/>
-      <c r="E204" s="13"/>
-      <c r="F204" s="13"/>
-      <c r="G204" s="13"/>
-      <c r="H204" s="13"/>
-      <c r="I204" s="13"/>
-      <c r="J204" s="13"/>
+      <c r="E204" s="14"/>
+      <c r="F204" s="14"/>
+      <c r="G204" s="14"/>
+      <c r="H204" s="14"/>
+      <c r="I204" s="14"/>
+      <c r="J204" s="14"/>
     </row>
     <row r="205">
       <c r="A205" s="4"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
       <c r="D205" s="4"/>
-      <c r="E205" s="14"/>
-      <c r="F205" s="14"/>
-      <c r="G205" s="14"/>
-      <c r="H205" s="14"/>
-      <c r="I205" s="14"/>
-      <c r="J205" s="14"/>
+      <c r="E205" s="13"/>
+      <c r="F205" s="13"/>
+      <c r="G205" s="13"/>
+      <c r="H205" s="13"/>
+      <c r="I205" s="13"/>
+      <c r="J205" s="13"/>
     </row>
     <row r="206">
       <c r="A206" s="4"/>
@@ -23611,8 +23879,8 @@
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
       <c r="D248" s="4"/>
-      <c r="E248" s="4"/>
-      <c r="F248" s="4"/>
+      <c r="E248" s="14"/>
+      <c r="F248" s="14"/>
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="14"/>
@@ -23623,8 +23891,8 @@
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
       <c r="D249" s="4"/>
-      <c r="E249" s="14"/>
-      <c r="F249" s="14"/>
+      <c r="E249" s="4"/>
+      <c r="F249" s="4"/>
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="14"/>
@@ -23699,7 +23967,7 @@
       <c r="F255" s="14"/>
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
-      <c r="I255" s="5"/>
+      <c r="I255" s="14"/>
       <c r="J255" s="14"/>
     </row>
     <row r="256">
@@ -23711,7 +23979,7 @@
       <c r="F256" s="14"/>
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
-      <c r="I256" s="14"/>
+      <c r="I256" s="5"/>
       <c r="J256" s="14"/>
     </row>
     <row r="257">
@@ -23763,10 +24031,10 @@
       <c r="J260" s="14"/>
     </row>
     <row r="261">
-      <c r="A261" s="14"/>
-      <c r="B261" s="14"/>
-      <c r="C261" s="14"/>
-      <c r="D261" s="14"/>
+      <c r="A261" s="4"/>
+      <c r="B261" s="5"/>
+      <c r="C261" s="5"/>
+      <c r="D261" s="4"/>
       <c r="E261" s="14"/>
       <c r="F261" s="14"/>
       <c r="G261" s="14"/>
@@ -23883,16 +24151,16 @@
       <c r="J270" s="14"/>
     </row>
     <row r="271">
-      <c r="A271" s="12"/>
-      <c r="B271" s="12"/>
-      <c r="C271" s="12"/>
-      <c r="D271" s="12"/>
-      <c r="E271" s="12"/>
-      <c r="F271" s="12"/>
-      <c r="G271" s="12"/>
-      <c r="H271" s="12"/>
-      <c r="I271" s="12"/>
-      <c r="J271" s="12"/>
+      <c r="A271" s="14"/>
+      <c r="B271" s="14"/>
+      <c r="C271" s="14"/>
+      <c r="D271" s="14"/>
+      <c r="E271" s="14"/>
+      <c r="F271" s="14"/>
+      <c r="G271" s="14"/>
+      <c r="H271" s="14"/>
+      <c r="I271" s="14"/>
+      <c r="J271" s="14"/>
     </row>
     <row r="272">
       <c r="A272" s="12"/>
@@ -33602,9 +33870,21 @@
       <c r="I1080" s="12"/>
       <c r="J1080" s="12"/>
     </row>
+    <row r="1081">
+      <c r="A1081" s="12"/>
+      <c r="B1081" s="12"/>
+      <c r="C1081" s="12"/>
+      <c r="D1081" s="12"/>
+      <c r="E1081" s="12"/>
+      <c r="F1081" s="12"/>
+      <c r="G1081" s="12"/>
+      <c r="H1081" s="12"/>
+      <c r="I1081" s="12"/>
+      <c r="J1081" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$260"/>
-  <conditionalFormatting sqref="A2:J1080">
+  <autoFilter ref="$B$1:$C$261"/>
+  <conditionalFormatting sqref="A2:J1081">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="479">
   <si>
     <t>Barcode</t>
   </si>
@@ -1335,6 +1335,9 @@
   </si>
   <si>
     <t>Cat Choize</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
   <si>
     <t>Djarum Coklat Bungkus SLOP</t>
@@ -1836,7 +1839,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A424" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A425" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -11017,10 +11020,19 @@
       <c r="J424" s="11"/>
     </row>
     <row r="425">
-      <c r="A425" s="12"/>
-      <c r="B425" s="12"/>
-      <c r="C425" s="12"/>
-      <c r="D425" s="11"/>
+      <c r="A425" s="4">
+        <f t="shared" si="1"/>
+        <v>424</v>
+      </c>
+      <c r="B425" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="C425" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D425" s="10">
+        <v>1.0</v>
+      </c>
       <c r="E425" s="11"/>
       <c r="F425" s="11"/>
       <c r="G425" s="11"/>
@@ -20468,7 +20480,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C424">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C425">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20548,7 +20560,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -20567,7 +20579,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -20586,7 +20598,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -20624,7 +20636,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -20662,7 +20674,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -20719,7 +20731,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -20738,7 +20750,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -20757,7 +20769,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -20795,7 +20807,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -20814,7 +20826,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -20871,7 +20883,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -20890,7 +20902,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -20909,7 +20921,7 @@
         <v>GROSIR21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4">
@@ -21023,7 +21035,7 @@
         <v>GROSIR27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="4">
@@ -21061,7 +21073,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -21080,7 +21092,7 @@
         <v>GROSIR30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="4">
@@ -21118,7 +21130,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -21137,7 +21149,7 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
@@ -21156,7 +21168,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -21175,7 +21187,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -21194,7 +21206,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -21213,7 +21225,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -21232,7 +21244,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -21251,7 +21263,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -21289,7 +21301,7 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
@@ -21327,7 +21339,7 @@
         <v>GROSIR43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="4">
@@ -21365,7 +21377,7 @@
         <v>GROSIR45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="4">
@@ -21403,7 +21415,7 @@
         <v>GROSIR47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="4">
@@ -21422,7 +21434,7 @@
         <v>GROSIR48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="4">
@@ -21441,7 +21453,7 @@
         <v>GROSIR49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="4">
@@ -21460,7 +21472,7 @@
         <v>GROSIR50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="4">
@@ -21479,7 +21491,7 @@
         <v>GROSIR51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="4">
@@ -21498,7 +21510,7 @@
         <v>GROSIR52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="4">
@@ -21517,7 +21529,7 @@
         <v>GROSIR53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="4">
@@ -21536,7 +21548,7 @@
         <v>GROSIR54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="4">
@@ -21555,7 +21567,7 @@
         <v>GROSIR55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="4">
@@ -21574,7 +21586,7 @@
         <v>GROSIR56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="4">
@@ -21593,7 +21605,7 @@
         <v>GROSIR57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,15 +7,15 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$425</definedName>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$261</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$426</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$262</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="481">
   <si>
     <t>Barcode</t>
   </si>
@@ -524,6 +524,12 @@
     <t>Gula Merah 250g</t>
   </si>
   <si>
+    <t>Racik Ikan</t>
+  </si>
+  <si>
+    <t>Racik Ikan Renceng</t>
+  </si>
+  <si>
     <t>Racik Lodeh</t>
   </si>
   <si>
@@ -1337,9 +1343,6 @@
     <t>Cat Choize</t>
   </si>
   <si>
-    <t>test</t>
-  </si>
-  <si>
     <t>Djarum Coklat Bungkus SLOP</t>
   </si>
   <si>
@@ -1385,7 +1388,10 @@
     <t>Janaka</t>
   </si>
   <si>
-    <t>Dji Sam Soe Super Premium</t>
+    <t>Dji Sam Soe Super Premium (Refill)</t>
+  </si>
+  <si>
+    <t>Dji Sam Soe Super Premium (Refill) SLOP</t>
   </si>
   <si>
     <t>Kuncimas 2L</t>
@@ -1839,7 +1845,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A425" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A426" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -5372,7 +5378,7 @@
         <v>130</v>
       </c>
       <c r="D168" s="4">
-        <v>5000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E168" s="6"/>
       <c r="F168" s="6"/>
@@ -5393,7 +5399,7 @@
         <v>130</v>
       </c>
       <c r="D169" s="4">
-        <v>10000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E169" s="6"/>
       <c r="F169" s="6"/>
@@ -5414,7 +5420,7 @@
         <v>130</v>
       </c>
       <c r="D170" s="4">
-        <v>18000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E170" s="6"/>
       <c r="F170" s="6"/>
@@ -5435,7 +5441,7 @@
         <v>130</v>
       </c>
       <c r="D171" s="4">
-        <v>4500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E171" s="6"/>
       <c r="F171" s="6"/>
@@ -5456,7 +5462,7 @@
         <v>130</v>
       </c>
       <c r="D172" s="4">
-        <v>9000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E172" s="6"/>
       <c r="F172" s="6"/>
@@ -5477,14 +5483,14 @@
         <v>130</v>
       </c>
       <c r="D173" s="4">
-        <v>18000.0</v>
-      </c>
-      <c r="E173" s="4"/>
-      <c r="F173" s="4"/>
-      <c r="G173" s="7"/>
-      <c r="H173" s="7"/>
-      <c r="I173" s="7"/>
-      <c r="J173" s="7"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E173" s="6"/>
+      <c r="F173" s="6"/>
+      <c r="G173" s="6"/>
+      <c r="H173" s="6"/>
+      <c r="I173" s="6"/>
+      <c r="J173" s="6"/>
     </row>
     <row r="174">
       <c r="A174" s="4">
@@ -5498,18 +5504,14 @@
         <v>130</v>
       </c>
       <c r="D174" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E174" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F174" s="4">
-        <v>10000.0</v>
-      </c>
-      <c r="G174" s="7"/>
-      <c r="H174" s="7"/>
-      <c r="I174" s="7"/>
-      <c r="J174" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E174" s="6"/>
+      <c r="F174" s="6"/>
+      <c r="G174" s="6"/>
+      <c r="H174" s="6"/>
+      <c r="I174" s="6"/>
+      <c r="J174" s="6"/>
     </row>
     <row r="175">
       <c r="A175" s="4">
@@ -5523,7 +5525,7 @@
         <v>130</v>
       </c>
       <c r="D175" s="4">
-        <v>3500.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E175" s="4"/>
       <c r="F175" s="4"/>
@@ -5544,13 +5546,13 @@
         <v>130</v>
       </c>
       <c r="D176" s="4">
-        <v>2500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E176" s="4">
         <v>4.0</v>
       </c>
       <c r="F176" s="4">
-        <v>8500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="G176" s="7"/>
       <c r="H176" s="7"/>
@@ -5569,10 +5571,10 @@
         <v>130</v>
       </c>
       <c r="D177" s="4">
-        <v>26000.0</v>
-      </c>
-      <c r="E177" s="7"/>
-      <c r="F177" s="7"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E177" s="4"/>
+      <c r="F177" s="4"/>
       <c r="G177" s="7"/>
       <c r="H177" s="7"/>
       <c r="I177" s="7"/>
@@ -5590,13 +5592,13 @@
         <v>130</v>
       </c>
       <c r="D178" s="4">
-        <v>4000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E178" s="4">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F178" s="4">
-        <v>17500.0</v>
+        <v>8500.0</v>
       </c>
       <c r="G178" s="7"/>
       <c r="H178" s="7"/>
@@ -5615,7 +5617,7 @@
         <v>130</v>
       </c>
       <c r="D179" s="4">
-        <v>175000.0</v>
+        <v>26000.0</v>
       </c>
       <c r="E179" s="7"/>
       <c r="F179" s="7"/>
@@ -5636,10 +5638,14 @@
         <v>130</v>
       </c>
       <c r="D180" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E180" s="7"/>
-      <c r="F180" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E180" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F180" s="4">
+        <v>17500.0</v>
+      </c>
       <c r="G180" s="7"/>
       <c r="H180" s="7"/>
       <c r="I180" s="7"/>
@@ -5657,14 +5663,10 @@
         <v>130</v>
       </c>
       <c r="D181" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="E181" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F181" s="4">
-        <v>22000.0</v>
-      </c>
+        <v>175000.0</v>
+      </c>
+      <c r="E181" s="7"/>
+      <c r="F181" s="7"/>
       <c r="G181" s="7"/>
       <c r="H181" s="7"/>
       <c r="I181" s="7"/>
@@ -5703,10 +5705,14 @@
         <v>130</v>
       </c>
       <c r="D183" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E183" s="7"/>
-      <c r="F183" s="7"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E183" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F183" s="4">
+        <v>22000.0</v>
+      </c>
       <c r="G183" s="7"/>
       <c r="H183" s="7"/>
       <c r="I183" s="7"/>
@@ -5724,7 +5730,7 @@
         <v>130</v>
       </c>
       <c r="D184" s="4">
-        <v>245000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
@@ -5745,7 +5751,7 @@
         <v>130</v>
       </c>
       <c r="D185" s="4">
-        <v>42000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E185" s="7"/>
       <c r="F185" s="7"/>
@@ -5766,7 +5772,7 @@
         <v>130</v>
       </c>
       <c r="D186" s="4">
-        <v>44000.0</v>
+        <v>245000.0</v>
       </c>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
@@ -5787,7 +5793,7 @@
         <v>130</v>
       </c>
       <c r="D187" s="4">
-        <v>255000.0</v>
+        <v>42000.0</v>
       </c>
       <c r="E187" s="7"/>
       <c r="F187" s="7"/>
@@ -5808,7 +5814,7 @@
         <v>130</v>
       </c>
       <c r="D188" s="4">
-        <v>21000.0</v>
+        <v>44000.0</v>
       </c>
       <c r="E188" s="7"/>
       <c r="F188" s="7"/>
@@ -5829,7 +5835,7 @@
         <v>130</v>
       </c>
       <c r="D189" s="4">
-        <v>42000.0</v>
+        <v>255000.0</v>
       </c>
       <c r="E189" s="7"/>
       <c r="F189" s="7"/>
@@ -5850,14 +5856,14 @@
         <v>130</v>
       </c>
       <c r="D190" s="4">
-        <v>14500.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E190" s="7"/>
       <c r="F190" s="7"/>
-      <c r="G190" s="4"/>
-      <c r="H190" s="4"/>
-      <c r="I190" s="4"/>
-      <c r="J190" s="4"/>
+      <c r="G190" s="7"/>
+      <c r="H190" s="7"/>
+      <c r="I190" s="7"/>
+      <c r="J190" s="7"/>
     </row>
     <row r="191">
       <c r="A191" s="4">
@@ -5868,25 +5874,17 @@
         <v>202</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>203</v>
+        <v>130</v>
       </c>
       <c r="D191" s="4">
-        <v>2000.0</v>
+        <v>42000.0</v>
       </c>
       <c r="E191" s="7"/>
       <c r="F191" s="7"/>
-      <c r="G191" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H191" s="4">
-        <v>5500.0</v>
-      </c>
-      <c r="I191" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J191" s="4">
-        <v>10000.0</v>
-      </c>
+      <c r="G191" s="7"/>
+      <c r="H191" s="7"/>
+      <c r="I191" s="7"/>
+      <c r="J191" s="7"/>
     </row>
     <row r="192">
       <c r="A192" s="4">
@@ -5894,20 +5892,20 @@
         <v>191</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>203</v>
+        <v>130</v>
       </c>
       <c r="D192" s="4">
-        <v>10000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E192" s="7"/>
       <c r="F192" s="7"/>
-      <c r="G192" s="7"/>
-      <c r="H192" s="7"/>
-      <c r="I192" s="7"/>
-      <c r="J192" s="7"/>
+      <c r="G192" s="4"/>
+      <c r="H192" s="4"/>
+      <c r="I192" s="4"/>
+      <c r="J192" s="4"/>
     </row>
     <row r="193">
       <c r="A193" s="4">
@@ -5915,10 +5913,10 @@
         <v>192</v>
       </c>
       <c r="B193" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C193" s="5" t="s">
         <v>205</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="D193" s="4">
         <v>2000.0</v>
@@ -5947,7 +5945,7 @@
         <v>206</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D194" s="4">
         <v>10000.0</v>
@@ -5968,7 +5966,7 @@
         <v>207</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D195" s="4">
         <v>2000.0</v>
@@ -5997,7 +5995,7 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D196" s="4">
         <v>10000.0</v>
@@ -6018,7 +6016,7 @@
         <v>209</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D197" s="4">
         <v>2000.0</v>
@@ -6029,13 +6027,13 @@
         <v>6.0</v>
       </c>
       <c r="H197" s="4">
-        <v>6000.0</v>
+        <v>5500.0</v>
       </c>
       <c r="I197" s="4">
         <v>12.0</v>
       </c>
       <c r="J197" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
     </row>
     <row r="198">
@@ -6047,10 +6045,10 @@
         <v>210</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D198" s="4">
-        <v>11000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E198" s="7"/>
       <c r="F198" s="7"/>
@@ -6068,7 +6066,7 @@
         <v>211</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D199" s="4">
         <v>2000.0</v>
@@ -6097,7 +6095,7 @@
         <v>212</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D200" s="4">
         <v>11000.0</v>
@@ -6118,7 +6116,7 @@
         <v>213</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D201" s="4">
         <v>2000.0</v>
@@ -6129,13 +6127,13 @@
         <v>6.0</v>
       </c>
       <c r="H201" s="4">
-        <v>8000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="I201" s="4">
         <v>12.0</v>
       </c>
       <c r="J201" s="4">
-        <v>15000.0</v>
+        <v>11000.0</v>
       </c>
     </row>
     <row r="202">
@@ -6147,10 +6145,10 @@
         <v>214</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D202" s="4">
-        <v>15000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="E202" s="7"/>
       <c r="F202" s="7"/>
@@ -6168,17 +6166,25 @@
         <v>215</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D203" s="4">
-        <v>15000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E203" s="7"/>
       <c r="F203" s="7"/>
-      <c r="G203" s="7"/>
-      <c r="H203" s="7"/>
-      <c r="I203" s="7"/>
-      <c r="J203" s="7"/>
+      <c r="G203" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H203" s="4">
+        <v>8000.0</v>
+      </c>
+      <c r="I203" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J203" s="4">
+        <v>15000.0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="4">
@@ -6189,29 +6195,17 @@
         <v>216</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D204" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E204" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F204" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="G204" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H204" s="4">
-        <v>8500.0</v>
-      </c>
-      <c r="I204" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J204" s="4">
-        <v>16000.0</v>
-      </c>
+        <v>15000.0</v>
+      </c>
+      <c r="E204" s="7"/>
+      <c r="F204" s="7"/>
+      <c r="G204" s="7"/>
+      <c r="H204" s="7"/>
+      <c r="I204" s="7"/>
+      <c r="J204" s="7"/>
     </row>
     <row r="205">
       <c r="A205" s="4">
@@ -6222,10 +6216,10 @@
         <v>217</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D205" s="4">
-        <v>16000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E205" s="7"/>
       <c r="F205" s="7"/>
@@ -6243,24 +6237,28 @@
         <v>218</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D206" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E206" s="7"/>
-      <c r="F206" s="7"/>
+      <c r="E206" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F206" s="4">
+        <v>5000.0</v>
+      </c>
       <c r="G206" s="4">
         <v>6.0</v>
       </c>
       <c r="H206" s="4">
-        <v>9000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="I206" s="4">
         <v>12.0</v>
       </c>
       <c r="J206" s="4">
-        <v>17000.0</v>
+        <v>16000.0</v>
       </c>
     </row>
     <row r="207">
@@ -6272,10 +6270,10 @@
         <v>219</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D207" s="4">
-        <v>17000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E207" s="7"/>
       <c r="F207" s="7"/>
@@ -6293,7 +6291,7 @@
         <v>220</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D208" s="4">
         <v>2000.0</v>
@@ -6322,7 +6320,7 @@
         <v>221</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D209" s="4">
         <v>17000.0</v>
@@ -6343,28 +6341,24 @@
         <v>222</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D210" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E210" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F210" s="4">
-        <v>5000.0</v>
-      </c>
+      <c r="E210" s="7"/>
+      <c r="F210" s="7"/>
       <c r="G210" s="4">
         <v>6.0</v>
       </c>
       <c r="H210" s="4">
-        <v>9500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="I210" s="4">
         <v>12.0</v>
       </c>
       <c r="J210" s="4">
-        <v>18000.0</v>
+        <v>17000.0</v>
       </c>
     </row>
     <row r="211">
@@ -6376,10 +6370,10 @@
         <v>223</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D211" s="4">
-        <v>18000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E211" s="7"/>
       <c r="F211" s="7"/>
@@ -6397,24 +6391,28 @@
         <v>224</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D212" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E212" s="7"/>
-      <c r="F212" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E212" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F212" s="4">
+        <v>5000.0</v>
+      </c>
       <c r="G212" s="4">
         <v>6.0</v>
       </c>
       <c r="H212" s="4">
-        <v>14500.0</v>
+        <v>9500.0</v>
       </c>
       <c r="I212" s="4">
         <v>12.0</v>
       </c>
       <c r="J212" s="4">
-        <v>28000.0</v>
+        <v>18000.0</v>
       </c>
     </row>
     <row r="213">
@@ -6426,10 +6424,10 @@
         <v>225</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D213" s="4">
-        <v>28000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E213" s="7"/>
       <c r="F213" s="7"/>
@@ -6447,7 +6445,7 @@
         <v>226</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D214" s="4">
         <v>2500.0</v>
@@ -6458,13 +6456,13 @@
         <v>6.0</v>
       </c>
       <c r="H214" s="4">
-        <v>10500.0</v>
+        <v>14500.0</v>
       </c>
       <c r="I214" s="4">
         <v>12.0</v>
       </c>
       <c r="J214" s="4">
-        <v>20000.0</v>
+        <v>28000.0</v>
       </c>
     </row>
     <row r="215">
@@ -6476,10 +6474,10 @@
         <v>227</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D215" s="4">
-        <v>20000.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E215" s="7"/>
       <c r="F215" s="7"/>
@@ -6497,7 +6495,7 @@
         <v>228</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D216" s="4">
         <v>2500.0</v>
@@ -6508,13 +6506,13 @@
         <v>6.0</v>
       </c>
       <c r="H216" s="4">
-        <v>13000.0</v>
+        <v>10500.0</v>
       </c>
       <c r="I216" s="4">
         <v>12.0</v>
       </c>
       <c r="J216" s="4">
-        <v>25000.0</v>
+        <v>20000.0</v>
       </c>
     </row>
     <row r="217">
@@ -6526,10 +6524,10 @@
         <v>229</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D217" s="4">
-        <v>25000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="E217" s="7"/>
       <c r="F217" s="7"/>
@@ -6547,7 +6545,7 @@
         <v>230</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D218" s="4">
         <v>2500.0</v>
@@ -6558,13 +6556,13 @@
         <v>6.0</v>
       </c>
       <c r="H218" s="4">
-        <v>11000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I218" s="4">
         <v>12.0</v>
       </c>
       <c r="J218" s="4">
-        <v>21000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="219">
@@ -6576,10 +6574,10 @@
         <v>231</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D219" s="4">
-        <v>21000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E219" s="7"/>
       <c r="F219" s="7"/>
@@ -6597,7 +6595,7 @@
         <v>232</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D220" s="4">
         <v>2500.0</v>
@@ -6608,13 +6606,13 @@
         <v>6.0</v>
       </c>
       <c r="H220" s="4">
-        <v>13000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="I220" s="4">
         <v>12.0</v>
       </c>
       <c r="J220" s="4">
-        <v>25000.0</v>
+        <v>21000.0</v>
       </c>
     </row>
     <row r="221">
@@ -6626,10 +6624,10 @@
         <v>233</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D221" s="4">
-        <v>25000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E221" s="7"/>
       <c r="F221" s="7"/>
@@ -6647,7 +6645,7 @@
         <v>234</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D222" s="4">
         <v>2500.0</v>
@@ -6658,13 +6656,13 @@
         <v>6.0</v>
       </c>
       <c r="H222" s="4">
-        <v>14000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I222" s="4">
         <v>12.0</v>
       </c>
       <c r="J222" s="4">
-        <v>28000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="223">
@@ -6676,10 +6674,10 @@
         <v>235</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D223" s="4">
-        <v>28000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E223" s="7"/>
       <c r="F223" s="7"/>
@@ -6697,7 +6695,7 @@
         <v>236</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D224" s="4">
         <v>2500.0</v>
@@ -6708,13 +6706,13 @@
         <v>6.0</v>
       </c>
       <c r="H224" s="4">
-        <v>13000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="I224" s="4">
         <v>12.0</v>
       </c>
       <c r="J224" s="4">
-        <v>25000.0</v>
+        <v>28000.0</v>
       </c>
     </row>
     <row r="225">
@@ -6726,10 +6724,10 @@
         <v>237</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D225" s="4">
-        <v>25000.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E225" s="7"/>
       <c r="F225" s="7"/>
@@ -6747,7 +6745,7 @@
         <v>238</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D226" s="4">
         <v>2500.0</v>
@@ -6758,13 +6756,13 @@
         <v>6.0</v>
       </c>
       <c r="H226" s="4">
-        <v>14000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I226" s="4">
         <v>12.0</v>
       </c>
       <c r="J226" s="4">
-        <v>27000.0</v>
+        <v>25000.0</v>
       </c>
     </row>
     <row r="227">
@@ -6776,10 +6774,10 @@
         <v>239</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D227" s="4">
-        <v>27000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E227" s="7"/>
       <c r="F227" s="7"/>
@@ -6797,7 +6795,7 @@
         <v>240</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D228" s="4">
         <v>2500.0</v>
@@ -6826,7 +6824,7 @@
         <v>241</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D229" s="4">
         <v>27000.0</v>
@@ -6847,17 +6845,25 @@
         <v>242</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D230" s="4">
-        <v>34000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E230" s="7"/>
       <c r="F230" s="7"/>
-      <c r="G230" s="7"/>
-      <c r="H230" s="7"/>
-      <c r="I230" s="7"/>
-      <c r="J230" s="7"/>
+      <c r="G230" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H230" s="4">
+        <v>14000.0</v>
+      </c>
+      <c r="I230" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J230" s="4">
+        <v>27000.0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="4">
@@ -6868,7 +6874,7 @@
         <v>243</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D231" s="4">
         <v>27000.0</v>
@@ -6889,19 +6895,17 @@
         <v>244</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D232" s="4">
-        <v>37000.0</v>
+        <v>34000.0</v>
       </c>
       <c r="E232" s="7"/>
       <c r="F232" s="7"/>
-      <c r="G232" s="4"/>
-      <c r="H232" s="4"/>
-      <c r="I232" s="4"/>
-      <c r="J232" s="4">
-        <v>37000.0</v>
-      </c>
+      <c r="G232" s="7"/>
+      <c r="H232" s="7"/>
+      <c r="I232" s="7"/>
+      <c r="J232" s="7"/>
     </row>
     <row r="233">
       <c r="A233" s="4">
@@ -6912,10 +6916,10 @@
         <v>245</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D233" s="4">
-        <v>16000.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="7"/>
@@ -6933,17 +6937,19 @@
         <v>246</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D234" s="4">
-        <v>43000.0</v>
+        <v>37000.0</v>
       </c>
       <c r="E234" s="7"/>
       <c r="F234" s="7"/>
-      <c r="G234" s="7"/>
-      <c r="H234" s="7"/>
-      <c r="I234" s="7"/>
-      <c r="J234" s="7"/>
+      <c r="G234" s="4"/>
+      <c r="H234" s="4"/>
+      <c r="I234" s="4"/>
+      <c r="J234" s="4">
+        <v>37000.0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="4">
@@ -6954,10 +6960,10 @@
         <v>247</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D235" s="4">
-        <v>23000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E235" s="7"/>
       <c r="F235" s="7"/>
@@ -6975,10 +6981,10 @@
         <v>248</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D236" s="4">
-        <v>17000.0</v>
+        <v>43000.0</v>
       </c>
       <c r="E236" s="7"/>
       <c r="F236" s="7"/>
@@ -6996,10 +7002,10 @@
         <v>249</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D237" s="4">
-        <v>29000.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="7"/>
@@ -7017,10 +7023,10 @@
         <v>250</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D238" s="4">
-        <v>13000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E238" s="7"/>
       <c r="F238" s="7"/>
@@ -7038,10 +7044,10 @@
         <v>251</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D239" s="4">
-        <v>39000.0</v>
+        <v>29000.0</v>
       </c>
       <c r="E239" s="7"/>
       <c r="F239" s="7"/>
@@ -7059,10 +7065,10 @@
         <v>252</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D240" s="4">
-        <v>382000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="E240" s="7"/>
       <c r="F240" s="7"/>
@@ -7080,10 +7086,10 @@
         <v>253</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D241" s="4">
-        <v>500.0</v>
+        <v>39000.0</v>
       </c>
       <c r="E241" s="7"/>
       <c r="F241" s="7"/>
@@ -7098,13 +7104,13 @@
         <v>241</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D242" s="4">
-        <v>4000.0</v>
+        <v>382000.0</v>
       </c>
       <c r="E242" s="7"/>
       <c r="F242" s="7"/>
@@ -7119,20 +7125,16 @@
         <v>242</v>
       </c>
       <c r="B243" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C243" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="C243" s="5" t="s">
-        <v>254</v>
-      </c>
       <c r="D243" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E243" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F243" s="4">
-        <v>10000.0</v>
-      </c>
+        <v>500.0</v>
+      </c>
+      <c r="E243" s="7"/>
+      <c r="F243" s="7"/>
       <c r="G243" s="7"/>
       <c r="H243" s="7"/>
       <c r="I243" s="7"/>
@@ -7147,17 +7149,13 @@
         <v>257</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D244" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E244" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F244" s="4">
-        <v>14000.0</v>
-      </c>
+        <v>4000.0</v>
+      </c>
+      <c r="E244" s="7"/>
+      <c r="F244" s="7"/>
       <c r="G244" s="7"/>
       <c r="H244" s="7"/>
       <c r="I244" s="7"/>
@@ -7169,16 +7167,20 @@
         <v>244</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D245" s="4">
-        <v>109000.0</v>
-      </c>
-      <c r="E245" s="7"/>
-      <c r="F245" s="7"/>
+        <v>2500.0</v>
+      </c>
+      <c r="E245" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F245" s="4">
+        <v>10000.0</v>
+      </c>
       <c r="G245" s="7"/>
       <c r="H245" s="7"/>
       <c r="I245" s="7"/>
@@ -7190,10 +7192,10 @@
         <v>245</v>
       </c>
       <c r="B246" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C246" s="5" t="s">
         <v>260</v>
-      </c>
-      <c r="C246" s="5" t="s">
-        <v>258</v>
       </c>
       <c r="D246" s="4">
         <v>3000.0</v>
@@ -7218,7 +7220,7 @@
         <v>261</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D247" s="4">
         <v>109000.0</v>
@@ -7239,13 +7241,17 @@
         <v>262</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D248" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E248" s="7"/>
-      <c r="F248" s="7"/>
+      <c r="E248" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F248" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G248" s="7"/>
       <c r="H248" s="7"/>
       <c r="I248" s="7"/>
@@ -7260,10 +7266,10 @@
         <v>263</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D249" s="4">
-        <v>114000.0</v>
+        <v>109000.0</v>
       </c>
       <c r="E249" s="7"/>
       <c r="F249" s="7"/>
@@ -7281,7 +7287,7 @@
         <v>264</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D250" s="4">
         <v>3000.0</v>
@@ -7302,17 +7308,13 @@
         <v>265</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D251" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E251" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F251" s="4">
-        <v>39000.0</v>
-      </c>
+        <v>114000.0</v>
+      </c>
+      <c r="E251" s="7"/>
+      <c r="F251" s="7"/>
       <c r="G251" s="7"/>
       <c r="H251" s="7"/>
       <c r="I251" s="7"/>
@@ -7327,10 +7329,10 @@
         <v>266</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D252" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E252" s="7"/>
       <c r="F252" s="7"/>
@@ -7348,13 +7350,17 @@
         <v>267</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D253" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E253" s="7"/>
-      <c r="F253" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E253" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F253" s="4">
+        <v>39000.0</v>
+      </c>
       <c r="G253" s="7"/>
       <c r="H253" s="7"/>
       <c r="I253" s="7"/>
@@ -7369,7 +7375,7 @@
         <v>268</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D254" s="4">
         <v>114000.0</v>
@@ -7390,7 +7396,7 @@
         <v>269</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D255" s="4">
         <v>3000.0</v>
@@ -7411,7 +7417,7 @@
         <v>270</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D256" s="4">
         <v>114000.0</v>
@@ -7432,7 +7438,7 @@
         <v>271</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D257" s="4">
         <v>3000.0</v>
@@ -7453,7 +7459,7 @@
         <v>272</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D258" s="4">
         <v>114000.0</v>
@@ -7474,7 +7480,7 @@
         <v>273</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D259" s="4">
         <v>3000.0</v>
@@ -7495,10 +7501,10 @@
         <v>274</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D260" s="4">
-        <v>107000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E260" s="7"/>
       <c r="F260" s="7"/>
@@ -7516,7 +7522,7 @@
         <v>275</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D261" s="4">
         <v>3000.0</v>
@@ -7537,17 +7543,17 @@
         <v>276</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D262" s="4">
-        <v>112000.0</v>
-      </c>
-      <c r="E262" s="6"/>
-      <c r="F262" s="6"/>
-      <c r="G262" s="6"/>
-      <c r="H262" s="6"/>
-      <c r="I262" s="6"/>
-      <c r="J262" s="6"/>
+        <v>107000.0</v>
+      </c>
+      <c r="E262" s="7"/>
+      <c r="F262" s="7"/>
+      <c r="G262" s="7"/>
+      <c r="H262" s="7"/>
+      <c r="I262" s="7"/>
+      <c r="J262" s="7"/>
     </row>
     <row r="263">
       <c r="A263" s="4">
@@ -7558,17 +7564,13 @@
         <v>277</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D263" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E263" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F263" s="4">
-        <v>19000.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E263" s="7"/>
+      <c r="F263" s="7"/>
       <c r="G263" s="7"/>
       <c r="H263" s="7"/>
       <c r="I263" s="7"/>
@@ -7583,21 +7585,17 @@
         <v>278</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D264" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E264" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F264" s="4">
-        <v>19000.0</v>
-      </c>
-      <c r="G264" s="7"/>
-      <c r="H264" s="7"/>
-      <c r="I264" s="7"/>
-      <c r="J264" s="7"/>
+        <v>112000.0</v>
+      </c>
+      <c r="E264" s="6"/>
+      <c r="F264" s="6"/>
+      <c r="G264" s="6"/>
+      <c r="H264" s="6"/>
+      <c r="I264" s="6"/>
+      <c r="J264" s="6"/>
     </row>
     <row r="265">
       <c r="A265" s="4">
@@ -7608,13 +7606,17 @@
         <v>279</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D265" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E265" s="4"/>
-      <c r="F265" s="4"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E265" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F265" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G265" s="7"/>
       <c r="H265" s="7"/>
       <c r="I265" s="7"/>
@@ -7629,13 +7631,17 @@
         <v>280</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D266" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E266" s="4"/>
-      <c r="F266" s="4"/>
+      <c r="E266" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F266" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G266" s="7"/>
       <c r="H266" s="7"/>
       <c r="I266" s="7"/>
@@ -7650,7 +7656,7 @@
         <v>281</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D267" s="4">
         <v>86000.0</v>
@@ -7671,18 +7677,14 @@
         <v>282</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D268" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E268" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F268" s="4">
-        <v>19500.0</v>
-      </c>
-      <c r="G268" s="4"/>
+      <c r="E268" s="4"/>
+      <c r="F268" s="4"/>
+      <c r="G268" s="7"/>
       <c r="H268" s="7"/>
       <c r="I268" s="7"/>
       <c r="J268" s="7"/>
@@ -7696,17 +7698,13 @@
         <v>283</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D269" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E269" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F269" s="4">
-        <v>6000.0</v>
-      </c>
+        <v>86000.0</v>
+      </c>
+      <c r="E269" s="4"/>
+      <c r="F269" s="4"/>
       <c r="G269" s="7"/>
       <c r="H269" s="7"/>
       <c r="I269" s="7"/>
@@ -7721,14 +7719,18 @@
         <v>284</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D270" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E270" s="7"/>
-      <c r="F270" s="7"/>
-      <c r="G270" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E270" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F270" s="4">
+        <v>19500.0</v>
+      </c>
+      <c r="G270" s="4"/>
       <c r="H270" s="7"/>
       <c r="I270" s="7"/>
       <c r="J270" s="7"/>
@@ -7742,13 +7744,17 @@
         <v>285</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D271" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E271" s="7"/>
-      <c r="F271" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E271" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F271" s="4">
+        <v>6000.0</v>
+      </c>
       <c r="G271" s="7"/>
       <c r="H271" s="7"/>
       <c r="I271" s="7"/>
@@ -7763,10 +7769,10 @@
         <v>286</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D272" s="4">
-        <v>89000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E272" s="7"/>
       <c r="F272" s="7"/>
@@ -7784,10 +7790,10 @@
         <v>287</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D273" s="4">
-        <v>7500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E273" s="7"/>
       <c r="F273" s="7"/>
@@ -7805,10 +7811,10 @@
         <v>288</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D274" s="4">
-        <v>5000.0</v>
+        <v>89000.0</v>
       </c>
       <c r="E274" s="7"/>
       <c r="F274" s="7"/>
@@ -7826,10 +7832,10 @@
         <v>289</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D275" s="4">
-        <v>3000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E275" s="7"/>
       <c r="F275" s="7"/>
@@ -7847,17 +7853,17 @@
         <v>290</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>291</v>
+        <v>260</v>
       </c>
       <c r="D276" s="4">
-        <v>80000.0</v>
-      </c>
-      <c r="E276" s="6"/>
-      <c r="F276" s="6"/>
-      <c r="G276" s="6"/>
-      <c r="H276" s="6"/>
-      <c r="I276" s="6"/>
-      <c r="J276" s="6"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E276" s="7"/>
+      <c r="F276" s="7"/>
+      <c r="G276" s="7"/>
+      <c r="H276" s="7"/>
+      <c r="I276" s="7"/>
+      <c r="J276" s="7"/>
     </row>
     <row r="277">
       <c r="A277" s="4">
@@ -7868,10 +7874,10 @@
         <v>291</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>291</v>
+        <v>260</v>
       </c>
       <c r="D277" s="4">
-        <v>14000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E277" s="7"/>
       <c r="F277" s="7"/>
@@ -7886,20 +7892,20 @@
         <v>277</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D278" s="4">
-        <v>14500.0</v>
-      </c>
-      <c r="E278" s="7"/>
-      <c r="F278" s="7"/>
-      <c r="G278" s="7"/>
-      <c r="H278" s="7"/>
-      <c r="I278" s="7"/>
-      <c r="J278" s="7"/>
+        <v>80000.0</v>
+      </c>
+      <c r="E278" s="6"/>
+      <c r="F278" s="6"/>
+      <c r="G278" s="6"/>
+      <c r="H278" s="6"/>
+      <c r="I278" s="6"/>
+      <c r="J278" s="6"/>
     </row>
     <row r="279">
       <c r="A279" s="4">
@@ -7907,13 +7913,13 @@
         <v>278</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D279" s="4">
-        <v>15000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E279" s="7"/>
       <c r="F279" s="7"/>
@@ -7928,13 +7934,13 @@
         <v>279</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D280" s="4">
-        <v>15500.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E280" s="7"/>
       <c r="F280" s="7"/>
@@ -7949,13 +7955,13 @@
         <v>280</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C281" s="5" t="s">
         <v>293</v>
       </c>
       <c r="D281" s="4">
-        <v>1500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E281" s="7"/>
       <c r="F281" s="7"/>
@@ -7970,13 +7976,13 @@
         <v>281</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C282" s="5" t="s">
         <v>293</v>
       </c>
       <c r="D282" s="4">
-        <v>12500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E282" s="7"/>
       <c r="F282" s="7"/>
@@ -7991,13 +7997,13 @@
         <v>282</v>
       </c>
       <c r="B283" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C283" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="C283" s="5" t="s">
-        <v>293</v>
-      </c>
       <c r="D283" s="4">
-        <v>500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E283" s="7"/>
       <c r="F283" s="7"/>
@@ -8015,10 +8021,10 @@
         <v>296</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D284" s="4">
-        <v>4500.0</v>
+        <v>12500.0</v>
       </c>
       <c r="E284" s="7"/>
       <c r="F284" s="7"/>
@@ -8036,10 +8042,10 @@
         <v>297</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D285" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E285" s="7"/>
       <c r="F285" s="7"/>
@@ -8057,10 +8063,10 @@
         <v>298</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D286" s="4">
-        <v>23000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E286" s="7"/>
       <c r="F286" s="7"/>
@@ -8078,17 +8084,13 @@
         <v>299</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D287" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E287" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F287" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E287" s="7"/>
+      <c r="F287" s="7"/>
       <c r="G287" s="7"/>
       <c r="H287" s="7"/>
       <c r="I287" s="7"/>
@@ -8103,13 +8105,13 @@
         <v>300</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D288" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E288" s="4"/>
-      <c r="F288" s="4"/>
+        <v>23000.0</v>
+      </c>
+      <c r="E288" s="7"/>
+      <c r="F288" s="7"/>
       <c r="G288" s="7"/>
       <c r="H288" s="7"/>
       <c r="I288" s="7"/>
@@ -8124,16 +8126,16 @@
         <v>301</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D289" s="4">
-        <v>2500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E289" s="4">
         <v>5.0</v>
       </c>
       <c r="F289" s="4">
-        <v>9000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="G289" s="7"/>
       <c r="H289" s="7"/>
@@ -8149,10 +8151,10 @@
         <v>302</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D290" s="4">
-        <v>9000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E290" s="4"/>
       <c r="F290" s="4"/>
@@ -8170,16 +8172,16 @@
         <v>303</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D291" s="4">
-        <v>2000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E291" s="4">
         <v>5.0</v>
       </c>
       <c r="F291" s="4">
-        <v>7500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="G291" s="7"/>
       <c r="H291" s="7"/>
@@ -8195,13 +8197,13 @@
         <v>304</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D292" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E292" s="7"/>
-      <c r="F292" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E292" s="4"/>
+      <c r="F292" s="4"/>
       <c r="G292" s="7"/>
       <c r="H292" s="7"/>
       <c r="I292" s="7"/>
@@ -8216,13 +8218,17 @@
         <v>305</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="D293" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E293" s="7"/>
-      <c r="F293" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E293" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F293" s="4">
+        <v>7500.0</v>
+      </c>
       <c r="G293" s="7"/>
       <c r="H293" s="7"/>
       <c r="I293" s="7"/>
@@ -8234,13 +8240,13 @@
         <v>293</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="D294" s="4">
-        <v>10000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E294" s="7"/>
       <c r="F294" s="7"/>
@@ -8255,13 +8261,13 @@
         <v>294</v>
       </c>
       <c r="B295" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="C295" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="C295" s="5" t="s">
-        <v>306</v>
-      </c>
       <c r="D295" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E295" s="7"/>
       <c r="F295" s="7"/>
@@ -8279,10 +8285,10 @@
         <v>309</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D296" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E296" s="7"/>
       <c r="F296" s="7"/>
@@ -8300,10 +8306,10 @@
         <v>310</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D297" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E297" s="7"/>
       <c r="F297" s="7"/>
@@ -8321,10 +8327,10 @@
         <v>311</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D298" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E298" s="7"/>
       <c r="F298" s="7"/>
@@ -8342,10 +8348,10 @@
         <v>312</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D299" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E299" s="7"/>
       <c r="F299" s="7"/>
@@ -8363,10 +8369,10 @@
         <v>313</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D300" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E300" s="7"/>
       <c r="F300" s="7"/>
@@ -8384,10 +8390,10 @@
         <v>314</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D301" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E301" s="7"/>
       <c r="F301" s="7"/>
@@ -8405,10 +8411,10 @@
         <v>315</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D302" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E302" s="7"/>
       <c r="F302" s="7"/>
@@ -8426,7 +8432,7 @@
         <v>316</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D303" s="4">
         <v>1000.0</v>
@@ -8447,7 +8453,7 @@
         <v>317</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D304" s="4">
         <v>10000.0</v>
@@ -8468,10 +8474,10 @@
         <v>318</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D305" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E305" s="7"/>
       <c r="F305" s="7"/>
@@ -8489,10 +8495,10 @@
         <v>319</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D306" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E306" s="7"/>
       <c r="F306" s="7"/>
@@ -8510,10 +8516,10 @@
         <v>320</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D307" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E307" s="7"/>
       <c r="F307" s="7"/>
@@ -8531,7 +8537,7 @@
         <v>321</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D308" s="4">
         <v>500.0</v>
@@ -8552,7 +8558,7 @@
         <v>322</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D309" s="4">
         <v>5000.0</v>
@@ -8573,10 +8579,10 @@
         <v>323</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D310" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E310" s="7"/>
       <c r="F310" s="7"/>
@@ -8594,10 +8600,10 @@
         <v>324</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D311" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E311" s="7"/>
       <c r="F311" s="7"/>
@@ -8615,10 +8621,10 @@
         <v>325</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D312" s="4">
-        <v>2000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E312" s="7"/>
       <c r="F312" s="7"/>
@@ -8636,10 +8642,10 @@
         <v>326</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D313" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E313" s="7"/>
       <c r="F313" s="7"/>
@@ -8657,10 +8663,10 @@
         <v>327</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D314" s="4">
-        <v>1000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E314" s="7"/>
       <c r="F314" s="7"/>
@@ -8678,7 +8684,7 @@
         <v>328</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D315" s="4">
         <v>5000.0</v>
@@ -8699,7 +8705,7 @@
         <v>329</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D316" s="4">
         <v>1000.0</v>
@@ -8720,7 +8726,7 @@
         <v>330</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D317" s="4">
         <v>5000.0</v>
@@ -8741,7 +8747,7 @@
         <v>331</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D318" s="4">
         <v>1000.0</v>
@@ -8762,7 +8768,7 @@
         <v>332</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D319" s="4">
         <v>5000.0</v>
@@ -8783,10 +8789,10 @@
         <v>333</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D320" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E320" s="7"/>
       <c r="F320" s="7"/>
@@ -8804,10 +8810,10 @@
         <v>334</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D321" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E321" s="7"/>
       <c r="F321" s="7"/>
@@ -8825,10 +8831,10 @@
         <v>335</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D322" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E322" s="7"/>
       <c r="F322" s="7"/>
@@ -8846,10 +8852,10 @@
         <v>336</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D323" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E323" s="7"/>
       <c r="F323" s="7"/>
@@ -8867,10 +8873,10 @@
         <v>337</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D324" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E324" s="7"/>
       <c r="F324" s="7"/>
@@ -8888,7 +8894,7 @@
         <v>338</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D325" s="4">
         <v>5000.0</v>
@@ -8909,7 +8915,7 @@
         <v>339</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D326" s="4">
         <v>500.0</v>
@@ -8930,7 +8936,7 @@
         <v>340</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D327" s="4">
         <v>5000.0</v>
@@ -8951,10 +8957,10 @@
         <v>341</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D328" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E328" s="7"/>
       <c r="F328" s="7"/>
@@ -8972,7 +8978,7 @@
         <v>342</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D329" s="4">
         <v>5000.0</v>
@@ -8993,17 +8999,13 @@
         <v>343</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D330" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E330" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F330" s="4">
-        <v>4500.0</v>
-      </c>
+      <c r="E330" s="7"/>
+      <c r="F330" s="7"/>
       <c r="G330" s="7"/>
       <c r="H330" s="7"/>
       <c r="I330" s="7"/>
@@ -9018,10 +9020,10 @@
         <v>344</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D331" s="4">
-        <v>4500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E331" s="7"/>
       <c r="F331" s="7"/>
@@ -9039,13 +9041,17 @@
         <v>345</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D332" s="4">
-        <v>51000.0</v>
-      </c>
-      <c r="E332" s="4"/>
-      <c r="F332" s="4"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E332" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F332" s="4">
+        <v>4500.0</v>
+      </c>
       <c r="G332" s="7"/>
       <c r="H332" s="7"/>
       <c r="I332" s="7"/>
@@ -9060,17 +9066,13 @@
         <v>346</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D333" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E333" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F333" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>4500.0</v>
+      </c>
+      <c r="E333" s="7"/>
+      <c r="F333" s="7"/>
       <c r="G333" s="7"/>
       <c r="H333" s="7"/>
       <c r="I333" s="7"/>
@@ -9085,13 +9087,13 @@
         <v>347</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D334" s="4">
-        <v>52000.0</v>
-      </c>
-      <c r="E334" s="7"/>
-      <c r="F334" s="7"/>
+        <v>51000.0</v>
+      </c>
+      <c r="E334" s="4"/>
+      <c r="F334" s="4"/>
       <c r="G334" s="7"/>
       <c r="H334" s="7"/>
       <c r="I334" s="7"/>
@@ -9106,13 +9108,17 @@
         <v>348</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D335" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E335" s="7"/>
-      <c r="F335" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E335" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F335" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G335" s="7"/>
       <c r="H335" s="7"/>
       <c r="I335" s="7"/>
@@ -9127,10 +9133,10 @@
         <v>349</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D336" s="4">
-        <v>5000.0</v>
+        <v>52000.0</v>
       </c>
       <c r="E336" s="7"/>
       <c r="F336" s="7"/>
@@ -9148,17 +9154,13 @@
         <v>350</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D337" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E337" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F337" s="4">
-        <v>17000.0</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E337" s="7"/>
+      <c r="F337" s="7"/>
       <c r="G337" s="7"/>
       <c r="H337" s="7"/>
       <c r="I337" s="7"/>
@@ -9173,7 +9175,7 @@
         <v>351</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D338" s="4">
         <v>5000.0</v>
@@ -9194,16 +9196,16 @@
         <v>352</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D339" s="4">
-        <v>7000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E339" s="4">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F339" s="4">
-        <v>32500.0</v>
+        <v>17000.0</v>
       </c>
       <c r="G339" s="7"/>
       <c r="H339" s="7"/>
@@ -9219,10 +9221,10 @@
         <v>353</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D340" s="4">
-        <v>7500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E340" s="7"/>
       <c r="F340" s="7"/>
@@ -9240,13 +9242,17 @@
         <v>354</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D341" s="4">
-        <v>9500.0</v>
-      </c>
-      <c r="E341" s="7"/>
-      <c r="F341" s="7"/>
+        <v>7000.0</v>
+      </c>
+      <c r="E341" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F341" s="4">
+        <v>32500.0</v>
+      </c>
       <c r="G341" s="7"/>
       <c r="H341" s="7"/>
       <c r="I341" s="7"/>
@@ -9261,10 +9267,10 @@
         <v>355</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D342" s="4">
-        <v>3500.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E342" s="7"/>
       <c r="F342" s="7"/>
@@ -9282,10 +9288,10 @@
         <v>356</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D343" s="4">
-        <v>5000.0</v>
+        <v>9500.0</v>
       </c>
       <c r="E343" s="7"/>
       <c r="F343" s="7"/>
@@ -9303,17 +9309,13 @@
         <v>357</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D344" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E344" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F344" s="4">
-        <v>22500.0</v>
-      </c>
+        <v>3500.0</v>
+      </c>
+      <c r="E344" s="7"/>
+      <c r="F344" s="7"/>
       <c r="G344" s="7"/>
       <c r="H344" s="7"/>
       <c r="I344" s="7"/>
@@ -9328,17 +9330,13 @@
         <v>358</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D345" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E345" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F345" s="4">
-        <v>12500.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E345" s="7"/>
+      <c r="F345" s="7"/>
       <c r="G345" s="7"/>
       <c r="H345" s="7"/>
       <c r="I345" s="7"/>
@@ -9353,13 +9351,17 @@
         <v>359</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D346" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E346" s="4"/>
-      <c r="F346" s="4"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E346" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F346" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G346" s="7"/>
       <c r="H346" s="7"/>
       <c r="I346" s="7"/>
@@ -9374,14 +9376,18 @@
         <v>360</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D347" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E347" s="4"/>
-      <c r="F347" s="4"/>
-      <c r="G347" s="4"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E347" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F347" s="4">
+        <v>12500.0</v>
+      </c>
+      <c r="G347" s="7"/>
       <c r="H347" s="7"/>
       <c r="I347" s="7"/>
       <c r="J347" s="7"/>
@@ -9395,17 +9401,13 @@
         <v>361</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D348" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E348" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F348" s="4">
-        <v>11500.0</v>
-      </c>
+        <v>3500.0</v>
+      </c>
+      <c r="E348" s="4"/>
+      <c r="F348" s="4"/>
       <c r="G348" s="7"/>
       <c r="H348" s="7"/>
       <c r="I348" s="7"/>
@@ -9420,14 +9422,14 @@
         <v>362</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D349" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E349" s="7"/>
-      <c r="F349" s="7"/>
-      <c r="G349" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E349" s="4"/>
+      <c r="F349" s="4"/>
+      <c r="G349" s="4"/>
       <c r="H349" s="7"/>
       <c r="I349" s="7"/>
       <c r="J349" s="7"/>
@@ -9441,16 +9443,16 @@
         <v>363</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D350" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E350" s="4">
         <v>5.0</v>
       </c>
       <c r="F350" s="4">
-        <v>22500.0</v>
+        <v>11500.0</v>
       </c>
       <c r="G350" s="7"/>
       <c r="H350" s="7"/>
@@ -9466,10 +9468,10 @@
         <v>364</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D351" s="4">
-        <v>1000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E351" s="7"/>
       <c r="F351" s="7"/>
@@ -9487,13 +9489,17 @@
         <v>365</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D352" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E352" s="7"/>
-      <c r="F352" s="7"/>
+      <c r="E352" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F352" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G352" s="7"/>
       <c r="H352" s="7"/>
       <c r="I352" s="7"/>
@@ -9508,10 +9514,10 @@
         <v>366</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D353" s="4">
-        <v>3000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E353" s="7"/>
       <c r="F353" s="7"/>
@@ -9529,10 +9535,10 @@
         <v>367</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D354" s="4">
-        <v>14000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E354" s="7"/>
       <c r="F354" s="7"/>
@@ -9550,10 +9556,10 @@
         <v>368</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>369</v>
+        <v>308</v>
       </c>
       <c r="D355" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E355" s="7"/>
       <c r="F355" s="7"/>
@@ -9568,13 +9574,13 @@
         <v>355</v>
       </c>
       <c r="B356" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>369</v>
+        <v>308</v>
       </c>
       <c r="D356" s="4">
-        <v>4000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E356" s="7"/>
       <c r="F356" s="7"/>
@@ -9589,10 +9595,10 @@
         <v>356</v>
       </c>
       <c r="B357" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="C357" s="5" t="s">
         <v>371</v>
-      </c>
-      <c r="C357" s="5" t="s">
-        <v>369</v>
       </c>
       <c r="D357" s="4">
         <v>1000.0</v>
@@ -9613,10 +9619,10 @@
         <v>372</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D358" s="4">
-        <v>10000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E358" s="7"/>
       <c r="F358" s="7"/>
@@ -9634,7 +9640,7 @@
         <v>373</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D359" s="4">
         <v>1000.0</v>
@@ -9655,7 +9661,7 @@
         <v>374</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D360" s="4">
         <v>10000.0</v>
@@ -9676,10 +9682,10 @@
         <v>375</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D361" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E361" s="7"/>
       <c r="F361" s="7"/>
@@ -9697,10 +9703,10 @@
         <v>376</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D362" s="4">
-        <v>2500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E362" s="7"/>
       <c r="F362" s="7"/>
@@ -9718,10 +9724,10 @@
         <v>377</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D363" s="4">
-        <v>3000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E363" s="7"/>
       <c r="F363" s="7"/>
@@ -9739,10 +9745,10 @@
         <v>378</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D364" s="4">
-        <v>5000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E364" s="7"/>
       <c r="F364" s="7"/>
@@ -9760,7 +9766,7 @@
         <v>379</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D365" s="4">
         <v>3000.0</v>
@@ -9781,17 +9787,13 @@
         <v>380</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D366" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E366" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F366" s="4">
-        <v>3000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E366" s="7"/>
+      <c r="F366" s="7"/>
       <c r="G366" s="7"/>
       <c r="H366" s="7"/>
       <c r="I366" s="7"/>
@@ -9806,10 +9808,10 @@
         <v>381</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D367" s="4">
-        <v>500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E367" s="7"/>
       <c r="F367" s="7"/>
@@ -9827,13 +9829,17 @@
         <v>382</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D368" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E368" s="7"/>
-      <c r="F368" s="7"/>
+      <c r="E368" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F368" s="4">
+        <v>3000.0</v>
+      </c>
       <c r="G368" s="7"/>
       <c r="H368" s="7"/>
       <c r="I368" s="7"/>
@@ -9848,10 +9854,10 @@
         <v>383</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D369" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E369" s="7"/>
       <c r="F369" s="7"/>
@@ -9869,10 +9875,10 @@
         <v>384</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D370" s="4">
-        <v>7000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E370" s="7"/>
       <c r="F370" s="7"/>
@@ -9890,10 +9896,10 @@
         <v>385</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D371" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E371" s="7"/>
       <c r="F371" s="7"/>
@@ -9911,10 +9917,10 @@
         <v>386</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D372" s="4">
-        <v>25000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E372" s="7"/>
       <c r="F372" s="7"/>
@@ -9932,10 +9938,10 @@
         <v>387</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D373" s="4">
-        <v>8000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E373" s="7"/>
       <c r="F373" s="7"/>
@@ -9953,10 +9959,10 @@
         <v>388</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D374" s="4">
-        <v>4000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E374" s="7"/>
       <c r="F374" s="7"/>
@@ -9974,10 +9980,10 @@
         <v>389</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="D375" s="4">
-        <v>2000.0</v>
+        <v>8000.0</v>
       </c>
       <c r="E375" s="7"/>
       <c r="F375" s="7"/>
@@ -9992,13 +9998,13 @@
         <v>375</v>
       </c>
       <c r="B376" s="5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="D376" s="4">
-        <v>45000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E376" s="7"/>
       <c r="F376" s="7"/>
@@ -10013,13 +10019,13 @@
         <v>376</v>
       </c>
       <c r="B377" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C377" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="C377" s="5" t="s">
-        <v>390</v>
-      </c>
       <c r="D377" s="4">
-        <v>2500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E377" s="7"/>
       <c r="F377" s="7"/>
@@ -10037,10 +10043,10 @@
         <v>393</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D378" s="4">
-        <v>2500.0</v>
+        <v>45000.0</v>
       </c>
       <c r="E378" s="7"/>
       <c r="F378" s="7"/>
@@ -10058,10 +10064,10 @@
         <v>394</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D379" s="4">
-        <v>4000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E379" s="7"/>
       <c r="F379" s="7"/>
@@ -10079,10 +10085,10 @@
         <v>395</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D380" s="4">
-        <v>40000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E380" s="7"/>
       <c r="F380" s="7"/>
@@ -10100,10 +10106,10 @@
         <v>396</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D381" s="4">
-        <v>5000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E381" s="7"/>
       <c r="F381" s="7"/>
@@ -10121,16 +10127,16 @@
         <v>397</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D382" s="4">
-        <v>46000.0</v>
+        <v>40000.0</v>
       </c>
       <c r="E382" s="7"/>
       <c r="F382" s="7"/>
       <c r="G382" s="7"/>
       <c r="H382" s="7"/>
-      <c r="I382" s="4"/>
+      <c r="I382" s="7"/>
       <c r="J382" s="7"/>
     </row>
     <row r="383">
@@ -10142,16 +10148,16 @@
         <v>398</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D383" s="4">
-        <v>2000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E383" s="7"/>
       <c r="F383" s="7"/>
       <c r="G383" s="7"/>
       <c r="H383" s="7"/>
-      <c r="I383" s="4"/>
+      <c r="I383" s="7"/>
       <c r="J383" s="7"/>
     </row>
     <row r="384">
@@ -10163,10 +10169,10 @@
         <v>399</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D384" s="4">
-        <v>17000.0</v>
+        <v>46000.0</v>
       </c>
       <c r="E384" s="7"/>
       <c r="F384" s="7"/>
@@ -10184,10 +10190,10 @@
         <v>400</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D385" s="4">
-        <v>500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E385" s="7"/>
       <c r="F385" s="7"/>
@@ -10205,16 +10211,16 @@
         <v>401</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D386" s="4">
-        <v>1000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E386" s="7"/>
       <c r="F386" s="7"/>
       <c r="G386" s="7"/>
       <c r="H386" s="7"/>
-      <c r="I386" s="7"/>
+      <c r="I386" s="4"/>
       <c r="J386" s="7"/>
     </row>
     <row r="387">
@@ -10226,16 +10232,16 @@
         <v>402</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D387" s="4">
-        <v>10000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E387" s="7"/>
       <c r="F387" s="7"/>
       <c r="G387" s="7"/>
       <c r="H387" s="7"/>
-      <c r="I387" s="7"/>
+      <c r="I387" s="4"/>
       <c r="J387" s="7"/>
     </row>
     <row r="388">
@@ -10247,10 +10253,10 @@
         <v>403</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D388" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E388" s="7"/>
       <c r="F388" s="7"/>
@@ -10268,10 +10274,10 @@
         <v>404</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D389" s="4">
-        <v>1500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E389" s="7"/>
       <c r="F389" s="7"/>
@@ -10289,10 +10295,10 @@
         <v>405</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D390" s="4">
-        <v>12000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E390" s="7"/>
       <c r="F390" s="7"/>
@@ -10310,10 +10316,10 @@
         <v>406</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D391" s="4">
-        <v>3000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E391" s="7"/>
       <c r="F391" s="7"/>
@@ -10331,10 +10337,10 @@
         <v>407</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D392" s="4">
-        <v>1000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E392" s="7"/>
       <c r="F392" s="7"/>
@@ -10352,10 +10358,10 @@
         <v>408</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D393" s="4">
-        <v>25000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E393" s="7"/>
       <c r="F393" s="7"/>
@@ -10373,10 +10379,10 @@
         <v>409</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D394" s="4">
-        <v>9000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E394" s="7"/>
       <c r="F394" s="7"/>
@@ -10394,12 +10400,12 @@
         <v>410</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D395" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E395" s="4"/>
+        <v>25000.0</v>
+      </c>
+      <c r="E395" s="7"/>
       <c r="F395" s="7"/>
       <c r="G395" s="7"/>
       <c r="H395" s="7"/>
@@ -10415,7 +10421,7 @@
         <v>411</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D396" s="4">
         <v>9000.0</v>
@@ -10436,12 +10442,12 @@
         <v>412</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D397" s="4">
-        <v>4500.0</v>
-      </c>
-      <c r="E397" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E397" s="4"/>
       <c r="F397" s="7"/>
       <c r="G397" s="7"/>
       <c r="H397" s="7"/>
@@ -10457,10 +10463,10 @@
         <v>413</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D398" s="4">
-        <v>500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E398" s="7"/>
       <c r="F398" s="7"/>
@@ -10478,10 +10484,10 @@
         <v>414</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D399" s="4">
-        <v>3000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E399" s="7"/>
       <c r="F399" s="7"/>
@@ -10499,10 +10505,10 @@
         <v>415</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D400" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E400" s="7"/>
       <c r="F400" s="7"/>
@@ -10516,42 +10522,42 @@
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
-      <c r="B401" s="9" t="s">
+      <c r="B401" s="5" t="s">
         <v>416</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="D401" s="10">
-        <v>4500.0</v>
-      </c>
-      <c r="E401" s="11"/>
-      <c r="F401" s="11"/>
-      <c r="G401" s="11"/>
-      <c r="H401" s="11"/>
-      <c r="I401" s="11"/>
-      <c r="J401" s="11"/>
+        <v>392</v>
+      </c>
+      <c r="D401" s="4">
+        <v>3000.0</v>
+      </c>
+      <c r="E401" s="7"/>
+      <c r="F401" s="7"/>
+      <c r="G401" s="7"/>
+      <c r="H401" s="7"/>
+      <c r="I401" s="7"/>
+      <c r="J401" s="7"/>
     </row>
     <row r="402">
       <c r="A402" s="4">
         <f t="shared" si="1"/>
         <v>401</v>
       </c>
-      <c r="B402" s="9" t="s">
+      <c r="B402" s="5" t="s">
         <v>417</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="D402" s="10">
-        <v>50000.0</v>
-      </c>
-      <c r="E402" s="11"/>
-      <c r="F402" s="11"/>
-      <c r="G402" s="11"/>
-      <c r="H402" s="11"/>
-      <c r="I402" s="11"/>
-      <c r="J402" s="11"/>
+        <v>392</v>
+      </c>
+      <c r="D402" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E402" s="7"/>
+      <c r="F402" s="7"/>
+      <c r="G402" s="7"/>
+      <c r="H402" s="7"/>
+      <c r="I402" s="7"/>
+      <c r="J402" s="7"/>
     </row>
     <row r="403">
       <c r="A403" s="4">
@@ -10562,10 +10568,10 @@
         <v>418</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D403" s="10">
-        <v>12000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E403" s="11"/>
       <c r="F403" s="11"/>
@@ -10579,14 +10585,14 @@
         <f t="shared" si="1"/>
         <v>403</v>
       </c>
-      <c r="B404" s="5" t="s">
+      <c r="B404" s="9" t="s">
         <v>419</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D404" s="10">
-        <v>4500.0</v>
+        <v>50000.0</v>
       </c>
       <c r="E404" s="11"/>
       <c r="F404" s="11"/>
@@ -10604,10 +10610,10 @@
         <v>420</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>421</v>
+        <v>392</v>
       </c>
       <c r="D405" s="10">
-        <v>3000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E405" s="11"/>
       <c r="F405" s="11"/>
@@ -10621,14 +10627,14 @@
         <f t="shared" si="1"/>
         <v>405</v>
       </c>
-      <c r="B406" s="9" t="s">
+      <c r="B406" s="5" t="s">
         <v>421</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>421</v>
+        <v>392</v>
       </c>
       <c r="D406" s="10">
-        <v>5000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E406" s="11"/>
       <c r="F406" s="11"/>
@@ -10646,10 +10652,10 @@
         <v>422</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D407" s="10">
-        <v>6000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E407" s="11"/>
       <c r="F407" s="11"/>
@@ -10667,10 +10673,10 @@
         <v>423</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>369</v>
+        <v>423</v>
       </c>
       <c r="D408" s="10">
-        <v>12000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E408" s="11"/>
       <c r="F408" s="11"/>
@@ -10688,13 +10694,13 @@
         <v>424</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>369</v>
+        <v>423</v>
       </c>
       <c r="D409" s="10">
-        <v>200.0</v>
-      </c>
-      <c r="E409" s="10"/>
-      <c r="F409" s="10"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E409" s="11"/>
+      <c r="F409" s="11"/>
       <c r="G409" s="11"/>
       <c r="H409" s="11"/>
       <c r="I409" s="11"/>
@@ -10709,17 +10715,13 @@
         <v>425</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D410" s="10">
-        <v>5000.0</v>
-      </c>
-      <c r="E410" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="F410" s="10">
-        <v>4500.0</v>
-      </c>
+        <v>12000.0</v>
+      </c>
+      <c r="E410" s="11"/>
+      <c r="F410" s="11"/>
       <c r="G410" s="11"/>
       <c r="H410" s="11"/>
       <c r="I410" s="11"/>
@@ -10734,13 +10736,13 @@
         <v>426</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D411" s="10">
-        <v>18000.0</v>
-      </c>
-      <c r="E411" s="11"/>
-      <c r="F411" s="11"/>
+        <v>200.0</v>
+      </c>
+      <c r="E411" s="10"/>
+      <c r="F411" s="10"/>
       <c r="G411" s="11"/>
       <c r="H411" s="11"/>
       <c r="I411" s="11"/>
@@ -10755,13 +10757,17 @@
         <v>427</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D412" s="10">
-        <v>17000.0</v>
-      </c>
-      <c r="E412" s="11"/>
-      <c r="F412" s="11"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E412" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="F412" s="10">
+        <v>4500.0</v>
+      </c>
       <c r="G412" s="11"/>
       <c r="H412" s="11"/>
       <c r="I412" s="11"/>
@@ -10776,10 +10782,10 @@
         <v>428</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D413" s="10">
-        <v>17500.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E413" s="11"/>
       <c r="F413" s="11"/>
@@ -10797,10 +10803,10 @@
         <v>429</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D414" s="10">
-        <v>9000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E414" s="11"/>
       <c r="F414" s="11"/>
@@ -10818,10 +10824,10 @@
         <v>430</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D415" s="10">
-        <v>9000.0</v>
+        <v>17500.0</v>
       </c>
       <c r="E415" s="11"/>
       <c r="F415" s="11"/>
@@ -10839,7 +10845,7 @@
         <v>431</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D416" s="10">
         <v>9000.0</v>
@@ -10860,10 +10866,10 @@
         <v>432</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D417" s="10">
-        <v>19500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E417" s="11"/>
       <c r="F417" s="11"/>
@@ -10881,10 +10887,10 @@
         <v>433</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D418" s="10">
-        <v>8500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E418" s="11"/>
       <c r="F418" s="11"/>
@@ -10902,10 +10908,10 @@
         <v>434</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D419" s="10">
-        <v>4500.0</v>
+        <v>19500.0</v>
       </c>
       <c r="E419" s="11"/>
       <c r="F419" s="11"/>
@@ -10923,10 +10929,10 @@
         <v>435</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D420" s="10">
-        <v>9000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="E420" s="11"/>
       <c r="F420" s="11"/>
@@ -10944,10 +10950,10 @@
         <v>436</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D421" s="10">
-        <v>14000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E421" s="11"/>
       <c r="F421" s="11"/>
@@ -10965,10 +10971,10 @@
         <v>437</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D422" s="10">
-        <v>3000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E422" s="11"/>
       <c r="F422" s="11"/>
@@ -10986,10 +10992,10 @@
         <v>438</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D423" s="10">
-        <v>12000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E423" s="11"/>
       <c r="F423" s="11"/>
@@ -11007,10 +11013,10 @@
         <v>439</v>
       </c>
       <c r="C424" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D424" s="10">
-        <v>20000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E424" s="11"/>
       <c r="F424" s="11"/>
@@ -11028,10 +11034,10 @@
         <v>440</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D425" s="10">
-        <v>1.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E425" s="11"/>
       <c r="F425" s="11"/>
@@ -11041,10 +11047,19 @@
       <c r="J425" s="11"/>
     </row>
     <row r="426">
-      <c r="A426" s="12"/>
-      <c r="B426" s="12"/>
-      <c r="C426" s="12"/>
-      <c r="D426" s="11"/>
+      <c r="A426" s="4">
+        <f t="shared" si="1"/>
+        <v>425</v>
+      </c>
+      <c r="B426" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="C426" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="D426" s="10">
+        <v>20000.0</v>
+      </c>
       <c r="E426" s="11"/>
       <c r="F426" s="11"/>
       <c r="G426" s="11"/>
@@ -12052,13 +12067,13 @@
       <c r="A510" s="12"/>
       <c r="B510" s="12"/>
       <c r="C510" s="12"/>
-      <c r="D510" s="12"/>
-      <c r="E510" s="12"/>
-      <c r="F510" s="12"/>
-      <c r="G510" s="12"/>
-      <c r="H510" s="12"/>
-      <c r="I510" s="12"/>
-      <c r="J510" s="12"/>
+      <c r="D510" s="11"/>
+      <c r="E510" s="11"/>
+      <c r="F510" s="11"/>
+      <c r="G510" s="11"/>
+      <c r="H510" s="11"/>
+      <c r="I510" s="11"/>
+      <c r="J510" s="11"/>
     </row>
     <row r="511">
       <c r="A511" s="12"/>
@@ -20472,15 +20487,27 @@
       <c r="I1211" s="12"/>
       <c r="J1211" s="12"/>
     </row>
+    <row r="1212">
+      <c r="A1212" s="12"/>
+      <c r="B1212" s="12"/>
+      <c r="C1212" s="12"/>
+      <c r="D1212" s="12"/>
+      <c r="E1212" s="12"/>
+      <c r="F1212" s="12"/>
+      <c r="G1212" s="12"/>
+      <c r="H1212" s="12"/>
+      <c r="I1212" s="12"/>
+      <c r="J1212" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$425"/>
-  <conditionalFormatting sqref="A2:J1211">
+  <autoFilter ref="$B$1:$C$426"/>
+  <conditionalFormatting sqref="A2:J1212">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C425">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C426">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20537,11 +20564,11 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="str">
-        <f t="shared" ref="A2:A58" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
+        <f t="shared" ref="A2:A59" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4">
@@ -20560,7 +20587,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -20579,7 +20606,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -20598,7 +20625,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -20617,7 +20644,7 @@
         <v>GROSIR5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="4">
@@ -20636,7 +20663,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -20655,7 +20682,7 @@
         <v>GROSIR7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="4">
@@ -20674,7 +20701,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -20693,7 +20720,7 @@
         <v>GROSIR9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="4">
@@ -20712,7 +20739,7 @@
         <v>GROSIR10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="4">
@@ -20731,7 +20758,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -20750,7 +20777,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -20769,7 +20796,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -20788,7 +20815,7 @@
         <v>GROSIR14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="4">
@@ -20807,7 +20834,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -20826,7 +20853,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -20845,7 +20872,7 @@
         <v>GROSIR17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="4">
@@ -20864,7 +20891,7 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
@@ -20883,7 +20910,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -20902,7 +20929,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -20921,7 +20948,7 @@
         <v>GROSIR21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4">
@@ -20940,7 +20967,7 @@
         <v>GROSIR22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="4">
@@ -20959,7 +20986,7 @@
         <v>GROSIR23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="4">
@@ -20978,7 +21005,7 @@
         <v>GROSIR24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="4">
@@ -20997,7 +21024,7 @@
         <v>GROSIR25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="4">
@@ -21016,7 +21043,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -21035,7 +21062,7 @@
         <v>GROSIR27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="4">
@@ -21054,7 +21081,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -21073,7 +21100,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -21092,11 +21119,11 @@
         <v>GROSIR30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="4">
-        <v>215000.0</v>
+        <v>21500.0</v>
       </c>
       <c r="E31" s="14"/>
       <c r="F31" s="14"/>
@@ -21111,18 +21138,18 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>196</v>
+        <v>458</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
-        <v>41000.0</v>
-      </c>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
+        <v>215000.0</v>
+      </c>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="str">
@@ -21130,11 +21157,11 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>457</v>
+        <v>198</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
-        <v>43000.0</v>
+        <v>41000.0</v>
       </c>
       <c r="E33" s="13"/>
       <c r="F33" s="13"/>
@@ -21149,18 +21176,18 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
+        <v>43000.0</v>
+      </c>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="str">
@@ -21168,18 +21195,18 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="str">
@@ -21187,11 +21214,11 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
-        <v>25000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
@@ -21206,11 +21233,11 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
-        <v>9000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E37" s="13"/>
       <c r="F37" s="13"/>
@@ -21225,11 +21252,11 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
-        <v>2500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
@@ -21244,7 +21271,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -21263,11 +21290,11 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
-        <v>2900.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
@@ -21281,12 +21308,12 @@
         <f t="shared" si="1"/>
         <v>GROSIR40</v>
       </c>
-      <c r="B41" s="9" t="s">
-        <v>418</v>
+      <c r="B41" s="5" t="s">
+        <v>466</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
-        <v>11000.0</v>
+        <v>2900.0</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
@@ -21300,12 +21327,12 @@
         <f t="shared" si="1"/>
         <v>GROSIR41</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>465</v>
+      <c r="B42" s="9" t="s">
+        <v>420</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
-        <v>1700.0</v>
+        <v>11000.0</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
@@ -21320,11 +21347,11 @@
         <v>GROSIR42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>419</v>
+        <v>467</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="4">
-        <v>4000.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
@@ -21339,11 +21366,11 @@
         <v>GROSIR43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>466</v>
+        <v>421</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="4">
-        <v>4500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
@@ -21358,11 +21385,11 @@
         <v>GROSIR44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>36</v>
+        <v>468</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="4">
-        <v>3500.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E45" s="13"/>
       <c r="F45" s="13"/>
@@ -21377,11 +21404,11 @@
         <v>GROSIR45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>467</v>
+        <v>36</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="4">
-        <v>2000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E46" s="13"/>
       <c r="F46" s="13"/>
@@ -21396,11 +21423,11 @@
         <v>GROSIR46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>38</v>
+        <v>469</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="4">
-        <v>3500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E47" s="13"/>
       <c r="F47" s="13"/>
@@ -21415,18 +21442,18 @@
         <v>GROSIR47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>468</v>
+        <v>38</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="4">
-        <v>169000.0</v>
-      </c>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="str">
@@ -21434,18 +21461,18 @@
         <v>GROSIR48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="4">
-        <v>171000.0</v>
-      </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
+        <v>169000.0</v>
+      </c>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="str">
@@ -21453,18 +21480,18 @@
         <v>GROSIR49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="4">
-        <v>169000.0</v>
-      </c>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
+        <v>171000.0</v>
+      </c>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="str">
@@ -21472,18 +21499,18 @@
         <v>GROSIR50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="4">
-        <v>196000.0</v>
-      </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
+        <v>169000.0</v>
+      </c>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="str">
@@ -21491,18 +21518,18 @@
         <v>GROSIR51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="4">
-        <v>175000.0</v>
-      </c>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="14"/>
+        <v>196000.0</v>
+      </c>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="str">
@@ -21510,18 +21537,18 @@
         <v>GROSIR52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="4">
-        <v>163000.0</v>
-      </c>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13"/>
-      <c r="J53" s="13"/>
+        <v>175000.0</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="str">
@@ -21529,11 +21556,11 @@
         <v>GROSIR53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="4">
-        <v>57000.0</v>
+        <v>163000.0</v>
       </c>
       <c r="E54" s="13"/>
       <c r="F54" s="13"/>
@@ -21548,11 +21575,11 @@
         <v>GROSIR54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="4">
-        <v>56000.0</v>
+        <v>57000.0</v>
       </c>
       <c r="E55" s="13"/>
       <c r="F55" s="13"/>
@@ -21567,18 +21594,18 @@
         <v>GROSIR55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="4">
-        <v>150000.0</v>
-      </c>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14"/>
+        <v>56000.0</v>
+      </c>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="str">
@@ -21586,18 +21613,18 @@
         <v>GROSIR56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="4">
-        <v>155000.0</v>
-      </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
+        <v>150000.0</v>
+      </c>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="str">
@@ -21605,78 +21632,85 @@
         <v>GROSIR57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="4">
+        <v>155000.0</v>
+      </c>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR58</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="C59" s="5"/>
+      <c r="D59" s="4">
         <v>198000.0</v>
       </c>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="14"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
     </row>
     <row r="60">
       <c r="A60" s="4"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="4"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
     </row>
     <row r="61">
       <c r="A61" s="4"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="4"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="13"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
     </row>
     <row r="62">
       <c r="A62" s="4"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="4"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
     </row>
     <row r="63">
       <c r="A63" s="4"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="4"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="13"/>
-      <c r="J63" s="13"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
     </row>
     <row r="64">
       <c r="A64" s="4"/>
@@ -21707,24 +21741,24 @@
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
       <c r="D66" s="4"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="14"/>
-      <c r="J66" s="14"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
     </row>
     <row r="67">
       <c r="A67" s="4"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
       <c r="D67" s="4"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="13"/>
-      <c r="J67" s="13"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
     </row>
     <row r="68">
       <c r="A68" s="4"/>
@@ -21767,48 +21801,48 @@
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
       <c r="D71" s="4"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="14"/>
-      <c r="J71" s="14"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="13"/>
     </row>
     <row r="72">
       <c r="A72" s="4"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
       <c r="D72" s="4"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
     </row>
     <row r="73">
       <c r="A73" s="4"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
       <c r="D73" s="4"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="14"/>
-      <c r="J73" s="14"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="13"/>
     </row>
     <row r="74">
       <c r="A74" s="4"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
       <c r="D74" s="4"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
     </row>
     <row r="75">
       <c r="A75" s="4"/>
@@ -21851,24 +21885,24 @@
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="4"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="14"/>
-      <c r="J78" s="14"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
+      <c r="J78" s="13"/>
     </row>
     <row r="79">
       <c r="A79" s="4"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="4"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="13"/>
-      <c r="J79" s="13"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
     </row>
     <row r="80">
       <c r="A80" s="4"/>
@@ -21899,12 +21933,12 @@
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
       <c r="D82" s="4"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="14"/>
-      <c r="J82" s="14"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="13"/>
+      <c r="I82" s="13"/>
+      <c r="J82" s="13"/>
     </row>
     <row r="83">
       <c r="A83" s="4"/>
@@ -21947,12 +21981,12 @@
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
       <c r="D86" s="4"/>
-      <c r="E86" s="13"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13"/>
-      <c r="H86" s="13"/>
-      <c r="I86" s="13"/>
-      <c r="J86" s="13"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="14"/>
     </row>
     <row r="87">
       <c r="A87" s="4"/>
@@ -22031,12 +22065,12 @@
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
       <c r="D93" s="4"/>
-      <c r="E93" s="14"/>
-      <c r="F93" s="14"/>
-      <c r="G93" s="14"/>
-      <c r="H93" s="14"/>
-      <c r="I93" s="14"/>
-      <c r="J93" s="14"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="13"/>
+      <c r="H93" s="13"/>
+      <c r="I93" s="13"/>
+      <c r="J93" s="13"/>
     </row>
     <row r="94">
       <c r="A94" s="4"/>
@@ -22079,12 +22113,12 @@
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
       <c r="D97" s="4"/>
-      <c r="E97" s="13"/>
-      <c r="F97" s="13"/>
-      <c r="G97" s="13"/>
-      <c r="H97" s="13"/>
-      <c r="I97" s="13"/>
-      <c r="J97" s="13"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
+      <c r="J97" s="14"/>
     </row>
     <row r="98">
       <c r="A98" s="4"/>
@@ -22175,8 +22209,8 @@
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
       <c r="D105" s="4"/>
-      <c r="E105" s="4"/>
-      <c r="F105" s="4"/>
+      <c r="E105" s="13"/>
+      <c r="F105" s="13"/>
       <c r="G105" s="13"/>
       <c r="H105" s="13"/>
       <c r="I105" s="13"/>
@@ -22187,8 +22221,8 @@
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
       <c r="D106" s="4"/>
-      <c r="E106" s="13"/>
-      <c r="F106" s="13"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
       <c r="G106" s="13"/>
       <c r="H106" s="13"/>
       <c r="I106" s="13"/>
@@ -22211,24 +22245,24 @@
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
       <c r="D108" s="4"/>
-      <c r="E108" s="14"/>
-      <c r="F108" s="14"/>
-      <c r="G108" s="14"/>
-      <c r="H108" s="14"/>
-      <c r="I108" s="14"/>
-      <c r="J108" s="14"/>
+      <c r="E108" s="13"/>
+      <c r="F108" s="13"/>
+      <c r="G108" s="13"/>
+      <c r="H108" s="13"/>
+      <c r="I108" s="13"/>
+      <c r="J108" s="13"/>
     </row>
     <row r="109">
       <c r="A109" s="4"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
       <c r="D109" s="4"/>
-      <c r="E109" s="13"/>
-      <c r="F109" s="13"/>
-      <c r="G109" s="13"/>
-      <c r="H109" s="13"/>
-      <c r="I109" s="13"/>
-      <c r="J109" s="13"/>
+      <c r="E109" s="14"/>
+      <c r="F109" s="14"/>
+      <c r="G109" s="14"/>
+      <c r="H109" s="14"/>
+      <c r="I109" s="14"/>
+      <c r="J109" s="14"/>
     </row>
     <row r="110">
       <c r="A110" s="4"/>
@@ -22295,24 +22329,24 @@
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
       <c r="D115" s="4"/>
-      <c r="E115" s="14"/>
-      <c r="F115" s="14"/>
-      <c r="G115" s="14"/>
-      <c r="H115" s="14"/>
-      <c r="I115" s="14"/>
-      <c r="J115" s="14"/>
+      <c r="E115" s="13"/>
+      <c r="F115" s="13"/>
+      <c r="G115" s="13"/>
+      <c r="H115" s="13"/>
+      <c r="I115" s="13"/>
+      <c r="J115" s="13"/>
     </row>
     <row r="116">
       <c r="A116" s="4"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
       <c r="D116" s="4"/>
-      <c r="E116" s="13"/>
-      <c r="F116" s="13"/>
-      <c r="G116" s="13"/>
-      <c r="H116" s="13"/>
-      <c r="I116" s="13"/>
-      <c r="J116" s="13"/>
+      <c r="E116" s="14"/>
+      <c r="F116" s="14"/>
+      <c r="G116" s="14"/>
+      <c r="H116" s="14"/>
+      <c r="I116" s="14"/>
+      <c r="J116" s="14"/>
     </row>
     <row r="117">
       <c r="A117" s="4"/>
@@ -22403,12 +22437,12 @@
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
       <c r="D124" s="4"/>
-      <c r="E124" s="14"/>
-      <c r="F124" s="14"/>
-      <c r="G124" s="14"/>
-      <c r="H124" s="14"/>
-      <c r="I124" s="14"/>
-      <c r="J124" s="14"/>
+      <c r="E124" s="13"/>
+      <c r="F124" s="13"/>
+      <c r="G124" s="13"/>
+      <c r="H124" s="13"/>
+      <c r="I124" s="13"/>
+      <c r="J124" s="13"/>
     </row>
     <row r="125">
       <c r="A125" s="4"/>
@@ -22549,10 +22583,10 @@
       <c r="D136" s="4"/>
       <c r="E136" s="14"/>
       <c r="F136" s="14"/>
-      <c r="G136" s="4"/>
-      <c r="H136" s="4"/>
-      <c r="I136" s="4"/>
-      <c r="J136" s="4"/>
+      <c r="G136" s="14"/>
+      <c r="H136" s="14"/>
+      <c r="I136" s="14"/>
+      <c r="J136" s="14"/>
     </row>
     <row r="137">
       <c r="A137" s="4"/>
@@ -22561,10 +22595,10 @@
       <c r="D137" s="4"/>
       <c r="E137" s="14"/>
       <c r="F137" s="14"/>
-      <c r="G137" s="14"/>
-      <c r="H137" s="14"/>
-      <c r="I137" s="14"/>
-      <c r="J137" s="14"/>
+      <c r="G137" s="4"/>
+      <c r="H137" s="4"/>
+      <c r="I137" s="4"/>
+      <c r="J137" s="4"/>
     </row>
     <row r="138">
       <c r="A138" s="4"/>
@@ -22573,10 +22607,10 @@
       <c r="D138" s="4"/>
       <c r="E138" s="14"/>
       <c r="F138" s="14"/>
-      <c r="G138" s="4"/>
-      <c r="H138" s="4"/>
-      <c r="I138" s="4"/>
-      <c r="J138" s="4"/>
+      <c r="G138" s="14"/>
+      <c r="H138" s="14"/>
+      <c r="I138" s="14"/>
+      <c r="J138" s="14"/>
     </row>
     <row r="139">
       <c r="A139" s="4"/>
@@ -22585,10 +22619,10 @@
       <c r="D139" s="4"/>
       <c r="E139" s="14"/>
       <c r="F139" s="14"/>
-      <c r="G139" s="14"/>
-      <c r="H139" s="14"/>
-      <c r="I139" s="14"/>
-      <c r="J139" s="14"/>
+      <c r="G139" s="4"/>
+      <c r="H139" s="4"/>
+      <c r="I139" s="4"/>
+      <c r="J139" s="4"/>
     </row>
     <row r="140">
       <c r="A140" s="4"/>
@@ -22597,10 +22631,10 @@
       <c r="D140" s="4"/>
       <c r="E140" s="14"/>
       <c r="F140" s="14"/>
-      <c r="G140" s="4"/>
-      <c r="H140" s="4"/>
-      <c r="I140" s="4"/>
-      <c r="J140" s="4"/>
+      <c r="G140" s="14"/>
+      <c r="H140" s="14"/>
+      <c r="I140" s="14"/>
+      <c r="J140" s="14"/>
     </row>
     <row r="141">
       <c r="A141" s="4"/>
@@ -22609,10 +22643,10 @@
       <c r="D141" s="4"/>
       <c r="E141" s="14"/>
       <c r="F141" s="14"/>
-      <c r="G141" s="14"/>
-      <c r="H141" s="14"/>
-      <c r="I141" s="14"/>
-      <c r="J141" s="14"/>
+      <c r="G141" s="4"/>
+      <c r="H141" s="4"/>
+      <c r="I141" s="4"/>
+      <c r="J141" s="4"/>
     </row>
     <row r="142">
       <c r="A142" s="4"/>
@@ -22621,10 +22655,10 @@
       <c r="D142" s="4"/>
       <c r="E142" s="14"/>
       <c r="F142" s="14"/>
-      <c r="G142" s="4"/>
-      <c r="H142" s="4"/>
-      <c r="I142" s="4"/>
-      <c r="J142" s="4"/>
+      <c r="G142" s="14"/>
+      <c r="H142" s="14"/>
+      <c r="I142" s="14"/>
+      <c r="J142" s="14"/>
     </row>
     <row r="143">
       <c r="A143" s="4"/>
@@ -22633,10 +22667,10 @@
       <c r="D143" s="4"/>
       <c r="E143" s="14"/>
       <c r="F143" s="14"/>
-      <c r="G143" s="14"/>
-      <c r="H143" s="14"/>
-      <c r="I143" s="14"/>
-      <c r="J143" s="14"/>
+      <c r="G143" s="4"/>
+      <c r="H143" s="4"/>
+      <c r="I143" s="4"/>
+      <c r="J143" s="4"/>
     </row>
     <row r="144">
       <c r="A144" s="4"/>
@@ -22645,10 +22679,10 @@
       <c r="D144" s="4"/>
       <c r="E144" s="14"/>
       <c r="F144" s="14"/>
-      <c r="G144" s="4"/>
-      <c r="H144" s="4"/>
-      <c r="I144" s="4"/>
-      <c r="J144" s="4"/>
+      <c r="G144" s="14"/>
+      <c r="H144" s="14"/>
+      <c r="I144" s="14"/>
+      <c r="J144" s="14"/>
     </row>
     <row r="145">
       <c r="A145" s="4"/>
@@ -22657,10 +22691,10 @@
       <c r="D145" s="4"/>
       <c r="E145" s="14"/>
       <c r="F145" s="14"/>
-      <c r="G145" s="14"/>
-      <c r="H145" s="14"/>
-      <c r="I145" s="14"/>
-      <c r="J145" s="14"/>
+      <c r="G145" s="4"/>
+      <c r="H145" s="4"/>
+      <c r="I145" s="4"/>
+      <c r="J145" s="4"/>
     </row>
     <row r="146">
       <c r="A146" s="4"/>
@@ -22669,10 +22703,10 @@
       <c r="D146" s="4"/>
       <c r="E146" s="14"/>
       <c r="F146" s="14"/>
-      <c r="G146" s="4"/>
-      <c r="H146" s="4"/>
-      <c r="I146" s="4"/>
-      <c r="J146" s="4"/>
+      <c r="G146" s="14"/>
+      <c r="H146" s="14"/>
+      <c r="I146" s="14"/>
+      <c r="J146" s="14"/>
     </row>
     <row r="147">
       <c r="A147" s="4"/>
@@ -22681,34 +22715,34 @@
       <c r="D147" s="4"/>
       <c r="E147" s="14"/>
       <c r="F147" s="14"/>
-      <c r="G147" s="14"/>
-      <c r="H147" s="14"/>
-      <c r="I147" s="14"/>
-      <c r="J147" s="14"/>
+      <c r="G147" s="4"/>
+      <c r="H147" s="4"/>
+      <c r="I147" s="4"/>
+      <c r="J147" s="4"/>
     </row>
     <row r="148">
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
       <c r="D148" s="4"/>
-      <c r="E148" s="4"/>
-      <c r="F148" s="4"/>
-      <c r="G148" s="4"/>
-      <c r="H148" s="4"/>
-      <c r="I148" s="4"/>
-      <c r="J148" s="4"/>
+      <c r="E148" s="14"/>
+      <c r="F148" s="14"/>
+      <c r="G148" s="14"/>
+      <c r="H148" s="14"/>
+      <c r="I148" s="14"/>
+      <c r="J148" s="14"/>
     </row>
     <row r="149">
       <c r="A149" s="4"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
       <c r="D149" s="4"/>
-      <c r="E149" s="14"/>
-      <c r="F149" s="14"/>
-      <c r="G149" s="14"/>
-      <c r="H149" s="14"/>
-      <c r="I149" s="14"/>
-      <c r="J149" s="14"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="4"/>
+      <c r="G149" s="4"/>
+      <c r="H149" s="4"/>
+      <c r="I149" s="4"/>
+      <c r="J149" s="4"/>
     </row>
     <row r="150">
       <c r="A150" s="4"/>
@@ -22717,10 +22751,10 @@
       <c r="D150" s="4"/>
       <c r="E150" s="14"/>
       <c r="F150" s="14"/>
-      <c r="G150" s="4"/>
-      <c r="H150" s="4"/>
-      <c r="I150" s="4"/>
-      <c r="J150" s="4"/>
+      <c r="G150" s="14"/>
+      <c r="H150" s="14"/>
+      <c r="I150" s="14"/>
+      <c r="J150" s="14"/>
     </row>
     <row r="151">
       <c r="A151" s="4"/>
@@ -22729,10 +22763,10 @@
       <c r="D151" s="4"/>
       <c r="E151" s="14"/>
       <c r="F151" s="14"/>
-      <c r="G151" s="14"/>
-      <c r="H151" s="14"/>
-      <c r="I151" s="14"/>
-      <c r="J151" s="14"/>
+      <c r="G151" s="4"/>
+      <c r="H151" s="4"/>
+      <c r="I151" s="4"/>
+      <c r="J151" s="4"/>
     </row>
     <row r="152">
       <c r="A152" s="4"/>
@@ -22741,10 +22775,10 @@
       <c r="D152" s="4"/>
       <c r="E152" s="14"/>
       <c r="F152" s="14"/>
-      <c r="G152" s="4"/>
-      <c r="H152" s="4"/>
-      <c r="I152" s="4"/>
-      <c r="J152" s="4"/>
+      <c r="G152" s="14"/>
+      <c r="H152" s="14"/>
+      <c r="I152" s="14"/>
+      <c r="J152" s="14"/>
     </row>
     <row r="153">
       <c r="A153" s="4"/>
@@ -22753,34 +22787,34 @@
       <c r="D153" s="4"/>
       <c r="E153" s="14"/>
       <c r="F153" s="14"/>
-      <c r="G153" s="14"/>
-      <c r="H153" s="14"/>
-      <c r="I153" s="14"/>
-      <c r="J153" s="14"/>
+      <c r="G153" s="4"/>
+      <c r="H153" s="4"/>
+      <c r="I153" s="4"/>
+      <c r="J153" s="4"/>
     </row>
     <row r="154">
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
       <c r="D154" s="4"/>
-      <c r="E154" s="4"/>
-      <c r="F154" s="4"/>
-      <c r="G154" s="4"/>
-      <c r="H154" s="4"/>
-      <c r="I154" s="4"/>
-      <c r="J154" s="4"/>
+      <c r="E154" s="14"/>
+      <c r="F154" s="14"/>
+      <c r="G154" s="14"/>
+      <c r="H154" s="14"/>
+      <c r="I154" s="14"/>
+      <c r="J154" s="14"/>
     </row>
     <row r="155">
       <c r="A155" s="4"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
       <c r="D155" s="4"/>
-      <c r="E155" s="14"/>
-      <c r="F155" s="14"/>
-      <c r="G155" s="14"/>
-      <c r="H155" s="14"/>
-      <c r="I155" s="14"/>
-      <c r="J155" s="14"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="4"/>
+      <c r="G155" s="4"/>
+      <c r="H155" s="4"/>
+      <c r="I155" s="4"/>
+      <c r="J155" s="4"/>
     </row>
     <row r="156">
       <c r="A156" s="4"/>
@@ -22789,10 +22823,10 @@
       <c r="D156" s="4"/>
       <c r="E156" s="14"/>
       <c r="F156" s="14"/>
-      <c r="G156" s="4"/>
-      <c r="H156" s="4"/>
-      <c r="I156" s="4"/>
-      <c r="J156" s="4"/>
+      <c r="G156" s="14"/>
+      <c r="H156" s="14"/>
+      <c r="I156" s="14"/>
+      <c r="J156" s="14"/>
     </row>
     <row r="157">
       <c r="A157" s="4"/>
@@ -22801,10 +22835,10 @@
       <c r="D157" s="4"/>
       <c r="E157" s="14"/>
       <c r="F157" s="14"/>
-      <c r="G157" s="14"/>
-      <c r="H157" s="14"/>
-      <c r="I157" s="14"/>
-      <c r="J157" s="14"/>
+      <c r="G157" s="4"/>
+      <c r="H157" s="4"/>
+      <c r="I157" s="4"/>
+      <c r="J157" s="4"/>
     </row>
     <row r="158">
       <c r="A158" s="4"/>
@@ -22813,10 +22847,10 @@
       <c r="D158" s="4"/>
       <c r="E158" s="14"/>
       <c r="F158" s="14"/>
-      <c r="G158" s="4"/>
-      <c r="H158" s="4"/>
-      <c r="I158" s="4"/>
-      <c r="J158" s="4"/>
+      <c r="G158" s="14"/>
+      <c r="H158" s="14"/>
+      <c r="I158" s="14"/>
+      <c r="J158" s="14"/>
     </row>
     <row r="159">
       <c r="A159" s="4"/>
@@ -22825,10 +22859,10 @@
       <c r="D159" s="4"/>
       <c r="E159" s="14"/>
       <c r="F159" s="14"/>
-      <c r="G159" s="14"/>
-      <c r="H159" s="14"/>
-      <c r="I159" s="14"/>
-      <c r="J159" s="14"/>
+      <c r="G159" s="4"/>
+      <c r="H159" s="4"/>
+      <c r="I159" s="4"/>
+      <c r="J159" s="4"/>
     </row>
     <row r="160">
       <c r="A160" s="4"/>
@@ -22837,10 +22871,10 @@
       <c r="D160" s="4"/>
       <c r="E160" s="14"/>
       <c r="F160" s="14"/>
-      <c r="G160" s="4"/>
-      <c r="H160" s="4"/>
-      <c r="I160" s="4"/>
-      <c r="J160" s="4"/>
+      <c r="G160" s="14"/>
+      <c r="H160" s="14"/>
+      <c r="I160" s="14"/>
+      <c r="J160" s="14"/>
     </row>
     <row r="161">
       <c r="A161" s="4"/>
@@ -22849,10 +22883,10 @@
       <c r="D161" s="4"/>
       <c r="E161" s="14"/>
       <c r="F161" s="14"/>
-      <c r="G161" s="14"/>
-      <c r="H161" s="14"/>
-      <c r="I161" s="14"/>
-      <c r="J161" s="14"/>
+      <c r="G161" s="4"/>
+      <c r="H161" s="4"/>
+      <c r="I161" s="4"/>
+      <c r="J161" s="4"/>
     </row>
     <row r="162">
       <c r="A162" s="4"/>
@@ -22861,10 +22895,10 @@
       <c r="D162" s="4"/>
       <c r="E162" s="14"/>
       <c r="F162" s="14"/>
-      <c r="G162" s="4"/>
-      <c r="H162" s="4"/>
-      <c r="I162" s="4"/>
-      <c r="J162" s="4"/>
+      <c r="G162" s="14"/>
+      <c r="H162" s="14"/>
+      <c r="I162" s="14"/>
+      <c r="J162" s="14"/>
     </row>
     <row r="163">
       <c r="A163" s="4"/>
@@ -22873,10 +22907,10 @@
       <c r="D163" s="4"/>
       <c r="E163" s="14"/>
       <c r="F163" s="14"/>
-      <c r="G163" s="14"/>
-      <c r="H163" s="14"/>
-      <c r="I163" s="14"/>
-      <c r="J163" s="14"/>
+      <c r="G163" s="4"/>
+      <c r="H163" s="4"/>
+      <c r="I163" s="4"/>
+      <c r="J163" s="4"/>
     </row>
     <row r="164">
       <c r="A164" s="4"/>
@@ -22885,10 +22919,10 @@
       <c r="D164" s="4"/>
       <c r="E164" s="14"/>
       <c r="F164" s="14"/>
-      <c r="G164" s="4"/>
-      <c r="H164" s="4"/>
-      <c r="I164" s="4"/>
-      <c r="J164" s="4"/>
+      <c r="G164" s="14"/>
+      <c r="H164" s="14"/>
+      <c r="I164" s="14"/>
+      <c r="J164" s="14"/>
     </row>
     <row r="165">
       <c r="A165" s="4"/>
@@ -22897,10 +22931,10 @@
       <c r="D165" s="4"/>
       <c r="E165" s="14"/>
       <c r="F165" s="14"/>
-      <c r="G165" s="14"/>
-      <c r="H165" s="14"/>
-      <c r="I165" s="14"/>
-      <c r="J165" s="14"/>
+      <c r="G165" s="4"/>
+      <c r="H165" s="4"/>
+      <c r="I165" s="4"/>
+      <c r="J165" s="4"/>
     </row>
     <row r="166">
       <c r="A166" s="4"/>
@@ -22909,10 +22943,10 @@
       <c r="D166" s="4"/>
       <c r="E166" s="14"/>
       <c r="F166" s="14"/>
-      <c r="G166" s="4"/>
-      <c r="H166" s="4"/>
-      <c r="I166" s="4"/>
-      <c r="J166" s="4"/>
+      <c r="G166" s="14"/>
+      <c r="H166" s="14"/>
+      <c r="I166" s="14"/>
+      <c r="J166" s="14"/>
     </row>
     <row r="167">
       <c r="A167" s="4"/>
@@ -22921,10 +22955,10 @@
       <c r="D167" s="4"/>
       <c r="E167" s="14"/>
       <c r="F167" s="14"/>
-      <c r="G167" s="14"/>
-      <c r="H167" s="14"/>
-      <c r="I167" s="14"/>
-      <c r="J167" s="14"/>
+      <c r="G167" s="4"/>
+      <c r="H167" s="4"/>
+      <c r="I167" s="4"/>
+      <c r="J167" s="4"/>
     </row>
     <row r="168">
       <c r="A168" s="4"/>
@@ -22933,10 +22967,10 @@
       <c r="D168" s="4"/>
       <c r="E168" s="14"/>
       <c r="F168" s="14"/>
-      <c r="G168" s="4"/>
-      <c r="H168" s="4"/>
-      <c r="I168" s="4"/>
-      <c r="J168" s="4"/>
+      <c r="G168" s="14"/>
+      <c r="H168" s="14"/>
+      <c r="I168" s="14"/>
+      <c r="J168" s="14"/>
     </row>
     <row r="169">
       <c r="A169" s="4"/>
@@ -22945,10 +22979,10 @@
       <c r="D169" s="4"/>
       <c r="E169" s="14"/>
       <c r="F169" s="14"/>
-      <c r="G169" s="14"/>
-      <c r="H169" s="14"/>
-      <c r="I169" s="14"/>
-      <c r="J169" s="14"/>
+      <c r="G169" s="4"/>
+      <c r="H169" s="4"/>
+      <c r="I169" s="4"/>
+      <c r="J169" s="4"/>
     </row>
     <row r="170">
       <c r="A170" s="4"/>
@@ -22957,10 +22991,10 @@
       <c r="D170" s="4"/>
       <c r="E170" s="14"/>
       <c r="F170" s="14"/>
-      <c r="G170" s="4"/>
-      <c r="H170" s="4"/>
-      <c r="I170" s="4"/>
-      <c r="J170" s="4"/>
+      <c r="G170" s="14"/>
+      <c r="H170" s="14"/>
+      <c r="I170" s="14"/>
+      <c r="J170" s="14"/>
     </row>
     <row r="171">
       <c r="A171" s="4"/>
@@ -22969,10 +23003,10 @@
       <c r="D171" s="4"/>
       <c r="E171" s="14"/>
       <c r="F171" s="14"/>
-      <c r="G171" s="14"/>
-      <c r="H171" s="14"/>
-      <c r="I171" s="14"/>
-      <c r="J171" s="14"/>
+      <c r="G171" s="4"/>
+      <c r="H171" s="4"/>
+      <c r="I171" s="4"/>
+      <c r="J171" s="4"/>
     </row>
     <row r="172">
       <c r="A172" s="4"/>
@@ -22981,10 +23015,10 @@
       <c r="D172" s="4"/>
       <c r="E172" s="14"/>
       <c r="F172" s="14"/>
-      <c r="G172" s="4"/>
-      <c r="H172" s="4"/>
-      <c r="I172" s="4"/>
-      <c r="J172" s="4"/>
+      <c r="G172" s="14"/>
+      <c r="H172" s="14"/>
+      <c r="I172" s="14"/>
+      <c r="J172" s="14"/>
     </row>
     <row r="173">
       <c r="A173" s="4"/>
@@ -22993,10 +23027,10 @@
       <c r="D173" s="4"/>
       <c r="E173" s="14"/>
       <c r="F173" s="14"/>
-      <c r="G173" s="14"/>
-      <c r="H173" s="14"/>
-      <c r="I173" s="14"/>
-      <c r="J173" s="14"/>
+      <c r="G173" s="4"/>
+      <c r="H173" s="4"/>
+      <c r="I173" s="4"/>
+      <c r="J173" s="4"/>
     </row>
     <row r="174">
       <c r="A174" s="4"/>
@@ -23005,10 +23039,10 @@
       <c r="D174" s="4"/>
       <c r="E174" s="14"/>
       <c r="F174" s="14"/>
-      <c r="G174" s="4"/>
-      <c r="H174" s="4"/>
-      <c r="I174" s="4"/>
-      <c r="J174" s="4"/>
+      <c r="G174" s="14"/>
+      <c r="H174" s="14"/>
+      <c r="I174" s="14"/>
+      <c r="J174" s="14"/>
     </row>
     <row r="175">
       <c r="A175" s="4"/>
@@ -23017,10 +23051,10 @@
       <c r="D175" s="4"/>
       <c r="E175" s="14"/>
       <c r="F175" s="14"/>
-      <c r="G175" s="15"/>
-      <c r="H175" s="15"/>
-      <c r="I175" s="14"/>
-      <c r="J175" s="14"/>
+      <c r="G175" s="4"/>
+      <c r="H175" s="4"/>
+      <c r="I175" s="4"/>
+      <c r="J175" s="4"/>
     </row>
     <row r="176">
       <c r="A176" s="4"/>
@@ -23029,8 +23063,8 @@
       <c r="D176" s="4"/>
       <c r="E176" s="14"/>
       <c r="F176" s="14"/>
-      <c r="G176" s="14"/>
-      <c r="H176" s="14"/>
+      <c r="G176" s="15"/>
+      <c r="H176" s="15"/>
       <c r="I176" s="14"/>
       <c r="J176" s="14"/>
     </row>
@@ -23267,24 +23301,24 @@
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
       <c r="D196" s="4"/>
-      <c r="E196" s="13"/>
-      <c r="F196" s="13"/>
-      <c r="G196" s="13"/>
-      <c r="H196" s="13"/>
-      <c r="I196" s="13"/>
-      <c r="J196" s="13"/>
+      <c r="E196" s="14"/>
+      <c r="F196" s="14"/>
+      <c r="G196" s="14"/>
+      <c r="H196" s="14"/>
+      <c r="I196" s="14"/>
+      <c r="J196" s="14"/>
     </row>
     <row r="197">
       <c r="A197" s="4"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
       <c r="D197" s="4"/>
-      <c r="E197" s="14"/>
-      <c r="F197" s="14"/>
-      <c r="G197" s="14"/>
-      <c r="H197" s="14"/>
-      <c r="I197" s="14"/>
-      <c r="J197" s="14"/>
+      <c r="E197" s="13"/>
+      <c r="F197" s="13"/>
+      <c r="G197" s="13"/>
+      <c r="H197" s="13"/>
+      <c r="I197" s="13"/>
+      <c r="J197" s="13"/>
     </row>
     <row r="198">
       <c r="A198" s="4"/>
@@ -23375,24 +23409,24 @@
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
       <c r="D205" s="4"/>
-      <c r="E205" s="13"/>
-      <c r="F205" s="13"/>
-      <c r="G205" s="13"/>
-      <c r="H205" s="13"/>
-      <c r="I205" s="13"/>
-      <c r="J205" s="13"/>
+      <c r="E205" s="14"/>
+      <c r="F205" s="14"/>
+      <c r="G205" s="14"/>
+      <c r="H205" s="14"/>
+      <c r="I205" s="14"/>
+      <c r="J205" s="14"/>
     </row>
     <row r="206">
       <c r="A206" s="4"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
       <c r="D206" s="4"/>
-      <c r="E206" s="14"/>
-      <c r="F206" s="14"/>
-      <c r="G206" s="14"/>
-      <c r="H206" s="14"/>
-      <c r="I206" s="14"/>
-      <c r="J206" s="14"/>
+      <c r="E206" s="13"/>
+      <c r="F206" s="13"/>
+      <c r="G206" s="13"/>
+      <c r="H206" s="13"/>
+      <c r="I206" s="13"/>
+      <c r="J206" s="13"/>
     </row>
     <row r="207">
       <c r="A207" s="4"/>
@@ -23903,8 +23937,8 @@
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
       <c r="D249" s="4"/>
-      <c r="E249" s="4"/>
-      <c r="F249" s="4"/>
+      <c r="E249" s="14"/>
+      <c r="F249" s="14"/>
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="14"/>
@@ -23915,8 +23949,8 @@
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
       <c r="D250" s="4"/>
-      <c r="E250" s="14"/>
-      <c r="F250" s="14"/>
+      <c r="E250" s="4"/>
+      <c r="F250" s="4"/>
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="14"/>
@@ -23991,7 +24025,7 @@
       <c r="F256" s="14"/>
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
-      <c r="I256" s="5"/>
+      <c r="I256" s="14"/>
       <c r="J256" s="14"/>
     </row>
     <row r="257">
@@ -24003,7 +24037,7 @@
       <c r="F257" s="14"/>
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
-      <c r="I257" s="14"/>
+      <c r="I257" s="5"/>
       <c r="J257" s="14"/>
     </row>
     <row r="258">
@@ -24055,10 +24089,10 @@
       <c r="J261" s="14"/>
     </row>
     <row r="262">
-      <c r="A262" s="14"/>
-      <c r="B262" s="14"/>
-      <c r="C262" s="14"/>
-      <c r="D262" s="14"/>
+      <c r="A262" s="4"/>
+      <c r="B262" s="5"/>
+      <c r="C262" s="5"/>
+      <c r="D262" s="4"/>
       <c r="E262" s="14"/>
       <c r="F262" s="14"/>
       <c r="G262" s="14"/>
@@ -24175,16 +24209,16 @@
       <c r="J271" s="14"/>
     </row>
     <row r="272">
-      <c r="A272" s="12"/>
-      <c r="B272" s="12"/>
-      <c r="C272" s="12"/>
-      <c r="D272" s="12"/>
-      <c r="E272" s="12"/>
-      <c r="F272" s="12"/>
-      <c r="G272" s="12"/>
-      <c r="H272" s="12"/>
-      <c r="I272" s="12"/>
-      <c r="J272" s="12"/>
+      <c r="A272" s="14"/>
+      <c r="B272" s="14"/>
+      <c r="C272" s="14"/>
+      <c r="D272" s="14"/>
+      <c r="E272" s="14"/>
+      <c r="F272" s="14"/>
+      <c r="G272" s="14"/>
+      <c r="H272" s="14"/>
+      <c r="I272" s="14"/>
+      <c r="J272" s="14"/>
     </row>
     <row r="273">
       <c r="A273" s="12"/>
@@ -33894,9 +33928,21 @@
       <c r="I1081" s="12"/>
       <c r="J1081" s="12"/>
     </row>
+    <row r="1082">
+      <c r="A1082" s="12"/>
+      <c r="B1082" s="12"/>
+      <c r="C1082" s="12"/>
+      <c r="D1082" s="12"/>
+      <c r="E1082" s="12"/>
+      <c r="F1082" s="12"/>
+      <c r="G1082" s="12"/>
+      <c r="H1082" s="12"/>
+      <c r="I1082" s="12"/>
+      <c r="J1082" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$261"/>
-  <conditionalFormatting sqref="A2:J1081">
+  <autoFilter ref="$B$1:$C$262"/>
+  <conditionalFormatting sqref="A2:J1082">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$426</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$427</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$262</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="482">
   <si>
     <t>Barcode</t>
   </si>
@@ -594,6 +594,9 @@
   </si>
   <si>
     <t>Tepung Beras Rosebrand 200gr KG</t>
+  </si>
+  <si>
+    <t>Tepung Beras Rosebrand 500gr Dus</t>
   </si>
   <si>
     <t>Minyak Curah Kompan</t>
@@ -1845,7 +1848,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A426" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A427" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -5663,7 +5666,7 @@
         <v>130</v>
       </c>
       <c r="D181" s="4">
-        <v>175000.0</v>
+        <v>17500.0</v>
       </c>
       <c r="E181" s="7"/>
       <c r="F181" s="7"/>
@@ -5684,7 +5687,7 @@
         <v>130</v>
       </c>
       <c r="D182" s="4">
-        <v>21000.0</v>
+        <v>165000.0</v>
       </c>
       <c r="E182" s="7"/>
       <c r="F182" s="7"/>
@@ -5705,14 +5708,10 @@
         <v>130</v>
       </c>
       <c r="D183" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="E183" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F183" s="4">
-        <v>22000.0</v>
-      </c>
+        <v>21000.0</v>
+      </c>
+      <c r="E183" s="7"/>
+      <c r="F183" s="7"/>
       <c r="G183" s="7"/>
       <c r="H183" s="7"/>
       <c r="I183" s="7"/>
@@ -5730,10 +5729,14 @@
         <v>130</v>
       </c>
       <c r="D184" s="4">
-        <v>21000.0</v>
-      </c>
-      <c r="E184" s="7"/>
-      <c r="F184" s="7"/>
+        <v>6000.0</v>
+      </c>
+      <c r="E184" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F184" s="4">
+        <v>22000.0</v>
+      </c>
       <c r="G184" s="7"/>
       <c r="H184" s="7"/>
       <c r="I184" s="7"/>
@@ -5772,7 +5775,7 @@
         <v>130</v>
       </c>
       <c r="D186" s="4">
-        <v>245000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
@@ -5793,7 +5796,7 @@
         <v>130</v>
       </c>
       <c r="D187" s="4">
-        <v>42000.0</v>
+        <v>245000.0</v>
       </c>
       <c r="E187" s="7"/>
       <c r="F187" s="7"/>
@@ -5814,7 +5817,7 @@
         <v>130</v>
       </c>
       <c r="D188" s="4">
-        <v>44000.0</v>
+        <v>42000.0</v>
       </c>
       <c r="E188" s="7"/>
       <c r="F188" s="7"/>
@@ -5835,7 +5838,7 @@
         <v>130</v>
       </c>
       <c r="D189" s="4">
-        <v>255000.0</v>
+        <v>44000.0</v>
       </c>
       <c r="E189" s="7"/>
       <c r="F189" s="7"/>
@@ -5856,7 +5859,7 @@
         <v>130</v>
       </c>
       <c r="D190" s="4">
-        <v>21000.0</v>
+        <v>255000.0</v>
       </c>
       <c r="E190" s="7"/>
       <c r="F190" s="7"/>
@@ -5877,7 +5880,7 @@
         <v>130</v>
       </c>
       <c r="D191" s="4">
-        <v>42000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E191" s="7"/>
       <c r="F191" s="7"/>
@@ -5898,14 +5901,14 @@
         <v>130</v>
       </c>
       <c r="D192" s="4">
-        <v>14500.0</v>
+        <v>42000.0</v>
       </c>
       <c r="E192" s="7"/>
       <c r="F192" s="7"/>
-      <c r="G192" s="4"/>
-      <c r="H192" s="4"/>
-      <c r="I192" s="4"/>
-      <c r="J192" s="4"/>
+      <c r="G192" s="7"/>
+      <c r="H192" s="7"/>
+      <c r="I192" s="7"/>
+      <c r="J192" s="7"/>
     </row>
     <row r="193">
       <c r="A193" s="4">
@@ -5916,25 +5919,17 @@
         <v>204</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>205</v>
+        <v>130</v>
       </c>
       <c r="D193" s="4">
-        <v>2000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E193" s="7"/>
       <c r="F193" s="7"/>
-      <c r="G193" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H193" s="4">
-        <v>5500.0</v>
-      </c>
-      <c r="I193" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J193" s="4">
-        <v>10000.0</v>
-      </c>
+      <c r="G193" s="4"/>
+      <c r="H193" s="4"/>
+      <c r="I193" s="4"/>
+      <c r="J193" s="4"/>
     </row>
     <row r="194">
       <c r="A194" s="4">
@@ -5942,20 +5937,28 @@
         <v>193</v>
       </c>
       <c r="B194" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C194" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C194" s="5" t="s">
-        <v>205</v>
-      </c>
       <c r="D194" s="4">
-        <v>10000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E194" s="7"/>
       <c r="F194" s="7"/>
-      <c r="G194" s="7"/>
-      <c r="H194" s="7"/>
-      <c r="I194" s="7"/>
-      <c r="J194" s="7"/>
+      <c r="G194" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H194" s="4">
+        <v>5500.0</v>
+      </c>
+      <c r="I194" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J194" s="4">
+        <v>10000.0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4">
@@ -5966,25 +5969,17 @@
         <v>207</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D195" s="4">
-        <v>2000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E195" s="7"/>
       <c r="F195" s="7"/>
-      <c r="G195" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H195" s="4">
-        <v>5500.0</v>
-      </c>
-      <c r="I195" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J195" s="4">
-        <v>10000.0</v>
-      </c>
+      <c r="G195" s="7"/>
+      <c r="H195" s="7"/>
+      <c r="I195" s="7"/>
+      <c r="J195" s="7"/>
     </row>
     <row r="196">
       <c r="A196" s="4">
@@ -5995,17 +5990,25 @@
         <v>208</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D196" s="4">
-        <v>10000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E196" s="7"/>
       <c r="F196" s="7"/>
-      <c r="G196" s="7"/>
-      <c r="H196" s="7"/>
-      <c r="I196" s="7"/>
-      <c r="J196" s="7"/>
+      <c r="G196" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H196" s="4">
+        <v>5500.0</v>
+      </c>
+      <c r="I196" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J196" s="4">
+        <v>10000.0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="4">
@@ -6016,25 +6019,17 @@
         <v>209</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D197" s="4">
-        <v>2000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E197" s="7"/>
       <c r="F197" s="7"/>
-      <c r="G197" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H197" s="4">
-        <v>5500.0</v>
-      </c>
-      <c r="I197" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J197" s="4">
-        <v>10000.0</v>
-      </c>
+      <c r="G197" s="7"/>
+      <c r="H197" s="7"/>
+      <c r="I197" s="7"/>
+      <c r="J197" s="7"/>
     </row>
     <row r="198">
       <c r="A198" s="4">
@@ -6045,17 +6040,25 @@
         <v>210</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D198" s="4">
-        <v>10000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E198" s="7"/>
       <c r="F198" s="7"/>
-      <c r="G198" s="7"/>
-      <c r="H198" s="7"/>
-      <c r="I198" s="7"/>
-      <c r="J198" s="7"/>
+      <c r="G198" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H198" s="4">
+        <v>5500.0</v>
+      </c>
+      <c r="I198" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J198" s="4">
+        <v>10000.0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4">
@@ -6066,25 +6069,17 @@
         <v>211</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D199" s="4">
-        <v>2000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E199" s="7"/>
       <c r="F199" s="7"/>
-      <c r="G199" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H199" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="I199" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J199" s="4">
-        <v>11000.0</v>
-      </c>
+      <c r="G199" s="7"/>
+      <c r="H199" s="7"/>
+      <c r="I199" s="7"/>
+      <c r="J199" s="7"/>
     </row>
     <row r="200">
       <c r="A200" s="4">
@@ -6095,17 +6090,25 @@
         <v>212</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D200" s="4">
-        <v>11000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E200" s="7"/>
       <c r="F200" s="7"/>
-      <c r="G200" s="7"/>
-      <c r="H200" s="7"/>
-      <c r="I200" s="7"/>
-      <c r="J200" s="7"/>
+      <c r="G200" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H200" s="4">
+        <v>6000.0</v>
+      </c>
+      <c r="I200" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J200" s="4">
+        <v>11000.0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="4">
@@ -6116,25 +6119,17 @@
         <v>213</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D201" s="4">
-        <v>2000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="E201" s="7"/>
       <c r="F201" s="7"/>
-      <c r="G201" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H201" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="I201" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J201" s="4">
-        <v>11000.0</v>
-      </c>
+      <c r="G201" s="7"/>
+      <c r="H201" s="7"/>
+      <c r="I201" s="7"/>
+      <c r="J201" s="7"/>
     </row>
     <row r="202">
       <c r="A202" s="4">
@@ -6145,17 +6140,25 @@
         <v>214</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D202" s="4">
-        <v>11000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E202" s="7"/>
       <c r="F202" s="7"/>
-      <c r="G202" s="7"/>
-      <c r="H202" s="7"/>
-      <c r="I202" s="7"/>
-      <c r="J202" s="7"/>
+      <c r="G202" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H202" s="4">
+        <v>6000.0</v>
+      </c>
+      <c r="I202" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J202" s="4">
+        <v>11000.0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4">
@@ -6166,25 +6169,17 @@
         <v>215</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D203" s="4">
-        <v>2000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="E203" s="7"/>
       <c r="F203" s="7"/>
-      <c r="G203" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H203" s="4">
-        <v>8000.0</v>
-      </c>
-      <c r="I203" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J203" s="4">
-        <v>15000.0</v>
-      </c>
+      <c r="G203" s="7"/>
+      <c r="H203" s="7"/>
+      <c r="I203" s="7"/>
+      <c r="J203" s="7"/>
     </row>
     <row r="204">
       <c r="A204" s="4">
@@ -6195,17 +6190,25 @@
         <v>216</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D204" s="4">
-        <v>15000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E204" s="7"/>
       <c r="F204" s="7"/>
-      <c r="G204" s="7"/>
-      <c r="H204" s="7"/>
-      <c r="I204" s="7"/>
-      <c r="J204" s="7"/>
+      <c r="G204" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H204" s="4">
+        <v>8000.0</v>
+      </c>
+      <c r="I204" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J204" s="4">
+        <v>15000.0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="4">
@@ -6216,7 +6219,7 @@
         <v>217</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D205" s="4">
         <v>15000.0</v>
@@ -6237,29 +6240,17 @@
         <v>218</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D206" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E206" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F206" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="G206" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H206" s="4">
-        <v>8500.0</v>
-      </c>
-      <c r="I206" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J206" s="4">
-        <v>16000.0</v>
-      </c>
+        <v>15000.0</v>
+      </c>
+      <c r="E206" s="7"/>
+      <c r="F206" s="7"/>
+      <c r="G206" s="7"/>
+      <c r="H206" s="7"/>
+      <c r="I206" s="7"/>
+      <c r="J206" s="7"/>
     </row>
     <row r="207">
       <c r="A207" s="4">
@@ -6270,17 +6261,29 @@
         <v>219</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D207" s="4">
+        <v>2000.0</v>
+      </c>
+      <c r="E207" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F207" s="4">
+        <v>5000.0</v>
+      </c>
+      <c r="G207" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H207" s="4">
+        <v>8500.0</v>
+      </c>
+      <c r="I207" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J207" s="4">
         <v>16000.0</v>
       </c>
-      <c r="E207" s="7"/>
-      <c r="F207" s="7"/>
-      <c r="G207" s="7"/>
-      <c r="H207" s="7"/>
-      <c r="I207" s="7"/>
-      <c r="J207" s="7"/>
     </row>
     <row r="208">
       <c r="A208" s="4">
@@ -6291,25 +6294,17 @@
         <v>220</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D208" s="4">
-        <v>2000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E208" s="7"/>
       <c r="F208" s="7"/>
-      <c r="G208" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H208" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="I208" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J208" s="4">
-        <v>17000.0</v>
-      </c>
+      <c r="G208" s="7"/>
+      <c r="H208" s="7"/>
+      <c r="I208" s="7"/>
+      <c r="J208" s="7"/>
     </row>
     <row r="209">
       <c r="A209" s="4">
@@ -6320,17 +6315,25 @@
         <v>221</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D209" s="4">
-        <v>17000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E209" s="7"/>
       <c r="F209" s="7"/>
-      <c r="G209" s="7"/>
-      <c r="H209" s="7"/>
-      <c r="I209" s="7"/>
-      <c r="J209" s="7"/>
+      <c r="G209" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H209" s="4">
+        <v>9000.0</v>
+      </c>
+      <c r="I209" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J209" s="4">
+        <v>17000.0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="4">
@@ -6341,25 +6344,17 @@
         <v>222</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D210" s="4">
-        <v>2000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E210" s="7"/>
       <c r="F210" s="7"/>
-      <c r="G210" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H210" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="I210" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J210" s="4">
-        <v>17000.0</v>
-      </c>
+      <c r="G210" s="7"/>
+      <c r="H210" s="7"/>
+      <c r="I210" s="7"/>
+      <c r="J210" s="7"/>
     </row>
     <row r="211">
       <c r="A211" s="4">
@@ -6370,17 +6365,25 @@
         <v>223</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D211" s="4">
-        <v>17000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E211" s="7"/>
       <c r="F211" s="7"/>
-      <c r="G211" s="7"/>
-      <c r="H211" s="7"/>
-      <c r="I211" s="7"/>
-      <c r="J211" s="7"/>
+      <c r="G211" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H211" s="4">
+        <v>9000.0</v>
+      </c>
+      <c r="I211" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J211" s="4">
+        <v>17000.0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="4">
@@ -6391,29 +6394,17 @@
         <v>224</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D212" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E212" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F212" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="G212" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H212" s="4">
-        <v>9500.0</v>
-      </c>
-      <c r="I212" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J212" s="4">
-        <v>18000.0</v>
-      </c>
+        <v>17000.0</v>
+      </c>
+      <c r="E212" s="7"/>
+      <c r="F212" s="7"/>
+      <c r="G212" s="7"/>
+      <c r="H212" s="7"/>
+      <c r="I212" s="7"/>
+      <c r="J212" s="7"/>
     </row>
     <row r="213">
       <c r="A213" s="4">
@@ -6424,17 +6415,29 @@
         <v>225</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D213" s="4">
+        <v>2000.0</v>
+      </c>
+      <c r="E213" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F213" s="4">
+        <v>5000.0</v>
+      </c>
+      <c r="G213" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H213" s="4">
+        <v>9500.0</v>
+      </c>
+      <c r="I213" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J213" s="4">
         <v>18000.0</v>
       </c>
-      <c r="E213" s="7"/>
-      <c r="F213" s="7"/>
-      <c r="G213" s="7"/>
-      <c r="H213" s="7"/>
-      <c r="I213" s="7"/>
-      <c r="J213" s="7"/>
     </row>
     <row r="214">
       <c r="A214" s="4">
@@ -6445,25 +6448,17 @@
         <v>226</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D214" s="4">
-        <v>2500.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E214" s="7"/>
       <c r="F214" s="7"/>
-      <c r="G214" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H214" s="4">
-        <v>14500.0</v>
-      </c>
-      <c r="I214" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J214" s="4">
-        <v>28000.0</v>
-      </c>
+      <c r="G214" s="7"/>
+      <c r="H214" s="7"/>
+      <c r="I214" s="7"/>
+      <c r="J214" s="7"/>
     </row>
     <row r="215">
       <c r="A215" s="4">
@@ -6474,17 +6469,25 @@
         <v>227</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D215" s="4">
-        <v>28000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E215" s="7"/>
       <c r="F215" s="7"/>
-      <c r="G215" s="7"/>
-      <c r="H215" s="7"/>
-      <c r="I215" s="7"/>
-      <c r="J215" s="7"/>
+      <c r="G215" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H215" s="4">
+        <v>14500.0</v>
+      </c>
+      <c r="I215" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J215" s="4">
+        <v>28000.0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="4">
@@ -6495,25 +6498,17 @@
         <v>228</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D216" s="4">
-        <v>2500.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E216" s="7"/>
       <c r="F216" s="7"/>
-      <c r="G216" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H216" s="4">
-        <v>10500.0</v>
-      </c>
-      <c r="I216" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J216" s="4">
-        <v>20000.0</v>
-      </c>
+      <c r="G216" s="7"/>
+      <c r="H216" s="7"/>
+      <c r="I216" s="7"/>
+      <c r="J216" s="7"/>
     </row>
     <row r="217">
       <c r="A217" s="4">
@@ -6524,17 +6519,25 @@
         <v>229</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D217" s="4">
-        <v>20000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E217" s="7"/>
       <c r="F217" s="7"/>
-      <c r="G217" s="7"/>
-      <c r="H217" s="7"/>
-      <c r="I217" s="7"/>
-      <c r="J217" s="7"/>
+      <c r="G217" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H217" s="4">
+        <v>10500.0</v>
+      </c>
+      <c r="I217" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J217" s="4">
+        <v>20000.0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="4">
@@ -6545,25 +6548,17 @@
         <v>230</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D218" s="4">
-        <v>2500.0</v>
+        <v>20000.0</v>
       </c>
       <c r="E218" s="7"/>
       <c r="F218" s="7"/>
-      <c r="G218" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H218" s="4">
-        <v>13000.0</v>
-      </c>
-      <c r="I218" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J218" s="4">
-        <v>25000.0</v>
-      </c>
+      <c r="G218" s="7"/>
+      <c r="H218" s="7"/>
+      <c r="I218" s="7"/>
+      <c r="J218" s="7"/>
     </row>
     <row r="219">
       <c r="A219" s="4">
@@ -6574,17 +6569,25 @@
         <v>231</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D219" s="4">
-        <v>25000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E219" s="7"/>
       <c r="F219" s="7"/>
-      <c r="G219" s="7"/>
-      <c r="H219" s="7"/>
-      <c r="I219" s="7"/>
-      <c r="J219" s="7"/>
+      <c r="G219" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H219" s="4">
+        <v>13000.0</v>
+      </c>
+      <c r="I219" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J219" s="4">
+        <v>25000.0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="4">
@@ -6595,25 +6598,17 @@
         <v>232</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D220" s="4">
-        <v>2500.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E220" s="7"/>
       <c r="F220" s="7"/>
-      <c r="G220" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H220" s="4">
-        <v>11000.0</v>
-      </c>
-      <c r="I220" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J220" s="4">
-        <v>21000.0</v>
-      </c>
+      <c r="G220" s="7"/>
+      <c r="H220" s="7"/>
+      <c r="I220" s="7"/>
+      <c r="J220" s="7"/>
     </row>
     <row r="221">
       <c r="A221" s="4">
@@ -6624,17 +6619,25 @@
         <v>233</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D221" s="4">
-        <v>21000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E221" s="7"/>
       <c r="F221" s="7"/>
-      <c r="G221" s="7"/>
-      <c r="H221" s="7"/>
-      <c r="I221" s="7"/>
-      <c r="J221" s="7"/>
+      <c r="G221" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H221" s="4">
+        <v>11000.0</v>
+      </c>
+      <c r="I221" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J221" s="4">
+        <v>21000.0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="4">
@@ -6645,25 +6648,17 @@
         <v>234</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D222" s="4">
-        <v>2500.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E222" s="7"/>
       <c r="F222" s="7"/>
-      <c r="G222" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H222" s="4">
-        <v>13000.0</v>
-      </c>
-      <c r="I222" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J222" s="4">
-        <v>25000.0</v>
-      </c>
+      <c r="G222" s="7"/>
+      <c r="H222" s="7"/>
+      <c r="I222" s="7"/>
+      <c r="J222" s="7"/>
     </row>
     <row r="223">
       <c r="A223" s="4">
@@ -6674,17 +6669,25 @@
         <v>235</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D223" s="4">
-        <v>25000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E223" s="7"/>
       <c r="F223" s="7"/>
-      <c r="G223" s="7"/>
-      <c r="H223" s="7"/>
-      <c r="I223" s="7"/>
-      <c r="J223" s="7"/>
+      <c r="G223" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H223" s="4">
+        <v>13000.0</v>
+      </c>
+      <c r="I223" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J223" s="4">
+        <v>25000.0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="4">
@@ -6695,25 +6698,17 @@
         <v>236</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D224" s="4">
-        <v>2500.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E224" s="7"/>
       <c r="F224" s="7"/>
-      <c r="G224" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H224" s="4">
-        <v>14000.0</v>
-      </c>
-      <c r="I224" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J224" s="4">
-        <v>28000.0</v>
-      </c>
+      <c r="G224" s="7"/>
+      <c r="H224" s="7"/>
+      <c r="I224" s="7"/>
+      <c r="J224" s="7"/>
     </row>
     <row r="225">
       <c r="A225" s="4">
@@ -6724,17 +6719,25 @@
         <v>237</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D225" s="4">
-        <v>28000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E225" s="7"/>
       <c r="F225" s="7"/>
-      <c r="G225" s="7"/>
-      <c r="H225" s="7"/>
-      <c r="I225" s="7"/>
-      <c r="J225" s="7"/>
+      <c r="G225" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H225" s="4">
+        <v>14000.0</v>
+      </c>
+      <c r="I225" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J225" s="4">
+        <v>28000.0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="4">
@@ -6745,25 +6748,17 @@
         <v>238</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D226" s="4">
-        <v>2500.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E226" s="7"/>
       <c r="F226" s="7"/>
-      <c r="G226" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H226" s="4">
-        <v>13000.0</v>
-      </c>
-      <c r="I226" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J226" s="4">
-        <v>25000.0</v>
-      </c>
+      <c r="G226" s="7"/>
+      <c r="H226" s="7"/>
+      <c r="I226" s="7"/>
+      <c r="J226" s="7"/>
     </row>
     <row r="227">
       <c r="A227" s="4">
@@ -6774,17 +6769,25 @@
         <v>239</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D227" s="4">
-        <v>25000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E227" s="7"/>
       <c r="F227" s="7"/>
-      <c r="G227" s="7"/>
-      <c r="H227" s="7"/>
-      <c r="I227" s="7"/>
-      <c r="J227" s="7"/>
+      <c r="G227" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H227" s="4">
+        <v>13000.0</v>
+      </c>
+      <c r="I227" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J227" s="4">
+        <v>25000.0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="4">
@@ -6795,25 +6798,17 @@
         <v>240</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D228" s="4">
-        <v>2500.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E228" s="7"/>
       <c r="F228" s="7"/>
-      <c r="G228" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H228" s="4">
-        <v>14000.0</v>
-      </c>
-      <c r="I228" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J228" s="4">
-        <v>27000.0</v>
-      </c>
+      <c r="G228" s="7"/>
+      <c r="H228" s="7"/>
+      <c r="I228" s="7"/>
+      <c r="J228" s="7"/>
     </row>
     <row r="229">
       <c r="A229" s="4">
@@ -6824,17 +6819,25 @@
         <v>241</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D229" s="4">
-        <v>27000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E229" s="7"/>
       <c r="F229" s="7"/>
-      <c r="G229" s="7"/>
-      <c r="H229" s="7"/>
-      <c r="I229" s="7"/>
-      <c r="J229" s="7"/>
+      <c r="G229" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H229" s="4">
+        <v>14000.0</v>
+      </c>
+      <c r="I229" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J229" s="4">
+        <v>27000.0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="4">
@@ -6845,25 +6848,17 @@
         <v>242</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D230" s="4">
-        <v>2500.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E230" s="7"/>
       <c r="F230" s="7"/>
-      <c r="G230" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H230" s="4">
-        <v>14000.0</v>
-      </c>
-      <c r="I230" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J230" s="4">
-        <v>27000.0</v>
-      </c>
+      <c r="G230" s="7"/>
+      <c r="H230" s="7"/>
+      <c r="I230" s="7"/>
+      <c r="J230" s="7"/>
     </row>
     <row r="231">
       <c r="A231" s="4">
@@ -6874,17 +6869,25 @@
         <v>243</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D231" s="4">
-        <v>27000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E231" s="7"/>
       <c r="F231" s="7"/>
-      <c r="G231" s="7"/>
-      <c r="H231" s="7"/>
-      <c r="I231" s="7"/>
-      <c r="J231" s="7"/>
+      <c r="G231" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H231" s="4">
+        <v>14000.0</v>
+      </c>
+      <c r="I231" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J231" s="4">
+        <v>27000.0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="4">
@@ -6895,10 +6898,10 @@
         <v>244</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D232" s="4">
-        <v>34000.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E232" s="7"/>
       <c r="F232" s="7"/>
@@ -6916,10 +6919,10 @@
         <v>245</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D233" s="4">
-        <v>27000.0</v>
+        <v>34000.0</v>
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="7"/>
@@ -6937,19 +6940,17 @@
         <v>246</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D234" s="4">
-        <v>37000.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E234" s="7"/>
       <c r="F234" s="7"/>
-      <c r="G234" s="4"/>
-      <c r="H234" s="4"/>
-      <c r="I234" s="4"/>
-      <c r="J234" s="4">
-        <v>37000.0</v>
-      </c>
+      <c r="G234" s="7"/>
+      <c r="H234" s="7"/>
+      <c r="I234" s="7"/>
+      <c r="J234" s="7"/>
     </row>
     <row r="235">
       <c r="A235" s="4">
@@ -6960,17 +6961,19 @@
         <v>247</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D235" s="4">
-        <v>16000.0</v>
+        <v>37000.0</v>
       </c>
       <c r="E235" s="7"/>
       <c r="F235" s="7"/>
-      <c r="G235" s="7"/>
-      <c r="H235" s="7"/>
-      <c r="I235" s="7"/>
-      <c r="J235" s="7"/>
+      <c r="G235" s="4"/>
+      <c r="H235" s="4"/>
+      <c r="I235" s="4"/>
+      <c r="J235" s="4">
+        <v>37000.0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="4">
@@ -6981,10 +6984,10 @@
         <v>248</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D236" s="4">
-        <v>43000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E236" s="7"/>
       <c r="F236" s="7"/>
@@ -7002,10 +7005,10 @@
         <v>249</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D237" s="4">
-        <v>23000.0</v>
+        <v>43000.0</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="7"/>
@@ -7023,10 +7026,10 @@
         <v>250</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D238" s="4">
-        <v>17000.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E238" s="7"/>
       <c r="F238" s="7"/>
@@ -7044,10 +7047,10 @@
         <v>251</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D239" s="4">
-        <v>29000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E239" s="7"/>
       <c r="F239" s="7"/>
@@ -7065,10 +7068,10 @@
         <v>252</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D240" s="4">
-        <v>13000.0</v>
+        <v>29000.0</v>
       </c>
       <c r="E240" s="7"/>
       <c r="F240" s="7"/>
@@ -7086,10 +7089,10 @@
         <v>253</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D241" s="4">
-        <v>39000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="E241" s="7"/>
       <c r="F241" s="7"/>
@@ -7107,10 +7110,10 @@
         <v>254</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D242" s="4">
-        <v>382000.0</v>
+        <v>39000.0</v>
       </c>
       <c r="E242" s="7"/>
       <c r="F242" s="7"/>
@@ -7128,10 +7131,10 @@
         <v>255</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>256</v>
+        <v>206</v>
       </c>
       <c r="D243" s="4">
-        <v>500.0</v>
+        <v>382000.0</v>
       </c>
       <c r="E243" s="7"/>
       <c r="F243" s="7"/>
@@ -7146,13 +7149,13 @@
         <v>243</v>
       </c>
       <c r="B244" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C244" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="C244" s="5" t="s">
-        <v>256</v>
-      </c>
       <c r="D244" s="4">
-        <v>4000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E244" s="7"/>
       <c r="F244" s="7"/>
@@ -7170,17 +7173,13 @@
         <v>258</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D245" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E245" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F245" s="4">
-        <v>10000.0</v>
-      </c>
+        <v>4000.0</v>
+      </c>
+      <c r="E245" s="7"/>
+      <c r="F245" s="7"/>
       <c r="G245" s="7"/>
       <c r="H245" s="7"/>
       <c r="I245" s="7"/>
@@ -7195,16 +7194,16 @@
         <v>259</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D246" s="4">
-        <v>3000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E246" s="4">
         <v>5.0</v>
       </c>
       <c r="F246" s="4">
-        <v>14000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="G246" s="7"/>
       <c r="H246" s="7"/>
@@ -7217,16 +7216,20 @@
         <v>246</v>
       </c>
       <c r="B247" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C247" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C247" s="5" t="s">
-        <v>260</v>
-      </c>
       <c r="D247" s="4">
-        <v>109000.0</v>
-      </c>
-      <c r="E247" s="7"/>
-      <c r="F247" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E247" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F247" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G247" s="7"/>
       <c r="H247" s="7"/>
       <c r="I247" s="7"/>
@@ -7241,17 +7244,13 @@
         <v>262</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D248" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E248" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F248" s="4">
-        <v>14000.0</v>
-      </c>
+        <v>109000.0</v>
+      </c>
+      <c r="E248" s="7"/>
+      <c r="F248" s="7"/>
       <c r="G248" s="7"/>
       <c r="H248" s="7"/>
       <c r="I248" s="7"/>
@@ -7266,13 +7265,17 @@
         <v>263</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D249" s="4">
-        <v>109000.0</v>
-      </c>
-      <c r="E249" s="7"/>
-      <c r="F249" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E249" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F249" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G249" s="7"/>
       <c r="H249" s="7"/>
       <c r="I249" s="7"/>
@@ -7287,10 +7290,10 @@
         <v>264</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D250" s="4">
-        <v>3000.0</v>
+        <v>109000.0</v>
       </c>
       <c r="E250" s="7"/>
       <c r="F250" s="7"/>
@@ -7308,10 +7311,10 @@
         <v>265</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D251" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E251" s="7"/>
       <c r="F251" s="7"/>
@@ -7329,10 +7332,10 @@
         <v>266</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D252" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E252" s="7"/>
       <c r="F252" s="7"/>
@@ -7350,17 +7353,13 @@
         <v>267</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D253" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E253" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F253" s="4">
-        <v>39000.0</v>
-      </c>
+        <v>3000.0</v>
+      </c>
+      <c r="E253" s="7"/>
+      <c r="F253" s="7"/>
       <c r="G253" s="7"/>
       <c r="H253" s="7"/>
       <c r="I253" s="7"/>
@@ -7375,13 +7374,17 @@
         <v>268</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D254" s="4">
-        <v>114000.0</v>
-      </c>
-      <c r="E254" s="7"/>
-      <c r="F254" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E254" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F254" s="4">
+        <v>39000.0</v>
+      </c>
       <c r="G254" s="7"/>
       <c r="H254" s="7"/>
       <c r="I254" s="7"/>
@@ -7396,10 +7399,10 @@
         <v>269</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D255" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E255" s="7"/>
       <c r="F255" s="7"/>
@@ -7417,10 +7420,10 @@
         <v>270</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D256" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E256" s="7"/>
       <c r="F256" s="7"/>
@@ -7438,10 +7441,10 @@
         <v>271</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D257" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E257" s="7"/>
       <c r="F257" s="7"/>
@@ -7459,10 +7462,10 @@
         <v>272</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D258" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E258" s="7"/>
       <c r="F258" s="7"/>
@@ -7480,10 +7483,10 @@
         <v>273</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D259" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E259" s="7"/>
       <c r="F259" s="7"/>
@@ -7501,10 +7504,10 @@
         <v>274</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D260" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E260" s="7"/>
       <c r="F260" s="7"/>
@@ -7522,10 +7525,10 @@
         <v>275</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D261" s="4">
-        <v>3000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E261" s="7"/>
       <c r="F261" s="7"/>
@@ -7543,10 +7546,10 @@
         <v>276</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D262" s="4">
-        <v>107000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E262" s="7"/>
       <c r="F262" s="7"/>
@@ -7564,10 +7567,10 @@
         <v>277</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D263" s="4">
-        <v>3000.0</v>
+        <v>107000.0</v>
       </c>
       <c r="E263" s="7"/>
       <c r="F263" s="7"/>
@@ -7585,17 +7588,17 @@
         <v>278</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D264" s="4">
-        <v>112000.0</v>
-      </c>
-      <c r="E264" s="6"/>
-      <c r="F264" s="6"/>
-      <c r="G264" s="6"/>
-      <c r="H264" s="6"/>
-      <c r="I264" s="6"/>
-      <c r="J264" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E264" s="7"/>
+      <c r="F264" s="7"/>
+      <c r="G264" s="7"/>
+      <c r="H264" s="7"/>
+      <c r="I264" s="7"/>
+      <c r="J264" s="7"/>
     </row>
     <row r="265">
       <c r="A265" s="4">
@@ -7606,21 +7609,17 @@
         <v>279</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D265" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E265" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F265" s="4">
-        <v>19000.0</v>
-      </c>
-      <c r="G265" s="7"/>
-      <c r="H265" s="7"/>
-      <c r="I265" s="7"/>
-      <c r="J265" s="7"/>
+        <v>112000.0</v>
+      </c>
+      <c r="E265" s="6"/>
+      <c r="F265" s="6"/>
+      <c r="G265" s="6"/>
+      <c r="H265" s="6"/>
+      <c r="I265" s="6"/>
+      <c r="J265" s="6"/>
     </row>
     <row r="266">
       <c r="A266" s="4">
@@ -7631,7 +7630,7 @@
         <v>280</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D266" s="4">
         <v>4000.0</v>
@@ -7656,13 +7655,17 @@
         <v>281</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D267" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E267" s="4"/>
-      <c r="F267" s="4"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E267" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F267" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G267" s="7"/>
       <c r="H267" s="7"/>
       <c r="I267" s="7"/>
@@ -7677,10 +7680,10 @@
         <v>282</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D268" s="4">
-        <v>4000.0</v>
+        <v>86000.0</v>
       </c>
       <c r="E268" s="4"/>
       <c r="F268" s="4"/>
@@ -7698,10 +7701,10 @@
         <v>283</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D269" s="4">
-        <v>86000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E269" s="4"/>
       <c r="F269" s="4"/>
@@ -7719,18 +7722,14 @@
         <v>284</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D270" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E270" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F270" s="4">
-        <v>19500.0</v>
-      </c>
-      <c r="G270" s="4"/>
+        <v>86000.0</v>
+      </c>
+      <c r="E270" s="4"/>
+      <c r="F270" s="4"/>
+      <c r="G270" s="7"/>
       <c r="H270" s="7"/>
       <c r="I270" s="7"/>
       <c r="J270" s="7"/>
@@ -7744,18 +7743,18 @@
         <v>285</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D271" s="4">
-        <v>2000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E271" s="4">
         <v>5.0</v>
       </c>
       <c r="F271" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="G271" s="7"/>
+        <v>19500.0</v>
+      </c>
+      <c r="G271" s="4"/>
       <c r="H271" s="7"/>
       <c r="I271" s="7"/>
       <c r="J271" s="7"/>
@@ -7769,13 +7768,17 @@
         <v>286</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D272" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E272" s="7"/>
-      <c r="F272" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E272" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F272" s="4">
+        <v>6000.0</v>
+      </c>
       <c r="G272" s="7"/>
       <c r="H272" s="7"/>
       <c r="I272" s="7"/>
@@ -7790,10 +7793,10 @@
         <v>287</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D273" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E273" s="7"/>
       <c r="F273" s="7"/>
@@ -7811,10 +7814,10 @@
         <v>288</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D274" s="4">
-        <v>89000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E274" s="7"/>
       <c r="F274" s="7"/>
@@ -7832,10 +7835,10 @@
         <v>289</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D275" s="4">
-        <v>7500.0</v>
+        <v>89000.0</v>
       </c>
       <c r="E275" s="7"/>
       <c r="F275" s="7"/>
@@ -7853,10 +7856,10 @@
         <v>290</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D276" s="4">
-        <v>5000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E276" s="7"/>
       <c r="F276" s="7"/>
@@ -7874,10 +7877,10 @@
         <v>291</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D277" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E277" s="7"/>
       <c r="F277" s="7"/>
@@ -7895,17 +7898,17 @@
         <v>292</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="D278" s="4">
-        <v>80000.0</v>
-      </c>
-      <c r="E278" s="6"/>
-      <c r="F278" s="6"/>
-      <c r="G278" s="6"/>
-      <c r="H278" s="6"/>
-      <c r="I278" s="6"/>
-      <c r="J278" s="6"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E278" s="7"/>
+      <c r="F278" s="7"/>
+      <c r="G278" s="7"/>
+      <c r="H278" s="7"/>
+      <c r="I278" s="7"/>
+      <c r="J278" s="7"/>
     </row>
     <row r="279">
       <c r="A279" s="4">
@@ -7916,17 +7919,17 @@
         <v>293</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D279" s="4">
-        <v>14000.0</v>
-      </c>
-      <c r="E279" s="7"/>
-      <c r="F279" s="7"/>
-      <c r="G279" s="7"/>
-      <c r="H279" s="7"/>
-      <c r="I279" s="7"/>
-      <c r="J279" s="7"/>
+        <v>80000.0</v>
+      </c>
+      <c r="E279" s="6"/>
+      <c r="F279" s="6"/>
+      <c r="G279" s="6"/>
+      <c r="H279" s="6"/>
+      <c r="I279" s="6"/>
+      <c r="J279" s="6"/>
     </row>
     <row r="280">
       <c r="A280" s="4">
@@ -7934,13 +7937,13 @@
         <v>279</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D280" s="4">
-        <v>14500.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E280" s="7"/>
       <c r="F280" s="7"/>
@@ -7955,13 +7958,13 @@
         <v>280</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D281" s="4">
-        <v>15000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E281" s="7"/>
       <c r="F281" s="7"/>
@@ -7976,13 +7979,13 @@
         <v>281</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D282" s="4">
-        <v>15500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E282" s="7"/>
       <c r="F282" s="7"/>
@@ -8000,10 +8003,10 @@
         <v>294</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D283" s="4">
-        <v>1500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E283" s="7"/>
       <c r="F283" s="7"/>
@@ -8018,13 +8021,13 @@
         <v>283</v>
       </c>
       <c r="B284" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C284" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="C284" s="5" t="s">
-        <v>295</v>
-      </c>
       <c r="D284" s="4">
-        <v>12500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E284" s="7"/>
       <c r="F284" s="7"/>
@@ -8042,10 +8045,10 @@
         <v>297</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D285" s="4">
-        <v>500.0</v>
+        <v>12500.0</v>
       </c>
       <c r="E285" s="7"/>
       <c r="F285" s="7"/>
@@ -8063,10 +8066,10 @@
         <v>298</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D286" s="4">
-        <v>4500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E286" s="7"/>
       <c r="F286" s="7"/>
@@ -8084,10 +8087,10 @@
         <v>299</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D287" s="4">
-        <v>3000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E287" s="7"/>
       <c r="F287" s="7"/>
@@ -8105,10 +8108,10 @@
         <v>300</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D288" s="4">
-        <v>23000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E288" s="7"/>
       <c r="F288" s="7"/>
@@ -8126,17 +8129,13 @@
         <v>301</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D289" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E289" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F289" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>23000.0</v>
+      </c>
+      <c r="E289" s="7"/>
+      <c r="F289" s="7"/>
       <c r="G289" s="7"/>
       <c r="H289" s="7"/>
       <c r="I289" s="7"/>
@@ -8151,13 +8150,17 @@
         <v>302</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D290" s="4">
+        <v>2000.0</v>
+      </c>
+      <c r="E290" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F290" s="4">
         <v>7500.0</v>
       </c>
-      <c r="E290" s="4"/>
-      <c r="F290" s="4"/>
       <c r="G290" s="7"/>
       <c r="H290" s="7"/>
       <c r="I290" s="7"/>
@@ -8172,17 +8175,13 @@
         <v>303</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D291" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E291" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F291" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>7500.0</v>
+      </c>
+      <c r="E291" s="4"/>
+      <c r="F291" s="4"/>
       <c r="G291" s="7"/>
       <c r="H291" s="7"/>
       <c r="I291" s="7"/>
@@ -8197,13 +8196,17 @@
         <v>304</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D292" s="4">
+        <v>2500.0</v>
+      </c>
+      <c r="E292" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F292" s="4">
         <v>9000.0</v>
       </c>
-      <c r="E292" s="4"/>
-      <c r="F292" s="4"/>
       <c r="G292" s="7"/>
       <c r="H292" s="7"/>
       <c r="I292" s="7"/>
@@ -8218,17 +8221,13 @@
         <v>305</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D293" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E293" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F293" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>9000.0</v>
+      </c>
+      <c r="E293" s="4"/>
+      <c r="F293" s="4"/>
       <c r="G293" s="7"/>
       <c r="H293" s="7"/>
       <c r="I293" s="7"/>
@@ -8243,13 +8242,17 @@
         <v>306</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D294" s="4">
+        <v>2000.0</v>
+      </c>
+      <c r="E294" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F294" s="4">
         <v>7500.0</v>
       </c>
-      <c r="E294" s="7"/>
-      <c r="F294" s="7"/>
       <c r="G294" s="7"/>
       <c r="H294" s="7"/>
       <c r="I294" s="7"/>
@@ -8264,10 +8267,10 @@
         <v>307</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="D295" s="4">
-        <v>1000.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E295" s="7"/>
       <c r="F295" s="7"/>
@@ -8282,13 +8285,13 @@
         <v>295</v>
       </c>
       <c r="B296" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C296" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="C296" s="5" t="s">
-        <v>308</v>
-      </c>
       <c r="D296" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E296" s="7"/>
       <c r="F296" s="7"/>
@@ -8306,10 +8309,10 @@
         <v>310</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D297" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E297" s="7"/>
       <c r="F297" s="7"/>
@@ -8327,10 +8330,10 @@
         <v>311</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D298" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E298" s="7"/>
       <c r="F298" s="7"/>
@@ -8348,10 +8351,10 @@
         <v>312</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D299" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E299" s="7"/>
       <c r="F299" s="7"/>
@@ -8369,10 +8372,10 @@
         <v>313</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D300" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E300" s="7"/>
       <c r="F300" s="7"/>
@@ -8390,10 +8393,10 @@
         <v>314</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D301" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E301" s="7"/>
       <c r="F301" s="7"/>
@@ -8411,10 +8414,10 @@
         <v>315</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D302" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E302" s="7"/>
       <c r="F302" s="7"/>
@@ -8432,10 +8435,10 @@
         <v>316</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D303" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E303" s="7"/>
       <c r="F303" s="7"/>
@@ -8453,10 +8456,10 @@
         <v>317</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D304" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E304" s="7"/>
       <c r="F304" s="7"/>
@@ -8474,10 +8477,10 @@
         <v>318</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D305" s="4">
-        <v>1000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E305" s="7"/>
       <c r="F305" s="7"/>
@@ -8495,10 +8498,10 @@
         <v>319</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D306" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E306" s="7"/>
       <c r="F306" s="7"/>
@@ -8516,7 +8519,7 @@
         <v>320</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D307" s="4">
         <v>10000.0</v>
@@ -8537,10 +8540,10 @@
         <v>321</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D308" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E308" s="7"/>
       <c r="F308" s="7"/>
@@ -8558,10 +8561,10 @@
         <v>322</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D309" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E309" s="7"/>
       <c r="F309" s="7"/>
@@ -8579,10 +8582,10 @@
         <v>323</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D310" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E310" s="7"/>
       <c r="F310" s="7"/>
@@ -8600,10 +8603,10 @@
         <v>324</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D311" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E311" s="7"/>
       <c r="F311" s="7"/>
@@ -8621,10 +8624,10 @@
         <v>325</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D312" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E312" s="7"/>
       <c r="F312" s="7"/>
@@ -8642,10 +8645,10 @@
         <v>326</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D313" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E313" s="7"/>
       <c r="F313" s="7"/>
@@ -8663,10 +8666,10 @@
         <v>327</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D314" s="4">
-        <v>2000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E314" s="7"/>
       <c r="F314" s="7"/>
@@ -8684,10 +8687,10 @@
         <v>328</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D315" s="4">
-        <v>5000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E315" s="7"/>
       <c r="F315" s="7"/>
@@ -8705,10 +8708,10 @@
         <v>329</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D316" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E316" s="7"/>
       <c r="F316" s="7"/>
@@ -8726,10 +8729,10 @@
         <v>330</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D317" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E317" s="7"/>
       <c r="F317" s="7"/>
@@ -8747,10 +8750,10 @@
         <v>331</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D318" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E318" s="7"/>
       <c r="F318" s="7"/>
@@ -8768,10 +8771,10 @@
         <v>332</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D319" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E319" s="7"/>
       <c r="F319" s="7"/>
@@ -8789,10 +8792,10 @@
         <v>333</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D320" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E320" s="7"/>
       <c r="F320" s="7"/>
@@ -8810,10 +8813,10 @@
         <v>334</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D321" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E321" s="7"/>
       <c r="F321" s="7"/>
@@ -8831,10 +8834,10 @@
         <v>335</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D322" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E322" s="7"/>
       <c r="F322" s="7"/>
@@ -8852,7 +8855,7 @@
         <v>336</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D323" s="4">
         <v>500.0</v>
@@ -8873,10 +8876,10 @@
         <v>337</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D324" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E324" s="7"/>
       <c r="F324" s="7"/>
@@ -8894,7 +8897,7 @@
         <v>338</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D325" s="4">
         <v>5000.0</v>
@@ -8915,10 +8918,10 @@
         <v>339</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D326" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E326" s="7"/>
       <c r="F326" s="7"/>
@@ -8936,10 +8939,10 @@
         <v>340</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D327" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E327" s="7"/>
       <c r="F327" s="7"/>
@@ -8957,10 +8960,10 @@
         <v>341</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D328" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E328" s="7"/>
       <c r="F328" s="7"/>
@@ -8978,10 +8981,10 @@
         <v>342</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D329" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E329" s="7"/>
       <c r="F329" s="7"/>
@@ -8999,10 +9002,10 @@
         <v>343</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D330" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E330" s="7"/>
       <c r="F330" s="7"/>
@@ -9020,10 +9023,10 @@
         <v>344</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D331" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E331" s="7"/>
       <c r="F331" s="7"/>
@@ -9041,17 +9044,13 @@
         <v>345</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D332" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E332" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F332" s="4">
-        <v>4500.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E332" s="7"/>
+      <c r="F332" s="7"/>
       <c r="G332" s="7"/>
       <c r="H332" s="7"/>
       <c r="I332" s="7"/>
@@ -9066,13 +9065,17 @@
         <v>346</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D333" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E333" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F333" s="4">
         <v>4500.0</v>
       </c>
-      <c r="E333" s="7"/>
-      <c r="F333" s="7"/>
       <c r="G333" s="7"/>
       <c r="H333" s="7"/>
       <c r="I333" s="7"/>
@@ -9087,13 +9090,13 @@
         <v>347</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D334" s="4">
-        <v>51000.0</v>
-      </c>
-      <c r="E334" s="4"/>
-      <c r="F334" s="4"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E334" s="7"/>
+      <c r="F334" s="7"/>
       <c r="G334" s="7"/>
       <c r="H334" s="7"/>
       <c r="I334" s="7"/>
@@ -9108,17 +9111,13 @@
         <v>348</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D335" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E335" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F335" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>51000.0</v>
+      </c>
+      <c r="E335" s="4"/>
+      <c r="F335" s="4"/>
       <c r="G335" s="7"/>
       <c r="H335" s="7"/>
       <c r="I335" s="7"/>
@@ -9133,13 +9132,17 @@
         <v>349</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D336" s="4">
-        <v>52000.0</v>
-      </c>
-      <c r="E336" s="7"/>
-      <c r="F336" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E336" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F336" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G336" s="7"/>
       <c r="H336" s="7"/>
       <c r="I336" s="7"/>
@@ -9154,10 +9157,10 @@
         <v>350</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D337" s="4">
-        <v>1000.0</v>
+        <v>52000.0</v>
       </c>
       <c r="E337" s="7"/>
       <c r="F337" s="7"/>
@@ -9175,10 +9178,10 @@
         <v>351</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D338" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E338" s="7"/>
       <c r="F338" s="7"/>
@@ -9196,17 +9199,13 @@
         <v>352</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D339" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E339" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F339" s="4">
-        <v>17000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E339" s="7"/>
+      <c r="F339" s="7"/>
       <c r="G339" s="7"/>
       <c r="H339" s="7"/>
       <c r="I339" s="7"/>
@@ -9221,13 +9220,17 @@
         <v>353</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D340" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E340" s="7"/>
-      <c r="F340" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E340" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F340" s="4">
+        <v>17000.0</v>
+      </c>
       <c r="G340" s="7"/>
       <c r="H340" s="7"/>
       <c r="I340" s="7"/>
@@ -9242,17 +9245,13 @@
         <v>354</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D341" s="4">
-        <v>7000.0</v>
-      </c>
-      <c r="E341" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F341" s="4">
-        <v>32500.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E341" s="7"/>
+      <c r="F341" s="7"/>
       <c r="G341" s="7"/>
       <c r="H341" s="7"/>
       <c r="I341" s="7"/>
@@ -9267,13 +9266,17 @@
         <v>355</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D342" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E342" s="7"/>
-      <c r="F342" s="7"/>
+        <v>7000.0</v>
+      </c>
+      <c r="E342" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F342" s="4">
+        <v>32500.0</v>
+      </c>
       <c r="G342" s="7"/>
       <c r="H342" s="7"/>
       <c r="I342" s="7"/>
@@ -9288,10 +9291,10 @@
         <v>356</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D343" s="4">
-        <v>9500.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E343" s="7"/>
       <c r="F343" s="7"/>
@@ -9309,10 +9312,10 @@
         <v>357</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D344" s="4">
-        <v>3500.0</v>
+        <v>9500.0</v>
       </c>
       <c r="E344" s="7"/>
       <c r="F344" s="7"/>
@@ -9330,10 +9333,10 @@
         <v>358</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D345" s="4">
-        <v>5000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E345" s="7"/>
       <c r="F345" s="7"/>
@@ -9351,17 +9354,13 @@
         <v>359</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D346" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E346" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F346" s="4">
-        <v>22500.0</v>
-      </c>
+      <c r="E346" s="7"/>
+      <c r="F346" s="7"/>
       <c r="G346" s="7"/>
       <c r="H346" s="7"/>
       <c r="I346" s="7"/>
@@ -9376,16 +9375,16 @@
         <v>360</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D347" s="4">
-        <v>3500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E347" s="4">
         <v>5.0</v>
       </c>
       <c r="F347" s="4">
-        <v>12500.0</v>
+        <v>22500.0</v>
       </c>
       <c r="G347" s="7"/>
       <c r="H347" s="7"/>
@@ -9401,13 +9400,17 @@
         <v>361</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D348" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E348" s="4"/>
-      <c r="F348" s="4"/>
+      <c r="E348" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F348" s="4">
+        <v>12500.0</v>
+      </c>
       <c r="G348" s="7"/>
       <c r="H348" s="7"/>
       <c r="I348" s="7"/>
@@ -9422,14 +9425,14 @@
         <v>362</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D349" s="4">
-        <v>3000.0</v>
+        <v>3500.0</v>
       </c>
       <c r="E349" s="4"/>
       <c r="F349" s="4"/>
-      <c r="G349" s="4"/>
+      <c r="G349" s="7"/>
       <c r="H349" s="7"/>
       <c r="I349" s="7"/>
       <c r="J349" s="7"/>
@@ -9443,18 +9446,14 @@
         <v>363</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D350" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E350" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F350" s="4">
-        <v>11500.0</v>
-      </c>
-      <c r="G350" s="7"/>
+      <c r="E350" s="4"/>
+      <c r="F350" s="4"/>
+      <c r="G350" s="4"/>
       <c r="H350" s="7"/>
       <c r="I350" s="7"/>
       <c r="J350" s="7"/>
@@ -9468,13 +9467,17 @@
         <v>364</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D351" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E351" s="7"/>
-      <c r="F351" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E351" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F351" s="4">
+        <v>11500.0</v>
+      </c>
       <c r="G351" s="7"/>
       <c r="H351" s="7"/>
       <c r="I351" s="7"/>
@@ -9489,17 +9492,13 @@
         <v>365</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D352" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E352" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F352" s="4">
-        <v>22500.0</v>
-      </c>
+        <v>4000.0</v>
+      </c>
+      <c r="E352" s="7"/>
+      <c r="F352" s="7"/>
       <c r="G352" s="7"/>
       <c r="H352" s="7"/>
       <c r="I352" s="7"/>
@@ -9514,13 +9513,17 @@
         <v>366</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D353" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E353" s="7"/>
-      <c r="F353" s="7"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E353" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F353" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G353" s="7"/>
       <c r="H353" s="7"/>
       <c r="I353" s="7"/>
@@ -9535,10 +9538,10 @@
         <v>367</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D354" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E354" s="7"/>
       <c r="F354" s="7"/>
@@ -9556,10 +9559,10 @@
         <v>368</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D355" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E355" s="7"/>
       <c r="F355" s="7"/>
@@ -9577,10 +9580,10 @@
         <v>369</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D356" s="4">
-        <v>14000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E356" s="7"/>
       <c r="F356" s="7"/>
@@ -9598,10 +9601,10 @@
         <v>370</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>371</v>
+        <v>309</v>
       </c>
       <c r="D357" s="4">
-        <v>1000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E357" s="7"/>
       <c r="F357" s="7"/>
@@ -9616,13 +9619,13 @@
         <v>357</v>
       </c>
       <c r="B358" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C358" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="C358" s="5" t="s">
-        <v>371</v>
-      </c>
       <c r="D358" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E358" s="7"/>
       <c r="F358" s="7"/>
@@ -9640,10 +9643,10 @@
         <v>373</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D359" s="4">
-        <v>1000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E359" s="7"/>
       <c r="F359" s="7"/>
@@ -9661,10 +9664,10 @@
         <v>374</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D360" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E360" s="7"/>
       <c r="F360" s="7"/>
@@ -9682,10 +9685,10 @@
         <v>375</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D361" s="4">
-        <v>1000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E361" s="7"/>
       <c r="F361" s="7"/>
@@ -9703,10 +9706,10 @@
         <v>376</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D362" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E362" s="7"/>
       <c r="F362" s="7"/>
@@ -9724,10 +9727,10 @@
         <v>377</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D363" s="4">
-        <v>4000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E363" s="7"/>
       <c r="F363" s="7"/>
@@ -9745,10 +9748,10 @@
         <v>378</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D364" s="4">
-        <v>2500.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E364" s="7"/>
       <c r="F364" s="7"/>
@@ -9766,10 +9769,10 @@
         <v>379</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D365" s="4">
-        <v>3000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E365" s="7"/>
       <c r="F365" s="7"/>
@@ -9787,10 +9790,10 @@
         <v>380</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D366" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E366" s="7"/>
       <c r="F366" s="7"/>
@@ -9808,10 +9811,10 @@
         <v>381</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D367" s="4">
-        <v>3000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E367" s="7"/>
       <c r="F367" s="7"/>
@@ -9829,17 +9832,13 @@
         <v>382</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D368" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E368" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F368" s="4">
         <v>3000.0</v>
       </c>
+      <c r="E368" s="7"/>
+      <c r="F368" s="7"/>
       <c r="G368" s="7"/>
       <c r="H368" s="7"/>
       <c r="I368" s="7"/>
@@ -9854,13 +9853,17 @@
         <v>383</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D369" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E369" s="7"/>
-      <c r="F369" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E369" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F369" s="4">
+        <v>3000.0</v>
+      </c>
       <c r="G369" s="7"/>
       <c r="H369" s="7"/>
       <c r="I369" s="7"/>
@@ -9875,10 +9878,10 @@
         <v>384</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D370" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E370" s="7"/>
       <c r="F370" s="7"/>
@@ -9896,10 +9899,10 @@
         <v>385</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D371" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E371" s="7"/>
       <c r="F371" s="7"/>
@@ -9917,10 +9920,10 @@
         <v>386</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D372" s="4">
-        <v>7000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E372" s="7"/>
       <c r="F372" s="7"/>
@@ -9938,10 +9941,10 @@
         <v>387</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D373" s="4">
-        <v>3000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E373" s="7"/>
       <c r="F373" s="7"/>
@@ -9959,10 +9962,10 @@
         <v>388</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D374" s="4">
-        <v>25000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E374" s="7"/>
       <c r="F374" s="7"/>
@@ -9980,10 +9983,10 @@
         <v>389</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D375" s="4">
-        <v>8000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E375" s="7"/>
       <c r="F375" s="7"/>
@@ -10001,10 +10004,10 @@
         <v>390</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D376" s="4">
-        <v>4000.0</v>
+        <v>8000.0</v>
       </c>
       <c r="E376" s="7"/>
       <c r="F376" s="7"/>
@@ -10022,10 +10025,10 @@
         <v>391</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="D377" s="4">
-        <v>2000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E377" s="7"/>
       <c r="F377" s="7"/>
@@ -10040,13 +10043,13 @@
         <v>377</v>
       </c>
       <c r="B378" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C378" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C378" s="5" t="s">
-        <v>392</v>
-      </c>
       <c r="D378" s="4">
-        <v>45000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E378" s="7"/>
       <c r="F378" s="7"/>
@@ -10064,10 +10067,10 @@
         <v>394</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D379" s="4">
-        <v>2500.0</v>
+        <v>45000.0</v>
       </c>
       <c r="E379" s="7"/>
       <c r="F379" s="7"/>
@@ -10085,7 +10088,7 @@
         <v>395</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D380" s="4">
         <v>2500.0</v>
@@ -10106,10 +10109,10 @@
         <v>396</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D381" s="4">
-        <v>4000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E381" s="7"/>
       <c r="F381" s="7"/>
@@ -10127,10 +10130,10 @@
         <v>397</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D382" s="4">
-        <v>40000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E382" s="7"/>
       <c r="F382" s="7"/>
@@ -10148,10 +10151,10 @@
         <v>398</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D383" s="4">
-        <v>5000.0</v>
+        <v>40000.0</v>
       </c>
       <c r="E383" s="7"/>
       <c r="F383" s="7"/>
@@ -10169,16 +10172,16 @@
         <v>399</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D384" s="4">
-        <v>46000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E384" s="7"/>
       <c r="F384" s="7"/>
       <c r="G384" s="7"/>
       <c r="H384" s="7"/>
-      <c r="I384" s="4"/>
+      <c r="I384" s="7"/>
       <c r="J384" s="7"/>
     </row>
     <row r="385">
@@ -10190,10 +10193,10 @@
         <v>400</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D385" s="4">
-        <v>2000.0</v>
+        <v>46000.0</v>
       </c>
       <c r="E385" s="7"/>
       <c r="F385" s="7"/>
@@ -10211,10 +10214,10 @@
         <v>401</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D386" s="4">
-        <v>17000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E386" s="7"/>
       <c r="F386" s="7"/>
@@ -10232,10 +10235,10 @@
         <v>402</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D387" s="4">
-        <v>500.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E387" s="7"/>
       <c r="F387" s="7"/>
@@ -10253,16 +10256,16 @@
         <v>403</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D388" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E388" s="7"/>
       <c r="F388" s="7"/>
       <c r="G388" s="7"/>
       <c r="H388" s="7"/>
-      <c r="I388" s="7"/>
+      <c r="I388" s="4"/>
       <c r="J388" s="7"/>
     </row>
     <row r="389">
@@ -10274,10 +10277,10 @@
         <v>404</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D389" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E389" s="7"/>
       <c r="F389" s="7"/>
@@ -10295,10 +10298,10 @@
         <v>405</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D390" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E390" s="7"/>
       <c r="F390" s="7"/>
@@ -10316,10 +10319,10 @@
         <v>406</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D391" s="4">
-        <v>1500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E391" s="7"/>
       <c r="F391" s="7"/>
@@ -10337,10 +10340,10 @@
         <v>407</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D392" s="4">
-        <v>12000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E392" s="7"/>
       <c r="F392" s="7"/>
@@ -10358,10 +10361,10 @@
         <v>408</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D393" s="4">
-        <v>3000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E393" s="7"/>
       <c r="F393" s="7"/>
@@ -10379,10 +10382,10 @@
         <v>409</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D394" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E394" s="7"/>
       <c r="F394" s="7"/>
@@ -10400,10 +10403,10 @@
         <v>410</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D395" s="4">
-        <v>25000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E395" s="7"/>
       <c r="F395" s="7"/>
@@ -10421,10 +10424,10 @@
         <v>411</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D396" s="4">
-        <v>9000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E396" s="7"/>
       <c r="F396" s="7"/>
@@ -10442,12 +10445,12 @@
         <v>412</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D397" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E397" s="4"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E397" s="7"/>
       <c r="F397" s="7"/>
       <c r="G397" s="7"/>
       <c r="H397" s="7"/>
@@ -10463,12 +10466,12 @@
         <v>413</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D398" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="E398" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E398" s="4"/>
       <c r="F398" s="7"/>
       <c r="G398" s="7"/>
       <c r="H398" s="7"/>
@@ -10484,10 +10487,10 @@
         <v>414</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D399" s="4">
-        <v>4500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E399" s="7"/>
       <c r="F399" s="7"/>
@@ -10505,10 +10508,10 @@
         <v>415</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D400" s="4">
-        <v>500.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E400" s="7"/>
       <c r="F400" s="7"/>
@@ -10526,10 +10529,10 @@
         <v>416</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D401" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E401" s="7"/>
       <c r="F401" s="7"/>
@@ -10547,10 +10550,10 @@
         <v>417</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D402" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E402" s="7"/>
       <c r="F402" s="7"/>
@@ -10564,21 +10567,21 @@
         <f t="shared" si="1"/>
         <v>402</v>
       </c>
-      <c r="B403" s="9" t="s">
+      <c r="B403" s="5" t="s">
         <v>418</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="D403" s="10">
-        <v>4500.0</v>
-      </c>
-      <c r="E403" s="11"/>
-      <c r="F403" s="11"/>
-      <c r="G403" s="11"/>
-      <c r="H403" s="11"/>
-      <c r="I403" s="11"/>
-      <c r="J403" s="11"/>
+        <v>393</v>
+      </c>
+      <c r="D403" s="4">
+        <v>1000.0</v>
+      </c>
+      <c r="E403" s="7"/>
+      <c r="F403" s="7"/>
+      <c r="G403" s="7"/>
+      <c r="H403" s="7"/>
+      <c r="I403" s="7"/>
+      <c r="J403" s="7"/>
     </row>
     <row r="404">
       <c r="A404" s="4">
@@ -10589,10 +10592,10 @@
         <v>419</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D404" s="10">
-        <v>50000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E404" s="11"/>
       <c r="F404" s="11"/>
@@ -10610,10 +10613,10 @@
         <v>420</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D405" s="10">
-        <v>12000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="E405" s="11"/>
       <c r="F405" s="11"/>
@@ -10627,14 +10630,14 @@
         <f t="shared" si="1"/>
         <v>405</v>
       </c>
-      <c r="B406" s="5" t="s">
+      <c r="B406" s="9" t="s">
         <v>421</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D406" s="10">
-        <v>4500.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E406" s="11"/>
       <c r="F406" s="11"/>
@@ -10648,14 +10651,14 @@
         <f t="shared" si="1"/>
         <v>406</v>
       </c>
-      <c r="B407" s="9" t="s">
+      <c r="B407" s="5" t="s">
         <v>422</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>423</v>
+        <v>393</v>
       </c>
       <c r="D407" s="10">
-        <v>3000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E407" s="11"/>
       <c r="F407" s="11"/>
@@ -10673,10 +10676,10 @@
         <v>423</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D408" s="10">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E408" s="11"/>
       <c r="F408" s="11"/>
@@ -10694,10 +10697,10 @@
         <v>424</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D409" s="10">
-        <v>6000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E409" s="11"/>
       <c r="F409" s="11"/>
@@ -10715,10 +10718,10 @@
         <v>425</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>371</v>
+        <v>424</v>
       </c>
       <c r="D410" s="10">
-        <v>12000.0</v>
+        <v>6000.0</v>
       </c>
       <c r="E410" s="11"/>
       <c r="F410" s="11"/>
@@ -10736,13 +10739,13 @@
         <v>426</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D411" s="10">
-        <v>200.0</v>
-      </c>
-      <c r="E411" s="10"/>
-      <c r="F411" s="10"/>
+        <v>12000.0</v>
+      </c>
+      <c r="E411" s="11"/>
+      <c r="F411" s="11"/>
       <c r="G411" s="11"/>
       <c r="H411" s="11"/>
       <c r="I411" s="11"/>
@@ -10757,17 +10760,13 @@
         <v>427</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D412" s="10">
-        <v>5000.0</v>
-      </c>
-      <c r="E412" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="F412" s="10">
-        <v>4500.0</v>
-      </c>
+        <v>200.0</v>
+      </c>
+      <c r="E412" s="10"/>
+      <c r="F412" s="10"/>
       <c r="G412" s="11"/>
       <c r="H412" s="11"/>
       <c r="I412" s="11"/>
@@ -10782,13 +10781,17 @@
         <v>428</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D413" s="10">
-        <v>18000.0</v>
-      </c>
-      <c r="E413" s="11"/>
-      <c r="F413" s="11"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E413" s="10">
+        <v>2.0</v>
+      </c>
+      <c r="F413" s="10">
+        <v>4500.0</v>
+      </c>
       <c r="G413" s="11"/>
       <c r="H413" s="11"/>
       <c r="I413" s="11"/>
@@ -10803,10 +10806,10 @@
         <v>429</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D414" s="10">
-        <v>17000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E414" s="11"/>
       <c r="F414" s="11"/>
@@ -10824,10 +10827,10 @@
         <v>430</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D415" s="10">
-        <v>17500.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E415" s="11"/>
       <c r="F415" s="11"/>
@@ -10845,10 +10848,10 @@
         <v>431</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D416" s="10">
-        <v>9000.0</v>
+        <v>17500.0</v>
       </c>
       <c r="E416" s="11"/>
       <c r="F416" s="11"/>
@@ -10866,7 +10869,7 @@
         <v>432</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D417" s="10">
         <v>9000.0</v>
@@ -10887,7 +10890,7 @@
         <v>433</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D418" s="10">
         <v>9000.0</v>
@@ -10908,10 +10911,10 @@
         <v>434</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D419" s="10">
-        <v>19500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E419" s="11"/>
       <c r="F419" s="11"/>
@@ -10929,10 +10932,10 @@
         <v>435</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D420" s="10">
-        <v>8500.0</v>
+        <v>19500.0</v>
       </c>
       <c r="E420" s="11"/>
       <c r="F420" s="11"/>
@@ -10950,10 +10953,10 @@
         <v>436</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D421" s="10">
-        <v>4500.0</v>
+        <v>8500.0</v>
       </c>
       <c r="E421" s="11"/>
       <c r="F421" s="11"/>
@@ -10971,10 +10974,10 @@
         <v>437</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D422" s="10">
-        <v>9000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E422" s="11"/>
       <c r="F422" s="11"/>
@@ -10992,10 +10995,10 @@
         <v>438</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D423" s="10">
-        <v>14000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E423" s="11"/>
       <c r="F423" s="11"/>
@@ -11013,10 +11016,10 @@
         <v>439</v>
       </c>
       <c r="C424" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D424" s="10">
-        <v>3000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E424" s="11"/>
       <c r="F424" s="11"/>
@@ -11034,10 +11037,10 @@
         <v>440</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D425" s="10">
-        <v>12000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E425" s="11"/>
       <c r="F425" s="11"/>
@@ -11055,10 +11058,10 @@
         <v>441</v>
       </c>
       <c r="C426" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D426" s="10">
-        <v>20000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E426" s="11"/>
       <c r="F426" s="11"/>
@@ -11068,10 +11071,19 @@
       <c r="J426" s="11"/>
     </row>
     <row r="427">
-      <c r="A427" s="12"/>
-      <c r="B427" s="12"/>
-      <c r="C427" s="12"/>
-      <c r="D427" s="11"/>
+      <c r="A427" s="4">
+        <f t="shared" si="1"/>
+        <v>426</v>
+      </c>
+      <c r="B427" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="C427" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D427" s="10">
+        <v>20000.0</v>
+      </c>
       <c r="E427" s="11"/>
       <c r="F427" s="11"/>
       <c r="G427" s="11"/>
@@ -12079,13 +12091,13 @@
       <c r="A511" s="12"/>
       <c r="B511" s="12"/>
       <c r="C511" s="12"/>
-      <c r="D511" s="12"/>
-      <c r="E511" s="12"/>
-      <c r="F511" s="12"/>
-      <c r="G511" s="12"/>
-      <c r="H511" s="12"/>
-      <c r="I511" s="12"/>
-      <c r="J511" s="12"/>
+      <c r="D511" s="11"/>
+      <c r="E511" s="11"/>
+      <c r="F511" s="11"/>
+      <c r="G511" s="11"/>
+      <c r="H511" s="11"/>
+      <c r="I511" s="11"/>
+      <c r="J511" s="11"/>
     </row>
     <row r="512">
       <c r="A512" s="12"/>
@@ -20499,15 +20511,27 @@
       <c r="I1212" s="12"/>
       <c r="J1212" s="12"/>
     </row>
+    <row r="1213">
+      <c r="A1213" s="12"/>
+      <c r="B1213" s="12"/>
+      <c r="C1213" s="12"/>
+      <c r="D1213" s="12"/>
+      <c r="E1213" s="12"/>
+      <c r="F1213" s="12"/>
+      <c r="G1213" s="12"/>
+      <c r="H1213" s="12"/>
+      <c r="I1213" s="12"/>
+      <c r="J1213" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$426"/>
-  <conditionalFormatting sqref="A2:J1212">
+  <autoFilter ref="$B$1:$C$427"/>
+  <conditionalFormatting sqref="A2:J1213">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C426">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C427">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20568,7 +20592,7 @@
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4">
@@ -20587,7 +20611,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -20606,7 +20630,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -20625,7 +20649,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -20644,7 +20668,7 @@
         <v>GROSIR5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="4">
@@ -20663,7 +20687,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -20682,7 +20706,7 @@
         <v>GROSIR7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="4">
@@ -20701,7 +20725,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -20720,7 +20744,7 @@
         <v>GROSIR9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="4">
@@ -20739,7 +20763,7 @@
         <v>GROSIR10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="4">
@@ -20758,7 +20782,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -20777,7 +20801,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -20796,7 +20820,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -20815,7 +20839,7 @@
         <v>GROSIR14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="4">
@@ -20834,7 +20858,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -20853,7 +20877,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -20872,7 +20896,7 @@
         <v>GROSIR17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="4">
@@ -20891,7 +20915,7 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
@@ -20910,7 +20934,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -20929,7 +20953,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -20948,7 +20972,7 @@
         <v>GROSIR21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4">
@@ -20967,7 +20991,7 @@
         <v>GROSIR22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="4">
@@ -20986,7 +21010,7 @@
         <v>GROSIR23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="4">
@@ -21005,7 +21029,7 @@
         <v>GROSIR24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="4">
@@ -21024,7 +21048,7 @@
         <v>GROSIR25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="4">
@@ -21043,7 +21067,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -21062,7 +21086,7 @@
         <v>GROSIR27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="4">
@@ -21081,7 +21105,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -21100,7 +21124,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -21119,7 +21143,7 @@
         <v>GROSIR30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="4">
@@ -21138,7 +21162,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -21157,7 +21181,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -21176,7 +21200,7 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
@@ -21195,7 +21219,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -21214,7 +21238,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -21233,7 +21257,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -21252,7 +21276,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -21271,7 +21295,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -21290,7 +21314,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -21309,7 +21333,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -21328,7 +21352,7 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
@@ -21347,7 +21371,7 @@
         <v>GROSIR42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="4">
@@ -21366,7 +21390,7 @@
         <v>GROSIR43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="4">
@@ -21385,7 +21409,7 @@
         <v>GROSIR44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="4">
@@ -21423,7 +21447,7 @@
         <v>GROSIR46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="4">
@@ -21461,7 +21485,7 @@
         <v>GROSIR48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="4">
@@ -21480,7 +21504,7 @@
         <v>GROSIR49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="4">
@@ -21499,7 +21523,7 @@
         <v>GROSIR50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="4">
@@ -21518,7 +21542,7 @@
         <v>GROSIR51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="4">
@@ -21537,7 +21561,7 @@
         <v>GROSIR52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="4">
@@ -21556,7 +21580,7 @@
         <v>GROSIR53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="4">
@@ -21575,7 +21599,7 @@
         <v>GROSIR54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="4">
@@ -21594,7 +21618,7 @@
         <v>GROSIR55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="4">
@@ -21613,7 +21637,7 @@
         <v>GROSIR56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="4">
@@ -21632,7 +21656,7 @@
         <v>GROSIR57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="4">
@@ -21651,7 +21675,7 @@
         <v>GROSIR58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="483">
   <si>
     <t>Barcode</t>
   </si>
@@ -1346,7 +1346,7 @@
     <t>Cat Choize</t>
   </si>
   <si>
-    <t>Djarum Coklat Bungkus SLOP</t>
+    <t>Djarum Coklat SLOP</t>
   </si>
   <si>
     <t>Djarum Coklat Elite Bungkus</t>
@@ -1461,6 +1461,9 @@
   </si>
   <si>
     <t>Top Kopi Gula Aren dus</t>
+  </si>
+  <si>
+    <t>Kilau Nipis 2000 Beli 2 Gratis 1</t>
   </si>
 </sst>
 </file>
@@ -20588,7 +20591,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="str">
-        <f t="shared" ref="A2:A59" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
+        <f t="shared" ref="A2:A60" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -21689,10 +21692,17 @@
       <c r="J59" s="14"/>
     </row>
     <row r="60">
-      <c r="A60" s="4"/>
-      <c r="B60" s="5"/>
+      <c r="A60" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR59</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>482</v>
+      </c>
       <c r="C60" s="5"/>
-      <c r="D60" s="4"/>
+      <c r="D60" s="4">
+        <v>3000.0</v>
+      </c>
       <c r="E60" s="13"/>
       <c r="F60" s="13"/>
       <c r="G60" s="13"/>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -8718,7 +8718,7 @@
         <v>263</v>
       </c>
       <c r="D277" s="4">
-        <v>5000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E277" s="4" t="s">
         <v>13</v>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -29,25 +29,25 @@
     <t>Price in single</t>
   </si>
   <si>
+    <t>MinQtyBulk1</t>
+  </si>
+  <si>
+    <t>PriceBulk1</t>
+  </si>
+  <si>
+    <t>MinQtyBulk2</t>
+  </si>
+  <si>
+    <t>PriceBulk2</t>
+  </si>
+  <si>
+    <t>MinQtyBulk3</t>
+  </si>
+  <si>
+    <t>PriceBulk3</t>
+  </si>
+  <si>
     <t>Type</t>
-  </si>
-  <si>
-    <t>MinQtyBulk1</t>
-  </si>
-  <si>
-    <t>PriceBulk1</t>
-  </si>
-  <si>
-    <t>MinQtyBulk2</t>
-  </si>
-  <si>
-    <t>PriceBulk2</t>
-  </si>
-  <si>
-    <t>MinQtyBulk3</t>
-  </si>
-  <si>
-    <t>PriceBulk3</t>
   </si>
   <si>
     <t>Nutrisari Jeruk Peras</t>
@@ -1819,9 +1819,9 @@
     <col customWidth="1" min="2" max="2" width="35.13"/>
     <col customWidth="1" min="3" max="3" width="15.75"/>
     <col customWidth="1" min="4" max="4" width="14.75"/>
-    <col customWidth="1" min="5" max="5" width="9.38"/>
-    <col customWidth="1" min="6" max="6" width="15.88"/>
-    <col customWidth="1" min="7" max="11" width="13.13"/>
+    <col customWidth="1" min="5" max="5" width="15.88"/>
+    <col customWidth="1" min="6" max="10" width="13.13"/>
+    <col customWidth="1" min="11" max="11" width="9.38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1873,15 +1873,15 @@
       <c r="D2" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
+      <c r="K2" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4">
@@ -1897,15 +1897,15 @@
       <c r="D3" s="4">
         <v>14000.0</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
+      <c r="K3" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4">
@@ -1921,15 +1921,15 @@
       <c r="D4" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
+      <c r="K4" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4">
@@ -1945,15 +1945,15 @@
       <c r="D5" s="4">
         <v>14000.0</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
+      <c r="K5" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4">
@@ -1969,15 +1969,15 @@
       <c r="D6" s="4">
         <v>500.0</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
+      <c r="K6" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4">
@@ -1993,19 +1993,19 @@
       <c r="D7" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>13</v>
+      <c r="E7" s="4">
+        <v>3.0</v>
       </c>
       <c r="F7" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="G7" s="4">
         <v>10000.0</v>
       </c>
+      <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="K7" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4">
@@ -2021,15 +2021,15 @@
       <c r="D8" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
+      <c r="K8" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4">
@@ -2045,15 +2045,15 @@
       <c r="D9" s="4">
         <v>52000.0</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="K9" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4">
@@ -2069,15 +2069,15 @@
       <c r="D10" s="4">
         <v>6000.0</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
+      <c r="K10" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4">
@@ -2093,15 +2093,15 @@
       <c r="D11" s="4">
         <v>52000.0</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
+      <c r="K11" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4">
@@ -2117,15 +2117,15 @@
       <c r="D12" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="K12" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4">
@@ -2141,15 +2141,15 @@
       <c r="D13" s="4">
         <v>20000.0</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="K13" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4">
@@ -2165,15 +2165,15 @@
       <c r="D14" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="K14" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4">
@@ -2189,15 +2189,15 @@
       <c r="D15" s="4">
         <v>20000.0</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
+      <c r="K15" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4">
@@ -2213,15 +2213,15 @@
       <c r="D16" s="4">
         <v>7000.0</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
+      <c r="K16" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4">
@@ -2237,15 +2237,15 @@
       <c r="D17" s="4">
         <v>150000.0</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
+      <c r="K17" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4">
@@ -2261,15 +2261,15 @@
       <c r="D18" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="K18" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4">
@@ -2285,15 +2285,15 @@
       <c r="D19" s="4">
         <v>19500.0</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
+      <c r="K19" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4">
@@ -2309,15 +2309,15 @@
       <c r="D20" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
+      <c r="K20" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4">
@@ -2333,15 +2333,15 @@
       <c r="D21" s="4">
         <v>20500.0</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
+      <c r="K21" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4">
@@ -2357,15 +2357,15 @@
       <c r="D22" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
+      <c r="K22" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4">
@@ -2381,15 +2381,15 @@
       <c r="D23" s="4">
         <v>20000.0</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
+      <c r="K23" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4">
@@ -2405,23 +2405,23 @@
       <c r="D24" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>13</v>
+      <c r="E24" s="8">
+        <v>5.0</v>
       </c>
       <c r="F24" s="8">
-        <v>5.0</v>
-      </c>
-      <c r="G24" s="8">
         <v>14500.0</v>
       </c>
+      <c r="G24" s="4">
+        <v>10.0</v>
+      </c>
       <c r="H24" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="I24" s="4">
         <v>29000.0</v>
       </c>
+      <c r="I24" s="6"/>
       <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
+      <c r="K24" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4">
@@ -2437,15 +2437,15 @@
       <c r="D25" s="4">
         <v>63000.0</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
+      <c r="K25" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4">
@@ -2461,20 +2461,20 @@
       <c r="D26" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="4">
+      <c r="E26" s="4">
         <v>5.0</v>
       </c>
-      <c r="G26" s="6">
+      <c r="F26" s="6">
         <f>3500*5</f>
         <v>17500</v>
       </c>
+      <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
+      <c r="K26" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4">
@@ -2490,15 +2490,15 @@
       <c r="D27" s="4">
         <v>80000.0</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
+      <c r="K27" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4">
@@ -2514,15 +2514,15 @@
       <c r="D28" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
+      <c r="K28" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4">
@@ -2538,15 +2538,15 @@
       <c r="D29" s="4">
         <v>40000.0</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E29" s="7"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
+      <c r="K29" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4">
@@ -2562,15 +2562,15 @@
       <c r="D30" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
+      <c r="K30" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4">
@@ -2586,15 +2586,15 @@
       <c r="D31" s="4">
         <v>29000.0</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
+      <c r="K31" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4">
@@ -2610,15 +2610,15 @@
       <c r="D32" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
+      <c r="K32" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4">
@@ -2634,15 +2634,15 @@
       <c r="D33" s="4">
         <v>35000.0</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
+      <c r="K33" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4">
@@ -2658,15 +2658,15 @@
       <c r="D34" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="6"/>
       <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
+      <c r="K34" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4">
@@ -2682,15 +2682,15 @@
       <c r="D35" s="4">
         <v>19000.0</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
+      <c r="K35" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4">
@@ -2706,15 +2706,15 @@
       <c r="D36" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
+      <c r="K36" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4">
@@ -2730,19 +2730,19 @@
       <c r="D37" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>13</v>
+      <c r="E37" s="4">
+        <v>5.0</v>
       </c>
       <c r="F37" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G37" s="4">
         <v>13500.0</v>
       </c>
+      <c r="G37" s="6"/>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
+      <c r="K37" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4">
@@ -2758,15 +2758,15 @@
       <c r="D38" s="4">
         <v>31000.0</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
+      <c r="K38" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4">
@@ -2782,15 +2782,15 @@
       <c r="D39" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E39" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
       <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
+      <c r="K39" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4">
@@ -2806,15 +2806,15 @@
       <c r="D40" s="4">
         <v>46000.0</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E40" s="6"/>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
+      <c r="K40" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4">
@@ -2830,15 +2830,15 @@
       <c r="D41" s="4">
         <v>6000.0</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E41" s="6"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
+      <c r="K41" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4">
@@ -2854,15 +2854,15 @@
       <c r="D42" s="4">
         <v>52000.0</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E42" s="6"/>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
+      <c r="K42" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4">
@@ -2878,15 +2878,15 @@
       <c r="D43" s="4">
         <v>21000.0</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E43" s="6"/>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
+      <c r="K43" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4">
@@ -2902,15 +2902,15 @@
       <c r="D44" s="4">
         <v>22000.0</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E44" s="6"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
+      <c r="K44" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4">
@@ -2926,15 +2926,15 @@
       <c r="D45" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
+      <c r="K45" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4">
@@ -2950,15 +2950,15 @@
       <c r="D46" s="4">
         <v>32000.0</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E46" s="6"/>
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
       <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
+      <c r="K46" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4">
@@ -2974,15 +2974,15 @@
       <c r="D47" s="4">
         <v>47000.0</v>
       </c>
-      <c r="E47" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E47" s="6"/>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
+      <c r="K47" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4">
@@ -2998,15 +2998,15 @@
       <c r="D48" s="4">
         <v>35000.0</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E48" s="6"/>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
+      <c r="K48" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4">
@@ -3022,15 +3022,15 @@
       <c r="D49" s="4">
         <v>33000.0</v>
       </c>
-      <c r="E49" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E49" s="6"/>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
       <c r="I49" s="6"/>
       <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
+      <c r="K49" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4">
@@ -3046,15 +3046,15 @@
       <c r="D50" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E50" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
       <c r="I50" s="6"/>
       <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
+      <c r="K50" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4">
@@ -3070,15 +3070,15 @@
       <c r="D51" s="4">
         <v>36000.0</v>
       </c>
-      <c r="E51" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E51" s="6"/>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
       <c r="I51" s="6"/>
       <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
+      <c r="K51" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4">
@@ -3094,15 +3094,15 @@
       <c r="D52" s="4">
         <v>7000.0</v>
       </c>
-      <c r="E52" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E52" s="6"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
       <c r="I52" s="6"/>
       <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
+      <c r="K52" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4">
@@ -3118,15 +3118,15 @@
       <c r="D53" s="4">
         <v>150000.0</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E53" s="6"/>
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
       <c r="I53" s="6"/>
       <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
+      <c r="K53" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4">
@@ -3142,19 +3142,19 @@
       <c r="D54" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>13</v>
+      <c r="E54" s="4">
+        <v>5.0</v>
       </c>
       <c r="F54" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G54" s="4">
         <v>16000.0</v>
       </c>
+      <c r="G54" s="6"/>
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
       <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
+      <c r="K54" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4">
@@ -3170,15 +3170,15 @@
       <c r="D55" s="4">
         <v>128000.0</v>
       </c>
-      <c r="E55" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E55" s="6"/>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
       <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
+      <c r="K55" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4">
@@ -3194,15 +3194,15 @@
       <c r="D56" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E56" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E56" s="7"/>
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
       <c r="I56" s="7"/>
       <c r="J56" s="7"/>
-      <c r="K56" s="7"/>
+      <c r="K56" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4">
@@ -3218,15 +3218,15 @@
       <c r="D57" s="4">
         <v>36000.0</v>
       </c>
-      <c r="E57" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
       <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
+      <c r="K57" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4">
@@ -3242,15 +3242,15 @@
       <c r="D58" s="4">
         <v>20000.0</v>
       </c>
-      <c r="E58" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
       <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
+      <c r="K58" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4">
@@ -3266,15 +3266,15 @@
       <c r="D59" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E59" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E59" s="6"/>
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
       <c r="I59" s="6"/>
       <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
+      <c r="K59" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4">
@@ -3290,15 +3290,15 @@
       <c r="D60" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E60" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E60" s="7"/>
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
       <c r="J60" s="7"/>
-      <c r="K60" s="7"/>
+      <c r="K60" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4">
@@ -3314,15 +3314,15 @@
       <c r="D61" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E61" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E61" s="6"/>
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
       <c r="I61" s="6"/>
       <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
+      <c r="K61" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4">
@@ -3338,15 +3338,15 @@
       <c r="D62" s="4">
         <v>21000.0</v>
       </c>
-      <c r="E62" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E62" s="7"/>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
       <c r="I62" s="7"/>
       <c r="J62" s="7"/>
-      <c r="K62" s="7"/>
+      <c r="K62" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4">
@@ -3362,15 +3362,15 @@
       <c r="D63" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E63" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E63" s="6"/>
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
       <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
+      <c r="K63" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4">
@@ -3386,15 +3386,15 @@
       <c r="D64" s="4">
         <v>9500.0</v>
       </c>
-      <c r="E64" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E64" s="6"/>
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
       <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
+      <c r="K64" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4">
@@ -3410,15 +3410,15 @@
       <c r="D65" s="4">
         <v>4500.0</v>
       </c>
-      <c r="E65" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E65" s="6"/>
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
       <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
+      <c r="K65" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4">
@@ -3434,15 +3434,15 @@
       <c r="D66" s="4">
         <v>38000.0</v>
       </c>
-      <c r="E66" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E66" s="7"/>
       <c r="F66" s="7"/>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
       <c r="I66" s="7"/>
       <c r="J66" s="7"/>
-      <c r="K66" s="7"/>
+      <c r="K66" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4">
@@ -3458,15 +3458,15 @@
       <c r="D67" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E67" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E67" s="6"/>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
       <c r="J67" s="6"/>
-      <c r="K67" s="6"/>
+      <c r="K67" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4">
@@ -3482,15 +3482,15 @@
       <c r="D68" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E68" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E68" s="7"/>
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
       <c r="J68" s="7"/>
-      <c r="K68" s="7"/>
+      <c r="K68" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4">
@@ -3506,15 +3506,15 @@
       <c r="D69" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E69" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E69" s="6"/>
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
       <c r="J69" s="6"/>
-      <c r="K69" s="6"/>
+      <c r="K69" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4">
@@ -3530,15 +3530,15 @@
       <c r="D70" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E70" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E70" s="7"/>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
       <c r="I70" s="7"/>
       <c r="J70" s="7"/>
-      <c r="K70" s="7"/>
+      <c r="K70" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4">
@@ -3554,15 +3554,15 @@
       <c r="D71" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E71" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E71" s="6"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
       <c r="J71" s="6"/>
-      <c r="K71" s="6"/>
+      <c r="K71" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4">
@@ -3578,15 +3578,15 @@
       <c r="D72" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E72" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E72" s="6"/>
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
       <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
+      <c r="K72" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4">
@@ -3602,15 +3602,15 @@
       <c r="D73" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E73" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E73" s="6"/>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
       <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
+      <c r="K73" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4">
@@ -3626,15 +3626,15 @@
       <c r="D74" s="4">
         <v>21000.0</v>
       </c>
-      <c r="E74" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E74" s="6"/>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
       <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
+      <c r="K74" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4">
@@ -3650,15 +3650,15 @@
       <c r="D75" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E75" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E75" s="6"/>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
       <c r="H75" s="6"/>
       <c r="I75" s="6"/>
       <c r="J75" s="6"/>
-      <c r="K75" s="6"/>
+      <c r="K75" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4">
@@ -3674,15 +3674,15 @@
       <c r="D76" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E76" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E76" s="7"/>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
       <c r="I76" s="7"/>
       <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
+      <c r="K76" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4">
@@ -3698,15 +3698,15 @@
       <c r="D77" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E77" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E77" s="6"/>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
       <c r="J77" s="6"/>
-      <c r="K77" s="6"/>
+      <c r="K77" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4">
@@ -3722,15 +3722,15 @@
       <c r="D78" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E78" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E78" s="6"/>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
       <c r="J78" s="6"/>
-      <c r="K78" s="6"/>
+      <c r="K78" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4">
@@ -3746,15 +3746,15 @@
       <c r="D79" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E79" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E79" s="6"/>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
       <c r="H79" s="6"/>
       <c r="I79" s="6"/>
       <c r="J79" s="6"/>
-      <c r="K79" s="6"/>
+      <c r="K79" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4">
@@ -3770,15 +3770,15 @@
       <c r="D80" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E80" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E80" s="6"/>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
       <c r="H80" s="6"/>
       <c r="I80" s="6"/>
       <c r="J80" s="6"/>
-      <c r="K80" s="6"/>
+      <c r="K80" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4">
@@ -3794,15 +3794,15 @@
       <c r="D81" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E81" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E81" s="6"/>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
       <c r="H81" s="6"/>
       <c r="I81" s="6"/>
       <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
+      <c r="K81" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4">
@@ -3818,15 +3818,15 @@
       <c r="D82" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E82" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E82" s="7"/>
       <c r="F82" s="7"/>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
       <c r="I82" s="7"/>
       <c r="J82" s="7"/>
-      <c r="K82" s="7"/>
+      <c r="K82" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4">
@@ -3842,15 +3842,15 @@
       <c r="D83" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E83" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E83" s="6"/>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
       <c r="H83" s="6"/>
       <c r="I83" s="6"/>
       <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
+      <c r="K83" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4">
@@ -3866,15 +3866,15 @@
       <c r="D84" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E84" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E84" s="6"/>
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
       <c r="H84" s="6"/>
       <c r="I84" s="6"/>
       <c r="J84" s="6"/>
-      <c r="K84" s="6"/>
+      <c r="K84" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4">
@@ -3890,15 +3890,15 @@
       <c r="D85" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E85" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E85" s="6"/>
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
       <c r="H85" s="6"/>
       <c r="I85" s="6"/>
       <c r="J85" s="6"/>
-      <c r="K85" s="6"/>
+      <c r="K85" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4">
@@ -3914,15 +3914,15 @@
       <c r="D86" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E86" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E86" s="6"/>
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
       <c r="H86" s="6"/>
       <c r="I86" s="6"/>
       <c r="J86" s="6"/>
-      <c r="K86" s="6"/>
+      <c r="K86" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4">
@@ -3938,15 +3938,15 @@
       <c r="D87" s="4">
         <v>16500.0</v>
       </c>
-      <c r="E87" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E87" s="7"/>
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
       <c r="I87" s="7"/>
       <c r="J87" s="7"/>
-      <c r="K87" s="7"/>
+      <c r="K87" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4">
@@ -3962,15 +3962,15 @@
       <c r="D88" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E88" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E88" s="6"/>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
       <c r="H88" s="6"/>
       <c r="I88" s="6"/>
       <c r="J88" s="6"/>
-      <c r="K88" s="6"/>
+      <c r="K88" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4">
@@ -3986,15 +3986,15 @@
       <c r="D89" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E89" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E89" s="7"/>
       <c r="F89" s="7"/>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
       <c r="I89" s="7"/>
       <c r="J89" s="7"/>
-      <c r="K89" s="7"/>
+      <c r="K89" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4">
@@ -4010,15 +4010,15 @@
       <c r="D90" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E90" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E90" s="6"/>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
       <c r="H90" s="6"/>
       <c r="I90" s="6"/>
       <c r="J90" s="6"/>
-      <c r="K90" s="6"/>
+      <c r="K90" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4">
@@ -4034,15 +4034,15 @@
       <c r="D91" s="4">
         <v>8500.0</v>
       </c>
-      <c r="E91" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E91" s="6"/>
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
       <c r="H91" s="6"/>
       <c r="I91" s="6"/>
       <c r="J91" s="6"/>
-      <c r="K91" s="6"/>
+      <c r="K91" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4">
@@ -4058,15 +4058,15 @@
       <c r="D92" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E92" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E92" s="6"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
       <c r="H92" s="6"/>
       <c r="I92" s="6"/>
       <c r="J92" s="6"/>
-      <c r="K92" s="6"/>
+      <c r="K92" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4">
@@ -4082,15 +4082,15 @@
       <c r="D93" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E93" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E93" s="6"/>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
       <c r="H93" s="6"/>
       <c r="I93" s="6"/>
       <c r="J93" s="6"/>
-      <c r="K93" s="6"/>
+      <c r="K93" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4">
@@ -4106,15 +4106,15 @@
       <c r="D94" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E94" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E94" s="6"/>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
       <c r="H94" s="6"/>
       <c r="I94" s="6"/>
       <c r="J94" s="6"/>
-      <c r="K94" s="6"/>
+      <c r="K94" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4">
@@ -4130,15 +4130,15 @@
       <c r="D95" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E95" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E95" s="7"/>
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
       <c r="I95" s="7"/>
       <c r="J95" s="7"/>
-      <c r="K95" s="7"/>
+      <c r="K95" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4">
@@ -4154,15 +4154,15 @@
       <c r="D96" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E96" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E96" s="6"/>
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
       <c r="H96" s="6"/>
       <c r="I96" s="6"/>
       <c r="J96" s="6"/>
-      <c r="K96" s="6"/>
+      <c r="K96" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4">
@@ -4178,15 +4178,15 @@
       <c r="D97" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E97" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E97" s="6"/>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
       <c r="H97" s="6"/>
       <c r="I97" s="6"/>
       <c r="J97" s="6"/>
-      <c r="K97" s="6"/>
+      <c r="K97" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4">
@@ -4202,15 +4202,15 @@
       <c r="D98" s="4">
         <v>90000.0</v>
       </c>
-      <c r="E98" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E98" s="6"/>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
       <c r="H98" s="6"/>
       <c r="I98" s="6"/>
       <c r="J98" s="6"/>
-      <c r="K98" s="6"/>
+      <c r="K98" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4">
@@ -4226,15 +4226,15 @@
       <c r="D99" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E99" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E99" s="6"/>
       <c r="F99" s="6"/>
       <c r="G99" s="6"/>
       <c r="H99" s="6"/>
       <c r="I99" s="6"/>
       <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
+      <c r="K99" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4">
@@ -4250,15 +4250,15 @@
       <c r="D100" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E100" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E100" s="7"/>
       <c r="F100" s="7"/>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
       <c r="I100" s="7"/>
       <c r="J100" s="7"/>
-      <c r="K100" s="7"/>
+      <c r="K100" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4">
@@ -4274,15 +4274,15 @@
       <c r="D101" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E101" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E101" s="7"/>
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
       <c r="I101" s="7"/>
       <c r="J101" s="7"/>
-      <c r="K101" s="7"/>
+      <c r="K101" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4">
@@ -4298,15 +4298,15 @@
       <c r="D102" s="4">
         <v>23000.0</v>
       </c>
-      <c r="E102" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E102" s="7"/>
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
       <c r="I102" s="7"/>
       <c r="J102" s="7"/>
-      <c r="K102" s="7"/>
+      <c r="K102" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4">
@@ -4322,15 +4322,15 @@
       <c r="D103" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E103" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E103" s="7"/>
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
       <c r="I103" s="7"/>
       <c r="J103" s="7"/>
-      <c r="K103" s="7"/>
+      <c r="K103" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4">
@@ -4346,15 +4346,15 @@
       <c r="D104" s="4">
         <v>15500.0</v>
       </c>
-      <c r="E104" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E104" s="6"/>
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>
       <c r="H104" s="6"/>
       <c r="I104" s="6"/>
       <c r="J104" s="6"/>
-      <c r="K104" s="6"/>
+      <c r="K104" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4">
@@ -4370,15 +4370,15 @@
       <c r="D105" s="4">
         <v>1500.0</v>
       </c>
-      <c r="E105" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E105" s="6"/>
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
       <c r="H105" s="6"/>
       <c r="I105" s="6"/>
       <c r="J105" s="6"/>
-      <c r="K105" s="6"/>
+      <c r="K105" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4">
@@ -4394,15 +4394,15 @@
       <c r="D106" s="4">
         <v>11500.0</v>
       </c>
-      <c r="E106" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E106" s="6"/>
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
       <c r="H106" s="6"/>
       <c r="I106" s="6"/>
       <c r="J106" s="6"/>
-      <c r="K106" s="6"/>
+      <c r="K106" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4">
@@ -4418,15 +4418,15 @@
       <c r="D107" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E107" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E107" s="6"/>
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
       <c r="H107" s="6"/>
       <c r="I107" s="6"/>
       <c r="J107" s="6"/>
-      <c r="K107" s="6"/>
+      <c r="K107" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4">
@@ -4442,15 +4442,15 @@
       <c r="D108" s="4">
         <v>9000.0</v>
       </c>
-      <c r="E108" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E108" s="6"/>
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
       <c r="H108" s="6"/>
       <c r="I108" s="6"/>
       <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
+      <c r="K108" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4">
@@ -4466,15 +4466,15 @@
       <c r="D109" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E109" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E109" s="6"/>
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
       <c r="H109" s="6"/>
       <c r="I109" s="6"/>
       <c r="J109" s="6"/>
-      <c r="K109" s="6"/>
+      <c r="K109" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4">
@@ -4490,15 +4490,15 @@
       <c r="D110" s="4">
         <v>19000.0</v>
       </c>
-      <c r="E110" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E110" s="6"/>
       <c r="F110" s="6"/>
       <c r="G110" s="6"/>
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
       <c r="J110" s="6"/>
-      <c r="K110" s="6"/>
+      <c r="K110" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4">
@@ -4514,15 +4514,15 @@
       <c r="D111" s="4">
         <v>1500.0</v>
       </c>
-      <c r="E111" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E111" s="6"/>
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
       <c r="J111" s="6"/>
-      <c r="K111" s="6"/>
+      <c r="K111" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4">
@@ -4538,15 +4538,15 @@
       <c r="D112" s="4">
         <v>8500.0</v>
       </c>
-      <c r="E112" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E112" s="6"/>
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
       <c r="H112" s="6"/>
       <c r="I112" s="6"/>
       <c r="J112" s="6"/>
-      <c r="K112" s="6"/>
+      <c r="K112" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4">
@@ -4562,15 +4562,15 @@
       <c r="D113" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E113" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E113" s="6"/>
       <c r="F113" s="6"/>
       <c r="G113" s="6"/>
       <c r="H113" s="6"/>
       <c r="I113" s="6"/>
       <c r="J113" s="6"/>
-      <c r="K113" s="6"/>
+      <c r="K113" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4">
@@ -4586,15 +4586,15 @@
       <c r="D114" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E114" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E114" s="6"/>
       <c r="F114" s="6"/>
       <c r="G114" s="6"/>
       <c r="H114" s="6"/>
       <c r="I114" s="6"/>
       <c r="J114" s="6"/>
-      <c r="K114" s="6"/>
+      <c r="K114" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4">
@@ -4610,15 +4610,15 @@
       <c r="D115" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E115" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E115" s="6"/>
       <c r="F115" s="6"/>
       <c r="G115" s="6"/>
       <c r="H115" s="6"/>
       <c r="I115" s="6"/>
       <c r="J115" s="6"/>
-      <c r="K115" s="6"/>
+      <c r="K115" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4">
@@ -4634,15 +4634,15 @@
       <c r="D116" s="4">
         <v>16000.0</v>
       </c>
-      <c r="E116" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E116" s="6"/>
       <c r="F116" s="6"/>
       <c r="G116" s="6"/>
       <c r="H116" s="6"/>
       <c r="I116" s="6"/>
       <c r="J116" s="6"/>
-      <c r="K116" s="6"/>
+      <c r="K116" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4">
@@ -4658,15 +4658,15 @@
       <c r="D117" s="4">
         <v>1500.0</v>
       </c>
-      <c r="E117" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E117" s="6"/>
       <c r="F117" s="6"/>
       <c r="G117" s="6"/>
       <c r="H117" s="6"/>
       <c r="I117" s="6"/>
       <c r="J117" s="6"/>
-      <c r="K117" s="6"/>
+      <c r="K117" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4">
@@ -4682,15 +4682,15 @@
       <c r="D118" s="4">
         <v>16000.0</v>
       </c>
-      <c r="E118" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E118" s="6"/>
       <c r="F118" s="6"/>
       <c r="G118" s="6"/>
       <c r="H118" s="6"/>
       <c r="I118" s="6"/>
       <c r="J118" s="6"/>
-      <c r="K118" s="6"/>
+      <c r="K118" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4">
@@ -4706,15 +4706,15 @@
       <c r="D119" s="4">
         <v>6000.0</v>
       </c>
-      <c r="E119" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E119" s="6"/>
       <c r="F119" s="6"/>
       <c r="G119" s="6"/>
       <c r="H119" s="6"/>
       <c r="I119" s="6"/>
       <c r="J119" s="6"/>
-      <c r="K119" s="6"/>
+      <c r="K119" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4">
@@ -4730,15 +4730,15 @@
       <c r="D120" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E120" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E120" s="7"/>
       <c r="F120" s="7"/>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
       <c r="I120" s="7"/>
       <c r="J120" s="7"/>
-      <c r="K120" s="7"/>
+      <c r="K120" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4">
@@ -4754,15 +4754,15 @@
       <c r="D121" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E121" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E121" s="7"/>
       <c r="F121" s="7"/>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
       <c r="I121" s="7"/>
       <c r="J121" s="7"/>
-      <c r="K121" s="7"/>
+      <c r="K121" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4">
@@ -4778,15 +4778,15 @@
       <c r="D122" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E122" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E122" s="7"/>
       <c r="F122" s="7"/>
       <c r="G122" s="7"/>
       <c r="H122" s="7"/>
       <c r="I122" s="7"/>
       <c r="J122" s="7"/>
-      <c r="K122" s="7"/>
+      <c r="K122" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4">
@@ -4802,15 +4802,15 @@
       <c r="D123" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E123" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E123" s="7"/>
       <c r="F123" s="7"/>
       <c r="G123" s="7"/>
       <c r="H123" s="7"/>
       <c r="I123" s="7"/>
       <c r="J123" s="7"/>
-      <c r="K123" s="7"/>
+      <c r="K123" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4">
@@ -4826,15 +4826,15 @@
       <c r="D124" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E124" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E124" s="7"/>
       <c r="F124" s="7"/>
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
       <c r="I124" s="7"/>
       <c r="J124" s="7"/>
-      <c r="K124" s="7"/>
+      <c r="K124" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4">
@@ -4850,15 +4850,15 @@
       <c r="D125" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E125" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E125" s="7"/>
       <c r="F125" s="7"/>
       <c r="G125" s="7"/>
       <c r="H125" s="7"/>
       <c r="I125" s="7"/>
       <c r="J125" s="7"/>
-      <c r="K125" s="7"/>
+      <c r="K125" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4">
@@ -4874,15 +4874,15 @@
       <c r="D126" s="4">
         <v>500.0</v>
       </c>
-      <c r="E126" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E126" s="7"/>
       <c r="F126" s="7"/>
       <c r="G126" s="7"/>
       <c r="H126" s="7"/>
       <c r="I126" s="7"/>
       <c r="J126" s="7"/>
-      <c r="K126" s="7"/>
+      <c r="K126" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4">
@@ -4898,15 +4898,15 @@
       <c r="D127" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E127" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E127" s="6"/>
       <c r="F127" s="6"/>
       <c r="G127" s="6"/>
       <c r="H127" s="6"/>
       <c r="I127" s="6"/>
       <c r="J127" s="6"/>
-      <c r="K127" s="6"/>
+      <c r="K127" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4">
@@ -4922,15 +4922,15 @@
       <c r="D128" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E128" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E128" s="6"/>
       <c r="F128" s="6"/>
       <c r="G128" s="6"/>
       <c r="H128" s="6"/>
       <c r="I128" s="6"/>
       <c r="J128" s="6"/>
-      <c r="K128" s="6"/>
+      <c r="K128" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4">
@@ -4946,15 +4946,15 @@
       <c r="D129" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E129" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E129" s="6"/>
       <c r="F129" s="6"/>
       <c r="G129" s="6"/>
       <c r="H129" s="6"/>
       <c r="I129" s="6"/>
       <c r="J129" s="6"/>
-      <c r="K129" s="6"/>
+      <c r="K129" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4">
@@ -4970,15 +4970,15 @@
       <c r="D130" s="4">
         <v>21000.0</v>
       </c>
-      <c r="E130" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E130" s="6"/>
       <c r="F130" s="6"/>
       <c r="G130" s="6"/>
       <c r="H130" s="6"/>
       <c r="I130" s="6"/>
       <c r="J130" s="6"/>
-      <c r="K130" s="6"/>
+      <c r="K130" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4">
@@ -4994,15 +4994,15 @@
       <c r="D131" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E131" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E131" s="6"/>
       <c r="F131" s="6"/>
       <c r="G131" s="6"/>
       <c r="H131" s="6"/>
       <c r="I131" s="6"/>
       <c r="J131" s="6"/>
-      <c r="K131" s="6"/>
+      <c r="K131" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4">
@@ -5018,15 +5018,15 @@
       <c r="D132" s="4">
         <v>500.0</v>
       </c>
-      <c r="E132" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E132" s="6"/>
       <c r="F132" s="6"/>
       <c r="G132" s="6"/>
       <c r="H132" s="6"/>
       <c r="I132" s="6"/>
       <c r="J132" s="6"/>
-      <c r="K132" s="6"/>
+      <c r="K132" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4">
@@ -5042,15 +5042,15 @@
       <c r="D133" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E133" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E133" s="6"/>
       <c r="F133" s="6"/>
       <c r="G133" s="6"/>
       <c r="H133" s="6"/>
       <c r="I133" s="6"/>
       <c r="J133" s="6"/>
-      <c r="K133" s="6"/>
+      <c r="K133" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4">
@@ -5066,15 +5066,15 @@
       <c r="D134" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E134" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E134" s="6"/>
       <c r="F134" s="6"/>
       <c r="G134" s="6"/>
       <c r="H134" s="6"/>
       <c r="I134" s="6"/>
       <c r="J134" s="6"/>
-      <c r="K134" s="6"/>
+      <c r="K134" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4">
@@ -5090,15 +5090,15 @@
       <c r="D135" s="4">
         <v>500.0</v>
       </c>
-      <c r="E135" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E135" s="6"/>
       <c r="F135" s="6"/>
       <c r="G135" s="6"/>
       <c r="H135" s="6"/>
       <c r="I135" s="6"/>
       <c r="J135" s="6"/>
-      <c r="K135" s="6"/>
+      <c r="K135" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4">
@@ -5114,15 +5114,15 @@
       <c r="D136" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E136" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E136" s="6"/>
       <c r="F136" s="6"/>
       <c r="G136" s="6"/>
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
       <c r="J136" s="6"/>
-      <c r="K136" s="6"/>
+      <c r="K136" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4">
@@ -5138,15 +5138,15 @@
       <c r="D137" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E137" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E137" s="6"/>
       <c r="F137" s="6"/>
       <c r="G137" s="6"/>
       <c r="H137" s="6"/>
       <c r="I137" s="6"/>
       <c r="J137" s="6"/>
-      <c r="K137" s="6"/>
+      <c r="K137" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4">
@@ -5162,19 +5162,19 @@
       <c r="D138" s="4">
         <v>500.0</v>
       </c>
-      <c r="E138" s="4" t="s">
-        <v>13</v>
+      <c r="E138" s="4">
+        <v>3.0</v>
       </c>
       <c r="F138" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="G138" s="4">
         <v>1000.0</v>
       </c>
+      <c r="G138" s="6"/>
       <c r="H138" s="6"/>
       <c r="I138" s="6"/>
       <c r="J138" s="6"/>
-      <c r="K138" s="6"/>
+      <c r="K138" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4">
@@ -5190,15 +5190,15 @@
       <c r="D139" s="4">
         <v>6500.0</v>
       </c>
-      <c r="E139" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E139" s="6"/>
       <c r="F139" s="6"/>
       <c r="G139" s="6"/>
       <c r="H139" s="6"/>
       <c r="I139" s="6"/>
       <c r="J139" s="6"/>
-      <c r="K139" s="6"/>
+      <c r="K139" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4">
@@ -5214,15 +5214,15 @@
       <c r="D140" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E140" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E140" s="6"/>
       <c r="F140" s="6"/>
       <c r="G140" s="6"/>
       <c r="H140" s="6"/>
       <c r="I140" s="6"/>
       <c r="J140" s="6"/>
-      <c r="K140" s="6"/>
+      <c r="K140" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4">
@@ -5238,15 +5238,15 @@
       <c r="D141" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E141" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E141" s="6"/>
       <c r="F141" s="6"/>
       <c r="G141" s="6"/>
       <c r="H141" s="6"/>
       <c r="I141" s="6"/>
       <c r="J141" s="6"/>
-      <c r="K141" s="6"/>
+      <c r="K141" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4">
@@ -5262,19 +5262,19 @@
       <c r="D142" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E142" s="4" t="s">
-        <v>13</v>
+      <c r="E142" s="4">
+        <v>5.0</v>
       </c>
       <c r="F142" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G142" s="4">
         <v>13000.0</v>
       </c>
+      <c r="G142" s="6"/>
       <c r="H142" s="6"/>
       <c r="I142" s="6"/>
       <c r="J142" s="6"/>
-      <c r="K142" s="6"/>
+      <c r="K142" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4">
@@ -5290,15 +5290,15 @@
       <c r="D143" s="4">
         <v>23000.0</v>
       </c>
-      <c r="E143" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E143" s="6"/>
       <c r="F143" s="6"/>
       <c r="G143" s="6"/>
       <c r="H143" s="6"/>
       <c r="I143" s="6"/>
       <c r="J143" s="6"/>
-      <c r="K143" s="6"/>
+      <c r="K143" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4">
@@ -5314,15 +5314,15 @@
       <c r="D144" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E144" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E144" s="7"/>
       <c r="F144" s="7"/>
       <c r="G144" s="7"/>
       <c r="H144" s="7"/>
       <c r="I144" s="7"/>
       <c r="J144" s="7"/>
-      <c r="K144" s="7"/>
+      <c r="K144" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4">
@@ -5338,15 +5338,15 @@
       <c r="D145" s="4">
         <v>26000.0</v>
       </c>
-      <c r="E145" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E145" s="6"/>
       <c r="F145" s="6"/>
       <c r="G145" s="6"/>
       <c r="H145" s="6"/>
       <c r="I145" s="6"/>
       <c r="J145" s="6"/>
-      <c r="K145" s="6"/>
+      <c r="K145" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4">
@@ -5362,15 +5362,15 @@
       <c r="D146" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E146" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E146" s="6"/>
       <c r="F146" s="6"/>
       <c r="G146" s="6"/>
       <c r="H146" s="6"/>
       <c r="I146" s="6"/>
       <c r="J146" s="6"/>
-      <c r="K146" s="6"/>
+      <c r="K146" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4">
@@ -5386,15 +5386,15 @@
       <c r="D147" s="4">
         <v>21000.0</v>
       </c>
-      <c r="E147" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E147" s="6"/>
       <c r="F147" s="6"/>
       <c r="G147" s="6"/>
       <c r="H147" s="6"/>
       <c r="I147" s="6"/>
       <c r="J147" s="6"/>
-      <c r="K147" s="6"/>
+      <c r="K147" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4">
@@ -5410,15 +5410,15 @@
       <c r="D148" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E148" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E148" s="6"/>
       <c r="F148" s="6"/>
       <c r="G148" s="6"/>
       <c r="H148" s="6"/>
       <c r="I148" s="6"/>
       <c r="J148" s="6"/>
-      <c r="K148" s="6"/>
+      <c r="K148" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4">
@@ -5434,15 +5434,15 @@
       <c r="D149" s="4">
         <v>36500.0</v>
       </c>
-      <c r="E149" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E149" s="6"/>
       <c r="F149" s="6"/>
       <c r="G149" s="6"/>
       <c r="H149" s="6"/>
       <c r="I149" s="6"/>
       <c r="J149" s="6"/>
-      <c r="K149" s="6"/>
+      <c r="K149" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4">
@@ -5458,15 +5458,15 @@
       <c r="D150" s="4">
         <v>13000.0</v>
       </c>
-      <c r="E150" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E150" s="6"/>
       <c r="F150" s="6"/>
       <c r="G150" s="6"/>
       <c r="H150" s="6"/>
       <c r="I150" s="6"/>
       <c r="J150" s="6"/>
-      <c r="K150" s="6"/>
+      <c r="K150" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4">
@@ -5482,15 +5482,15 @@
       <c r="D151" s="4">
         <v>500.0</v>
       </c>
-      <c r="E151" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E151" s="6"/>
       <c r="F151" s="6"/>
       <c r="G151" s="6"/>
       <c r="H151" s="6"/>
       <c r="I151" s="6"/>
       <c r="J151" s="6"/>
-      <c r="K151" s="6"/>
+      <c r="K151" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4">
@@ -5506,15 +5506,15 @@
       <c r="D152" s="4">
         <v>13500.0</v>
       </c>
-      <c r="E152" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E152" s="6"/>
       <c r="F152" s="6"/>
       <c r="G152" s="6"/>
       <c r="H152" s="6"/>
       <c r="I152" s="6"/>
       <c r="J152" s="6"/>
-      <c r="K152" s="6"/>
+      <c r="K152" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4">
@@ -5530,15 +5530,15 @@
       <c r="D153" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E153" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E153" s="6"/>
       <c r="F153" s="6"/>
       <c r="G153" s="6"/>
       <c r="H153" s="6"/>
       <c r="I153" s="6"/>
       <c r="J153" s="6"/>
-      <c r="K153" s="6"/>
+      <c r="K153" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4">
@@ -5554,15 +5554,15 @@
       <c r="D154" s="4">
         <v>160000.0</v>
       </c>
-      <c r="E154" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E154" s="6"/>
       <c r="F154" s="6"/>
       <c r="G154" s="6"/>
       <c r="H154" s="6"/>
       <c r="I154" s="6"/>
       <c r="J154" s="6"/>
-      <c r="K154" s="6"/>
+      <c r="K154" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4">
@@ -5578,19 +5578,19 @@
       <c r="D155" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E155" s="4" t="s">
-        <v>13</v>
+      <c r="E155" s="4">
+        <v>5.0</v>
       </c>
       <c r="F155" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G155" s="4">
         <v>9000.0</v>
       </c>
+      <c r="G155" s="6"/>
       <c r="H155" s="6"/>
       <c r="I155" s="6"/>
       <c r="J155" s="6"/>
-      <c r="K155" s="6"/>
+      <c r="K155" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4">
@@ -5606,15 +5606,15 @@
       <c r="D156" s="4">
         <v>65000.0</v>
       </c>
-      <c r="E156" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E156" s="7"/>
       <c r="F156" s="7"/>
       <c r="G156" s="7"/>
       <c r="H156" s="7"/>
       <c r="I156" s="7"/>
       <c r="J156" s="7"/>
-      <c r="K156" s="7"/>
+      <c r="K156" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4">
@@ -5630,15 +5630,15 @@
       <c r="D157" s="4">
         <v>4500.0</v>
       </c>
-      <c r="E157" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E157" s="7"/>
       <c r="F157" s="7"/>
       <c r="G157" s="7"/>
       <c r="H157" s="7"/>
       <c r="I157" s="7"/>
       <c r="J157" s="7"/>
-      <c r="K157" s="7"/>
+      <c r="K157" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4">
@@ -5654,15 +5654,15 @@
       <c r="D158" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E158" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E158" s="6"/>
       <c r="F158" s="6"/>
       <c r="G158" s="6"/>
       <c r="H158" s="6"/>
       <c r="I158" s="6"/>
       <c r="J158" s="6"/>
-      <c r="K158" s="6"/>
+      <c r="K158" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4">
@@ -5678,15 +5678,15 @@
       <c r="D159" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E159" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E159" s="6"/>
       <c r="F159" s="6"/>
       <c r="G159" s="6"/>
       <c r="H159" s="6"/>
       <c r="I159" s="6"/>
       <c r="J159" s="6"/>
-      <c r="K159" s="6"/>
+      <c r="K159" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4">
@@ -5702,15 +5702,15 @@
       <c r="D160" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E160" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E160" s="6"/>
       <c r="F160" s="6"/>
       <c r="G160" s="6"/>
       <c r="H160" s="6"/>
       <c r="I160" s="6"/>
       <c r="J160" s="6"/>
-      <c r="K160" s="6"/>
+      <c r="K160" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4">
@@ -5726,15 +5726,15 @@
       <c r="D161" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E161" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E161" s="6"/>
       <c r="F161" s="6"/>
       <c r="G161" s="6"/>
       <c r="H161" s="6"/>
       <c r="I161" s="6"/>
       <c r="J161" s="6"/>
-      <c r="K161" s="6"/>
+      <c r="K161" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4">
@@ -5750,15 +5750,15 @@
       <c r="D162" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E162" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E162" s="6"/>
       <c r="F162" s="6"/>
       <c r="G162" s="6"/>
       <c r="H162" s="6"/>
       <c r="I162" s="6"/>
       <c r="J162" s="6"/>
-      <c r="K162" s="6"/>
+      <c r="K162" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4">
@@ -5774,15 +5774,15 @@
       <c r="D163" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E163" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E163" s="6"/>
       <c r="F163" s="6"/>
       <c r="G163" s="6"/>
       <c r="H163" s="6"/>
       <c r="I163" s="6"/>
       <c r="J163" s="6"/>
-      <c r="K163" s="6"/>
+      <c r="K163" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4">
@@ -5798,15 +5798,15 @@
       <c r="D164" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E164" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E164" s="6"/>
       <c r="F164" s="6"/>
       <c r="G164" s="6"/>
       <c r="H164" s="6"/>
       <c r="I164" s="6"/>
       <c r="J164" s="6"/>
-      <c r="K164" s="6"/>
+      <c r="K164" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4">
@@ -5822,15 +5822,15 @@
       <c r="D165" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E165" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E165" s="6"/>
       <c r="F165" s="6"/>
       <c r="G165" s="6"/>
       <c r="H165" s="6"/>
       <c r="I165" s="6"/>
       <c r="J165" s="6"/>
-      <c r="K165" s="6"/>
+      <c r="K165" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4">
@@ -5846,15 +5846,15 @@
       <c r="D166" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E166" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E166" s="6"/>
       <c r="F166" s="6"/>
       <c r="G166" s="6"/>
       <c r="H166" s="6"/>
       <c r="I166" s="6"/>
       <c r="J166" s="6"/>
-      <c r="K166" s="6"/>
+      <c r="K166" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4">
@@ -5870,15 +5870,15 @@
       <c r="D167" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E167" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E167" s="6"/>
       <c r="F167" s="6"/>
       <c r="G167" s="6"/>
       <c r="H167" s="6"/>
       <c r="I167" s="6"/>
       <c r="J167" s="6"/>
-      <c r="K167" s="6"/>
+      <c r="K167" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4">
@@ -5894,15 +5894,15 @@
       <c r="D168" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E168" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E168" s="6"/>
       <c r="F168" s="6"/>
       <c r="G168" s="6"/>
       <c r="H168" s="6"/>
       <c r="I168" s="6"/>
       <c r="J168" s="6"/>
-      <c r="K168" s="6"/>
+      <c r="K168" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4">
@@ -5918,15 +5918,15 @@
       <c r="D169" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E169" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E169" s="6"/>
       <c r="F169" s="6"/>
       <c r="G169" s="6"/>
       <c r="H169" s="6"/>
       <c r="I169" s="6"/>
       <c r="J169" s="6"/>
-      <c r="K169" s="6"/>
+      <c r="K169" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4">
@@ -5942,15 +5942,15 @@
       <c r="D170" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E170" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E170" s="6"/>
       <c r="F170" s="6"/>
       <c r="G170" s="6"/>
       <c r="H170" s="6"/>
       <c r="I170" s="6"/>
       <c r="J170" s="6"/>
-      <c r="K170" s="6"/>
+      <c r="K170" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4">
@@ -5966,15 +5966,15 @@
       <c r="D171" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E171" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E171" s="6"/>
       <c r="F171" s="6"/>
       <c r="G171" s="6"/>
       <c r="H171" s="6"/>
       <c r="I171" s="6"/>
       <c r="J171" s="6"/>
-      <c r="K171" s="6"/>
+      <c r="K171" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4">
@@ -5990,15 +5990,15 @@
       <c r="D172" s="4">
         <v>18000.0</v>
       </c>
-      <c r="E172" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E172" s="6"/>
       <c r="F172" s="6"/>
       <c r="G172" s="6"/>
       <c r="H172" s="6"/>
       <c r="I172" s="6"/>
       <c r="J172" s="6"/>
-      <c r="K172" s="6"/>
+      <c r="K172" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4">
@@ -6014,15 +6014,15 @@
       <c r="D173" s="4">
         <v>4500.0</v>
       </c>
-      <c r="E173" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E173" s="6"/>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
       <c r="H173" s="6"/>
       <c r="I173" s="6"/>
       <c r="J173" s="6"/>
-      <c r="K173" s="6"/>
+      <c r="K173" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="4">
@@ -6038,15 +6038,15 @@
       <c r="D174" s="4">
         <v>9000.0</v>
       </c>
-      <c r="E174" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E174" s="6"/>
       <c r="F174" s="6"/>
       <c r="G174" s="6"/>
       <c r="H174" s="6"/>
       <c r="I174" s="6"/>
       <c r="J174" s="6"/>
-      <c r="K174" s="6"/>
+      <c r="K174" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4">
@@ -6062,15 +6062,15 @@
       <c r="D175" s="4">
         <v>18000.0</v>
       </c>
-      <c r="E175" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E175" s="4"/>
       <c r="F175" s="4"/>
-      <c r="G175" s="4"/>
+      <c r="G175" s="7"/>
       <c r="H175" s="7"/>
       <c r="I175" s="7"/>
       <c r="J175" s="7"/>
-      <c r="K175" s="7"/>
+      <c r="K175" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4">
@@ -6086,19 +6086,19 @@
       <c r="D176" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E176" s="4" t="s">
-        <v>13</v>
+      <c r="E176" s="4">
+        <v>4.0</v>
       </c>
       <c r="F176" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="G176" s="4">
         <v>10000.0</v>
       </c>
+      <c r="G176" s="7"/>
       <c r="H176" s="7"/>
       <c r="I176" s="7"/>
       <c r="J176" s="7"/>
-      <c r="K176" s="7"/>
+      <c r="K176" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4">
@@ -6114,15 +6114,15 @@
       <c r="D177" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E177" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E177" s="4"/>
       <c r="F177" s="4"/>
-      <c r="G177" s="4"/>
+      <c r="G177" s="7"/>
       <c r="H177" s="7"/>
       <c r="I177" s="7"/>
       <c r="J177" s="7"/>
-      <c r="K177" s="7"/>
+      <c r="K177" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4">
@@ -6138,19 +6138,19 @@
       <c r="D178" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E178" s="4" t="s">
-        <v>13</v>
+      <c r="E178" s="4">
+        <v>4.0</v>
       </c>
       <c r="F178" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="G178" s="4">
         <v>8500.0</v>
       </c>
+      <c r="G178" s="7"/>
       <c r="H178" s="7"/>
       <c r="I178" s="7"/>
       <c r="J178" s="7"/>
-      <c r="K178" s="7"/>
+      <c r="K178" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4">
@@ -6166,15 +6166,15 @@
       <c r="D179" s="4">
         <v>26000.0</v>
       </c>
-      <c r="E179" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E179" s="7"/>
       <c r="F179" s="7"/>
       <c r="G179" s="7"/>
       <c r="H179" s="7"/>
       <c r="I179" s="7"/>
       <c r="J179" s="7"/>
-      <c r="K179" s="7"/>
+      <c r="K179" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4">
@@ -6190,19 +6190,19 @@
       <c r="D180" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E180" s="4" t="s">
-        <v>13</v>
+      <c r="E180" s="4">
+        <v>5.0</v>
       </c>
       <c r="F180" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G180" s="4">
         <v>17500.0</v>
       </c>
+      <c r="G180" s="7"/>
       <c r="H180" s="7"/>
       <c r="I180" s="7"/>
       <c r="J180" s="7"/>
-      <c r="K180" s="7"/>
+      <c r="K180" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4">
@@ -6218,15 +6218,15 @@
       <c r="D181" s="4">
         <v>17500.0</v>
       </c>
-      <c r="E181" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E181" s="7"/>
       <c r="F181" s="7"/>
       <c r="G181" s="7"/>
       <c r="H181" s="7"/>
       <c r="I181" s="7"/>
       <c r="J181" s="7"/>
-      <c r="K181" s="7"/>
+      <c r="K181" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="4">
@@ -6242,15 +6242,15 @@
       <c r="D182" s="4">
         <v>165000.0</v>
       </c>
-      <c r="E182" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E182" s="7"/>
       <c r="F182" s="7"/>
       <c r="G182" s="7"/>
       <c r="H182" s="7"/>
       <c r="I182" s="7"/>
       <c r="J182" s="7"/>
-      <c r="K182" s="7"/>
+      <c r="K182" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4">
@@ -6266,15 +6266,15 @@
       <c r="D183" s="4">
         <v>21000.0</v>
       </c>
-      <c r="E183" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E183" s="7"/>
       <c r="F183" s="7"/>
       <c r="G183" s="7"/>
       <c r="H183" s="7"/>
       <c r="I183" s="7"/>
       <c r="J183" s="7"/>
-      <c r="K183" s="7"/>
+      <c r="K183" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="4">
@@ -6290,19 +6290,19 @@
       <c r="D184" s="4">
         <v>6000.0</v>
       </c>
-      <c r="E184" s="4" t="s">
-        <v>13</v>
+      <c r="E184" s="4">
+        <v>4.0</v>
       </c>
       <c r="F184" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="G184" s="4">
         <v>22000.0</v>
       </c>
+      <c r="G184" s="7"/>
       <c r="H184" s="7"/>
       <c r="I184" s="7"/>
       <c r="J184" s="7"/>
-      <c r="K184" s="7"/>
+      <c r="K184" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="4">
@@ -6318,15 +6318,15 @@
       <c r="D185" s="4">
         <v>21000.0</v>
       </c>
-      <c r="E185" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E185" s="7"/>
       <c r="F185" s="7"/>
       <c r="G185" s="7"/>
       <c r="H185" s="7"/>
       <c r="I185" s="7"/>
       <c r="J185" s="7"/>
-      <c r="K185" s="7"/>
+      <c r="K185" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="4">
@@ -6342,15 +6342,15 @@
       <c r="D186" s="4">
         <v>21000.0</v>
       </c>
-      <c r="E186" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E186" s="7"/>
       <c r="F186" s="7"/>
       <c r="G186" s="7"/>
       <c r="H186" s="7"/>
       <c r="I186" s="7"/>
       <c r="J186" s="7"/>
-      <c r="K186" s="7"/>
+      <c r="K186" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4">
@@ -6366,15 +6366,15 @@
       <c r="D187" s="4">
         <v>245000.0</v>
       </c>
-      <c r="E187" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E187" s="7"/>
       <c r="F187" s="7"/>
       <c r="G187" s="7"/>
       <c r="H187" s="7"/>
       <c r="I187" s="7"/>
       <c r="J187" s="7"/>
-      <c r="K187" s="7"/>
+      <c r="K187" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4">
@@ -6390,15 +6390,15 @@
       <c r="D188" s="4">
         <v>42000.0</v>
       </c>
-      <c r="E188" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E188" s="7"/>
       <c r="F188" s="7"/>
       <c r="G188" s="7"/>
       <c r="H188" s="7"/>
       <c r="I188" s="7"/>
       <c r="J188" s="7"/>
-      <c r="K188" s="7"/>
+      <c r="K188" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4">
@@ -6414,15 +6414,15 @@
       <c r="D189" s="4">
         <v>44000.0</v>
       </c>
-      <c r="E189" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E189" s="7"/>
       <c r="F189" s="7"/>
       <c r="G189" s="7"/>
       <c r="H189" s="7"/>
       <c r="I189" s="7"/>
       <c r="J189" s="7"/>
-      <c r="K189" s="7"/>
+      <c r="K189" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="4">
@@ -6438,15 +6438,15 @@
       <c r="D190" s="4">
         <v>255000.0</v>
       </c>
-      <c r="E190" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E190" s="7"/>
       <c r="F190" s="7"/>
       <c r="G190" s="7"/>
       <c r="H190" s="7"/>
       <c r="I190" s="7"/>
       <c r="J190" s="7"/>
-      <c r="K190" s="7"/>
+      <c r="K190" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4">
@@ -6462,15 +6462,15 @@
       <c r="D191" s="4">
         <v>21000.0</v>
       </c>
-      <c r="E191" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E191" s="7"/>
       <c r="F191" s="7"/>
       <c r="G191" s="7"/>
       <c r="H191" s="7"/>
       <c r="I191" s="7"/>
       <c r="J191" s="7"/>
-      <c r="K191" s="7"/>
+      <c r="K191" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4">
@@ -6486,15 +6486,15 @@
       <c r="D192" s="4">
         <v>42000.0</v>
       </c>
-      <c r="E192" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E192" s="7"/>
       <c r="F192" s="7"/>
       <c r="G192" s="7"/>
       <c r="H192" s="7"/>
       <c r="I192" s="7"/>
       <c r="J192" s="7"/>
-      <c r="K192" s="7"/>
+      <c r="K192" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4">
@@ -6510,15 +6510,15 @@
       <c r="D193" s="4">
         <v>14500.0</v>
       </c>
-      <c r="E193" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E193" s="7"/>
       <c r="F193" s="7"/>
-      <c r="G193" s="7"/>
+      <c r="G193" s="4"/>
       <c r="H193" s="4"/>
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
-      <c r="K193" s="4"/>
+      <c r="K193" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4">
@@ -6534,22 +6534,22 @@
       <c r="D194" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E194" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E194" s="7"/>
       <c r="F194" s="7"/>
-      <c r="G194" s="7"/>
+      <c r="G194" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H194" s="4">
-        <v>6.0</v>
+        <v>5500.0</v>
       </c>
       <c r="I194" s="4">
-        <v>5500.0</v>
+        <v>12.0</v>
       </c>
       <c r="J194" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K194" s="4">
         <v>10000.0</v>
+      </c>
+      <c r="K194" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="195">
@@ -6566,15 +6566,15 @@
       <c r="D195" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E195" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E195" s="7"/>
       <c r="F195" s="7"/>
       <c r="G195" s="7"/>
       <c r="H195" s="7"/>
       <c r="I195" s="7"/>
       <c r="J195" s="7"/>
-      <c r="K195" s="7"/>
+      <c r="K195" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="4">
@@ -6590,22 +6590,22 @@
       <c r="D196" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E196" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E196" s="7"/>
       <c r="F196" s="7"/>
-      <c r="G196" s="7"/>
+      <c r="G196" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H196" s="4">
-        <v>6.0</v>
+        <v>5500.0</v>
       </c>
       <c r="I196" s="4">
-        <v>5500.0</v>
+        <v>12.0</v>
       </c>
       <c r="J196" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K196" s="4">
         <v>10000.0</v>
+      </c>
+      <c r="K196" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="197">
@@ -6622,15 +6622,15 @@
       <c r="D197" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E197" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E197" s="7"/>
       <c r="F197" s="7"/>
       <c r="G197" s="7"/>
       <c r="H197" s="7"/>
       <c r="I197" s="7"/>
       <c r="J197" s="7"/>
-      <c r="K197" s="7"/>
+      <c r="K197" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="4">
@@ -6646,22 +6646,22 @@
       <c r="D198" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E198" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E198" s="7"/>
       <c r="F198" s="7"/>
-      <c r="G198" s="7"/>
+      <c r="G198" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H198" s="4">
-        <v>6.0</v>
+        <v>5500.0</v>
       </c>
       <c r="I198" s="4">
-        <v>5500.0</v>
+        <v>12.0</v>
       </c>
       <c r="J198" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K198" s="4">
         <v>10000.0</v>
+      </c>
+      <c r="K198" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="199">
@@ -6678,15 +6678,15 @@
       <c r="D199" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E199" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E199" s="7"/>
       <c r="F199" s="7"/>
       <c r="G199" s="7"/>
       <c r="H199" s="7"/>
       <c r="I199" s="7"/>
       <c r="J199" s="7"/>
-      <c r="K199" s="7"/>
+      <c r="K199" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="4">
@@ -6702,22 +6702,22 @@
       <c r="D200" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E200" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E200" s="7"/>
       <c r="F200" s="7"/>
-      <c r="G200" s="7"/>
+      <c r="G200" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H200" s="4">
-        <v>6.0</v>
+        <v>6000.0</v>
       </c>
       <c r="I200" s="4">
-        <v>6000.0</v>
+        <v>12.0</v>
       </c>
       <c r="J200" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K200" s="4">
         <v>11000.0</v>
+      </c>
+      <c r="K200" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="201">
@@ -6734,15 +6734,15 @@
       <c r="D201" s="4">
         <v>11000.0</v>
       </c>
-      <c r="E201" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E201" s="7"/>
       <c r="F201" s="7"/>
       <c r="G201" s="7"/>
       <c r="H201" s="7"/>
       <c r="I201" s="7"/>
       <c r="J201" s="7"/>
-      <c r="K201" s="7"/>
+      <c r="K201" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4">
@@ -6758,22 +6758,22 @@
       <c r="D202" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E202" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E202" s="7"/>
       <c r="F202" s="7"/>
-      <c r="G202" s="7"/>
+      <c r="G202" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H202" s="4">
-        <v>6.0</v>
+        <v>6000.0</v>
       </c>
       <c r="I202" s="4">
-        <v>6000.0</v>
+        <v>12.0</v>
       </c>
       <c r="J202" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K202" s="4">
         <v>11000.0</v>
+      </c>
+      <c r="K202" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="203">
@@ -6790,15 +6790,15 @@
       <c r="D203" s="4">
         <v>11000.0</v>
       </c>
-      <c r="E203" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E203" s="7"/>
       <c r="F203" s="7"/>
       <c r="G203" s="7"/>
       <c r="H203" s="7"/>
       <c r="I203" s="7"/>
       <c r="J203" s="7"/>
-      <c r="K203" s="7"/>
+      <c r="K203" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="4">
@@ -6814,22 +6814,22 @@
       <c r="D204" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E204" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E204" s="7"/>
       <c r="F204" s="7"/>
-      <c r="G204" s="7"/>
+      <c r="G204" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H204" s="4">
-        <v>6.0</v>
+        <v>8000.0</v>
       </c>
       <c r="I204" s="4">
-        <v>8000.0</v>
+        <v>12.0</v>
       </c>
       <c r="J204" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K204" s="4">
         <v>15000.0</v>
+      </c>
+      <c r="K204" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="205">
@@ -6846,15 +6846,15 @@
       <c r="D205" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E205" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E205" s="7"/>
       <c r="F205" s="7"/>
       <c r="G205" s="7"/>
       <c r="H205" s="7"/>
       <c r="I205" s="7"/>
       <c r="J205" s="7"/>
-      <c r="K205" s="7"/>
+      <c r="K205" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="4">
@@ -6870,15 +6870,15 @@
       <c r="D206" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E206" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E206" s="7"/>
       <c r="F206" s="7"/>
       <c r="G206" s="7"/>
       <c r="H206" s="7"/>
       <c r="I206" s="7"/>
       <c r="J206" s="7"/>
-      <c r="K206" s="7"/>
+      <c r="K206" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="4">
@@ -6894,26 +6894,26 @@
       <c r="D207" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E207" s="4" t="s">
-        <v>13</v>
+      <c r="E207" s="4">
+        <v>3.0</v>
       </c>
       <c r="F207" s="4">
-        <v>3.0</v>
+        <v>5000.0</v>
       </c>
       <c r="G207" s="4">
-        <v>5000.0</v>
+        <v>6.0</v>
       </c>
       <c r="H207" s="4">
-        <v>6.0</v>
+        <v>8500.0</v>
       </c>
       <c r="I207" s="4">
-        <v>8500.0</v>
+        <v>12.0</v>
       </c>
       <c r="J207" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K207" s="4">
         <v>16000.0</v>
+      </c>
+      <c r="K207" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="208">
@@ -6930,15 +6930,15 @@
       <c r="D208" s="4">
         <v>16000.0</v>
       </c>
-      <c r="E208" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E208" s="7"/>
       <c r="F208" s="7"/>
       <c r="G208" s="7"/>
       <c r="H208" s="7"/>
       <c r="I208" s="7"/>
       <c r="J208" s="7"/>
-      <c r="K208" s="7"/>
+      <c r="K208" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="4">
@@ -6954,22 +6954,22 @@
       <c r="D209" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E209" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E209" s="7"/>
       <c r="F209" s="7"/>
-      <c r="G209" s="7"/>
+      <c r="G209" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H209" s="4">
-        <v>6.0</v>
+        <v>9000.0</v>
       </c>
       <c r="I209" s="4">
-        <v>9000.0</v>
+        <v>12.0</v>
       </c>
       <c r="J209" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K209" s="4">
         <v>17000.0</v>
+      </c>
+      <c r="K209" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="210">
@@ -6986,15 +6986,15 @@
       <c r="D210" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E210" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E210" s="7"/>
       <c r="F210" s="7"/>
       <c r="G210" s="7"/>
       <c r="H210" s="7"/>
       <c r="I210" s="7"/>
       <c r="J210" s="7"/>
-      <c r="K210" s="7"/>
+      <c r="K210" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="4">
@@ -7010,22 +7010,22 @@
       <c r="D211" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E211" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E211" s="7"/>
       <c r="F211" s="7"/>
-      <c r="G211" s="7"/>
+      <c r="G211" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H211" s="4">
-        <v>6.0</v>
+        <v>9000.0</v>
       </c>
       <c r="I211" s="4">
-        <v>9000.0</v>
+        <v>12.0</v>
       </c>
       <c r="J211" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K211" s="4">
         <v>17000.0</v>
+      </c>
+      <c r="K211" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="212">
@@ -7042,15 +7042,15 @@
       <c r="D212" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E212" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E212" s="7"/>
       <c r="F212" s="7"/>
       <c r="G212" s="7"/>
       <c r="H212" s="7"/>
       <c r="I212" s="7"/>
       <c r="J212" s="7"/>
-      <c r="K212" s="7"/>
+      <c r="K212" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="4">
@@ -7066,26 +7066,26 @@
       <c r="D213" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E213" s="4" t="s">
-        <v>13</v>
+      <c r="E213" s="4">
+        <v>3.0</v>
       </c>
       <c r="F213" s="4">
-        <v>3.0</v>
+        <v>5000.0</v>
       </c>
       <c r="G213" s="4">
-        <v>5000.0</v>
+        <v>6.0</v>
       </c>
       <c r="H213" s="4">
-        <v>6.0</v>
+        <v>9500.0</v>
       </c>
       <c r="I213" s="4">
-        <v>9500.0</v>
+        <v>12.0</v>
       </c>
       <c r="J213" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K213" s="4">
         <v>18000.0</v>
+      </c>
+      <c r="K213" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="214">
@@ -7102,15 +7102,15 @@
       <c r="D214" s="4">
         <v>18000.0</v>
       </c>
-      <c r="E214" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E214" s="7"/>
       <c r="F214" s="7"/>
       <c r="G214" s="7"/>
       <c r="H214" s="7"/>
       <c r="I214" s="7"/>
       <c r="J214" s="7"/>
-      <c r="K214" s="7"/>
+      <c r="K214" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="4">
@@ -7126,22 +7126,22 @@
       <c r="D215" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E215" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E215" s="7"/>
       <c r="F215" s="7"/>
-      <c r="G215" s="7"/>
+      <c r="G215" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H215" s="4">
-        <v>6.0</v>
+        <v>14500.0</v>
       </c>
       <c r="I215" s="4">
-        <v>14500.0</v>
+        <v>12.0</v>
       </c>
       <c r="J215" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K215" s="4">
         <v>28000.0</v>
+      </c>
+      <c r="K215" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="216">
@@ -7158,15 +7158,15 @@
       <c r="D216" s="4">
         <v>28000.0</v>
       </c>
-      <c r="E216" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E216" s="7"/>
       <c r="F216" s="7"/>
       <c r="G216" s="7"/>
       <c r="H216" s="7"/>
       <c r="I216" s="7"/>
       <c r="J216" s="7"/>
-      <c r="K216" s="7"/>
+      <c r="K216" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="4">
@@ -7182,22 +7182,22 @@
       <c r="D217" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E217" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E217" s="7"/>
       <c r="F217" s="7"/>
-      <c r="G217" s="7"/>
+      <c r="G217" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H217" s="4">
-        <v>6.0</v>
+        <v>10500.0</v>
       </c>
       <c r="I217" s="4">
-        <v>10500.0</v>
+        <v>12.0</v>
       </c>
       <c r="J217" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K217" s="4">
         <v>20000.0</v>
+      </c>
+      <c r="K217" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="218">
@@ -7214,15 +7214,15 @@
       <c r="D218" s="4">
         <v>20000.0</v>
       </c>
-      <c r="E218" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E218" s="7"/>
       <c r="F218" s="7"/>
       <c r="G218" s="7"/>
       <c r="H218" s="7"/>
       <c r="I218" s="7"/>
       <c r="J218" s="7"/>
-      <c r="K218" s="7"/>
+      <c r="K218" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="4">
@@ -7238,22 +7238,22 @@
       <c r="D219" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E219" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E219" s="7"/>
       <c r="F219" s="7"/>
-      <c r="G219" s="7"/>
+      <c r="G219" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H219" s="4">
-        <v>6.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I219" s="4">
-        <v>13000.0</v>
+        <v>12.0</v>
       </c>
       <c r="J219" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K219" s="4">
         <v>25000.0</v>
+      </c>
+      <c r="K219" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="220">
@@ -7270,15 +7270,15 @@
       <c r="D220" s="4">
         <v>25000.0</v>
       </c>
-      <c r="E220" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E220" s="7"/>
       <c r="F220" s="7"/>
       <c r="G220" s="7"/>
       <c r="H220" s="7"/>
       <c r="I220" s="7"/>
       <c r="J220" s="7"/>
-      <c r="K220" s="7"/>
+      <c r="K220" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="4">
@@ -7294,22 +7294,22 @@
       <c r="D221" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E221" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E221" s="7"/>
       <c r="F221" s="7"/>
-      <c r="G221" s="7"/>
+      <c r="G221" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H221" s="4">
-        <v>6.0</v>
+        <v>11000.0</v>
       </c>
       <c r="I221" s="4">
-        <v>11000.0</v>
+        <v>12.0</v>
       </c>
       <c r="J221" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K221" s="4">
         <v>21000.0</v>
+      </c>
+      <c r="K221" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="222">
@@ -7326,15 +7326,15 @@
       <c r="D222" s="4">
         <v>21000.0</v>
       </c>
-      <c r="E222" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E222" s="7"/>
       <c r="F222" s="7"/>
       <c r="G222" s="7"/>
       <c r="H222" s="7"/>
       <c r="I222" s="7"/>
       <c r="J222" s="7"/>
-      <c r="K222" s="7"/>
+      <c r="K222" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="4">
@@ -7350,22 +7350,22 @@
       <c r="D223" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E223" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E223" s="7"/>
       <c r="F223" s="7"/>
-      <c r="G223" s="7"/>
+      <c r="G223" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H223" s="4">
-        <v>6.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I223" s="4">
-        <v>13000.0</v>
+        <v>12.0</v>
       </c>
       <c r="J223" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K223" s="4">
         <v>25000.0</v>
+      </c>
+      <c r="K223" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="224">
@@ -7382,15 +7382,15 @@
       <c r="D224" s="4">
         <v>25000.0</v>
       </c>
-      <c r="E224" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E224" s="7"/>
       <c r="F224" s="7"/>
       <c r="G224" s="7"/>
       <c r="H224" s="7"/>
       <c r="I224" s="7"/>
       <c r="J224" s="7"/>
-      <c r="K224" s="7"/>
+      <c r="K224" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="4">
@@ -7406,22 +7406,22 @@
       <c r="D225" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E225" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E225" s="7"/>
       <c r="F225" s="7"/>
-      <c r="G225" s="7"/>
+      <c r="G225" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H225" s="4">
-        <v>6.0</v>
+        <v>14000.0</v>
       </c>
       <c r="I225" s="4">
-        <v>14000.0</v>
+        <v>12.0</v>
       </c>
       <c r="J225" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K225" s="4">
         <v>28000.0</v>
+      </c>
+      <c r="K225" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="226">
@@ -7438,15 +7438,15 @@
       <c r="D226" s="4">
         <v>28000.0</v>
       </c>
-      <c r="E226" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E226" s="7"/>
       <c r="F226" s="7"/>
       <c r="G226" s="7"/>
       <c r="H226" s="7"/>
       <c r="I226" s="7"/>
       <c r="J226" s="7"/>
-      <c r="K226" s="7"/>
+      <c r="K226" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="4">
@@ -7462,22 +7462,22 @@
       <c r="D227" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E227" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E227" s="7"/>
       <c r="F227" s="7"/>
-      <c r="G227" s="7"/>
+      <c r="G227" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H227" s="4">
-        <v>6.0</v>
+        <v>13000.0</v>
       </c>
       <c r="I227" s="4">
-        <v>13000.0</v>
+        <v>12.0</v>
       </c>
       <c r="J227" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K227" s="4">
         <v>25000.0</v>
+      </c>
+      <c r="K227" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="228">
@@ -7494,15 +7494,15 @@
       <c r="D228" s="4">
         <v>25000.0</v>
       </c>
-      <c r="E228" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E228" s="7"/>
       <c r="F228" s="7"/>
       <c r="G228" s="7"/>
       <c r="H228" s="7"/>
       <c r="I228" s="7"/>
       <c r="J228" s="7"/>
-      <c r="K228" s="7"/>
+      <c r="K228" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="4">
@@ -7518,22 +7518,22 @@
       <c r="D229" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E229" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E229" s="7"/>
       <c r="F229" s="7"/>
-      <c r="G229" s="7"/>
+      <c r="G229" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H229" s="4">
-        <v>6.0</v>
+        <v>14000.0</v>
       </c>
       <c r="I229" s="4">
-        <v>14000.0</v>
+        <v>12.0</v>
       </c>
       <c r="J229" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K229" s="4">
         <v>27000.0</v>
+      </c>
+      <c r="K229" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="230">
@@ -7550,15 +7550,15 @@
       <c r="D230" s="4">
         <v>27000.0</v>
       </c>
-      <c r="E230" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E230" s="7"/>
       <c r="F230" s="7"/>
       <c r="G230" s="7"/>
       <c r="H230" s="7"/>
       <c r="I230" s="7"/>
       <c r="J230" s="7"/>
-      <c r="K230" s="7"/>
+      <c r="K230" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="4">
@@ -7574,22 +7574,22 @@
       <c r="D231" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E231" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E231" s="7"/>
       <c r="F231" s="7"/>
-      <c r="G231" s="7"/>
+      <c r="G231" s="4">
+        <v>6.0</v>
+      </c>
       <c r="H231" s="4">
-        <v>6.0</v>
+        <v>14000.0</v>
       </c>
       <c r="I231" s="4">
-        <v>14000.0</v>
+        <v>12.0</v>
       </c>
       <c r="J231" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="K231" s="4">
         <v>27000.0</v>
+      </c>
+      <c r="K231" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="232">
@@ -7606,15 +7606,15 @@
       <c r="D232" s="4">
         <v>27000.0</v>
       </c>
-      <c r="E232" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E232" s="7"/>
       <c r="F232" s="7"/>
       <c r="G232" s="7"/>
       <c r="H232" s="7"/>
       <c r="I232" s="7"/>
       <c r="J232" s="7"/>
-      <c r="K232" s="7"/>
+      <c r="K232" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="4">
@@ -7630,15 +7630,15 @@
       <c r="D233" s="4">
         <v>34000.0</v>
       </c>
-      <c r="E233" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E233" s="7"/>
       <c r="F233" s="7"/>
       <c r="G233" s="7"/>
       <c r="H233" s="7"/>
       <c r="I233" s="7"/>
       <c r="J233" s="7"/>
-      <c r="K233" s="7"/>
+      <c r="K233" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="4">
@@ -7654,15 +7654,15 @@
       <c r="D234" s="4">
         <v>27000.0</v>
       </c>
-      <c r="E234" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E234" s="7"/>
       <c r="F234" s="7"/>
       <c r="G234" s="7"/>
       <c r="H234" s="7"/>
       <c r="I234" s="7"/>
       <c r="J234" s="7"/>
-      <c r="K234" s="7"/>
+      <c r="K234" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="4">
@@ -7678,16 +7678,16 @@
       <c r="D235" s="4">
         <v>37000.0</v>
       </c>
-      <c r="E235" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E235" s="7"/>
       <c r="F235" s="7"/>
-      <c r="G235" s="7"/>
+      <c r="G235" s="4"/>
       <c r="H235" s="4"/>
       <c r="I235" s="4"/>
-      <c r="J235" s="4"/>
-      <c r="K235" s="4">
+      <c r="J235" s="4">
         <v>37000.0</v>
+      </c>
+      <c r="K235" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="236">
@@ -7704,15 +7704,15 @@
       <c r="D236" s="4">
         <v>16000.0</v>
       </c>
-      <c r="E236" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E236" s="7"/>
       <c r="F236" s="7"/>
       <c r="G236" s="7"/>
       <c r="H236" s="7"/>
       <c r="I236" s="7"/>
       <c r="J236" s="7"/>
-      <c r="K236" s="7"/>
+      <c r="K236" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="4">
@@ -7728,15 +7728,15 @@
       <c r="D237" s="4">
         <v>43000.0</v>
       </c>
-      <c r="E237" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E237" s="7"/>
       <c r="F237" s="7"/>
       <c r="G237" s="7"/>
       <c r="H237" s="7"/>
       <c r="I237" s="7"/>
       <c r="J237" s="7"/>
-      <c r="K237" s="7"/>
+      <c r="K237" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="4">
@@ -7752,15 +7752,15 @@
       <c r="D238" s="4">
         <v>23000.0</v>
       </c>
-      <c r="E238" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E238" s="7"/>
       <c r="F238" s="7"/>
       <c r="G238" s="7"/>
       <c r="H238" s="7"/>
       <c r="I238" s="7"/>
       <c r="J238" s="7"/>
-      <c r="K238" s="7"/>
+      <c r="K238" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="4">
@@ -7776,15 +7776,15 @@
       <c r="D239" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E239" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E239" s="7"/>
       <c r="F239" s="7"/>
       <c r="G239" s="7"/>
       <c r="H239" s="7"/>
       <c r="I239" s="7"/>
       <c r="J239" s="7"/>
-      <c r="K239" s="7"/>
+      <c r="K239" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="4">
@@ -7800,15 +7800,15 @@
       <c r="D240" s="4">
         <v>29000.0</v>
       </c>
-      <c r="E240" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E240" s="7"/>
       <c r="F240" s="7"/>
       <c r="G240" s="7"/>
       <c r="H240" s="7"/>
       <c r="I240" s="7"/>
       <c r="J240" s="7"/>
-      <c r="K240" s="7"/>
+      <c r="K240" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="4">
@@ -7824,15 +7824,15 @@
       <c r="D241" s="4">
         <v>13000.0</v>
       </c>
-      <c r="E241" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E241" s="7"/>
       <c r="F241" s="7"/>
       <c r="G241" s="7"/>
       <c r="H241" s="7"/>
       <c r="I241" s="7"/>
       <c r="J241" s="7"/>
-      <c r="K241" s="7"/>
+      <c r="K241" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="4">
@@ -7848,15 +7848,15 @@
       <c r="D242" s="4">
         <v>39000.0</v>
       </c>
-      <c r="E242" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E242" s="7"/>
       <c r="F242" s="7"/>
       <c r="G242" s="7"/>
       <c r="H242" s="7"/>
       <c r="I242" s="7"/>
       <c r="J242" s="7"/>
-      <c r="K242" s="7"/>
+      <c r="K242" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="4">
@@ -7872,15 +7872,15 @@
       <c r="D243" s="4">
         <v>382000.0</v>
       </c>
-      <c r="E243" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E243" s="7"/>
       <c r="F243" s="7"/>
       <c r="G243" s="7"/>
       <c r="H243" s="7"/>
       <c r="I243" s="7"/>
       <c r="J243" s="7"/>
-      <c r="K243" s="7"/>
+      <c r="K243" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="4">
@@ -7896,15 +7896,15 @@
       <c r="D244" s="4">
         <v>500.0</v>
       </c>
-      <c r="E244" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E244" s="7"/>
       <c r="F244" s="7"/>
       <c r="G244" s="7"/>
       <c r="H244" s="7"/>
       <c r="I244" s="7"/>
       <c r="J244" s="7"/>
-      <c r="K244" s="7"/>
+      <c r="K244" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="4">
@@ -7920,15 +7920,15 @@
       <c r="D245" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E245" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E245" s="7"/>
       <c r="F245" s="7"/>
       <c r="G245" s="7"/>
       <c r="H245" s="7"/>
       <c r="I245" s="7"/>
       <c r="J245" s="7"/>
-      <c r="K245" s="7"/>
+      <c r="K245" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="4">
@@ -7944,19 +7944,19 @@
       <c r="D246" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E246" s="4" t="s">
-        <v>13</v>
+      <c r="E246" s="4">
+        <v>5.0</v>
       </c>
       <c r="F246" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G246" s="4">
         <v>10000.0</v>
       </c>
+      <c r="G246" s="7"/>
       <c r="H246" s="7"/>
       <c r="I246" s="7"/>
       <c r="J246" s="7"/>
-      <c r="K246" s="7"/>
+      <c r="K246" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="4">
@@ -7972,19 +7972,19 @@
       <c r="D247" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E247" s="4" t="s">
-        <v>13</v>
+      <c r="E247" s="4">
+        <v>5.0</v>
       </c>
       <c r="F247" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G247" s="4">
         <v>14000.0</v>
       </c>
+      <c r="G247" s="7"/>
       <c r="H247" s="7"/>
       <c r="I247" s="7"/>
       <c r="J247" s="7"/>
-      <c r="K247" s="7"/>
+      <c r="K247" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="4">
@@ -8000,15 +8000,15 @@
       <c r="D248" s="4">
         <v>109000.0</v>
       </c>
-      <c r="E248" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E248" s="7"/>
       <c r="F248" s="7"/>
       <c r="G248" s="7"/>
       <c r="H248" s="7"/>
       <c r="I248" s="7"/>
       <c r="J248" s="7"/>
-      <c r="K248" s="7"/>
+      <c r="K248" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="4">
@@ -8024,19 +8024,19 @@
       <c r="D249" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E249" s="4" t="s">
-        <v>13</v>
+      <c r="E249" s="4">
+        <v>5.0</v>
       </c>
       <c r="F249" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G249" s="4">
         <v>14000.0</v>
       </c>
+      <c r="G249" s="7"/>
       <c r="H249" s="7"/>
       <c r="I249" s="7"/>
       <c r="J249" s="7"/>
-      <c r="K249" s="7"/>
+      <c r="K249" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="4">
@@ -8052,15 +8052,15 @@
       <c r="D250" s="4">
         <v>109000.0</v>
       </c>
-      <c r="E250" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E250" s="7"/>
       <c r="F250" s="7"/>
       <c r="G250" s="7"/>
       <c r="H250" s="7"/>
       <c r="I250" s="7"/>
       <c r="J250" s="7"/>
-      <c r="K250" s="7"/>
+      <c r="K250" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="4">
@@ -8076,15 +8076,15 @@
       <c r="D251" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E251" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E251" s="7"/>
       <c r="F251" s="7"/>
       <c r="G251" s="7"/>
       <c r="H251" s="7"/>
       <c r="I251" s="7"/>
       <c r="J251" s="7"/>
-      <c r="K251" s="7"/>
+      <c r="K251" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="4">
@@ -8100,15 +8100,15 @@
       <c r="D252" s="4">
         <v>114000.0</v>
       </c>
-      <c r="E252" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E252" s="7"/>
       <c r="F252" s="7"/>
       <c r="G252" s="7"/>
       <c r="H252" s="7"/>
       <c r="I252" s="7"/>
       <c r="J252" s="7"/>
-      <c r="K252" s="7"/>
+      <c r="K252" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="4">
@@ -8124,15 +8124,15 @@
       <c r="D253" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E253" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E253" s="7"/>
       <c r="F253" s="7"/>
       <c r="G253" s="7"/>
       <c r="H253" s="7"/>
       <c r="I253" s="7"/>
       <c r="J253" s="7"/>
-      <c r="K253" s="7"/>
+      <c r="K253" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="4">
@@ -8148,19 +8148,19 @@
       <c r="D254" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E254" s="4" t="s">
-        <v>13</v>
+      <c r="E254" s="4">
+        <v>10.0</v>
       </c>
       <c r="F254" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="G254" s="4">
         <v>39000.0</v>
       </c>
+      <c r="G254" s="7"/>
       <c r="H254" s="7"/>
       <c r="I254" s="7"/>
       <c r="J254" s="7"/>
-      <c r="K254" s="7"/>
+      <c r="K254" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="4">
@@ -8176,15 +8176,15 @@
       <c r="D255" s="4">
         <v>114000.0</v>
       </c>
-      <c r="E255" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E255" s="7"/>
       <c r="F255" s="7"/>
       <c r="G255" s="7"/>
       <c r="H255" s="7"/>
       <c r="I255" s="7"/>
       <c r="J255" s="7"/>
-      <c r="K255" s="7"/>
+      <c r="K255" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="4">
@@ -8200,15 +8200,15 @@
       <c r="D256" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E256" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E256" s="7"/>
       <c r="F256" s="7"/>
       <c r="G256" s="7"/>
       <c r="H256" s="7"/>
       <c r="I256" s="7"/>
       <c r="J256" s="7"/>
-      <c r="K256" s="7"/>
+      <c r="K256" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="4">
@@ -8224,15 +8224,15 @@
       <c r="D257" s="4">
         <v>114000.0</v>
       </c>
-      <c r="E257" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E257" s="7"/>
       <c r="F257" s="7"/>
       <c r="G257" s="7"/>
       <c r="H257" s="7"/>
       <c r="I257" s="7"/>
       <c r="J257" s="7"/>
-      <c r="K257" s="7"/>
+      <c r="K257" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="4">
@@ -8248,15 +8248,15 @@
       <c r="D258" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E258" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E258" s="7"/>
       <c r="F258" s="7"/>
       <c r="G258" s="7"/>
       <c r="H258" s="7"/>
       <c r="I258" s="7"/>
       <c r="J258" s="7"/>
-      <c r="K258" s="7"/>
+      <c r="K258" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="4">
@@ -8272,15 +8272,15 @@
       <c r="D259" s="4">
         <v>114000.0</v>
       </c>
-      <c r="E259" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E259" s="7"/>
       <c r="F259" s="7"/>
       <c r="G259" s="7"/>
       <c r="H259" s="7"/>
       <c r="I259" s="7"/>
       <c r="J259" s="7"/>
-      <c r="K259" s="7"/>
+      <c r="K259" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="4">
@@ -8296,15 +8296,15 @@
       <c r="D260" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E260" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E260" s="7"/>
       <c r="F260" s="7"/>
       <c r="G260" s="7"/>
       <c r="H260" s="7"/>
       <c r="I260" s="7"/>
       <c r="J260" s="7"/>
-      <c r="K260" s="7"/>
+      <c r="K260" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="4">
@@ -8320,15 +8320,15 @@
       <c r="D261" s="4">
         <v>114000.0</v>
       </c>
-      <c r="E261" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E261" s="7"/>
       <c r="F261" s="7"/>
       <c r="G261" s="7"/>
       <c r="H261" s="7"/>
       <c r="I261" s="7"/>
       <c r="J261" s="7"/>
-      <c r="K261" s="7"/>
+      <c r="K261" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="4">
@@ -8344,15 +8344,15 @@
       <c r="D262" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E262" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E262" s="7"/>
       <c r="F262" s="7"/>
       <c r="G262" s="7"/>
       <c r="H262" s="7"/>
       <c r="I262" s="7"/>
       <c r="J262" s="7"/>
-      <c r="K262" s="7"/>
+      <c r="K262" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="4">
@@ -8368,15 +8368,15 @@
       <c r="D263" s="4">
         <v>107000.0</v>
       </c>
-      <c r="E263" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E263" s="7"/>
       <c r="F263" s="7"/>
       <c r="G263" s="7"/>
       <c r="H263" s="7"/>
       <c r="I263" s="7"/>
       <c r="J263" s="7"/>
-      <c r="K263" s="7"/>
+      <c r="K263" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="4">
@@ -8392,15 +8392,15 @@
       <c r="D264" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E264" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E264" s="7"/>
       <c r="F264" s="7"/>
       <c r="G264" s="7"/>
       <c r="H264" s="7"/>
       <c r="I264" s="7"/>
       <c r="J264" s="7"/>
-      <c r="K264" s="7"/>
+      <c r="K264" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="4">
@@ -8416,15 +8416,15 @@
       <c r="D265" s="4">
         <v>112000.0</v>
       </c>
-      <c r="E265" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E265" s="6"/>
       <c r="F265" s="6"/>
       <c r="G265" s="6"/>
       <c r="H265" s="6"/>
       <c r="I265" s="6"/>
       <c r="J265" s="6"/>
-      <c r="K265" s="6"/>
+      <c r="K265" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="4">
@@ -8440,19 +8440,19 @@
       <c r="D266" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E266" s="4" t="s">
-        <v>13</v>
+      <c r="E266" s="4">
+        <v>5.0</v>
       </c>
       <c r="F266" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G266" s="4">
         <v>19000.0</v>
       </c>
+      <c r="G266" s="7"/>
       <c r="H266" s="7"/>
       <c r="I266" s="7"/>
       <c r="J266" s="7"/>
-      <c r="K266" s="7"/>
+      <c r="K266" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="4">
@@ -8468,19 +8468,19 @@
       <c r="D267" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E267" s="4" t="s">
-        <v>13</v>
+      <c r="E267" s="4">
+        <v>5.0</v>
       </c>
       <c r="F267" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G267" s="4">
         <v>19000.0</v>
       </c>
+      <c r="G267" s="7"/>
       <c r="H267" s="7"/>
       <c r="I267" s="7"/>
       <c r="J267" s="7"/>
-      <c r="K267" s="7"/>
+      <c r="K267" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="4">
@@ -8496,15 +8496,15 @@
       <c r="D268" s="4">
         <v>86000.0</v>
       </c>
-      <c r="E268" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E268" s="4"/>
       <c r="F268" s="4"/>
-      <c r="G268" s="4"/>
+      <c r="G268" s="7"/>
       <c r="H268" s="7"/>
       <c r="I268" s="7"/>
       <c r="J268" s="7"/>
-      <c r="K268" s="7"/>
+      <c r="K268" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="4">
@@ -8520,15 +8520,15 @@
       <c r="D269" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E269" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E269" s="4"/>
       <c r="F269" s="4"/>
-      <c r="G269" s="4"/>
+      <c r="G269" s="7"/>
       <c r="H269" s="7"/>
       <c r="I269" s="7"/>
       <c r="J269" s="7"/>
-      <c r="K269" s="7"/>
+      <c r="K269" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="4">
@@ -8544,15 +8544,15 @@
       <c r="D270" s="4">
         <v>86000.0</v>
       </c>
-      <c r="E270" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E270" s="4"/>
       <c r="F270" s="4"/>
-      <c r="G270" s="4"/>
+      <c r="G270" s="7"/>
       <c r="H270" s="7"/>
       <c r="I270" s="7"/>
       <c r="J270" s="7"/>
-      <c r="K270" s="7"/>
+      <c r="K270" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="4">
@@ -8568,19 +8568,19 @@
       <c r="D271" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E271" s="4" t="s">
-        <v>13</v>
+      <c r="E271" s="4">
+        <v>5.0</v>
       </c>
       <c r="F271" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G271" s="4">
         <v>19500.0</v>
       </c>
-      <c r="H271" s="4"/>
+      <c r="G271" s="4"/>
+      <c r="H271" s="7"/>
       <c r="I271" s="7"/>
       <c r="J271" s="7"/>
-      <c r="K271" s="7"/>
+      <c r="K271" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="4">
@@ -8596,19 +8596,19 @@
       <c r="D272" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E272" s="4" t="s">
-        <v>13</v>
+      <c r="E272" s="4">
+        <v>5.0</v>
       </c>
       <c r="F272" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G272" s="4">
         <v>6000.0</v>
       </c>
+      <c r="G272" s="7"/>
       <c r="H272" s="7"/>
       <c r="I272" s="7"/>
       <c r="J272" s="7"/>
-      <c r="K272" s="7"/>
+      <c r="K272" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="4">
@@ -8624,15 +8624,15 @@
       <c r="D273" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E273" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E273" s="7"/>
       <c r="F273" s="7"/>
       <c r="G273" s="7"/>
       <c r="H273" s="7"/>
       <c r="I273" s="7"/>
       <c r="J273" s="7"/>
-      <c r="K273" s="7"/>
+      <c r="K273" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="4">
@@ -8648,15 +8648,15 @@
       <c r="D274" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E274" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E274" s="7"/>
       <c r="F274" s="7"/>
       <c r="G274" s="7"/>
       <c r="H274" s="7"/>
       <c r="I274" s="7"/>
       <c r="J274" s="7"/>
-      <c r="K274" s="7"/>
+      <c r="K274" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="4">
@@ -8672,15 +8672,15 @@
       <c r="D275" s="4">
         <v>89000.0</v>
       </c>
-      <c r="E275" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E275" s="7"/>
       <c r="F275" s="7"/>
       <c r="G275" s="7"/>
       <c r="H275" s="7"/>
       <c r="I275" s="7"/>
       <c r="J275" s="7"/>
-      <c r="K275" s="7"/>
+      <c r="K275" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="4">
@@ -8696,15 +8696,15 @@
       <c r="D276" s="4">
         <v>7500.0</v>
       </c>
-      <c r="E276" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E276" s="7"/>
       <c r="F276" s="7"/>
       <c r="G276" s="7"/>
       <c r="H276" s="7"/>
       <c r="I276" s="7"/>
       <c r="J276" s="7"/>
-      <c r="K276" s="7"/>
+      <c r="K276" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="4">
@@ -8720,15 +8720,15 @@
       <c r="D277" s="4">
         <v>4500.0</v>
       </c>
-      <c r="E277" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E277" s="7"/>
       <c r="F277" s="7"/>
       <c r="G277" s="7"/>
       <c r="H277" s="7"/>
       <c r="I277" s="7"/>
       <c r="J277" s="7"/>
-      <c r="K277" s="7"/>
+      <c r="K277" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="4">
@@ -8744,15 +8744,15 @@
       <c r="D278" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E278" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E278" s="7"/>
       <c r="F278" s="7"/>
       <c r="G278" s="7"/>
       <c r="H278" s="7"/>
       <c r="I278" s="7"/>
       <c r="J278" s="7"/>
-      <c r="K278" s="7"/>
+      <c r="K278" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="4">
@@ -8768,15 +8768,15 @@
       <c r="D279" s="4">
         <v>80000.0</v>
       </c>
-      <c r="E279" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E279" s="6"/>
       <c r="F279" s="6"/>
       <c r="G279" s="6"/>
       <c r="H279" s="6"/>
       <c r="I279" s="6"/>
       <c r="J279" s="6"/>
-      <c r="K279" s="6"/>
+      <c r="K279" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="4">
@@ -8792,15 +8792,15 @@
       <c r="D280" s="4">
         <v>14000.0</v>
       </c>
-      <c r="E280" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E280" s="7"/>
       <c r="F280" s="7"/>
       <c r="G280" s="7"/>
       <c r="H280" s="7"/>
       <c r="I280" s="7"/>
       <c r="J280" s="7"/>
-      <c r="K280" s="7"/>
+      <c r="K280" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="4">
@@ -8816,15 +8816,15 @@
       <c r="D281" s="4">
         <v>14500.0</v>
       </c>
-      <c r="E281" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E281" s="7"/>
       <c r="F281" s="7"/>
       <c r="G281" s="7"/>
       <c r="H281" s="7"/>
       <c r="I281" s="7"/>
       <c r="J281" s="7"/>
-      <c r="K281" s="7"/>
+      <c r="K281" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="4">
@@ -8840,15 +8840,15 @@
       <c r="D282" s="4">
         <v>15000.0</v>
       </c>
-      <c r="E282" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E282" s="7"/>
       <c r="F282" s="7"/>
       <c r="G282" s="7"/>
       <c r="H282" s="7"/>
       <c r="I282" s="7"/>
       <c r="J282" s="7"/>
-      <c r="K282" s="7"/>
+      <c r="K282" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="4">
@@ -8864,15 +8864,15 @@
       <c r="D283" s="4">
         <v>15500.0</v>
       </c>
-      <c r="E283" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E283" s="7"/>
       <c r="F283" s="7"/>
       <c r="G283" s="7"/>
       <c r="H283" s="7"/>
       <c r="I283" s="7"/>
       <c r="J283" s="7"/>
-      <c r="K283" s="7"/>
+      <c r="K283" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="4">
@@ -8888,15 +8888,15 @@
       <c r="D284" s="4">
         <v>1500.0</v>
       </c>
-      <c r="E284" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E284" s="7"/>
       <c r="F284" s="7"/>
       <c r="G284" s="7"/>
       <c r="H284" s="7"/>
       <c r="I284" s="7"/>
       <c r="J284" s="7"/>
-      <c r="K284" s="7"/>
+      <c r="K284" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="4">
@@ -8912,15 +8912,15 @@
       <c r="D285" s="4">
         <v>12500.0</v>
       </c>
-      <c r="E285" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E285" s="7"/>
       <c r="F285" s="7"/>
       <c r="G285" s="7"/>
       <c r="H285" s="7"/>
       <c r="I285" s="7"/>
       <c r="J285" s="7"/>
-      <c r="K285" s="7"/>
+      <c r="K285" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="4">
@@ -8936,15 +8936,15 @@
       <c r="D286" s="4">
         <v>500.0</v>
       </c>
-      <c r="E286" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E286" s="7"/>
       <c r="F286" s="7"/>
       <c r="G286" s="7"/>
       <c r="H286" s="7"/>
       <c r="I286" s="7"/>
       <c r="J286" s="7"/>
-      <c r="K286" s="7"/>
+      <c r="K286" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="4">
@@ -8960,15 +8960,15 @@
       <c r="D287" s="4">
         <v>4500.0</v>
       </c>
-      <c r="E287" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E287" s="7"/>
       <c r="F287" s="7"/>
       <c r="G287" s="7"/>
       <c r="H287" s="7"/>
       <c r="I287" s="7"/>
       <c r="J287" s="7"/>
-      <c r="K287" s="7"/>
+      <c r="K287" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="4">
@@ -8984,15 +8984,15 @@
       <c r="D288" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E288" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E288" s="7"/>
       <c r="F288" s="7"/>
       <c r="G288" s="7"/>
       <c r="H288" s="7"/>
       <c r="I288" s="7"/>
       <c r="J288" s="7"/>
-      <c r="K288" s="7"/>
+      <c r="K288" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="4">
@@ -9008,15 +9008,15 @@
       <c r="D289" s="4">
         <v>23000.0</v>
       </c>
-      <c r="E289" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E289" s="7"/>
       <c r="F289" s="7"/>
       <c r="G289" s="7"/>
       <c r="H289" s="7"/>
       <c r="I289" s="7"/>
       <c r="J289" s="7"/>
-      <c r="K289" s="7"/>
+      <c r="K289" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="4">
@@ -9032,19 +9032,19 @@
       <c r="D290" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E290" s="4" t="s">
-        <v>13</v>
+      <c r="E290" s="4">
+        <v>5.0</v>
       </c>
       <c r="F290" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G290" s="4">
         <v>7500.0</v>
       </c>
+      <c r="G290" s="7"/>
       <c r="H290" s="7"/>
       <c r="I290" s="7"/>
       <c r="J290" s="7"/>
-      <c r="K290" s="7"/>
+      <c r="K290" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="4">
@@ -9060,15 +9060,15 @@
       <c r="D291" s="4">
         <v>7500.0</v>
       </c>
-      <c r="E291" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E291" s="4"/>
       <c r="F291" s="4"/>
-      <c r="G291" s="4"/>
+      <c r="G291" s="7"/>
       <c r="H291" s="7"/>
       <c r="I291" s="7"/>
       <c r="J291" s="7"/>
-      <c r="K291" s="7"/>
+      <c r="K291" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="4">
@@ -9084,19 +9084,19 @@
       <c r="D292" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E292" s="4" t="s">
-        <v>13</v>
+      <c r="E292" s="4">
+        <v>5.0</v>
       </c>
       <c r="F292" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G292" s="4">
         <v>9000.0</v>
       </c>
+      <c r="G292" s="7"/>
       <c r="H292" s="7"/>
       <c r="I292" s="7"/>
       <c r="J292" s="7"/>
-      <c r="K292" s="7"/>
+      <c r="K292" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="4">
@@ -9112,15 +9112,15 @@
       <c r="D293" s="4">
         <v>9000.0</v>
       </c>
-      <c r="E293" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E293" s="4"/>
       <c r="F293" s="4"/>
-      <c r="G293" s="4"/>
+      <c r="G293" s="7"/>
       <c r="H293" s="7"/>
       <c r="I293" s="7"/>
       <c r="J293" s="7"/>
-      <c r="K293" s="7"/>
+      <c r="K293" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="4">
@@ -9136,19 +9136,19 @@
       <c r="D294" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E294" s="4" t="s">
-        <v>13</v>
+      <c r="E294" s="4">
+        <v>5.0</v>
       </c>
       <c r="F294" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G294" s="4">
         <v>7500.0</v>
       </c>
+      <c r="G294" s="7"/>
       <c r="H294" s="7"/>
       <c r="I294" s="7"/>
       <c r="J294" s="7"/>
-      <c r="K294" s="7"/>
+      <c r="K294" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="4">
@@ -9164,15 +9164,15 @@
       <c r="D295" s="4">
         <v>7500.0</v>
       </c>
-      <c r="E295" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E295" s="7"/>
       <c r="F295" s="7"/>
       <c r="G295" s="7"/>
       <c r="H295" s="7"/>
       <c r="I295" s="7"/>
       <c r="J295" s="7"/>
-      <c r="K295" s="7"/>
+      <c r="K295" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="4">
@@ -9188,15 +9188,15 @@
       <c r="D296" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E296" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E296" s="7"/>
       <c r="F296" s="7"/>
       <c r="G296" s="7"/>
       <c r="H296" s="7"/>
       <c r="I296" s="7"/>
       <c r="J296" s="7"/>
-      <c r="K296" s="7"/>
+      <c r="K296" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="4">
@@ -9212,15 +9212,15 @@
       <c r="D297" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E297" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E297" s="7"/>
       <c r="F297" s="7"/>
       <c r="G297" s="7"/>
       <c r="H297" s="7"/>
       <c r="I297" s="7"/>
       <c r="J297" s="7"/>
-      <c r="K297" s="7"/>
+      <c r="K297" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="4">
@@ -9236,15 +9236,15 @@
       <c r="D298" s="4">
         <v>500.0</v>
       </c>
-      <c r="E298" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E298" s="7"/>
       <c r="F298" s="7"/>
       <c r="G298" s="7"/>
       <c r="H298" s="7"/>
       <c r="I298" s="7"/>
       <c r="J298" s="7"/>
-      <c r="K298" s="7"/>
+      <c r="K298" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="4">
@@ -9260,15 +9260,15 @@
       <c r="D299" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E299" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E299" s="7"/>
       <c r="F299" s="7"/>
       <c r="G299" s="7"/>
       <c r="H299" s="7"/>
       <c r="I299" s="7"/>
       <c r="J299" s="7"/>
-      <c r="K299" s="7"/>
+      <c r="K299" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="4">
@@ -9284,15 +9284,15 @@
       <c r="D300" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E300" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E300" s="7"/>
       <c r="F300" s="7"/>
       <c r="G300" s="7"/>
       <c r="H300" s="7"/>
       <c r="I300" s="7"/>
       <c r="J300" s="7"/>
-      <c r="K300" s="7"/>
+      <c r="K300" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="4">
@@ -9308,15 +9308,15 @@
       <c r="D301" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E301" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E301" s="7"/>
       <c r="F301" s="7"/>
       <c r="G301" s="7"/>
       <c r="H301" s="7"/>
       <c r="I301" s="7"/>
       <c r="J301" s="7"/>
-      <c r="K301" s="7"/>
+      <c r="K301" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="4">
@@ -9332,15 +9332,15 @@
       <c r="D302" s="4">
         <v>500.0</v>
       </c>
-      <c r="E302" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E302" s="7"/>
       <c r="F302" s="7"/>
       <c r="G302" s="7"/>
       <c r="H302" s="7"/>
       <c r="I302" s="7"/>
       <c r="J302" s="7"/>
-      <c r="K302" s="7"/>
+      <c r="K302" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="4">
@@ -9356,15 +9356,15 @@
       <c r="D303" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E303" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E303" s="7"/>
       <c r="F303" s="7"/>
       <c r="G303" s="7"/>
       <c r="H303" s="7"/>
       <c r="I303" s="7"/>
       <c r="J303" s="7"/>
-      <c r="K303" s="7"/>
+      <c r="K303" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="4">
@@ -9380,15 +9380,15 @@
       <c r="D304" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E304" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E304" s="7"/>
       <c r="F304" s="7"/>
       <c r="G304" s="7"/>
       <c r="H304" s="7"/>
       <c r="I304" s="7"/>
       <c r="J304" s="7"/>
-      <c r="K304" s="7"/>
+      <c r="K304" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="4">
@@ -9404,15 +9404,15 @@
       <c r="D305" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E305" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E305" s="7"/>
       <c r="F305" s="7"/>
       <c r="G305" s="7"/>
       <c r="H305" s="7"/>
       <c r="I305" s="7"/>
       <c r="J305" s="7"/>
-      <c r="K305" s="7"/>
+      <c r="K305" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="4">
@@ -9428,15 +9428,15 @@
       <c r="D306" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E306" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E306" s="7"/>
       <c r="F306" s="7"/>
       <c r="G306" s="7"/>
       <c r="H306" s="7"/>
       <c r="I306" s="7"/>
       <c r="J306" s="7"/>
-      <c r="K306" s="7"/>
+      <c r="K306" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="4">
@@ -9452,15 +9452,15 @@
       <c r="D307" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E307" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E307" s="7"/>
       <c r="F307" s="7"/>
       <c r="G307" s="7"/>
       <c r="H307" s="7"/>
       <c r="I307" s="7"/>
       <c r="J307" s="7"/>
-      <c r="K307" s="7"/>
+      <c r="K307" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="4">
@@ -9476,15 +9476,15 @@
       <c r="D308" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E308" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E308" s="7"/>
       <c r="F308" s="7"/>
       <c r="G308" s="7"/>
       <c r="H308" s="7"/>
       <c r="I308" s="7"/>
       <c r="J308" s="7"/>
-      <c r="K308" s="7"/>
+      <c r="K308" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="4">
@@ -9500,15 +9500,15 @@
       <c r="D309" s="4">
         <v>500.0</v>
       </c>
-      <c r="E309" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E309" s="7"/>
       <c r="F309" s="7"/>
       <c r="G309" s="7"/>
       <c r="H309" s="7"/>
       <c r="I309" s="7"/>
       <c r="J309" s="7"/>
-      <c r="K309" s="7"/>
+      <c r="K309" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="4">
@@ -9524,15 +9524,15 @@
       <c r="D310" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E310" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E310" s="7"/>
       <c r="F310" s="7"/>
       <c r="G310" s="7"/>
       <c r="H310" s="7"/>
       <c r="I310" s="7"/>
       <c r="J310" s="7"/>
-      <c r="K310" s="7"/>
+      <c r="K310" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="4">
@@ -9548,15 +9548,15 @@
       <c r="D311" s="4">
         <v>500.0</v>
       </c>
-      <c r="E311" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E311" s="7"/>
       <c r="F311" s="7"/>
       <c r="G311" s="7"/>
       <c r="H311" s="7"/>
       <c r="I311" s="7"/>
       <c r="J311" s="7"/>
-      <c r="K311" s="7"/>
+      <c r="K311" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="4">
@@ -9572,15 +9572,15 @@
       <c r="D312" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E312" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E312" s="7"/>
       <c r="F312" s="7"/>
       <c r="G312" s="7"/>
       <c r="H312" s="7"/>
       <c r="I312" s="7"/>
       <c r="J312" s="7"/>
-      <c r="K312" s="7"/>
+      <c r="K312" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="4">
@@ -9596,15 +9596,15 @@
       <c r="D313" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E313" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E313" s="7"/>
       <c r="F313" s="7"/>
       <c r="G313" s="7"/>
       <c r="H313" s="7"/>
       <c r="I313" s="7"/>
       <c r="J313" s="7"/>
-      <c r="K313" s="7"/>
+      <c r="K313" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="4">
@@ -9620,15 +9620,15 @@
       <c r="D314" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E314" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E314" s="7"/>
       <c r="F314" s="7"/>
       <c r="G314" s="7"/>
       <c r="H314" s="7"/>
       <c r="I314" s="7"/>
       <c r="J314" s="7"/>
-      <c r="K314" s="7"/>
+      <c r="K314" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="4">
@@ -9644,15 +9644,15 @@
       <c r="D315" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E315" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E315" s="7"/>
       <c r="F315" s="7"/>
       <c r="G315" s="7"/>
       <c r="H315" s="7"/>
       <c r="I315" s="7"/>
       <c r="J315" s="7"/>
-      <c r="K315" s="7"/>
+      <c r="K315" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="4">
@@ -9668,15 +9668,15 @@
       <c r="D316" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E316" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E316" s="7"/>
       <c r="F316" s="7"/>
       <c r="G316" s="7"/>
       <c r="H316" s="7"/>
       <c r="I316" s="7"/>
       <c r="J316" s="7"/>
-      <c r="K316" s="7"/>
+      <c r="K316" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="4">
@@ -9692,15 +9692,15 @@
       <c r="D317" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E317" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E317" s="7"/>
       <c r="F317" s="7"/>
       <c r="G317" s="7"/>
       <c r="H317" s="7"/>
       <c r="I317" s="7"/>
       <c r="J317" s="7"/>
-      <c r="K317" s="7"/>
+      <c r="K317" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="4">
@@ -9716,15 +9716,15 @@
       <c r="D318" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E318" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E318" s="7"/>
       <c r="F318" s="7"/>
       <c r="G318" s="7"/>
       <c r="H318" s="7"/>
       <c r="I318" s="7"/>
       <c r="J318" s="7"/>
-      <c r="K318" s="7"/>
+      <c r="K318" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="4">
@@ -9740,15 +9740,15 @@
       <c r="D319" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E319" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E319" s="7"/>
       <c r="F319" s="7"/>
       <c r="G319" s="7"/>
       <c r="H319" s="7"/>
       <c r="I319" s="7"/>
       <c r="J319" s="7"/>
-      <c r="K319" s="7"/>
+      <c r="K319" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="4">
@@ -9764,15 +9764,15 @@
       <c r="D320" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E320" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E320" s="7"/>
       <c r="F320" s="7"/>
       <c r="G320" s="7"/>
       <c r="H320" s="7"/>
       <c r="I320" s="7"/>
       <c r="J320" s="7"/>
-      <c r="K320" s="7"/>
+      <c r="K320" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="4">
@@ -9788,15 +9788,15 @@
       <c r="D321" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E321" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E321" s="7"/>
       <c r="F321" s="7"/>
       <c r="G321" s="7"/>
       <c r="H321" s="7"/>
       <c r="I321" s="7"/>
       <c r="J321" s="7"/>
-      <c r="K321" s="7"/>
+      <c r="K321" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="4">
@@ -9812,15 +9812,15 @@
       <c r="D322" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E322" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E322" s="7"/>
       <c r="F322" s="7"/>
       <c r="G322" s="7"/>
       <c r="H322" s="7"/>
       <c r="I322" s="7"/>
       <c r="J322" s="7"/>
-      <c r="K322" s="7"/>
+      <c r="K322" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="4">
@@ -9836,15 +9836,15 @@
       <c r="D323" s="4">
         <v>500.0</v>
       </c>
-      <c r="E323" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E323" s="7"/>
       <c r="F323" s="7"/>
       <c r="G323" s="7"/>
       <c r="H323" s="7"/>
       <c r="I323" s="7"/>
       <c r="J323" s="7"/>
-      <c r="K323" s="7"/>
+      <c r="K323" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="4">
@@ -9860,15 +9860,15 @@
       <c r="D324" s="4">
         <v>500.0</v>
       </c>
-      <c r="E324" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E324" s="7"/>
       <c r="F324" s="7"/>
       <c r="G324" s="7"/>
       <c r="H324" s="7"/>
       <c r="I324" s="7"/>
       <c r="J324" s="7"/>
-      <c r="K324" s="7"/>
+      <c r="K324" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="4">
@@ -9884,15 +9884,15 @@
       <c r="D325" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E325" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E325" s="7"/>
       <c r="F325" s="7"/>
       <c r="G325" s="7"/>
       <c r="H325" s="7"/>
       <c r="I325" s="7"/>
       <c r="J325" s="7"/>
-      <c r="K325" s="7"/>
+      <c r="K325" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="4">
@@ -9908,15 +9908,15 @@
       <c r="D326" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E326" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E326" s="7"/>
       <c r="F326" s="7"/>
       <c r="G326" s="7"/>
       <c r="H326" s="7"/>
       <c r="I326" s="7"/>
       <c r="J326" s="7"/>
-      <c r="K326" s="7"/>
+      <c r="K326" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="4">
@@ -9932,15 +9932,15 @@
       <c r="D327" s="4">
         <v>500.0</v>
       </c>
-      <c r="E327" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E327" s="7"/>
       <c r="F327" s="7"/>
       <c r="G327" s="7"/>
       <c r="H327" s="7"/>
       <c r="I327" s="7"/>
       <c r="J327" s="7"/>
-      <c r="K327" s="7"/>
+      <c r="K327" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="4">
@@ -9956,15 +9956,15 @@
       <c r="D328" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E328" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E328" s="7"/>
       <c r="F328" s="7"/>
       <c r="G328" s="7"/>
       <c r="H328" s="7"/>
       <c r="I328" s="7"/>
       <c r="J328" s="7"/>
-      <c r="K328" s="7"/>
+      <c r="K328" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="4">
@@ -9980,15 +9980,15 @@
       <c r="D329" s="4">
         <v>500.0</v>
       </c>
-      <c r="E329" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E329" s="7"/>
       <c r="F329" s="7"/>
       <c r="G329" s="7"/>
       <c r="H329" s="7"/>
       <c r="I329" s="7"/>
       <c r="J329" s="7"/>
-      <c r="K329" s="7"/>
+      <c r="K329" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="4">
@@ -10004,15 +10004,15 @@
       <c r="D330" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E330" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E330" s="7"/>
       <c r="F330" s="7"/>
       <c r="G330" s="7"/>
       <c r="H330" s="7"/>
       <c r="I330" s="7"/>
       <c r="J330" s="7"/>
-      <c r="K330" s="7"/>
+      <c r="K330" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="4">
@@ -10028,15 +10028,15 @@
       <c r="D331" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E331" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E331" s="7"/>
       <c r="F331" s="7"/>
       <c r="G331" s="7"/>
       <c r="H331" s="7"/>
       <c r="I331" s="7"/>
       <c r="J331" s="7"/>
-      <c r="K331" s="7"/>
+      <c r="K331" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="4">
@@ -10052,15 +10052,15 @@
       <c r="D332" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E332" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E332" s="7"/>
       <c r="F332" s="7"/>
       <c r="G332" s="7"/>
       <c r="H332" s="7"/>
       <c r="I332" s="7"/>
       <c r="J332" s="7"/>
-      <c r="K332" s="7"/>
+      <c r="K332" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="4">
@@ -10076,19 +10076,19 @@
       <c r="D333" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E333" s="4" t="s">
-        <v>13</v>
+      <c r="E333" s="4">
+        <v>5.0</v>
       </c>
       <c r="F333" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G333" s="4">
         <v>4500.0</v>
       </c>
+      <c r="G333" s="7"/>
       <c r="H333" s="7"/>
       <c r="I333" s="7"/>
       <c r="J333" s="7"/>
-      <c r="K333" s="7"/>
+      <c r="K333" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="4">
@@ -10104,15 +10104,15 @@
       <c r="D334" s="4">
         <v>4500.0</v>
       </c>
-      <c r="E334" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E334" s="7"/>
       <c r="F334" s="7"/>
       <c r="G334" s="7"/>
       <c r="H334" s="7"/>
       <c r="I334" s="7"/>
       <c r="J334" s="7"/>
-      <c r="K334" s="7"/>
+      <c r="K334" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="4">
@@ -10128,15 +10128,15 @@
       <c r="D335" s="4">
         <v>51000.0</v>
       </c>
-      <c r="E335" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E335" s="4"/>
       <c r="F335" s="4"/>
-      <c r="G335" s="4"/>
+      <c r="G335" s="7"/>
       <c r="H335" s="7"/>
       <c r="I335" s="7"/>
       <c r="J335" s="7"/>
-      <c r="K335" s="7"/>
+      <c r="K335" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="4">
@@ -10152,19 +10152,19 @@
       <c r="D336" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E336" s="4" t="s">
-        <v>13</v>
+      <c r="E336" s="4">
+        <v>5.0</v>
       </c>
       <c r="F336" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G336" s="4">
         <v>9000.0</v>
       </c>
+      <c r="G336" s="7"/>
       <c r="H336" s="7"/>
       <c r="I336" s="7"/>
       <c r="J336" s="7"/>
-      <c r="K336" s="7"/>
+      <c r="K336" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="4">
@@ -10180,15 +10180,15 @@
       <c r="D337" s="4">
         <v>52000.0</v>
       </c>
-      <c r="E337" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E337" s="7"/>
       <c r="F337" s="7"/>
       <c r="G337" s="7"/>
       <c r="H337" s="7"/>
       <c r="I337" s="7"/>
       <c r="J337" s="7"/>
-      <c r="K337" s="7"/>
+      <c r="K337" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="4">
@@ -10204,15 +10204,15 @@
       <c r="D338" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E338" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E338" s="7"/>
       <c r="F338" s="7"/>
       <c r="G338" s="7"/>
       <c r="H338" s="7"/>
       <c r="I338" s="7"/>
       <c r="J338" s="7"/>
-      <c r="K338" s="7"/>
+      <c r="K338" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="4">
@@ -10228,15 +10228,15 @@
       <c r="D339" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E339" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E339" s="7"/>
       <c r="F339" s="7"/>
       <c r="G339" s="7"/>
       <c r="H339" s="7"/>
       <c r="I339" s="7"/>
       <c r="J339" s="7"/>
-      <c r="K339" s="7"/>
+      <c r="K339" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="4">
@@ -10252,19 +10252,19 @@
       <c r="D340" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E340" s="4" t="s">
-        <v>13</v>
+      <c r="E340" s="4">
+        <v>10.0</v>
       </c>
       <c r="F340" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="G340" s="4">
         <v>17000.0</v>
       </c>
+      <c r="G340" s="7"/>
       <c r="H340" s="7"/>
       <c r="I340" s="7"/>
       <c r="J340" s="7"/>
-      <c r="K340" s="7"/>
+      <c r="K340" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="4">
@@ -10280,15 +10280,15 @@
       <c r="D341" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E341" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E341" s="7"/>
       <c r="F341" s="7"/>
       <c r="G341" s="7"/>
       <c r="H341" s="7"/>
       <c r="I341" s="7"/>
       <c r="J341" s="7"/>
-      <c r="K341" s="7"/>
+      <c r="K341" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="4">
@@ -10304,19 +10304,19 @@
       <c r="D342" s="4">
         <v>7000.0</v>
       </c>
-      <c r="E342" s="4" t="s">
-        <v>13</v>
+      <c r="E342" s="4">
+        <v>5.0</v>
       </c>
       <c r="F342" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G342" s="4">
         <v>32500.0</v>
       </c>
+      <c r="G342" s="7"/>
       <c r="H342" s="7"/>
       <c r="I342" s="7"/>
       <c r="J342" s="7"/>
-      <c r="K342" s="7"/>
+      <c r="K342" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="4">
@@ -10332,15 +10332,15 @@
       <c r="D343" s="4">
         <v>7500.0</v>
       </c>
-      <c r="E343" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E343" s="7"/>
       <c r="F343" s="7"/>
       <c r="G343" s="7"/>
       <c r="H343" s="7"/>
       <c r="I343" s="7"/>
       <c r="J343" s="7"/>
-      <c r="K343" s="7"/>
+      <c r="K343" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="4">
@@ -10356,15 +10356,15 @@
       <c r="D344" s="4">
         <v>9500.0</v>
       </c>
-      <c r="E344" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E344" s="7"/>
       <c r="F344" s="7"/>
       <c r="G344" s="7"/>
       <c r="H344" s="7"/>
       <c r="I344" s="7"/>
       <c r="J344" s="7"/>
-      <c r="K344" s="7"/>
+      <c r="K344" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="4">
@@ -10380,15 +10380,15 @@
       <c r="D345" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E345" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E345" s="7"/>
       <c r="F345" s="7"/>
       <c r="G345" s="7"/>
       <c r="H345" s="7"/>
       <c r="I345" s="7"/>
       <c r="J345" s="7"/>
-      <c r="K345" s="7"/>
+      <c r="K345" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="4">
@@ -10404,15 +10404,15 @@
       <c r="D346" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E346" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E346" s="7"/>
       <c r="F346" s="7"/>
       <c r="G346" s="7"/>
       <c r="H346" s="7"/>
       <c r="I346" s="7"/>
       <c r="J346" s="7"/>
-      <c r="K346" s="7"/>
+      <c r="K346" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="4">
@@ -10428,19 +10428,19 @@
       <c r="D347" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E347" s="4" t="s">
-        <v>13</v>
+      <c r="E347" s="4">
+        <v>5.0</v>
       </c>
       <c r="F347" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G347" s="4">
         <v>22500.0</v>
       </c>
+      <c r="G347" s="7"/>
       <c r="H347" s="7"/>
       <c r="I347" s="7"/>
       <c r="J347" s="7"/>
-      <c r="K347" s="7"/>
+      <c r="K347" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="4">
@@ -10456,19 +10456,19 @@
       <c r="D348" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E348" s="4" t="s">
-        <v>13</v>
+      <c r="E348" s="4">
+        <v>5.0</v>
       </c>
       <c r="F348" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G348" s="4">
         <v>12500.0</v>
       </c>
+      <c r="G348" s="7"/>
       <c r="H348" s="7"/>
       <c r="I348" s="7"/>
       <c r="J348" s="7"/>
-      <c r="K348" s="7"/>
+      <c r="K348" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="4">
@@ -10484,15 +10484,15 @@
       <c r="D349" s="4">
         <v>3500.0</v>
       </c>
-      <c r="E349" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E349" s="4"/>
       <c r="F349" s="4"/>
-      <c r="G349" s="4"/>
+      <c r="G349" s="7"/>
       <c r="H349" s="7"/>
       <c r="I349" s="7"/>
       <c r="J349" s="7"/>
-      <c r="K349" s="7"/>
+      <c r="K349" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="4">
@@ -10508,15 +10508,15 @@
       <c r="D350" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E350" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E350" s="4"/>
       <c r="F350" s="4"/>
       <c r="G350" s="4"/>
-      <c r="H350" s="4"/>
+      <c r="H350" s="7"/>
       <c r="I350" s="7"/>
       <c r="J350" s="7"/>
-      <c r="K350" s="7"/>
+      <c r="K350" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="4">
@@ -10532,19 +10532,19 @@
       <c r="D351" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E351" s="4" t="s">
-        <v>13</v>
+      <c r="E351" s="4">
+        <v>5.0</v>
       </c>
       <c r="F351" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G351" s="4">
         <v>11500.0</v>
       </c>
+      <c r="G351" s="7"/>
       <c r="H351" s="7"/>
       <c r="I351" s="7"/>
       <c r="J351" s="7"/>
-      <c r="K351" s="7"/>
+      <c r="K351" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="4">
@@ -10560,15 +10560,15 @@
       <c r="D352" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E352" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E352" s="7"/>
       <c r="F352" s="7"/>
       <c r="G352" s="7"/>
       <c r="H352" s="7"/>
       <c r="I352" s="7"/>
       <c r="J352" s="7"/>
-      <c r="K352" s="7"/>
+      <c r="K352" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="4">
@@ -10584,19 +10584,19 @@
       <c r="D353" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E353" s="4" t="s">
-        <v>13</v>
+      <c r="E353" s="4">
+        <v>5.0</v>
       </c>
       <c r="F353" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="G353" s="4">
         <v>22500.0</v>
       </c>
+      <c r="G353" s="7"/>
       <c r="H353" s="7"/>
       <c r="I353" s="7"/>
       <c r="J353" s="7"/>
-      <c r="K353" s="7"/>
+      <c r="K353" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="4">
@@ -10612,15 +10612,15 @@
       <c r="D354" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E354" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E354" s="7"/>
       <c r="F354" s="7"/>
       <c r="G354" s="7"/>
       <c r="H354" s="7"/>
       <c r="I354" s="7"/>
       <c r="J354" s="7"/>
-      <c r="K354" s="7"/>
+      <c r="K354" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="4">
@@ -10636,15 +10636,15 @@
       <c r="D355" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E355" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E355" s="7"/>
       <c r="F355" s="7"/>
       <c r="G355" s="7"/>
       <c r="H355" s="7"/>
       <c r="I355" s="7"/>
       <c r="J355" s="7"/>
-      <c r="K355" s="7"/>
+      <c r="K355" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="4">
@@ -10660,15 +10660,15 @@
       <c r="D356" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E356" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E356" s="7"/>
       <c r="F356" s="7"/>
       <c r="G356" s="7"/>
       <c r="H356" s="7"/>
       <c r="I356" s="7"/>
       <c r="J356" s="7"/>
-      <c r="K356" s="7"/>
+      <c r="K356" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="4">
@@ -10684,15 +10684,15 @@
       <c r="D357" s="4">
         <v>14000.0</v>
       </c>
-      <c r="E357" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E357" s="7"/>
       <c r="F357" s="7"/>
       <c r="G357" s="7"/>
       <c r="H357" s="7"/>
       <c r="I357" s="7"/>
       <c r="J357" s="7"/>
-      <c r="K357" s="7"/>
+      <c r="K357" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="4">
@@ -10708,15 +10708,15 @@
       <c r="D358" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E358" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E358" s="7"/>
       <c r="F358" s="7"/>
       <c r="G358" s="7"/>
       <c r="H358" s="7"/>
       <c r="I358" s="7"/>
       <c r="J358" s="7"/>
-      <c r="K358" s="7"/>
+      <c r="K358" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="4">
@@ -10732,15 +10732,15 @@
       <c r="D359" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E359" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E359" s="7"/>
       <c r="F359" s="7"/>
       <c r="G359" s="7"/>
       <c r="H359" s="7"/>
       <c r="I359" s="7"/>
       <c r="J359" s="7"/>
-      <c r="K359" s="7"/>
+      <c r="K359" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="4">
@@ -10756,15 +10756,15 @@
       <c r="D360" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E360" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E360" s="7"/>
       <c r="F360" s="7"/>
       <c r="G360" s="7"/>
       <c r="H360" s="7"/>
       <c r="I360" s="7"/>
       <c r="J360" s="7"/>
-      <c r="K360" s="7"/>
+      <c r="K360" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="4">
@@ -10780,15 +10780,15 @@
       <c r="D361" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E361" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E361" s="7"/>
       <c r="F361" s="7"/>
       <c r="G361" s="7"/>
       <c r="H361" s="7"/>
       <c r="I361" s="7"/>
       <c r="J361" s="7"/>
-      <c r="K361" s="7"/>
+      <c r="K361" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="4">
@@ -10804,15 +10804,15 @@
       <c r="D362" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E362" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E362" s="7"/>
       <c r="F362" s="7"/>
       <c r="G362" s="7"/>
       <c r="H362" s="7"/>
       <c r="I362" s="7"/>
       <c r="J362" s="7"/>
-      <c r="K362" s="7"/>
+      <c r="K362" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="4">
@@ -10828,15 +10828,15 @@
       <c r="D363" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E363" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E363" s="7"/>
       <c r="F363" s="7"/>
       <c r="G363" s="7"/>
       <c r="H363" s="7"/>
       <c r="I363" s="7"/>
       <c r="J363" s="7"/>
-      <c r="K363" s="7"/>
+      <c r="K363" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="4">
@@ -10852,15 +10852,15 @@
       <c r="D364" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E364" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E364" s="7"/>
       <c r="F364" s="7"/>
       <c r="G364" s="7"/>
       <c r="H364" s="7"/>
       <c r="I364" s="7"/>
       <c r="J364" s="7"/>
-      <c r="K364" s="7"/>
+      <c r="K364" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="4">
@@ -10876,15 +10876,15 @@
       <c r="D365" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E365" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E365" s="7"/>
       <c r="F365" s="7"/>
       <c r="G365" s="7"/>
       <c r="H365" s="7"/>
       <c r="I365" s="7"/>
       <c r="J365" s="7"/>
-      <c r="K365" s="7"/>
+      <c r="K365" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="4">
@@ -10900,15 +10900,15 @@
       <c r="D366" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E366" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E366" s="7"/>
       <c r="F366" s="7"/>
       <c r="G366" s="7"/>
       <c r="H366" s="7"/>
       <c r="I366" s="7"/>
       <c r="J366" s="7"/>
-      <c r="K366" s="7"/>
+      <c r="K366" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="4">
@@ -10924,15 +10924,15 @@
       <c r="D367" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E367" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E367" s="7"/>
       <c r="F367" s="7"/>
       <c r="G367" s="7"/>
       <c r="H367" s="7"/>
       <c r="I367" s="7"/>
       <c r="J367" s="7"/>
-      <c r="K367" s="7"/>
+      <c r="K367" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="4">
@@ -10948,15 +10948,15 @@
       <c r="D368" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E368" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E368" s="7"/>
       <c r="F368" s="7"/>
       <c r="G368" s="7"/>
       <c r="H368" s="7"/>
       <c r="I368" s="7"/>
       <c r="J368" s="7"/>
-      <c r="K368" s="7"/>
+      <c r="K368" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="4">
@@ -10972,19 +10972,19 @@
       <c r="D369" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E369" s="4" t="s">
-        <v>13</v>
+      <c r="E369" s="4">
+        <v>4.0</v>
       </c>
       <c r="F369" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="G369" s="4">
         <v>3000.0</v>
       </c>
+      <c r="G369" s="7"/>
       <c r="H369" s="7"/>
       <c r="I369" s="7"/>
       <c r="J369" s="7"/>
-      <c r="K369" s="7"/>
+      <c r="K369" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="4">
@@ -11000,15 +11000,15 @@
       <c r="D370" s="4">
         <v>500.0</v>
       </c>
-      <c r="E370" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E370" s="7"/>
       <c r="F370" s="7"/>
       <c r="G370" s="7"/>
       <c r="H370" s="7"/>
       <c r="I370" s="7"/>
       <c r="J370" s="7"/>
-      <c r="K370" s="7"/>
+      <c r="K370" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="4">
@@ -11024,15 +11024,15 @@
       <c r="D371" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E371" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E371" s="7"/>
       <c r="F371" s="7"/>
       <c r="G371" s="7"/>
       <c r="H371" s="7"/>
       <c r="I371" s="7"/>
       <c r="J371" s="7"/>
-      <c r="K371" s="7"/>
+      <c r="K371" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="4">
@@ -11048,15 +11048,15 @@
       <c r="D372" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E372" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E372" s="7"/>
       <c r="F372" s="7"/>
       <c r="G372" s="7"/>
       <c r="H372" s="7"/>
       <c r="I372" s="7"/>
       <c r="J372" s="7"/>
-      <c r="K372" s="7"/>
+      <c r="K372" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="4">
@@ -11072,15 +11072,15 @@
       <c r="D373" s="4">
         <v>7000.0</v>
       </c>
-      <c r="E373" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E373" s="7"/>
       <c r="F373" s="7"/>
       <c r="G373" s="7"/>
       <c r="H373" s="7"/>
       <c r="I373" s="7"/>
       <c r="J373" s="7"/>
-      <c r="K373" s="7"/>
+      <c r="K373" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="4">
@@ -11096,15 +11096,15 @@
       <c r="D374" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E374" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E374" s="7"/>
       <c r="F374" s="7"/>
       <c r="G374" s="7"/>
       <c r="H374" s="7"/>
       <c r="I374" s="7"/>
       <c r="J374" s="7"/>
-      <c r="K374" s="7"/>
+      <c r="K374" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="4">
@@ -11120,15 +11120,15 @@
       <c r="D375" s="4">
         <v>25000.0</v>
       </c>
-      <c r="E375" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E375" s="7"/>
       <c r="F375" s="7"/>
       <c r="G375" s="7"/>
       <c r="H375" s="7"/>
       <c r="I375" s="7"/>
       <c r="J375" s="7"/>
-      <c r="K375" s="7"/>
+      <c r="K375" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="4">
@@ -11144,15 +11144,15 @@
       <c r="D376" s="4">
         <v>8000.0</v>
       </c>
-      <c r="E376" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E376" s="7"/>
       <c r="F376" s="7"/>
       <c r="G376" s="7"/>
       <c r="H376" s="7"/>
       <c r="I376" s="7"/>
       <c r="J376" s="7"/>
-      <c r="K376" s="7"/>
+      <c r="K376" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="4">
@@ -11168,15 +11168,15 @@
       <c r="D377" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E377" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E377" s="7"/>
       <c r="F377" s="7"/>
       <c r="G377" s="7"/>
       <c r="H377" s="7"/>
       <c r="I377" s="7"/>
       <c r="J377" s="7"/>
-      <c r="K377" s="7"/>
+      <c r="K377" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="4">
@@ -11192,15 +11192,15 @@
       <c r="D378" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E378" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E378" s="7"/>
       <c r="F378" s="7"/>
       <c r="G378" s="7"/>
       <c r="H378" s="7"/>
       <c r="I378" s="7"/>
       <c r="J378" s="7"/>
-      <c r="K378" s="7"/>
+      <c r="K378" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="4">
@@ -11216,15 +11216,15 @@
       <c r="D379" s="4">
         <v>45000.0</v>
       </c>
-      <c r="E379" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E379" s="7"/>
       <c r="F379" s="7"/>
       <c r="G379" s="7"/>
       <c r="H379" s="7"/>
       <c r="I379" s="7"/>
       <c r="J379" s="7"/>
-      <c r="K379" s="7"/>
+      <c r="K379" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="4">
@@ -11240,15 +11240,15 @@
       <c r="D380" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E380" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E380" s="7"/>
       <c r="F380" s="7"/>
       <c r="G380" s="7"/>
       <c r="H380" s="7"/>
       <c r="I380" s="7"/>
       <c r="J380" s="7"/>
-      <c r="K380" s="7"/>
+      <c r="K380" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="4">
@@ -11264,15 +11264,15 @@
       <c r="D381" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E381" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E381" s="7"/>
       <c r="F381" s="7"/>
       <c r="G381" s="7"/>
       <c r="H381" s="7"/>
       <c r="I381" s="7"/>
       <c r="J381" s="7"/>
-      <c r="K381" s="7"/>
+      <c r="K381" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="4">
@@ -11288,15 +11288,15 @@
       <c r="D382" s="4">
         <v>4000.0</v>
       </c>
-      <c r="E382" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E382" s="7"/>
       <c r="F382" s="7"/>
       <c r="G382" s="7"/>
       <c r="H382" s="7"/>
       <c r="I382" s="7"/>
       <c r="J382" s="7"/>
-      <c r="K382" s="7"/>
+      <c r="K382" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="4">
@@ -11312,15 +11312,15 @@
       <c r="D383" s="4">
         <v>40000.0</v>
       </c>
-      <c r="E383" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E383" s="7"/>
       <c r="F383" s="7"/>
       <c r="G383" s="7"/>
       <c r="H383" s="7"/>
       <c r="I383" s="7"/>
       <c r="J383" s="7"/>
-      <c r="K383" s="7"/>
+      <c r="K383" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="4">
@@ -11336,15 +11336,15 @@
       <c r="D384" s="4">
         <v>5000.0</v>
       </c>
-      <c r="E384" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E384" s="7"/>
       <c r="F384" s="7"/>
       <c r="G384" s="7"/>
       <c r="H384" s="7"/>
       <c r="I384" s="7"/>
       <c r="J384" s="7"/>
-      <c r="K384" s="7"/>
+      <c r="K384" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="4">
@@ -11360,15 +11360,15 @@
       <c r="D385" s="4">
         <v>46000.0</v>
       </c>
-      <c r="E385" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E385" s="7"/>
       <c r="F385" s="7"/>
       <c r="G385" s="7"/>
       <c r="H385" s="7"/>
-      <c r="I385" s="7"/>
-      <c r="J385" s="4"/>
-      <c r="K385" s="7"/>
+      <c r="I385" s="4"/>
+      <c r="J385" s="7"/>
+      <c r="K385" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="4">
@@ -11384,15 +11384,15 @@
       <c r="D386" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E386" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E386" s="7"/>
       <c r="F386" s="7"/>
       <c r="G386" s="7"/>
       <c r="H386" s="7"/>
-      <c r="I386" s="7"/>
-      <c r="J386" s="4"/>
-      <c r="K386" s="7"/>
+      <c r="I386" s="4"/>
+      <c r="J386" s="7"/>
+      <c r="K386" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="4">
@@ -11408,15 +11408,15 @@
       <c r="D387" s="4">
         <v>17000.0</v>
       </c>
-      <c r="E387" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E387" s="7"/>
       <c r="F387" s="7"/>
       <c r="G387" s="7"/>
       <c r="H387" s="7"/>
-      <c r="I387" s="7"/>
-      <c r="J387" s="4"/>
-      <c r="K387" s="7"/>
+      <c r="I387" s="4"/>
+      <c r="J387" s="7"/>
+      <c r="K387" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="4">
@@ -11432,15 +11432,15 @@
       <c r="D388" s="4">
         <v>500.0</v>
       </c>
-      <c r="E388" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E388" s="7"/>
       <c r="F388" s="7"/>
       <c r="G388" s="7"/>
       <c r="H388" s="7"/>
-      <c r="I388" s="7"/>
-      <c r="J388" s="4"/>
-      <c r="K388" s="7"/>
+      <c r="I388" s="4"/>
+      <c r="J388" s="7"/>
+      <c r="K388" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="4">
@@ -11456,15 +11456,15 @@
       <c r="D389" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E389" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E389" s="7"/>
       <c r="F389" s="7"/>
       <c r="G389" s="7"/>
       <c r="H389" s="7"/>
       <c r="I389" s="7"/>
       <c r="J389" s="7"/>
-      <c r="K389" s="7"/>
+      <c r="K389" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="4">
@@ -11480,15 +11480,15 @@
       <c r="D390" s="4">
         <v>10000.0</v>
       </c>
-      <c r="E390" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E390" s="7"/>
       <c r="F390" s="7"/>
       <c r="G390" s="7"/>
       <c r="H390" s="7"/>
       <c r="I390" s="7"/>
       <c r="J390" s="7"/>
-      <c r="K390" s="7"/>
+      <c r="K390" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="4">
@@ -11504,15 +11504,15 @@
       <c r="D391" s="4">
         <v>500.0</v>
       </c>
-      <c r="E391" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E391" s="7"/>
       <c r="F391" s="7"/>
       <c r="G391" s="7"/>
       <c r="H391" s="7"/>
       <c r="I391" s="7"/>
       <c r="J391" s="7"/>
-      <c r="K391" s="7"/>
+      <c r="K391" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="4">
@@ -11528,15 +11528,15 @@
       <c r="D392" s="4">
         <v>1500.0</v>
       </c>
-      <c r="E392" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E392" s="7"/>
       <c r="F392" s="7"/>
       <c r="G392" s="7"/>
       <c r="H392" s="7"/>
       <c r="I392" s="7"/>
       <c r="J392" s="7"/>
-      <c r="K392" s="7"/>
+      <c r="K392" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="4">
@@ -11552,15 +11552,15 @@
       <c r="D393" s="4">
         <v>12000.0</v>
       </c>
-      <c r="E393" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E393" s="7"/>
       <c r="F393" s="7"/>
       <c r="G393" s="7"/>
       <c r="H393" s="7"/>
       <c r="I393" s="7"/>
       <c r="J393" s="7"/>
-      <c r="K393" s="7"/>
+      <c r="K393" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="4">
@@ -11576,15 +11576,15 @@
       <c r="D394" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E394" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E394" s="7"/>
       <c r="F394" s="7"/>
       <c r="G394" s="7"/>
       <c r="H394" s="7"/>
       <c r="I394" s="7"/>
       <c r="J394" s="7"/>
-      <c r="K394" s="7"/>
+      <c r="K394" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="4">
@@ -11600,15 +11600,15 @@
       <c r="D395" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E395" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E395" s="7"/>
       <c r="F395" s="7"/>
       <c r="G395" s="7"/>
       <c r="H395" s="7"/>
       <c r="I395" s="7"/>
       <c r="J395" s="7"/>
-      <c r="K395" s="7"/>
+      <c r="K395" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="4">
@@ -11624,15 +11624,15 @@
       <c r="D396" s="4">
         <v>25000.0</v>
       </c>
-      <c r="E396" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E396" s="7"/>
       <c r="F396" s="7"/>
       <c r="G396" s="7"/>
       <c r="H396" s="7"/>
       <c r="I396" s="7"/>
       <c r="J396" s="7"/>
-      <c r="K396" s="7"/>
+      <c r="K396" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="4">
@@ -11648,15 +11648,15 @@
       <c r="D397" s="4">
         <v>9000.0</v>
       </c>
-      <c r="E397" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E397" s="7"/>
       <c r="F397" s="7"/>
       <c r="G397" s="7"/>
       <c r="H397" s="7"/>
       <c r="I397" s="7"/>
       <c r="J397" s="7"/>
-      <c r="K397" s="7"/>
+      <c r="K397" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="4">
@@ -11672,15 +11672,15 @@
       <c r="D398" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E398" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F398" s="4"/>
+      <c r="E398" s="4"/>
+      <c r="F398" s="7"/>
       <c r="G398" s="7"/>
       <c r="H398" s="7"/>
       <c r="I398" s="7"/>
       <c r="J398" s="7"/>
-      <c r="K398" s="7"/>
+      <c r="K398" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="4">
@@ -11696,15 +11696,15 @@
       <c r="D399" s="4">
         <v>9000.0</v>
       </c>
-      <c r="E399" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E399" s="7"/>
       <c r="F399" s="7"/>
       <c r="G399" s="7"/>
       <c r="H399" s="7"/>
       <c r="I399" s="7"/>
       <c r="J399" s="7"/>
-      <c r="K399" s="7"/>
+      <c r="K399" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="4">
@@ -11720,15 +11720,15 @@
       <c r="D400" s="4">
         <v>4500.0</v>
       </c>
-      <c r="E400" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E400" s="7"/>
       <c r="F400" s="7"/>
       <c r="G400" s="7"/>
       <c r="H400" s="7"/>
       <c r="I400" s="7"/>
       <c r="J400" s="7"/>
-      <c r="K400" s="7"/>
+      <c r="K400" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="4">
@@ -11744,15 +11744,15 @@
       <c r="D401" s="4">
         <v>500.0</v>
       </c>
-      <c r="E401" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E401" s="7"/>
       <c r="F401" s="7"/>
       <c r="G401" s="7"/>
       <c r="H401" s="7"/>
       <c r="I401" s="7"/>
       <c r="J401" s="7"/>
-      <c r="K401" s="7"/>
+      <c r="K401" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="4">
@@ -11768,15 +11768,15 @@
       <c r="D402" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E402" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E402" s="7"/>
       <c r="F402" s="7"/>
       <c r="G402" s="7"/>
       <c r="H402" s="7"/>
       <c r="I402" s="7"/>
       <c r="J402" s="7"/>
-      <c r="K402" s="7"/>
+      <c r="K402" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="4">
@@ -11792,15 +11792,15 @@
       <c r="D403" s="4">
         <v>1000.0</v>
       </c>
-      <c r="E403" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E403" s="7"/>
       <c r="F403" s="7"/>
       <c r="G403" s="7"/>
       <c r="H403" s="7"/>
       <c r="I403" s="7"/>
       <c r="J403" s="7"/>
-      <c r="K403" s="7"/>
+      <c r="K403" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="4">
@@ -11816,15 +11816,15 @@
       <c r="D404" s="10">
         <v>4500.0</v>
       </c>
-      <c r="E404" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E404" s="11"/>
       <c r="F404" s="11"/>
       <c r="G404" s="11"/>
       <c r="H404" s="11"/>
       <c r="I404" s="11"/>
       <c r="J404" s="11"/>
-      <c r="K404" s="11"/>
+      <c r="K404" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="4">
@@ -11840,15 +11840,15 @@
       <c r="D405" s="10">
         <v>50000.0</v>
       </c>
-      <c r="E405" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E405" s="11"/>
       <c r="F405" s="11"/>
       <c r="G405" s="11"/>
       <c r="H405" s="11"/>
       <c r="I405" s="11"/>
       <c r="J405" s="11"/>
-      <c r="K405" s="11"/>
+      <c r="K405" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="4">
@@ -11864,15 +11864,15 @@
       <c r="D406" s="10">
         <v>12000.0</v>
       </c>
-      <c r="E406" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E406" s="11"/>
       <c r="F406" s="11"/>
       <c r="G406" s="11"/>
       <c r="H406" s="11"/>
       <c r="I406" s="11"/>
       <c r="J406" s="11"/>
-      <c r="K406" s="11"/>
+      <c r="K406" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="4">
@@ -11888,15 +11888,15 @@
       <c r="D407" s="10">
         <v>4500.0</v>
       </c>
-      <c r="E407" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E407" s="11"/>
       <c r="F407" s="11"/>
       <c r="G407" s="11"/>
       <c r="H407" s="11"/>
       <c r="I407" s="11"/>
       <c r="J407" s="11"/>
-      <c r="K407" s="11"/>
+      <c r="K407" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="4">
@@ -11912,15 +11912,15 @@
       <c r="D408" s="10">
         <v>3000.0</v>
       </c>
-      <c r="E408" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E408" s="11"/>
       <c r="F408" s="11"/>
       <c r="G408" s="11"/>
       <c r="H408" s="11"/>
       <c r="I408" s="11"/>
       <c r="J408" s="11"/>
-      <c r="K408" s="11"/>
+      <c r="K408" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="4">
@@ -11936,15 +11936,15 @@
       <c r="D409" s="10">
         <v>5000.0</v>
       </c>
-      <c r="E409" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E409" s="11"/>
       <c r="F409" s="11"/>
       <c r="G409" s="11"/>
       <c r="H409" s="11"/>
       <c r="I409" s="11"/>
       <c r="J409" s="11"/>
-      <c r="K409" s="11"/>
+      <c r="K409" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="4">
@@ -11960,15 +11960,15 @@
       <c r="D410" s="10">
         <v>6000.0</v>
       </c>
-      <c r="E410" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E410" s="11"/>
       <c r="F410" s="11"/>
       <c r="G410" s="11"/>
       <c r="H410" s="11"/>
       <c r="I410" s="11"/>
       <c r="J410" s="11"/>
-      <c r="K410" s="11"/>
+      <c r="K410" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="4">
@@ -11984,15 +11984,15 @@
       <c r="D411" s="10">
         <v>12000.0</v>
       </c>
-      <c r="E411" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E411" s="11"/>
       <c r="F411" s="11"/>
       <c r="G411" s="11"/>
       <c r="H411" s="11"/>
       <c r="I411" s="11"/>
       <c r="J411" s="11"/>
-      <c r="K411" s="11"/>
+      <c r="K411" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="4">
@@ -12008,15 +12008,15 @@
       <c r="D412" s="10">
         <v>200.0</v>
       </c>
-      <c r="E412" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E412" s="10"/>
       <c r="F412" s="10"/>
-      <c r="G412" s="10"/>
+      <c r="G412" s="11"/>
       <c r="H412" s="11"/>
       <c r="I412" s="11"/>
       <c r="J412" s="11"/>
-      <c r="K412" s="11"/>
+      <c r="K412" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="4">
@@ -12032,19 +12032,19 @@
       <c r="D413" s="10">
         <v>5000.0</v>
       </c>
-      <c r="E413" s="4" t="s">
-        <v>13</v>
+      <c r="E413" s="10">
+        <v>2.0</v>
       </c>
       <c r="F413" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="G413" s="10">
         <v>4500.0</v>
       </c>
+      <c r="G413" s="11"/>
       <c r="H413" s="11"/>
       <c r="I413" s="11"/>
       <c r="J413" s="11"/>
-      <c r="K413" s="11"/>
+      <c r="K413" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="4">
@@ -12060,15 +12060,15 @@
       <c r="D414" s="10">
         <v>18000.0</v>
       </c>
-      <c r="E414" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E414" s="11"/>
       <c r="F414" s="11"/>
       <c r="G414" s="11"/>
       <c r="H414" s="11"/>
       <c r="I414" s="11"/>
       <c r="J414" s="11"/>
-      <c r="K414" s="11"/>
+      <c r="K414" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="4">
@@ -12084,15 +12084,15 @@
       <c r="D415" s="10">
         <v>17000.0</v>
       </c>
-      <c r="E415" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E415" s="11"/>
       <c r="F415" s="11"/>
       <c r="G415" s="11"/>
       <c r="H415" s="11"/>
       <c r="I415" s="11"/>
       <c r="J415" s="11"/>
-      <c r="K415" s="11"/>
+      <c r="K415" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="4">
@@ -12108,15 +12108,15 @@
       <c r="D416" s="10">
         <v>17500.0</v>
       </c>
-      <c r="E416" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E416" s="11"/>
       <c r="F416" s="11"/>
       <c r="G416" s="11"/>
       <c r="H416" s="11"/>
       <c r="I416" s="11"/>
       <c r="J416" s="11"/>
-      <c r="K416" s="11"/>
+      <c r="K416" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="4">
@@ -12132,15 +12132,15 @@
       <c r="D417" s="10">
         <v>9000.0</v>
       </c>
-      <c r="E417" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E417" s="11"/>
       <c r="F417" s="11"/>
       <c r="G417" s="11"/>
       <c r="H417" s="11"/>
       <c r="I417" s="11"/>
       <c r="J417" s="11"/>
-      <c r="K417" s="11"/>
+      <c r="K417" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="4">
@@ -12156,15 +12156,15 @@
       <c r="D418" s="10">
         <v>9000.0</v>
       </c>
-      <c r="E418" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E418" s="11"/>
       <c r="F418" s="11"/>
       <c r="G418" s="11"/>
       <c r="H418" s="11"/>
       <c r="I418" s="11"/>
       <c r="J418" s="11"/>
-      <c r="K418" s="11"/>
+      <c r="K418" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="4">
@@ -12180,15 +12180,15 @@
       <c r="D419" s="10">
         <v>9000.0</v>
       </c>
-      <c r="E419" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E419" s="11"/>
       <c r="F419" s="11"/>
       <c r="G419" s="11"/>
       <c r="H419" s="11"/>
       <c r="I419" s="11"/>
       <c r="J419" s="11"/>
-      <c r="K419" s="11"/>
+      <c r="K419" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="4">
@@ -12204,15 +12204,15 @@
       <c r="D420" s="10">
         <v>19500.0</v>
       </c>
-      <c r="E420" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E420" s="11"/>
       <c r="F420" s="11"/>
       <c r="G420" s="11"/>
       <c r="H420" s="11"/>
       <c r="I420" s="11"/>
       <c r="J420" s="11"/>
-      <c r="K420" s="11"/>
+      <c r="K420" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="4">
@@ -12228,15 +12228,15 @@
       <c r="D421" s="10">
         <v>8500.0</v>
       </c>
-      <c r="E421" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E421" s="11"/>
       <c r="F421" s="11"/>
       <c r="G421" s="11"/>
       <c r="H421" s="11"/>
       <c r="I421" s="11"/>
       <c r="J421" s="11"/>
-      <c r="K421" s="11"/>
+      <c r="K421" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="4">
@@ -12252,15 +12252,15 @@
       <c r="D422" s="10">
         <v>4500.0</v>
       </c>
-      <c r="E422" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E422" s="11"/>
       <c r="F422" s="11"/>
       <c r="G422" s="11"/>
       <c r="H422" s="11"/>
       <c r="I422" s="11"/>
       <c r="J422" s="11"/>
-      <c r="K422" s="11"/>
+      <c r="K422" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="4">
@@ -12276,15 +12276,15 @@
       <c r="D423" s="10">
         <v>9000.0</v>
       </c>
-      <c r="E423" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E423" s="11"/>
       <c r="F423" s="11"/>
       <c r="G423" s="11"/>
       <c r="H423" s="11"/>
       <c r="I423" s="11"/>
       <c r="J423" s="11"/>
-      <c r="K423" s="11"/>
+      <c r="K423" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="4">
@@ -12300,15 +12300,15 @@
       <c r="D424" s="10">
         <v>14000.0</v>
       </c>
-      <c r="E424" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E424" s="11"/>
       <c r="F424" s="11"/>
       <c r="G424" s="11"/>
       <c r="H424" s="11"/>
       <c r="I424" s="11"/>
       <c r="J424" s="11"/>
-      <c r="K424" s="11"/>
+      <c r="K424" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="4">
@@ -12324,15 +12324,15 @@
       <c r="D425" s="10">
         <v>3000.0</v>
       </c>
-      <c r="E425" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E425" s="11"/>
       <c r="F425" s="11"/>
       <c r="G425" s="11"/>
       <c r="H425" s="11"/>
       <c r="I425" s="11"/>
       <c r="J425" s="11"/>
-      <c r="K425" s="11"/>
+      <c r="K425" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="4">
@@ -12348,15 +12348,15 @@
       <c r="D426" s="10">
         <v>12000.0</v>
       </c>
-      <c r="E426" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E426" s="11"/>
       <c r="F426" s="11"/>
       <c r="G426" s="11"/>
       <c r="H426" s="11"/>
       <c r="I426" s="11"/>
       <c r="J426" s="11"/>
-      <c r="K426" s="11"/>
+      <c r="K426" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="4">
@@ -12372,15 +12372,15 @@
       <c r="D427" s="10">
         <v>20000.0</v>
       </c>
-      <c r="E427" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E427" s="11"/>
       <c r="F427" s="11"/>
       <c r="G427" s="11"/>
       <c r="H427" s="11"/>
       <c r="I427" s="11"/>
       <c r="J427" s="11"/>
-      <c r="K427" s="11"/>
+      <c r="K427" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="12"/>
@@ -22611,7 +22611,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C427">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E427">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K427">
       <formula1>"Ecer,KRT"</formula1>
     </dataValidation>
   </dataValidations>
@@ -22648,22 +22648,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -1358,16 +1358,16 @@
     <t>Djarum Coklat SLOP</t>
   </si>
   <si>
-    <t>Djarum Coklat Elite Bungkus</t>
+    <t>Djarum Coklat Elite</t>
   </si>
   <si>
     <t>Djarum Coklat Elite SLOP</t>
   </si>
   <si>
-    <t>76 Apel Bungkus SLOP</t>
-  </si>
-  <si>
-    <t>Djarum Super Bungkus SLOP</t>
+    <t>76 Apel SLOP</t>
+  </si>
+  <si>
+    <t>Djarum Super SLOP</t>
   </si>
   <si>
     <t>Magnum Bintang SLOP</t>
@@ -1820,10 +1820,10 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="13.0"/>
     <col customWidth="1" min="2" max="2" width="35.13"/>
-    <col customWidth="1" hidden="1" min="3" max="3" width="15.75"/>
-    <col customWidth="1" hidden="1" min="4" max="4" width="14.75"/>
-    <col customWidth="1" hidden="1" min="5" max="5" width="15.88"/>
-    <col customWidth="1" hidden="1" min="6" max="10" width="13.13"/>
+    <col customWidth="1" min="3" max="3" width="15.75"/>
+    <col customWidth="1" min="4" max="4" width="14.75"/>
+    <col customWidth="1" min="5" max="5" width="15.88"/>
+    <col customWidth="1" min="6" max="10" width="13.13"/>
     <col customWidth="1" min="11" max="11" width="9.38"/>
   </cols>
   <sheetData>
@@ -22679,7 +22679,7 @@
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4">
@@ -22767,7 +22767,7 @@
         <v>GROSIR5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="4">
@@ -22811,7 +22811,7 @@
         <v>GROSIR7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="4">
@@ -22855,7 +22855,7 @@
         <v>GROSIR9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$429</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$430</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$262</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="490">
   <si>
     <t>Barcode</t>
   </si>
@@ -1361,6 +1361,9 @@
     <t>Cat Choize</t>
   </si>
   <si>
+    <t>Mixagrip Flu dan Batuk</t>
+  </si>
+  <si>
     <t>Djarum Coklat SLOP</t>
   </si>
   <si>
@@ -1479,6 +1482,9 @@
   </si>
   <si>
     <t>Kilau Nipis 2000 Beli 2 Gratis 1</t>
+  </si>
+  <si>
+    <t>Mixagrip Flu Batuk</t>
   </si>
 </sst>
 </file>
@@ -1898,7 +1904,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A429" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A430" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -12468,17 +12474,28 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="18"/>
-      <c r="B430" s="18"/>
-      <c r="C430" s="18"/>
-      <c r="D430" s="17"/>
+      <c r="A430" s="4">
+        <f t="shared" si="1"/>
+        <v>429</v>
+      </c>
+      <c r="B430" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="C430" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D430" s="16">
+        <v>4500.0</v>
+      </c>
       <c r="E430" s="17"/>
       <c r="F430" s="17"/>
       <c r="G430" s="17"/>
       <c r="H430" s="17"/>
       <c r="I430" s="17"/>
       <c r="J430" s="17"/>
-      <c r="K430" s="17"/>
+      <c r="K430" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="18"/>
@@ -22686,17 +22703,17 @@
       <c r="K1215" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$429"/>
+  <autoFilter ref="$B$1:$C$430"/>
   <conditionalFormatting sqref="A2:K1215">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C429">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C430">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K429">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K430">
       <formula1>"Ecer,KRT"</formula1>
     </dataValidation>
   </dataValidations>
@@ -22757,7 +22774,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="str">
-        <f t="shared" ref="A2:A60" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
+        <f t="shared" ref="A2:A61" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -22783,7 +22800,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -22805,7 +22822,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -22827,7 +22844,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -22871,7 +22888,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -22915,7 +22932,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -22981,7 +22998,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -23003,7 +23020,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -23025,7 +23042,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -23069,7 +23086,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -23091,7 +23108,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -23157,7 +23174,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -23179,7 +23196,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -23201,7 +23218,7 @@
         <v>GROSIR21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4">
@@ -23333,7 +23350,7 @@
         <v>GROSIR27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="4">
@@ -23377,7 +23394,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -23399,7 +23416,7 @@
         <v>GROSIR30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="4">
@@ -23421,7 +23438,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -23465,7 +23482,7 @@
         <v>GROSIR33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="4">
@@ -23487,7 +23504,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -23509,7 +23526,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -23531,7 +23548,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -23553,7 +23570,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -23575,7 +23592,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -23597,7 +23614,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -23619,7 +23636,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -23663,7 +23680,7 @@
         <v>GROSIR42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="4">
@@ -23707,7 +23724,7 @@
         <v>GROSIR44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="4">
@@ -23751,7 +23768,7 @@
         <v>GROSIR46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="4">
@@ -23795,7 +23812,7 @@
         <v>GROSIR48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="4">
@@ -23817,7 +23834,7 @@
         <v>GROSIR49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="4">
@@ -23839,7 +23856,7 @@
         <v>GROSIR50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="4">
@@ -23861,7 +23878,7 @@
         <v>GROSIR51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="4">
@@ -23883,7 +23900,7 @@
         <v>GROSIR52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="4">
@@ -23905,7 +23922,7 @@
         <v>GROSIR53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="4">
@@ -23927,7 +23944,7 @@
         <v>GROSIR54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="4">
@@ -23949,7 +23966,7 @@
         <v>GROSIR55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="4">
@@ -23971,7 +23988,7 @@
         <v>GROSIR56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="4">
@@ -23993,7 +24010,7 @@
         <v>GROSIR57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="4">
@@ -24015,7 +24032,7 @@
         <v>GROSIR58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="4">
@@ -24037,7 +24054,7 @@
         <v>GROSIR59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="4">
@@ -24054,17 +24071,26 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4"/>
-      <c r="B61" s="5"/>
+      <c r="A61" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR60</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>489</v>
+      </c>
       <c r="C61" s="5"/>
-      <c r="D61" s="4"/>
+      <c r="D61" s="4">
+        <v>4000.0</v>
+      </c>
       <c r="E61" s="20"/>
       <c r="F61" s="20"/>
       <c r="G61" s="20"/>
       <c r="H61" s="20"/>
       <c r="I61" s="20"/>
       <c r="J61" s="20"/>
-      <c r="K61" s="20"/>
+      <c r="K61" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4"/>
@@ -37347,7 +37373,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K60">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K61">
       <formula1>"Ecer,KRT"</formula1>
     </dataValidation>
   </dataValidations>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="525">
   <si>
     <t>Barcode</t>
   </si>
@@ -1587,6 +1587,9 @@
   </si>
   <si>
     <t>Jenaka12</t>
+  </si>
+  <si>
+    <t>Telur Grosir Kg</t>
   </si>
 </sst>
 </file>
@@ -23437,7 +23440,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="str">
-        <f t="shared" ref="A2:A75" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
+        <f t="shared" ref="A2:A76" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -25064,17 +25067,26 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4"/>
-      <c r="B76" s="5"/>
+      <c r="A76" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR75</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>524</v>
+      </c>
       <c r="C76" s="5"/>
-      <c r="D76" s="4"/>
+      <c r="D76" s="4">
+        <v>25500.0</v>
+      </c>
       <c r="E76" s="19"/>
       <c r="F76" s="19"/>
       <c r="G76" s="19"/>
       <c r="H76" s="19"/>
       <c r="I76" s="19"/>
       <c r="J76" s="19"/>
-      <c r="K76" s="19"/>
+      <c r="K76" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4"/>
@@ -38175,7 +38187,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K75">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K76">
       <formula1>"Ecer,KRT"</formula1>
     </dataValidation>
   </dataValidations>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="526">
   <si>
     <t>Barcode</t>
   </si>
@@ -1590,6 +1590,9 @@
   </si>
   <si>
     <t>Telur Grosir Kg</t>
+  </si>
+  <si>
+    <t>Tango 5000</t>
   </si>
 </sst>
 </file>
@@ -23440,7 +23443,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="str">
-        <f t="shared" ref="A2:A76" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
+        <f t="shared" ref="A2:A77" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -25089,17 +25092,26 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4"/>
-      <c r="B77" s="5"/>
+      <c r="A77" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR76</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>525</v>
+      </c>
       <c r="C77" s="5"/>
-      <c r="D77" s="4"/>
+      <c r="D77" s="4">
+        <v>4500.0</v>
+      </c>
       <c r="E77" s="19"/>
       <c r="F77" s="19"/>
       <c r="G77" s="19"/>
       <c r="H77" s="19"/>
       <c r="I77" s="19"/>
       <c r="J77" s="19"/>
-      <c r="K77" s="19"/>
+      <c r="K77" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4"/>
@@ -38187,7 +38199,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K76">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K77">
       <formula1>"Ecer,KRT"</formula1>
     </dataValidation>
   </dataValidations>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$457</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$447</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$263</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="520">
   <si>
     <t>Barcode</t>
   </si>
@@ -491,7 +491,7 @@
     <t>Tepung Bumbu Serba Guna Sasa Renceng</t>
   </si>
   <si>
-    <t>Masako besar</t>
+    <t>Masako 250gr</t>
   </si>
   <si>
     <t>Royco</t>
@@ -500,7 +500,7 @@
     <t>Royco Renceng</t>
   </si>
   <si>
-    <t>Royco Besar</t>
+    <t>Royco 250gr</t>
   </si>
   <si>
     <t>Kecap ABC</t>
@@ -683,811 +683,793 @@
     <t xml:space="preserve">Nestle Renceng </t>
   </si>
   <si>
-    <t>Nes</t>
+    <t>Nes Bungkus</t>
   </si>
   <si>
     <t>Rokok</t>
   </si>
   <si>
-    <t>Nes Bungkus</t>
+    <t>Bhumi Bungkus</t>
+  </si>
+  <si>
+    <t>Jazy Kretek Bungkus</t>
+  </si>
+  <si>
+    <t>Jenaka Smootea Bungkus</t>
+  </si>
+  <si>
+    <t>Jenaka 12 Bungkus</t>
+  </si>
+  <si>
+    <t>Juara Teh Bungkus</t>
+  </si>
+  <si>
+    <t>Juara Berry Bungkus</t>
+  </si>
+  <si>
+    <t>76 Apel</t>
+  </si>
+  <si>
+    <t>76 Apel Bungkus</t>
+  </si>
+  <si>
+    <t>Gudang Garam Merah Bungkus</t>
+  </si>
+  <si>
+    <t>Sampoerna Kretek Bungkus</t>
+  </si>
+  <si>
+    <t>Djarum Coklat</t>
+  </si>
+  <si>
+    <t>Djarum Coklat Bungkus</t>
+  </si>
+  <si>
+    <t>Jazy Bold Bungkus</t>
+  </si>
+  <si>
+    <t>Camel Bungkus</t>
+  </si>
+  <si>
+    <t>Marlboro Black Bungkus</t>
+  </si>
+  <si>
+    <t>Dji Sam Soe</t>
+  </si>
+  <si>
+    <t>Dji Sam Soe Bungkus</t>
+  </si>
+  <si>
+    <t>Magnum Bintang</t>
+  </si>
+  <si>
+    <t>Magnum Bintang Bungkus</t>
+  </si>
+  <si>
+    <t>Magnum Filter</t>
+  </si>
+  <si>
+    <t>Magnum Filter Bungkus</t>
+  </si>
+  <si>
+    <t>Djarum Super</t>
+  </si>
+  <si>
+    <t>Djarum Super Bungkus</t>
+  </si>
+  <si>
+    <t>Gudang Garam Filter</t>
+  </si>
+  <si>
+    <t>Gudang Garam Filter Bungkus</t>
+  </si>
+  <si>
+    <t>Gudang Garam Surya</t>
+  </si>
+  <si>
+    <t>Gudang Garam Surya Bungkus</t>
+  </si>
+  <si>
+    <t>Surya Pro Merah Bungkus</t>
+  </si>
+  <si>
+    <t>Gudang Garam Signature</t>
+  </si>
+  <si>
+    <t>Sampoerna A Mild Bungkus</t>
+  </si>
+  <si>
+    <t>Sampoerna Prima Bungkus</t>
+  </si>
+  <si>
+    <t>Esse Change Bungkus</t>
+  </si>
+  <si>
+    <t>Dji Sam Soe Super Premium Refill</t>
+  </si>
+  <si>
+    <t>76 Apel Royal Bungkus</t>
+  </si>
+  <si>
+    <t>Magnum Max</t>
+  </si>
+  <si>
+    <t>Harmoni</t>
+  </si>
+  <si>
+    <t>Marlboro Black 20</t>
+  </si>
+  <si>
+    <t>Marlboro Black 20 SLOP</t>
+  </si>
+  <si>
+    <t>Korek Api Durian</t>
+  </si>
+  <si>
+    <t>Korek</t>
+  </si>
+  <si>
+    <t>Korek Api Durian Pack</t>
+  </si>
+  <si>
+    <t>Korek Api Tokai</t>
+  </si>
+  <si>
+    <t>Indomie Ayam Bawang</t>
+  </si>
+  <si>
+    <t>MIE</t>
+  </si>
+  <si>
+    <t>Indomie Ayam Bawang Dus</t>
+  </si>
+  <si>
+    <t>Indomie Soto</t>
+  </si>
+  <si>
+    <t>Indomie Soto Dus</t>
+  </si>
+  <si>
+    <t>Indomie Ayam Geprek</t>
+  </si>
+  <si>
+    <t>Indomie Ayam Geprek Dus</t>
+  </si>
+  <si>
+    <t>Indomie Goreng</t>
+  </si>
+  <si>
+    <t>Indomie Goreng Jumbo</t>
+  </si>
+  <si>
+    <t>Indomie Goreng Dus</t>
+  </si>
+  <si>
+    <t>Indomie Goreng Rendang</t>
+  </si>
+  <si>
+    <t>Indomie Goreng Rendang Dus</t>
+  </si>
+  <si>
+    <t>Indomie Goreng Aceh</t>
+  </si>
+  <si>
+    <t>Indomie Goreng Aceh Dus</t>
+  </si>
+  <si>
+    <t>Indomie Empal Gentong</t>
+  </si>
+  <si>
+    <t>Indomie Empal Gentong Dus</t>
+  </si>
+  <si>
+    <t>Mie Sedap Ayam Bawang</t>
+  </si>
+  <si>
+    <t>Mie Sedap Ayam Bawang Dus</t>
+  </si>
+  <si>
+    <t>Mie Sedap Soto</t>
+  </si>
+  <si>
+    <t>Mie Sedap Soto Dus</t>
+  </si>
+  <si>
+    <t>Mie Sedap Korean Spicy Soup</t>
+  </si>
+  <si>
+    <t>Mie Sedap Korean Spicy Soup Dus</t>
+  </si>
+  <si>
+    <t>Mie Sukses Isi 2 Ayam Bawang</t>
+  </si>
+  <si>
+    <t>Mie Sukses Isi 2 Ayam Kecap</t>
+  </si>
+  <si>
+    <t>Mie Sukses Isi 2 Ayam Kecap Dus</t>
+  </si>
+  <si>
+    <t>Mie Sukses Isi 2 Ayam Gepreg</t>
+  </si>
+  <si>
+    <t>Mie Sukses Isi 2 Ayam Gepreg Dus</t>
+  </si>
+  <si>
+    <t>Mie Sukses Isi 2 Goreng</t>
+  </si>
+  <si>
+    <t>Sohun Kaca</t>
+  </si>
+  <si>
+    <t>Sarimi gelas</t>
+  </si>
+  <si>
+    <t>Sarimi gelas Renceng</t>
+  </si>
+  <si>
+    <t>Sarimi Duo Ayam Kecap</t>
+  </si>
+  <si>
+    <t>Sarimi Duo Ayam Kecap Dus</t>
+  </si>
+  <si>
+    <t>Bihun Jagung Padamu</t>
+  </si>
+  <si>
+    <t>Pop Mie mini</t>
+  </si>
+  <si>
+    <t>Pop Mie mini Dus</t>
+  </si>
+  <si>
+    <t>Pop Mie Jumbo</t>
+  </si>
+  <si>
+    <t>Pop Mie Jumbo Dus</t>
+  </si>
+  <si>
+    <t>Mie Burung Dara</t>
+  </si>
+  <si>
+    <t>Beras Sedap Wangi 5kg per Bungkus</t>
+  </si>
+  <si>
+    <t>Beras</t>
+  </si>
+  <si>
+    <t>Charm extra maxi wing</t>
+  </si>
+  <si>
+    <t>Popok</t>
+  </si>
+  <si>
+    <t>Charm extra maxi wing Renceng</t>
+  </si>
+  <si>
+    <t>Charm extra maxi non wing</t>
+  </si>
+  <si>
+    <t>Charm extra maxi non wing Renceng</t>
+  </si>
+  <si>
+    <t>Charm Safe Night</t>
+  </si>
+  <si>
+    <t>Charm Safe Night Renceng</t>
+  </si>
+  <si>
+    <t>MamyPoko M</t>
+  </si>
+  <si>
+    <t>MamyPoko M Renceng</t>
+  </si>
+  <si>
+    <t>MamyPoko XL</t>
+  </si>
+  <si>
+    <t>MamyPoko XL Renceng</t>
+  </si>
+  <si>
+    <t>MamyPoko L</t>
+  </si>
+  <si>
+    <t>MamyPoko L Renceng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunsilk </t>
+  </si>
+  <si>
+    <t>Kamar Mandi</t>
+  </si>
+  <si>
+    <t>Sunsilk Renceng</t>
+  </si>
+  <si>
+    <t>Sampo Lifebuoy</t>
+  </si>
+  <si>
+    <t>Sampo Lifebuoy Renceg</t>
+  </si>
+  <si>
+    <t>Sampo Pantene</t>
+  </si>
+  <si>
+    <t>Sampo Pantene Renceg</t>
+  </si>
+  <si>
+    <t>Sampo Zinc</t>
+  </si>
+  <si>
+    <t>Sampo Zinc Renceg</t>
+  </si>
+  <si>
+    <t>Sampo Clear</t>
+  </si>
+  <si>
+    <t>Sampo Clear Renceg</t>
+  </si>
+  <si>
+    <t>Sampo Head &amp; Shoulders</t>
+  </si>
+  <si>
+    <t>Sampo Head &amp; Shoulders Renceg</t>
+  </si>
+  <si>
+    <t>Sampo Dove</t>
+  </si>
+  <si>
+    <t>Soklin Liquid 500</t>
+  </si>
+  <si>
+    <t>Soklin Liquid 500 Renceg</t>
+  </si>
+  <si>
+    <t>Soklin Lantai</t>
+  </si>
+  <si>
+    <t>Soklin Lantai Renceng</t>
+  </si>
+  <si>
+    <t>Gentle Gen</t>
+  </si>
+  <si>
+    <t>Gentle Gen Renceg</t>
+  </si>
+  <si>
+    <t>Kilau Nipis 2000</t>
+  </si>
+  <si>
+    <t>Kilau Nipis 5000</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>Attack Renceg</t>
+  </si>
+  <si>
+    <t>Rinso Bubuk</t>
+  </si>
+  <si>
+    <t>Rinso Bubuk Renceg</t>
+  </si>
+  <si>
+    <t>Rinso Cair</t>
+  </si>
+  <si>
+    <t>Rinso Cair Renceg</t>
+  </si>
+  <si>
+    <t>Molto</t>
+  </si>
+  <si>
+    <t>Kispray</t>
+  </si>
+  <si>
+    <t>Kispray Renceng</t>
+  </si>
+  <si>
+    <t>Molto Renceg</t>
+  </si>
+  <si>
+    <t>Soklin Softener 500</t>
+  </si>
+  <si>
+    <t>Soklin Softener 500 Renceg</t>
+  </si>
+  <si>
+    <t>Downy 500</t>
+  </si>
+  <si>
+    <t>Downy 500 Renceg</t>
+  </si>
+  <si>
+    <t>Wipol</t>
+  </si>
+  <si>
+    <t>Wipol Renceng</t>
+  </si>
+  <si>
+    <t>Ekonomi 1000</t>
+  </si>
+  <si>
+    <t>Ekonomi 1000 Renceg</t>
+  </si>
+  <si>
+    <t>Ekonomi 1000 Dus</t>
+  </si>
+  <si>
+    <t>Ekonomi 2000</t>
+  </si>
+  <si>
+    <t>Ekonomi 2000 Dus</t>
+  </si>
+  <si>
+    <t>Daia</t>
+  </si>
+  <si>
+    <t>Daia Renceg</t>
+  </si>
+  <si>
+    <t>Sunlight</t>
+  </si>
+  <si>
+    <t>Sunlight Besar</t>
+  </si>
+  <si>
+    <t>Ciptadent</t>
+  </si>
+  <si>
+    <t>CloseUp</t>
+  </si>
+  <si>
+    <t>Pepsodent</t>
+  </si>
+  <si>
+    <t>Sikat Gigi Formula</t>
+  </si>
+  <si>
+    <t>Sabun Shin Zui</t>
+  </si>
+  <si>
+    <t>Sabun Lux</t>
+  </si>
+  <si>
+    <t>Sabun Nuvo</t>
+  </si>
+  <si>
+    <t>Sabun Lifebuoy</t>
+  </si>
+  <si>
+    <t>Sabun Giv</t>
+  </si>
+  <si>
+    <t>Sabun Nuvo Cair 60g</t>
+  </si>
+  <si>
+    <t>Fair and Lovely Cream</t>
+  </si>
+  <si>
+    <t>Pepsodent kecil</t>
+  </si>
+  <si>
+    <t>Biosol</t>
+  </si>
+  <si>
+    <t>Biosol Renceng</t>
+  </si>
+  <si>
+    <t>Fair and Lovely Facial Foam</t>
+  </si>
+  <si>
+    <t>Posh</t>
+  </si>
+  <si>
+    <t>Obat Nyamuk Bakar</t>
+  </si>
+  <si>
+    <t>Lainya</t>
+  </si>
+  <si>
+    <t>Obat Nyamuk Bakar Dus</t>
+  </si>
+  <si>
+    <t>Hit Mat</t>
+  </si>
+  <si>
+    <t>Hit Mat Renceng</t>
+  </si>
+  <si>
+    <t>Autan</t>
+  </si>
+  <si>
+    <t>Autan Renceng</t>
+  </si>
+  <si>
+    <t>Solatif</t>
+  </si>
+  <si>
+    <t>Silet Cukur</t>
+  </si>
+  <si>
+    <t>Silet Gillette</t>
+  </si>
+  <si>
+    <t>Double Tip</t>
+  </si>
+  <si>
+    <t>Batre AA ABC</t>
+  </si>
+  <si>
+    <t>Batre AAA</t>
+  </si>
+  <si>
+    <t>Masker Biru</t>
+  </si>
+  <si>
+    <t>Masker Abu</t>
+  </si>
+  <si>
+    <t>Gunting Kecil</t>
+  </si>
+  <si>
+    <t>Gunting Besar</t>
+  </si>
+  <si>
+    <t>Lem Super Glue</t>
+  </si>
+  <si>
+    <t>Lem Super Glue Renceng</t>
+  </si>
+  <si>
+    <t>Cup Kertas</t>
+  </si>
+  <si>
+    <t>Cup Plastik</t>
+  </si>
+  <si>
+    <t>Huut (kg)</t>
+  </si>
+  <si>
+    <t>komix</t>
+  </si>
+  <si>
+    <t>Obat</t>
+  </si>
+  <si>
+    <t>komix pack</t>
+  </si>
+  <si>
+    <t>Oskadon biru strip</t>
+  </si>
+  <si>
+    <t>Oskadon sp strip</t>
+  </si>
+  <si>
+    <t>Antangin</t>
+  </si>
+  <si>
+    <t>Antangin Box</t>
+  </si>
+  <si>
+    <t>Tolak Angin</t>
+  </si>
+  <si>
+    <t>Tolak Angin Box</t>
+  </si>
+  <si>
+    <t>Tolak Linu</t>
+  </si>
+  <si>
+    <t>Tolak Linu Box</t>
+  </si>
+  <si>
+    <t>Bodrex Satuan</t>
+  </si>
+  <si>
+    <t>Salonpas</t>
+  </si>
+  <si>
+    <t>Salonpas Bungkus</t>
+  </si>
+  <si>
+    <t>Hansaplast</t>
+  </si>
+  <si>
+    <t>Koyo Cabe</t>
+  </si>
+  <si>
+    <t>Koyo Cabe Bungkus</t>
+  </si>
+  <si>
+    <t>Paramex Strip</t>
+  </si>
+  <si>
+    <t>Paramex Satuan</t>
+  </si>
+  <si>
+    <t>Promag Pak</t>
+  </si>
+  <si>
+    <t>Promag Lembar</t>
+  </si>
+  <si>
+    <t>Promag Satuan</t>
+  </si>
+  <si>
+    <t>Rheumacyl Pak</t>
+  </si>
+  <si>
+    <t>Rheumacyl Lembar</t>
+  </si>
+  <si>
+    <t>Rheumacyl Satuan</t>
+  </si>
+  <si>
+    <t>Bodrex Extra Strip</t>
+  </si>
+  <si>
+    <t>Bodrex Extra Satuan</t>
+  </si>
+  <si>
+    <t>Bodrexin per pack</t>
+  </si>
+  <si>
+    <t>Bodrexin per BAL</t>
+  </si>
+  <si>
+    <t>Kayu putih 30ml</t>
+  </si>
+  <si>
+    <t>Poldan mig</t>
+  </si>
+  <si>
+    <t>Tambah Telur</t>
+  </si>
+  <si>
+    <t>Mie Seduh</t>
+  </si>
+  <si>
+    <t>Mie isi 2 Seduh</t>
+  </si>
+  <si>
+    <t>Amplop box</t>
+  </si>
+  <si>
+    <t>Amplop</t>
+  </si>
+  <si>
+    <t>Agar Swallow</t>
+  </si>
+  <si>
+    <t>Choki choki</t>
+  </si>
+  <si>
+    <t>Fruta Gumnmy</t>
+  </si>
+  <si>
+    <t>Chiki Ball</t>
+  </si>
+  <si>
+    <t>Chitato</t>
+  </si>
+  <si>
+    <t>Roma Malkist 1000 Renceng</t>
+  </si>
+  <si>
+    <t>Taro 1000 Renceng</t>
+  </si>
+  <si>
+    <t>Garuda Renceng</t>
+  </si>
+  <si>
+    <t>Sosis So Nice Toples</t>
+  </si>
+  <si>
+    <t>Siip 500 dus</t>
+  </si>
+  <si>
+    <t>Nabati Aah</t>
+  </si>
+  <si>
+    <t>Pilus 500 Renceng</t>
+  </si>
+  <si>
+    <t>Pilus 1000 Renceng</t>
+  </si>
+  <si>
+    <t>Chocolatos 500</t>
+  </si>
+  <si>
+    <t>Wow Spagheti</t>
+  </si>
+  <si>
+    <t>Wow Spagheti Renceng</t>
+  </si>
+  <si>
+    <t>Cat Choize</t>
+  </si>
+  <si>
+    <t>Mixagrip Flu dan Batuk</t>
+  </si>
+  <si>
+    <t>Bodrex Flu dan Batuk</t>
+  </si>
+  <si>
+    <t>Yupi baby bear Box</t>
+  </si>
+  <si>
+    <t>Snack Copico Renceng</t>
+  </si>
+  <si>
+    <t>Roti mini 1000</t>
+  </si>
+  <si>
+    <t>Choco Pie 2000 Renceng</t>
+  </si>
+  <si>
+    <t>Roma Sandwich</t>
+  </si>
+  <si>
+    <t>Roma Sandwich Dus</t>
+  </si>
+  <si>
+    <t>Djarum Coklat SLOP</t>
+  </si>
+  <si>
+    <t>Djarum Coklat Elite</t>
+  </si>
+  <si>
+    <t>Djarum Coklat Elite SLOP</t>
+  </si>
+  <si>
+    <t>76 Apel SLOP</t>
+  </si>
+  <si>
+    <t>Djarum Super SLOP</t>
+  </si>
+  <si>
+    <t>Magnum Filter SLOP</t>
+  </si>
+  <si>
+    <t>Magnum Bintang SLOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dji Sam Soe </t>
+  </si>
+  <si>
+    <t>Jazy Bold</t>
+  </si>
+  <si>
+    <t>Sampoerna Mild</t>
+  </si>
+  <si>
+    <t>Sampoerna Prima</t>
+  </si>
+  <si>
+    <t>Surya Pro Merah</t>
+  </si>
+  <si>
+    <t>Surya Pro Merah Slop</t>
+  </si>
+  <si>
+    <t>76 Apel Royal</t>
+  </si>
+  <si>
+    <t>Gudang Garam Merah</t>
+  </si>
+  <si>
+    <t>Sampoerna Kretek</t>
+  </si>
+  <si>
+    <t>Jazy Kretek</t>
+  </si>
+  <si>
+    <t>Jazy Kretek SLOP</t>
   </si>
   <si>
     <t>Bhumi</t>
-  </si>
-  <si>
-    <t>Bhumi Bungkus</t>
-  </si>
-  <si>
-    <t>Jazy Kretek</t>
-  </si>
-  <si>
-    <t>Jazy Kretek Bungkus</t>
-  </si>
-  <si>
-    <t>Jenaka Smootea</t>
-  </si>
-  <si>
-    <t>Jenaka Smootea Bungkus</t>
-  </si>
-  <si>
-    <t>Jenaka</t>
-  </si>
-  <si>
-    <t>Jenaka 12 Bungkus</t>
-  </si>
-  <si>
-    <t>Juara Jambu Bungkus</t>
-  </si>
-  <si>
-    <t>Juara Teh Bungkus</t>
-  </si>
-  <si>
-    <t>Juara Berry Bungkus</t>
-  </si>
-  <si>
-    <t>76 Apel</t>
-  </si>
-  <si>
-    <t>76 Apel Bungkus</t>
-  </si>
-  <si>
-    <t>Gudang Garam Merah</t>
-  </si>
-  <si>
-    <t>Gudang Garam Merah Bungkus</t>
-  </si>
-  <si>
-    <t>Sampoerna Kretek</t>
-  </si>
-  <si>
-    <t>Sampoerna Kretek Bungkus</t>
-  </si>
-  <si>
-    <t>Djarum Coklat</t>
-  </si>
-  <si>
-    <t>Djarum Coklat Bungkus</t>
-  </si>
-  <si>
-    <t>Jazy Bold</t>
-  </si>
-  <si>
-    <t>Jazy Bold Bungkus</t>
-  </si>
-  <si>
-    <t>Camel</t>
-  </si>
-  <si>
-    <t>Camel Bungkus</t>
-  </si>
-  <si>
-    <t>Marlboro Black</t>
-  </si>
-  <si>
-    <t>Marlboro Black Bungkus</t>
-  </si>
-  <si>
-    <t>Dji Sam Soe</t>
-  </si>
-  <si>
-    <t>Dji Sam Soe Bungkus</t>
-  </si>
-  <si>
-    <t>Magnum Bintang</t>
-  </si>
-  <si>
-    <t>Magnum Bintang Bungkus</t>
-  </si>
-  <si>
-    <t>Magnum Filter</t>
-  </si>
-  <si>
-    <t>Magnum Filter Bungkus</t>
-  </si>
-  <si>
-    <t>Djarum Super</t>
-  </si>
-  <si>
-    <t>Djarum Super Bungkus</t>
-  </si>
-  <si>
-    <t>Gudang Garam International (Garpit)</t>
-  </si>
-  <si>
-    <t>Gudang Garam International (Garpit) Bungkus</t>
-  </si>
-  <si>
-    <t>Gudang Garam Surya</t>
-  </si>
-  <si>
-    <t>Gudang Garam Surya Bungkus</t>
-  </si>
-  <si>
-    <t>Surya Pro Merah Bungkus</t>
-  </si>
-  <si>
-    <t>Gudang Garam Signature</t>
-  </si>
-  <si>
-    <t>Sampoerna A Mild Bungkus</t>
-  </si>
-  <si>
-    <t>Sampoerna Prima Bungkus</t>
-  </si>
-  <si>
-    <t>Esse Change Bungkus</t>
-  </si>
-  <si>
-    <t>Dji Sam Soe Super Premium Refill</t>
-  </si>
-  <si>
-    <t>76 Apel Royal Bungkus</t>
-  </si>
-  <si>
-    <t>Magnum Max</t>
-  </si>
-  <si>
-    <t>Harmoni</t>
-  </si>
-  <si>
-    <t>Marlboro Black 20</t>
-  </si>
-  <si>
-    <t>Marlboro Black 20 SLOP</t>
-  </si>
-  <si>
-    <t>Korek Api Durian</t>
-  </si>
-  <si>
-    <t>Korek</t>
-  </si>
-  <si>
-    <t>Korek Api Durian Pack</t>
-  </si>
-  <si>
-    <t>Korek Api Tokai</t>
-  </si>
-  <si>
-    <t>Indomie Ayam Bawang</t>
-  </si>
-  <si>
-    <t>MIE</t>
-  </si>
-  <si>
-    <t>Indomie Ayam Bawang Dus</t>
-  </si>
-  <si>
-    <t>Indomie Soto</t>
-  </si>
-  <si>
-    <t>Indomie Soto Dus</t>
-  </si>
-  <si>
-    <t>Indomie Ayam Geprek</t>
-  </si>
-  <si>
-    <t>Indomie Ayam Geprek Dus</t>
-  </si>
-  <si>
-    <t>Indomie Goreng</t>
-  </si>
-  <si>
-    <t>Indomie Goreng Jumbo</t>
-  </si>
-  <si>
-    <t>Indomie Goreng Dus</t>
-  </si>
-  <si>
-    <t>Indomie Goreng Rendang</t>
-  </si>
-  <si>
-    <t>Indomie Goreng Rendang Dus</t>
-  </si>
-  <si>
-    <t>Indomie Goreng Aceh</t>
-  </si>
-  <si>
-    <t>Indomie Goreng Aceh Dus</t>
-  </si>
-  <si>
-    <t>Indomie Empal Gentong</t>
-  </si>
-  <si>
-    <t>Indomie Empal Gentong Dus</t>
-  </si>
-  <si>
-    <t>Mie Sedap Ayam Bawang</t>
-  </si>
-  <si>
-    <t>Mie Sedap Ayam Bawang Dus</t>
-  </si>
-  <si>
-    <t>Mie Sedap Soto</t>
-  </si>
-  <si>
-    <t>Mie Sedap Soto Dus</t>
-  </si>
-  <si>
-    <t>Mie Sedap Korean Spicy Soup</t>
-  </si>
-  <si>
-    <t>Mie Sedap Korean Spicy Soup Dus</t>
-  </si>
-  <si>
-    <t>Mie Sukses Isi 2 Ayam Bawang</t>
-  </si>
-  <si>
-    <t>Mie Sukses Isi 2 Ayam Kecap</t>
-  </si>
-  <si>
-    <t>Mie Sukses Isi 2 Ayam Kecap Dus</t>
-  </si>
-  <si>
-    <t>Mie Sukses Isi 2 Ayam Gepreg</t>
-  </si>
-  <si>
-    <t>Mie Sukses Isi 2 Ayam Gepreg Dus</t>
-  </si>
-  <si>
-    <t>Mie Sukses Isi 2 Goreng</t>
-  </si>
-  <si>
-    <t>Sohun Kaca</t>
-  </si>
-  <si>
-    <t>Sarimi gelas</t>
-  </si>
-  <si>
-    <t>Sarimi Duo Ayam Kecap</t>
-  </si>
-  <si>
-    <t>Sarimi Duo Ayam Kecap Dus</t>
-  </si>
-  <si>
-    <t>Bihun Jagung Padamu</t>
-  </si>
-  <si>
-    <t>Pop Mie mini</t>
-  </si>
-  <si>
-    <t>Pop Mie mini Dus</t>
-  </si>
-  <si>
-    <t>Pop Mie Jumbo</t>
-  </si>
-  <si>
-    <t>Pop Mie Jumbo Dus</t>
-  </si>
-  <si>
-    <t>Mie Burung Dara</t>
-  </si>
-  <si>
-    <t>Beras Sedap Wangi 5kg per Bungkus</t>
-  </si>
-  <si>
-    <t>Beras</t>
-  </si>
-  <si>
-    <t>Charm extra maxi wing</t>
-  </si>
-  <si>
-    <t>Popok</t>
-  </si>
-  <si>
-    <t>Charm extra maxi wing Renceng</t>
-  </si>
-  <si>
-    <t>Charm extra maxi non wing</t>
-  </si>
-  <si>
-    <t>Charm extra maxi non wing Renceng</t>
-  </si>
-  <si>
-    <t>Charm Safe Night</t>
-  </si>
-  <si>
-    <t>Charm Safe Night Renceng</t>
-  </si>
-  <si>
-    <t>MamyPoko M</t>
-  </si>
-  <si>
-    <t>MamyPoko M Renceng</t>
-  </si>
-  <si>
-    <t>MamyPoko XL</t>
-  </si>
-  <si>
-    <t>MamyPoko XL Renceng</t>
-  </si>
-  <si>
-    <t>MamyPoko L</t>
-  </si>
-  <si>
-    <t>MamyPoko L Renceng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunsilk </t>
-  </si>
-  <si>
-    <t>Kamar Mandi</t>
-  </si>
-  <si>
-    <t>Sunsilk Renceng</t>
-  </si>
-  <si>
-    <t>Sampo Lifebuoy</t>
-  </si>
-  <si>
-    <t>Sampo Lifebuoy Renceg</t>
-  </si>
-  <si>
-    <t>Sampo Pantene</t>
-  </si>
-  <si>
-    <t>Sampo Pantene Renceg</t>
-  </si>
-  <si>
-    <t>Sampo Zinc</t>
-  </si>
-  <si>
-    <t>Sampo Zinc Renceg</t>
-  </si>
-  <si>
-    <t>Sampo Clear</t>
-  </si>
-  <si>
-    <t>Sampo Clear Renceg</t>
-  </si>
-  <si>
-    <t>Sampo Head &amp; Shoulders</t>
-  </si>
-  <si>
-    <t>Sampo Head &amp; Shoulders Renceg</t>
-  </si>
-  <si>
-    <t>Sampo Dove</t>
-  </si>
-  <si>
-    <t>Soklin Liquid 500</t>
-  </si>
-  <si>
-    <t>Soklin Liquid 500 Renceg</t>
-  </si>
-  <si>
-    <t>Soklin Lantai</t>
-  </si>
-  <si>
-    <t>Soklin Lantai Renceng</t>
-  </si>
-  <si>
-    <t>Gentle Gen</t>
-  </si>
-  <si>
-    <t>Gentle Gen Renceg</t>
-  </si>
-  <si>
-    <t>Kilau Nipis 2000</t>
-  </si>
-  <si>
-    <t>Kilau Nipis 5000</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>Attack Renceg</t>
-  </si>
-  <si>
-    <t>Rinso Bubuk</t>
-  </si>
-  <si>
-    <t>Rinso Bubuk Renceg</t>
-  </si>
-  <si>
-    <t>Rinso Cair</t>
-  </si>
-  <si>
-    <t>Rinso Cair Renceg</t>
-  </si>
-  <si>
-    <t>Molto</t>
-  </si>
-  <si>
-    <t>Kispray</t>
-  </si>
-  <si>
-    <t>Kispray Renceng</t>
-  </si>
-  <si>
-    <t>Molto Renceg</t>
-  </si>
-  <si>
-    <t>Soklin Softener 500</t>
-  </si>
-  <si>
-    <t>Soklin Softener 500 Renceg</t>
-  </si>
-  <si>
-    <t>Downy 500</t>
-  </si>
-  <si>
-    <t>Downy 500 Renceg</t>
-  </si>
-  <si>
-    <t>Wipol</t>
-  </si>
-  <si>
-    <t>Wipol Renceng</t>
-  </si>
-  <si>
-    <t>Ekonomi 1000</t>
-  </si>
-  <si>
-    <t>Ekonomi 1000 Renceg</t>
-  </si>
-  <si>
-    <t>Ekonomi 1000 Dus</t>
-  </si>
-  <si>
-    <t>Ekonomi 2000</t>
-  </si>
-  <si>
-    <t>Ekonomi 2000 Dus</t>
-  </si>
-  <si>
-    <t>Daia</t>
-  </si>
-  <si>
-    <t>Daia Renceg</t>
-  </si>
-  <si>
-    <t>Sunlight</t>
-  </si>
-  <si>
-    <t>Sunlight Besar</t>
-  </si>
-  <si>
-    <t>Ciptadent</t>
-  </si>
-  <si>
-    <t>CloseUp</t>
-  </si>
-  <si>
-    <t>Pepsodent</t>
-  </si>
-  <si>
-    <t>Sikat Gigi Formula</t>
-  </si>
-  <si>
-    <t>Sabun Shin Zui</t>
-  </si>
-  <si>
-    <t>Sabun Lux</t>
-  </si>
-  <si>
-    <t>Sabun Nuvo</t>
-  </si>
-  <si>
-    <t>Sabun Lifebuoy</t>
-  </si>
-  <si>
-    <t>Sabun Giv</t>
-  </si>
-  <si>
-    <t>Sabun Nuvo Cair 60g</t>
-  </si>
-  <si>
-    <t>Fair and Lovely Cream</t>
-  </si>
-  <si>
-    <t>Pepsodent kecil</t>
-  </si>
-  <si>
-    <t>Biosol</t>
-  </si>
-  <si>
-    <t>Biosol Renceng</t>
-  </si>
-  <si>
-    <t>Fair and Lovely Facial Foam</t>
-  </si>
-  <si>
-    <t>Posh</t>
-  </si>
-  <si>
-    <t>Obat Nyamuk Bakar</t>
-  </si>
-  <si>
-    <t>Lainya</t>
-  </si>
-  <si>
-    <t>Obat Nyamuk Bakar Dus</t>
-  </si>
-  <si>
-    <t>Hit Mat</t>
-  </si>
-  <si>
-    <t>Hit Mat Renceng</t>
-  </si>
-  <si>
-    <t>Autan</t>
-  </si>
-  <si>
-    <t>Autan Renceng</t>
-  </si>
-  <si>
-    <t>Solatif</t>
-  </si>
-  <si>
-    <t>Silet Cukur</t>
-  </si>
-  <si>
-    <t>Silet Gillette</t>
-  </si>
-  <si>
-    <t>Double Tip</t>
-  </si>
-  <si>
-    <t>Batre AA ABC</t>
-  </si>
-  <si>
-    <t>Batre AAA</t>
-  </si>
-  <si>
-    <t>Masker Biru</t>
-  </si>
-  <si>
-    <t>Masker Abu</t>
-  </si>
-  <si>
-    <t>Gunting Kecil</t>
-  </si>
-  <si>
-    <t>Gunting Besar</t>
-  </si>
-  <si>
-    <t>Lem Super Glue</t>
-  </si>
-  <si>
-    <t>Lem Super Glue Renceng</t>
-  </si>
-  <si>
-    <t>Cup Kertas</t>
-  </si>
-  <si>
-    <t>Cup Plastik</t>
-  </si>
-  <si>
-    <t>Huut (kg)</t>
-  </si>
-  <si>
-    <t>komix</t>
-  </si>
-  <si>
-    <t>Obat</t>
-  </si>
-  <si>
-    <t>komix pack</t>
-  </si>
-  <si>
-    <t>Oskadon biru strip</t>
-  </si>
-  <si>
-    <t>Oskadon sp strip</t>
-  </si>
-  <si>
-    <t>Antangin</t>
-  </si>
-  <si>
-    <t>Antangin Box</t>
-  </si>
-  <si>
-    <t>Tolak Angin</t>
-  </si>
-  <si>
-    <t>Tolak Angin Box</t>
-  </si>
-  <si>
-    <t>Tolak Linu</t>
-  </si>
-  <si>
-    <t>Tolak Linu Box</t>
-  </si>
-  <si>
-    <t>Bodrex Satuan</t>
-  </si>
-  <si>
-    <t>Salonpas</t>
-  </si>
-  <si>
-    <t>Salonpas Bungkus</t>
-  </si>
-  <si>
-    <t>Hansaplast</t>
-  </si>
-  <si>
-    <t>Koyo Cabe</t>
-  </si>
-  <si>
-    <t>Koyo Cabe Bungkus</t>
-  </si>
-  <si>
-    <t>Paramex Strip</t>
-  </si>
-  <si>
-    <t>Paramex Satuan</t>
-  </si>
-  <si>
-    <t>Promag Pak</t>
-  </si>
-  <si>
-    <t>Promag Lembar</t>
-  </si>
-  <si>
-    <t>Promag Satuan</t>
-  </si>
-  <si>
-    <t>Rheumacyl Pak</t>
-  </si>
-  <si>
-    <t>Rheumacyl Lembar</t>
-  </si>
-  <si>
-    <t>Rheumacyl Satuan</t>
-  </si>
-  <si>
-    <t>Bodrex Extra Strip</t>
-  </si>
-  <si>
-    <t>Bodrex Extra Satuan</t>
-  </si>
-  <si>
-    <t>Bodrexin per pack</t>
-  </si>
-  <si>
-    <t>Bodrexin per BAL</t>
-  </si>
-  <si>
-    <t>Kayu putih 30ml</t>
-  </si>
-  <si>
-    <t>Poldan mig</t>
-  </si>
-  <si>
-    <t>Tambah Telur</t>
-  </si>
-  <si>
-    <t>Mie Seduh</t>
-  </si>
-  <si>
-    <t>Mie isi 2 Seduh</t>
-  </si>
-  <si>
-    <t>Amplop box</t>
-  </si>
-  <si>
-    <t>Amplop</t>
-  </si>
-  <si>
-    <t>Agar Swallow</t>
-  </si>
-  <si>
-    <t>Choki choki</t>
-  </si>
-  <si>
-    <t>Fruta Gumnmy</t>
-  </si>
-  <si>
-    <t>Chiki Ball</t>
-  </si>
-  <si>
-    <t>Chitato</t>
-  </si>
-  <si>
-    <t>Roma Malkist 1000 Renceng</t>
-  </si>
-  <si>
-    <t>Taro 1000 Renceng</t>
-  </si>
-  <si>
-    <t>Garuda Renceng</t>
-  </si>
-  <si>
-    <t>Sosis So Nice Toples</t>
-  </si>
-  <si>
-    <t>Siip 500 dus</t>
-  </si>
-  <si>
-    <t>Nabati Aah</t>
-  </si>
-  <si>
-    <t>Pilus 500 Renceng</t>
-  </si>
-  <si>
-    <t>Pilus 1000 Renceng</t>
-  </si>
-  <si>
-    <t>Chocolatos 500</t>
-  </si>
-  <si>
-    <t>Wow Spagheti</t>
-  </si>
-  <si>
-    <t>Wow Spagheti Renceng</t>
-  </si>
-  <si>
-    <t>Cat Choize</t>
-  </si>
-  <si>
-    <t>Mixagrip Flu dan Batuk</t>
-  </si>
-  <si>
-    <t>Bodrex Flu dan Batuk</t>
-  </si>
-  <si>
-    <t>Yupi baby bear Box</t>
-  </si>
-  <si>
-    <t>Snack Copico Renceng</t>
-  </si>
-  <si>
-    <t>Roti mini 1000</t>
-  </si>
-  <si>
-    <t>Choco Pie 2000 Renceng</t>
-  </si>
-  <si>
-    <t>Roma Sandwich</t>
-  </si>
-  <si>
-    <t>Roma Sandwich Dus</t>
-  </si>
-  <si>
-    <t>Djarum Coklat SLOP</t>
-  </si>
-  <si>
-    <t>Djarum Coklat Elite</t>
-  </si>
-  <si>
-    <t>Djarum Coklat Elite SLOP</t>
-  </si>
-  <si>
-    <t>76 Apel SLOP</t>
-  </si>
-  <si>
-    <t>Djarum Super SLOP</t>
-  </si>
-  <si>
-    <t>Magnum Filter SLOP</t>
-  </si>
-  <si>
-    <t>Magnum Bintang SLOP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dji Sam Soe </t>
-  </si>
-  <si>
-    <t>Gudang Garam Filter</t>
-  </si>
-  <si>
-    <t>Sampoerna Mild</t>
-  </si>
-  <si>
-    <t>Sampoerna Prima</t>
-  </si>
-  <si>
-    <t>Surya Pro Merah</t>
-  </si>
-  <si>
-    <t>Surya Pro Merah Slop</t>
-  </si>
-  <si>
-    <t>76 Apel Royal</t>
-  </si>
-  <si>
-    <t>Jazy Kretek SLOP</t>
   </si>
   <si>
     <t>Janaka</t>
@@ -2015,7 +1997,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A457" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A447" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -5438,7 +5420,7 @@
         <v>146</v>
       </c>
       <c r="D143" s="4">
-        <v>21000.0</v>
+        <v>22000.0</v>
       </c>
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
@@ -7022,22 +7004,14 @@
         <v>223</v>
       </c>
       <c r="D208" s="4">
-        <v>2000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E208" s="7"/>
       <c r="F208" s="7"/>
-      <c r="G208" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H208" s="4">
-        <v>5500.0</v>
-      </c>
-      <c r="I208" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J208" s="4">
-        <v>10000.0</v>
-      </c>
+      <c r="G208" s="7"/>
+      <c r="H208" s="7"/>
+      <c r="I208" s="7"/>
+      <c r="J208" s="7"/>
       <c r="K208" s="4" t="s">
         <v>13</v>
       </c>
@@ -7078,22 +7052,14 @@
         <v>223</v>
       </c>
       <c r="D210" s="4">
-        <v>2000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E210" s="7"/>
       <c r="F210" s="7"/>
-      <c r="G210" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H210" s="4">
-        <v>5500.0</v>
-      </c>
-      <c r="I210" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J210" s="4">
-        <v>10000.0</v>
-      </c>
+      <c r="G210" s="7"/>
+      <c r="H210" s="7"/>
+      <c r="I210" s="7"/>
+      <c r="J210" s="7"/>
       <c r="K210" s="4" t="s">
         <v>13</v>
       </c>
@@ -7110,7 +7076,7 @@
         <v>223</v>
       </c>
       <c r="D211" s="4">
-        <v>10000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="E211" s="7"/>
       <c r="F211" s="7"/>
@@ -7134,22 +7100,14 @@
         <v>223</v>
       </c>
       <c r="D212" s="4">
-        <v>2000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="E212" s="7"/>
       <c r="F212" s="7"/>
-      <c r="G212" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H212" s="4">
-        <v>5500.0</v>
-      </c>
-      <c r="I212" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J212" s="4">
-        <v>10000.0</v>
-      </c>
+      <c r="G212" s="7"/>
+      <c r="H212" s="7"/>
+      <c r="I212" s="7"/>
+      <c r="J212" s="7"/>
       <c r="K212" s="4" t="s">
         <v>13</v>
       </c>
@@ -7166,7 +7124,7 @@
         <v>223</v>
       </c>
       <c r="D213" s="4">
-        <v>10000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E213" s="7"/>
       <c r="F213" s="7"/>
@@ -7190,22 +7148,14 @@
         <v>223</v>
       </c>
       <c r="D214" s="4">
-        <v>2000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E214" s="7"/>
       <c r="F214" s="7"/>
-      <c r="G214" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H214" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="I214" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J214" s="4">
-        <v>11000.0</v>
-      </c>
+      <c r="G214" s="7"/>
+      <c r="H214" s="7"/>
+      <c r="I214" s="7"/>
+      <c r="J214" s="7"/>
       <c r="K214" s="4" t="s">
         <v>13</v>
       </c>
@@ -7222,14 +7172,26 @@
         <v>223</v>
       </c>
       <c r="D215" s="4">
-        <v>11000.0</v>
-      </c>
-      <c r="E215" s="7"/>
-      <c r="F215" s="7"/>
-      <c r="G215" s="7"/>
-      <c r="H215" s="7"/>
-      <c r="I215" s="7"/>
-      <c r="J215" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E215" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F215" s="4">
+        <v>5000.0</v>
+      </c>
+      <c r="G215" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H215" s="4">
+        <v>8500.0</v>
+      </c>
+      <c r="I215" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J215" s="4">
+        <v>16000.0</v>
+      </c>
       <c r="K215" s="4" t="s">
         <v>13</v>
       </c>
@@ -7246,22 +7208,14 @@
         <v>223</v>
       </c>
       <c r="D216" s="4">
-        <v>2000.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E216" s="7"/>
       <c r="F216" s="7"/>
-      <c r="G216" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H216" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="I216" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J216" s="4">
-        <v>11000.0</v>
-      </c>
+      <c r="G216" s="7"/>
+      <c r="H216" s="7"/>
+      <c r="I216" s="7"/>
+      <c r="J216" s="7"/>
       <c r="K216" s="4" t="s">
         <v>13</v>
       </c>
@@ -7278,7 +7232,7 @@
         <v>223</v>
       </c>
       <c r="D217" s="4">
-        <v>11000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E217" s="7"/>
       <c r="F217" s="7"/>
@@ -7302,22 +7256,14 @@
         <v>223</v>
       </c>
       <c r="D218" s="4">
-        <v>2000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E218" s="7"/>
       <c r="F218" s="7"/>
-      <c r="G218" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H218" s="4">
-        <v>8000.0</v>
-      </c>
-      <c r="I218" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J218" s="4">
-        <v>15000.0</v>
-      </c>
+      <c r="G218" s="7"/>
+      <c r="H218" s="7"/>
+      <c r="I218" s="7"/>
+      <c r="J218" s="7"/>
       <c r="K218" s="4" t="s">
         <v>13</v>
       </c>
@@ -7334,14 +7280,26 @@
         <v>223</v>
       </c>
       <c r="D219" s="4">
-        <v>15000.0</v>
-      </c>
-      <c r="E219" s="7"/>
-      <c r="F219" s="7"/>
-      <c r="G219" s="7"/>
-      <c r="H219" s="7"/>
-      <c r="I219" s="7"/>
-      <c r="J219" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E219" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F219" s="4">
+        <v>5000.0</v>
+      </c>
+      <c r="G219" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H219" s="4">
+        <v>9500.0</v>
+      </c>
+      <c r="I219" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J219" s="4">
+        <v>18000.0</v>
+      </c>
       <c r="K219" s="4" t="s">
         <v>13</v>
       </c>
@@ -7358,7 +7316,7 @@
         <v>223</v>
       </c>
       <c r="D220" s="4">
-        <v>15000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E220" s="7"/>
       <c r="F220" s="7"/>
@@ -7382,26 +7340,14 @@
         <v>223</v>
       </c>
       <c r="D221" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E221" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F221" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="G221" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H221" s="4">
-        <v>8500.0</v>
-      </c>
-      <c r="I221" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J221" s="4">
-        <v>16000.0</v>
-      </c>
+        <v>28000.0</v>
+      </c>
+      <c r="E221" s="7"/>
+      <c r="F221" s="7"/>
+      <c r="G221" s="7"/>
+      <c r="H221" s="7"/>
+      <c r="I221" s="7"/>
+      <c r="J221" s="7"/>
       <c r="K221" s="4" t="s">
         <v>13</v>
       </c>
@@ -7418,7 +7364,7 @@
         <v>223</v>
       </c>
       <c r="D222" s="4">
-        <v>16000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="E222" s="7"/>
       <c r="F222" s="7"/>
@@ -7442,22 +7388,14 @@
         <v>223</v>
       </c>
       <c r="D223" s="4">
-        <v>2000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E223" s="7"/>
       <c r="F223" s="7"/>
-      <c r="G223" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H223" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="I223" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J223" s="4">
-        <v>17000.0</v>
-      </c>
+      <c r="G223" s="7"/>
+      <c r="H223" s="7"/>
+      <c r="I223" s="7"/>
+      <c r="J223" s="7"/>
       <c r="K223" s="4" t="s">
         <v>13</v>
       </c>
@@ -7474,14 +7412,22 @@
         <v>223</v>
       </c>
       <c r="D224" s="4">
-        <v>17000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E224" s="7"/>
       <c r="F224" s="7"/>
-      <c r="G224" s="7"/>
-      <c r="H224" s="7"/>
-      <c r="I224" s="7"/>
-      <c r="J224" s="7"/>
+      <c r="G224" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H224" s="4">
+        <v>11000.0</v>
+      </c>
+      <c r="I224" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J224" s="4">
+        <v>21000.0</v>
+      </c>
       <c r="K224" s="4" t="s">
         <v>13</v>
       </c>
@@ -7498,22 +7444,14 @@
         <v>223</v>
       </c>
       <c r="D225" s="4">
-        <v>2000.0</v>
+        <v>21000.0</v>
       </c>
       <c r="E225" s="7"/>
       <c r="F225" s="7"/>
-      <c r="G225" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H225" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="I225" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J225" s="4">
-        <v>17000.0</v>
-      </c>
+      <c r="G225" s="7"/>
+      <c r="H225" s="7"/>
+      <c r="I225" s="7"/>
+      <c r="J225" s="7"/>
       <c r="K225" s="4" t="s">
         <v>13</v>
       </c>
@@ -7530,14 +7468,22 @@
         <v>223</v>
       </c>
       <c r="D226" s="4">
-        <v>17000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E226" s="7"/>
       <c r="F226" s="7"/>
-      <c r="G226" s="7"/>
-      <c r="H226" s="7"/>
-      <c r="I226" s="7"/>
-      <c r="J226" s="7"/>
+      <c r="G226" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H226" s="4">
+        <v>13000.0</v>
+      </c>
+      <c r="I226" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J226" s="4">
+        <v>25000.0</v>
+      </c>
       <c r="K226" s="4" t="s">
         <v>13</v>
       </c>
@@ -7554,26 +7500,14 @@
         <v>223</v>
       </c>
       <c r="D227" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E227" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="F227" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="G227" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H227" s="4">
-        <v>9500.0</v>
-      </c>
-      <c r="I227" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J227" s="4">
-        <v>18000.0</v>
-      </c>
+        <v>25000.0</v>
+      </c>
+      <c r="E227" s="7"/>
+      <c r="F227" s="7"/>
+      <c r="G227" s="7"/>
+      <c r="H227" s="7"/>
+      <c r="I227" s="7"/>
+      <c r="J227" s="7"/>
       <c r="K227" s="4" t="s">
         <v>13</v>
       </c>
@@ -7590,14 +7524,22 @@
         <v>223</v>
       </c>
       <c r="D228" s="4">
-        <v>18000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E228" s="7"/>
       <c r="F228" s="7"/>
-      <c r="G228" s="7"/>
-      <c r="H228" s="7"/>
-      <c r="I228" s="7"/>
-      <c r="J228" s="7"/>
+      <c r="G228" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H228" s="4">
+        <v>14000.0</v>
+      </c>
+      <c r="I228" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J228" s="4">
+        <v>28000.0</v>
+      </c>
       <c r="K228" s="4" t="s">
         <v>13</v>
       </c>
@@ -7614,22 +7556,14 @@
         <v>223</v>
       </c>
       <c r="D229" s="4">
-        <v>2500.0</v>
+        <v>28000.0</v>
       </c>
       <c r="E229" s="7"/>
       <c r="F229" s="7"/>
-      <c r="G229" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H229" s="4">
-        <v>14500.0</v>
-      </c>
-      <c r="I229" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J229" s="4">
-        <v>28000.0</v>
-      </c>
+      <c r="G229" s="7"/>
+      <c r="H229" s="7"/>
+      <c r="I229" s="7"/>
+      <c r="J229" s="7"/>
       <c r="K229" s="4" t="s">
         <v>13</v>
       </c>
@@ -7646,14 +7580,22 @@
         <v>223</v>
       </c>
       <c r="D230" s="4">
-        <v>28000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E230" s="7"/>
       <c r="F230" s="7"/>
-      <c r="G230" s="7"/>
-      <c r="H230" s="7"/>
-      <c r="I230" s="7"/>
-      <c r="J230" s="7"/>
+      <c r="G230" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H230" s="4">
+        <v>13000.0</v>
+      </c>
+      <c r="I230" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J230" s="4">
+        <v>25000.0</v>
+      </c>
       <c r="K230" s="4" t="s">
         <v>13</v>
       </c>
@@ -7670,22 +7612,14 @@
         <v>223</v>
       </c>
       <c r="D231" s="4">
-        <v>2500.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E231" s="7"/>
       <c r="F231" s="7"/>
-      <c r="G231" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H231" s="4">
-        <v>10500.0</v>
-      </c>
-      <c r="I231" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J231" s="4">
-        <v>20000.0</v>
-      </c>
+      <c r="G231" s="7"/>
+      <c r="H231" s="7"/>
+      <c r="I231" s="7"/>
+      <c r="J231" s="7"/>
       <c r="K231" s="4" t="s">
         <v>13</v>
       </c>
@@ -7702,14 +7636,22 @@
         <v>223</v>
       </c>
       <c r="D232" s="4">
-        <v>20000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E232" s="7"/>
       <c r="F232" s="7"/>
-      <c r="G232" s="7"/>
-      <c r="H232" s="7"/>
-      <c r="I232" s="7"/>
-      <c r="J232" s="7"/>
+      <c r="G232" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H232" s="4">
+        <v>14000.0</v>
+      </c>
+      <c r="I232" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J232" s="4">
+        <v>27000.0</v>
+      </c>
       <c r="K232" s="4" t="s">
         <v>13</v>
       </c>
@@ -7726,22 +7668,14 @@
         <v>223</v>
       </c>
       <c r="D233" s="4">
-        <v>2500.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="7"/>
-      <c r="G233" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H233" s="4">
-        <v>13000.0</v>
-      </c>
-      <c r="I233" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J233" s="4">
-        <v>25000.0</v>
-      </c>
+      <c r="G233" s="7"/>
+      <c r="H233" s="7"/>
+      <c r="I233" s="7"/>
+      <c r="J233" s="7"/>
       <c r="K233" s="4" t="s">
         <v>13</v>
       </c>
@@ -7758,14 +7692,22 @@
         <v>223</v>
       </c>
       <c r="D234" s="4">
-        <v>25000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E234" s="7"/>
       <c r="F234" s="7"/>
-      <c r="G234" s="7"/>
-      <c r="H234" s="7"/>
-      <c r="I234" s="7"/>
-      <c r="J234" s="7"/>
+      <c r="G234" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H234" s="4">
+        <v>14000.0</v>
+      </c>
+      <c r="I234" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J234" s="4">
+        <v>27000.0</v>
+      </c>
       <c r="K234" s="4" t="s">
         <v>13</v>
       </c>
@@ -7782,22 +7724,14 @@
         <v>223</v>
       </c>
       <c r="D235" s="4">
-        <v>2500.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E235" s="7"/>
       <c r="F235" s="7"/>
-      <c r="G235" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H235" s="4">
-        <v>11000.0</v>
-      </c>
-      <c r="I235" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J235" s="4">
-        <v>21000.0</v>
-      </c>
+      <c r="G235" s="7"/>
+      <c r="H235" s="7"/>
+      <c r="I235" s="7"/>
+      <c r="J235" s="7"/>
       <c r="K235" s="4" t="s">
         <v>13</v>
       </c>
@@ -7814,7 +7748,7 @@
         <v>223</v>
       </c>
       <c r="D236" s="4">
-        <v>21000.0</v>
+        <v>34000.0</v>
       </c>
       <c r="E236" s="7"/>
       <c r="F236" s="7"/>
@@ -7838,22 +7772,14 @@
         <v>223</v>
       </c>
       <c r="D237" s="4">
-        <v>2500.0</v>
+        <v>27000.0</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="7"/>
-      <c r="G237" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H237" s="4">
-        <v>13000.0</v>
-      </c>
-      <c r="I237" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J237" s="4">
-        <v>25000.0</v>
-      </c>
+      <c r="G237" s="7"/>
+      <c r="H237" s="7"/>
+      <c r="I237" s="7"/>
+      <c r="J237" s="7"/>
       <c r="K237" s="4" t="s">
         <v>13</v>
       </c>
@@ -7870,14 +7796,16 @@
         <v>223</v>
       </c>
       <c r="D238" s="4">
-        <v>25000.0</v>
+        <v>37000.0</v>
       </c>
       <c r="E238" s="7"/>
       <c r="F238" s="7"/>
-      <c r="G238" s="7"/>
-      <c r="H238" s="7"/>
-      <c r="I238" s="7"/>
-      <c r="J238" s="7"/>
+      <c r="G238" s="4"/>
+      <c r="H238" s="4"/>
+      <c r="I238" s="4"/>
+      <c r="J238" s="4">
+        <v>37000.0</v>
+      </c>
       <c r="K238" s="4" t="s">
         <v>13</v>
       </c>
@@ -7894,22 +7822,14 @@
         <v>223</v>
       </c>
       <c r="D239" s="4">
-        <v>2500.0</v>
+        <v>16000.0</v>
       </c>
       <c r="E239" s="7"/>
       <c r="F239" s="7"/>
-      <c r="G239" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H239" s="4">
-        <v>14000.0</v>
-      </c>
-      <c r="I239" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J239" s="4">
-        <v>28000.0</v>
-      </c>
+      <c r="G239" s="7"/>
+      <c r="H239" s="7"/>
+      <c r="I239" s="7"/>
+      <c r="J239" s="7"/>
       <c r="K239" s="4" t="s">
         <v>13</v>
       </c>
@@ -7926,7 +7846,7 @@
         <v>223</v>
       </c>
       <c r="D240" s="4">
-        <v>28000.0</v>
+        <v>43000.0</v>
       </c>
       <c r="E240" s="7"/>
       <c r="F240" s="7"/>
@@ -7950,22 +7870,14 @@
         <v>223</v>
       </c>
       <c r="D241" s="4">
-        <v>2500.0</v>
+        <v>23000.0</v>
       </c>
       <c r="E241" s="7"/>
       <c r="F241" s="7"/>
-      <c r="G241" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H241" s="4">
-        <v>13000.0</v>
-      </c>
-      <c r="I241" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J241" s="4">
-        <v>25000.0</v>
-      </c>
+      <c r="G241" s="7"/>
+      <c r="H241" s="7"/>
+      <c r="I241" s="7"/>
+      <c r="J241" s="7"/>
       <c r="K241" s="4" t="s">
         <v>13</v>
       </c>
@@ -7982,7 +7894,7 @@
         <v>223</v>
       </c>
       <c r="D242" s="4">
-        <v>25000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E242" s="7"/>
       <c r="F242" s="7"/>
@@ -8006,22 +7918,14 @@
         <v>223</v>
       </c>
       <c r="D243" s="4">
-        <v>2500.0</v>
+        <v>29000.0</v>
       </c>
       <c r="E243" s="7"/>
       <c r="F243" s="7"/>
-      <c r="G243" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H243" s="4">
-        <v>14000.0</v>
-      </c>
-      <c r="I243" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J243" s="4">
-        <v>27000.0</v>
-      </c>
+      <c r="G243" s="7"/>
+      <c r="H243" s="7"/>
+      <c r="I243" s="7"/>
+      <c r="J243" s="7"/>
       <c r="K243" s="4" t="s">
         <v>13</v>
       </c>
@@ -8038,7 +7942,7 @@
         <v>223</v>
       </c>
       <c r="D244" s="4">
-        <v>27000.0</v>
+        <v>13000.0</v>
       </c>
       <c r="E244" s="7"/>
       <c r="F244" s="7"/>
@@ -8062,22 +7966,14 @@
         <v>223</v>
       </c>
       <c r="D245" s="4">
-        <v>2500.0</v>
+        <v>39000.0</v>
       </c>
       <c r="E245" s="7"/>
       <c r="F245" s="7"/>
-      <c r="G245" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="H245" s="4">
-        <v>14000.0</v>
-      </c>
-      <c r="I245" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="J245" s="4">
-        <v>27000.0</v>
-      </c>
+      <c r="G245" s="7"/>
+      <c r="H245" s="7"/>
+      <c r="I245" s="7"/>
+      <c r="J245" s="7"/>
       <c r="K245" s="4" t="s">
         <v>13</v>
       </c>
@@ -8094,7 +7990,7 @@
         <v>223</v>
       </c>
       <c r="D246" s="4">
-        <v>27000.0</v>
+        <v>382000.0</v>
       </c>
       <c r="E246" s="7"/>
       <c r="F246" s="7"/>
@@ -8103,7 +7999,7 @@
       <c r="I246" s="7"/>
       <c r="J246" s="7"/>
       <c r="K246" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="247">
@@ -8115,10 +8011,10 @@
         <v>262</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>223</v>
+        <v>263</v>
       </c>
       <c r="D247" s="4">
-        <v>34000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E247" s="7"/>
       <c r="F247" s="7"/>
@@ -8136,13 +8032,13 @@
         <v>247</v>
       </c>
       <c r="B248" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C248" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="C248" s="5" t="s">
-        <v>223</v>
-      </c>
       <c r="D248" s="4">
-        <v>27000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E248" s="7"/>
       <c r="F248" s="7"/>
@@ -8151,7 +8047,7 @@
       <c r="I248" s="7"/>
       <c r="J248" s="7"/>
       <c r="K248" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="249">
@@ -8160,22 +8056,24 @@
         <v>248</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>223</v>
+        <v>263</v>
       </c>
       <c r="D249" s="4">
-        <v>37000.0</v>
-      </c>
-      <c r="E249" s="7"/>
-      <c r="F249" s="7"/>
-      <c r="G249" s="4"/>
-      <c r="H249" s="4"/>
-      <c r="I249" s="4"/>
-      <c r="J249" s="4">
-        <v>37000.0</v>
-      </c>
+        <v>2500.0</v>
+      </c>
+      <c r="E249" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F249" s="4">
+        <v>10000.0</v>
+      </c>
+      <c r="G249" s="7"/>
+      <c r="H249" s="7"/>
+      <c r="I249" s="7"/>
+      <c r="J249" s="7"/>
       <c r="K249" s="4" t="s">
         <v>13</v>
       </c>
@@ -8186,16 +8084,20 @@
         <v>249</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>223</v>
+        <v>267</v>
       </c>
       <c r="D250" s="4">
-        <v>16000.0</v>
-      </c>
-      <c r="E250" s="7"/>
-      <c r="F250" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E250" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F250" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G250" s="7"/>
       <c r="H250" s="7"/>
       <c r="I250" s="7"/>
@@ -8210,13 +8112,13 @@
         <v>250</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>223</v>
+        <v>267</v>
       </c>
       <c r="D251" s="4">
-        <v>43000.0</v>
+        <v>109000.0</v>
       </c>
       <c r="E251" s="7"/>
       <c r="F251" s="7"/>
@@ -8225,7 +8127,7 @@
       <c r="I251" s="7"/>
       <c r="J251" s="7"/>
       <c r="K251" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="252">
@@ -8234,16 +8136,20 @@
         <v>251</v>
       </c>
       <c r="B252" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C252" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="C252" s="5" t="s">
-        <v>223</v>
-      </c>
       <c r="D252" s="4">
-        <v>23000.0</v>
-      </c>
-      <c r="E252" s="7"/>
-      <c r="F252" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E252" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F252" s="4">
+        <v>14000.0</v>
+      </c>
       <c r="G252" s="7"/>
       <c r="H252" s="7"/>
       <c r="I252" s="7"/>
@@ -8258,13 +8164,13 @@
         <v>252</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>223</v>
+        <v>267</v>
       </c>
       <c r="D253" s="4">
-        <v>17000.0</v>
+        <v>109000.0</v>
       </c>
       <c r="E253" s="7"/>
       <c r="F253" s="7"/>
@@ -8273,7 +8179,7 @@
       <c r="I253" s="7"/>
       <c r="J253" s="7"/>
       <c r="K253" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="254">
@@ -8282,13 +8188,13 @@
         <v>253</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>223</v>
+        <v>267</v>
       </c>
       <c r="D254" s="4">
-        <v>29000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E254" s="7"/>
       <c r="F254" s="7"/>
@@ -8306,13 +8212,13 @@
         <v>254</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>223</v>
+        <v>267</v>
       </c>
       <c r="D255" s="4">
-        <v>13000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E255" s="7"/>
       <c r="F255" s="7"/>
@@ -8321,7 +8227,7 @@
       <c r="I255" s="7"/>
       <c r="J255" s="7"/>
       <c r="K255" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="256">
@@ -8330,13 +8236,13 @@
         <v>255</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>223</v>
+        <v>267</v>
       </c>
       <c r="D256" s="4">
-        <v>39000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E256" s="7"/>
       <c r="F256" s="7"/>
@@ -8354,22 +8260,26 @@
         <v>256</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>223</v>
+        <v>267</v>
       </c>
       <c r="D257" s="4">
-        <v>382000.0</v>
-      </c>
-      <c r="E257" s="7"/>
-      <c r="F257" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E257" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F257" s="4">
+        <v>39000.0</v>
+      </c>
       <c r="G257" s="7"/>
       <c r="H257" s="7"/>
       <c r="I257" s="7"/>
       <c r="J257" s="7"/>
       <c r="K257" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="258">
@@ -8378,13 +8288,13 @@
         <v>257</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D258" s="4">
-        <v>500.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E258" s="7"/>
       <c r="F258" s="7"/>
@@ -8393,7 +8303,7 @@
       <c r="I258" s="7"/>
       <c r="J258" s="7"/>
       <c r="K258" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="259">
@@ -8402,13 +8312,13 @@
         <v>258</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D259" s="4">
-        <v>4000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E259" s="7"/>
       <c r="F259" s="7"/>
@@ -8417,7 +8327,7 @@
       <c r="I259" s="7"/>
       <c r="J259" s="7"/>
       <c r="K259" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="260">
@@ -8426,26 +8336,22 @@
         <v>259</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D260" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E260" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F260" s="4">
-        <v>10000.0</v>
-      </c>
+        <v>114000.0</v>
+      </c>
+      <c r="E260" s="7"/>
+      <c r="F260" s="7"/>
       <c r="G260" s="7"/>
       <c r="H260" s="7"/>
       <c r="I260" s="7"/>
       <c r="J260" s="7"/>
       <c r="K260" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="261">
@@ -8454,20 +8360,16 @@
         <v>260</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D261" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E261" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F261" s="4">
-        <v>14000.0</v>
-      </c>
+      <c r="E261" s="7"/>
+      <c r="F261" s="7"/>
       <c r="G261" s="7"/>
       <c r="H261" s="7"/>
       <c r="I261" s="7"/>
@@ -8485,10 +8387,10 @@
         <v>279</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D262" s="4">
-        <v>109000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E262" s="7"/>
       <c r="F262" s="7"/>
@@ -8509,17 +8411,13 @@
         <v>280</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D263" s="4">
         <v>3000.0</v>
       </c>
-      <c r="E263" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F263" s="4">
-        <v>14000.0</v>
-      </c>
+      <c r="E263" s="7"/>
+      <c r="F263" s="7"/>
       <c r="G263" s="7"/>
       <c r="H263" s="7"/>
       <c r="I263" s="7"/>
@@ -8537,10 +8435,10 @@
         <v>281</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D264" s="4">
-        <v>109000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="E264" s="7"/>
       <c r="F264" s="7"/>
@@ -8561,7 +8459,7 @@
         <v>282</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D265" s="4">
         <v>3000.0</v>
@@ -8585,10 +8483,10 @@
         <v>283</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D266" s="4">
-        <v>114000.0</v>
+        <v>107000.0</v>
       </c>
       <c r="E266" s="7"/>
       <c r="F266" s="7"/>
@@ -8609,7 +8507,7 @@
         <v>284</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D267" s="4">
         <v>3000.0</v>
@@ -8620,9 +8518,7 @@
       <c r="H267" s="7"/>
       <c r="I267" s="7"/>
       <c r="J267" s="7"/>
-      <c r="K267" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="K267" s="4"/>
     </row>
     <row r="268">
       <c r="A268" s="4">
@@ -8633,24 +8529,18 @@
         <v>285</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D268" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E268" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F268" s="4">
-        <v>39000.0</v>
-      </c>
+        <v>107000.0</v>
+      </c>
+      <c r="E268" s="7"/>
+      <c r="F268" s="7"/>
       <c r="G268" s="7"/>
       <c r="H268" s="7"/>
       <c r="I268" s="7"/>
       <c r="J268" s="7"/>
-      <c r="K268" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="K268" s="4"/>
     </row>
     <row r="269">
       <c r="A269" s="4">
@@ -8661,10 +8551,10 @@
         <v>286</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D269" s="4">
-        <v>114000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E269" s="7"/>
       <c r="F269" s="7"/>
@@ -8673,7 +8563,7 @@
       <c r="I269" s="7"/>
       <c r="J269" s="7"/>
       <c r="K269" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="270">
@@ -8685,19 +8575,19 @@
         <v>287</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D270" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E270" s="7"/>
-      <c r="F270" s="7"/>
-      <c r="G270" s="7"/>
-      <c r="H270" s="7"/>
-      <c r="I270" s="7"/>
-      <c r="J270" s="7"/>
+        <v>112000.0</v>
+      </c>
+      <c r="E270" s="6"/>
+      <c r="F270" s="6"/>
+      <c r="G270" s="6"/>
+      <c r="H270" s="6"/>
+      <c r="I270" s="6"/>
+      <c r="J270" s="6"/>
       <c r="K270" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="271">
@@ -8709,19 +8599,23 @@
         <v>288</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D271" s="4">
-        <v>114000.0</v>
-      </c>
-      <c r="E271" s="7"/>
-      <c r="F271" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E271" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F271" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G271" s="7"/>
       <c r="H271" s="7"/>
       <c r="I271" s="7"/>
       <c r="J271" s="7"/>
       <c r="K271" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="272">
@@ -8733,13 +8627,17 @@
         <v>289</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D272" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E272" s="7"/>
-      <c r="F272" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E272" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F272" s="4">
+        <v>19000.0</v>
+      </c>
       <c r="G272" s="7"/>
       <c r="H272" s="7"/>
       <c r="I272" s="7"/>
@@ -8757,13 +8655,13 @@
         <v>290</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D273" s="4">
-        <v>114000.0</v>
-      </c>
-      <c r="E273" s="7"/>
-      <c r="F273" s="7"/>
+        <v>86000.0</v>
+      </c>
+      <c r="E273" s="4"/>
+      <c r="F273" s="4"/>
       <c r="G273" s="7"/>
       <c r="H273" s="7"/>
       <c r="I273" s="7"/>
@@ -8781,13 +8679,13 @@
         <v>291</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D274" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E274" s="7"/>
-      <c r="F274" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E274" s="4"/>
+      <c r="F274" s="4"/>
       <c r="G274" s="7"/>
       <c r="H274" s="7"/>
       <c r="I274" s="7"/>
@@ -8805,13 +8703,13 @@
         <v>292</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D275" s="4">
-        <v>114000.0</v>
-      </c>
-      <c r="E275" s="7"/>
-      <c r="F275" s="7"/>
+        <v>86000.0</v>
+      </c>
+      <c r="E275" s="4"/>
+      <c r="F275" s="4"/>
       <c r="G275" s="7"/>
       <c r="H275" s="7"/>
       <c r="I275" s="7"/>
@@ -8829,14 +8727,18 @@
         <v>293</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D276" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E276" s="7"/>
-      <c r="F276" s="7"/>
-      <c r="G276" s="7"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E276" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F276" s="4">
+        <v>19500.0</v>
+      </c>
+      <c r="G276" s="4"/>
       <c r="H276" s="7"/>
       <c r="I276" s="7"/>
       <c r="J276" s="7"/>
@@ -8853,19 +8755,23 @@
         <v>294</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D277" s="4">
-        <v>107000.0</v>
-      </c>
-      <c r="E277" s="7"/>
-      <c r="F277" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E277" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F277" s="4">
+        <v>6000.0</v>
+      </c>
       <c r="G277" s="7"/>
       <c r="H277" s="7"/>
       <c r="I277" s="7"/>
       <c r="J277" s="7"/>
       <c r="K277" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="278">
@@ -8877,10 +8783,10 @@
         <v>295</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D278" s="4">
-        <v>3000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E278" s="7"/>
       <c r="F278" s="7"/>
@@ -8888,7 +8794,9 @@
       <c r="H278" s="7"/>
       <c r="I278" s="7"/>
       <c r="J278" s="7"/>
-      <c r="K278" s="4"/>
+      <c r="K278" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="4">
@@ -8899,10 +8807,10 @@
         <v>296</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D279" s="4">
-        <v>107000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E279" s="7"/>
       <c r="F279" s="7"/>
@@ -8921,10 +8829,10 @@
         <v>297</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D280" s="4">
-        <v>3000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E280" s="7"/>
       <c r="F280" s="7"/>
@@ -8945,17 +8853,17 @@
         <v>298</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D281" s="4">
-        <v>112000.0</v>
-      </c>
-      <c r="E281" s="6"/>
-      <c r="F281" s="6"/>
-      <c r="G281" s="6"/>
-      <c r="H281" s="6"/>
-      <c r="I281" s="6"/>
-      <c r="J281" s="6"/>
+        <v>88000.0</v>
+      </c>
+      <c r="E281" s="7"/>
+      <c r="F281" s="7"/>
+      <c r="G281" s="7"/>
+      <c r="H281" s="7"/>
+      <c r="I281" s="7"/>
+      <c r="J281" s="7"/>
       <c r="K281" s="4" t="s">
         <v>15</v>
       </c>
@@ -8969,17 +8877,13 @@
         <v>299</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D282" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E282" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F282" s="4">
-        <v>19000.0</v>
-      </c>
+        <v>7500.0</v>
+      </c>
+      <c r="E282" s="7"/>
+      <c r="F282" s="7"/>
       <c r="G282" s="7"/>
       <c r="H282" s="7"/>
       <c r="I282" s="7"/>
@@ -8997,17 +8901,13 @@
         <v>300</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D283" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E283" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F283" s="4">
-        <v>19000.0</v>
-      </c>
+        <v>3500.0</v>
+      </c>
+      <c r="E283" s="7"/>
+      <c r="F283" s="7"/>
       <c r="G283" s="7"/>
       <c r="H283" s="7"/>
       <c r="I283" s="7"/>
@@ -9025,13 +8925,13 @@
         <v>301</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D284" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E284" s="4"/>
-      <c r="F284" s="4"/>
+        <v>36000.0</v>
+      </c>
+      <c r="E284" s="7"/>
+      <c r="F284" s="7"/>
       <c r="G284" s="7"/>
       <c r="H284" s="7"/>
       <c r="I284" s="7"/>
@@ -9049,13 +8949,13 @@
         <v>302</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D285" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E285" s="4"/>
-      <c r="F285" s="4"/>
+        <v>4500.0</v>
+      </c>
+      <c r="E285" s="7"/>
+      <c r="F285" s="7"/>
       <c r="G285" s="7"/>
       <c r="H285" s="7"/>
       <c r="I285" s="7"/>
@@ -9073,13 +8973,13 @@
         <v>303</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D286" s="4">
-        <v>86000.0</v>
-      </c>
-      <c r="E286" s="4"/>
-      <c r="F286" s="4"/>
+        <v>102000.0</v>
+      </c>
+      <c r="E286" s="7"/>
+      <c r="F286" s="7"/>
       <c r="G286" s="7"/>
       <c r="H286" s="7"/>
       <c r="I286" s="7"/>
@@ -9097,18 +8997,14 @@
         <v>304</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="D287" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E287" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F287" s="4">
-        <v>19500.0</v>
-      </c>
-      <c r="G287" s="4"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E287" s="7"/>
+      <c r="F287" s="7"/>
+      <c r="G287" s="7"/>
       <c r="H287" s="7"/>
       <c r="I287" s="7"/>
       <c r="J287" s="7"/>
@@ -9125,21 +9021,17 @@
         <v>305</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="D288" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E288" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F288" s="4">
-        <v>6000.0</v>
-      </c>
-      <c r="G288" s="7"/>
-      <c r="H288" s="7"/>
-      <c r="I288" s="7"/>
-      <c r="J288" s="7"/>
+        <v>80000.0</v>
+      </c>
+      <c r="E288" s="6"/>
+      <c r="F288" s="6"/>
+      <c r="G288" s="6"/>
+      <c r="H288" s="6"/>
+      <c r="I288" s="6"/>
+      <c r="J288" s="6"/>
       <c r="K288" s="4" t="s">
         <v>13</v>
       </c>
@@ -9153,10 +9045,10 @@
         <v>306</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="D289" s="4">
-        <v>1000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E289" s="7"/>
       <c r="F289" s="7"/>
@@ -9174,13 +9066,13 @@
         <v>289</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="D290" s="4">
-        <v>4000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E290" s="7"/>
       <c r="F290" s="7"/>
@@ -9198,13 +9090,13 @@
         <v>290</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="D291" s="4">
-        <v>88000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E291" s="7"/>
       <c r="F291" s="7"/>
@@ -9213,7 +9105,7 @@
       <c r="I291" s="7"/>
       <c r="J291" s="7"/>
       <c r="K291" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="292">
@@ -9222,13 +9114,13 @@
         <v>291</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="D292" s="4">
-        <v>7500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E292" s="7"/>
       <c r="F292" s="7"/>
@@ -9246,13 +9138,13 @@
         <v>292</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="D293" s="4">
-        <v>3500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E293" s="7"/>
       <c r="F293" s="7"/>
@@ -9270,13 +9162,13 @@
         <v>293</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="D294" s="4">
-        <v>36000.0</v>
+        <v>12500.0</v>
       </c>
       <c r="E294" s="7"/>
       <c r="F294" s="7"/>
@@ -9294,13 +9186,13 @@
         <v>294</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="D295" s="4">
-        <v>4500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E295" s="7"/>
       <c r="F295" s="7"/>
@@ -9318,13 +9210,13 @@
         <v>295</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="D296" s="4">
-        <v>102000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E296" s="7"/>
       <c r="F296" s="7"/>
@@ -9342,10 +9234,10 @@
         <v>296</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="D297" s="4">
         <v>3000.0</v>
@@ -9366,22 +9258,22 @@
         <v>297</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D298" s="4">
-        <v>80000.0</v>
-      </c>
-      <c r="E298" s="6"/>
-      <c r="F298" s="6"/>
-      <c r="G298" s="6"/>
-      <c r="H298" s="6"/>
-      <c r="I298" s="6"/>
-      <c r="J298" s="6"/>
+        <v>23000.0</v>
+      </c>
+      <c r="E298" s="7"/>
+      <c r="F298" s="7"/>
+      <c r="G298" s="7"/>
+      <c r="H298" s="7"/>
+      <c r="I298" s="7"/>
+      <c r="J298" s="7"/>
       <c r="K298" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="299">
@@ -9390,16 +9282,20 @@
         <v>298</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D299" s="4">
-        <v>14000.0</v>
-      </c>
-      <c r="E299" s="7"/>
-      <c r="F299" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E299" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F299" s="4">
+        <v>7500.0</v>
+      </c>
       <c r="G299" s="7"/>
       <c r="H299" s="7"/>
       <c r="I299" s="7"/>
@@ -9414,22 +9310,22 @@
         <v>299</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D300" s="4">
-        <v>14500.0</v>
-      </c>
-      <c r="E300" s="7"/>
-      <c r="F300" s="7"/>
+        <v>7500.0</v>
+      </c>
+      <c r="E300" s="4"/>
+      <c r="F300" s="4"/>
       <c r="G300" s="7"/>
       <c r="H300" s="7"/>
       <c r="I300" s="7"/>
       <c r="J300" s="7"/>
       <c r="K300" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="301">
@@ -9441,13 +9337,17 @@
         <v>316</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D301" s="4">
-        <v>15000.0</v>
-      </c>
-      <c r="E301" s="7"/>
-      <c r="F301" s="7"/>
+        <v>2500.0</v>
+      </c>
+      <c r="E301" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F301" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G301" s="7"/>
       <c r="H301" s="7"/>
       <c r="I301" s="7"/>
@@ -9462,22 +9362,22 @@
         <v>301</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D302" s="4">
-        <v>15500.0</v>
-      </c>
-      <c r="E302" s="7"/>
-      <c r="F302" s="7"/>
+        <v>9000.0</v>
+      </c>
+      <c r="E302" s="4"/>
+      <c r="F302" s="4"/>
       <c r="G302" s="7"/>
       <c r="H302" s="7"/>
       <c r="I302" s="7"/>
       <c r="J302" s="7"/>
       <c r="K302" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="303">
@@ -9486,16 +9386,20 @@
         <v>302</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D303" s="4">
-        <v>1500.0</v>
-      </c>
-      <c r="E303" s="7"/>
-      <c r="F303" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E303" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F303" s="4">
+        <v>7500.0</v>
+      </c>
       <c r="G303" s="7"/>
       <c r="H303" s="7"/>
       <c r="I303" s="7"/>
@@ -9513,10 +9417,10 @@
         <v>319</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D304" s="4">
-        <v>12500.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E304" s="7"/>
       <c r="F304" s="7"/>
@@ -9537,10 +9441,10 @@
         <v>320</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D305" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E305" s="7"/>
       <c r="F305" s="7"/>
@@ -9558,13 +9462,13 @@
         <v>305</v>
       </c>
       <c r="B306" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C306" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="C306" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D306" s="4">
-        <v>4500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E306" s="7"/>
       <c r="F306" s="7"/>
@@ -9582,13 +9486,13 @@
         <v>306</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D307" s="4">
-        <v>3000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E307" s="7"/>
       <c r="F307" s="7"/>
@@ -9606,13 +9510,13 @@
         <v>307</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D308" s="4">
-        <v>23000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E308" s="7"/>
       <c r="F308" s="7"/>
@@ -9630,20 +9534,16 @@
         <v>308</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D309" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E309" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F309" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E309" s="7"/>
+      <c r="F309" s="7"/>
       <c r="G309" s="7"/>
       <c r="H309" s="7"/>
       <c r="I309" s="7"/>
@@ -9658,16 +9558,16 @@
         <v>309</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D310" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E310" s="4"/>
-      <c r="F310" s="4"/>
+        <v>10000.0</v>
+      </c>
+      <c r="E310" s="7"/>
+      <c r="F310" s="7"/>
       <c r="G310" s="7"/>
       <c r="H310" s="7"/>
       <c r="I310" s="7"/>
@@ -9682,20 +9582,16 @@
         <v>310</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D311" s="4">
-        <v>2500.0</v>
-      </c>
-      <c r="E311" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F311" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>500.0</v>
+      </c>
+      <c r="E311" s="7"/>
+      <c r="F311" s="7"/>
       <c r="G311" s="7"/>
       <c r="H311" s="7"/>
       <c r="I311" s="7"/>
@@ -9710,16 +9606,16 @@
         <v>311</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D312" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="E312" s="4"/>
-      <c r="F312" s="4"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E312" s="7"/>
+      <c r="F312" s="7"/>
       <c r="G312" s="7"/>
       <c r="H312" s="7"/>
       <c r="I312" s="7"/>
@@ -9734,20 +9630,16 @@
         <v>312</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D313" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E313" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F313" s="4">
-        <v>7500.0</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E313" s="7"/>
+      <c r="F313" s="7"/>
       <c r="G313" s="7"/>
       <c r="H313" s="7"/>
       <c r="I313" s="7"/>
@@ -9762,13 +9654,13 @@
         <v>313</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D314" s="4">
-        <v>7500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E314" s="7"/>
       <c r="F314" s="7"/>
@@ -9786,10 +9678,10 @@
         <v>314</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D315" s="4">
         <v>1000.0</v>
@@ -9813,7 +9705,7 @@
         <v>332</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D316" s="4">
         <v>10000.0</v>
@@ -9837,10 +9729,10 @@
         <v>333</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D317" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E317" s="7"/>
       <c r="F317" s="7"/>
@@ -9861,10 +9753,10 @@
         <v>334</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D318" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E318" s="7"/>
       <c r="F318" s="7"/>
@@ -9873,7 +9765,7 @@
       <c r="I318" s="7"/>
       <c r="J318" s="7"/>
       <c r="K318" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="319">
@@ -9885,10 +9777,10 @@
         <v>335</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D319" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E319" s="7"/>
       <c r="F319" s="7"/>
@@ -9897,7 +9789,7 @@
       <c r="I319" s="7"/>
       <c r="J319" s="7"/>
       <c r="K319" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="320">
@@ -9909,10 +9801,10 @@
         <v>336</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D320" s="4">
-        <v>10000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E320" s="7"/>
       <c r="F320" s="7"/>
@@ -9921,7 +9813,7 @@
       <c r="I320" s="7"/>
       <c r="J320" s="7"/>
       <c r="K320" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="321">
@@ -9933,10 +9825,10 @@
         <v>337</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D321" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E321" s="7"/>
       <c r="F321" s="7"/>
@@ -9945,7 +9837,7 @@
       <c r="I321" s="7"/>
       <c r="J321" s="7"/>
       <c r="K321" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="322">
@@ -9957,10 +9849,10 @@
         <v>338</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D322" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E322" s="7"/>
       <c r="F322" s="7"/>
@@ -9969,7 +9861,7 @@
       <c r="I322" s="7"/>
       <c r="J322" s="7"/>
       <c r="K322" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="323">
@@ -9981,10 +9873,10 @@
         <v>339</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D323" s="4">
-        <v>1000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E323" s="7"/>
       <c r="F323" s="7"/>
@@ -9993,7 +9885,7 @@
       <c r="I323" s="7"/>
       <c r="J323" s="7"/>
       <c r="K323" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="324">
@@ -10005,10 +9897,10 @@
         <v>340</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D324" s="4">
-        <v>10000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E324" s="7"/>
       <c r="F324" s="7"/>
@@ -10017,7 +9909,7 @@
       <c r="I324" s="7"/>
       <c r="J324" s="7"/>
       <c r="K324" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="325">
@@ -10029,10 +9921,10 @@
         <v>341</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D325" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E325" s="7"/>
       <c r="F325" s="7"/>
@@ -10053,10 +9945,10 @@
         <v>342</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D326" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E326" s="7"/>
       <c r="F326" s="7"/>
@@ -10065,7 +9957,7 @@
       <c r="I326" s="7"/>
       <c r="J326" s="7"/>
       <c r="K326" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="327">
@@ -10077,10 +9969,10 @@
         <v>343</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D327" s="4">
-        <v>10000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E327" s="7"/>
       <c r="F327" s="7"/>
@@ -10089,7 +9981,7 @@
       <c r="I327" s="7"/>
       <c r="J327" s="7"/>
       <c r="K327" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="328">
@@ -10101,10 +9993,10 @@
         <v>344</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D328" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E328" s="7"/>
       <c r="F328" s="7"/>
@@ -10125,7 +10017,7 @@
         <v>345</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D329" s="4">
         <v>5000.0</v>
@@ -10149,10 +10041,10 @@
         <v>346</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D330" s="4">
-        <v>500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E330" s="7"/>
       <c r="F330" s="7"/>
@@ -10173,7 +10065,7 @@
         <v>347</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D331" s="4">
         <v>5000.0</v>
@@ -10197,10 +10089,10 @@
         <v>348</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D332" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E332" s="7"/>
       <c r="F332" s="7"/>
@@ -10221,10 +10113,10 @@
         <v>349</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D333" s="4">
-        <v>10000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E333" s="7"/>
       <c r="F333" s="7"/>
@@ -10233,7 +10125,7 @@
       <c r="I333" s="7"/>
       <c r="J333" s="7"/>
       <c r="K333" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="334">
@@ -10245,10 +10137,10 @@
         <v>350</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D334" s="4">
-        <v>2000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E334" s="7"/>
       <c r="F334" s="7"/>
@@ -10257,7 +10149,7 @@
       <c r="I334" s="7"/>
       <c r="J334" s="7"/>
       <c r="K334" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="335">
@@ -10269,7 +10161,7 @@
         <v>351</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D335" s="4">
         <v>5000.0</v>
@@ -10293,10 +10185,10 @@
         <v>352</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D336" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E336" s="7"/>
       <c r="F336" s="7"/>
@@ -10317,7 +10209,7 @@
         <v>353</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D337" s="4">
         <v>5000.0</v>
@@ -10341,10 +10233,10 @@
         <v>354</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D338" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E338" s="7"/>
       <c r="F338" s="7"/>
@@ -10365,7 +10257,7 @@
         <v>355</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D339" s="4">
         <v>5000.0</v>
@@ -10389,7 +10281,7 @@
         <v>356</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D340" s="4">
         <v>1000.0</v>
@@ -10413,7 +10305,7 @@
         <v>357</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D341" s="4">
         <v>5000.0</v>
@@ -10437,13 +10329,17 @@
         <v>358</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D342" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E342" s="7"/>
-      <c r="F342" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E342" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F342" s="4">
+        <v>4500.0</v>
+      </c>
       <c r="G342" s="7"/>
       <c r="H342" s="7"/>
       <c r="I342" s="7"/>
@@ -10461,10 +10357,10 @@
         <v>359</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D343" s="4">
-        <v>500.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E343" s="7"/>
       <c r="F343" s="7"/>
@@ -10473,7 +10369,7 @@
       <c r="I343" s="7"/>
       <c r="J343" s="7"/>
       <c r="K343" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="344">
@@ -10485,13 +10381,13 @@
         <v>360</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D344" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E344" s="7"/>
-      <c r="F344" s="7"/>
+        <v>51000.0</v>
+      </c>
+      <c r="E344" s="4"/>
+      <c r="F344" s="4"/>
       <c r="G344" s="7"/>
       <c r="H344" s="7"/>
       <c r="I344" s="7"/>
@@ -10509,13 +10405,17 @@
         <v>361</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D345" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E345" s="7"/>
-      <c r="F345" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E345" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F345" s="4">
+        <v>9000.0</v>
+      </c>
       <c r="G345" s="7"/>
       <c r="H345" s="7"/>
       <c r="I345" s="7"/>
@@ -10533,10 +10433,10 @@
         <v>362</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D346" s="4">
-        <v>500.0</v>
+        <v>52000.0</v>
       </c>
       <c r="E346" s="7"/>
       <c r="F346" s="7"/>
@@ -10545,7 +10445,7 @@
       <c r="I346" s="7"/>
       <c r="J346" s="7"/>
       <c r="K346" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="347">
@@ -10557,10 +10457,10 @@
         <v>363</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D347" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E347" s="7"/>
       <c r="F347" s="7"/>
@@ -10569,7 +10469,7 @@
       <c r="I347" s="7"/>
       <c r="J347" s="7"/>
       <c r="K347" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="348">
@@ -10581,10 +10481,10 @@
         <v>364</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D348" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E348" s="7"/>
       <c r="F348" s="7"/>
@@ -10593,7 +10493,7 @@
       <c r="I348" s="7"/>
       <c r="J348" s="7"/>
       <c r="K348" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="349">
@@ -10605,19 +10505,23 @@
         <v>365</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D349" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E349" s="7"/>
-      <c r="F349" s="7"/>
+        <v>2000.0</v>
+      </c>
+      <c r="E349" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="F349" s="4">
+        <v>17000.0</v>
+      </c>
       <c r="G349" s="7"/>
       <c r="H349" s="7"/>
       <c r="I349" s="7"/>
       <c r="J349" s="7"/>
       <c r="K349" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="350">
@@ -10629,10 +10533,10 @@
         <v>366</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D350" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E350" s="7"/>
       <c r="F350" s="7"/>
@@ -10641,7 +10545,7 @@
       <c r="I350" s="7"/>
       <c r="J350" s="7"/>
       <c r="K350" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="351">
@@ -10653,19 +10557,23 @@
         <v>367</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D351" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E351" s="7"/>
-      <c r="F351" s="7"/>
+        <v>7000.0</v>
+      </c>
+      <c r="E351" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F351" s="4">
+        <v>32500.0</v>
+      </c>
       <c r="G351" s="7"/>
       <c r="H351" s="7"/>
       <c r="I351" s="7"/>
       <c r="J351" s="7"/>
       <c r="K351" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="352">
@@ -10677,17 +10585,13 @@
         <v>368</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D352" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E352" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F352" s="4">
-        <v>4500.0</v>
-      </c>
+        <v>7500.0</v>
+      </c>
+      <c r="E352" s="7"/>
+      <c r="F352" s="7"/>
       <c r="G352" s="7"/>
       <c r="H352" s="7"/>
       <c r="I352" s="7"/>
@@ -10705,10 +10609,10 @@
         <v>369</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D353" s="4">
-        <v>4500.0</v>
+        <v>9500.0</v>
       </c>
       <c r="E353" s="7"/>
       <c r="F353" s="7"/>
@@ -10717,7 +10621,7 @@
       <c r="I353" s="7"/>
       <c r="J353" s="7"/>
       <c r="K353" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="354">
@@ -10729,19 +10633,19 @@
         <v>370</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D354" s="4">
-        <v>51000.0</v>
-      </c>
-      <c r="E354" s="4"/>
-      <c r="F354" s="4"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E354" s="7"/>
+      <c r="F354" s="7"/>
       <c r="G354" s="7"/>
       <c r="H354" s="7"/>
       <c r="I354" s="7"/>
       <c r="J354" s="7"/>
       <c r="K354" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="355">
@@ -10753,17 +10657,13 @@
         <v>371</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D355" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E355" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F355" s="4">
-        <v>9000.0</v>
-      </c>
+        <v>5000.0</v>
+      </c>
+      <c r="E355" s="7"/>
+      <c r="F355" s="7"/>
       <c r="G355" s="7"/>
       <c r="H355" s="7"/>
       <c r="I355" s="7"/>
@@ -10781,19 +10681,23 @@
         <v>372</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D356" s="4">
-        <v>52000.0</v>
-      </c>
-      <c r="E356" s="7"/>
-      <c r="F356" s="7"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E356" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F356" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G356" s="7"/>
       <c r="H356" s="7"/>
       <c r="I356" s="7"/>
       <c r="J356" s="7"/>
       <c r="K356" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="357">
@@ -10805,13 +10709,17 @@
         <v>373</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D357" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E357" s="7"/>
-      <c r="F357" s="7"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E357" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F357" s="4">
+        <v>12500.0</v>
+      </c>
       <c r="G357" s="7"/>
       <c r="H357" s="7"/>
       <c r="I357" s="7"/>
@@ -10829,19 +10737,19 @@
         <v>374</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D358" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E358" s="7"/>
-      <c r="F358" s="7"/>
+        <v>3500.0</v>
+      </c>
+      <c r="E358" s="4"/>
+      <c r="F358" s="4"/>
       <c r="G358" s="7"/>
       <c r="H358" s="7"/>
       <c r="I358" s="7"/>
       <c r="J358" s="7"/>
       <c r="K358" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="359">
@@ -10853,18 +10761,14 @@
         <v>375</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D359" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E359" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="F359" s="4">
-        <v>17000.0</v>
-      </c>
-      <c r="G359" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E359" s="4"/>
+      <c r="F359" s="4"/>
+      <c r="G359" s="4"/>
       <c r="H359" s="7"/>
       <c r="I359" s="7"/>
       <c r="J359" s="7"/>
@@ -10881,19 +10785,23 @@
         <v>376</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D360" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E360" s="7"/>
-      <c r="F360" s="7"/>
+        <v>3000.0</v>
+      </c>
+      <c r="E360" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F360" s="4">
+        <v>11500.0</v>
+      </c>
       <c r="G360" s="7"/>
       <c r="H360" s="7"/>
       <c r="I360" s="7"/>
       <c r="J360" s="7"/>
       <c r="K360" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="361">
@@ -10905,17 +10813,13 @@
         <v>377</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D361" s="4">
-        <v>7000.0</v>
-      </c>
-      <c r="E361" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F361" s="4">
-        <v>32500.0</v>
-      </c>
+        <v>4000.0</v>
+      </c>
+      <c r="E361" s="7"/>
+      <c r="F361" s="7"/>
       <c r="G361" s="7"/>
       <c r="H361" s="7"/>
       <c r="I361" s="7"/>
@@ -10933,13 +10837,17 @@
         <v>378</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D362" s="4">
-        <v>7500.0</v>
-      </c>
-      <c r="E362" s="7"/>
-      <c r="F362" s="7"/>
+        <v>5000.0</v>
+      </c>
+      <c r="E362" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F362" s="4">
+        <v>22500.0</v>
+      </c>
       <c r="G362" s="7"/>
       <c r="H362" s="7"/>
       <c r="I362" s="7"/>
@@ -10957,10 +10865,10 @@
         <v>379</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D363" s="4">
-        <v>9500.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E363" s="7"/>
       <c r="F363" s="7"/>
@@ -10981,10 +10889,10 @@
         <v>380</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D364" s="4">
-        <v>3500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E364" s="7"/>
       <c r="F364" s="7"/>
@@ -10993,7 +10901,7 @@
       <c r="I364" s="7"/>
       <c r="J364" s="7"/>
       <c r="K364" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="365">
@@ -11005,10 +10913,10 @@
         <v>381</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D365" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E365" s="7"/>
       <c r="F365" s="7"/>
@@ -11029,17 +10937,13 @@
         <v>382</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D366" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E366" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F366" s="4">
-        <v>22500.0</v>
-      </c>
+        <v>14000.0</v>
+      </c>
+      <c r="E366" s="7"/>
+      <c r="F366" s="7"/>
       <c r="G366" s="7"/>
       <c r="H366" s="7"/>
       <c r="I366" s="7"/>
@@ -11057,17 +10961,13 @@
         <v>383</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>331</v>
+        <v>384</v>
       </c>
       <c r="D367" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E367" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F367" s="4">
-        <v>12500.0</v>
-      </c>
+        <v>1000.0</v>
+      </c>
+      <c r="E367" s="7"/>
+      <c r="F367" s="7"/>
       <c r="G367" s="7"/>
       <c r="H367" s="7"/>
       <c r="I367" s="7"/>
@@ -11082,22 +10982,22 @@
         <v>367</v>
       </c>
       <c r="B368" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C368" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="C368" s="5" t="s">
-        <v>331</v>
-      </c>
       <c r="D368" s="4">
-        <v>3500.0</v>
-      </c>
-      <c r="E368" s="4"/>
-      <c r="F368" s="4"/>
+        <v>4000.0</v>
+      </c>
+      <c r="E368" s="7"/>
+      <c r="F368" s="7"/>
       <c r="G368" s="7"/>
       <c r="H368" s="7"/>
       <c r="I368" s="7"/>
       <c r="J368" s="7"/>
       <c r="K368" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="369">
@@ -11106,17 +11006,17 @@
         <v>368</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>331</v>
+        <v>384</v>
       </c>
       <c r="D369" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E369" s="4"/>
-      <c r="F369" s="4"/>
-      <c r="G369" s="4"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E369" s="7"/>
+      <c r="F369" s="7"/>
+      <c r="G369" s="7"/>
       <c r="H369" s="7"/>
       <c r="I369" s="7"/>
       <c r="J369" s="7"/>
@@ -11130,20 +11030,16 @@
         <v>369</v>
       </c>
       <c r="B370" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>331</v>
+        <v>384</v>
       </c>
       <c r="D370" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E370" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F370" s="4">
-        <v>11500.0</v>
-      </c>
+        <v>10000.0</v>
+      </c>
+      <c r="E370" s="7"/>
+      <c r="F370" s="7"/>
       <c r="G370" s="7"/>
       <c r="H370" s="7"/>
       <c r="I370" s="7"/>
@@ -11158,13 +11054,13 @@
         <v>370</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>331</v>
+        <v>384</v>
       </c>
       <c r="D371" s="4">
-        <v>4000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E371" s="7"/>
       <c r="F371" s="7"/>
@@ -11182,20 +11078,16 @@
         <v>371</v>
       </c>
       <c r="B372" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>331</v>
+        <v>384</v>
       </c>
       <c r="D372" s="4">
-        <v>5000.0</v>
-      </c>
-      <c r="E372" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F372" s="4">
-        <v>22500.0</v>
-      </c>
+        <v>10000.0</v>
+      </c>
+      <c r="E372" s="7"/>
+      <c r="F372" s="7"/>
       <c r="G372" s="7"/>
       <c r="H372" s="7"/>
       <c r="I372" s="7"/>
@@ -11210,13 +11102,13 @@
         <v>372</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>331</v>
+        <v>384</v>
       </c>
       <c r="D373" s="4">
-        <v>1000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E373" s="7"/>
       <c r="F373" s="7"/>
@@ -11234,13 +11126,13 @@
         <v>373</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>331</v>
+        <v>384</v>
       </c>
       <c r="D374" s="4">
-        <v>5000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E374" s="7"/>
       <c r="F374" s="7"/>
@@ -11249,7 +11141,7 @@
       <c r="I374" s="7"/>
       <c r="J374" s="7"/>
       <c r="K374" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="375">
@@ -11258,10 +11150,10 @@
         <v>374</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>331</v>
+        <v>384</v>
       </c>
       <c r="D375" s="4">
         <v>3000.0</v>
@@ -11282,13 +11174,13 @@
         <v>375</v>
       </c>
       <c r="B376" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>331</v>
+        <v>384</v>
       </c>
       <c r="D376" s="4">
-        <v>14000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E376" s="7"/>
       <c r="F376" s="7"/>
@@ -11306,13 +11198,13 @@
         <v>376</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D377" s="4">
-        <v>1000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E377" s="7"/>
       <c r="F377" s="7"/>
@@ -11333,19 +11225,23 @@
         <v>395</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D378" s="4">
-        <v>4000.0</v>
-      </c>
-      <c r="E378" s="7"/>
-      <c r="F378" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E378" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F378" s="4">
+        <v>3000.0</v>
+      </c>
       <c r="G378" s="7"/>
       <c r="H378" s="7"/>
       <c r="I378" s="7"/>
       <c r="J378" s="7"/>
       <c r="K378" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="379">
@@ -11357,10 +11253,10 @@
         <v>396</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D379" s="4">
-        <v>1000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E379" s="7"/>
       <c r="F379" s="7"/>
@@ -11381,10 +11277,10 @@
         <v>397</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D380" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E380" s="7"/>
       <c r="F380" s="7"/>
@@ -11405,10 +11301,10 @@
         <v>398</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D381" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E381" s="7"/>
       <c r="F381" s="7"/>
@@ -11429,10 +11325,10 @@
         <v>399</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D382" s="4">
-        <v>10000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E382" s="7"/>
       <c r="F382" s="7"/>
@@ -11453,10 +11349,10 @@
         <v>400</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D383" s="4">
-        <v>4000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E383" s="7"/>
       <c r="F383" s="7"/>
@@ -11477,10 +11373,10 @@
         <v>401</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D384" s="4">
-        <v>2500.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E384" s="7"/>
       <c r="F384" s="7"/>
@@ -11489,7 +11385,7 @@
       <c r="I384" s="7"/>
       <c r="J384" s="7"/>
       <c r="K384" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="385">
@@ -11501,10 +11397,10 @@
         <v>402</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D385" s="4">
-        <v>3000.0</v>
+        <v>8000.0</v>
       </c>
       <c r="E385" s="7"/>
       <c r="F385" s="7"/>
@@ -11513,7 +11409,7 @@
       <c r="I385" s="7"/>
       <c r="J385" s="7"/>
       <c r="K385" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="386">
@@ -11525,10 +11421,10 @@
         <v>403</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D386" s="4">
-        <v>5000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E386" s="7"/>
       <c r="F386" s="7"/>
@@ -11537,7 +11433,7 @@
       <c r="I386" s="7"/>
       <c r="J386" s="7"/>
       <c r="K386" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="387">
@@ -11549,10 +11445,10 @@
         <v>404</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D387" s="4">
-        <v>3000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E387" s="7"/>
       <c r="F387" s="7"/>
@@ -11573,17 +11469,13 @@
         <v>405</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D388" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E388" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="F388" s="4">
-        <v>3000.0</v>
-      </c>
+        <v>2000.0</v>
+      </c>
+      <c r="E388" s="7"/>
+      <c r="F388" s="7"/>
       <c r="G388" s="7"/>
       <c r="H388" s="7"/>
       <c r="I388" s="7"/>
@@ -11598,13 +11490,13 @@
         <v>388</v>
       </c>
       <c r="B389" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C389" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="C389" s="5" t="s">
-        <v>394</v>
-      </c>
       <c r="D389" s="4">
-        <v>500.0</v>
+        <v>45000.0</v>
       </c>
       <c r="E389" s="7"/>
       <c r="F389" s="7"/>
@@ -11613,7 +11505,7 @@
       <c r="I389" s="7"/>
       <c r="J389" s="7"/>
       <c r="K389" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="390">
@@ -11622,13 +11514,13 @@
         <v>389</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D390" s="4">
-        <v>1000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E390" s="7"/>
       <c r="F390" s="7"/>
@@ -11646,13 +11538,13 @@
         <v>390</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D391" s="4">
-        <v>5000.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E391" s="7"/>
       <c r="F391" s="7"/>
@@ -11670,13 +11562,13 @@
         <v>391</v>
       </c>
       <c r="B392" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D392" s="4">
-        <v>7000.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E392" s="7"/>
       <c r="F392" s="7"/>
@@ -11694,13 +11586,13 @@
         <v>392</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D393" s="4">
-        <v>3000.0</v>
+        <v>40000.0</v>
       </c>
       <c r="E393" s="7"/>
       <c r="F393" s="7"/>
@@ -11709,7 +11601,7 @@
       <c r="I393" s="7"/>
       <c r="J393" s="7"/>
       <c r="K393" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="394">
@@ -11718,13 +11610,13 @@
         <v>393</v>
       </c>
       <c r="B394" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D394" s="4">
-        <v>25000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E394" s="7"/>
       <c r="F394" s="7"/>
@@ -11733,7 +11625,7 @@
       <c r="I394" s="7"/>
       <c r="J394" s="7"/>
       <c r="K394" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="395">
@@ -11742,19 +11634,19 @@
         <v>394</v>
       </c>
       <c r="B395" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D395" s="4">
-        <v>8000.0</v>
+        <v>46000.0</v>
       </c>
       <c r="E395" s="7"/>
       <c r="F395" s="7"/>
       <c r="G395" s="7"/>
       <c r="H395" s="7"/>
-      <c r="I395" s="7"/>
+      <c r="I395" s="4"/>
       <c r="J395" s="7"/>
       <c r="K395" s="4" t="s">
         <v>15</v>
@@ -11766,22 +11658,22 @@
         <v>395</v>
       </c>
       <c r="B396" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D396" s="4">
-        <v>7000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E396" s="7"/>
       <c r="F396" s="7"/>
       <c r="G396" s="7"/>
       <c r="H396" s="7"/>
-      <c r="I396" s="7"/>
+      <c r="I396" s="4"/>
       <c r="J396" s="7"/>
       <c r="K396" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="397">
@@ -11790,22 +11682,22 @@
         <v>396</v>
       </c>
       <c r="B397" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D397" s="4">
-        <v>4000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E397" s="7"/>
       <c r="F397" s="7"/>
       <c r="G397" s="7"/>
       <c r="H397" s="7"/>
-      <c r="I397" s="7"/>
+      <c r="I397" s="4"/>
       <c r="J397" s="7"/>
       <c r="K397" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="398">
@@ -11814,19 +11706,19 @@
         <v>397</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D398" s="4">
-        <v>2000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E398" s="7"/>
       <c r="F398" s="7"/>
       <c r="G398" s="7"/>
       <c r="H398" s="7"/>
-      <c r="I398" s="7"/>
+      <c r="I398" s="4"/>
       <c r="J398" s="7"/>
       <c r="K398" s="4" t="s">
         <v>13</v>
@@ -11841,10 +11733,10 @@
         <v>417</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D399" s="4">
-        <v>45000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E399" s="7"/>
       <c r="F399" s="7"/>
@@ -11853,7 +11745,7 @@
       <c r="I399" s="7"/>
       <c r="J399" s="7"/>
       <c r="K399" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="400">
@@ -11865,10 +11757,10 @@
         <v>418</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D400" s="4">
-        <v>2500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E400" s="7"/>
       <c r="F400" s="7"/>
@@ -11877,7 +11769,7 @@
       <c r="I400" s="7"/>
       <c r="J400" s="7"/>
       <c r="K400" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="401">
@@ -11889,10 +11781,10 @@
         <v>419</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D401" s="4">
-        <v>2500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E401" s="7"/>
       <c r="F401" s="7"/>
@@ -11913,10 +11805,10 @@
         <v>420</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D402" s="4">
-        <v>4000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E402" s="7"/>
       <c r="F402" s="7"/>
@@ -11937,10 +11829,10 @@
         <v>421</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D403" s="4">
-        <v>40000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E403" s="7"/>
       <c r="F403" s="7"/>
@@ -11961,10 +11853,10 @@
         <v>422</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D404" s="4">
-        <v>5000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E404" s="7"/>
       <c r="F404" s="7"/>
@@ -11985,19 +11877,19 @@
         <v>423</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D405" s="4">
-        <v>46000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E405" s="7"/>
       <c r="F405" s="7"/>
       <c r="G405" s="7"/>
       <c r="H405" s="7"/>
-      <c r="I405" s="4"/>
+      <c r="I405" s="7"/>
       <c r="J405" s="7"/>
       <c r="K405" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="406">
@@ -12009,16 +11901,16 @@
         <v>424</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D406" s="4">
-        <v>2000.0</v>
+        <v>25000.0</v>
       </c>
       <c r="E406" s="7"/>
       <c r="F406" s="7"/>
       <c r="G406" s="7"/>
       <c r="H406" s="7"/>
-      <c r="I406" s="4"/>
+      <c r="I406" s="7"/>
       <c r="J406" s="7"/>
       <c r="K406" s="4" t="s">
         <v>13</v>
@@ -12033,19 +11925,19 @@
         <v>425</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D407" s="4">
-        <v>17000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E407" s="7"/>
       <c r="F407" s="7"/>
       <c r="G407" s="7"/>
       <c r="H407" s="7"/>
-      <c r="I407" s="4"/>
+      <c r="I407" s="7"/>
       <c r="J407" s="7"/>
       <c r="K407" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="408">
@@ -12057,16 +11949,16 @@
         <v>426</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D408" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E408" s="7"/>
+        <v>1000.0</v>
+      </c>
+      <c r="E408" s="4"/>
       <c r="F408" s="7"/>
       <c r="G408" s="7"/>
       <c r="H408" s="7"/>
-      <c r="I408" s="4"/>
+      <c r="I408" s="7"/>
       <c r="J408" s="7"/>
       <c r="K408" s="4" t="s">
         <v>13</v>
@@ -12081,10 +11973,10 @@
         <v>427</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D409" s="4">
-        <v>1000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E409" s="7"/>
       <c r="F409" s="7"/>
@@ -12105,10 +11997,10 @@
         <v>428</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D410" s="4">
-        <v>10000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E410" s="7"/>
       <c r="F410" s="7"/>
@@ -12117,7 +12009,7 @@
       <c r="I410" s="7"/>
       <c r="J410" s="7"/>
       <c r="K410" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="411">
@@ -12129,7 +12021,7 @@
         <v>429</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D411" s="4">
         <v>500.0</v>
@@ -12153,10 +12045,10 @@
         <v>430</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D412" s="4">
-        <v>1500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E412" s="7"/>
       <c r="F412" s="7"/>
@@ -12177,10 +12069,10 @@
         <v>431</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D413" s="4">
-        <v>12000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E413" s="7"/>
       <c r="F413" s="7"/>
@@ -12189,7 +12081,7 @@
       <c r="I413" s="7"/>
       <c r="J413" s="7"/>
       <c r="K413" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="414">
@@ -12197,21 +12089,21 @@
         <f t="shared" si="1"/>
         <v>413</v>
       </c>
-      <c r="B414" s="5" t="s">
+      <c r="B414" s="15" t="s">
         <v>432</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D414" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E414" s="7"/>
-      <c r="F414" s="7"/>
-      <c r="G414" s="7"/>
-      <c r="H414" s="7"/>
-      <c r="I414" s="7"/>
-      <c r="J414" s="7"/>
+        <v>406</v>
+      </c>
+      <c r="D414" s="16">
+        <v>4500.0</v>
+      </c>
+      <c r="E414" s="17"/>
+      <c r="F414" s="17"/>
+      <c r="G414" s="17"/>
+      <c r="H414" s="17"/>
+      <c r="I414" s="17"/>
+      <c r="J414" s="17"/>
       <c r="K414" s="4" t="s">
         <v>13</v>
       </c>
@@ -12221,23 +12113,23 @@
         <f t="shared" si="1"/>
         <v>414</v>
       </c>
-      <c r="B415" s="5" t="s">
+      <c r="B415" s="15" t="s">
         <v>433</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D415" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E415" s="7"/>
-      <c r="F415" s="7"/>
-      <c r="G415" s="7"/>
-      <c r="H415" s="7"/>
-      <c r="I415" s="7"/>
-      <c r="J415" s="7"/>
+        <v>406</v>
+      </c>
+      <c r="D415" s="16">
+        <v>50000.0</v>
+      </c>
+      <c r="E415" s="17"/>
+      <c r="F415" s="17"/>
+      <c r="G415" s="17"/>
+      <c r="H415" s="17"/>
+      <c r="I415" s="17"/>
+      <c r="J415" s="17"/>
       <c r="K415" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="416">
@@ -12245,21 +12137,21 @@
         <f t="shared" si="1"/>
         <v>415</v>
       </c>
-      <c r="B416" s="5" t="s">
+      <c r="B416" s="15" t="s">
         <v>434</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D416" s="4">
-        <v>25000.0</v>
-      </c>
-      <c r="E416" s="7"/>
-      <c r="F416" s="7"/>
-      <c r="G416" s="7"/>
-      <c r="H416" s="7"/>
-      <c r="I416" s="7"/>
-      <c r="J416" s="7"/>
+        <v>406</v>
+      </c>
+      <c r="D416" s="16">
+        <v>12000.0</v>
+      </c>
+      <c r="E416" s="17"/>
+      <c r="F416" s="17"/>
+      <c r="G416" s="17"/>
+      <c r="H416" s="17"/>
+      <c r="I416" s="17"/>
+      <c r="J416" s="17"/>
       <c r="K416" s="4" t="s">
         <v>13</v>
       </c>
@@ -12273,17 +12165,17 @@
         <v>435</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D417" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="E417" s="7"/>
-      <c r="F417" s="7"/>
-      <c r="G417" s="7"/>
-      <c r="H417" s="7"/>
-      <c r="I417" s="7"/>
-      <c r="J417" s="7"/>
+        <v>406</v>
+      </c>
+      <c r="D417" s="16">
+        <v>4500.0</v>
+      </c>
+      <c r="E417" s="17"/>
+      <c r="F417" s="17"/>
+      <c r="G417" s="17"/>
+      <c r="H417" s="17"/>
+      <c r="I417" s="17"/>
+      <c r="J417" s="17"/>
       <c r="K417" s="4" t="s">
         <v>13</v>
       </c>
@@ -12293,21 +12185,21 @@
         <f t="shared" si="1"/>
         <v>417</v>
       </c>
-      <c r="B418" s="5" t="s">
+      <c r="B418" s="15" t="s">
         <v>436</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D418" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E418" s="4"/>
-      <c r="F418" s="7"/>
-      <c r="G418" s="7"/>
-      <c r="H418" s="7"/>
-      <c r="I418" s="7"/>
-      <c r="J418" s="7"/>
+        <v>437</v>
+      </c>
+      <c r="D418" s="16">
+        <v>3000.0</v>
+      </c>
+      <c r="E418" s="17"/>
+      <c r="F418" s="17"/>
+      <c r="G418" s="17"/>
+      <c r="H418" s="17"/>
+      <c r="I418" s="17"/>
+      <c r="J418" s="17"/>
       <c r="K418" s="4" t="s">
         <v>13</v>
       </c>
@@ -12317,21 +12209,21 @@
         <f t="shared" si="1"/>
         <v>418</v>
       </c>
-      <c r="B419" s="5" t="s">
+      <c r="B419" s="15" t="s">
         <v>437</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D419" s="4">
-        <v>9000.0</v>
-      </c>
-      <c r="E419" s="7"/>
-      <c r="F419" s="7"/>
-      <c r="G419" s="7"/>
-      <c r="H419" s="7"/>
-      <c r="I419" s="7"/>
-      <c r="J419" s="7"/>
+        <v>437</v>
+      </c>
+      <c r="D419" s="16">
+        <v>5000.0</v>
+      </c>
+      <c r="E419" s="17"/>
+      <c r="F419" s="17"/>
+      <c r="G419" s="17"/>
+      <c r="H419" s="17"/>
+      <c r="I419" s="17"/>
+      <c r="J419" s="17"/>
       <c r="K419" s="4" t="s">
         <v>13</v>
       </c>
@@ -12341,21 +12233,21 @@
         <f t="shared" si="1"/>
         <v>419</v>
       </c>
-      <c r="B420" s="5" t="s">
+      <c r="B420" s="15" t="s">
         <v>438</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D420" s="4">
-        <v>4500.0</v>
-      </c>
-      <c r="E420" s="7"/>
-      <c r="F420" s="7"/>
-      <c r="G420" s="7"/>
-      <c r="H420" s="7"/>
-      <c r="I420" s="7"/>
-      <c r="J420" s="7"/>
+        <v>437</v>
+      </c>
+      <c r="D420" s="16">
+        <v>6000.0</v>
+      </c>
+      <c r="E420" s="17"/>
+      <c r="F420" s="17"/>
+      <c r="G420" s="17"/>
+      <c r="H420" s="17"/>
+      <c r="I420" s="17"/>
+      <c r="J420" s="17"/>
       <c r="K420" s="4" t="s">
         <v>13</v>
       </c>
@@ -12365,23 +12257,23 @@
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
-      <c r="B421" s="5" t="s">
+      <c r="B421" s="15" t="s">
         <v>439</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D421" s="4">
-        <v>500.0</v>
-      </c>
-      <c r="E421" s="7"/>
-      <c r="F421" s="7"/>
-      <c r="G421" s="7"/>
-      <c r="H421" s="7"/>
-      <c r="I421" s="7"/>
-      <c r="J421" s="7"/>
+        <v>384</v>
+      </c>
+      <c r="D421" s="16">
+        <v>12000.0</v>
+      </c>
+      <c r="E421" s="17"/>
+      <c r="F421" s="17"/>
+      <c r="G421" s="17"/>
+      <c r="H421" s="17"/>
+      <c r="I421" s="17"/>
+      <c r="J421" s="17"/>
       <c r="K421" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="422">
@@ -12389,21 +12281,21 @@
         <f t="shared" si="1"/>
         <v>421</v>
       </c>
-      <c r="B422" s="5" t="s">
+      <c r="B422" s="15" t="s">
         <v>440</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D422" s="4">
-        <v>3000.0</v>
-      </c>
-      <c r="E422" s="7"/>
-      <c r="F422" s="7"/>
-      <c r="G422" s="7"/>
-      <c r="H422" s="7"/>
-      <c r="I422" s="7"/>
-      <c r="J422" s="7"/>
+        <v>384</v>
+      </c>
+      <c r="D422" s="16">
+        <v>200.0</v>
+      </c>
+      <c r="E422" s="16"/>
+      <c r="F422" s="16"/>
+      <c r="G422" s="17"/>
+      <c r="H422" s="17"/>
+      <c r="I422" s="17"/>
+      <c r="J422" s="17"/>
       <c r="K422" s="4" t="s">
         <v>13</v>
       </c>
@@ -12413,21 +12305,25 @@
         <f t="shared" si="1"/>
         <v>422</v>
       </c>
-      <c r="B423" s="5" t="s">
+      <c r="B423" s="15" t="s">
         <v>441</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D423" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E423" s="7"/>
-      <c r="F423" s="7"/>
-      <c r="G423" s="7"/>
-      <c r="H423" s="7"/>
-      <c r="I423" s="7"/>
-      <c r="J423" s="7"/>
+        <v>384</v>
+      </c>
+      <c r="D423" s="16">
+        <v>5000.0</v>
+      </c>
+      <c r="E423" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="F423" s="16">
+        <v>4500.0</v>
+      </c>
+      <c r="G423" s="17"/>
+      <c r="H423" s="17"/>
+      <c r="I423" s="17"/>
+      <c r="J423" s="17"/>
       <c r="K423" s="4" t="s">
         <v>13</v>
       </c>
@@ -12441,10 +12337,10 @@
         <v>442</v>
       </c>
       <c r="C424" s="5" t="s">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="D424" s="16">
-        <v>4500.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E424" s="17"/>
       <c r="F424" s="17"/>
@@ -12453,7 +12349,7 @@
       <c r="I424" s="17"/>
       <c r="J424" s="17"/>
       <c r="K424" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="425">
@@ -12465,10 +12361,10 @@
         <v>443</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="D425" s="16">
-        <v>50000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E425" s="17"/>
       <c r="F425" s="17"/>
@@ -12489,10 +12385,10 @@
         <v>444</v>
       </c>
       <c r="C426" s="5" t="s">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="D426" s="16">
-        <v>12000.0</v>
+        <v>17000.0</v>
       </c>
       <c r="E426" s="17"/>
       <c r="F426" s="17"/>
@@ -12501,7 +12397,7 @@
       <c r="I426" s="17"/>
       <c r="J426" s="17"/>
       <c r="K426" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="427">
@@ -12509,14 +12405,14 @@
         <f t="shared" si="1"/>
         <v>426</v>
       </c>
-      <c r="B427" s="5" t="s">
+      <c r="B427" s="15" t="s">
         <v>445</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="D427" s="16">
-        <v>4500.0</v>
+        <v>17500.0</v>
       </c>
       <c r="E427" s="17"/>
       <c r="F427" s="17"/>
@@ -12525,7 +12421,7 @@
       <c r="I427" s="17"/>
       <c r="J427" s="17"/>
       <c r="K427" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="428">
@@ -12537,10 +12433,10 @@
         <v>446</v>
       </c>
       <c r="C428" s="5" t="s">
-        <v>447</v>
+        <v>384</v>
       </c>
       <c r="D428" s="16">
-        <v>3000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E428" s="17"/>
       <c r="F428" s="17"/>
@@ -12549,7 +12445,7 @@
       <c r="I428" s="17"/>
       <c r="J428" s="17"/>
       <c r="K428" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="429">
@@ -12561,10 +12457,10 @@
         <v>447</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>447</v>
+        <v>384</v>
       </c>
       <c r="D429" s="16">
-        <v>5000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E429" s="17"/>
       <c r="F429" s="17"/>
@@ -12573,7 +12469,7 @@
       <c r="I429" s="17"/>
       <c r="J429" s="17"/>
       <c r="K429" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="430">
@@ -12585,10 +12481,10 @@
         <v>448</v>
       </c>
       <c r="C430" s="5" t="s">
-        <v>447</v>
+        <v>384</v>
       </c>
       <c r="D430" s="16">
-        <v>6000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E430" s="17"/>
       <c r="F430" s="17"/>
@@ -12597,7 +12493,7 @@
       <c r="I430" s="17"/>
       <c r="J430" s="17"/>
       <c r="K430" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="431">
@@ -12609,10 +12505,10 @@
         <v>449</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D431" s="16">
-        <v>12000.0</v>
+        <v>19500.0</v>
       </c>
       <c r="E431" s="17"/>
       <c r="F431" s="17"/>
@@ -12633,19 +12529,19 @@
         <v>450</v>
       </c>
       <c r="C432" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D432" s="16">
-        <v>200.0</v>
-      </c>
-      <c r="E432" s="16"/>
-      <c r="F432" s="16"/>
+        <v>8500.0</v>
+      </c>
+      <c r="E432" s="17"/>
+      <c r="F432" s="17"/>
       <c r="G432" s="17"/>
       <c r="H432" s="17"/>
       <c r="I432" s="17"/>
       <c r="J432" s="17"/>
       <c r="K432" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="433">
@@ -12657,23 +12553,19 @@
         <v>451</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D433" s="16">
-        <v>5000.0</v>
-      </c>
-      <c r="E433" s="16">
-        <v>2.0</v>
-      </c>
-      <c r="F433" s="16">
-        <v>4500.0</v>
-      </c>
+        <v>8500.0</v>
+      </c>
+      <c r="E433" s="17"/>
+      <c r="F433" s="17"/>
       <c r="G433" s="17"/>
       <c r="H433" s="17"/>
       <c r="I433" s="17"/>
       <c r="J433" s="17"/>
       <c r="K433" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="434">
@@ -12685,10 +12577,10 @@
         <v>452</v>
       </c>
       <c r="C434" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D434" s="16">
-        <v>18000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E434" s="17"/>
       <c r="F434" s="17"/>
@@ -12709,10 +12601,10 @@
         <v>453</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D435" s="16">
-        <v>17000.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E435" s="17"/>
       <c r="F435" s="17"/>
@@ -12733,10 +12625,10 @@
         <v>454</v>
       </c>
       <c r="C436" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D436" s="16">
-        <v>17000.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E436" s="17"/>
       <c r="F436" s="17"/>
@@ -12757,10 +12649,10 @@
         <v>455</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D437" s="16">
-        <v>17500.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E437" s="17"/>
       <c r="F437" s="17"/>
@@ -12769,7 +12661,7 @@
       <c r="I437" s="17"/>
       <c r="J437" s="17"/>
       <c r="K437" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="438">
@@ -12781,10 +12673,10 @@
         <v>456</v>
       </c>
       <c r="C438" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D438" s="16">
-        <v>9000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="E438" s="17"/>
       <c r="F438" s="17"/>
@@ -12805,10 +12697,10 @@
         <v>457</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D439" s="16">
-        <v>9000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="E439" s="17"/>
       <c r="F439" s="17"/>
@@ -12817,7 +12709,7 @@
       <c r="I439" s="17"/>
       <c r="J439" s="17"/>
       <c r="K439" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="440">
@@ -12829,10 +12721,10 @@
         <v>458</v>
       </c>
       <c r="C440" s="5" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D440" s="16">
-        <v>9000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E440" s="17"/>
       <c r="F440" s="17"/>
@@ -12841,7 +12733,7 @@
       <c r="I440" s="17"/>
       <c r="J440" s="17"/>
       <c r="K440" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="441">
@@ -12853,10 +12745,10 @@
         <v>459</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D441" s="16">
-        <v>19500.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E441" s="17"/>
       <c r="F441" s="17"/>
@@ -12865,7 +12757,7 @@
       <c r="I441" s="17"/>
       <c r="J441" s="17"/>
       <c r="K441" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="442">
@@ -12873,14 +12765,14 @@
         <f t="shared" si="1"/>
         <v>441</v>
       </c>
-      <c r="B442" s="15" t="s">
+      <c r="B442" s="5" t="s">
         <v>460</v>
       </c>
       <c r="C442" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D442" s="16">
-        <v>8500.0</v>
+        <v>11000.0</v>
       </c>
       <c r="E442" s="17"/>
       <c r="F442" s="17"/>
@@ -12889,7 +12781,7 @@
       <c r="I442" s="17"/>
       <c r="J442" s="17"/>
       <c r="K442" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="443">
@@ -12901,10 +12793,10 @@
         <v>461</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D443" s="16">
-        <v>8500.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E443" s="17"/>
       <c r="F443" s="17"/>
@@ -12913,7 +12805,7 @@
       <c r="I443" s="17"/>
       <c r="J443" s="17"/>
       <c r="K443" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="444">
@@ -12925,10 +12817,10 @@
         <v>462</v>
       </c>
       <c r="C444" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D444" s="16">
-        <v>4500.0</v>
+        <v>9000.0</v>
       </c>
       <c r="E444" s="17"/>
       <c r="F444" s="17"/>
@@ -12949,10 +12841,10 @@
         <v>463</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D445" s="16">
-        <v>9000.0</v>
+        <v>18000.0</v>
       </c>
       <c r="E445" s="17"/>
       <c r="F445" s="17"/>
@@ -12973,10 +12865,10 @@
         <v>464</v>
       </c>
       <c r="C446" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D446" s="16">
-        <v>14000.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E446" s="17"/>
       <c r="F446" s="17"/>
@@ -12985,7 +12877,7 @@
       <c r="I446" s="17"/>
       <c r="J446" s="17"/>
       <c r="K446" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="447">
@@ -12997,10 +12889,10 @@
         <v>465</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D447" s="16">
-        <v>3000.0</v>
+        <v>260000.0</v>
       </c>
       <c r="E447" s="17"/>
       <c r="F447" s="17"/>
@@ -13009,248 +12901,138 @@
       <c r="I447" s="17"/>
       <c r="J447" s="17"/>
       <c r="K447" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="4">
-        <f t="shared" si="1"/>
-        <v>447</v>
-      </c>
-      <c r="B448" s="15" t="s">
-        <v>466</v>
-      </c>
-      <c r="C448" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="D448" s="16">
-        <v>12000.0</v>
-      </c>
+      <c r="A448" s="18"/>
+      <c r="B448" s="18"/>
+      <c r="C448" s="18"/>
+      <c r="D448" s="17"/>
       <c r="E448" s="17"/>
       <c r="F448" s="17"/>
       <c r="G448" s="17"/>
       <c r="H448" s="17"/>
       <c r="I448" s="17"/>
       <c r="J448" s="17"/>
-      <c r="K448" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="K448" s="17"/>
     </row>
     <row r="449">
-      <c r="A449" s="4">
-        <f t="shared" si="1"/>
-        <v>448</v>
-      </c>
-      <c r="B449" s="15" t="s">
-        <v>467</v>
-      </c>
-      <c r="C449" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="D449" s="16">
-        <v>20000.0</v>
-      </c>
+      <c r="A449" s="18"/>
+      <c r="B449" s="18"/>
+      <c r="C449" s="18"/>
+      <c r="D449" s="17"/>
       <c r="E449" s="17"/>
       <c r="F449" s="17"/>
       <c r="G449" s="17"/>
       <c r="H449" s="17"/>
       <c r="I449" s="17"/>
       <c r="J449" s="17"/>
-      <c r="K449" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="K449" s="17"/>
     </row>
     <row r="450">
-      <c r="A450" s="4">
-        <f t="shared" si="1"/>
-        <v>449</v>
-      </c>
-      <c r="B450" s="15" t="s">
-        <v>468</v>
-      </c>
-      <c r="C450" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D450" s="16">
-        <v>4500.0</v>
-      </c>
+      <c r="A450" s="18"/>
+      <c r="B450" s="18"/>
+      <c r="C450" s="18"/>
+      <c r="D450" s="17"/>
       <c r="E450" s="17"/>
       <c r="F450" s="17"/>
       <c r="G450" s="17"/>
       <c r="H450" s="17"/>
       <c r="I450" s="17"/>
       <c r="J450" s="17"/>
-      <c r="K450" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="K450" s="17"/>
     </row>
     <row r="451">
-      <c r="A451" s="4">
-        <f t="shared" si="1"/>
-        <v>450</v>
-      </c>
-      <c r="B451" s="15" t="s">
-        <v>469</v>
-      </c>
-      <c r="C451" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="D451" s="16">
-        <v>2500.0</v>
-      </c>
+      <c r="A451" s="18"/>
+      <c r="B451" s="18"/>
+      <c r="C451" s="18"/>
+      <c r="D451" s="17"/>
       <c r="E451" s="17"/>
       <c r="F451" s="17"/>
       <c r="G451" s="17"/>
       <c r="H451" s="17"/>
       <c r="I451" s="17"/>
       <c r="J451" s="17"/>
-      <c r="K451" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="K451" s="17"/>
     </row>
     <row r="452">
-      <c r="A452" s="4">
-        <f t="shared" si="1"/>
-        <v>451</v>
-      </c>
-      <c r="B452" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="C452" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="D452" s="16">
-        <v>11000.0</v>
-      </c>
+      <c r="A452" s="18"/>
+      <c r="B452" s="18"/>
+      <c r="C452" s="18"/>
+      <c r="D452" s="17"/>
       <c r="E452" s="17"/>
       <c r="F452" s="17"/>
       <c r="G452" s="17"/>
       <c r="H452" s="17"/>
       <c r="I452" s="17"/>
       <c r="J452" s="17"/>
-      <c r="K452" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="K452" s="17"/>
     </row>
     <row r="453">
-      <c r="A453" s="4">
-        <f t="shared" si="1"/>
-        <v>452</v>
-      </c>
-      <c r="B453" s="15" t="s">
-        <v>471</v>
-      </c>
-      <c r="C453" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="D453" s="16">
-        <v>18000.0</v>
-      </c>
+      <c r="A453" s="18"/>
+      <c r="B453" s="18"/>
+      <c r="C453" s="18"/>
+      <c r="D453" s="17"/>
       <c r="E453" s="17"/>
       <c r="F453" s="17"/>
       <c r="G453" s="17"/>
       <c r="H453" s="17"/>
       <c r="I453" s="17"/>
       <c r="J453" s="17"/>
-      <c r="K453" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="K453" s="17"/>
     </row>
     <row r="454">
-      <c r="A454" s="4">
-        <f t="shared" si="1"/>
-        <v>453</v>
-      </c>
-      <c r="B454" s="15" t="s">
-        <v>472</v>
-      </c>
-      <c r="C454" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="D454" s="16">
-        <v>9000.0</v>
-      </c>
+      <c r="A454" s="18"/>
+      <c r="B454" s="18"/>
+      <c r="C454" s="18"/>
+      <c r="D454" s="17"/>
       <c r="E454" s="17"/>
       <c r="F454" s="17"/>
       <c r="G454" s="17"/>
       <c r="H454" s="17"/>
       <c r="I454" s="17"/>
       <c r="J454" s="17"/>
-      <c r="K454" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="K454" s="17"/>
     </row>
     <row r="455">
-      <c r="A455" s="4">
-        <f t="shared" si="1"/>
-        <v>454</v>
-      </c>
-      <c r="B455" s="15" t="s">
-        <v>473</v>
-      </c>
-      <c r="C455" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="D455" s="16">
-        <v>18000.0</v>
-      </c>
+      <c r="A455" s="18"/>
+      <c r="B455" s="18"/>
+      <c r="C455" s="18"/>
+      <c r="D455" s="17"/>
       <c r="E455" s="17"/>
       <c r="F455" s="17"/>
       <c r="G455" s="17"/>
       <c r="H455" s="17"/>
       <c r="I455" s="17"/>
       <c r="J455" s="17"/>
-      <c r="K455" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="K455" s="17"/>
     </row>
     <row r="456">
-      <c r="A456" s="4">
-        <f t="shared" si="1"/>
-        <v>455</v>
-      </c>
-      <c r="B456" s="15" t="s">
-        <v>474</v>
-      </c>
-      <c r="C456" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="D456" s="16">
-        <v>7000.0</v>
-      </c>
+      <c r="A456" s="18"/>
+      <c r="B456" s="18"/>
+      <c r="C456" s="18"/>
+      <c r="D456" s="17"/>
       <c r="E456" s="17"/>
       <c r="F456" s="17"/>
       <c r="G456" s="17"/>
       <c r="H456" s="17"/>
       <c r="I456" s="17"/>
       <c r="J456" s="17"/>
-      <c r="K456" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="K456" s="17"/>
     </row>
     <row r="457">
-      <c r="A457" s="4">
-        <f t="shared" si="1"/>
-        <v>456</v>
-      </c>
-      <c r="B457" s="15" t="s">
-        <v>475</v>
-      </c>
-      <c r="C457" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="D457" s="16">
-        <v>260000.0</v>
-      </c>
+      <c r="A457" s="18"/>
+      <c r="B457" s="18"/>
+      <c r="C457" s="18"/>
+      <c r="D457" s="17"/>
       <c r="E457" s="17"/>
       <c r="F457" s="17"/>
       <c r="G457" s="17"/>
       <c r="H457" s="17"/>
       <c r="I457" s="17"/>
       <c r="J457" s="17"/>
-      <c r="K457" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="K457" s="17"/>
     </row>
     <row r="458">
       <c r="A458" s="18"/>
@@ -14114,131 +13896,131 @@
       <c r="A524" s="18"/>
       <c r="B524" s="18"/>
       <c r="C524" s="18"/>
-      <c r="D524" s="17"/>
-      <c r="E524" s="17"/>
-      <c r="F524" s="17"/>
-      <c r="G524" s="17"/>
-      <c r="H524" s="17"/>
-      <c r="I524" s="17"/>
-      <c r="J524" s="17"/>
-      <c r="K524" s="17"/>
+      <c r="D524" s="18"/>
+      <c r="E524" s="18"/>
+      <c r="F524" s="18"/>
+      <c r="G524" s="18"/>
+      <c r="H524" s="18"/>
+      <c r="I524" s="18"/>
+      <c r="J524" s="18"/>
+      <c r="K524" s="18"/>
     </row>
     <row r="525">
       <c r="A525" s="18"/>
       <c r="B525" s="18"/>
       <c r="C525" s="18"/>
-      <c r="D525" s="17"/>
-      <c r="E525" s="17"/>
-      <c r="F525" s="17"/>
-      <c r="G525" s="17"/>
-      <c r="H525" s="17"/>
-      <c r="I525" s="17"/>
-      <c r="J525" s="17"/>
-      <c r="K525" s="17"/>
+      <c r="D525" s="18"/>
+      <c r="E525" s="18"/>
+      <c r="F525" s="18"/>
+      <c r="G525" s="18"/>
+      <c r="H525" s="18"/>
+      <c r="I525" s="18"/>
+      <c r="J525" s="18"/>
+      <c r="K525" s="18"/>
     </row>
     <row r="526">
       <c r="A526" s="18"/>
       <c r="B526" s="18"/>
       <c r="C526" s="18"/>
-      <c r="D526" s="17"/>
-      <c r="E526" s="17"/>
-      <c r="F526" s="17"/>
-      <c r="G526" s="17"/>
-      <c r="H526" s="17"/>
-      <c r="I526" s="17"/>
-      <c r="J526" s="17"/>
-      <c r="K526" s="17"/>
+      <c r="D526" s="18"/>
+      <c r="E526" s="18"/>
+      <c r="F526" s="18"/>
+      <c r="G526" s="18"/>
+      <c r="H526" s="18"/>
+      <c r="I526" s="18"/>
+      <c r="J526" s="18"/>
+      <c r="K526" s="18"/>
     </row>
     <row r="527">
       <c r="A527" s="18"/>
       <c r="B527" s="18"/>
       <c r="C527" s="18"/>
-      <c r="D527" s="17"/>
-      <c r="E527" s="17"/>
-      <c r="F527" s="17"/>
-      <c r="G527" s="17"/>
-      <c r="H527" s="17"/>
-      <c r="I527" s="17"/>
-      <c r="J527" s="17"/>
-      <c r="K527" s="17"/>
+      <c r="D527" s="18"/>
+      <c r="E527" s="18"/>
+      <c r="F527" s="18"/>
+      <c r="G527" s="18"/>
+      <c r="H527" s="18"/>
+      <c r="I527" s="18"/>
+      <c r="J527" s="18"/>
+      <c r="K527" s="18"/>
     </row>
     <row r="528">
       <c r="A528" s="18"/>
       <c r="B528" s="18"/>
       <c r="C528" s="18"/>
-      <c r="D528" s="17"/>
-      <c r="E528" s="17"/>
-      <c r="F528" s="17"/>
-      <c r="G528" s="17"/>
-      <c r="H528" s="17"/>
-      <c r="I528" s="17"/>
-      <c r="J528" s="17"/>
-      <c r="K528" s="17"/>
+      <c r="D528" s="18"/>
+      <c r="E528" s="18"/>
+      <c r="F528" s="18"/>
+      <c r="G528" s="18"/>
+      <c r="H528" s="18"/>
+      <c r="I528" s="18"/>
+      <c r="J528" s="18"/>
+      <c r="K528" s="18"/>
     </row>
     <row r="529">
       <c r="A529" s="18"/>
       <c r="B529" s="18"/>
       <c r="C529" s="18"/>
-      <c r="D529" s="17"/>
-      <c r="E529" s="17"/>
-      <c r="F529" s="17"/>
-      <c r="G529" s="17"/>
-      <c r="H529" s="17"/>
-      <c r="I529" s="17"/>
-      <c r="J529" s="17"/>
-      <c r="K529" s="17"/>
+      <c r="D529" s="18"/>
+      <c r="E529" s="18"/>
+      <c r="F529" s="18"/>
+      <c r="G529" s="18"/>
+      <c r="H529" s="18"/>
+      <c r="I529" s="18"/>
+      <c r="J529" s="18"/>
+      <c r="K529" s="18"/>
     </row>
     <row r="530">
       <c r="A530" s="18"/>
       <c r="B530" s="18"/>
       <c r="C530" s="18"/>
-      <c r="D530" s="17"/>
-      <c r="E530" s="17"/>
-      <c r="F530" s="17"/>
-      <c r="G530" s="17"/>
-      <c r="H530" s="17"/>
-      <c r="I530" s="17"/>
-      <c r="J530" s="17"/>
-      <c r="K530" s="17"/>
+      <c r="D530" s="18"/>
+      <c r="E530" s="18"/>
+      <c r="F530" s="18"/>
+      <c r="G530" s="18"/>
+      <c r="H530" s="18"/>
+      <c r="I530" s="18"/>
+      <c r="J530" s="18"/>
+      <c r="K530" s="18"/>
     </row>
     <row r="531">
       <c r="A531" s="18"/>
       <c r="B531" s="18"/>
       <c r="C531" s="18"/>
-      <c r="D531" s="17"/>
-      <c r="E531" s="17"/>
-      <c r="F531" s="17"/>
-      <c r="G531" s="17"/>
-      <c r="H531" s="17"/>
-      <c r="I531" s="17"/>
-      <c r="J531" s="17"/>
-      <c r="K531" s="17"/>
+      <c r="D531" s="18"/>
+      <c r="E531" s="18"/>
+      <c r="F531" s="18"/>
+      <c r="G531" s="18"/>
+      <c r="H531" s="18"/>
+      <c r="I531" s="18"/>
+      <c r="J531" s="18"/>
+      <c r="K531" s="18"/>
     </row>
     <row r="532">
       <c r="A532" s="18"/>
       <c r="B532" s="18"/>
       <c r="C532" s="18"/>
-      <c r="D532" s="17"/>
-      <c r="E532" s="17"/>
-      <c r="F532" s="17"/>
-      <c r="G532" s="17"/>
-      <c r="H532" s="17"/>
-      <c r="I532" s="17"/>
-      <c r="J532" s="17"/>
-      <c r="K532" s="17"/>
+      <c r="D532" s="18"/>
+      <c r="E532" s="18"/>
+      <c r="F532" s="18"/>
+      <c r="G532" s="18"/>
+      <c r="H532" s="18"/>
+      <c r="I532" s="18"/>
+      <c r="J532" s="18"/>
+      <c r="K532" s="18"/>
     </row>
     <row r="533">
       <c r="A533" s="18"/>
       <c r="B533" s="18"/>
       <c r="C533" s="18"/>
-      <c r="D533" s="17"/>
-      <c r="E533" s="17"/>
-      <c r="F533" s="17"/>
-      <c r="G533" s="17"/>
-      <c r="H533" s="17"/>
-      <c r="I533" s="17"/>
-      <c r="J533" s="17"/>
-      <c r="K533" s="17"/>
+      <c r="D533" s="18"/>
+      <c r="E533" s="18"/>
+      <c r="F533" s="18"/>
+      <c r="G533" s="18"/>
+      <c r="H533" s="18"/>
+      <c r="I533" s="18"/>
+      <c r="J533" s="18"/>
+      <c r="K533" s="18"/>
     </row>
     <row r="534">
       <c r="A534" s="18"/>
@@ -23236,153 +23018,23 @@
       <c r="J1225" s="18"/>
       <c r="K1225" s="18"/>
     </row>
-    <row r="1226">
-      <c r="A1226" s="18"/>
-      <c r="B1226" s="18"/>
-      <c r="C1226" s="18"/>
-      <c r="D1226" s="18"/>
-      <c r="E1226" s="18"/>
-      <c r="F1226" s="18"/>
-      <c r="G1226" s="18"/>
-      <c r="H1226" s="18"/>
-      <c r="I1226" s="18"/>
-      <c r="J1226" s="18"/>
-      <c r="K1226" s="18"/>
-    </row>
-    <row r="1227">
-      <c r="A1227" s="18"/>
-      <c r="B1227" s="18"/>
-      <c r="C1227" s="18"/>
-      <c r="D1227" s="18"/>
-      <c r="E1227" s="18"/>
-      <c r="F1227" s="18"/>
-      <c r="G1227" s="18"/>
-      <c r="H1227" s="18"/>
-      <c r="I1227" s="18"/>
-      <c r="J1227" s="18"/>
-      <c r="K1227" s="18"/>
-    </row>
-    <row r="1228">
-      <c r="A1228" s="18"/>
-      <c r="B1228" s="18"/>
-      <c r="C1228" s="18"/>
-      <c r="D1228" s="18"/>
-      <c r="E1228" s="18"/>
-      <c r="F1228" s="18"/>
-      <c r="G1228" s="18"/>
-      <c r="H1228" s="18"/>
-      <c r="I1228" s="18"/>
-      <c r="J1228" s="18"/>
-      <c r="K1228" s="18"/>
-    </row>
-    <row r="1229">
-      <c r="A1229" s="18"/>
-      <c r="B1229" s="18"/>
-      <c r="C1229" s="18"/>
-      <c r="D1229" s="18"/>
-      <c r="E1229" s="18"/>
-      <c r="F1229" s="18"/>
-      <c r="G1229" s="18"/>
-      <c r="H1229" s="18"/>
-      <c r="I1229" s="18"/>
-      <c r="J1229" s="18"/>
-      <c r="K1229" s="18"/>
-    </row>
-    <row r="1230">
-      <c r="A1230" s="18"/>
-      <c r="B1230" s="18"/>
-      <c r="C1230" s="18"/>
-      <c r="D1230" s="18"/>
-      <c r="E1230" s="18"/>
-      <c r="F1230" s="18"/>
-      <c r="G1230" s="18"/>
-      <c r="H1230" s="18"/>
-      <c r="I1230" s="18"/>
-      <c r="J1230" s="18"/>
-      <c r="K1230" s="18"/>
-    </row>
-    <row r="1231">
-      <c r="A1231" s="18"/>
-      <c r="B1231" s="18"/>
-      <c r="C1231" s="18"/>
-      <c r="D1231" s="18"/>
-      <c r="E1231" s="18"/>
-      <c r="F1231" s="18"/>
-      <c r="G1231" s="18"/>
-      <c r="H1231" s="18"/>
-      <c r="I1231" s="18"/>
-      <c r="J1231" s="18"/>
-      <c r="K1231" s="18"/>
-    </row>
-    <row r="1232">
-      <c r="A1232" s="18"/>
-      <c r="B1232" s="18"/>
-      <c r="C1232" s="18"/>
-      <c r="D1232" s="18"/>
-      <c r="E1232" s="18"/>
-      <c r="F1232" s="18"/>
-      <c r="G1232" s="18"/>
-      <c r="H1232" s="18"/>
-      <c r="I1232" s="18"/>
-      <c r="J1232" s="18"/>
-      <c r="K1232" s="18"/>
-    </row>
-    <row r="1233">
-      <c r="A1233" s="18"/>
-      <c r="B1233" s="18"/>
-      <c r="C1233" s="18"/>
-      <c r="D1233" s="18"/>
-      <c r="E1233" s="18"/>
-      <c r="F1233" s="18"/>
-      <c r="G1233" s="18"/>
-      <c r="H1233" s="18"/>
-      <c r="I1233" s="18"/>
-      <c r="J1233" s="18"/>
-      <c r="K1233" s="18"/>
-    </row>
-    <row r="1234">
-      <c r="A1234" s="18"/>
-      <c r="B1234" s="18"/>
-      <c r="C1234" s="18"/>
-      <c r="D1234" s="18"/>
-      <c r="E1234" s="18"/>
-      <c r="F1234" s="18"/>
-      <c r="G1234" s="18"/>
-      <c r="H1234" s="18"/>
-      <c r="I1234" s="18"/>
-      <c r="J1234" s="18"/>
-      <c r="K1234" s="18"/>
-    </row>
-    <row r="1235">
-      <c r="A1235" s="18"/>
-      <c r="B1235" s="18"/>
-      <c r="C1235" s="18"/>
-      <c r="D1235" s="18"/>
-      <c r="E1235" s="18"/>
-      <c r="F1235" s="18"/>
-      <c r="G1235" s="18"/>
-      <c r="H1235" s="18"/>
-      <c r="I1235" s="18"/>
-      <c r="J1235" s="18"/>
-      <c r="K1235" s="18"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$457"/>
-  <conditionalFormatting sqref="B452">
+  <autoFilter ref="$B$1:$C$447"/>
+  <conditionalFormatting sqref="B442">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A1235 B2:B451 C2:K1235 B453:B1235">
+  <conditionalFormatting sqref="A2:A1225 B2:B441 C2:K1225 B443:B1225">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C457">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C447">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K457">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K447">
       <formula1>"Ecer,KRT"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23447,7 +23099,7 @@
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4">
@@ -23469,7 +23121,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -23491,7 +23143,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -23513,7 +23165,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -23535,7 +23187,7 @@
         <v>GROSIR5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="4">
@@ -23557,7 +23209,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -23579,7 +23231,7 @@
         <v>GROSIR7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="4">
@@ -23601,7 +23253,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -23623,7 +23275,7 @@
         <v>GROSIR9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="4">
@@ -23645,7 +23297,7 @@
         <v>GROSIR10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="4">
@@ -23667,7 +23319,7 @@
         <v>GROSIR11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="4">
@@ -23689,7 +23341,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -23711,7 +23363,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -23733,7 +23385,7 @@
         <v>GROSIR14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>484</v>
+        <v>247</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="4">
@@ -23755,7 +23407,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>244</v>
+        <v>474</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -23777,7 +23429,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -23799,7 +23451,7 @@
         <v>GROSIR17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="4">
@@ -23821,7 +23473,7 @@
         <v>GROSIR18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4">
@@ -23843,7 +23495,7 @@
         <v>GROSIR19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4">
@@ -23865,7 +23517,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -23887,7 +23539,7 @@
         <v>GROSIR21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4">
@@ -23909,7 +23561,7 @@
         <v>GROSIR22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="4">
@@ -23931,7 +23583,7 @@
         <v>GROSIR23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="4">
@@ -23953,7 +23605,7 @@
         <v>GROSIR24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="4">
@@ -23975,7 +23627,7 @@
         <v>GROSIR25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>238</v>
+        <v>480</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="4">
@@ -23997,7 +23649,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>240</v>
+        <v>481</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -24019,7 +23671,7 @@
         <v>GROSIR27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>227</v>
+        <v>482</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="4">
@@ -24041,7 +23693,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -24063,7 +23715,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>225</v>
+        <v>484</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -24085,7 +23737,7 @@
         <v>GROSIR30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="4">
@@ -24107,7 +23759,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -24129,7 +23781,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -24173,7 +23825,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -24195,7 +23847,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -24217,7 +23869,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -24239,7 +23891,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -24261,7 +23913,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -24283,7 +23935,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -24305,7 +23957,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -24327,7 +23979,7 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
@@ -24349,7 +24001,7 @@
         <v>GROSIR42</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="4">
@@ -24371,7 +24023,7 @@
         <v>GROSIR43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="4">
@@ -24393,7 +24045,7 @@
         <v>GROSIR44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="4">
@@ -24415,7 +24067,7 @@
         <v>GROSIR45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="4">
@@ -24459,7 +24111,7 @@
         <v>GROSIR47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="4">
@@ -24503,7 +24155,7 @@
         <v>GROSIR49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="4">
@@ -24525,7 +24177,7 @@
         <v>GROSIR50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="4">
@@ -24547,7 +24199,7 @@
         <v>GROSIR51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="4">
@@ -24569,7 +24221,7 @@
         <v>GROSIR52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="4">
@@ -24591,7 +24243,7 @@
         <v>GROSIR53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="4">
@@ -24613,7 +24265,7 @@
         <v>GROSIR54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="4">
@@ -24635,7 +24287,7 @@
         <v>GROSIR55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="4">
@@ -24657,7 +24309,7 @@
         <v>GROSIR56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="4">
@@ -24679,7 +24331,7 @@
         <v>GROSIR57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="4">
@@ -24701,7 +24353,7 @@
         <v>GROSIR58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="4">
@@ -24723,7 +24375,7 @@
         <v>GROSIR59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="4">
@@ -24745,7 +24397,7 @@
         <v>GROSIR60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="4">
@@ -24767,7 +24419,7 @@
         <v>GROSIR61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="4">
@@ -24789,7 +24441,7 @@
         <v>GROSIR62</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="4">
@@ -24833,7 +24485,7 @@
         <v>GROSIR64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="4">
@@ -24943,7 +24595,7 @@
         <v>GROSIR69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="C70" s="5"/>
       <c r="D70" s="4">
@@ -24965,7 +24617,7 @@
         <v>GROSIR70</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="C71" s="5"/>
       <c r="D71" s="4">
@@ -24987,7 +24639,7 @@
         <v>GROSIR71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="4">
@@ -25053,7 +24705,7 @@
         <v>GROSIR74</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="4">
@@ -25075,7 +24727,7 @@
         <v>GROSIR75</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="C76" s="5"/>
       <c r="D76" s="4">
@@ -25097,7 +24749,7 @@
         <v>GROSIR76</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="C77" s="5"/>
       <c r="D77" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -1070,13 +1070,13 @@
     <t>Kispray Renceng</t>
   </si>
   <si>
-    <t>Molto Renceg</t>
+    <t>Molto Renceng</t>
   </si>
   <si>
     <t>Soklin Softener 500</t>
   </si>
   <si>
-    <t>Soklin Softener 500 Renceg</t>
+    <t>Soklin Softener 500 Renceng</t>
   </si>
   <si>
     <t>Downy 500</t>
@@ -10179,7 +10179,7 @@
       <c r="I335" s="7"/>
       <c r="J335" s="7"/>
       <c r="K335" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="336">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -59,7 +59,7 @@
     <t>Ecer</t>
   </si>
   <si>
-    <t>Nutrisari Jeruk Peras Renceng</t>
+    <t>Nutrisari Jeruk Peras RC</t>
   </si>
   <si>
     <t>KRT</t>
@@ -68,13 +68,13 @@
     <t>Nutrisari Florida Orange</t>
   </si>
   <si>
-    <t>Nutrisari Florida Orange Renceng</t>
+    <t>Nutrisari Florida Orange RC</t>
   </si>
   <si>
     <t>Marimas</t>
   </si>
   <si>
-    <t>Marimas Renceng</t>
+    <t>Marimas RC</t>
   </si>
   <si>
     <t>Adem Sari Bubuk</t>
@@ -263,85 +263,85 @@
     <t>Krating daeng KRT</t>
   </si>
   <si>
-    <t>Chocolatos Renceng</t>
+    <t>Chocolatos RC</t>
   </si>
   <si>
     <t>Sariwangi</t>
   </si>
   <si>
-    <t>Sariwangi Renceng</t>
+    <t>Sariwangi RC</t>
   </si>
   <si>
     <t>Energen</t>
   </si>
   <si>
-    <t>Energen Renceng</t>
+    <t>Energen RC</t>
   </si>
   <si>
     <t>Segar Dingin</t>
   </si>
   <si>
-    <t>Segar Dingin Renceng</t>
+    <t>Segar Dingin RC</t>
   </si>
   <si>
     <t>Dancow</t>
   </si>
   <si>
-    <t>Dancow Renceng</t>
+    <t>Dancow RC</t>
   </si>
   <si>
     <t>Champion</t>
   </si>
   <si>
-    <t>Champion Renceng</t>
+    <t>Champion RC</t>
   </si>
   <si>
     <t>Indocafe Coffemix</t>
   </si>
   <si>
-    <t>Indocafe Coffemix Renceng</t>
+    <t>Indocafe Coffemix RC</t>
   </si>
   <si>
     <t>Good Day Moccacino</t>
   </si>
   <si>
-    <t>Good Day Moccacino Renceng</t>
+    <t>Good Day Moccacino RC</t>
   </si>
   <si>
     <t>Good Day Cappuccino</t>
   </si>
   <si>
-    <t>Good Day Cappuccino Renceng</t>
+    <t>Good Day Cappuccino RC</t>
   </si>
   <si>
     <t>Good Day Chococinno</t>
   </si>
   <si>
-    <t>Good Day Chococinno Renceng</t>
+    <t>Good Day Chococinno RC</t>
   </si>
   <si>
     <t>Good Day Carrebian Nut</t>
   </si>
   <si>
-    <t>Good Day Carrebian Nut Renceng</t>
+    <t>Good Day Carrebian Nut RC</t>
   </si>
   <si>
     <t>Good Day Vanilla Latte</t>
   </si>
   <si>
-    <t>Good Day Vanilla Latte Renceng</t>
+    <t>Good Day Vanilla Latte RC</t>
   </si>
   <si>
     <t>Good Day Latte Butterscotch</t>
   </si>
   <si>
-    <t>Good Day Latte Butterscotch Renceng</t>
+    <t>Good Day Latte Butterscotch RC</t>
   </si>
   <si>
     <t>Good Day Coolin Caffe</t>
   </si>
   <si>
-    <t>Good Day Coolin Caffe Renceng</t>
+    <t>Good Day Coolin Caffe RC</t>
   </si>
   <si>
     <t>Tora Bika Duo</t>
@@ -350,25 +350,25 @@
     <t>Tora Bika Creamy Latte</t>
   </si>
   <si>
-    <t>Tora Bika Creamy Latte Renceng</t>
+    <t>Tora Bika Creamy Latte RC</t>
   </si>
   <si>
     <t>ABC Susu</t>
   </si>
   <si>
-    <t>ABC Susu Renceng</t>
+    <t>ABC Susu RC</t>
   </si>
   <si>
     <t>ABC Plus</t>
   </si>
   <si>
-    <t>ABC Plus Renceng</t>
+    <t>ABC Plus RC</t>
   </si>
   <si>
     <t>Top Kopi Gula Aren</t>
   </si>
   <si>
-    <t>Top Kopi Gula Aren Renceng</t>
+    <t>Top Kopi Gula Aren RC</t>
   </si>
   <si>
     <t>Kopi Tubruk Gadjah</t>
@@ -377,49 +377,49 @@
     <t>Jahe Merah AMH</t>
   </si>
   <si>
-    <t>Jahe Merah AMH Renceng</t>
+    <t>Jahe Merah AMH RC</t>
   </si>
   <si>
     <t>Kapal Api 60g</t>
   </si>
   <si>
-    <t>Kapal Api 60g Renceng</t>
+    <t>Kapal Api 60g RC</t>
   </si>
   <si>
     <t>Kapal Api 23g</t>
   </si>
   <si>
-    <t>Kapal Api 23g Renceng</t>
+    <t>Kapal Api 23g RC</t>
   </si>
   <si>
     <t>MaxTea Tarik (Teh Tarik)</t>
   </si>
   <si>
-    <t>MaxTea Tarik (Teh Tarik) Renceng</t>
+    <t>MaxTea Tarik (Teh Tarik) RC</t>
   </si>
   <si>
     <t>Luwak White Koffie</t>
   </si>
   <si>
-    <t>Luwak White Koffie Renceng</t>
+    <t>Luwak White Koffie RC</t>
   </si>
   <si>
     <t>Anget Sari Susu Jahe</t>
   </si>
   <si>
-    <t>Anget Sari Susu Jahe Renceng</t>
+    <t>Anget Sari Susu Jahe RC</t>
   </si>
   <si>
     <t>Teh Cap Botol</t>
   </si>
   <si>
-    <t>Teh Cap Botol Renceng</t>
+    <t>Teh Cap Botol RC</t>
   </si>
   <si>
     <t>Susu Milo</t>
   </si>
   <si>
-    <t>Susu Milo Renceng</t>
+    <t>Susu Milo RC</t>
   </si>
   <si>
     <t>Susu Frisian Flag P</t>
@@ -437,7 +437,7 @@
     <t>STMJ</t>
   </si>
   <si>
-    <t>STMJ Renceng</t>
+    <t>STMJ RC</t>
   </si>
   <si>
     <t>Extrajoss</t>
@@ -449,7 +449,7 @@
     <t>Fresco</t>
   </si>
   <si>
-    <t>Fresco R</t>
+    <t>Fresco RC</t>
   </si>
   <si>
     <t>Kerupuk Sumber Sari</t>
@@ -461,34 +461,34 @@
     <t>Ladaku Merica Bubuk</t>
   </si>
   <si>
-    <t>Ladaku Merica Bubuk Renceng</t>
+    <t>Ladaku Merica Bubuk RC</t>
   </si>
   <si>
     <t>Desaku Ketumbar Bubuk</t>
   </si>
   <si>
-    <t>Desaku Ketumbar Bubuk Renceng</t>
+    <t>Desaku Ketumbar Bubuk RC</t>
   </si>
   <si>
     <t>Desaku Bawang Putih</t>
   </si>
   <si>
-    <t>Desaku Bawang Putih Renceng</t>
+    <t>Desaku Bawang Putih RC</t>
   </si>
   <si>
     <t>Masako</t>
   </si>
   <si>
-    <t>Masako Ayam Renceng</t>
-  </si>
-  <si>
-    <t>Masako Sapi Renceng</t>
+    <t>Masako Ayam RC</t>
+  </si>
+  <si>
+    <t>Masako Sapi RC</t>
   </si>
   <si>
     <t>Tepung Bumbu Serba Guna Sasa</t>
   </si>
   <si>
-    <t>Tepung Bumbu Serba Guna Sasa Renceng</t>
+    <t>Tepung Bumbu Serba Guna Sasa RC</t>
   </si>
   <si>
     <t>Masako 250gr</t>
@@ -497,7 +497,7 @@
     <t>Royco</t>
   </si>
   <si>
-    <t>Royco Renceng</t>
+    <t>Royco RC</t>
   </si>
   <si>
     <t>Royco 250gr</t>
@@ -506,7 +506,7 @@
     <t>Kecap ABC</t>
   </si>
   <si>
-    <t>Kecap ABC Renceng</t>
+    <t>Kecap ABC RC</t>
   </si>
   <si>
     <t>Bumbu Pecel</t>
@@ -521,7 +521,7 @@
     <t>Bango 1000</t>
   </si>
   <si>
-    <t>Bango 1000 Renceng</t>
+    <t>Bango 1000 RC</t>
   </si>
   <si>
     <t>Bango 3000</t>
@@ -533,13 +533,13 @@
     <t>Saori Saus Tiram</t>
   </si>
   <si>
-    <t>Saori Saus Tiram Renceng</t>
+    <t>Saori Saus Tiram RC</t>
   </si>
   <si>
     <t>Saori Saus Teriyaki</t>
   </si>
   <si>
-    <t>Saori Saus Teriyaki Renceng</t>
+    <t>Saori Saus Teriyaki RC</t>
   </si>
   <si>
     <t>Pecin Sasa 30g 2000</t>
@@ -575,37 +575,37 @@
     <t>Racik Ikan</t>
   </si>
   <si>
-    <t>Racik Ikan Renceng</t>
+    <t>Racik Ikan RC</t>
   </si>
   <si>
     <t>Racik Lodeh</t>
   </si>
   <si>
-    <t>Racik Lodeh Renceng</t>
+    <t>Racik Lodeh RC</t>
   </si>
   <si>
     <t>Racik Asem</t>
   </si>
   <si>
-    <t>Racik Asem Renceng</t>
+    <t>Racik Asem RC</t>
   </si>
   <si>
     <t>Racik Sop</t>
   </si>
   <si>
-    <t>Racik Sop Renceng</t>
+    <t>Racik Sop RC</t>
   </si>
   <si>
     <t>Racik Ayam Goreng</t>
   </si>
   <si>
-    <t>Racik Ayam Goreng Renceng</t>
+    <t>Racik Ayam Goreng RC</t>
   </si>
   <si>
     <t>Racik Nasi Goreng</t>
   </si>
   <si>
-    <t>Racik Nasi Goreng Renceng</t>
+    <t>Racik Nasi Goreng RC</t>
   </si>
   <si>
     <t>Bawang Putih</t>
@@ -680,7 +680,7 @@
     <t>Minyak Sovia 2L</t>
   </si>
   <si>
-    <t xml:space="preserve">Nestle Renceng </t>
+    <t xml:space="preserve">Nestle RC </t>
   </si>
   <si>
     <t>Nes Bungkus</t>
@@ -905,7 +905,7 @@
     <t>Sarimi gelas</t>
   </si>
   <si>
-    <t>Sarimi gelas Renceng</t>
+    <t>Sarimi gelas RC</t>
   </si>
   <si>
     <t>Sarimi Duo Ayam Kecap</t>
@@ -944,37 +944,37 @@
     <t>Popok</t>
   </si>
   <si>
-    <t>Charm extra maxi wing Renceng</t>
+    <t>Charm extra maxi wing RC</t>
   </si>
   <si>
     <t>Charm extra maxi non wing</t>
   </si>
   <si>
-    <t>Charm extra maxi non wing Renceng</t>
+    <t>Charm extra maxi non wing RC</t>
   </si>
   <si>
     <t>Charm Safe Night</t>
   </si>
   <si>
-    <t>Charm Safe Night Renceng</t>
+    <t>Charm Safe Night RC</t>
   </si>
   <si>
     <t>MamyPoko M</t>
   </si>
   <si>
-    <t>MamyPoko M Renceng</t>
+    <t>MamyPoko M RC</t>
   </si>
   <si>
     <t>MamyPoko XL</t>
   </si>
   <si>
-    <t>MamyPoko XL Renceng</t>
+    <t>MamyPoko XL RC</t>
   </si>
   <si>
     <t>MamyPoko L</t>
   </si>
   <si>
-    <t>MamyPoko L Renceng</t>
+    <t>MamyPoko L RC</t>
   </si>
   <si>
     <t xml:space="preserve">Sunsilk </t>
@@ -983,37 +983,37 @@
     <t>Kamar Mandi</t>
   </si>
   <si>
-    <t>Sunsilk Renceng</t>
+    <t>Sunsilk RC</t>
   </si>
   <si>
     <t>Sampo Lifebuoy</t>
   </si>
   <si>
-    <t>Sampo Lifebuoy Renceg</t>
+    <t>Sampo Lifebuoy RC</t>
   </si>
   <si>
     <t>Sampo Pantene</t>
   </si>
   <si>
-    <t>Sampo Pantene Renceg</t>
+    <t>Sampo Pantene RC</t>
   </si>
   <si>
     <t>Sampo Zinc</t>
   </si>
   <si>
-    <t>Sampo Zinc Renceg</t>
+    <t>Sampo Zinc RC</t>
   </si>
   <si>
     <t>Sampo Clear</t>
   </si>
   <si>
-    <t>Sampo Clear Renceg</t>
+    <t>Sampo Clear RC</t>
   </si>
   <si>
     <t>Sampo Head &amp; Shoulders</t>
   </si>
   <si>
-    <t>Sampo Head &amp; Shoulders Renceg</t>
+    <t>Sampo Head &amp; Shoulders RC</t>
   </si>
   <si>
     <t>Sampo Dove</t>
@@ -1022,19 +1022,19 @@
     <t>Soklin Liquid 500</t>
   </si>
   <si>
-    <t>Soklin Liquid 500 Renceg</t>
+    <t>Soklin Liquid 500 RC</t>
   </si>
   <si>
     <t>Soklin Lantai</t>
   </si>
   <si>
-    <t>Soklin Lantai Renceng</t>
+    <t>Soklin Lantai RC</t>
   </si>
   <si>
     <t>Gentle Gen</t>
   </si>
   <si>
-    <t>Gentle Gen Renceg</t>
+    <t>Gentle Gen RC</t>
   </si>
   <si>
     <t>Kilau Nipis 2000</t>
@@ -1046,19 +1046,19 @@
     <t>Attack</t>
   </si>
   <si>
-    <t>Attack Renceg</t>
+    <t>Attack RC</t>
   </si>
   <si>
     <t>Rinso Bubuk</t>
   </si>
   <si>
-    <t>Rinso Bubuk Renceg</t>
+    <t>Rinso Bubuk RC</t>
   </si>
   <si>
     <t>Rinso Cair</t>
   </si>
   <si>
-    <t>Rinso Cair Renceg</t>
+    <t>Rinso Cair RC</t>
   </si>
   <si>
     <t>Molto</t>
@@ -1067,34 +1067,34 @@
     <t>Kispray</t>
   </si>
   <si>
-    <t>Kispray Renceng</t>
-  </si>
-  <si>
-    <t>Molto Renceng</t>
+    <t>Kispray RC</t>
+  </si>
+  <si>
+    <t>Molto RC</t>
   </si>
   <si>
     <t>Soklin Softener 500</t>
   </si>
   <si>
-    <t>Soklin Softener 500 Renceng</t>
+    <t>Soklin Softener 500 RC</t>
   </si>
   <si>
     <t>Downy 500</t>
   </si>
   <si>
-    <t>Downy 500 Renceg</t>
+    <t>Downy 500 RC</t>
   </si>
   <si>
     <t>Wipol</t>
   </si>
   <si>
-    <t>Wipol Renceng</t>
+    <t>Wipol RC</t>
   </si>
   <si>
     <t>Ekonomi 1000</t>
   </si>
   <si>
-    <t>Ekonomi 1000 Renceg</t>
+    <t>Ekonomi 1000 RC</t>
   </si>
   <si>
     <t>Ekonomi 1000 Dus</t>
@@ -1109,7 +1109,7 @@
     <t>Daia</t>
   </si>
   <si>
-    <t>Daia Renceg</t>
+    <t>Daia RC</t>
   </si>
   <si>
     <t>Sunlight</t>
@@ -1157,7 +1157,7 @@
     <t>Biosol</t>
   </si>
   <si>
-    <t>Biosol Renceng</t>
+    <t>Biosol RC</t>
   </si>
   <si>
     <t>Fair and Lovely Facial Foam</t>
@@ -1178,13 +1178,13 @@
     <t>Hit Mat</t>
   </si>
   <si>
-    <t>Hit Mat Renceng</t>
+    <t>Hit Mat RC</t>
   </si>
   <si>
     <t>Autan</t>
   </si>
   <si>
-    <t>Autan Renceng</t>
+    <t>Autan RC</t>
   </si>
   <si>
     <t>Solatif</t>
@@ -1220,7 +1220,7 @@
     <t>Lem Super Glue</t>
   </si>
   <si>
-    <t>Lem Super Glue Renceng</t>
+    <t>Lem Super Glue RC</t>
   </si>
   <si>
     <t>Cup Kertas</t>
@@ -1355,13 +1355,13 @@
     <t>Chitato</t>
   </si>
   <si>
-    <t>Roma Malkist 1000 Renceng</t>
-  </si>
-  <si>
-    <t>Taro 1000 Renceng</t>
-  </si>
-  <si>
-    <t>Garuda Renceng</t>
+    <t>Roma Malkist 1000 RC</t>
+  </si>
+  <si>
+    <t>Taro 1000 RC</t>
+  </si>
+  <si>
+    <t>Garuda RC</t>
   </si>
   <si>
     <t>Sosis So Nice Toples</t>
@@ -1373,10 +1373,10 @@
     <t>Nabati Aah</t>
   </si>
   <si>
-    <t>Pilus 500 Renceng</t>
-  </si>
-  <si>
-    <t>Pilus 1000 Renceng</t>
+    <t>Pilus 500 RC</t>
+  </si>
+  <si>
+    <t>Pilus 1000 RC</t>
   </si>
   <si>
     <t>Chocolatos 500</t>
@@ -1385,7 +1385,7 @@
     <t>Wow Spagheti</t>
   </si>
   <si>
-    <t>Wow Spagheti Renceng</t>
+    <t>Wow Spagheti RC</t>
   </si>
   <si>
     <t>Cat Choize</t>
@@ -1400,13 +1400,13 @@
     <t>Yupi baby bear Box</t>
   </si>
   <si>
-    <t>Snack Copico Renceng</t>
+    <t>Snack Copico RC</t>
   </si>
   <si>
     <t>Roti mini 1000</t>
   </si>
   <si>
-    <t>Choco Pie 2000 Renceng</t>
+    <t>Choco Pie 2000 RC</t>
   </si>
   <si>
     <t>Roma Sandwich</t>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="522">
   <si>
-    <t>Barcode</t>
+    <t>Ba- RCode</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Ecer</t>
   </si>
   <si>
-    <t>Nutrisari Jeruk Peras RC</t>
+    <t>Nutrisari Jeruk Peras - RC</t>
   </si>
   <si>
     <t>KRT</t>
@@ -68,13 +68,13 @@
     <t>Nutrisari Florida Orange</t>
   </si>
   <si>
-    <t>Nutrisari Florida Orange RC</t>
+    <t>Nutrisari Florida Orange - RC</t>
   </si>
   <si>
     <t>Marimas</t>
   </si>
   <si>
-    <t>Marimas RC</t>
+    <t>Marimas - RC</t>
   </si>
   <si>
     <t>Adem Sari Bubuk</t>
@@ -263,85 +263,85 @@
     <t>Krating daeng KRT</t>
   </si>
   <si>
-    <t>Chocolatos RC</t>
+    <t>Chocolatos - RC</t>
   </si>
   <si>
     <t>Sariwangi</t>
   </si>
   <si>
-    <t>Sariwangi RC</t>
+    <t>Sariwangi - RC</t>
   </si>
   <si>
     <t>Energen</t>
   </si>
   <si>
-    <t>Energen RC</t>
+    <t>Energen - RC</t>
   </si>
   <si>
     <t>Segar Dingin</t>
   </si>
   <si>
-    <t>Segar Dingin RC</t>
+    <t>Segar Dingin - RC</t>
   </si>
   <si>
     <t>Dancow</t>
   </si>
   <si>
-    <t>Dancow RC</t>
+    <t>Dancow - RC</t>
   </si>
   <si>
     <t>Champion</t>
   </si>
   <si>
-    <t>Champion RC</t>
+    <t>Champion - RC</t>
   </si>
   <si>
     <t>Indocafe Coffemix</t>
   </si>
   <si>
-    <t>Indocafe Coffemix RC</t>
+    <t>Indocafe Coffemix - RC</t>
   </si>
   <si>
     <t>Good Day Moccacino</t>
   </si>
   <si>
-    <t>Good Day Moccacino RC</t>
+    <t>Good Day Moccacino - RC</t>
   </si>
   <si>
     <t>Good Day Cappuccino</t>
   </si>
   <si>
-    <t>Good Day Cappuccino RC</t>
+    <t>Good Day Cappuccino - RC</t>
   </si>
   <si>
     <t>Good Day Chococinno</t>
   </si>
   <si>
-    <t>Good Day Chococinno RC</t>
+    <t>Good Day Chococinno - RC</t>
   </si>
   <si>
     <t>Good Day Carrebian Nut</t>
   </si>
   <si>
-    <t>Good Day Carrebian Nut RC</t>
+    <t>Good Day Carrebian Nut - RC</t>
   </si>
   <si>
     <t>Good Day Vanilla Latte</t>
   </si>
   <si>
-    <t>Good Day Vanilla Latte RC</t>
+    <t>Good Day Vanilla Latte - RC</t>
   </si>
   <si>
     <t>Good Day Latte Butterscotch</t>
   </si>
   <si>
-    <t>Good Day Latte Butterscotch RC</t>
+    <t>Good Day Latte Butterscotch - RC</t>
   </si>
   <si>
     <t>Good Day Coolin Caffe</t>
   </si>
   <si>
-    <t>Good Day Coolin Caffe RC</t>
+    <t>Good Day Coolin Caffe - RC</t>
   </si>
   <si>
     <t>Tora Bika Duo</t>
@@ -350,25 +350,25 @@
     <t>Tora Bika Creamy Latte</t>
   </si>
   <si>
-    <t>Tora Bika Creamy Latte RC</t>
+    <t>Tora Bika Creamy Latte - RC</t>
   </si>
   <si>
     <t>ABC Susu</t>
   </si>
   <si>
-    <t>ABC Susu RC</t>
+    <t>ABC Susu - RC</t>
   </si>
   <si>
     <t>ABC Plus</t>
   </si>
   <si>
-    <t>ABC Plus RC</t>
+    <t>ABC Plus - RC</t>
   </si>
   <si>
     <t>Top Kopi Gula Aren</t>
   </si>
   <si>
-    <t>Top Kopi Gula Aren RC</t>
+    <t>Top Kopi Gula Aren - RC</t>
   </si>
   <si>
     <t>Kopi Tubruk Gadjah</t>
@@ -377,49 +377,49 @@
     <t>Jahe Merah AMH</t>
   </si>
   <si>
-    <t>Jahe Merah AMH RC</t>
+    <t>Jahe Merah AMH - RC</t>
   </si>
   <si>
     <t>Kapal Api 60g</t>
   </si>
   <si>
-    <t>Kapal Api 60g RC</t>
+    <t>Kapal Api 60g - RC</t>
   </si>
   <si>
     <t>Kapal Api 23g</t>
   </si>
   <si>
-    <t>Kapal Api 23g RC</t>
+    <t>Kapal Api 23g - RC</t>
   </si>
   <si>
     <t>MaxTea Tarik (Teh Tarik)</t>
   </si>
   <si>
-    <t>MaxTea Tarik (Teh Tarik) RC</t>
+    <t>MaxTea Tarik (Teh Tarik) - RC</t>
   </si>
   <si>
     <t>Luwak White Koffie</t>
   </si>
   <si>
-    <t>Luwak White Koffie RC</t>
+    <t>Luwak White Koffie - RC</t>
   </si>
   <si>
     <t>Anget Sari Susu Jahe</t>
   </si>
   <si>
-    <t>Anget Sari Susu Jahe RC</t>
+    <t>Anget Sari Susu Jahe - RC</t>
   </si>
   <si>
     <t>Teh Cap Botol</t>
   </si>
   <si>
-    <t>Teh Cap Botol RC</t>
+    <t>Teh Cap Botol - RC</t>
   </si>
   <si>
     <t>Susu Milo</t>
   </si>
   <si>
-    <t>Susu Milo RC</t>
+    <t>Susu Milo - RC</t>
   </si>
   <si>
     <t>Susu Frisian Flag P</t>
@@ -437,7 +437,7 @@
     <t>STMJ</t>
   </si>
   <si>
-    <t>STMJ RC</t>
+    <t>STMJ - RC</t>
   </si>
   <si>
     <t>Extrajoss</t>
@@ -449,7 +449,7 @@
     <t>Fresco</t>
   </si>
   <si>
-    <t>Fresco RC</t>
+    <t>Fresco - RC</t>
   </si>
   <si>
     <t>Kerupuk Sumber Sari</t>
@@ -461,34 +461,34 @@
     <t>Ladaku Merica Bubuk</t>
   </si>
   <si>
-    <t>Ladaku Merica Bubuk RC</t>
+    <t>Ladaku Merica Bubuk - RC</t>
   </si>
   <si>
     <t>Desaku Ketumbar Bubuk</t>
   </si>
   <si>
-    <t>Desaku Ketumbar Bubuk RC</t>
+    <t>Desaku Ketumbar Bubuk - RC</t>
   </si>
   <si>
     <t>Desaku Bawang Putih</t>
   </si>
   <si>
-    <t>Desaku Bawang Putih RC</t>
+    <t>Desaku Bawang Putih - RC</t>
   </si>
   <si>
     <t>Masako</t>
   </si>
   <si>
-    <t>Masako Ayam RC</t>
-  </si>
-  <si>
-    <t>Masako Sapi RC</t>
+    <t>Masako Ayam - RC</t>
+  </si>
+  <si>
+    <t>Masako Sapi - RC</t>
   </si>
   <si>
     <t>Tepung Bumbu Serba Guna Sasa</t>
   </si>
   <si>
-    <t>Tepung Bumbu Serba Guna Sasa RC</t>
+    <t>Tepung Bumbu Serba Guna Sasa - RC</t>
   </si>
   <si>
     <t>Masako 250gr</t>
@@ -497,7 +497,7 @@
     <t>Royco</t>
   </si>
   <si>
-    <t>Royco RC</t>
+    <t>Royco - RC</t>
   </si>
   <si>
     <t>Royco 250gr</t>
@@ -506,7 +506,7 @@
     <t>Kecap ABC</t>
   </si>
   <si>
-    <t>Kecap ABC RC</t>
+    <t>Kecap ABC - RC</t>
   </si>
   <si>
     <t>Bumbu Pecel</t>
@@ -521,7 +521,7 @@
     <t>Bango 1000</t>
   </si>
   <si>
-    <t>Bango 1000 RC</t>
+    <t>Bango 1000 - RC</t>
   </si>
   <si>
     <t>Bango 3000</t>
@@ -533,13 +533,13 @@
     <t>Saori Saus Tiram</t>
   </si>
   <si>
-    <t>Saori Saus Tiram RC</t>
+    <t>Saori Saus Tiram - RC</t>
   </si>
   <si>
     <t>Saori Saus Teriyaki</t>
   </si>
   <si>
-    <t>Saori Saus Teriyaki RC</t>
+    <t>Saori Saus Teriyaki - RC</t>
   </si>
   <si>
     <t>Pecin Sasa 30g 2000</t>
@@ -575,37 +575,37 @@
     <t>Racik Ikan</t>
   </si>
   <si>
-    <t>Racik Ikan RC</t>
+    <t>Racik Ikan - RC</t>
   </si>
   <si>
     <t>Racik Lodeh</t>
   </si>
   <si>
-    <t>Racik Lodeh RC</t>
+    <t>Racik Lodeh - RC</t>
   </si>
   <si>
     <t>Racik Asem</t>
   </si>
   <si>
-    <t>Racik Asem RC</t>
+    <t>Racik Asem - RC</t>
   </si>
   <si>
     <t>Racik Sop</t>
   </si>
   <si>
-    <t>Racik Sop RC</t>
+    <t>Racik Sop - RC</t>
   </si>
   <si>
     <t>Racik Ayam Goreng</t>
   </si>
   <si>
-    <t>Racik Ayam Goreng RC</t>
+    <t>Racik Ayam Goreng - RC</t>
   </si>
   <si>
     <t>Racik Nasi Goreng</t>
   </si>
   <si>
-    <t>Racik Nasi Goreng RC</t>
+    <t>Racik Nasi Goreng - RC</t>
   </si>
   <si>
     <t>Bawang Putih</t>
@@ -680,7 +680,7 @@
     <t>Minyak Sovia 2L</t>
   </si>
   <si>
-    <t xml:space="preserve">Nestle RC </t>
+    <t xml:space="preserve">Nestle - RC </t>
   </si>
   <si>
     <t>Nes Bungkus</t>
@@ -905,7 +905,7 @@
     <t>Sarimi gelas</t>
   </si>
   <si>
-    <t>Sarimi gelas RC</t>
+    <t>Sarimi gelas - RC</t>
   </si>
   <si>
     <t>Sarimi Duo Ayam Kecap</t>
@@ -944,37 +944,37 @@
     <t>Popok</t>
   </si>
   <si>
-    <t>Charm extra maxi wing RC</t>
+    <t>Charm extra maxi wing - RC</t>
   </si>
   <si>
     <t>Charm extra maxi non wing</t>
   </si>
   <si>
-    <t>Charm extra maxi non wing RC</t>
+    <t>Charm extra maxi non wing - RC</t>
   </si>
   <si>
     <t>Charm Safe Night</t>
   </si>
   <si>
-    <t>Charm Safe Night RC</t>
+    <t>Charm Safe Night - RC</t>
   </si>
   <si>
     <t>MamyPoko M</t>
   </si>
   <si>
-    <t>MamyPoko M RC</t>
+    <t>MamyPoko M - RC</t>
   </si>
   <si>
     <t>MamyPoko XL</t>
   </si>
   <si>
-    <t>MamyPoko XL RC</t>
+    <t>MamyPoko XL - RC</t>
   </si>
   <si>
     <t>MamyPoko L</t>
   </si>
   <si>
-    <t>MamyPoko L RC</t>
+    <t>MamyPoko L - RC</t>
   </si>
   <si>
     <t xml:space="preserve">Sunsilk </t>
@@ -983,37 +983,37 @@
     <t>Kamar Mandi</t>
   </si>
   <si>
-    <t>Sunsilk RC</t>
+    <t>Sunsilk - RC</t>
   </si>
   <si>
     <t>Sampo Lifebuoy</t>
   </si>
   <si>
-    <t>Sampo Lifebuoy RC</t>
+    <t>Sampo Lifebuoy - RC</t>
   </si>
   <si>
     <t>Sampo Pantene</t>
   </si>
   <si>
-    <t>Sampo Pantene RC</t>
+    <t>Sampo Pantene - RC</t>
   </si>
   <si>
     <t>Sampo Zinc</t>
   </si>
   <si>
-    <t>Sampo Zinc RC</t>
+    <t>Sampo Zinc - RC</t>
   </si>
   <si>
     <t>Sampo Clear</t>
   </si>
   <si>
-    <t>Sampo Clear RC</t>
+    <t>Sampo Clear - RC</t>
   </si>
   <si>
     <t>Sampo Head &amp; Shoulders</t>
   </si>
   <si>
-    <t>Sampo Head &amp; Shoulders RC</t>
+    <t>Sampo Head &amp; Shoulders - RC</t>
   </si>
   <si>
     <t>Sampo Dove</t>
@@ -1022,19 +1022,19 @@
     <t>Soklin Liquid 500</t>
   </si>
   <si>
-    <t>Soklin Liquid 500 RC</t>
+    <t>Soklin Liquid 500 - RC</t>
   </si>
   <si>
     <t>Soklin Lantai</t>
   </si>
   <si>
-    <t>Soklin Lantai RC</t>
+    <t>Soklin Lantai - RC</t>
   </si>
   <si>
     <t>Gentle Gen</t>
   </si>
   <si>
-    <t>Gentle Gen RC</t>
+    <t>Gentle Gen - RC</t>
   </si>
   <si>
     <t>Kilau Nipis 2000</t>
@@ -1046,19 +1046,19 @@
     <t>Attack</t>
   </si>
   <si>
-    <t>Attack RC</t>
+    <t>Attack - RC</t>
   </si>
   <si>
     <t>Rinso Bubuk</t>
   </si>
   <si>
-    <t>Rinso Bubuk RC</t>
+    <t>Rinso Bubuk - RC</t>
   </si>
   <si>
     <t>Rinso Cair</t>
   </si>
   <si>
-    <t>Rinso Cair RC</t>
+    <t>Rinso Cair - RC</t>
   </si>
   <si>
     <t>Molto</t>
@@ -1067,34 +1067,34 @@
     <t>Kispray</t>
   </si>
   <si>
-    <t>Kispray RC</t>
-  </si>
-  <si>
-    <t>Molto RC</t>
+    <t>Kispray - RC</t>
+  </si>
+  <si>
+    <t>Molto - RC</t>
   </si>
   <si>
     <t>Soklin Softener 500</t>
   </si>
   <si>
-    <t>Soklin Softener 500 RC</t>
+    <t>Soklin Softener 500 - RC</t>
   </si>
   <si>
     <t>Downy 500</t>
   </si>
   <si>
-    <t>Downy 500 RC</t>
+    <t>Downy 500 - RC</t>
   </si>
   <si>
     <t>Wipol</t>
   </si>
   <si>
-    <t>Wipol RC</t>
+    <t>Wipol - RC</t>
   </si>
   <si>
     <t>Ekonomi 1000</t>
   </si>
   <si>
-    <t>Ekonomi 1000 RC</t>
+    <t>Ekonomi 1000 - RC</t>
   </si>
   <si>
     <t>Ekonomi 1000 Dus</t>
@@ -1109,7 +1109,7 @@
     <t>Daia</t>
   </si>
   <si>
-    <t>Daia RC</t>
+    <t>Daia - RC</t>
   </si>
   <si>
     <t>Sunlight</t>
@@ -1157,7 +1157,7 @@
     <t>Biosol</t>
   </si>
   <si>
-    <t>Biosol RC</t>
+    <t>Biosol - RC</t>
   </si>
   <si>
     <t>Fair and Lovely Facial Foam</t>
@@ -1178,13 +1178,13 @@
     <t>Hit Mat</t>
   </si>
   <si>
-    <t>Hit Mat RC</t>
+    <t>Hit Mat - RC</t>
   </si>
   <si>
     <t>Autan</t>
   </si>
   <si>
-    <t>Autan RC</t>
+    <t>Autan - RC</t>
   </si>
   <si>
     <t>Solatif</t>
@@ -1220,7 +1220,7 @@
     <t>Lem Super Glue</t>
   </si>
   <si>
-    <t>Lem Super Glue RC</t>
+    <t>Lem Super Glue - RC</t>
   </si>
   <si>
     <t>Cup Kertas</t>
@@ -1355,13 +1355,13 @@
     <t>Chitato</t>
   </si>
   <si>
-    <t>Roma Malkist 1000 RC</t>
-  </si>
-  <si>
-    <t>Taro 1000 RC</t>
-  </si>
-  <si>
-    <t>Garuda RC</t>
+    <t>Roma Malkist 1000 - RC</t>
+  </si>
+  <si>
+    <t>Taro 1000 - RC</t>
+  </si>
+  <si>
+    <t>Garuda - RC</t>
   </si>
   <si>
     <t>Sosis So Nice Toples</t>
@@ -1373,10 +1373,10 @@
     <t>Nabati Aah</t>
   </si>
   <si>
-    <t>Pilus 500 RC</t>
-  </si>
-  <si>
-    <t>Pilus 1000 RC</t>
+    <t>Pilus 500 - RC</t>
+  </si>
+  <si>
+    <t>Pilus 1000 - RC</t>
   </si>
   <si>
     <t>Chocolatos 500</t>
@@ -1385,7 +1385,7 @@
     <t>Wow Spagheti</t>
   </si>
   <si>
-    <t>Wow Spagheti RC</t>
+    <t>Wow Spagheti - RC</t>
   </si>
   <si>
     <t>Cat Choize</t>
@@ -1400,13 +1400,13 @@
     <t>Yupi baby bear Box</t>
   </si>
   <si>
-    <t>Snack Copico RC</t>
+    <t>Snack Copico - RC</t>
   </si>
   <si>
     <t>Roti mini 1000</t>
   </si>
   <si>
-    <t>Choco Pie 2000 RC</t>
+    <t>Choco Pie 2000 - RC</t>
   </si>
   <si>
     <t>Roma Sandwich</t>
@@ -11406,7 +11406,7 @@
         <v>384</v>
       </c>
       <c r="D385" s="4">
-        <v>8000.0</v>
+        <v>8500.0</v>
       </c>
       <c r="E385" s="7"/>
       <c r="F385" s="7"/>
@@ -12294,10 +12294,14 @@
         <v>384</v>
       </c>
       <c r="D422" s="17">
-        <v>200.0</v>
-      </c>
-      <c r="E422" s="17"/>
-      <c r="F422" s="17"/>
+        <v>300.0</v>
+      </c>
+      <c r="E422" s="17">
+        <v>2.0</v>
+      </c>
+      <c r="F422" s="17">
+        <v>500.0</v>
+      </c>
       <c r="G422" s="18"/>
       <c r="H422" s="18"/>
       <c r="I422" s="18"/>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="523">
   <si>
     <t>Ba- RCode</t>
   </si>
@@ -1581,6 +1581,9 @@
   </si>
   <si>
     <t>Minyak Fitri 400ml KRT</t>
+  </si>
+  <si>
+    <t>Adem Sari Ching ku</t>
   </si>
 </sst>
 </file>
@@ -23105,7 +23108,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="str">
-        <f t="shared" ref="A2:A79" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
+        <f t="shared" ref="A2:A80" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -24820,17 +24823,26 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4"/>
-      <c r="B80" s="5"/>
+      <c r="A80" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR79</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>522</v>
+      </c>
       <c r="C80" s="5"/>
-      <c r="D80" s="4"/>
+      <c r="D80" s="4">
+        <v>6500.0</v>
+      </c>
       <c r="E80" s="21"/>
       <c r="F80" s="21"/>
       <c r="G80" s="21"/>
       <c r="H80" s="21"/>
       <c r="I80" s="21"/>
       <c r="J80" s="21"/>
-      <c r="K80" s="21"/>
+      <c r="K80" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4"/>
@@ -37879,7 +37891,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K79">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K80">
       <formula1>"Ecer,KRT"</formula1>
     </dataValidation>
   </dataValidations>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -4603,7 +4603,7 @@
         <v>12</v>
       </c>
       <c r="D108" s="4">
-        <v>10000.0</v>
+        <v>9500.0</v>
       </c>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
@@ -8316,10 +8316,10 @@
         <v>4000.0</v>
       </c>
       <c r="E258" s="4">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F258" s="4">
-        <v>39000.0</v>
+        <v>19500.0</v>
       </c>
       <c r="G258" s="7"/>
       <c r="H258" s="7"/>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$449</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$452</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$263</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="530">
   <si>
     <t>Ba- RCode</t>
   </si>
@@ -1419,6 +1419,15 @@
   </si>
   <si>
     <t>Class Mild 16</t>
+  </si>
+  <si>
+    <t>Desaku balado</t>
+  </si>
+  <si>
+    <t>Desaku Balado pak</t>
+  </si>
+  <si>
+    <t>Sabun Dettol</t>
   </si>
   <si>
     <t>Djarum Coklat SLOP</t>
@@ -2018,7 +2027,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A449" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A452" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -12980,43 +12989,76 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="19"/>
-      <c r="B450" s="19"/>
-      <c r="C450" s="19"/>
-      <c r="D450" s="18"/>
+      <c r="A450" s="4">
+        <f t="shared" si="1"/>
+        <v>449</v>
+      </c>
+      <c r="B450" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="C450" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D450" s="17">
+        <v>3000.0</v>
+      </c>
       <c r="E450" s="18"/>
       <c r="F450" s="18"/>
       <c r="G450" s="18"/>
       <c r="H450" s="18"/>
       <c r="I450" s="18"/>
       <c r="J450" s="18"/>
-      <c r="K450" s="18"/>
+      <c r="K450" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="451">
-      <c r="A451" s="19"/>
-      <c r="B451" s="19"/>
-      <c r="C451" s="19"/>
-      <c r="D451" s="18"/>
+      <c r="A451" s="4">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="B451" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="C451" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D451" s="17">
+        <v>25000.0</v>
+      </c>
       <c r="E451" s="18"/>
       <c r="F451" s="18"/>
       <c r="G451" s="18"/>
       <c r="H451" s="18"/>
       <c r="I451" s="18"/>
       <c r="J451" s="18"/>
-      <c r="K451" s="18"/>
+      <c r="K451" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="452">
-      <c r="A452" s="19"/>
-      <c r="B452" s="19"/>
-      <c r="C452" s="19"/>
-      <c r="D452" s="18"/>
+      <c r="A452" s="4">
+        <f t="shared" si="1"/>
+        <v>451</v>
+      </c>
+      <c r="B452" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C452" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="D452" s="17">
+        <v>4000.0</v>
+      </c>
       <c r="E452" s="18"/>
       <c r="F452" s="18"/>
       <c r="G452" s="18"/>
       <c r="H452" s="18"/>
       <c r="I452" s="18"/>
       <c r="J452" s="18"/>
-      <c r="K452" s="18"/>
+      <c r="K452" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="19"/>
@@ -23081,7 +23123,7 @@
       <c r="K1226" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$449"/>
+  <autoFilter ref="$B$1:$C$452"/>
   <conditionalFormatting sqref="B443">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
@@ -23093,10 +23135,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C449">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C452">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K449">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K452">
       <formula1>"Ecer,KRT"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23183,7 +23225,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -23205,7 +23247,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -23227,7 +23269,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -23271,7 +23313,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -23315,7 +23357,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -23359,7 +23401,7 @@
         <v>GROSIR10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="4">
@@ -23403,7 +23445,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -23425,7 +23467,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -23469,7 +23511,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -23491,7 +23533,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -23513,7 +23555,7 @@
         <v>GROSIR17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="4">
@@ -23579,7 +23621,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -23601,7 +23643,7 @@
         <v>GROSIR21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4">
@@ -23623,7 +23665,7 @@
         <v>GROSIR22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="4">
@@ -23689,7 +23731,7 @@
         <v>GROSIR25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="4">
@@ -23711,7 +23753,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -23733,7 +23775,7 @@
         <v>GROSIR27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="4">
@@ -23755,7 +23797,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -23777,7 +23819,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -23799,7 +23841,7 @@
         <v>GROSIR30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="4">
@@ -23821,7 +23863,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -23843,7 +23885,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -23887,7 +23929,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -23909,7 +23951,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -23931,7 +23973,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -23953,7 +23995,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -23975,7 +24017,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -23997,7 +24039,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -24019,7 +24061,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -24041,7 +24083,7 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
@@ -24085,7 +24127,7 @@
         <v>GROSIR43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="4">
@@ -24129,7 +24171,7 @@
         <v>GROSIR45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="4">
@@ -24173,7 +24215,7 @@
         <v>GROSIR47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="4">
@@ -24217,7 +24259,7 @@
         <v>GROSIR49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="4">
@@ -24239,7 +24281,7 @@
         <v>GROSIR50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="4">
@@ -24261,7 +24303,7 @@
         <v>GROSIR51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="4">
@@ -24283,7 +24325,7 @@
         <v>GROSIR52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="4">
@@ -24305,7 +24347,7 @@
         <v>GROSIR53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="4">
@@ -24327,7 +24369,7 @@
         <v>GROSIR54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="4">
@@ -24349,7 +24391,7 @@
         <v>GROSIR55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="4">
@@ -24371,7 +24413,7 @@
         <v>GROSIR56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="4">
@@ -24393,7 +24435,7 @@
         <v>GROSIR57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="4">
@@ -24415,7 +24457,7 @@
         <v>GROSIR58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="4">
@@ -24437,7 +24479,7 @@
         <v>GROSIR59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="4">
@@ -24459,7 +24501,7 @@
         <v>GROSIR60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="4">
@@ -24481,7 +24523,7 @@
         <v>GROSIR61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="4">
@@ -24503,7 +24545,7 @@
         <v>GROSIR62</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="4">
@@ -24547,7 +24589,7 @@
         <v>GROSIR64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="4">
@@ -24657,7 +24699,7 @@
         <v>GROSIR69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C70" s="5"/>
       <c r="D70" s="4">
@@ -24679,7 +24721,7 @@
         <v>GROSIR70</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C71" s="5"/>
       <c r="D71" s="4">
@@ -24701,7 +24743,7 @@
         <v>GROSIR71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="4">
@@ -24767,7 +24809,7 @@
         <v>GROSIR74</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="4">
@@ -24789,7 +24831,7 @@
         <v>GROSIR75</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C76" s="5"/>
       <c r="D76" s="4">
@@ -24811,7 +24853,7 @@
         <v>GROSIR76</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C77" s="5"/>
       <c r="D77" s="4">
@@ -24833,7 +24875,7 @@
         <v>GROSIR77</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C78" s="5"/>
       <c r="D78" s="4">
@@ -24855,7 +24897,7 @@
         <v>GROSIR78</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C79" s="5"/>
       <c r="D79" s="4">
@@ -24877,7 +24919,7 @@
         <v>GROSIR79</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C80" s="5"/>
       <c r="D80" s="4">
@@ -24899,7 +24941,7 @@
         <v>GROSIR80</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C81" s="5"/>
       <c r="D81" s="4">
@@ -24967,7 +25009,7 @@
         <v>GROSIR83</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C84" s="5"/>
       <c r="D84" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$452</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$453</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$263</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="531">
   <si>
     <t>Ba- RCode</t>
   </si>
@@ -1428,6 +1428,9 @@
   </si>
   <si>
     <t>Sabun Dettol</t>
+  </si>
+  <si>
+    <t>Gas Melon</t>
   </si>
   <si>
     <t>Djarum Coklat SLOP</t>
@@ -2027,7 +2030,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A452" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A453" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -13061,17 +13064,28 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="19"/>
-      <c r="B453" s="19"/>
-      <c r="C453" s="19"/>
-      <c r="D453" s="18"/>
+      <c r="A453" s="4">
+        <f t="shared" si="1"/>
+        <v>452</v>
+      </c>
+      <c r="B453" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="C453" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D453" s="17">
+        <v>23000.0</v>
+      </c>
       <c r="E453" s="18"/>
       <c r="F453" s="18"/>
       <c r="G453" s="18"/>
       <c r="H453" s="18"/>
       <c r="I453" s="18"/>
       <c r="J453" s="18"/>
-      <c r="K453" s="18"/>
+      <c r="K453" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="19"/>
@@ -13987,14 +14001,14 @@
       <c r="A524" s="19"/>
       <c r="B524" s="19"/>
       <c r="C524" s="19"/>
-      <c r="D524" s="18"/>
-      <c r="E524" s="18"/>
-      <c r="F524" s="18"/>
-      <c r="G524" s="18"/>
-      <c r="H524" s="18"/>
-      <c r="I524" s="18"/>
-      <c r="J524" s="18"/>
-      <c r="K524" s="18"/>
+      <c r="D524" s="19"/>
+      <c r="E524" s="19"/>
+      <c r="F524" s="19"/>
+      <c r="G524" s="19"/>
+      <c r="H524" s="19"/>
+      <c r="I524" s="19"/>
+      <c r="J524" s="19"/>
+      <c r="K524" s="19"/>
     </row>
     <row r="525">
       <c r="A525" s="19"/>
@@ -23109,36 +23123,23 @@
       <c r="J1225" s="19"/>
       <c r="K1225" s="19"/>
     </row>
-    <row r="1226">
-      <c r="A1226" s="19"/>
-      <c r="B1226" s="19"/>
-      <c r="C1226" s="19"/>
-      <c r="D1226" s="19"/>
-      <c r="E1226" s="19"/>
-      <c r="F1226" s="19"/>
-      <c r="G1226" s="19"/>
-      <c r="H1226" s="19"/>
-      <c r="I1226" s="19"/>
-      <c r="J1226" s="19"/>
-      <c r="K1226" s="19"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$452"/>
+  <autoFilter ref="$B$1:$C$453"/>
   <conditionalFormatting sqref="B443">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A1226 B2:B442 C2:K1226 B444:B1226">
+  <conditionalFormatting sqref="A2:A1225 B2:B442 C2:K1225 B444:B1225">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>isodd(row())</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C452">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C453">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K452">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K453">
       <formula1>"Ecer,KRT"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23225,7 +23226,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -23247,7 +23248,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -23269,7 +23270,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -23313,7 +23314,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -23357,7 +23358,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -23401,7 +23402,7 @@
         <v>GROSIR10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="4">
@@ -23445,7 +23446,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -23467,7 +23468,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -23511,7 +23512,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -23533,7 +23534,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -23555,7 +23556,7 @@
         <v>GROSIR17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="4">
@@ -23621,7 +23622,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -23643,7 +23644,7 @@
         <v>GROSIR21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4">
@@ -23665,7 +23666,7 @@
         <v>GROSIR22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="4">
@@ -23731,7 +23732,7 @@
         <v>GROSIR25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="4">
@@ -23753,7 +23754,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -23775,7 +23776,7 @@
         <v>GROSIR27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="4">
@@ -23797,7 +23798,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -23819,7 +23820,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -23841,7 +23842,7 @@
         <v>GROSIR30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="4">
@@ -23863,7 +23864,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -23885,7 +23886,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -23929,7 +23930,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -23951,7 +23952,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -23973,7 +23974,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -23995,7 +23996,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -24017,7 +24018,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -24039,7 +24040,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -24061,7 +24062,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -24083,7 +24084,7 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
@@ -24127,7 +24128,7 @@
         <v>GROSIR43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="4">
@@ -24171,7 +24172,7 @@
         <v>GROSIR45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="4">
@@ -24215,7 +24216,7 @@
         <v>GROSIR47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="4">
@@ -24259,7 +24260,7 @@
         <v>GROSIR49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="4">
@@ -24281,7 +24282,7 @@
         <v>GROSIR50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="4">
@@ -24303,7 +24304,7 @@
         <v>GROSIR51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="4">
@@ -24325,7 +24326,7 @@
         <v>GROSIR52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="4">
@@ -24347,7 +24348,7 @@
         <v>GROSIR53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="4">
@@ -24369,7 +24370,7 @@
         <v>GROSIR54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="4">
@@ -24391,7 +24392,7 @@
         <v>GROSIR55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="4">
@@ -24413,7 +24414,7 @@
         <v>GROSIR56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="4">
@@ -24435,7 +24436,7 @@
         <v>GROSIR57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="4">
@@ -24457,7 +24458,7 @@
         <v>GROSIR58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="4">
@@ -24479,7 +24480,7 @@
         <v>GROSIR59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="4">
@@ -24501,7 +24502,7 @@
         <v>GROSIR60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="4">
@@ -24523,7 +24524,7 @@
         <v>GROSIR61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="4">
@@ -24545,7 +24546,7 @@
         <v>GROSIR62</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="4">
@@ -24589,7 +24590,7 @@
         <v>GROSIR64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="4">
@@ -24699,7 +24700,7 @@
         <v>GROSIR69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C70" s="5"/>
       <c r="D70" s="4">
@@ -24721,7 +24722,7 @@
         <v>GROSIR70</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C71" s="5"/>
       <c r="D71" s="4">
@@ -24743,7 +24744,7 @@
         <v>GROSIR71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="4">
@@ -24809,7 +24810,7 @@
         <v>GROSIR74</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="4">
@@ -24831,7 +24832,7 @@
         <v>GROSIR75</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C76" s="5"/>
       <c r="D76" s="4">
@@ -24853,7 +24854,7 @@
         <v>GROSIR76</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C77" s="5"/>
       <c r="D77" s="4">
@@ -24875,7 +24876,7 @@
         <v>GROSIR77</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C78" s="5"/>
       <c r="D78" s="4">
@@ -24897,7 +24898,7 @@
         <v>GROSIR78</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C79" s="5"/>
       <c r="D79" s="4">
@@ -24919,7 +24920,7 @@
         <v>GROSIR79</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C80" s="5"/>
       <c r="D80" s="4">
@@ -24941,7 +24942,7 @@
         <v>GROSIR80</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C81" s="5"/>
       <c r="D81" s="4">
@@ -25009,7 +25010,7 @@
         <v>GROSIR83</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C84" s="5"/>
       <c r="D84" s="4">

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$455</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$456</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$263</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="539">
   <si>
     <t>Ba- RCode</t>
   </si>
@@ -110,7 +110,7 @@
     <t>Ale Ale Dus</t>
   </si>
   <si>
-    <t>Adem Sari Minuman</t>
+    <t>Adem Sari Minuman Ching ku</t>
   </si>
   <si>
     <t>Adem Sari Minuman Dus</t>
@@ -611,7 +611,7 @@
     <t>Racik Nasi Goreng - RC</t>
   </si>
   <si>
-    <t>Bawang Putih</t>
+    <t>Bawang Putih per 1/4kg</t>
   </si>
   <si>
     <t>Gula Aren 1/2kg</t>
@@ -1437,6 +1437,24 @@
   </si>
   <si>
     <t>Madu Rasa Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sambal Uleg Terasi </t>
+  </si>
+  <si>
+    <t>Sambal Uleg Terasi - RC</t>
+  </si>
+  <si>
+    <t>Permen Karet Big Babol Bungkus</t>
+  </si>
+  <si>
+    <t>Lilin</t>
+  </si>
+  <si>
+    <t>Lilin Pak</t>
+  </si>
+  <si>
+    <t>Teh Sisri</t>
   </si>
   <si>
     <t>Djarum Coklat SLOP</t>
@@ -2039,7 +2057,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A455" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A461" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -2245,7 +2263,7 @@
         <v>23</v>
       </c>
       <c r="D10" s="4">
-        <v>6500.0</v>
+        <v>7000.0</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -2253,7 +2271,9 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
-      <c r="K10" s="4"/>
+      <c r="K10" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4">
@@ -2435,10 +2455,14 @@
         <v>23</v>
       </c>
       <c r="D18" s="4">
-        <v>7000.0</v>
-      </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
+        <v>8000.0</v>
+      </c>
+      <c r="E18" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F18" s="4">
+        <v>35000.0</v>
+      </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
@@ -2459,7 +2483,7 @@
         <v>23</v>
       </c>
       <c r="D19" s="4">
-        <v>150000.0</v>
+        <v>160000.0</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
@@ -2716,7 +2740,7 @@
         <v>23</v>
       </c>
       <c r="D29" s="4">
-        <v>80000.0</v>
+        <v>82000.0</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
@@ -6456,7 +6480,7 @@
         <v>147</v>
       </c>
       <c r="D184" s="4">
-        <v>5000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E184" s="6"/>
       <c r="F184" s="6"/>
@@ -8586,7 +8610,9 @@
       <c r="H268" s="7"/>
       <c r="I268" s="7"/>
       <c r="J268" s="7"/>
-      <c r="K268" s="4"/>
+      <c r="K268" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="4">
@@ -8608,7 +8634,9 @@
       <c r="H269" s="7"/>
       <c r="I269" s="7"/>
       <c r="J269" s="7"/>
-      <c r="K269" s="4"/>
+      <c r="K269" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="4">
@@ -8886,7 +8914,9 @@
       <c r="H280" s="7"/>
       <c r="I280" s="7"/>
       <c r="J280" s="7"/>
-      <c r="K280" s="4"/>
+      <c r="K280" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="4">
@@ -9358,12 +9388,8 @@
       <c r="D300" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E300" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F300" s="4">
-        <v>7500.0</v>
-      </c>
+      <c r="E300" s="4"/>
+      <c r="F300" s="4"/>
       <c r="G300" s="7"/>
       <c r="H300" s="7"/>
       <c r="I300" s="7"/>
@@ -9410,12 +9436,8 @@
       <c r="D302" s="4">
         <v>2500.0</v>
       </c>
-      <c r="E302" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F302" s="4">
-        <v>9000.0</v>
-      </c>
+      <c r="E302" s="4"/>
+      <c r="F302" s="4"/>
       <c r="G302" s="7"/>
       <c r="H302" s="7"/>
       <c r="I302" s="7"/>
@@ -9436,7 +9458,7 @@
         <v>309</v>
       </c>
       <c r="D303" s="4">
-        <v>9000.0</v>
+        <v>9500.0</v>
       </c>
       <c r="E303" s="4"/>
       <c r="F303" s="4"/>
@@ -9462,12 +9484,8 @@
       <c r="D304" s="4">
         <v>2000.0</v>
       </c>
-      <c r="E304" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="F304" s="4">
-        <v>7500.0</v>
-      </c>
+      <c r="E304" s="4"/>
+      <c r="F304" s="4"/>
       <c r="G304" s="7"/>
       <c r="H304" s="7"/>
       <c r="I304" s="7"/>
@@ -9490,8 +9508,8 @@
       <c r="D305" s="4">
         <v>7500.0</v>
       </c>
-      <c r="E305" s="7"/>
-      <c r="F305" s="7"/>
+      <c r="E305" s="4"/>
+      <c r="F305" s="4"/>
       <c r="G305" s="7"/>
       <c r="H305" s="7"/>
       <c r="I305" s="7"/>
@@ -13145,82 +13163,152 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="20"/>
-      <c r="B456" s="20"/>
-      <c r="C456" s="20"/>
-      <c r="D456" s="18"/>
+      <c r="A456" s="4">
+        <f t="shared" si="1"/>
+        <v>455</v>
+      </c>
+      <c r="B456" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="C456" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D456" s="17">
+        <v>2000.0</v>
+      </c>
       <c r="E456" s="18"/>
       <c r="F456" s="18"/>
       <c r="G456" s="18"/>
       <c r="H456" s="18"/>
       <c r="I456" s="18"/>
       <c r="J456" s="18"/>
-      <c r="K456" s="18"/>
+      <c r="K456" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="457">
-      <c r="A457" s="20"/>
-      <c r="B457" s="20"/>
-      <c r="C457" s="20"/>
-      <c r="D457" s="18"/>
+      <c r="A457" s="4">
+        <f t="shared" si="1"/>
+        <v>456</v>
+      </c>
+      <c r="B457" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="C457" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D457" s="17">
+        <v>13000.0</v>
+      </c>
       <c r="E457" s="18"/>
       <c r="F457" s="18"/>
       <c r="G457" s="18"/>
       <c r="H457" s="18"/>
       <c r="I457" s="18"/>
       <c r="J457" s="18"/>
-      <c r="K457" s="18"/>
+      <c r="K457" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="458">
-      <c r="A458" s="20"/>
-      <c r="B458" s="20"/>
-      <c r="C458" s="20"/>
-      <c r="D458" s="18"/>
+      <c r="A458" s="4">
+        <f t="shared" si="1"/>
+        <v>457</v>
+      </c>
+      <c r="B458" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="C458" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D458" s="17">
+        <v>11000.0</v>
+      </c>
       <c r="E458" s="18"/>
       <c r="F458" s="18"/>
       <c r="G458" s="18"/>
       <c r="H458" s="18"/>
       <c r="I458" s="18"/>
       <c r="J458" s="18"/>
-      <c r="K458" s="18"/>
+      <c r="K458" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="459">
-      <c r="A459" s="20"/>
-      <c r="B459" s="20"/>
-      <c r="C459" s="20"/>
-      <c r="D459" s="18"/>
-      <c r="E459" s="18"/>
-      <c r="F459" s="18"/>
+      <c r="A459" s="4">
+        <f t="shared" si="1"/>
+        <v>458</v>
+      </c>
+      <c r="B459" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="C459" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D459" s="17">
+        <v>2000.0</v>
+      </c>
+      <c r="E459" s="17">
+        <v>3.0</v>
+      </c>
+      <c r="F459" s="17">
+        <v>5000.0</v>
+      </c>
       <c r="G459" s="18"/>
       <c r="H459" s="18"/>
       <c r="I459" s="18"/>
       <c r="J459" s="18"/>
-      <c r="K459" s="18"/>
+      <c r="K459" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="460">
-      <c r="A460" s="20"/>
-      <c r="B460" s="20"/>
-      <c r="C460" s="20"/>
-      <c r="D460" s="18"/>
+      <c r="A460" s="4">
+        <f t="shared" si="1"/>
+        <v>459</v>
+      </c>
+      <c r="B460" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="C460" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D460" s="17">
+        <v>10000.0</v>
+      </c>
       <c r="E460" s="18"/>
       <c r="F460" s="18"/>
       <c r="G460" s="18"/>
       <c r="H460" s="18"/>
       <c r="I460" s="18"/>
       <c r="J460" s="18"/>
-      <c r="K460" s="18"/>
+      <c r="K460" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="461">
-      <c r="A461" s="20"/>
-      <c r="B461" s="20"/>
-      <c r="C461" s="20"/>
-      <c r="D461" s="18"/>
+      <c r="A461" s="4">
+        <f t="shared" si="1"/>
+        <v>460</v>
+      </c>
+      <c r="B461" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="C461" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D461" s="17">
+        <v>3500.0</v>
+      </c>
       <c r="E461" s="18"/>
       <c r="F461" s="18"/>
       <c r="G461" s="18"/>
       <c r="H461" s="18"/>
       <c r="I461" s="18"/>
       <c r="J461" s="18"/>
-      <c r="K461" s="18"/>
+      <c r="K461" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="20"/>
@@ -23155,7 +23243,7 @@
       <c r="K1225" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="$B$1:$C$455"/>
+  <autoFilter ref="$B$1:$C$456"/>
   <conditionalFormatting sqref="B443">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>isodd(row())</formula>
@@ -23167,10 +23255,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C455">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C461">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K455">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K461">
       <formula1>"Ecer,KRT"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23231,7 +23319,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="str">
-        <f t="shared" ref="A2:A84" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
+        <f t="shared" ref="A2:A86" si="1">CONCATENATE("GROSIR", ROW()-1)</f>
         <v>GROSIR1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -23257,7 +23345,7 @@
         <v>GROSIR2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="4">
@@ -23279,7 +23367,7 @@
         <v>GROSIR3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4">
@@ -23301,7 +23389,7 @@
         <v>GROSIR4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="4">
@@ -23345,7 +23433,7 @@
         <v>GROSIR6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4">
@@ -23389,7 +23477,7 @@
         <v>GROSIR8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4">
@@ -23433,7 +23521,7 @@
         <v>GROSIR10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="4">
@@ -23477,7 +23565,7 @@
         <v>GROSIR12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4">
@@ -23499,7 +23587,7 @@
         <v>GROSIR13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4">
@@ -23543,7 +23631,7 @@
         <v>GROSIR15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4">
@@ -23565,7 +23653,7 @@
         <v>GROSIR16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4">
@@ -23587,7 +23675,7 @@
         <v>GROSIR17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="4">
@@ -23653,7 +23741,7 @@
         <v>GROSIR20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4">
@@ -23675,7 +23763,7 @@
         <v>GROSIR21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4">
@@ -23697,7 +23785,7 @@
         <v>GROSIR22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="4">
@@ -23763,7 +23851,7 @@
         <v>GROSIR25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="4">
@@ -23785,7 +23873,7 @@
         <v>GROSIR26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="4">
@@ -23807,7 +23895,7 @@
         <v>GROSIR27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="4">
@@ -23829,7 +23917,7 @@
         <v>GROSIR28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="4">
@@ -23851,7 +23939,7 @@
         <v>GROSIR29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="4">
@@ -23873,7 +23961,7 @@
         <v>GROSIR30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="4">
@@ -23895,7 +23983,7 @@
         <v>GROSIR31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="4">
@@ -23917,7 +24005,7 @@
         <v>GROSIR32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="4">
@@ -23961,7 +24049,7 @@
         <v>GROSIR34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="4">
@@ -23983,7 +24071,7 @@
         <v>GROSIR35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="4">
@@ -24005,7 +24093,7 @@
         <v>GROSIR36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="4">
@@ -24027,7 +24115,7 @@
         <v>GROSIR37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4">
@@ -24049,7 +24137,7 @@
         <v>GROSIR38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="4">
@@ -24071,7 +24159,7 @@
         <v>GROSIR39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="4">
@@ -24093,7 +24181,7 @@
         <v>GROSIR40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="4">
@@ -24115,7 +24203,7 @@
         <v>GROSIR41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="4">
@@ -24159,7 +24247,7 @@
         <v>GROSIR43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="4">
@@ -24203,7 +24291,7 @@
         <v>GROSIR45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="4">
@@ -24247,7 +24335,7 @@
         <v>GROSIR47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="4">
@@ -24291,7 +24379,7 @@
         <v>GROSIR49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="4">
@@ -24313,7 +24401,7 @@
         <v>GROSIR50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="4">
@@ -24335,7 +24423,7 @@
         <v>GROSIR51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="4">
@@ -24357,7 +24445,7 @@
         <v>GROSIR52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="4">
@@ -24379,7 +24467,7 @@
         <v>GROSIR53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="4">
@@ -24401,7 +24489,7 @@
         <v>GROSIR54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="4">
@@ -24423,7 +24511,7 @@
         <v>GROSIR55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="4">
@@ -24445,7 +24533,7 @@
         <v>GROSIR56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="4">
@@ -24467,7 +24555,7 @@
         <v>GROSIR57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="4">
@@ -24489,7 +24577,7 @@
         <v>GROSIR58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="4">
@@ -24511,7 +24599,7 @@
         <v>GROSIR59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="4">
@@ -24533,7 +24621,7 @@
         <v>GROSIR60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="4">
@@ -24555,7 +24643,7 @@
         <v>GROSIR61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="4">
@@ -24577,7 +24665,7 @@
         <v>GROSIR62</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="4">
@@ -24621,7 +24709,7 @@
         <v>GROSIR64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="4">
@@ -24731,7 +24819,7 @@
         <v>GROSIR69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C70" s="5"/>
       <c r="D70" s="4">
@@ -24753,7 +24841,7 @@
         <v>GROSIR70</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C71" s="5"/>
       <c r="D71" s="4">
@@ -24775,7 +24863,7 @@
         <v>GROSIR71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="4">
@@ -24841,7 +24929,7 @@
         <v>GROSIR74</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="4">
@@ -24863,7 +24951,7 @@
         <v>GROSIR75</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C76" s="5"/>
       <c r="D76" s="4">
@@ -24885,7 +24973,7 @@
         <v>GROSIR76</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="C77" s="5"/>
       <c r="D77" s="4">
@@ -24907,7 +24995,7 @@
         <v>GROSIR77</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="C78" s="5"/>
       <c r="D78" s="4">
@@ -24929,7 +25017,7 @@
         <v>GROSIR78</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="C79" s="5"/>
       <c r="D79" s="4">
@@ -24951,7 +25039,7 @@
         <v>GROSIR79</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="C80" s="5"/>
       <c r="D80" s="4">
@@ -24973,7 +25061,7 @@
         <v>GROSIR80</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C81" s="5"/>
       <c r="D81" s="4">
@@ -25041,7 +25129,7 @@
         <v>GROSIR83</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C84" s="5"/>
       <c r="D84" s="4">
@@ -25058,30 +25146,52 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="4"/>
+      <c r="A85" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR84</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D85" s="4">
+        <v>7000.0</v>
+      </c>
       <c r="E85" s="22"/>
       <c r="F85" s="22"/>
       <c r="G85" s="22"/>
       <c r="H85" s="22"/>
       <c r="I85" s="22"/>
       <c r="J85" s="22"/>
-      <c r="K85" s="22"/>
+      <c r="K85" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="4"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="5"/>
-      <c r="D86" s="4"/>
+      <c r="A86" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>GROSIR85</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D86" s="4">
+        <v>8500.0</v>
+      </c>
       <c r="E86" s="22"/>
       <c r="F86" s="22"/>
       <c r="G86" s="22"/>
       <c r="H86" s="22"/>
       <c r="I86" s="22"/>
       <c r="J86" s="22"/>
-      <c r="K86" s="22"/>
+      <c r="K86" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4"/>
@@ -38052,10 +38162,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C82">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C82 C85:C86">
       <formula1>"Beras,Dapur,Kamar Mandi,Korek,Lainya,MIE,Minuman,Obat,Popok,Rokok,Seduh,Mie Seduh"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K84">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K86">
       <formula1>"Ecer,KRT"</formula1>
     </dataValidation>
   </dataValidations>

--- a/TokoYakin.xlsx
+++ b/TokoYakin.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="Grosir" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$456</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Biasa!$B$1:$C$457</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Grosir!$B$1:$C$263</definedName>
   </definedNames>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1599" uniqueCount="546">
   <si>
     <t>Ba- RCode</t>
   </si>
@@ -935,12 +935,15 @@
     <t>Mie Burung Dara</t>
   </si>
   <si>
+    <t>Beras Lahap</t>
+  </si>
+  <si>
+    <t>Beras</t>
+  </si>
+  <si>
     <t>Beras Sedap Wangi 5kg per Bungkus</t>
   </si>
   <si>
-    <t>Beras</t>
-  </si>
-  <si>
     <t>Charm extra maxi wing</t>
   </si>
   <si>
@@ -1430,7 +1433,7 @@
     <t>Sabun Dettol</t>
   </si>
   <si>
-    <t>Gas Melon</t>
+    <t>Gas 3kg</t>
   </si>
   <si>
     <t xml:space="preserve">Madu Rasa </t>
@@ -1455,6 +1458,24 @@
   </si>
   <si>
     <t>Teh Sisri</t>
+  </si>
+  <si>
+    <t>Hexos</t>
+  </si>
+  <si>
+    <t>Fresh tea 350</t>
+  </si>
+  <si>
+    <t>Fresh tea 350 KRT</t>
+  </si>
+  <si>
+    <t>Nutri boost</t>
+  </si>
+  <si>
+    <t>Nutri boost KRT</t>
+  </si>
+  <si>
+    <t>Magnum Kretek</t>
   </si>
   <si>
     <t>Djarum Coklat SLOP</t>
@@ -2057,7 +2078,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A461" si="1">ROW()-1</f>
+        <f t="shared" ref="A2:A468" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -9122,7 +9143,7 @@
         <v>307</v>
       </c>
       <c r="D289" s="4">
-        <v>80000.0</v>
+        <v>82000.0</v>
       </c>
       <c r="E289" s="6"/>
       <c r="F289" s="6"/>
@@ -9131,7 +9152,7 @@
       <c r="I289" s="6"/>
       <c r="J289" s="6"/>
       <c r="K289" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="290">
@@ -9140,20 +9161,20 @@
         <v>289</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C290" s="5" t="s">
         <v>307</v>
       </c>
       <c r="D290" s="4">
-        <v>14000.0</v>
-      </c>
-      <c r="E290" s="7"/>
-      <c r="F290" s="7"/>
-      <c r="G290" s="7"/>
-      <c r="H290" s="7"/>
-      <c r="I290" s="7"/>
-      <c r="J290" s="7"/>
+        <v>80000.0</v>
+      </c>
+      <c r="E290" s="6"/>
+      <c r="F290" s="6"/>
+      <c r="G290" s="6"/>
+      <c r="H290" s="6"/>
+      <c r="I290" s="6"/>
+      <c r="J290" s="6"/>
       <c r="K290" s="4" t="s">
         <v>13</v>
       </c>
@@ -9170,7 +9191,7 @@
         <v>307</v>
       </c>
       <c r="D291" s="4">
-        <v>14500.0</v>
+        <v>14000.0</v>
       </c>
       <c r="E291" s="7"/>
       <c r="F291" s="7"/>
@@ -9194,7 +9215,7 @@
         <v>307</v>
       </c>
       <c r="D292" s="4">
-        <v>15000.0</v>
+        <v>14500.0</v>
       </c>
       <c r="E292" s="7"/>
       <c r="F292" s="7"/>
@@ -9218,7 +9239,7 @@
         <v>307</v>
       </c>
       <c r="D293" s="4">
-        <v>15500.0</v>
+        <v>15000.0</v>
       </c>
       <c r="E293" s="7"/>
       <c r="F293" s="7"/>
@@ -9236,13 +9257,13 @@
         <v>293</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D294" s="4">
-        <v>1500.0</v>
+        <v>15500.0</v>
       </c>
       <c r="E294" s="7"/>
       <c r="F294" s="7"/>
@@ -9260,13 +9281,13 @@
         <v>294</v>
       </c>
       <c r="B295" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C295" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="C295" s="5" t="s">
-        <v>309</v>
-      </c>
       <c r="D295" s="4">
-        <v>12500.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E295" s="7"/>
       <c r="F295" s="7"/>
@@ -9275,7 +9296,7 @@
       <c r="I295" s="7"/>
       <c r="J295" s="7"/>
       <c r="K295" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="296">
@@ -9287,10 +9308,10 @@
         <v>311</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D296" s="4">
-        <v>500.0</v>
+        <v>12500.0</v>
       </c>
       <c r="E296" s="7"/>
       <c r="F296" s="7"/>
@@ -9299,7 +9320,7 @@
       <c r="I296" s="7"/>
       <c r="J296" s="7"/>
       <c r="K296" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="297">
@@ -9311,10 +9332,10 @@
         <v>312</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D297" s="4">
-        <v>4500.0</v>
+        <v>500.0</v>
       </c>
       <c r="E297" s="7"/>
       <c r="F297" s="7"/>
@@ -9323,7 +9344,7 @@
       <c r="I297" s="7"/>
       <c r="J297" s="7"/>
       <c r="K297" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="298">
@@ -9335,10 +9356,10 @@
         <v>313</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D298" s="4">
-        <v>3000.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E298" s="7"/>
       <c r="F298" s="7"/>
@@ -9347,7 +9368,7 @@
       <c r="I298" s="7"/>
       <c r="J298" s="7"/>
       <c r="K298" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="299">
@@ -9359,10 +9380,10 @@
         <v>314</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D299" s="4">
-        <v>23000.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E299" s="7"/>
       <c r="F299" s="7"/>
@@ -9371,7 +9392,7 @@
       <c r="I299" s="7"/>
       <c r="J299" s="7"/>
       <c r="K299" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="300">
@@ -9383,19 +9404,19 @@
         <v>315</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D300" s="4">
-        <v>2000.0</v>
-      </c>
-      <c r="E300" s="4"/>
-      <c r="F300" s="4"/>
+        <v>23000.0</v>
+      </c>
+      <c r="E300" s="7"/>
+      <c r="F300" s="7"/>
       <c r="G300" s="7"/>
       <c r="H300" s="7"/>
       <c r="I300" s="7"/>
       <c r="J300" s="7"/>
       <c r="K300" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="301">
@@ -9407,10 +9428,10 @@
         <v>316</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D301" s="4">
-        <v>7500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E301" s="4"/>
       <c r="F301" s="4"/>
@@ -9419,7 +9440,7 @@
       <c r="I301" s="7"/>
       <c r="J301" s="7"/>
       <c r="K301" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="302">
@@ -9431,10 +9452,10 @@
         <v>317</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D302" s="4">
-        <v>2500.0</v>
+        <v>7500.0</v>
       </c>
       <c r="E302" s="4"/>
       <c r="F302" s="4"/>
@@ -9443,7 +9464,7 @@
       <c r="I302" s="7"/>
       <c r="J302" s="7"/>
       <c r="K302" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="303">
@@ -9455,10 +9476,10 @@
         <v>318</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D303" s="4">
-        <v>9500.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E303" s="4"/>
       <c r="F303" s="4"/>
@@ -9467,7 +9488,7 @@
       <c r="I303" s="7"/>
       <c r="J303" s="7"/>
       <c r="K303" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="304">
@@ -9479,10 +9500,10 @@
         <v>319</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D304" s="4">
-        <v>2000.0</v>
+        <v>9500.0</v>
       </c>
       <c r="E304" s="4"/>
       <c r="F304" s="4"/>
@@ -9491,7 +9512,7 @@
       <c r="I304" s="7"/>
       <c r="J304" s="7"/>
       <c r="K304" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="305">
@@ -9503,10 +9524,10 @@
         <v>320</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D305" s="4">
-        <v>7500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E305" s="4"/>
       <c r="F305" s="4"/>
@@ -9515,7 +9536,7 @@
       <c r="I305" s="7"/>
       <c r="J305" s="7"/>
       <c r="K305" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="306">
@@ -9527,19 +9548,19 @@
         <v>321</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="D306" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="E306" s="7"/>
-      <c r="F306" s="7"/>
+        <v>7500.0</v>
+      </c>
+      <c r="E306" s="4"/>
+      <c r="F306" s="4"/>
       <c r="G306" s="7"/>
       <c r="H306" s="7"/>
       <c r="I306" s="7"/>
       <c r="J306" s="7"/>
       <c r="K306" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="307">
@@ -9548,13 +9569,13 @@
         <v>306</v>
       </c>
       <c r="B307" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C307" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="C307" s="5" t="s">
-        <v>322</v>
-      </c>
       <c r="D307" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E307" s="7"/>
       <c r="F307" s="7"/>
@@ -9563,7 +9584,7 @@
       <c r="I307" s="7"/>
       <c r="J307" s="7"/>
       <c r="K307" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="308">
@@ -9575,10 +9596,10 @@
         <v>324</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D308" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E308" s="7"/>
       <c r="F308" s="7"/>
@@ -9587,7 +9608,7 @@
       <c r="I308" s="7"/>
       <c r="J308" s="7"/>
       <c r="K308" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="309">
@@ -9599,10 +9620,10 @@
         <v>325</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D309" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E309" s="7"/>
       <c r="F309" s="7"/>
@@ -9611,7 +9632,7 @@
       <c r="I309" s="7"/>
       <c r="J309" s="7"/>
       <c r="K309" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="310">
@@ -9623,10 +9644,10 @@
         <v>326</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D310" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E310" s="7"/>
       <c r="F310" s="7"/>
@@ -9635,7 +9656,7 @@
       <c r="I310" s="7"/>
       <c r="J310" s="7"/>
       <c r="K310" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="311">
@@ -9647,10 +9668,10 @@
         <v>327</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D311" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E311" s="7"/>
       <c r="F311" s="7"/>
@@ -9659,7 +9680,7 @@
       <c r="I311" s="7"/>
       <c r="J311" s="7"/>
       <c r="K311" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="312">
@@ -9671,10 +9692,10 @@
         <v>328</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D312" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E312" s="7"/>
       <c r="F312" s="7"/>
@@ -9683,7 +9704,7 @@
       <c r="I312" s="7"/>
       <c r="J312" s="7"/>
       <c r="K312" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="313">
@@ -9695,10 +9716,10 @@
         <v>329</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D313" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E313" s="7"/>
       <c r="F313" s="7"/>
@@ -9707,7 +9728,7 @@
       <c r="I313" s="7"/>
       <c r="J313" s="7"/>
       <c r="K313" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="314">
@@ -9719,10 +9740,10 @@
         <v>330</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D314" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E314" s="7"/>
       <c r="F314" s="7"/>
@@ -9731,7 +9752,7 @@
       <c r="I314" s="7"/>
       <c r="J314" s="7"/>
       <c r="K314" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="315">
@@ -9743,10 +9764,10 @@
         <v>331</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D315" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E315" s="7"/>
       <c r="F315" s="7"/>
@@ -9755,7 +9776,7 @@
       <c r="I315" s="7"/>
       <c r="J315" s="7"/>
       <c r="K315" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="316">
@@ -9767,10 +9788,10 @@
         <v>332</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D316" s="4">
-        <v>1000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E316" s="7"/>
       <c r="F316" s="7"/>
@@ -9779,7 +9800,7 @@
       <c r="I316" s="7"/>
       <c r="J316" s="7"/>
       <c r="K316" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="317">
@@ -9791,10 +9812,10 @@
         <v>333</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D317" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E317" s="7"/>
       <c r="F317" s="7"/>
@@ -9803,7 +9824,7 @@
       <c r="I317" s="7"/>
       <c r="J317" s="7"/>
       <c r="K317" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="318">
@@ -9815,7 +9836,7 @@
         <v>334</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D318" s="4">
         <v>10000.0</v>
@@ -9827,7 +9848,7 @@
       <c r="I318" s="7"/>
       <c r="J318" s="7"/>
       <c r="K318" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="319">
@@ -9839,10 +9860,10 @@
         <v>335</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D319" s="4">
-        <v>500.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E319" s="7"/>
       <c r="F319" s="7"/>
@@ -9863,10 +9884,10 @@
         <v>336</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D320" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E320" s="7"/>
       <c r="F320" s="7"/>
@@ -9875,7 +9896,7 @@
       <c r="I320" s="7"/>
       <c r="J320" s="7"/>
       <c r="K320" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="321">
@@ -9887,10 +9908,10 @@
         <v>337</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D321" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E321" s="7"/>
       <c r="F321" s="7"/>
@@ -9899,7 +9920,7 @@
       <c r="I321" s="7"/>
       <c r="J321" s="7"/>
       <c r="K321" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="322">
@@ -9911,10 +9932,10 @@
         <v>338</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D322" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E322" s="7"/>
       <c r="F322" s="7"/>
@@ -9923,7 +9944,7 @@
       <c r="I322" s="7"/>
       <c r="J322" s="7"/>
       <c r="K322" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="323">
@@ -9935,10 +9956,10 @@
         <v>339</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D323" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E323" s="7"/>
       <c r="F323" s="7"/>
@@ -9947,7 +9968,7 @@
       <c r="I323" s="7"/>
       <c r="J323" s="7"/>
       <c r="K323" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="324">
@@ -9959,10 +9980,10 @@
         <v>340</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D324" s="4">
-        <v>10000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E324" s="7"/>
       <c r="F324" s="7"/>
@@ -9971,7 +9992,7 @@
       <c r="I324" s="7"/>
       <c r="J324" s="7"/>
       <c r="K324" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="325">
@@ -9983,10 +10004,10 @@
         <v>341</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D325" s="4">
-        <v>2000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="E325" s="7"/>
       <c r="F325" s="7"/>
@@ -9995,7 +10016,7 @@
       <c r="I325" s="7"/>
       <c r="J325" s="7"/>
       <c r="K325" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="326">
@@ -10007,10 +10028,10 @@
         <v>342</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D326" s="4">
-        <v>5000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="E326" s="7"/>
       <c r="F326" s="7"/>
@@ -10031,10 +10052,10 @@
         <v>343</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D327" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E327" s="7"/>
       <c r="F327" s="7"/>
@@ -10055,10 +10076,10 @@
         <v>344</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D328" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E328" s="7"/>
       <c r="F328" s="7"/>
@@ -10067,7 +10088,7 @@
       <c r="I328" s="7"/>
       <c r="J328" s="7"/>
       <c r="K328" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="329">
@@ -10079,10 +10100,10 @@
         <v>345</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D329" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E329" s="7"/>
       <c r="F329" s="7"/>
@@ -10091,7 +10112,7 @@
       <c r="I329" s="7"/>
       <c r="J329" s="7"/>
       <c r="K329" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="330">
@@ -10103,10 +10124,10 @@
         <v>346</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D330" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E330" s="7"/>
       <c r="F330" s="7"/>
@@ -10115,7 +10136,7 @@
       <c r="I330" s="7"/>
       <c r="J330" s="7"/>
       <c r="K330" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="331">
@@ -10127,10 +10148,10 @@
         <v>347</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D331" s="4">
-        <v>1000.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E331" s="7"/>
       <c r="F331" s="7"/>
@@ -10139,7 +10160,7 @@
       <c r="I331" s="7"/>
       <c r="J331" s="7"/>
       <c r="K331" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="332">
@@ -10151,10 +10172,10 @@
         <v>348</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D332" s="4">
-        <v>5000.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E332" s="7"/>
       <c r="F332" s="7"/>
@@ -10163,7 +10184,7 @@
       <c r="I332" s="7"/>
       <c r="J332" s="7"/>
       <c r="K332" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="333">
@@ -10175,10 +10196,10 @@
         <v>349</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D333" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E333" s="7"/>
       <c r="F333" s="7"/>
@@ -10187,7 +10208,7 @@
       <c r="I333" s="7"/>
       <c r="J333" s="7"/>
       <c r="K333" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="334">
@@ -10199,7 +10220,7 @@
         <v>350</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D334" s="4">
         <v>500.0</v>
@@ -10223,10 +10244,10 @@
         <v>351</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D335" s="4">
-        <v>5000.0</v>
+        <v>500.0</v>
       </c>
       <c r="E335" s="7"/>
       <c r="F335" s="7"/>
@@ -10235,7 +10256,7 @@
       <c r="I335" s="7"/>
       <c r="J335" s="7"/>
       <c r="K335" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="336">
@@ -10247,7 +10268,7 @@
         <v>352</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D336" s="4">
         <v>5000.0</v>
@@ -10271,10 +10292,10 @@
         <v>353</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D337" s="4">
-        <v>500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="E337" s="7"/>
       <c r="F337" s="7"/>
@@ -10283,7 +10304,7 @@
       <c r="I337" s="7"/>
       <c r="J337" s="7"/>
       <c r="K337" s="4" t="s">
-        <